--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C10" s="77" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C14" s="76" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -2370,9 +2370,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C23" s="77" t="inlineStr">
-        <is>
-          <t>63%</t>
+      <c r="C23" s="78" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="C24" s="76" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="C25" s="77" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="C35" s="77" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C38" s="77" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C58" s="78" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="D58" s="23" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C60" s="78" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D60" s="23" t="inlineStr">
@@ -4330,9 +4330,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C61" s="76" t="inlineStr">
-        <is>
-          <t>46%</t>
+      <c r="C61" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D61" s="23" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C65" s="78" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D65" s="23" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="C66" s="78" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D66" s="23" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="C67" s="78" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D67" s="23" t="inlineStr">
@@ -4750,9 +4750,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C69" s="77" t="inlineStr">
-        <is>
-          <t>68%</t>
+      <c r="C69" s="78" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="D69" s="23" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C71" s="77" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="D71" s="23" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="C76" s="78" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="D76" s="23" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C79" s="78" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D79" s="23" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="C114" s="76" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="D114" s="23" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="C128" s="77" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="D128" s="23" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="C130" s="77" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="D130" s="23" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C132" s="77" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="D132" s="23" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="C134" s="77" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="D134" s="23" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="C135" s="77" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="D135" s="23" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C137" s="77" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D137" s="23" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="C138" s="78" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D138" s="23" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="C139" s="77" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D139" s="23" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C140" s="78" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D140" s="23" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="C149" s="77" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="D149" s="23" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="C153" s="77" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="D153" s="23" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="C154" s="77" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="D154" s="23" t="inlineStr">
@@ -9052,9 +9052,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C156" s="77" t="inlineStr">
-        <is>
-          <t>83%</t>
+      <c r="C156" s="78" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="D156" s="23" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="C157" s="77" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="D157" s="23" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="C160" s="78" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="D160" s="23" t="inlineStr">
@@ -9506,9 +9506,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C165" s="77" t="inlineStr">
-        <is>
-          <t>68%</t>
+      <c r="C165" s="78" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="D165" s="23" t="inlineStr">
@@ -9560,9 +9560,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C166" s="76" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="C166" s="77" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="D166" s="23" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="C184" s="77" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="D184" s="23" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C196" s="77" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="D196" s="23" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C197" s="78" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D197" s="23" t="inlineStr">
@@ -11362,9 +11362,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C201" s="76" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="C201" s="77" t="inlineStr">
+        <is>
+          <t>71%</t>
         </is>
       </c>
       <c r="D201" s="23" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C209" s="77" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D209" s="23" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="C210" s="77" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="D210" s="23" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="C228" s="76" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="D228" s="23" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C244" s="77" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="D244" s="23" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="C246" s="77" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="D246" s="23" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="C250" s="77" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="D250" s="23" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="C251" s="77" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="D251" s="23" t="inlineStr">
@@ -13970,9 +13970,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C252" s="77" t="inlineStr">
-        <is>
-          <t>81%</t>
+      <c r="C252" s="78" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D252" s="23" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="C257" s="77" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="D257" s="23" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="C258" s="76" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="D258" s="23" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="C260" s="77" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="D260" s="23" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="C262" s="76" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D262" s="23" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="C263" s="76" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="D263" s="23" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="C264" s="76" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D264" s="23" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="C265" s="76" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="D265" s="23" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="C266" s="76" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="D266" s="23" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C267" s="76" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="D267" s="23" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="C268" s="76" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="D268" s="23" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="C269" s="76" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="D269" s="23" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="C270" s="76" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="D270" s="23" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C271" s="76" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="D271" s="23" t="inlineStr">
@@ -15052,7 +15052,7 @@
       </c>
       <c r="C272" s="76" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="D272" s="23" t="inlineStr">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="C273" s="76" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="D273" s="23" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="C282" s="76" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="D282" s="23" t="inlineStr">

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -303,12 +303,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -518,6 +512,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,10 +524,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -542,19 +539,16 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -564,10 +558,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,21 +573,21 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -683,13 +677,10 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -707,10 +698,7 @@
     <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,13 +710,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -737,37 +719,37 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1175,17 +1157,17 @@
           <t>PS5 COMPLETION PLATFORM  |  BLOCKERS - sorted by blocking count</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="100" t="n"/>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="100" t="n"/>
-      <c r="J1" s="100" t="n"/>
-      <c r="K1" s="100" t="n"/>
-      <c r="L1" s="101" t="n"/>
+      <c r="B1" s="96" t="n"/>
+      <c r="C1" s="96" t="n"/>
+      <c r="D1" s="96" t="n"/>
+      <c r="E1" s="96" t="n"/>
+      <c r="F1" s="96" t="n"/>
+      <c r="G1" s="96" t="n"/>
+      <c r="H1" s="96" t="n"/>
+      <c r="I1" s="96" t="n"/>
+      <c r="J1" s="96" t="n"/>
+      <c r="K1" s="96" t="n"/>
+      <c r="L1" s="97" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1260,7 +1242,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="76" t="inlineStr">
+      <c r="C3" s="74" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -1285,11 +1267,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H3" s="65" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
+      <c r="H3" s="65" t="inlineStr"/>
       <c r="I3" s="65" t="inlineStr">
         <is>
           <t>54 IES (Local control switch not arrived) 
@@ -1305,7 +1283,7 @@
         </is>
       </c>
       <c r="K3" s="23" t="n"/>
-      <c r="L3" s="67" t="inlineStr"/>
+      <c r="L3" s="66" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="53" t="inlineStr">
@@ -1318,7 +1296,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C4" s="76" t="inlineStr">
+      <c r="C4" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1343,11 +1321,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H4" s="65" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="H4" s="65" t="inlineStr"/>
       <c r="I4" s="65" t="inlineStr">
         <is>
           <t>all material not arrived</t>
@@ -1359,7 +1333,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="n"/>
-      <c r="L4" s="67" t="inlineStr"/>
+      <c r="L4" s="66" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
@@ -1372,7 +1346,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C5" s="76" t="inlineStr">
+      <c r="C5" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1397,11 +1371,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="65" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="H5" s="65" t="inlineStr"/>
       <c r="I5" s="65" t="inlineStr">
         <is>
           <t>all material not arrived</t>
@@ -1413,7 +1383,7 @@
         </is>
       </c>
       <c r="K5" s="23" t="n"/>
-      <c r="L5" s="67" t="inlineStr"/>
+      <c r="L5" s="66" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="53" t="inlineStr">
@@ -1426,7 +1396,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C6" s="76" t="inlineStr">
+      <c r="C6" s="74" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -1451,11 +1421,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H6" s="65" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+      <c r="H6" s="65" t="inlineStr"/>
       <c r="I6" s="65" t="inlineStr">
         <is>
           <t>cannot start termination due to unavailabiity of gland plate sketch.
@@ -1473,7 +1439,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="n"/>
-      <c r="L6" s="67" t="inlineStr"/>
+      <c r="L6" s="66" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="53" t="inlineStr">
@@ -1486,7 +1452,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C7" s="77" t="inlineStr">
+      <c r="C7" s="75" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -1511,11 +1477,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H7" s="65" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="H7" s="65" t="inlineStr"/>
       <c r="I7" s="65" t="inlineStr">
         <is>
           <t>cable drum not available for 24 cables, added in Rev09of cable schedule.
@@ -1529,7 +1491,7 @@
         </is>
       </c>
       <c r="K7" s="23" t="n"/>
-      <c r="L7" s="67" t="inlineStr"/>
+      <c r="L7" s="66" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="53" t="inlineStr">
@@ -1542,7 +1504,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="76" t="inlineStr">
+      <c r="C8" s="74" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -1567,14 +1529,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H8" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H8" s="65" t="inlineStr"/>
       <c r="I8" s="65" t="inlineStr">
         <is>
-          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -1583,7 +1541,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="n"/>
-      <c r="L8" s="67" t="inlineStr"/>
+      <c r="L8" s="66" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="53" t="inlineStr">
@@ -1596,7 +1554,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C9" s="77" t="inlineStr">
+      <c r="C9" s="75" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -1621,11 +1579,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H9" s="65" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+      <c r="H9" s="65" t="inlineStr"/>
       <c r="I9" s="65" t="inlineStr">
         <is>
           <t>Lugs not available, nut bolts not available</t>
@@ -1637,7 +1591,7 @@
         </is>
       </c>
       <c r="K9" s="23" t="n"/>
-      <c r="L9" s="67" t="inlineStr"/>
+      <c r="L9" s="66" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="53" t="inlineStr">
@@ -1650,7 +1604,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C10" s="77" t="inlineStr">
+      <c r="C10" s="75" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -1675,11 +1629,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H10" s="65" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="H10" s="65" t="inlineStr"/>
       <c r="I10" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BI-0001A-CC01 12P X 0.75 OS FL RTD 20m
@@ -1711,7 +1661,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="n"/>
-      <c r="L10" s="67" t="inlineStr"/>
+      <c r="L10" s="66" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="53" t="inlineStr">
@@ -1724,7 +1674,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C11" s="76" t="inlineStr">
+      <c r="C11" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1749,11 +1699,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H11" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H11" s="65" t="inlineStr"/>
       <c r="I11" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -1765,7 +1711,7 @@
         </is>
       </c>
       <c r="K11" s="23" t="n"/>
-      <c r="L11" s="67" t="inlineStr"/>
+      <c r="L11" s="66" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="53" t="inlineStr">
@@ -1778,7 +1724,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C12" s="76" t="inlineStr">
+      <c r="C12" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1803,11 +1749,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H12" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H12" s="65" t="inlineStr"/>
       <c r="I12" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -1819,7 +1761,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="n"/>
-      <c r="L12" s="67" t="inlineStr"/>
+      <c r="L12" s="66" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="53" t="inlineStr">
@@ -1832,7 +1774,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C13" s="77" t="inlineStr">
+      <c r="C13" s="75" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -1857,11 +1799,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H13" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="H13" s="65" t="inlineStr"/>
       <c r="I13" s="65" t="inlineStr">
         <is>
           <t>Fiber optic cables cannot be terminated due to drawing issues
@@ -1875,7 +1813,7 @@
         </is>
       </c>
       <c r="K13" s="23" t="n"/>
-      <c r="L13" s="67" t="inlineStr"/>
+      <c r="L13" s="66" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="53" t="inlineStr">
@@ -1888,7 +1826,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C14" s="76" t="inlineStr">
+      <c r="C14" s="74" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -1913,15 +1851,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H14" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H14" s="65" t="inlineStr"/>
       <c r="I14" s="65" t="inlineStr"/>
       <c r="J14" s="23" t="inlineStr"/>
       <c r="K14" s="23" t="n"/>
-      <c r="L14" s="67" t="inlineStr"/>
+      <c r="L14" s="66" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="53" t="inlineStr">
@@ -1934,7 +1868,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C15" s="76" t="inlineStr">
+      <c r="C15" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1959,11 +1893,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H15" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H15" s="65" t="inlineStr"/>
       <c r="I15" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -1975,7 +1905,7 @@
         </is>
       </c>
       <c r="K15" s="23" t="n"/>
-      <c r="L15" s="67" t="inlineStr"/>
+      <c r="L15" s="66" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="53" t="inlineStr">
@@ -1988,7 +1918,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C16" s="78" t="inlineStr">
+      <c r="C16" s="76" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -2013,11 +1943,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H16" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H16" s="65" t="inlineStr"/>
       <c r="I16" s="65" t="inlineStr">
         <is>
           <t>Nut bolts not available for  termination in busbar
@@ -2031,7 +1957,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="n"/>
-      <c r="L16" s="67" t="inlineStr"/>
+      <c r="L16" s="66" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="53" t="inlineStr">
@@ -2044,7 +1970,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="77" t="inlineStr">
+      <c r="C17" s="75" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -2069,11 +1995,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H17" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="H17" s="65" t="inlineStr"/>
       <c r="I17" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BE-0005-CL01 4C+E 16 210m , PS5-71-BE-0005-CL02 2C+E 2.5 210m ,   PS5-71-BE-0005-CL03 4C+E 6 210m
@@ -2087,7 +2009,7 @@
         </is>
       </c>
       <c r="K17" s="23" t="n"/>
-      <c r="L17" s="67" t="inlineStr"/>
+      <c r="L17" s="66" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="53" t="inlineStr">
@@ -2100,7 +2022,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C18" s="78" t="inlineStr">
+      <c r="C18" s="76" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -2125,11 +2047,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H18" s="65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="H18" s="65" t="inlineStr"/>
       <c r="I18" s="65" t="inlineStr">
         <is>
           <t>PS5-03-GDIR-1101, PS5-03-GDIR-1102, PS5-03-GDIR-1103, PS5-03-GDIR-1104, PS5-03-GDIR-1106, PS5-03-GDIR-1107, PS5-03-GDIR-1108, PS5-03-GDIR-1109 INSTRUMENT Not arrived</t>
@@ -2141,7 +2059,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="n"/>
-      <c r="L18" s="67" t="inlineStr"/>
+      <c r="L18" s="66" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="53" t="inlineStr">
@@ -2154,7 +2072,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C19" s="76" t="inlineStr">
+      <c r="C19" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2179,11 +2097,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H19" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H19" s="65" t="inlineStr"/>
       <c r="I19" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-1501/1502/1503 not arrived</t>
@@ -2195,7 +2109,7 @@
         </is>
       </c>
       <c r="K19" s="23" t="n"/>
-      <c r="L19" s="67" t="inlineStr"/>
+      <c r="L19" s="66" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="53" t="inlineStr">
@@ -2208,7 +2122,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C20" s="76" t="inlineStr">
+      <c r="C20" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2233,11 +2147,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H20" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H20" s="65" t="inlineStr"/>
       <c r="I20" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-1601/1602/1603 not arrived yet</t>
@@ -2249,7 +2159,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="n"/>
-      <c r="L20" s="67" t="inlineStr"/>
+      <c r="L20" s="66" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="53" t="inlineStr">
@@ -2262,7 +2172,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C21" s="76" t="inlineStr">
+      <c r="C21" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2287,11 +2197,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H21" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H21" s="65" t="inlineStr"/>
       <c r="I21" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDH-1901/1902/1903 not arrived</t>
@@ -2303,7 +2209,7 @@
         </is>
       </c>
       <c r="K21" s="23" t="n"/>
-      <c r="L21" s="67" t="inlineStr"/>
+      <c r="L21" s="66" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="53" t="inlineStr">
@@ -2316,7 +2222,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C22" s="78" t="inlineStr">
+      <c r="C22" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2341,11 +2247,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H22" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H22" s="65" t="inlineStr"/>
       <c r="I22" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -2357,7 +2259,7 @@
         </is>
       </c>
       <c r="K22" s="23" t="n"/>
-      <c r="L22" s="67" t="inlineStr"/>
+      <c r="L22" s="66" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
@@ -2370,7 +2272,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C23" s="78" t="inlineStr">
+      <c r="C23" s="76" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -2395,11 +2297,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H23" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="H23" s="65" t="inlineStr"/>
       <c r="I23" s="65" t="inlineStr">
         <is>
           <t>PS5-03-GDIR-1201, PS5-03-GDIR-1202, PS5-03-GDIR-1203, PS5-03-GDIR-1204 instrument not arrived</t>
@@ -2411,7 +2309,7 @@
         </is>
       </c>
       <c r="K23" s="23" t="n"/>
-      <c r="L23" s="67" t="inlineStr"/>
+      <c r="L23" s="66" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
@@ -2424,7 +2322,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C24" s="76" t="inlineStr">
+      <c r="C24" s="74" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -2449,11 +2347,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H24" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H24" s="65" t="inlineStr"/>
       <c r="I24" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-0007, PS5-71-TW-0003, PS5-71-TW-0004, PS5-71-TW-0006 not arrived</t>
@@ -2465,7 +2359,7 @@
         </is>
       </c>
       <c r="K24" s="23" t="n"/>
-      <c r="L24" s="67" t="inlineStr"/>
+      <c r="L24" s="66" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="53" t="inlineStr">
@@ -2478,7 +2372,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C25" s="77" t="inlineStr">
+      <c r="C25" s="75" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -2503,11 +2397,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H25" s="65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="H25" s="65" t="inlineStr"/>
       <c r="I25" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BI-0002-CC01, 155m ,Cable type:12P X 0.75 OS FL RTD
@@ -2523,7 +2413,7 @@
         </is>
       </c>
       <c r="K25" s="23" t="n"/>
-      <c r="L25" s="67" t="inlineStr"/>
+      <c r="L25" s="66" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="53" t="inlineStr">
@@ -2536,7 +2426,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C26" s="78" t="inlineStr">
+      <c r="C26" s="76" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -2561,11 +2451,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="H26" s="65" t="inlineStr"/>
       <c r="I26" s="65" t="inlineStr">
         <is>
           <t>PS5-71-21-0331 - Test Package - CPP Item Nipple and 1/2 Flange not available at site. CPY/EPS Supply Item PS5-71-FIT-0019 – SRN-01997, awaiting collection from vendor by MLC (airfreight).
@@ -2579,7 +2465,7 @@
         </is>
       </c>
       <c r="K26" s="23" t="n"/>
-      <c r="L26" s="67" t="inlineStr"/>
+      <c r="L26" s="66" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="53" t="inlineStr">
@@ -2592,7 +2478,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C27" s="76" t="inlineStr">
+      <c r="C27" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2617,11 +2503,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H27" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H27" s="65" t="inlineStr"/>
       <c r="I27" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-1701, PS5-03-RDOS-1702, PS5-03-RDOS-1703 instrument not arrived</t>
@@ -2633,7 +2515,7 @@
         </is>
       </c>
       <c r="K27" s="23" t="n"/>
-      <c r="L27" s="67" t="inlineStr"/>
+      <c r="L27" s="66" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="53" t="inlineStr">
@@ -2646,7 +2528,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C28" s="76" t="inlineStr">
+      <c r="C28" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2671,11 +2553,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H28" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H28" s="65" t="inlineStr"/>
       <c r="I28" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-1801, PS5-03-RDOS-1802, PS5-03-RDOS-1803 instrument not arrived</t>
@@ -2687,7 +2565,7 @@
         </is>
       </c>
       <c r="K28" s="23" t="n"/>
-      <c r="L28" s="67" t="inlineStr"/>
+      <c r="L28" s="66" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="53" t="inlineStr">
@@ -2700,7 +2578,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C29" s="76" t="inlineStr">
+      <c r="C29" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2725,11 +2603,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H29" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H29" s="65" t="inlineStr"/>
       <c r="I29" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-2101, PS5-03-RDOS-2102, PS5-03-RDOS-2103 not arrived</t>
@@ -2741,7 +2615,7 @@
         </is>
       </c>
       <c r="K29" s="23" t="n"/>
-      <c r="L29" s="67" t="inlineStr"/>
+      <c r="L29" s="66" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="53" t="inlineStr">
@@ -2754,7 +2628,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C30" s="77" t="inlineStr">
+      <c r="C30" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -2779,11 +2653,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H30" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H30" s="65" t="inlineStr"/>
       <c r="I30" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -2795,7 +2665,7 @@
         </is>
       </c>
       <c r="K30" s="23" t="n"/>
-      <c r="L30" s="67" t="inlineStr"/>
+      <c r="L30" s="66" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="53" t="inlineStr">
@@ -2808,7 +2678,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C31" s="77" t="inlineStr">
+      <c r="C31" s="75" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -2833,11 +2703,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H31" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H31" s="65" t="inlineStr"/>
       <c r="I31" s="65" t="inlineStr">
         <is>
           <t>6 ITRS pending due to LIT 1201/1202 (not arrived yet)</t>
@@ -2849,7 +2715,7 @@
         </is>
       </c>
       <c r="K31" s="23" t="n"/>
-      <c r="L31" s="67" t="inlineStr"/>
+      <c r="L31" s="66" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="53" t="inlineStr">
@@ -2862,7 +2728,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C32" s="77" t="inlineStr">
+      <c r="C32" s="75" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -2887,15 +2753,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H32" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H32" s="65" t="inlineStr"/>
       <c r="I32" s="65" t="inlineStr"/>
       <c r="J32" s="23" t="inlineStr"/>
       <c r="K32" s="23" t="n"/>
-      <c r="L32" s="67" t="inlineStr"/>
+      <c r="L32" s="66" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="53" t="inlineStr">
@@ -2908,7 +2770,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C33" s="78" t="inlineStr">
+      <c r="C33" s="76" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -2933,11 +2795,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H33" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="H33" s="65" t="inlineStr"/>
       <c r="I33" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BI-0003-CC04 6P X 0.75 OS FL RTD 20m
@@ -2951,7 +2809,7 @@
         </is>
       </c>
       <c r="K33" s="23" t="n"/>
-      <c r="L33" s="67" t="inlineStr"/>
+      <c r="L33" s="66" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="53" t="inlineStr">
@@ -2964,7 +2822,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C34" s="78" t="inlineStr">
+      <c r="C34" s="76" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -2989,11 +2847,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H34" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H34" s="65" t="inlineStr"/>
       <c r="I34" s="65" t="inlineStr">
         <is>
           <t>3 Cables cannot be terminated due to rusty heater</t>
@@ -3005,7 +2859,7 @@
         </is>
       </c>
       <c r="K34" s="23" t="n"/>
-      <c r="L34" s="67" t="inlineStr"/>
+      <c r="L34" s="66" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="53" t="inlineStr">
@@ -3018,7 +2872,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C35" s="77" t="inlineStr">
+      <c r="C35" s="75" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -3043,11 +2897,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H35" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H35" s="65" t="inlineStr"/>
       <c r="I35" s="65" t="inlineStr">
         <is>
           <t>PS5-28-PSV-3901B, PS5-28-PSV-3901A not arrived</t>
@@ -3059,7 +2909,7 @@
         </is>
       </c>
       <c r="K35" s="23" t="n"/>
-      <c r="L35" s="67" t="inlineStr"/>
+      <c r="L35" s="66" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="53" t="inlineStr">
@@ -3072,7 +2922,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C36" s="78" t="inlineStr">
+      <c r="C36" s="76" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -3097,15 +2947,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H36" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H36" s="65" t="inlineStr"/>
       <c r="I36" s="65" t="inlineStr"/>
       <c r="J36" s="23" t="inlineStr"/>
       <c r="K36" s="23" t="n"/>
-      <c r="L36" s="67" t="inlineStr"/>
+      <c r="L36" s="66" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="53" t="inlineStr">
@@ -3118,7 +2964,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C37" s="78" t="inlineStr">
+      <c r="C37" s="76" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -3143,11 +2989,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H37" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H37" s="65" t="inlineStr"/>
       <c r="I37" s="65" t="inlineStr">
         <is>
           <t>PS5-60-BI-0016D-CCO4 6T X 0.75 IS/OS FL RTD 121m</t>
@@ -3159,7 +3001,7 @@
         </is>
       </c>
       <c r="K37" s="23" t="n"/>
-      <c r="L37" s="67" t="inlineStr"/>
+      <c r="L37" s="66" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="53" t="inlineStr">
@@ -3172,7 +3014,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C38" s="77" t="inlineStr">
+      <c r="C38" s="75" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -3197,11 +3039,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H38" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H38" s="65" t="inlineStr"/>
       <c r="I38" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-4103, PS5-71-TW-4102
@@ -3215,7 +3053,7 @@
         </is>
       </c>
       <c r="K38" s="23" t="n"/>
-      <c r="L38" s="67" t="inlineStr"/>
+      <c r="L38" s="66" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="53" t="inlineStr">
@@ -3228,7 +3066,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C39" s="77" t="inlineStr">
+      <c r="C39" s="75" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -3253,11 +3091,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H39" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H39" s="65" t="inlineStr"/>
       <c r="I39" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-4203, PS5-71-TW-4202 not arrived</t>
@@ -3269,7 +3103,7 @@
         </is>
       </c>
       <c r="K39" s="23" t="n"/>
-      <c r="L39" s="67" t="inlineStr"/>
+      <c r="L39" s="66" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="53" t="inlineStr">
@@ -3282,7 +3116,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C40" s="78" t="inlineStr">
+      <c r="C40" s="76" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -3307,14 +3141,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H40" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H40" s="65" t="inlineStr"/>
       <c r="I40" s="65" t="inlineStr">
         <is>
-          <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
+          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -3323,7 +3153,7 @@
         </is>
       </c>
       <c r="K40" s="23" t="n"/>
-      <c r="L40" s="67" t="inlineStr"/>
+      <c r="L40" s="66" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="53" t="inlineStr">
@@ -3336,7 +3166,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C41" s="78" t="inlineStr">
+      <c r="C41" s="76" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -3361,11 +3191,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H41" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H41" s="65" t="inlineStr"/>
       <c r="I41" s="65" t="inlineStr">
         <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
@@ -3377,7 +3203,7 @@
         </is>
       </c>
       <c r="K41" s="23" t="n"/>
-      <c r="L41" s="67" t="inlineStr"/>
+      <c r="L41" s="66" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="53" t="inlineStr">
@@ -3390,7 +3216,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C42" s="78" t="inlineStr">
+      <c r="C42" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3415,15 +3241,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H42" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H42" s="65" t="inlineStr"/>
       <c r="I42" s="65" t="inlineStr"/>
       <c r="J42" s="23" t="inlineStr"/>
       <c r="K42" s="23" t="n"/>
-      <c r="L42" s="67" t="inlineStr"/>
+      <c r="L42" s="66" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="53" t="inlineStr">
@@ -3436,7 +3258,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C43" s="78" t="inlineStr">
+      <c r="C43" s="76" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -3461,11 +3283,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H43" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H43" s="65" t="inlineStr"/>
       <c r="I43" s="65" t="inlineStr">
         <is>
           <t>PS5-60-BI-0016C-CCO4 6T X 0.75 IS/OS FL RTD 131m
@@ -3479,7 +3297,7 @@
         </is>
       </c>
       <c r="K43" s="23" t="n"/>
-      <c r="L43" s="67" t="inlineStr"/>
+      <c r="L43" s="66" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="53" t="inlineStr">
@@ -3492,7 +3310,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C44" s="78" t="inlineStr">
+      <c r="C44" s="76" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3517,11 +3335,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H44" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H44" s="65" t="inlineStr"/>
       <c r="I44" s="65" t="inlineStr">
         <is>
           <t>PS5-60-LIT-4301 not arrived.</t>
@@ -3533,7 +3347,7 @@
         </is>
       </c>
       <c r="K44" s="23" t="n"/>
-      <c r="L44" s="67" t="inlineStr"/>
+      <c r="L44" s="66" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="53" t="inlineStr">
@@ -3546,7 +3360,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C45" s="78" t="inlineStr">
+      <c r="C45" s="76" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3571,11 +3385,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H45" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H45" s="65" t="inlineStr"/>
       <c r="I45" s="65" t="inlineStr">
         <is>
           <t>PS5-60-LIT-4401 not arrived</t>
@@ -3587,7 +3397,7 @@
         </is>
       </c>
       <c r="K45" s="23" t="n"/>
-      <c r="L45" s="67" t="inlineStr"/>
+      <c r="L45" s="66" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="53" t="inlineStr">
@@ -3600,7 +3410,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C46" s="78" t="inlineStr">
+      <c r="C46" s="76" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3625,15 +3435,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H46" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H46" s="65" t="inlineStr"/>
       <c r="I46" s="65" t="inlineStr"/>
       <c r="J46" s="23" t="inlineStr"/>
       <c r="K46" s="23" t="n"/>
-      <c r="L46" s="67" t="inlineStr"/>
+      <c r="L46" s="66" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="53" t="inlineStr">
@@ -3646,7 +3452,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C47" s="78" t="inlineStr">
+      <c r="C47" s="76" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3671,15 +3477,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H47" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H47" s="65" t="inlineStr"/>
       <c r="I47" s="65" t="inlineStr"/>
       <c r="J47" s="23" t="inlineStr"/>
       <c r="K47" s="23" t="n"/>
-      <c r="L47" s="67" t="inlineStr"/>
+      <c r="L47" s="66" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="53" t="inlineStr">
@@ -3692,7 +3494,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C48" s="78" t="inlineStr">
+      <c r="C48" s="76" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3717,15 +3519,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H48" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H48" s="65" t="inlineStr"/>
       <c r="I48" s="65" t="inlineStr"/>
       <c r="J48" s="23" t="inlineStr"/>
       <c r="K48" s="23" t="n"/>
-      <c r="L48" s="67" t="inlineStr"/>
+      <c r="L48" s="66" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="53" t="inlineStr">
@@ -3738,7 +3536,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C49" s="78" t="inlineStr">
+      <c r="C49" s="76" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3763,15 +3561,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H49" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H49" s="65" t="inlineStr"/>
       <c r="I49" s="65" t="inlineStr"/>
       <c r="J49" s="23" t="inlineStr"/>
       <c r="K49" s="23" t="n"/>
-      <c r="L49" s="67" t="inlineStr"/>
+      <c r="L49" s="66" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="53" t="inlineStr">
@@ -3784,7 +3578,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C50" s="77" t="inlineStr">
+      <c r="C50" s="75" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -3809,11 +3603,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H50" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H50" s="65" t="inlineStr"/>
       <c r="I50" s="65" t="inlineStr">
         <is>
           <t>PS5-71-BI-0005-CC01 12P X 0.75 OS FL RTD cable not available</t>
@@ -3825,35 +3615,35 @@
         </is>
       </c>
       <c r="K50" s="23" t="n"/>
-      <c r="L50" s="67" t="inlineStr"/>
+      <c r="L50" s="66" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="79" t="inlineStr">
+      <c r="A51" s="53" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
       </c>
-      <c r="B51" s="66" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="C51" s="80" t="inlineStr">
+      <c r="C51" s="76" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
-      <c r="D51" s="66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E51" s="66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F51" s="66" t="inlineStr">
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3863,23 +3653,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H51" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H51" s="65" t="inlineStr"/>
       <c r="I51" s="65" t="inlineStr">
         <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="J51" s="66" t="inlineStr">
+      <c r="J51" s="23" t="inlineStr">
         <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="K51" s="66" t="n"/>
-      <c r="L51" s="67" t="inlineStr"/>
+      <c r="K51" s="23" t="n"/>
+      <c r="L51" s="66" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="53" t="inlineStr">
@@ -3892,7 +3678,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C52" s="77" t="inlineStr">
+      <c r="C52" s="75" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -3917,11 +3703,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H52" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H52" s="65" t="inlineStr"/>
       <c r="I52" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3933,7 +3715,7 @@
         </is>
       </c>
       <c r="K52" s="23" t="n"/>
-      <c r="L52" s="67" t="inlineStr"/>
+      <c r="L52" s="66" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="53" t="inlineStr">
@@ -3946,7 +3728,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C53" s="78" t="inlineStr">
+      <c r="C53" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3971,11 +3753,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H53" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H53" s="65" t="inlineStr"/>
       <c r="I53" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -3987,7 +3765,7 @@
         </is>
       </c>
       <c r="K53" s="23" t="n"/>
-      <c r="L53" s="67" t="inlineStr"/>
+      <c r="L53" s="66" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="53" t="inlineStr">
@@ -4000,7 +3778,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C54" s="78" t="inlineStr">
+      <c r="C54" s="76" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -4025,15 +3803,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H54" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H54" s="65" t="inlineStr"/>
       <c r="I54" s="65" t="inlineStr"/>
       <c r="J54" s="23" t="inlineStr"/>
       <c r="K54" s="23" t="n"/>
-      <c r="L54" s="67" t="inlineStr"/>
+      <c r="L54" s="66" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="53" t="inlineStr">
@@ -4046,7 +3820,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C55" s="77" t="inlineStr">
+      <c r="C55" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -4071,15 +3845,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H55" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H55" s="65" t="inlineStr"/>
       <c r="I55" s="65" t="inlineStr"/>
       <c r="J55" s="23" t="inlineStr"/>
       <c r="K55" s="23" t="n"/>
-      <c r="L55" s="67" t="inlineStr"/>
+      <c r="L55" s="66" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="53" t="inlineStr">
@@ -4092,7 +3862,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C56" s="78" t="inlineStr">
+      <c r="C56" s="76" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -4117,15 +3887,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H56" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H56" s="65" t="inlineStr"/>
       <c r="I56" s="65" t="inlineStr"/>
       <c r="J56" s="23" t="inlineStr"/>
       <c r="K56" s="23" t="n"/>
-      <c r="L56" s="67" t="inlineStr"/>
+      <c r="L56" s="66" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="53" t="inlineStr">
@@ -4138,7 +3904,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C57" s="77" t="inlineStr">
+      <c r="C57" s="75" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -4163,15 +3929,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H57" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H57" s="65" t="inlineStr"/>
       <c r="I57" s="65" t="inlineStr"/>
       <c r="J57" s="23" t="inlineStr"/>
       <c r="K57" s="23" t="n"/>
-      <c r="L57" s="67" t="inlineStr"/>
+      <c r="L57" s="66" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="53" t="inlineStr">
@@ -4184,7 +3946,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C58" s="78" t="inlineStr">
+      <c r="C58" s="76" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -4209,11 +3971,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H58" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H58" s="65" t="inlineStr"/>
       <c r="I58" s="65" t="inlineStr">
         <is>
           <t>PS5-60-BI-0016F-CCO4 6T X 0.75 IS/OS FL RTD</t>
@@ -4225,7 +3983,7 @@
         </is>
       </c>
       <c r="K58" s="23" t="n"/>
-      <c r="L58" s="67" t="inlineStr"/>
+      <c r="L58" s="66" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="53" t="inlineStr">
@@ -4238,7 +3996,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C59" s="78" t="inlineStr">
+      <c r="C59" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4263,15 +4021,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H59" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H59" s="65" t="inlineStr"/>
       <c r="I59" s="65" t="inlineStr"/>
       <c r="J59" s="23" t="inlineStr"/>
       <c r="K59" s="23" t="n"/>
-      <c r="L59" s="67" t="inlineStr"/>
+      <c r="L59" s="66" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="53" t="inlineStr">
@@ -4284,7 +4038,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C60" s="78" t="inlineStr">
+      <c r="C60" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4309,15 +4063,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H60" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H60" s="65" t="inlineStr"/>
       <c r="I60" s="65" t="inlineStr"/>
       <c r="J60" s="23" t="inlineStr"/>
       <c r="K60" s="23" t="n"/>
-      <c r="L60" s="67" t="inlineStr"/>
+      <c r="L60" s="66" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="53" t="inlineStr">
@@ -4330,7 +4080,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C61" s="77" t="inlineStr">
+      <c r="C61" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -4355,11 +4105,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H61" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H61" s="65" t="inlineStr"/>
       <c r="I61" s="65" t="inlineStr">
         <is>
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
@@ -4371,7 +4117,7 @@
         </is>
       </c>
       <c r="K61" s="23" t="n"/>
-      <c r="L61" s="67" t="inlineStr"/>
+      <c r="L61" s="66" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="53" t="inlineStr">
@@ -4384,7 +4130,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C62" s="77" t="inlineStr">
+      <c r="C62" s="75" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -4409,11 +4155,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H62" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H62" s="65" t="inlineStr"/>
       <c r="I62" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -4425,7 +4167,7 @@
         </is>
       </c>
       <c r="K62" s="23" t="n"/>
-      <c r="L62" s="67" t="inlineStr"/>
+      <c r="L62" s="66" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="53" t="inlineStr">
@@ -4438,7 +4180,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C63" s="78" t="inlineStr">
+      <c r="C63" s="76" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4463,19 +4205,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H63" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H63" s="65" t="inlineStr"/>
       <c r="I63" s="65" t="inlineStr"/>
-      <c r="J63" s="23" t="inlineStr">
-        <is>
-          <t>OBSERVATION -CLEANING ON PROGRESS</t>
-        </is>
-      </c>
+      <c r="J63" s="23" t="inlineStr"/>
       <c r="K63" s="23" t="n"/>
-      <c r="L63" s="67" t="inlineStr"/>
+      <c r="L63" s="66" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="53" t="inlineStr">
@@ -4488,7 +4222,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C64" s="78" t="inlineStr">
+      <c r="C64" s="76" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4513,15 +4247,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H64" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H64" s="65" t="inlineStr"/>
       <c r="I64" s="65" t="inlineStr"/>
       <c r="J64" s="23" t="inlineStr"/>
       <c r="K64" s="23" t="n"/>
-      <c r="L64" s="67" t="inlineStr"/>
+      <c r="L64" s="66" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="53" t="inlineStr">
@@ -4534,7 +4264,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C65" s="78" t="inlineStr">
+      <c r="C65" s="76" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -4559,11 +4289,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H65" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H65" s="65" t="inlineStr"/>
       <c r="I65" s="65" t="inlineStr">
         <is>
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
@@ -4575,7 +4301,7 @@
         </is>
       </c>
       <c r="K65" s="23" t="n"/>
-      <c r="L65" s="67" t="inlineStr"/>
+      <c r="L65" s="66" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="53" t="inlineStr">
@@ -4588,7 +4314,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C66" s="78" t="inlineStr">
+      <c r="C66" s="76" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -4613,11 +4339,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H66" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H66" s="65" t="inlineStr"/>
       <c r="I66" s="65" t="inlineStr">
         <is>
           <t>Cables pending due to PIT location issue, colliding with pipes</t>
@@ -4629,7 +4351,7 @@
         </is>
       </c>
       <c r="K66" s="23" t="n"/>
-      <c r="L66" s="67" t="inlineStr"/>
+      <c r="L66" s="66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="53" t="inlineStr">
@@ -4642,7 +4364,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C67" s="78" t="inlineStr">
+      <c r="C67" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4667,11 +4389,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H67" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H67" s="65" t="inlineStr"/>
       <c r="I67" s="65" t="inlineStr">
         <is>
           <t>PS5-61-IV-0001B cannot close ITR due to transformer leakage issue.</t>
@@ -4683,7 +4401,7 @@
         </is>
       </c>
       <c r="K67" s="23" t="n"/>
-      <c r="L67" s="67" t="inlineStr"/>
+      <c r="L67" s="66" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="53" t="inlineStr">
@@ -4696,7 +4414,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C68" s="78" t="inlineStr">
+      <c r="C68" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4721,11 +4439,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H68" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H68" s="65" t="inlineStr"/>
       <c r="I68" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -4737,7 +4451,7 @@
         </is>
       </c>
       <c r="K68" s="23" t="n"/>
-      <c r="L68" s="67" t="inlineStr"/>
+      <c r="L68" s="66" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="53" t="inlineStr">
@@ -4750,7 +4464,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C69" s="78" t="inlineStr">
+      <c r="C69" s="76" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -4775,11 +4489,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H69" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H69" s="65" t="inlineStr"/>
       <c r="I69" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -4791,7 +4501,7 @@
         </is>
       </c>
       <c r="K69" s="23" t="n"/>
-      <c r="L69" s="67" t="inlineStr"/>
+      <c r="L69" s="66" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="53" t="inlineStr">
@@ -4804,7 +4514,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C70" s="78" t="inlineStr">
+      <c r="C70" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4829,11 +4539,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H70" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H70" s="65" t="inlineStr"/>
       <c r="I70" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -4845,7 +4551,7 @@
         </is>
       </c>
       <c r="K70" s="23" t="n"/>
-      <c r="L70" s="67" t="inlineStr"/>
+      <c r="L70" s="66" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="53" t="inlineStr">
@@ -4858,7 +4564,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C71" s="77" t="inlineStr">
+      <c r="C71" s="75" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -4883,11 +4589,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H71" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H71" s="65" t="inlineStr"/>
       <c r="I71" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -4899,7 +4601,7 @@
         </is>
       </c>
       <c r="K71" s="23" t="n"/>
-      <c r="L71" s="67" t="inlineStr"/>
+      <c r="L71" s="66" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="53" t="inlineStr">
@@ -4912,7 +4614,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C72" s="77" t="inlineStr">
+      <c r="C72" s="75" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -4937,11 +4639,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H72" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H72" s="65" t="inlineStr"/>
       <c r="I72" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -4953,7 +4651,7 @@
         </is>
       </c>
       <c r="K72" s="23" t="n"/>
-      <c r="L72" s="67" t="inlineStr"/>
+      <c r="L72" s="66" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="53" t="inlineStr">
@@ -4966,7 +4664,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C73" s="78" t="inlineStr">
+      <c r="C73" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4991,11 +4689,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H73" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H73" s="65" t="inlineStr"/>
       <c r="I73" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5007,7 +4701,7 @@
         </is>
       </c>
       <c r="K73" s="23" t="n"/>
-      <c r="L73" s="67" t="inlineStr"/>
+      <c r="L73" s="66" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="53" t="inlineStr">
@@ -5020,7 +4714,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C74" s="76" t="inlineStr">
+      <c r="C74" s="74" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -5045,11 +4739,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H74" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H74" s="65" t="inlineStr"/>
       <c r="I74" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5061,7 +4751,7 @@
         </is>
       </c>
       <c r="K74" s="23" t="n"/>
-      <c r="L74" s="67" t="inlineStr"/>
+      <c r="L74" s="66" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="53" t="inlineStr">
@@ -5074,7 +4764,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C75" s="76" t="inlineStr">
+      <c r="C75" s="74" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -5099,11 +4789,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H75" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H75" s="65" t="inlineStr"/>
       <c r="I75" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5115,7 +4801,7 @@
         </is>
       </c>
       <c r="K75" s="23" t="n"/>
-      <c r="L75" s="67" t="inlineStr"/>
+      <c r="L75" s="66" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="53" t="inlineStr">
@@ -5128,7 +4814,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C76" s="78" t="inlineStr">
+      <c r="C76" s="76" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -5153,11 +4839,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H76" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H76" s="65" t="inlineStr"/>
       <c r="I76" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5169,7 +4851,7 @@
         </is>
       </c>
       <c r="K76" s="23" t="n"/>
-      <c r="L76" s="67" t="inlineStr"/>
+      <c r="L76" s="66" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="53" t="inlineStr">
@@ -5182,7 +4864,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C77" s="76" t="inlineStr">
+      <c r="C77" s="74" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -5207,11 +4889,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H77" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H77" s="65" t="inlineStr"/>
       <c r="I77" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5223,7 +4901,7 @@
         </is>
       </c>
       <c r="K77" s="23" t="n"/>
-      <c r="L77" s="67" t="inlineStr"/>
+      <c r="L77" s="66" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="53" t="inlineStr">
@@ -5236,7 +4914,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C78" s="78" t="inlineStr">
+      <c r="C78" s="76" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -5261,11 +4939,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H78" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H78" s="65" t="inlineStr"/>
       <c r="I78" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5277,7 +4951,7 @@
         </is>
       </c>
       <c r="K78" s="23" t="n"/>
-      <c r="L78" s="67" t="inlineStr"/>
+      <c r="L78" s="66" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="53" t="inlineStr">
@@ -5290,7 +4964,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C79" s="78" t="inlineStr">
+      <c r="C79" s="76" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -5315,11 +4989,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H79" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H79" s="65" t="inlineStr"/>
       <c r="I79" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5331,7 +5001,7 @@
         </is>
       </c>
       <c r="K79" s="23" t="n"/>
-      <c r="L79" s="67" t="inlineStr"/>
+      <c r="L79" s="66" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="53" t="inlineStr">
@@ -5344,7 +5014,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C80" s="78" t="inlineStr">
+      <c r="C80" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5369,11 +5039,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H80" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H80" s="65" t="inlineStr"/>
       <c r="I80" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5385,7 +5051,7 @@
         </is>
       </c>
       <c r="K80" s="23" t="n"/>
-      <c r="L80" s="67" t="inlineStr"/>
+      <c r="L80" s="66" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="53" t="inlineStr">
@@ -5398,7 +5064,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C81" s="78" t="inlineStr">
+      <c r="C81" s="76" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -5423,11 +5089,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H81" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H81" s="65" t="inlineStr"/>
       <c r="I81" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5439,7 +5101,7 @@
         </is>
       </c>
       <c r="K81" s="23" t="n"/>
-      <c r="L81" s="67" t="inlineStr"/>
+      <c r="L81" s="66" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="53" t="inlineStr">
@@ -5452,7 +5114,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C82" s="78" t="inlineStr">
+      <c r="C82" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5477,11 +5139,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H82" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H82" s="65" t="inlineStr"/>
       <c r="I82" s="65" t="inlineStr">
         <is>
           <t>Due to gland plate issue of SEA-0001 we cannot terminate the cablesof F&amp;G Instruments.</t>
@@ -5493,7 +5151,7 @@
         </is>
       </c>
       <c r="K82" s="23" t="n"/>
-      <c r="L82" s="67" t="inlineStr"/>
+      <c r="L82" s="66" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="53" t="inlineStr">
@@ -5506,7 +5164,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C83" s="78" t="inlineStr">
+      <c r="C83" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5539,7 +5197,7 @@
       <c r="I83" s="65" t="inlineStr"/>
       <c r="J83" s="23" t="inlineStr"/>
       <c r="K83" s="23" t="n"/>
-      <c r="L83" s="67" t="inlineStr"/>
+      <c r="L83" s="66" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="53" t="inlineStr">
@@ -5552,7 +5210,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C84" s="78" t="inlineStr">
+      <c r="C84" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5577,11 +5235,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H84" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H84" s="65" t="inlineStr"/>
       <c r="I84" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5593,7 +5247,7 @@
         </is>
       </c>
       <c r="K84" s="23" t="n"/>
-      <c r="L84" s="67" t="inlineStr"/>
+      <c r="L84" s="66" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="53" t="inlineStr">
@@ -5606,7 +5260,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C85" s="78" t="inlineStr">
+      <c r="C85" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5631,11 +5285,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H85" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H85" s="65" t="inlineStr"/>
       <c r="I85" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5647,7 +5297,7 @@
         </is>
       </c>
       <c r="K85" s="23" t="n"/>
-      <c r="L85" s="67" t="inlineStr"/>
+      <c r="L85" s="66" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="53" t="inlineStr">
@@ -5660,7 +5310,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C86" s="76" t="inlineStr">
+      <c r="C86" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5685,11 +5335,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H86" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H86" s="65" t="inlineStr"/>
       <c r="I86" s="65" t="inlineStr">
         <is>
           <t>PS5-03-RDOS-G101A, PS5-03-RDOS-G101B
@@ -5703,7 +5349,7 @@
         </is>
       </c>
       <c r="K86" s="23" t="n"/>
-      <c r="L86" s="67" t="inlineStr"/>
+      <c r="L86" s="66" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="53" t="inlineStr">
@@ -5712,7 +5358,7 @@
         </is>
       </c>
       <c r="B87" s="23" t="inlineStr"/>
-      <c r="C87" s="78" t="inlineStr">
+      <c r="C87" s="76" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -5731,7 +5377,7 @@
       <c r="I87" s="65" t="inlineStr"/>
       <c r="J87" s="23" t="inlineStr"/>
       <c r="K87" s="23" t="n"/>
-      <c r="L87" s="67" t="inlineStr"/>
+      <c r="L87" s="66" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="53" t="inlineStr">
@@ -5740,7 +5386,7 @@
         </is>
       </c>
       <c r="B88" s="23" t="inlineStr"/>
-      <c r="C88" s="76" t="inlineStr">
+      <c r="C88" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5759,7 +5405,7 @@
       <c r="I88" s="65" t="inlineStr"/>
       <c r="J88" s="23" t="inlineStr"/>
       <c r="K88" s="23" t="n"/>
-      <c r="L88" s="67" t="inlineStr"/>
+      <c r="L88" s="66" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="53" t="inlineStr">
@@ -5772,7 +5418,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C89" s="76" t="inlineStr">
+      <c r="C89" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5797,11 +5443,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H89" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H89" s="65" t="inlineStr"/>
       <c r="I89" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5813,7 +5455,7 @@
         </is>
       </c>
       <c r="K89" s="23" t="n"/>
-      <c r="L89" s="67" t="inlineStr"/>
+      <c r="L89" s="66" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="53" t="inlineStr">
@@ -5822,7 +5464,7 @@
         </is>
       </c>
       <c r="B90" s="23" t="inlineStr"/>
-      <c r="C90" s="78" t="inlineStr">
+      <c r="C90" s="76" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -5841,7 +5483,7 @@
       <c r="I90" s="65" t="inlineStr"/>
       <c r="J90" s="23" t="inlineStr"/>
       <c r="K90" s="23" t="n"/>
-      <c r="L90" s="67" t="inlineStr"/>
+      <c r="L90" s="66" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="53" t="inlineStr">
@@ -5850,7 +5492,7 @@
         </is>
       </c>
       <c r="B91" s="23" t="inlineStr"/>
-      <c r="C91" s="78" t="inlineStr">
+      <c r="C91" s="76" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -5869,7 +5511,7 @@
       <c r="I91" s="65" t="inlineStr"/>
       <c r="J91" s="23" t="inlineStr"/>
       <c r="K91" s="23" t="n"/>
-      <c r="L91" s="67" t="inlineStr"/>
+      <c r="L91" s="66" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="53" t="inlineStr">
@@ -5878,7 +5520,7 @@
         </is>
       </c>
       <c r="B92" s="23" t="inlineStr"/>
-      <c r="C92" s="77" t="inlineStr">
+      <c r="C92" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -5897,7 +5539,7 @@
       <c r="I92" s="65" t="inlineStr"/>
       <c r="J92" s="23" t="inlineStr"/>
       <c r="K92" s="23" t="n"/>
-      <c r="L92" s="67" t="inlineStr"/>
+      <c r="L92" s="66" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="53" t="inlineStr">
@@ -5910,7 +5552,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C93" s="78" t="inlineStr">
+      <c r="C93" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5935,11 +5577,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H93" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H93" s="65" t="inlineStr"/>
       <c r="I93" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -5951,7 +5589,7 @@
         </is>
       </c>
       <c r="K93" s="23" t="n"/>
-      <c r="L93" s="67" t="inlineStr"/>
+      <c r="L93" s="66" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="53" t="inlineStr">
@@ -5964,7 +5602,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C94" s="78" t="inlineStr">
+      <c r="C94" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5989,11 +5627,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H94" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H94" s="65" t="inlineStr"/>
       <c r="I94" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6005,7 +5639,7 @@
         </is>
       </c>
       <c r="K94" s="23" t="n"/>
-      <c r="L94" s="67" t="inlineStr"/>
+      <c r="L94" s="66" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="53" t="inlineStr">
@@ -6014,7 +5648,7 @@
         </is>
       </c>
       <c r="B95" s="23" t="inlineStr"/>
-      <c r="C95" s="77" t="inlineStr">
+      <c r="C95" s="75" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6033,7 +5667,7 @@
       <c r="I95" s="65" t="inlineStr"/>
       <c r="J95" s="23" t="inlineStr"/>
       <c r="K95" s="23" t="n"/>
-      <c r="L95" s="67" t="inlineStr"/>
+      <c r="L95" s="66" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="53" t="inlineStr">
@@ -6046,7 +5680,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C96" s="78" t="inlineStr">
+      <c r="C96" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6071,11 +5705,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H96" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H96" s="65" t="inlineStr"/>
       <c r="I96" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6087,7 +5717,7 @@
         </is>
       </c>
       <c r="K96" s="23" t="n"/>
-      <c r="L96" s="67" t="inlineStr"/>
+      <c r="L96" s="66" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="53" t="inlineStr">
@@ -6100,7 +5730,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C97" s="76" t="inlineStr">
+      <c r="C97" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6125,11 +5755,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H97" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H97" s="65" t="inlineStr"/>
       <c r="I97" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6141,7 +5767,7 @@
         </is>
       </c>
       <c r="K97" s="23" t="n"/>
-      <c r="L97" s="67" t="inlineStr"/>
+      <c r="L97" s="66" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="53" t="inlineStr">
@@ -6154,7 +5780,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C98" s="76" t="inlineStr">
+      <c r="C98" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6179,11 +5805,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H98" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H98" s="65" t="inlineStr"/>
       <c r="I98" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6195,7 +5817,7 @@
         </is>
       </c>
       <c r="K98" s="23" t="n"/>
-      <c r="L98" s="67" t="inlineStr"/>
+      <c r="L98" s="66" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="53" t="inlineStr">
@@ -6208,7 +5830,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C99" s="76" t="inlineStr">
+      <c r="C99" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6233,11 +5855,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H99" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H99" s="65" t="inlineStr"/>
       <c r="I99" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6249,7 +5867,7 @@
         </is>
       </c>
       <c r="K99" s="23" t="n"/>
-      <c r="L99" s="67" t="inlineStr"/>
+      <c r="L99" s="66" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="53" t="inlineStr">
@@ -6262,7 +5880,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C100" s="76" t="inlineStr">
+      <c r="C100" s="74" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -6287,11 +5905,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H100" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H100" s="65" t="inlineStr"/>
       <c r="I100" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6303,7 +5917,7 @@
         </is>
       </c>
       <c r="K100" s="23" t="n"/>
-      <c r="L100" s="67" t="inlineStr"/>
+      <c r="L100" s="66" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="53" t="inlineStr">
@@ -6316,7 +5930,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C101" s="76" t="inlineStr">
+      <c r="C101" s="74" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -6341,11 +5955,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H101" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H101" s="65" t="inlineStr"/>
       <c r="I101" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6357,7 +5967,7 @@
         </is>
       </c>
       <c r="K101" s="23" t="n"/>
-      <c r="L101" s="67" t="inlineStr"/>
+      <c r="L101" s="66" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="53" t="inlineStr">
@@ -6366,7 +5976,7 @@
         </is>
       </c>
       <c r="B102" s="23" t="inlineStr"/>
-      <c r="C102" s="76" t="inlineStr">
+      <c r="C102" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6385,7 +5995,7 @@
       <c r="I102" s="65" t="inlineStr"/>
       <c r="J102" s="23" t="inlineStr"/>
       <c r="K102" s="23" t="n"/>
-      <c r="L102" s="67" t="inlineStr"/>
+      <c r="L102" s="66" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="53" t="inlineStr">
@@ -6394,7 +6004,7 @@
         </is>
       </c>
       <c r="B103" s="23" t="inlineStr"/>
-      <c r="C103" s="76" t="inlineStr">
+      <c r="C103" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6413,7 +6023,7 @@
       <c r="I103" s="65" t="inlineStr"/>
       <c r="J103" s="23" t="inlineStr"/>
       <c r="K103" s="23" t="n"/>
-      <c r="L103" s="67" t="inlineStr"/>
+      <c r="L103" s="66" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="53" t="inlineStr">
@@ -6426,7 +6036,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C104" s="76" t="inlineStr">
+      <c r="C104" s="74" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6451,11 +6061,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H104" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H104" s="65" t="inlineStr"/>
       <c r="I104" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6467,7 +6073,7 @@
         </is>
       </c>
       <c r="K104" s="23" t="n"/>
-      <c r="L104" s="67" t="inlineStr"/>
+      <c r="L104" s="66" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="53" t="inlineStr">
@@ -6480,7 +6086,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C105" s="76" t="inlineStr">
+      <c r="C105" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6505,11 +6111,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H105" s="65" t="inlineStr"/>
       <c r="I105" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6521,7 +6123,7 @@
         </is>
       </c>
       <c r="K105" s="23" t="n"/>
-      <c r="L105" s="67" t="inlineStr"/>
+      <c r="L105" s="66" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="53" t="inlineStr">
@@ -6534,7 +6136,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C106" s="76" t="inlineStr">
+      <c r="C106" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6559,11 +6161,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H106" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H106" s="65" t="inlineStr"/>
       <c r="I106" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6575,7 +6173,7 @@
         </is>
       </c>
       <c r="K106" s="23" t="n"/>
-      <c r="L106" s="67" t="inlineStr"/>
+      <c r="L106" s="66" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="53" t="inlineStr">
@@ -6588,7 +6186,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C107" s="76" t="inlineStr">
+      <c r="C107" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6613,11 +6211,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H107" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H107" s="65" t="inlineStr"/>
       <c r="I107" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6629,7 +6223,7 @@
         </is>
       </c>
       <c r="K107" s="23" t="n"/>
-      <c r="L107" s="67" t="inlineStr"/>
+      <c r="L107" s="66" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="53" t="inlineStr">
@@ -6642,7 +6236,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C108" s="76" t="inlineStr">
+      <c r="C108" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6667,11 +6261,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H108" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H108" s="65" t="inlineStr"/>
       <c r="I108" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6683,7 +6273,7 @@
         </is>
       </c>
       <c r="K108" s="23" t="n"/>
-      <c r="L108" s="67" t="inlineStr"/>
+      <c r="L108" s="66" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="53" t="inlineStr">
@@ -6696,7 +6286,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C109" s="76" t="inlineStr">
+      <c r="C109" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6721,11 +6311,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H109" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H109" s="65" t="inlineStr"/>
       <c r="I109" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6737,7 +6323,7 @@
         </is>
       </c>
       <c r="K109" s="23" t="n"/>
-      <c r="L109" s="67" t="inlineStr"/>
+      <c r="L109" s="66" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="53" t="inlineStr">
@@ -6750,7 +6336,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C110" s="76" t="inlineStr">
+      <c r="C110" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6775,11 +6361,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H110" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H110" s="65" t="inlineStr"/>
       <c r="I110" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6791,7 +6373,7 @@
         </is>
       </c>
       <c r="K110" s="23" t="n"/>
-      <c r="L110" s="67" t="inlineStr"/>
+      <c r="L110" s="66" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="53" t="inlineStr">
@@ -6800,7 +6382,7 @@
         </is>
       </c>
       <c r="B111" s="23" t="inlineStr"/>
-      <c r="C111" s="77" t="inlineStr">
+      <c r="C111" s="75" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -6819,7 +6401,7 @@
       <c r="I111" s="65" t="inlineStr"/>
       <c r="J111" s="23" t="inlineStr"/>
       <c r="K111" s="23" t="n"/>
-      <c r="L111" s="67" t="inlineStr"/>
+      <c r="L111" s="66" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="53" t="inlineStr">
@@ -6832,7 +6414,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C112" s="76" t="inlineStr">
+      <c r="C112" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6857,11 +6439,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H112" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H112" s="65" t="inlineStr"/>
       <c r="I112" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6873,7 +6451,7 @@
         </is>
       </c>
       <c r="K112" s="23" t="n"/>
-      <c r="L112" s="67" t="inlineStr"/>
+      <c r="L112" s="66" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="53" t="inlineStr">
@@ -6886,7 +6464,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C113" s="76" t="inlineStr">
+      <c r="C113" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6911,11 +6489,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H113" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H113" s="65" t="inlineStr"/>
       <c r="I113" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6927,7 +6501,7 @@
         </is>
       </c>
       <c r="K113" s="23" t="n"/>
-      <c r="L113" s="67" t="inlineStr"/>
+      <c r="L113" s="66" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="53" t="inlineStr">
@@ -6940,7 +6514,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C114" s="76" t="inlineStr">
+      <c r="C114" s="74" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -6965,11 +6539,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H114" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H114" s="65" t="inlineStr"/>
       <c r="I114" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -6981,7 +6551,7 @@
         </is>
       </c>
       <c r="K114" s="23" t="n"/>
-      <c r="L114" s="67" t="inlineStr"/>
+      <c r="L114" s="66" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="53" t="inlineStr">
@@ -6990,7 +6560,7 @@
         </is>
       </c>
       <c r="B115" s="23" t="inlineStr"/>
-      <c r="C115" s="76" t="inlineStr">
+      <c r="C115" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7009,7 +6579,7 @@
       <c r="I115" s="65" t="inlineStr"/>
       <c r="J115" s="23" t="inlineStr"/>
       <c r="K115" s="23" t="n"/>
-      <c r="L115" s="67" t="inlineStr"/>
+      <c r="L115" s="66" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="53" t="inlineStr">
@@ -7022,7 +6592,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C116" s="76" t="inlineStr">
+      <c r="C116" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7047,11 +6617,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H116" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H116" s="65" t="inlineStr"/>
       <c r="I116" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7063,7 +6629,7 @@
         </is>
       </c>
       <c r="K116" s="23" t="n"/>
-      <c r="L116" s="67" t="inlineStr"/>
+      <c r="L116" s="66" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="53" t="inlineStr">
@@ -7076,7 +6642,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C117" s="76" t="inlineStr">
+      <c r="C117" s="74" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -7101,11 +6667,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H117" s="65" t="inlineStr"/>
       <c r="I117" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7117,7 +6679,7 @@
         </is>
       </c>
       <c r="K117" s="23" t="n"/>
-      <c r="L117" s="67" t="inlineStr"/>
+      <c r="L117" s="66" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="53" t="inlineStr">
@@ -7130,7 +6692,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C118" s="76" t="inlineStr">
+      <c r="C118" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7155,11 +6717,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H118" s="65" t="inlineStr"/>
       <c r="I118" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7171,7 +6729,7 @@
         </is>
       </c>
       <c r="K118" s="23" t="n"/>
-      <c r="L118" s="67" t="inlineStr"/>
+      <c r="L118" s="66" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="53" t="inlineStr">
@@ -7180,7 +6738,7 @@
         </is>
       </c>
       <c r="B119" s="23" t="inlineStr"/>
-      <c r="C119" s="76" t="inlineStr">
+      <c r="C119" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7199,7 +6757,7 @@
       <c r="I119" s="65" t="inlineStr"/>
       <c r="J119" s="23" t="inlineStr"/>
       <c r="K119" s="23" t="n"/>
-      <c r="L119" s="67" t="inlineStr"/>
+      <c r="L119" s="66" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="53" t="inlineStr">
@@ -7208,7 +6766,7 @@
         </is>
       </c>
       <c r="B120" s="23" t="inlineStr"/>
-      <c r="C120" s="76" t="inlineStr">
+      <c r="C120" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7227,7 +6785,7 @@
       <c r="I120" s="65" t="inlineStr"/>
       <c r="J120" s="23" t="inlineStr"/>
       <c r="K120" s="23" t="n"/>
-      <c r="L120" s="67" t="inlineStr"/>
+      <c r="L120" s="66" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="53" t="inlineStr">
@@ -7240,7 +6798,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C121" s="76" t="inlineStr">
+      <c r="C121" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7265,11 +6823,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H121" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H121" s="65" t="inlineStr"/>
       <c r="I121" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7281,7 +6835,7 @@
         </is>
       </c>
       <c r="K121" s="23" t="n"/>
-      <c r="L121" s="67" t="inlineStr"/>
+      <c r="L121" s="66" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="53" t="inlineStr">
@@ -7294,7 +6848,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C122" s="76" t="inlineStr">
+      <c r="C122" s="74" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -7319,11 +6873,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H122" s="65" t="inlineStr"/>
       <c r="I122" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7335,7 +6885,7 @@
         </is>
       </c>
       <c r="K122" s="23" t="n"/>
-      <c r="L122" s="67" t="inlineStr"/>
+      <c r="L122" s="66" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="53" t="inlineStr">
@@ -7344,7 +6894,7 @@
         </is>
       </c>
       <c r="B123" s="23" t="inlineStr"/>
-      <c r="C123" s="76" t="inlineStr">
+      <c r="C123" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7363,7 +6913,7 @@
       <c r="I123" s="65" t="inlineStr"/>
       <c r="J123" s="23" t="inlineStr"/>
       <c r="K123" s="23" t="n"/>
-      <c r="L123" s="67" t="inlineStr"/>
+      <c r="L123" s="66" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="53" t="inlineStr">
@@ -7372,7 +6922,7 @@
         </is>
       </c>
       <c r="B124" s="23" t="inlineStr"/>
-      <c r="C124" s="76" t="inlineStr">
+      <c r="C124" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7391,7 +6941,7 @@
       <c r="I124" s="65" t="inlineStr"/>
       <c r="J124" s="23" t="inlineStr"/>
       <c r="K124" s="23" t="n"/>
-      <c r="L124" s="67" t="inlineStr"/>
+      <c r="L124" s="66" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="53" t="inlineStr">
@@ -7404,7 +6954,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C125" s="76" t="inlineStr">
+      <c r="C125" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7429,11 +6979,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H125" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H125" s="65" t="inlineStr"/>
       <c r="I125" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7445,7 +6991,7 @@
         </is>
       </c>
       <c r="K125" s="23" t="n"/>
-      <c r="L125" s="67" t="inlineStr"/>
+      <c r="L125" s="66" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="53" t="inlineStr">
@@ -7458,7 +7004,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C126" s="76" t="inlineStr">
+      <c r="C126" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7483,11 +7029,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H126" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H126" s="65" t="inlineStr"/>
       <c r="I126" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7499,7 +7041,7 @@
         </is>
       </c>
       <c r="K126" s="23" t="n"/>
-      <c r="L126" s="67" t="inlineStr"/>
+      <c r="L126" s="66" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="53" t="inlineStr">
@@ -7508,7 +7050,7 @@
         </is>
       </c>
       <c r="B127" s="23" t="inlineStr"/>
-      <c r="C127" s="77" t="inlineStr">
+      <c r="C127" s="75" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -7527,7 +7069,7 @@
       <c r="I127" s="65" t="inlineStr"/>
       <c r="J127" s="23" t="inlineStr"/>
       <c r="K127" s="23" t="n"/>
-      <c r="L127" s="67" t="inlineStr"/>
+      <c r="L127" s="66" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="53" t="inlineStr">
@@ -7540,7 +7082,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C128" s="77" t="inlineStr">
+      <c r="C128" s="75" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -7565,11 +7107,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H128" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H128" s="65" t="inlineStr"/>
       <c r="I128" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7581,7 +7119,7 @@
         </is>
       </c>
       <c r="K128" s="23" t="n"/>
-      <c r="L128" s="67" t="inlineStr"/>
+      <c r="L128" s="66" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="53" t="inlineStr">
@@ -7594,7 +7132,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C129" s="77" t="inlineStr">
+      <c r="C129" s="75" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -7619,11 +7157,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H129" s="65" t="inlineStr"/>
       <c r="I129" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7635,7 +7169,7 @@
         </is>
       </c>
       <c r="K129" s="23" t="n"/>
-      <c r="L129" s="67" t="inlineStr"/>
+      <c r="L129" s="66" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="53" t="inlineStr">
@@ -7648,7 +7182,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C130" s="77" t="inlineStr">
+      <c r="C130" s="75" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -7673,11 +7207,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H130" s="65" t="inlineStr"/>
       <c r="I130" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7689,7 +7219,7 @@
         </is>
       </c>
       <c r="K130" s="23" t="n"/>
-      <c r="L130" s="67" t="inlineStr"/>
+      <c r="L130" s="66" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="53" t="inlineStr">
@@ -7702,7 +7232,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C131" s="77" t="inlineStr">
+      <c r="C131" s="75" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7727,11 +7257,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H131" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H131" s="65" t="inlineStr"/>
       <c r="I131" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7743,7 +7269,7 @@
         </is>
       </c>
       <c r="K131" s="23" t="n"/>
-      <c r="L131" s="67" t="inlineStr"/>
+      <c r="L131" s="66" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="53" t="inlineStr">
@@ -7756,7 +7282,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C132" s="77" t="inlineStr">
+      <c r="C132" s="75" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -7781,11 +7307,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H132" s="65" t="inlineStr"/>
       <c r="I132" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7797,7 +7319,7 @@
         </is>
       </c>
       <c r="K132" s="23" t="n"/>
-      <c r="L132" s="67" t="inlineStr"/>
+      <c r="L132" s="66" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="53" t="inlineStr">
@@ -7810,7 +7332,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C133" s="77" t="inlineStr">
+      <c r="C133" s="75" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -7835,11 +7357,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H133" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H133" s="65" t="inlineStr"/>
       <c r="I133" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7851,7 +7369,7 @@
         </is>
       </c>
       <c r="K133" s="23" t="n"/>
-      <c r="L133" s="67" t="inlineStr"/>
+      <c r="L133" s="66" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="53" t="inlineStr">
@@ -7864,7 +7382,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C134" s="77" t="inlineStr">
+      <c r="C134" s="75" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7889,11 +7407,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H134" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H134" s="65" t="inlineStr"/>
       <c r="I134" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7905,7 +7419,7 @@
         </is>
       </c>
       <c r="K134" s="23" t="n"/>
-      <c r="L134" s="67" t="inlineStr"/>
+      <c r="L134" s="66" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="53" t="inlineStr">
@@ -7918,7 +7432,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C135" s="77" t="inlineStr">
+      <c r="C135" s="75" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -7943,11 +7457,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H135" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H135" s="65" t="inlineStr"/>
       <c r="I135" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7959,7 +7469,7 @@
         </is>
       </c>
       <c r="K135" s="23" t="n"/>
-      <c r="L135" s="67" t="inlineStr"/>
+      <c r="L135" s="66" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="53" t="inlineStr">
@@ -7972,7 +7482,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C136" s="78" t="inlineStr">
+      <c r="C136" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7997,11 +7507,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H136" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H136" s="65" t="inlineStr"/>
       <c r="I136" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8013,7 +7519,7 @@
         </is>
       </c>
       <c r="K136" s="23" t="n"/>
-      <c r="L136" s="67" t="inlineStr"/>
+      <c r="L136" s="66" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="53" t="inlineStr">
@@ -8026,7 +7532,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C137" s="77" t="inlineStr">
+      <c r="C137" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8051,11 +7557,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H137" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H137" s="65" t="inlineStr"/>
       <c r="I137" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8067,7 +7569,7 @@
         </is>
       </c>
       <c r="K137" s="23" t="n"/>
-      <c r="L137" s="67" t="inlineStr"/>
+      <c r="L137" s="66" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="53" t="inlineStr">
@@ -8080,7 +7582,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C138" s="78" t="inlineStr">
+      <c r="C138" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8105,11 +7607,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H138" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H138" s="65" t="inlineStr"/>
       <c r="I138" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8121,7 +7619,7 @@
         </is>
       </c>
       <c r="K138" s="23" t="n"/>
-      <c r="L138" s="67" t="inlineStr"/>
+      <c r="L138" s="66" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="53" t="inlineStr">
@@ -8134,7 +7632,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C139" s="77" t="inlineStr">
+      <c r="C139" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8159,11 +7657,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H139" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H139" s="65" t="inlineStr"/>
       <c r="I139" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8175,7 +7669,7 @@
         </is>
       </c>
       <c r="K139" s="23" t="n"/>
-      <c r="L139" s="67" t="inlineStr"/>
+      <c r="L139" s="66" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="53" t="inlineStr">
@@ -8188,7 +7682,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C140" s="78" t="inlineStr">
+      <c r="C140" s="76" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -8213,11 +7707,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H140" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H140" s="65" t="inlineStr"/>
       <c r="I140" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8229,7 +7719,7 @@
         </is>
       </c>
       <c r="K140" s="23" t="n"/>
-      <c r="L140" s="67" t="inlineStr"/>
+      <c r="L140" s="66" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="53" t="inlineStr">
@@ -8242,7 +7732,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C141" s="76" t="inlineStr">
+      <c r="C141" s="74" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -8267,11 +7757,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H141" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H141" s="65" t="inlineStr"/>
       <c r="I141" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8283,7 +7769,7 @@
         </is>
       </c>
       <c r="K141" s="23" t="n"/>
-      <c r="L141" s="67" t="inlineStr"/>
+      <c r="L141" s="66" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="53" t="inlineStr">
@@ -8296,7 +7782,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C142" s="77" t="inlineStr">
+      <c r="C142" s="75" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -8321,11 +7807,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H142" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H142" s="65" t="inlineStr"/>
       <c r="I142" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8337,7 +7819,7 @@
         </is>
       </c>
       <c r="K142" s="23" t="n"/>
-      <c r="L142" s="67" t="inlineStr"/>
+      <c r="L142" s="66" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="53" t="inlineStr">
@@ -8350,7 +7832,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C143" s="76" t="inlineStr">
+      <c r="C143" s="74" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -8375,11 +7857,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H143" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H143" s="65" t="inlineStr"/>
       <c r="I143" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8391,7 +7869,7 @@
         </is>
       </c>
       <c r="K143" s="23" t="n"/>
-      <c r="L143" s="67" t="inlineStr"/>
+      <c r="L143" s="66" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="53" t="inlineStr">
@@ -8404,7 +7882,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C144" s="77" t="inlineStr">
+      <c r="C144" s="75" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8429,11 +7907,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H144" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H144" s="65" t="inlineStr"/>
       <c r="I144" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8445,7 +7919,7 @@
         </is>
       </c>
       <c r="K144" s="23" t="n"/>
-      <c r="L144" s="67" t="inlineStr"/>
+      <c r="L144" s="66" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="53" t="inlineStr">
@@ -8458,7 +7932,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C145" s="77" t="inlineStr">
+      <c r="C145" s="75" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8483,11 +7957,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H145" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H145" s="65" t="inlineStr"/>
       <c r="I145" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8499,7 +7969,7 @@
         </is>
       </c>
       <c r="K145" s="23" t="n"/>
-      <c r="L145" s="67" t="inlineStr"/>
+      <c r="L145" s="66" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="53" t="inlineStr">
@@ -8512,7 +7982,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C146" s="77" t="inlineStr">
+      <c r="C146" s="75" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8537,11 +8007,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H146" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H146" s="65" t="inlineStr"/>
       <c r="I146" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8553,7 +8019,7 @@
         </is>
       </c>
       <c r="K146" s="23" t="n"/>
-      <c r="L146" s="67" t="inlineStr"/>
+      <c r="L146" s="66" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="53" t="inlineStr">
@@ -8566,7 +8032,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C147" s="77" t="inlineStr">
+      <c r="C147" s="75" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8591,11 +8057,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H147" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H147" s="65" t="inlineStr"/>
       <c r="I147" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8607,7 +8069,7 @@
         </is>
       </c>
       <c r="K147" s="23" t="n"/>
-      <c r="L147" s="67" t="inlineStr"/>
+      <c r="L147" s="66" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="53" t="inlineStr">
@@ -8620,7 +8082,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C148" s="77" t="inlineStr">
+      <c r="C148" s="75" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8645,11 +8107,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H148" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H148" s="65" t="inlineStr"/>
       <c r="I148" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8661,7 +8119,7 @@
         </is>
       </c>
       <c r="K148" s="23" t="n"/>
-      <c r="L148" s="67" t="inlineStr"/>
+      <c r="L148" s="66" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="53" t="inlineStr">
@@ -8674,7 +8132,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C149" s="77" t="inlineStr">
+      <c r="C149" s="75" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -8699,11 +8157,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H149" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H149" s="65" t="inlineStr"/>
       <c r="I149" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8715,7 +8169,7 @@
         </is>
       </c>
       <c r="K149" s="23" t="n"/>
-      <c r="L149" s="67" t="inlineStr"/>
+      <c r="L149" s="66" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="53" t="inlineStr">
@@ -8728,7 +8182,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C150" s="76" t="inlineStr">
+      <c r="C150" s="74" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8753,11 +8207,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H150" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H150" s="65" t="inlineStr"/>
       <c r="I150" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8769,7 +8219,7 @@
         </is>
       </c>
       <c r="K150" s="23" t="n"/>
-      <c r="L150" s="67" t="inlineStr"/>
+      <c r="L150" s="66" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="53" t="inlineStr">
@@ -8782,7 +8232,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C151" s="76" t="inlineStr">
+      <c r="C151" s="74" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8807,11 +8257,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H151" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H151" s="65" t="inlineStr"/>
       <c r="I151" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8823,7 +8269,7 @@
         </is>
       </c>
       <c r="K151" s="23" t="n"/>
-      <c r="L151" s="67" t="inlineStr"/>
+      <c r="L151" s="66" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="53" t="inlineStr">
@@ -8836,7 +8282,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C152" s="76" t="inlineStr">
+      <c r="C152" s="74" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8861,11 +8307,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H152" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H152" s="65" t="inlineStr"/>
       <c r="I152" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8877,7 +8319,7 @@
         </is>
       </c>
       <c r="K152" s="23" t="n"/>
-      <c r="L152" s="67" t="inlineStr"/>
+      <c r="L152" s="66" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="53" t="inlineStr">
@@ -8890,7 +8332,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C153" s="77" t="inlineStr">
+      <c r="C153" s="75" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -8915,11 +8357,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H153" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H153" s="65" t="inlineStr"/>
       <c r="I153" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8931,7 +8369,7 @@
         </is>
       </c>
       <c r="K153" s="23" t="n"/>
-      <c r="L153" s="67" t="inlineStr"/>
+      <c r="L153" s="66" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="53" t="inlineStr">
@@ -8944,7 +8382,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C154" s="77" t="inlineStr">
+      <c r="C154" s="75" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8969,11 +8407,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H154" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H154" s="65" t="inlineStr"/>
       <c r="I154" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -8985,7 +8419,7 @@
         </is>
       </c>
       <c r="K154" s="23" t="n"/>
-      <c r="L154" s="67" t="inlineStr"/>
+      <c r="L154" s="66" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="53" t="inlineStr">
@@ -8998,7 +8432,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C155" s="76" t="inlineStr">
+      <c r="C155" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9023,11 +8457,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H155" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H155" s="65" t="inlineStr"/>
       <c r="I155" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9039,7 +8469,7 @@
         </is>
       </c>
       <c r="K155" s="23" t="n"/>
-      <c r="L155" s="67" t="inlineStr"/>
+      <c r="L155" s="66" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="53" t="inlineStr">
@@ -9052,7 +8482,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C156" s="78" t="inlineStr">
+      <c r="C156" s="76" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -9077,11 +8507,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H156" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H156" s="65" t="inlineStr"/>
       <c r="I156" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9093,7 +8519,7 @@
         </is>
       </c>
       <c r="K156" s="23" t="n"/>
-      <c r="L156" s="67" t="inlineStr"/>
+      <c r="L156" s="66" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="53" t="inlineStr">
@@ -9106,7 +8532,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C157" s="77" t="inlineStr">
+      <c r="C157" s="75" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9131,11 +8557,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H157" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H157" s="65" t="inlineStr"/>
       <c r="I157" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9147,7 +8569,7 @@
         </is>
       </c>
       <c r="K157" s="23" t="n"/>
-      <c r="L157" s="67" t="inlineStr"/>
+      <c r="L157" s="66" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="53" t="inlineStr">
@@ -9160,7 +8582,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C158" s="78" t="inlineStr">
+      <c r="C158" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9185,11 +8607,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H158" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H158" s="65" t="inlineStr"/>
       <c r="I158" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9197,11 +8615,11 @@
       </c>
       <c r="J158" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K158" s="23" t="n"/>
-      <c r="L158" s="67" t="inlineStr"/>
+      <c r="L158" s="66" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="53" t="inlineStr">
@@ -9214,7 +8632,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C159" s="78" t="inlineStr">
+      <c r="C159" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9239,11 +8657,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H159" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H159" s="65" t="inlineStr"/>
       <c r="I159" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9255,7 +8669,7 @@
         </is>
       </c>
       <c r="K159" s="23" t="n"/>
-      <c r="L159" s="67" t="inlineStr"/>
+      <c r="L159" s="66" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="53" t="inlineStr">
@@ -9268,7 +8682,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C160" s="78" t="inlineStr">
+      <c r="C160" s="76" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -9293,11 +8707,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H160" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H160" s="65" t="inlineStr"/>
       <c r="I160" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9309,7 +8719,7 @@
         </is>
       </c>
       <c r="K160" s="23" t="n"/>
-      <c r="L160" s="67" t="inlineStr"/>
+      <c r="L160" s="66" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="53" t="inlineStr">
@@ -9322,7 +8732,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C161" s="78" t="inlineStr">
+      <c r="C161" s="76" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -9347,15 +8757,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H161" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H161" s="65" t="inlineStr"/>
       <c r="I161" s="65" t="inlineStr"/>
       <c r="J161" s="23" t="inlineStr"/>
       <c r="K161" s="23" t="n"/>
-      <c r="L161" s="67" t="inlineStr"/>
+      <c r="L161" s="66" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="53" t="inlineStr">
@@ -9368,7 +8774,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C162" s="77" t="inlineStr">
+      <c r="C162" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9393,15 +8799,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H162" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H162" s="65" t="inlineStr"/>
       <c r="I162" s="65" t="inlineStr"/>
       <c r="J162" s="23" t="inlineStr"/>
       <c r="K162" s="23" t="n"/>
-      <c r="L162" s="67" t="inlineStr"/>
+      <c r="L162" s="66" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="53" t="inlineStr">
@@ -9414,7 +8816,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C163" s="77" t="inlineStr">
+      <c r="C163" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9439,15 +8841,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H163" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H163" s="65" t="inlineStr"/>
       <c r="I163" s="65" t="inlineStr"/>
       <c r="J163" s="23" t="inlineStr"/>
       <c r="K163" s="23" t="n"/>
-      <c r="L163" s="67" t="inlineStr"/>
+      <c r="L163" s="66" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="53" t="inlineStr">
@@ -9460,7 +8858,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C164" s="77" t="inlineStr">
+      <c r="C164" s="75" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9485,15 +8883,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H164" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H164" s="65" t="inlineStr"/>
       <c r="I164" s="65" t="inlineStr"/>
       <c r="J164" s="23" t="inlineStr"/>
       <c r="K164" s="23" t="n"/>
-      <c r="L164" s="67" t="inlineStr"/>
+      <c r="L164" s="66" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="53" t="inlineStr">
@@ -9506,7 +8900,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C165" s="78" t="inlineStr">
+      <c r="C165" s="76" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -9531,11 +8925,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H165" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H165" s="65" t="inlineStr"/>
       <c r="I165" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9547,7 +8937,7 @@
         </is>
       </c>
       <c r="K165" s="23" t="n"/>
-      <c r="L165" s="67" t="inlineStr"/>
+      <c r="L165" s="66" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="53" t="inlineStr">
@@ -9560,7 +8950,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C166" s="77" t="inlineStr">
+      <c r="C166" s="75" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -9585,15 +8975,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H166" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H166" s="65" t="inlineStr"/>
       <c r="I166" s="65" t="inlineStr"/>
       <c r="J166" s="23" t="inlineStr"/>
       <c r="K166" s="23" t="n"/>
-      <c r="L166" s="67" t="inlineStr"/>
+      <c r="L166" s="66" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="53" t="inlineStr">
@@ -9606,7 +8992,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C167" s="77" t="inlineStr">
+      <c r="C167" s="75" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -9631,15 +9017,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H167" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H167" s="65" t="inlineStr"/>
       <c r="I167" s="65" t="inlineStr"/>
       <c r="J167" s="23" t="inlineStr"/>
       <c r="K167" s="23" t="n"/>
-      <c r="L167" s="67" t="inlineStr"/>
+      <c r="L167" s="66" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="53" t="inlineStr">
@@ -9652,7 +9034,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C168" s="78" t="inlineStr">
+      <c r="C168" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9677,11 +9059,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H168" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H168" s="65" t="inlineStr"/>
       <c r="I168" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9693,7 +9071,7 @@
         </is>
       </c>
       <c r="K168" s="23" t="n"/>
-      <c r="L168" s="67" t="inlineStr"/>
+      <c r="L168" s="66" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="53" t="inlineStr">
@@ -9706,7 +9084,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C169" s="78" t="inlineStr">
+      <c r="C169" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9731,11 +9109,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H169" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H169" s="65" t="inlineStr"/>
       <c r="I169" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9747,7 +9121,7 @@
         </is>
       </c>
       <c r="K169" s="23" t="n"/>
-      <c r="L169" s="67" t="inlineStr"/>
+      <c r="L169" s="66" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="53" t="inlineStr">
@@ -9760,7 +9134,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C170" s="78" t="inlineStr">
+      <c r="C170" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9785,11 +9159,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H170" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H170" s="65" t="inlineStr"/>
       <c r="I170" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9801,7 +9171,7 @@
         </is>
       </c>
       <c r="K170" s="23" t="n"/>
-      <c r="L170" s="67" t="inlineStr"/>
+      <c r="L170" s="66" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="53" t="inlineStr">
@@ -9814,7 +9184,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C171" s="78" t="inlineStr">
+      <c r="C171" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9839,11 +9209,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H171" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H171" s="65" t="inlineStr"/>
       <c r="I171" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9855,7 +9221,7 @@
         </is>
       </c>
       <c r="K171" s="23" t="n"/>
-      <c r="L171" s="67" t="inlineStr"/>
+      <c r="L171" s="66" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="53" t="inlineStr">
@@ -9868,7 +9234,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C172" s="78" t="inlineStr">
+      <c r="C172" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9893,11 +9259,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H172" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H172" s="65" t="inlineStr"/>
       <c r="I172" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9909,7 +9271,7 @@
         </is>
       </c>
       <c r="K172" s="23" t="n"/>
-      <c r="L172" s="67" t="inlineStr"/>
+      <c r="L172" s="66" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="53" t="inlineStr">
@@ -9922,7 +9284,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C173" s="78" t="inlineStr">
+      <c r="C173" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9947,11 +9309,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H173" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H173" s="65" t="inlineStr"/>
       <c r="I173" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9963,7 +9321,7 @@
         </is>
       </c>
       <c r="K173" s="23" t="n"/>
-      <c r="L173" s="67" t="inlineStr"/>
+      <c r="L173" s="66" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="53" t="inlineStr">
@@ -9976,7 +9334,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C174" s="78" t="inlineStr">
+      <c r="C174" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10001,11 +9359,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H174" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H174" s="65" t="inlineStr"/>
       <c r="I174" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10017,7 +9371,7 @@
         </is>
       </c>
       <c r="K174" s="23" t="n"/>
-      <c r="L174" s="67" t="inlineStr"/>
+      <c r="L174" s="66" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="53" t="inlineStr">
@@ -10030,7 +9384,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C175" s="78" t="inlineStr">
+      <c r="C175" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10055,11 +9409,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H175" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H175" s="65" t="inlineStr"/>
       <c r="I175" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10071,7 +9421,7 @@
         </is>
       </c>
       <c r="K175" s="23" t="n"/>
-      <c r="L175" s="67" t="inlineStr"/>
+      <c r="L175" s="66" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="53" t="inlineStr">
@@ -10084,7 +9434,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C176" s="78" t="inlineStr">
+      <c r="C176" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10109,11 +9459,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H176" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H176" s="65" t="inlineStr"/>
       <c r="I176" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10125,7 +9471,7 @@
         </is>
       </c>
       <c r="K176" s="23" t="n"/>
-      <c r="L176" s="67" t="inlineStr"/>
+      <c r="L176" s="66" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="53" t="inlineStr">
@@ -10138,7 +9484,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C177" s="78" t="inlineStr">
+      <c r="C177" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10163,11 +9509,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H177" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H177" s="65" t="inlineStr"/>
       <c r="I177" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10179,7 +9521,7 @@
         </is>
       </c>
       <c r="K177" s="23" t="n"/>
-      <c r="L177" s="67" t="inlineStr"/>
+      <c r="L177" s="66" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="53" t="inlineStr">
@@ -10192,7 +9534,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C178" s="78" t="inlineStr">
+      <c r="C178" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10217,11 +9559,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H178" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H178" s="65" t="inlineStr"/>
       <c r="I178" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10233,7 +9571,7 @@
         </is>
       </c>
       <c r="K178" s="23" t="n"/>
-      <c r="L178" s="67" t="inlineStr"/>
+      <c r="L178" s="66" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="53" t="inlineStr">
@@ -10246,7 +9584,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C179" s="78" t="inlineStr">
+      <c r="C179" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10271,11 +9609,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H179" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H179" s="65" t="inlineStr"/>
       <c r="I179" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10287,7 +9621,7 @@
         </is>
       </c>
       <c r="K179" s="23" t="n"/>
-      <c r="L179" s="67" t="inlineStr"/>
+      <c r="L179" s="66" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="53" t="inlineStr">
@@ -10300,7 +9634,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C180" s="78" t="inlineStr">
+      <c r="C180" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10325,11 +9659,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H180" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H180" s="65" t="inlineStr"/>
       <c r="I180" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10341,7 +9671,7 @@
         </is>
       </c>
       <c r="K180" s="23" t="n"/>
-      <c r="L180" s="67" t="inlineStr"/>
+      <c r="L180" s="66" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="53" t="inlineStr">
@@ -10354,7 +9684,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C181" s="78" t="inlineStr">
+      <c r="C181" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10379,11 +9709,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H181" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H181" s="65" t="inlineStr"/>
       <c r="I181" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10395,7 +9721,7 @@
         </is>
       </c>
       <c r="K181" s="23" t="n"/>
-      <c r="L181" s="67" t="inlineStr"/>
+      <c r="L181" s="66" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="53" t="inlineStr">
@@ -10408,7 +9734,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C182" s="78" t="inlineStr">
+      <c r="C182" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10433,11 +9759,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H182" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H182" s="65" t="inlineStr"/>
       <c r="I182" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10449,7 +9771,7 @@
         </is>
       </c>
       <c r="K182" s="23" t="n"/>
-      <c r="L182" s="67" t="inlineStr"/>
+      <c r="L182" s="66" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="53" t="inlineStr">
@@ -10462,7 +9784,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C183" s="78" t="inlineStr">
+      <c r="C183" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10487,11 +9809,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H183" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H183" s="65" t="inlineStr"/>
       <c r="I183" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10503,7 +9821,7 @@
         </is>
       </c>
       <c r="K183" s="23" t="n"/>
-      <c r="L183" s="67" t="inlineStr"/>
+      <c r="L183" s="66" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="53" t="inlineStr">
@@ -10516,7 +9834,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C184" s="77" t="inlineStr">
+      <c r="C184" s="75" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -10541,11 +9859,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H184" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H184" s="65" t="inlineStr"/>
       <c r="I184" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10557,7 +9871,7 @@
         </is>
       </c>
       <c r="K184" s="23" t="n"/>
-      <c r="L184" s="67" t="inlineStr"/>
+      <c r="L184" s="66" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="53" t="inlineStr">
@@ -10570,7 +9884,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C185" s="78" t="inlineStr">
+      <c r="C185" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10595,11 +9909,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H185" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H185" s="65" t="inlineStr"/>
       <c r="I185" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10611,7 +9921,7 @@
         </is>
       </c>
       <c r="K185" s="23" t="n"/>
-      <c r="L185" s="67" t="inlineStr"/>
+      <c r="L185" s="66" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="53" t="inlineStr">
@@ -10624,7 +9934,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C186" s="78" t="inlineStr">
+      <c r="C186" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10649,11 +9959,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H186" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H186" s="65" t="inlineStr"/>
       <c r="I186" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10665,7 +9971,7 @@
         </is>
       </c>
       <c r="K186" s="23" t="n"/>
-      <c r="L186" s="67" t="inlineStr"/>
+      <c r="L186" s="66" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="53" t="inlineStr">
@@ -10678,7 +9984,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C187" s="78" t="inlineStr">
+      <c r="C187" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10703,11 +10009,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H187" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H187" s="65" t="inlineStr"/>
       <c r="I187" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10719,7 +10021,7 @@
         </is>
       </c>
       <c r="K187" s="23" t="n"/>
-      <c r="L187" s="67" t="inlineStr"/>
+      <c r="L187" s="66" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="53" t="inlineStr">
@@ -10732,7 +10034,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C188" s="78" t="inlineStr">
+      <c r="C188" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10757,11 +10059,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H188" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H188" s="65" t="inlineStr"/>
       <c r="I188" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10773,7 +10071,7 @@
         </is>
       </c>
       <c r="K188" s="23" t="n"/>
-      <c r="L188" s="67" t="inlineStr"/>
+      <c r="L188" s="66" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="53" t="inlineStr">
@@ -10786,7 +10084,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C189" s="78" t="inlineStr">
+      <c r="C189" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10811,11 +10109,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H189" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H189" s="65" t="inlineStr"/>
       <c r="I189" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10827,7 +10121,7 @@
         </is>
       </c>
       <c r="K189" s="23" t="n"/>
-      <c r="L189" s="67" t="inlineStr"/>
+      <c r="L189" s="66" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="53" t="inlineStr">
@@ -10840,7 +10134,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C190" s="78" t="inlineStr">
+      <c r="C190" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10865,11 +10159,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H190" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H190" s="65" t="inlineStr"/>
       <c r="I190" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10881,7 +10171,7 @@
         </is>
       </c>
       <c r="K190" s="23" t="n"/>
-      <c r="L190" s="67" t="inlineStr"/>
+      <c r="L190" s="66" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="53" t="inlineStr">
@@ -10894,7 +10184,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C191" s="78" t="inlineStr">
+      <c r="C191" s="76" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -10919,11 +10209,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H191" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H191" s="65" t="inlineStr"/>
       <c r="I191" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -10935,7 +10221,7 @@
         </is>
       </c>
       <c r="K191" s="23" t="n"/>
-      <c r="L191" s="67" t="inlineStr"/>
+      <c r="L191" s="66" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="53" t="inlineStr">
@@ -10948,7 +10234,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C192" s="78" t="inlineStr">
+      <c r="C192" s="76" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -10973,15 +10259,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H192" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H192" s="65" t="inlineStr"/>
       <c r="I192" s="65" t="inlineStr"/>
       <c r="J192" s="23" t="inlineStr"/>
       <c r="K192" s="23" t="n"/>
-      <c r="L192" s="67" t="inlineStr"/>
+      <c r="L192" s="66" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="53" t="inlineStr">
@@ -10994,7 +10276,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C193" s="77" t="inlineStr">
+      <c r="C193" s="75" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -11019,15 +10301,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H193" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H193" s="65" t="inlineStr"/>
       <c r="I193" s="65" t="inlineStr"/>
       <c r="J193" s="23" t="inlineStr"/>
       <c r="K193" s="23" t="n"/>
-      <c r="L193" s="67" t="inlineStr"/>
+      <c r="L193" s="66" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="53" t="inlineStr">
@@ -11040,7 +10318,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C194" s="78" t="inlineStr">
+      <c r="C194" s="76" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -11065,15 +10343,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H194" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H194" s="65" t="inlineStr"/>
       <c r="I194" s="65" t="inlineStr"/>
       <c r="J194" s="23" t="inlineStr"/>
       <c r="K194" s="23" t="n"/>
-      <c r="L194" s="67" t="inlineStr"/>
+      <c r="L194" s="66" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="53" t="inlineStr">
@@ -11086,7 +10360,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C195" s="78" t="inlineStr">
+      <c r="C195" s="76" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -11111,15 +10385,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H195" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H195" s="65" t="inlineStr"/>
       <c r="I195" s="65" t="inlineStr"/>
       <c r="J195" s="23" t="inlineStr"/>
       <c r="K195" s="23" t="n"/>
-      <c r="L195" s="67" t="inlineStr"/>
+      <c r="L195" s="66" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="53" t="inlineStr">
@@ -11132,7 +10402,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C196" s="77" t="inlineStr">
+      <c r="C196" s="75" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -11157,15 +10427,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H196" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H196" s="65" t="inlineStr"/>
       <c r="I196" s="65" t="inlineStr"/>
       <c r="J196" s="23" t="inlineStr"/>
       <c r="K196" s="23" t="n"/>
-      <c r="L196" s="67" t="inlineStr"/>
+      <c r="L196" s="66" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="53" t="inlineStr">
@@ -11178,7 +10444,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C197" s="78" t="inlineStr">
+      <c r="C197" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11203,15 +10469,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H197" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H197" s="65" t="inlineStr"/>
       <c r="I197" s="65" t="inlineStr"/>
       <c r="J197" s="23" t="inlineStr"/>
       <c r="K197" s="23" t="n"/>
-      <c r="L197" s="67" t="inlineStr"/>
+      <c r="L197" s="66" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="53" t="inlineStr">
@@ -11224,7 +10486,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C198" s="78" t="inlineStr">
+      <c r="C198" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11249,15 +10511,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H198" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H198" s="65" t="inlineStr"/>
       <c r="I198" s="65" t="inlineStr"/>
       <c r="J198" s="23" t="inlineStr"/>
       <c r="K198" s="23" t="n"/>
-      <c r="L198" s="67" t="inlineStr"/>
+      <c r="L198" s="66" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="53" t="inlineStr">
@@ -11270,7 +10528,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C199" s="77" t="inlineStr">
+      <c r="C199" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -11295,15 +10553,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H199" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H199" s="65" t="inlineStr"/>
       <c r="I199" s="65" t="inlineStr"/>
       <c r="J199" s="23" t="inlineStr"/>
       <c r="K199" s="23" t="n"/>
-      <c r="L199" s="67" t="inlineStr"/>
+      <c r="L199" s="66" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="53" t="inlineStr">
@@ -11316,7 +10570,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C200" s="77" t="inlineStr">
+      <c r="C200" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -11341,15 +10595,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H200" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H200" s="65" t="inlineStr"/>
       <c r="I200" s="65" t="inlineStr"/>
       <c r="J200" s="23" t="inlineStr"/>
       <c r="K200" s="23" t="n"/>
-      <c r="L200" s="67" t="inlineStr"/>
+      <c r="L200" s="66" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="53" t="inlineStr">
@@ -11362,7 +10612,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C201" s="77" t="inlineStr">
+      <c r="C201" s="75" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -11387,15 +10637,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H201" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H201" s="65" t="inlineStr"/>
       <c r="I201" s="65" t="inlineStr"/>
       <c r="J201" s="23" t="inlineStr"/>
       <c r="K201" s="23" t="n"/>
-      <c r="L201" s="67" t="inlineStr"/>
+      <c r="L201" s="66" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="53" t="inlineStr">
@@ -11408,7 +10654,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C202" s="78" t="inlineStr">
+      <c r="C202" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11433,11 +10679,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H202" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H202" s="65" t="inlineStr"/>
       <c r="I202" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11449,7 +10691,7 @@
         </is>
       </c>
       <c r="K202" s="23" t="n"/>
-      <c r="L202" s="67" t="inlineStr"/>
+      <c r="L202" s="66" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="53" t="inlineStr">
@@ -11462,7 +10704,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C203" s="78" t="inlineStr">
+      <c r="C203" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11487,11 +10729,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H203" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H203" s="65" t="inlineStr"/>
       <c r="I203" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11503,7 +10741,7 @@
         </is>
       </c>
       <c r="K203" s="23" t="n"/>
-      <c r="L203" s="67" t="inlineStr"/>
+      <c r="L203" s="66" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="53" t="inlineStr">
@@ -11516,7 +10754,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C204" s="78" t="inlineStr">
+      <c r="C204" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11541,11 +10779,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H204" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H204" s="65" t="inlineStr"/>
       <c r="I204" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11557,7 +10791,7 @@
         </is>
       </c>
       <c r="K204" s="23" t="n"/>
-      <c r="L204" s="67" t="inlineStr"/>
+      <c r="L204" s="66" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="53" t="inlineStr">
@@ -11570,7 +10804,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C205" s="78" t="inlineStr">
+      <c r="C205" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11595,11 +10829,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H205" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H205" s="65" t="inlineStr"/>
       <c r="I205" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11611,7 +10841,7 @@
         </is>
       </c>
       <c r="K205" s="23" t="n"/>
-      <c r="L205" s="67" t="inlineStr"/>
+      <c r="L205" s="66" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="53" t="inlineStr">
@@ -11624,7 +10854,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C206" s="78" t="inlineStr">
+      <c r="C206" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11649,11 +10879,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H206" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H206" s="65" t="inlineStr"/>
       <c r="I206" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11665,7 +10891,7 @@
         </is>
       </c>
       <c r="K206" s="23" t="n"/>
-      <c r="L206" s="67" t="inlineStr"/>
+      <c r="L206" s="66" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="53" t="inlineStr">
@@ -11678,7 +10904,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C207" s="78" t="inlineStr">
+      <c r="C207" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11703,11 +10929,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H207" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H207" s="65" t="inlineStr"/>
       <c r="I207" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11719,7 +10941,7 @@
         </is>
       </c>
       <c r="K207" s="23" t="n"/>
-      <c r="L207" s="67" t="inlineStr"/>
+      <c r="L207" s="66" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="53" t="inlineStr">
@@ -11732,7 +10954,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C208" s="78" t="inlineStr">
+      <c r="C208" s="76" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -11757,11 +10979,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H208" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H208" s="65" t="inlineStr"/>
       <c r="I208" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11773,7 +10991,7 @@
         </is>
       </c>
       <c r="K208" s="23" t="n"/>
-      <c r="L208" s="67" t="inlineStr"/>
+      <c r="L208" s="66" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="53" t="inlineStr">
@@ -11786,7 +11004,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C209" s="77" t="inlineStr">
+      <c r="C209" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -11811,11 +11029,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H209" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H209" s="65" t="inlineStr"/>
       <c r="I209" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11827,7 +11041,7 @@
         </is>
       </c>
       <c r="K209" s="23" t="n"/>
-      <c r="L209" s="67" t="inlineStr"/>
+      <c r="L209" s="66" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="53" t="inlineStr">
@@ -11840,7 +11054,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C210" s="77" t="inlineStr">
+      <c r="C210" s="75" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11865,11 +11079,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H210" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H210" s="65" t="inlineStr"/>
       <c r="I210" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11881,7 +11091,7 @@
         </is>
       </c>
       <c r="K210" s="23" t="n"/>
-      <c r="L210" s="67" t="inlineStr"/>
+      <c r="L210" s="66" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="53" t="inlineStr">
@@ -11894,7 +11104,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C211" s="78" t="inlineStr">
+      <c r="C211" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11919,11 +11129,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H211" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H211" s="65" t="inlineStr"/>
       <c r="I211" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11935,7 +11141,7 @@
         </is>
       </c>
       <c r="K211" s="23" t="n"/>
-      <c r="L211" s="67" t="inlineStr"/>
+      <c r="L211" s="66" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="53" t="inlineStr">
@@ -11948,7 +11154,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C212" s="76" t="inlineStr">
+      <c r="C212" s="74" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -11973,11 +11179,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H212" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H212" s="65" t="inlineStr"/>
       <c r="I212" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -11989,7 +11191,7 @@
         </is>
       </c>
       <c r="K212" s="23" t="n"/>
-      <c r="L212" s="67" t="inlineStr"/>
+      <c r="L212" s="66" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="53" t="inlineStr">
@@ -12002,7 +11204,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C213" s="76" t="inlineStr">
+      <c r="C213" s="74" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -12027,11 +11229,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H213" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H213" s="65" t="inlineStr"/>
       <c r="I213" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12043,7 +11241,7 @@
         </is>
       </c>
       <c r="K213" s="23" t="n"/>
-      <c r="L213" s="67" t="inlineStr"/>
+      <c r="L213" s="66" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="53" t="inlineStr">
@@ -12056,7 +11254,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C214" s="78" t="inlineStr">
+      <c r="C214" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -12081,11 +11279,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H214" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H214" s="65" t="inlineStr"/>
       <c r="I214" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12097,7 +11291,7 @@
         </is>
       </c>
       <c r="K214" s="23" t="n"/>
-      <c r="L214" s="67" t="inlineStr"/>
+      <c r="L214" s="66" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="53" t="inlineStr">
@@ -12110,7 +11304,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C215" s="78" t="inlineStr">
+      <c r="C215" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -12135,11 +11329,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H215" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H215" s="65" t="inlineStr"/>
       <c r="I215" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12151,7 +11341,7 @@
         </is>
       </c>
       <c r="K215" s="23" t="n"/>
-      <c r="L215" s="67" t="inlineStr"/>
+      <c r="L215" s="66" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="53" t="inlineStr">
@@ -12160,7 +11350,7 @@
         </is>
       </c>
       <c r="B216" s="23" t="inlineStr"/>
-      <c r="C216" s="76" t="inlineStr">
+      <c r="C216" s="74" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -12179,7 +11369,7 @@
       <c r="I216" s="65" t="inlineStr"/>
       <c r="J216" s="23" t="inlineStr"/>
       <c r="K216" s="23" t="n"/>
-      <c r="L216" s="67" t="inlineStr"/>
+      <c r="L216" s="66" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="53" t="inlineStr">
@@ -12192,7 +11382,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C217" s="76" t="inlineStr">
+      <c r="C217" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12217,11 +11407,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H217" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H217" s="65" t="inlineStr"/>
       <c r="I217" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12233,7 +11419,7 @@
         </is>
       </c>
       <c r="K217" s="23" t="n"/>
-      <c r="L217" s="67" t="inlineStr"/>
+      <c r="L217" s="66" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="53" t="inlineStr">
@@ -12246,7 +11432,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C218" s="76" t="inlineStr">
+      <c r="C218" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12271,11 +11457,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H218" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H218" s="65" t="inlineStr"/>
       <c r="I218" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12287,7 +11469,7 @@
         </is>
       </c>
       <c r="K218" s="23" t="n"/>
-      <c r="L218" s="67" t="inlineStr"/>
+      <c r="L218" s="66" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="53" t="inlineStr">
@@ -12300,7 +11482,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C219" s="76" t="inlineStr">
+      <c r="C219" s="74" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -12325,11 +11507,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H219" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H219" s="65" t="inlineStr"/>
       <c r="I219" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12341,7 +11519,7 @@
         </is>
       </c>
       <c r="K219" s="23" t="n"/>
-      <c r="L219" s="67" t="inlineStr"/>
+      <c r="L219" s="66" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="53" t="inlineStr">
@@ -12354,7 +11532,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C220" s="76" t="inlineStr">
+      <c r="C220" s="74" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -12379,11 +11557,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H220" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H220" s="65" t="inlineStr"/>
       <c r="I220" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12395,7 +11569,7 @@
         </is>
       </c>
       <c r="K220" s="23" t="n"/>
-      <c r="L220" s="67" t="inlineStr"/>
+      <c r="L220" s="66" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="53" t="inlineStr">
@@ -12408,7 +11582,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C221" s="77" t="inlineStr">
+      <c r="C221" s="75" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -12433,11 +11607,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H221" s="65" t="inlineStr"/>
       <c r="I221" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12449,7 +11619,7 @@
         </is>
       </c>
       <c r="K221" s="23" t="n"/>
-      <c r="L221" s="67" t="inlineStr"/>
+      <c r="L221" s="66" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="53" t="inlineStr">
@@ -12462,7 +11632,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C222" s="78" t="inlineStr">
+      <c r="C222" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -12487,11 +11657,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H222" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H222" s="65" t="inlineStr"/>
       <c r="I222" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12503,7 +11669,7 @@
         </is>
       </c>
       <c r="K222" s="23" t="n"/>
-      <c r="L222" s="67" t="inlineStr"/>
+      <c r="L222" s="66" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="53" t="inlineStr">
@@ -12516,7 +11682,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C223" s="76" t="inlineStr">
+      <c r="C223" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12541,11 +11707,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H223" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H223" s="65" t="inlineStr"/>
       <c r="I223" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12557,7 +11719,7 @@
         </is>
       </c>
       <c r="K223" s="23" t="n"/>
-      <c r="L223" s="67" t="inlineStr"/>
+      <c r="L223" s="66" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="53" t="inlineStr">
@@ -12570,7 +11732,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C224" s="76" t="inlineStr">
+      <c r="C224" s="74" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -12595,11 +11757,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H224" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H224" s="65" t="inlineStr"/>
       <c r="I224" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12611,7 +11769,7 @@
         </is>
       </c>
       <c r="K224" s="23" t="n"/>
-      <c r="L224" s="67" t="inlineStr"/>
+      <c r="L224" s="66" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="53" t="inlineStr">
@@ -12624,7 +11782,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C225" s="76" t="inlineStr">
+      <c r="C225" s="74" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -12649,11 +11807,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H225" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H225" s="65" t="inlineStr"/>
       <c r="I225" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12665,7 +11819,7 @@
         </is>
       </c>
       <c r="K225" s="23" t="n"/>
-      <c r="L225" s="67" t="inlineStr"/>
+      <c r="L225" s="66" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="53" t="inlineStr">
@@ -12678,7 +11832,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C226" s="76" t="inlineStr">
+      <c r="C226" s="74" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -12703,11 +11857,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H226" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H226" s="65" t="inlineStr"/>
       <c r="I226" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12719,7 +11869,7 @@
         </is>
       </c>
       <c r="K226" s="23" t="n"/>
-      <c r="L226" s="67" t="inlineStr"/>
+      <c r="L226" s="66" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="53" t="inlineStr">
@@ -12732,7 +11882,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C227" s="76" t="inlineStr">
+      <c r="C227" s="74" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -12757,11 +11907,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H227" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H227" s="65" t="inlineStr"/>
       <c r="I227" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12773,7 +11919,7 @@
         </is>
       </c>
       <c r="K227" s="23" t="n"/>
-      <c r="L227" s="67" t="inlineStr"/>
+      <c r="L227" s="66" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="53" t="inlineStr">
@@ -12786,7 +11932,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C228" s="76" t="inlineStr">
+      <c r="C228" s="74" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -12811,11 +11957,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H228" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H228" s="65" t="inlineStr"/>
       <c r="I228" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12827,7 +11969,7 @@
         </is>
       </c>
       <c r="K228" s="23" t="n"/>
-      <c r="L228" s="67" t="inlineStr"/>
+      <c r="L228" s="66" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="53" t="inlineStr">
@@ -12840,7 +11982,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C229" s="76" t="inlineStr">
+      <c r="C229" s="74" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -12865,11 +12007,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H229" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H229" s="65" t="inlineStr"/>
       <c r="I229" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12881,7 +12019,7 @@
         </is>
       </c>
       <c r="K229" s="23" t="n"/>
-      <c r="L229" s="67" t="inlineStr"/>
+      <c r="L229" s="66" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="53" t="inlineStr">
@@ -12890,7 +12028,7 @@
         </is>
       </c>
       <c r="B230" s="23" t="inlineStr"/>
-      <c r="C230" s="78" t="inlineStr">
+      <c r="C230" s="76" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -12909,7 +12047,7 @@
       <c r="I230" s="65" t="inlineStr"/>
       <c r="J230" s="23" t="inlineStr"/>
       <c r="K230" s="23" t="n"/>
-      <c r="L230" s="67" t="inlineStr"/>
+      <c r="L230" s="66" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="53" t="inlineStr">
@@ -12918,7 +12056,7 @@
         </is>
       </c>
       <c r="B231" s="23" t="inlineStr"/>
-      <c r="C231" s="78" t="inlineStr">
+      <c r="C231" s="76" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -12937,7 +12075,7 @@
       <c r="I231" s="65" t="inlineStr"/>
       <c r="J231" s="23" t="inlineStr"/>
       <c r="K231" s="23" t="n"/>
-      <c r="L231" s="67" t="inlineStr"/>
+      <c r="L231" s="66" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="53" t="inlineStr">
@@ -12950,7 +12088,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C232" s="76" t="inlineStr">
+      <c r="C232" s="74" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -12975,11 +12113,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H232" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H232" s="65" t="inlineStr"/>
       <c r="I232" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -12991,7 +12125,7 @@
         </is>
       </c>
       <c r="K232" s="23" t="n"/>
-      <c r="L232" s="67" t="inlineStr"/>
+      <c r="L232" s="66" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="53" t="inlineStr">
@@ -13004,7 +12138,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C233" s="76" t="inlineStr">
+      <c r="C233" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13029,11 +12163,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H233" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H233" s="65" t="inlineStr"/>
       <c r="I233" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13045,7 +12175,7 @@
         </is>
       </c>
       <c r="K233" s="23" t="n"/>
-      <c r="L233" s="67" t="inlineStr"/>
+      <c r="L233" s="66" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="53" t="inlineStr">
@@ -13058,7 +12188,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C234" s="76" t="inlineStr">
+      <c r="C234" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13083,11 +12213,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H234" s="65" t="inlineStr"/>
       <c r="I234" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13099,7 +12225,7 @@
         </is>
       </c>
       <c r="K234" s="23" t="n"/>
-      <c r="L234" s="67" t="inlineStr"/>
+      <c r="L234" s="66" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="53" t="inlineStr">
@@ -13112,7 +12238,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C235" s="76" t="inlineStr">
+      <c r="C235" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13137,11 +12263,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H235" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H235" s="65" t="inlineStr"/>
       <c r="I235" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13153,7 +12275,7 @@
         </is>
       </c>
       <c r="K235" s="23" t="n"/>
-      <c r="L235" s="67" t="inlineStr"/>
+      <c r="L235" s="66" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="53" t="inlineStr">
@@ -13166,7 +12288,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C236" s="76" t="inlineStr">
+      <c r="C236" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13191,11 +12313,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H236" s="65" t="inlineStr"/>
       <c r="I236" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13207,7 +12325,7 @@
         </is>
       </c>
       <c r="K236" s="23" t="n"/>
-      <c r="L236" s="67" t="inlineStr"/>
+      <c r="L236" s="66" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="53" t="inlineStr">
@@ -13220,7 +12338,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C237" s="76" t="inlineStr">
+      <c r="C237" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13245,11 +12363,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H237" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H237" s="65" t="inlineStr"/>
       <c r="I237" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13261,7 +12375,7 @@
         </is>
       </c>
       <c r="K237" s="23" t="n"/>
-      <c r="L237" s="67" t="inlineStr"/>
+      <c r="L237" s="66" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="53" t="inlineStr">
@@ -13274,7 +12388,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C238" s="76" t="inlineStr">
+      <c r="C238" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13299,11 +12413,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H238" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H238" s="65" t="inlineStr"/>
       <c r="I238" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13315,7 +12425,7 @@
         </is>
       </c>
       <c r="K238" s="23" t="n"/>
-      <c r="L238" s="67" t="inlineStr"/>
+      <c r="L238" s="66" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="53" t="inlineStr">
@@ -13328,7 +12438,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C239" s="76" t="inlineStr">
+      <c r="C239" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13353,11 +12463,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H239" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H239" s="65" t="inlineStr"/>
       <c r="I239" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13369,7 +12475,7 @@
         </is>
       </c>
       <c r="K239" s="23" t="n"/>
-      <c r="L239" s="67" t="inlineStr"/>
+      <c r="L239" s="66" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="53" t="inlineStr">
@@ -13378,7 +12484,7 @@
         </is>
       </c>
       <c r="B240" s="23" t="inlineStr"/>
-      <c r="C240" s="78" t="inlineStr">
+      <c r="C240" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -13397,7 +12503,7 @@
       <c r="I240" s="65" t="inlineStr"/>
       <c r="J240" s="23" t="inlineStr"/>
       <c r="K240" s="23" t="n"/>
-      <c r="L240" s="67" t="inlineStr"/>
+      <c r="L240" s="66" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="53" t="inlineStr">
@@ -13410,7 +12516,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C241" s="76" t="inlineStr">
+      <c r="C241" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13435,11 +12541,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H241" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H241" s="65" t="inlineStr"/>
       <c r="I241" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13451,7 +12553,7 @@
         </is>
       </c>
       <c r="K241" s="23" t="n"/>
-      <c r="L241" s="67" t="inlineStr"/>
+      <c r="L241" s="66" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="53" t="inlineStr">
@@ -13464,7 +12566,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C242" s="76" t="inlineStr">
+      <c r="C242" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13489,11 +12591,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H242" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H242" s="65" t="inlineStr"/>
       <c r="I242" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13505,7 +12603,7 @@
         </is>
       </c>
       <c r="K242" s="23" t="n"/>
-      <c r="L242" s="67" t="inlineStr"/>
+      <c r="L242" s="66" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="53" t="inlineStr">
@@ -13518,7 +12616,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C243" s="76" t="inlineStr">
+      <c r="C243" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13543,11 +12641,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H243" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H243" s="65" t="inlineStr"/>
       <c r="I243" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13559,7 +12653,7 @@
         </is>
       </c>
       <c r="K243" s="23" t="n"/>
-      <c r="L243" s="67" t="inlineStr"/>
+      <c r="L243" s="66" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="53" t="inlineStr">
@@ -13572,7 +12666,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C244" s="77" t="inlineStr">
+      <c r="C244" s="75" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -13597,11 +12691,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H244" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H244" s="65" t="inlineStr"/>
       <c r="I244" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13613,7 +12703,7 @@
         </is>
       </c>
       <c r="K244" s="23" t="n"/>
-      <c r="L244" s="67" t="inlineStr"/>
+      <c r="L244" s="66" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="53" t="inlineStr">
@@ -13622,7 +12712,7 @@
         </is>
       </c>
       <c r="B245" s="23" t="inlineStr"/>
-      <c r="C245" s="76" t="inlineStr">
+      <c r="C245" s="74" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -13641,7 +12731,7 @@
       <c r="I245" s="65" t="inlineStr"/>
       <c r="J245" s="23" t="inlineStr"/>
       <c r="K245" s="23" t="n"/>
-      <c r="L245" s="67" t="inlineStr"/>
+      <c r="L245" s="66" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="53" t="inlineStr">
@@ -13654,7 +12744,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C246" s="77" t="inlineStr">
+      <c r="C246" s="75" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -13679,11 +12769,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H246" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H246" s="65" t="inlineStr"/>
       <c r="I246" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13695,7 +12781,7 @@
         </is>
       </c>
       <c r="K246" s="23" t="n"/>
-      <c r="L246" s="67" t="inlineStr"/>
+      <c r="L246" s="66" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="53" t="inlineStr">
@@ -13708,7 +12794,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C247" s="78" t="inlineStr">
+      <c r="C247" s="76" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -13733,15 +12819,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H247" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H247" s="65" t="inlineStr"/>
       <c r="I247" s="65" t="inlineStr"/>
       <c r="J247" s="23" t="inlineStr"/>
       <c r="K247" s="23" t="n"/>
-      <c r="L247" s="67" t="inlineStr"/>
+      <c r="L247" s="66" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="53" t="inlineStr">
@@ -13754,7 +12836,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C248" s="77" t="inlineStr">
+      <c r="C248" s="75" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -13779,11 +12861,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H248" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H248" s="65" t="inlineStr"/>
       <c r="I248" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13795,7 +12873,7 @@
         </is>
       </c>
       <c r="K248" s="23" t="n"/>
-      <c r="L248" s="67" t="inlineStr"/>
+      <c r="L248" s="66" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="53" t="inlineStr">
@@ -13808,7 +12886,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C249" s="77" t="inlineStr">
+      <c r="C249" s="75" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -13833,11 +12911,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H249" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H249" s="65" t="inlineStr"/>
       <c r="I249" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13849,7 +12923,7 @@
         </is>
       </c>
       <c r="K249" s="23" t="n"/>
-      <c r="L249" s="67" t="inlineStr"/>
+      <c r="L249" s="66" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="53" t="inlineStr">
@@ -13862,7 +12936,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C250" s="77" t="inlineStr">
+      <c r="C250" s="75" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -13887,11 +12961,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H250" s="65" t="inlineStr"/>
       <c r="I250" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13903,7 +12973,7 @@
         </is>
       </c>
       <c r="K250" s="23" t="n"/>
-      <c r="L250" s="67" t="inlineStr"/>
+      <c r="L250" s="66" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="53" t="inlineStr">
@@ -13916,7 +12986,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C251" s="77" t="inlineStr">
+      <c r="C251" s="75" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -13941,11 +13011,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H251" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H251" s="65" t="inlineStr"/>
       <c r="I251" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13957,7 +13023,7 @@
         </is>
       </c>
       <c r="K251" s="23" t="n"/>
-      <c r="L251" s="67" t="inlineStr"/>
+      <c r="L251" s="66" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="53" t="inlineStr">
@@ -13970,7 +13036,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C252" s="78" t="inlineStr">
+      <c r="C252" s="76" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -13995,11 +13061,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H252" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H252" s="65" t="inlineStr"/>
       <c r="I252" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14011,7 +13073,7 @@
         </is>
       </c>
       <c r="K252" s="23" t="n"/>
-      <c r="L252" s="67" t="inlineStr"/>
+      <c r="L252" s="66" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="53" t="inlineStr">
@@ -14024,7 +13086,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C253" s="78" t="inlineStr">
+      <c r="C253" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14049,11 +13111,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H253" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H253" s="65" t="inlineStr"/>
       <c r="I253" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14065,7 +13123,7 @@
         </is>
       </c>
       <c r="K253" s="23" t="n"/>
-      <c r="L253" s="67" t="inlineStr"/>
+      <c r="L253" s="66" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="53" t="inlineStr">
@@ -14078,7 +13136,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C254" s="77" t="inlineStr">
+      <c r="C254" s="75" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -14103,11 +13161,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H254" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H254" s="65" t="inlineStr"/>
       <c r="I254" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14119,7 +13173,7 @@
         </is>
       </c>
       <c r="K254" s="23" t="n"/>
-      <c r="L254" s="67" t="inlineStr"/>
+      <c r="L254" s="66" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="53" t="inlineStr">
@@ -14132,7 +13186,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C255" s="77" t="inlineStr">
+      <c r="C255" s="75" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -14157,11 +13211,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H255" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H255" s="65" t="inlineStr"/>
       <c r="I255" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14173,7 +13223,7 @@
         </is>
       </c>
       <c r="K255" s="23" t="n"/>
-      <c r="L255" s="67" t="inlineStr"/>
+      <c r="L255" s="66" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="53" t="inlineStr">
@@ -14186,7 +13236,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C256" s="78" t="inlineStr">
+      <c r="C256" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14211,11 +13261,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H256" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H256" s="65" t="inlineStr"/>
       <c r="I256" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14227,7 +13273,7 @@
         </is>
       </c>
       <c r="K256" s="23" t="n"/>
-      <c r="L256" s="67" t="inlineStr"/>
+      <c r="L256" s="66" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="53" t="inlineStr">
@@ -14240,7 +13286,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C257" s="77" t="inlineStr">
+      <c r="C257" s="75" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -14265,11 +13311,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H257" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H257" s="65" t="inlineStr"/>
       <c r="I257" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14281,7 +13323,7 @@
         </is>
       </c>
       <c r="K257" s="23" t="n"/>
-      <c r="L257" s="67" t="inlineStr"/>
+      <c r="L257" s="66" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="53" t="inlineStr">
@@ -14294,7 +13336,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C258" s="76" t="inlineStr">
+      <c r="C258" s="74" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -14319,11 +13361,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H258" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H258" s="65" t="inlineStr"/>
       <c r="I258" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14335,7 +13373,7 @@
         </is>
       </c>
       <c r="K258" s="23" t="n"/>
-      <c r="L258" s="67" t="inlineStr"/>
+      <c r="L258" s="66" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="53" t="inlineStr">
@@ -14348,7 +13386,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C259" s="77" t="inlineStr">
+      <c r="C259" s="75" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -14373,11 +13411,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H259" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H259" s="65" t="inlineStr"/>
       <c r="I259" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14389,7 +13423,7 @@
         </is>
       </c>
       <c r="K259" s="23" t="n"/>
-      <c r="L259" s="67" t="inlineStr"/>
+      <c r="L259" s="66" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="53" t="inlineStr">
@@ -14402,7 +13436,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C260" s="77" t="inlineStr">
+      <c r="C260" s="75" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -14427,11 +13461,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H260" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H260" s="65" t="inlineStr"/>
       <c r="I260" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14443,7 +13473,7 @@
         </is>
       </c>
       <c r="K260" s="23" t="n"/>
-      <c r="L260" s="67" t="inlineStr"/>
+      <c r="L260" s="66" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="53" t="inlineStr">
@@ -14456,7 +13486,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C261" s="77" t="inlineStr">
+      <c r="C261" s="75" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -14481,11 +13511,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H261" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H261" s="65" t="inlineStr"/>
       <c r="I261" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14497,7 +13523,7 @@
         </is>
       </c>
       <c r="K261" s="23" t="n"/>
-      <c r="L261" s="67" t="inlineStr"/>
+      <c r="L261" s="66" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="53" t="inlineStr">
@@ -14510,7 +13536,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C262" s="76" t="inlineStr">
+      <c r="C262" s="74" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -14535,11 +13561,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H262" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H262" s="65" t="inlineStr"/>
       <c r="I262" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14551,7 +13573,7 @@
         </is>
       </c>
       <c r="K262" s="23" t="n"/>
-      <c r="L262" s="67" t="inlineStr"/>
+      <c r="L262" s="66" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="53" t="inlineStr">
@@ -14564,7 +13586,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C263" s="76" t="inlineStr">
+      <c r="C263" s="74" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -14589,11 +13611,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H263" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H263" s="65" t="inlineStr"/>
       <c r="I263" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14605,7 +13623,7 @@
         </is>
       </c>
       <c r="K263" s="23" t="n"/>
-      <c r="L263" s="67" t="inlineStr"/>
+      <c r="L263" s="66" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="53" t="inlineStr">
@@ -14618,7 +13636,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C264" s="76" t="inlineStr">
+      <c r="C264" s="74" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -14643,11 +13661,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H264" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H264" s="65" t="inlineStr"/>
       <c r="I264" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14659,7 +13673,7 @@
         </is>
       </c>
       <c r="K264" s="23" t="n"/>
-      <c r="L264" s="67" t="inlineStr"/>
+      <c r="L264" s="66" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="53" t="inlineStr">
@@ -14672,7 +13686,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C265" s="76" t="inlineStr">
+      <c r="C265" s="74" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -14697,11 +13711,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H265" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H265" s="65" t="inlineStr"/>
       <c r="I265" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14713,7 +13723,7 @@
         </is>
       </c>
       <c r="K265" s="23" t="n"/>
-      <c r="L265" s="67" t="inlineStr"/>
+      <c r="L265" s="66" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="53" t="inlineStr">
@@ -14726,7 +13736,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C266" s="76" t="inlineStr">
+      <c r="C266" s="74" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -14751,11 +13761,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H266" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H266" s="65" t="inlineStr"/>
       <c r="I266" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14767,7 +13773,7 @@
         </is>
       </c>
       <c r="K266" s="23" t="n"/>
-      <c r="L266" s="67" t="inlineStr"/>
+      <c r="L266" s="66" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="53" t="inlineStr">
@@ -14780,7 +13786,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C267" s="76" t="inlineStr">
+      <c r="C267" s="74" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -14805,11 +13811,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H267" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H267" s="65" t="inlineStr"/>
       <c r="I267" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14821,7 +13823,7 @@
         </is>
       </c>
       <c r="K267" s="23" t="n"/>
-      <c r="L267" s="67" t="inlineStr"/>
+      <c r="L267" s="66" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="53" t="inlineStr">
@@ -14834,7 +13836,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C268" s="76" t="inlineStr">
+      <c r="C268" s="74" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -14859,11 +13861,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H268" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H268" s="65" t="inlineStr"/>
       <c r="I268" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14875,7 +13873,7 @@
         </is>
       </c>
       <c r="K268" s="23" t="n"/>
-      <c r="L268" s="67" t="inlineStr"/>
+      <c r="L268" s="66" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="53" t="inlineStr">
@@ -14888,7 +13886,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C269" s="76" t="inlineStr">
+      <c r="C269" s="74" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -14913,11 +13911,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H269" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H269" s="65" t="inlineStr"/>
       <c r="I269" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14929,7 +13923,7 @@
         </is>
       </c>
       <c r="K269" s="23" t="n"/>
-      <c r="L269" s="67" t="inlineStr"/>
+      <c r="L269" s="66" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="53" t="inlineStr">
@@ -14942,7 +13936,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C270" s="76" t="inlineStr">
+      <c r="C270" s="74" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -14967,11 +13961,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H270" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H270" s="65" t="inlineStr"/>
       <c r="I270" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -14983,7 +13973,7 @@
         </is>
       </c>
       <c r="K270" s="23" t="n"/>
-      <c r="L270" s="67" t="inlineStr"/>
+      <c r="L270" s="66" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="53" t="inlineStr">
@@ -14996,7 +13986,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C271" s="76" t="inlineStr">
+      <c r="C271" s="74" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -15021,11 +14011,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H271" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H271" s="65" t="inlineStr"/>
       <c r="I271" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15037,7 +14023,7 @@
         </is>
       </c>
       <c r="K271" s="23" t="n"/>
-      <c r="L271" s="67" t="inlineStr"/>
+      <c r="L271" s="66" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="53" t="inlineStr">
@@ -15050,7 +14036,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C272" s="76" t="inlineStr">
+      <c r="C272" s="74" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -15075,11 +14061,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H272" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H272" s="65" t="inlineStr"/>
       <c r="I272" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15091,7 +14073,7 @@
         </is>
       </c>
       <c r="K272" s="23" t="n"/>
-      <c r="L272" s="67" t="inlineStr"/>
+      <c r="L272" s="66" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="53" t="inlineStr">
@@ -15104,7 +14086,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C273" s="76" t="inlineStr">
+      <c r="C273" s="74" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -15129,11 +14111,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H273" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H273" s="65" t="inlineStr"/>
       <c r="I273" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15145,7 +14123,7 @@
         </is>
       </c>
       <c r="K273" s="23" t="n"/>
-      <c r="L273" s="67" t="inlineStr"/>
+      <c r="L273" s="66" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="53" t="inlineStr">
@@ -15158,7 +14136,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C274" s="77" t="inlineStr">
+      <c r="C274" s="75" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -15183,11 +14161,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H274" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H274" s="65" t="inlineStr"/>
       <c r="I274" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15199,7 +14173,7 @@
         </is>
       </c>
       <c r="K274" s="23" t="n"/>
-      <c r="L274" s="67" t="inlineStr"/>
+      <c r="L274" s="66" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="53" t="inlineStr">
@@ -15212,7 +14186,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C275" s="76" t="inlineStr">
+      <c r="C275" s="74" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -15237,11 +14211,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H275" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H275" s="65" t="inlineStr"/>
       <c r="I275" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15253,7 +14223,7 @@
         </is>
       </c>
       <c r="K275" s="23" t="n"/>
-      <c r="L275" s="67" t="inlineStr"/>
+      <c r="L275" s="66" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="53" t="inlineStr">
@@ -15266,7 +14236,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C276" s="76" t="inlineStr">
+      <c r="C276" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15291,11 +14261,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H276" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H276" s="65" t="inlineStr"/>
       <c r="I276" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15307,7 +14273,7 @@
         </is>
       </c>
       <c r="K276" s="23" t="n"/>
-      <c r="L276" s="67" t="inlineStr"/>
+      <c r="L276" s="66" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="53" t="inlineStr">
@@ -15320,7 +14286,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C277" s="77" t="inlineStr">
+      <c r="C277" s="75" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -15345,11 +14311,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H277" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H277" s="65" t="inlineStr"/>
       <c r="I277" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15361,7 +14323,7 @@
         </is>
       </c>
       <c r="K277" s="23" t="n"/>
-      <c r="L277" s="67" t="inlineStr"/>
+      <c r="L277" s="66" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="53" t="inlineStr">
@@ -15374,7 +14336,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C278" s="76" t="inlineStr">
+      <c r="C278" s="74" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -15399,11 +14361,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H278" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H278" s="65" t="inlineStr"/>
       <c r="I278" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15415,7 +14373,7 @@
         </is>
       </c>
       <c r="K278" s="23" t="n"/>
-      <c r="L278" s="67" t="inlineStr"/>
+      <c r="L278" s="66" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="53" t="inlineStr">
@@ -15428,7 +14386,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C279" s="76" t="inlineStr">
+      <c r="C279" s="74" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -15453,11 +14411,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H279" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H279" s="65" t="inlineStr"/>
       <c r="I279" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15469,7 +14423,7 @@
         </is>
       </c>
       <c r="K279" s="23" t="n"/>
-      <c r="L279" s="67" t="inlineStr"/>
+      <c r="L279" s="66" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="53" t="inlineStr">
@@ -15482,7 +14436,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C280" s="76" t="inlineStr">
+      <c r="C280" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15507,11 +14461,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H280" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H280" s="65" t="inlineStr"/>
       <c r="I280" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15523,7 +14473,7 @@
         </is>
       </c>
       <c r="K280" s="23" t="n"/>
-      <c r="L280" s="67" t="inlineStr"/>
+      <c r="L280" s="66" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="53" t="inlineStr">
@@ -15536,7 +14486,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C281" s="78" t="inlineStr">
+      <c r="C281" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -15561,11 +14511,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H281" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H281" s="65" t="inlineStr"/>
       <c r="I281" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15577,7 +14523,7 @@
         </is>
       </c>
       <c r="K281" s="23" t="n"/>
-      <c r="L281" s="67" t="inlineStr"/>
+      <c r="L281" s="66" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="53" t="inlineStr">
@@ -15590,7 +14536,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C282" s="76" t="inlineStr">
+      <c r="C282" s="74" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -15615,11 +14561,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H282" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H282" s="65" t="inlineStr"/>
       <c r="I282" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15631,7 +14573,7 @@
         </is>
       </c>
       <c r="K282" s="23" t="n"/>
-      <c r="L282" s="67" t="inlineStr"/>
+      <c r="L282" s="66" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="53" t="inlineStr">
@@ -15644,7 +14586,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C283" s="76" t="inlineStr">
+      <c r="C283" s="74" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -15669,11 +14611,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H283" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H283" s="65" t="inlineStr"/>
       <c r="I283" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15685,7 +14623,7 @@
         </is>
       </c>
       <c r="K283" s="23" t="n"/>
-      <c r="L283" s="67" t="inlineStr"/>
+      <c r="L283" s="66" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="53" t="inlineStr">
@@ -15698,7 +14636,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C284" s="78" t="inlineStr">
+      <c r="C284" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -15723,11 +14661,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H284" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H284" s="65" t="inlineStr"/>
       <c r="I284" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15739,7 +14673,7 @@
         </is>
       </c>
       <c r="K284" s="23" t="n"/>
-      <c r="L284" s="67" t="inlineStr"/>
+      <c r="L284" s="66" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="53" t="inlineStr">
@@ -15752,7 +14686,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C285" s="78" t="inlineStr">
+      <c r="C285" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -15777,11 +14711,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H285" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H285" s="65" t="inlineStr"/>
       <c r="I285" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15793,7 +14723,7 @@
         </is>
       </c>
       <c r="K285" s="23" t="n"/>
-      <c r="L285" s="67" t="inlineStr"/>
+      <c r="L285" s="66" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="53" t="inlineStr">
@@ -15806,7 +14736,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C286" s="78" t="inlineStr">
+      <c r="C286" s="76" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -15831,11 +14761,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H286" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H286" s="65" t="inlineStr"/>
       <c r="I286" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15847,7 +14773,7 @@
         </is>
       </c>
       <c r="K286" s="23" t="n"/>
-      <c r="L286" s="67" t="inlineStr"/>
+      <c r="L286" s="66" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="53" t="inlineStr">
@@ -15860,7 +14786,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C287" s="76" t="inlineStr">
+      <c r="C287" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15885,11 +14811,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H287" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H287" s="65" t="inlineStr"/>
       <c r="I287" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15901,7 +14823,7 @@
         </is>
       </c>
       <c r="K287" s="23" t="n"/>
-      <c r="L287" s="67" t="inlineStr"/>
+      <c r="L287" s="66" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="53" t="inlineStr">
@@ -15914,7 +14836,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C288" s="76" t="inlineStr">
+      <c r="C288" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15939,11 +14861,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H288" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H288" s="65" t="inlineStr"/>
       <c r="I288" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -15955,7 +14873,7 @@
         </is>
       </c>
       <c r="K288" s="23" t="n"/>
-      <c r="L288" s="67" t="inlineStr"/>
+      <c r="L288" s="66" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="53" t="inlineStr">
@@ -15968,7 +14886,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C289" s="76" t="inlineStr">
+      <c r="C289" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15993,11 +14911,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H289" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H289" s="65" t="inlineStr"/>
       <c r="I289" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -16009,7 +14923,7 @@
         </is>
       </c>
       <c r="K289" s="23" t="n"/>
-      <c r="L289" s="67" t="inlineStr"/>
+      <c r="L289" s="66" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="53" t="inlineStr">
@@ -16022,7 +14936,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C290" s="76" t="inlineStr">
+      <c r="C290" s="74" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16047,11 +14961,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H290" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H290" s="65" t="inlineStr"/>
       <c r="I290" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -16063,7 +14973,7 @@
         </is>
       </c>
       <c r="K290" s="23" t="n"/>
-      <c r="L290" s="67" t="inlineStr"/>
+      <c r="L290" s="66" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="53" t="inlineStr">
@@ -16076,7 +14986,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C291" s="76" t="inlineStr">
+      <c r="C291" s="74" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -16101,11 +15011,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H291" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H291" s="65" t="inlineStr"/>
       <c r="I291" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -16117,7 +15023,7 @@
         </is>
       </c>
       <c r="K291" s="23" t="n"/>
-      <c r="L291" s="67" t="inlineStr"/>
+      <c r="L291" s="66" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="53" t="inlineStr">
@@ -16130,7 +15036,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C292" s="77" t="inlineStr">
+      <c r="C292" s="75" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -16155,11 +15061,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H292" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H292" s="65" t="inlineStr"/>
       <c r="I292" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -16171,7 +15073,7 @@
         </is>
       </c>
       <c r="K292" s="23" t="n"/>
-      <c r="L292" s="67" t="inlineStr"/>
+      <c r="L292" s="66" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L292"/>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -303,6 +303,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -512,9 +518,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,10 +527,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,16 +542,19 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,10 +564,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -573,21 +579,21 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,10 +683,13 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,7 +707,10 @@
     <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,7 +722,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -719,37 +737,37 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1157,17 +1175,17 @@
           <t>PS5 COMPLETION PLATFORM  |  BLOCKERS - sorted by blocking count</t>
         </is>
       </c>
-      <c r="B1" s="96" t="n"/>
-      <c r="C1" s="96" t="n"/>
-      <c r="D1" s="96" t="n"/>
-      <c r="E1" s="96" t="n"/>
-      <c r="F1" s="96" t="n"/>
-      <c r="G1" s="96" t="n"/>
-      <c r="H1" s="96" t="n"/>
-      <c r="I1" s="96" t="n"/>
-      <c r="J1" s="96" t="n"/>
-      <c r="K1" s="96" t="n"/>
-      <c r="L1" s="97" t="n"/>
+      <c r="B1" s="100" t="n"/>
+      <c r="C1" s="100" t="n"/>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="100" t="n"/>
+      <c r="G1" s="100" t="n"/>
+      <c r="H1" s="100" t="n"/>
+      <c r="I1" s="100" t="n"/>
+      <c r="J1" s="100" t="n"/>
+      <c r="K1" s="100" t="n"/>
+      <c r="L1" s="101" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1242,7 +1260,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="74" t="inlineStr">
+      <c r="C3" s="76" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -1283,7 +1301,7 @@
         </is>
       </c>
       <c r="K3" s="23" t="n"/>
-      <c r="L3" s="66" t="inlineStr"/>
+      <c r="L3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="53" t="inlineStr">
@@ -1296,7 +1314,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C4" s="74" t="inlineStr">
+      <c r="C4" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1333,7 +1351,7 @@
         </is>
       </c>
       <c r="K4" s="23" t="n"/>
-      <c r="L4" s="66" t="inlineStr"/>
+      <c r="L4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
@@ -1346,7 +1364,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C5" s="74" t="inlineStr">
+      <c r="C5" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1383,7 +1401,7 @@
         </is>
       </c>
       <c r="K5" s="23" t="n"/>
-      <c r="L5" s="66" t="inlineStr"/>
+      <c r="L5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="53" t="inlineStr">
@@ -1396,7 +1414,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C6" s="74" t="inlineStr">
+      <c r="C6" s="76" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -1439,7 +1457,7 @@
         </is>
       </c>
       <c r="K6" s="23" t="n"/>
-      <c r="L6" s="66" t="inlineStr"/>
+      <c r="L6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="53" t="inlineStr">
@@ -1452,7 +1470,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C7" s="75" t="inlineStr">
+      <c r="C7" s="77" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -1491,7 +1509,7 @@
         </is>
       </c>
       <c r="K7" s="23" t="n"/>
-      <c r="L7" s="66" t="inlineStr"/>
+      <c r="L7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="53" t="inlineStr">
@@ -1504,7 +1522,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="74" t="inlineStr">
+      <c r="C8" s="76" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -1532,7 +1550,7 @@
       <c r="H8" s="65" t="inlineStr"/>
       <c r="I8" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -1541,7 +1559,7 @@
         </is>
       </c>
       <c r="K8" s="23" t="n"/>
-      <c r="L8" s="66" t="inlineStr"/>
+      <c r="L8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="53" t="inlineStr">
@@ -1554,7 +1572,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C9" s="75" t="inlineStr">
+      <c r="C9" s="77" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -1591,7 +1609,7 @@
         </is>
       </c>
       <c r="K9" s="23" t="n"/>
-      <c r="L9" s="66" t="inlineStr"/>
+      <c r="L9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="53" t="inlineStr">
@@ -1604,7 +1622,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C10" s="75" t="inlineStr">
+      <c r="C10" s="77" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -1661,7 +1679,7 @@
         </is>
       </c>
       <c r="K10" s="23" t="n"/>
-      <c r="L10" s="66" t="inlineStr"/>
+      <c r="L10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="53" t="inlineStr">
@@ -1674,7 +1692,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C11" s="74" t="inlineStr">
+      <c r="C11" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1711,7 +1729,7 @@
         </is>
       </c>
       <c r="K11" s="23" t="n"/>
-      <c r="L11" s="66" t="inlineStr"/>
+      <c r="L11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="53" t="inlineStr">
@@ -1724,7 +1742,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C12" s="74" t="inlineStr">
+      <c r="C12" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1761,7 +1779,7 @@
         </is>
       </c>
       <c r="K12" s="23" t="n"/>
-      <c r="L12" s="66" t="inlineStr"/>
+      <c r="L12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="53" t="inlineStr">
@@ -1774,7 +1792,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C13" s="75" t="inlineStr">
+      <c r="C13" s="77" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -1813,7 +1831,7 @@
         </is>
       </c>
       <c r="K13" s="23" t="n"/>
-      <c r="L13" s="66" t="inlineStr"/>
+      <c r="L13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="53" t="inlineStr">
@@ -1826,7 +1844,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C14" s="74" t="inlineStr">
+      <c r="C14" s="76" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -1855,7 +1873,7 @@
       <c r="I14" s="65" t="inlineStr"/>
       <c r="J14" s="23" t="inlineStr"/>
       <c r="K14" s="23" t="n"/>
-      <c r="L14" s="66" t="inlineStr"/>
+      <c r="L14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="53" t="inlineStr">
@@ -1868,7 +1886,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C15" s="74" t="inlineStr">
+      <c r="C15" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1905,7 +1923,7 @@
         </is>
       </c>
       <c r="K15" s="23" t="n"/>
-      <c r="L15" s="66" t="inlineStr"/>
+      <c r="L15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="53" t="inlineStr">
@@ -1918,7 +1936,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C16" s="76" t="inlineStr">
+      <c r="C16" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -1957,7 +1975,7 @@
         </is>
       </c>
       <c r="K16" s="23" t="n"/>
-      <c r="L16" s="66" t="inlineStr"/>
+      <c r="L16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="53" t="inlineStr">
@@ -1970,7 +1988,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="75" t="inlineStr">
+      <c r="C17" s="77" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -2009,7 +2027,7 @@
         </is>
       </c>
       <c r="K17" s="23" t="n"/>
-      <c r="L17" s="66" t="inlineStr"/>
+      <c r="L17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="53" t="inlineStr">
@@ -2022,7 +2040,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C18" s="76" t="inlineStr">
+      <c r="C18" s="78" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -2059,7 +2077,7 @@
         </is>
       </c>
       <c r="K18" s="23" t="n"/>
-      <c r="L18" s="66" t="inlineStr"/>
+      <c r="L18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="53" t="inlineStr">
@@ -2072,7 +2090,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C19" s="74" t="inlineStr">
+      <c r="C19" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2109,7 +2127,7 @@
         </is>
       </c>
       <c r="K19" s="23" t="n"/>
-      <c r="L19" s="66" t="inlineStr"/>
+      <c r="L19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="53" t="inlineStr">
@@ -2122,7 +2140,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C20" s="74" t="inlineStr">
+      <c r="C20" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2159,7 +2177,7 @@
         </is>
       </c>
       <c r="K20" s="23" t="n"/>
-      <c r="L20" s="66" t="inlineStr"/>
+      <c r="L20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="53" t="inlineStr">
@@ -2172,7 +2190,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C21" s="74" t="inlineStr">
+      <c r="C21" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2209,7 +2227,7 @@
         </is>
       </c>
       <c r="K21" s="23" t="n"/>
-      <c r="L21" s="66" t="inlineStr"/>
+      <c r="L21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="53" t="inlineStr">
@@ -2222,7 +2240,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C22" s="76" t="inlineStr">
+      <c r="C22" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2259,7 +2277,7 @@
         </is>
       </c>
       <c r="K22" s="23" t="n"/>
-      <c r="L22" s="66" t="inlineStr"/>
+      <c r="L22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
@@ -2272,7 +2290,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C23" s="76" t="inlineStr">
+      <c r="C23" s="78" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -2309,7 +2327,7 @@
         </is>
       </c>
       <c r="K23" s="23" t="n"/>
-      <c r="L23" s="66" t="inlineStr"/>
+      <c r="L23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
@@ -2322,7 +2340,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C24" s="74" t="inlineStr">
+      <c r="C24" s="76" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -2347,7 +2365,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H24" s="65" t="inlineStr"/>
+      <c r="H24" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I24" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-0007, PS5-71-TW-0003, PS5-71-TW-0004, PS5-71-TW-0006 not arrived</t>
@@ -2359,7 +2381,7 @@
         </is>
       </c>
       <c r="K24" s="23" t="n"/>
-      <c r="L24" s="66" t="inlineStr"/>
+      <c r="L24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="53" t="inlineStr">
@@ -2372,7 +2394,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C25" s="75" t="inlineStr">
+      <c r="C25" s="77" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -2413,7 +2435,7 @@
         </is>
       </c>
       <c r="K25" s="23" t="n"/>
-      <c r="L25" s="66" t="inlineStr"/>
+      <c r="L25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="53" t="inlineStr">
@@ -2426,7 +2448,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C26" s="76" t="inlineStr">
+      <c r="C26" s="78" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -2465,7 +2487,7 @@
         </is>
       </c>
       <c r="K26" s="23" t="n"/>
-      <c r="L26" s="66" t="inlineStr"/>
+      <c r="L26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="53" t="inlineStr">
@@ -2478,7 +2500,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C27" s="74" t="inlineStr">
+      <c r="C27" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2515,7 +2537,7 @@
         </is>
       </c>
       <c r="K27" s="23" t="n"/>
-      <c r="L27" s="66" t="inlineStr"/>
+      <c r="L27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="53" t="inlineStr">
@@ -2528,7 +2550,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C28" s="74" t="inlineStr">
+      <c r="C28" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2565,7 +2587,7 @@
         </is>
       </c>
       <c r="K28" s="23" t="n"/>
-      <c r="L28" s="66" t="inlineStr"/>
+      <c r="L28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="53" t="inlineStr">
@@ -2578,7 +2600,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C29" s="74" t="inlineStr">
+      <c r="C29" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2615,7 +2637,7 @@
         </is>
       </c>
       <c r="K29" s="23" t="n"/>
-      <c r="L29" s="66" t="inlineStr"/>
+      <c r="L29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="53" t="inlineStr">
@@ -2628,7 +2650,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C30" s="75" t="inlineStr">
+      <c r="C30" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -2665,7 +2687,7 @@
         </is>
       </c>
       <c r="K30" s="23" t="n"/>
-      <c r="L30" s="66" t="inlineStr"/>
+      <c r="L30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="53" t="inlineStr">
@@ -2678,7 +2700,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C31" s="75" t="inlineStr">
+      <c r="C31" s="77" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -2715,7 +2737,7 @@
         </is>
       </c>
       <c r="K31" s="23" t="n"/>
-      <c r="L31" s="66" t="inlineStr"/>
+      <c r="L31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="53" t="inlineStr">
@@ -2728,7 +2750,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C32" s="75" t="inlineStr">
+      <c r="C32" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -2757,7 +2779,7 @@
       <c r="I32" s="65" t="inlineStr"/>
       <c r="J32" s="23" t="inlineStr"/>
       <c r="K32" s="23" t="n"/>
-      <c r="L32" s="66" t="inlineStr"/>
+      <c r="L32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="53" t="inlineStr">
@@ -2770,7 +2792,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C33" s="76" t="inlineStr">
+      <c r="C33" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -2809,7 +2831,7 @@
         </is>
       </c>
       <c r="K33" s="23" t="n"/>
-      <c r="L33" s="66" t="inlineStr"/>
+      <c r="L33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="53" t="inlineStr">
@@ -2822,7 +2844,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C34" s="76" t="inlineStr">
+      <c r="C34" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -2859,7 +2881,7 @@
         </is>
       </c>
       <c r="K34" s="23" t="n"/>
-      <c r="L34" s="66" t="inlineStr"/>
+      <c r="L34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="53" t="inlineStr">
@@ -2872,7 +2894,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C35" s="75" t="inlineStr">
+      <c r="C35" s="77" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -2909,7 +2931,7 @@
         </is>
       </c>
       <c r="K35" s="23" t="n"/>
-      <c r="L35" s="66" t="inlineStr"/>
+      <c r="L35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="53" t="inlineStr">
@@ -2922,7 +2944,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C36" s="76" t="inlineStr">
+      <c r="C36" s="78" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -2951,7 +2973,7 @@
       <c r="I36" s="65" t="inlineStr"/>
       <c r="J36" s="23" t="inlineStr"/>
       <c r="K36" s="23" t="n"/>
-      <c r="L36" s="66" t="inlineStr"/>
+      <c r="L36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="53" t="inlineStr">
@@ -2964,7 +2986,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C37" s="76" t="inlineStr">
+      <c r="C37" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -3001,7 +3023,7 @@
         </is>
       </c>
       <c r="K37" s="23" t="n"/>
-      <c r="L37" s="66" t="inlineStr"/>
+      <c r="L37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="53" t="inlineStr">
@@ -3014,7 +3036,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C38" s="75" t="inlineStr">
+      <c r="C38" s="77" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -3053,7 +3075,7 @@
         </is>
       </c>
       <c r="K38" s="23" t="n"/>
-      <c r="L38" s="66" t="inlineStr"/>
+      <c r="L38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="53" t="inlineStr">
@@ -3066,7 +3088,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C39" s="75" t="inlineStr">
+      <c r="C39" s="77" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -3103,7 +3125,7 @@
         </is>
       </c>
       <c r="K39" s="23" t="n"/>
-      <c r="L39" s="66" t="inlineStr"/>
+      <c r="L39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="53" t="inlineStr">
@@ -3116,7 +3138,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C40" s="76" t="inlineStr">
+      <c r="C40" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -3144,16 +3166,16 @@
       <c r="H40" s="65" t="inlineStr"/>
       <c r="I40" s="65" t="inlineStr">
         <is>
+          <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
-        </is>
-      </c>
       <c r="K40" s="23" t="n"/>
-      <c r="L40" s="66" t="inlineStr"/>
+      <c r="L40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="53" t="inlineStr">
@@ -3166,7 +3188,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C41" s="76" t="inlineStr">
+      <c r="C41" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -3203,7 +3225,7 @@
         </is>
       </c>
       <c r="K41" s="23" t="n"/>
-      <c r="L41" s="66" t="inlineStr"/>
+      <c r="L41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="53" t="inlineStr">
@@ -3216,7 +3238,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C42" s="76" t="inlineStr">
+      <c r="C42" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3245,7 +3267,7 @@
       <c r="I42" s="65" t="inlineStr"/>
       <c r="J42" s="23" t="inlineStr"/>
       <c r="K42" s="23" t="n"/>
-      <c r="L42" s="66" t="inlineStr"/>
+      <c r="L42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="53" t="inlineStr">
@@ -3258,7 +3280,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C43" s="76" t="inlineStr">
+      <c r="C43" s="78" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -3297,7 +3319,7 @@
         </is>
       </c>
       <c r="K43" s="23" t="n"/>
-      <c r="L43" s="66" t="inlineStr"/>
+      <c r="L43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="53" t="inlineStr">
@@ -3310,7 +3332,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C44" s="76" t="inlineStr">
+      <c r="C44" s="78" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3347,7 +3369,7 @@
         </is>
       </c>
       <c r="K44" s="23" t="n"/>
-      <c r="L44" s="66" t="inlineStr"/>
+      <c r="L44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="53" t="inlineStr">
@@ -3360,7 +3382,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C45" s="76" t="inlineStr">
+      <c r="C45" s="78" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3397,7 +3419,7 @@
         </is>
       </c>
       <c r="K45" s="23" t="n"/>
-      <c r="L45" s="66" t="inlineStr"/>
+      <c r="L45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="53" t="inlineStr">
@@ -3410,7 +3432,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C46" s="76" t="inlineStr">
+      <c r="C46" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3439,7 +3461,7 @@
       <c r="I46" s="65" t="inlineStr"/>
       <c r="J46" s="23" t="inlineStr"/>
       <c r="K46" s="23" t="n"/>
-      <c r="L46" s="66" t="inlineStr"/>
+      <c r="L46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="53" t="inlineStr">
@@ -3452,7 +3474,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C47" s="76" t="inlineStr">
+      <c r="C47" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3481,7 +3503,7 @@
       <c r="I47" s="65" t="inlineStr"/>
       <c r="J47" s="23" t="inlineStr"/>
       <c r="K47" s="23" t="n"/>
-      <c r="L47" s="66" t="inlineStr"/>
+      <c r="L47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="53" t="inlineStr">
@@ -3494,7 +3516,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C48" s="76" t="inlineStr">
+      <c r="C48" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3523,7 +3545,7 @@
       <c r="I48" s="65" t="inlineStr"/>
       <c r="J48" s="23" t="inlineStr"/>
       <c r="K48" s="23" t="n"/>
-      <c r="L48" s="66" t="inlineStr"/>
+      <c r="L48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="53" t="inlineStr">
@@ -3536,7 +3558,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C49" s="76" t="inlineStr">
+      <c r="C49" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3565,7 +3587,7 @@
       <c r="I49" s="65" t="inlineStr"/>
       <c r="J49" s="23" t="inlineStr"/>
       <c r="K49" s="23" t="n"/>
-      <c r="L49" s="66" t="inlineStr"/>
+      <c r="L49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="53" t="inlineStr">
@@ -3578,7 +3600,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C50" s="75" t="inlineStr">
+      <c r="C50" s="77" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -3615,35 +3637,35 @@
         </is>
       </c>
       <c r="K50" s="23" t="n"/>
-      <c r="L50" s="66" t="inlineStr"/>
+      <c r="L50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="53" t="inlineStr">
+      <c r="A51" s="79" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="66" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="C51" s="76" t="inlineStr">
+      <c r="C51" s="80" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="D51" s="66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E51" s="66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3659,13 +3681,13 @@
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="J51" s="23" t="inlineStr">
+      <c r="J51" s="66" t="inlineStr">
         <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="K51" s="23" t="n"/>
-      <c r="L51" s="66" t="inlineStr"/>
+      <c r="K51" s="66" t="n"/>
+      <c r="L51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="53" t="inlineStr">
@@ -3678,7 +3700,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C52" s="75" t="inlineStr">
+      <c r="C52" s="77" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -3715,7 +3737,7 @@
         </is>
       </c>
       <c r="K52" s="23" t="n"/>
-      <c r="L52" s="66" t="inlineStr"/>
+      <c r="L52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="53" t="inlineStr">
@@ -3728,7 +3750,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C53" s="76" t="inlineStr">
+      <c r="C53" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3765,7 +3787,7 @@
         </is>
       </c>
       <c r="K53" s="23" t="n"/>
-      <c r="L53" s="66" t="inlineStr"/>
+      <c r="L53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="53" t="inlineStr">
@@ -3778,7 +3800,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C54" s="76" t="inlineStr">
+      <c r="C54" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -3807,7 +3829,7 @@
       <c r="I54" s="65" t="inlineStr"/>
       <c r="J54" s="23" t="inlineStr"/>
       <c r="K54" s="23" t="n"/>
-      <c r="L54" s="66" t="inlineStr"/>
+      <c r="L54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="53" t="inlineStr">
@@ -3820,7 +3842,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C55" s="75" t="inlineStr">
+      <c r="C55" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -3849,7 +3871,7 @@
       <c r="I55" s="65" t="inlineStr"/>
       <c r="J55" s="23" t="inlineStr"/>
       <c r="K55" s="23" t="n"/>
-      <c r="L55" s="66" t="inlineStr"/>
+      <c r="L55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="53" t="inlineStr">
@@ -3862,7 +3884,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C56" s="76" t="inlineStr">
+      <c r="C56" s="78" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -3891,7 +3913,7 @@
       <c r="I56" s="65" t="inlineStr"/>
       <c r="J56" s="23" t="inlineStr"/>
       <c r="K56" s="23" t="n"/>
-      <c r="L56" s="66" t="inlineStr"/>
+      <c r="L56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="53" t="inlineStr">
@@ -3904,7 +3926,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C57" s="75" t="inlineStr">
+      <c r="C57" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -3933,7 +3955,7 @@
       <c r="I57" s="65" t="inlineStr"/>
       <c r="J57" s="23" t="inlineStr"/>
       <c r="K57" s="23" t="n"/>
-      <c r="L57" s="66" t="inlineStr"/>
+      <c r="L57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="53" t="inlineStr">
@@ -3946,7 +3968,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C58" s="76" t="inlineStr">
+      <c r="C58" s="78" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -3983,7 +4005,7 @@
         </is>
       </c>
       <c r="K58" s="23" t="n"/>
-      <c r="L58" s="66" t="inlineStr"/>
+      <c r="L58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="53" t="inlineStr">
@@ -3996,7 +4018,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C59" s="76" t="inlineStr">
+      <c r="C59" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4025,7 +4047,7 @@
       <c r="I59" s="65" t="inlineStr"/>
       <c r="J59" s="23" t="inlineStr"/>
       <c r="K59" s="23" t="n"/>
-      <c r="L59" s="66" t="inlineStr"/>
+      <c r="L59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="53" t="inlineStr">
@@ -4038,7 +4060,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C60" s="76" t="inlineStr">
+      <c r="C60" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4067,7 +4089,7 @@
       <c r="I60" s="65" t="inlineStr"/>
       <c r="J60" s="23" t="inlineStr"/>
       <c r="K60" s="23" t="n"/>
-      <c r="L60" s="66" t="inlineStr"/>
+      <c r="L60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="53" t="inlineStr">
@@ -4080,7 +4102,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C61" s="75" t="inlineStr">
+      <c r="C61" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -4117,7 +4139,7 @@
         </is>
       </c>
       <c r="K61" s="23" t="n"/>
-      <c r="L61" s="66" t="inlineStr"/>
+      <c r="L61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="53" t="inlineStr">
@@ -4130,7 +4152,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C62" s="75" t="inlineStr">
+      <c r="C62" s="77" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -4167,7 +4189,7 @@
         </is>
       </c>
       <c r="K62" s="23" t="n"/>
-      <c r="L62" s="66" t="inlineStr"/>
+      <c r="L62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="53" t="inlineStr">
@@ -4180,7 +4202,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C63" s="76" t="inlineStr">
+      <c r="C63" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4207,9 +4229,13 @@
       </c>
       <c r="H63" s="65" t="inlineStr"/>
       <c r="I63" s="65" t="inlineStr"/>
-      <c r="J63" s="23" t="inlineStr"/>
+      <c r="J63" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVATION -CLEANING ON PROGRESS</t>
+        </is>
+      </c>
       <c r="K63" s="23" t="n"/>
-      <c r="L63" s="66" t="inlineStr"/>
+      <c r="L63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="53" t="inlineStr">
@@ -4222,7 +4248,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C64" s="76" t="inlineStr">
+      <c r="C64" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4251,7 +4277,7 @@
       <c r="I64" s="65" t="inlineStr"/>
       <c r="J64" s="23" t="inlineStr"/>
       <c r="K64" s="23" t="n"/>
-      <c r="L64" s="66" t="inlineStr"/>
+      <c r="L64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="53" t="inlineStr">
@@ -4264,7 +4290,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C65" s="76" t="inlineStr">
+      <c r="C65" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -4301,7 +4327,7 @@
         </is>
       </c>
       <c r="K65" s="23" t="n"/>
-      <c r="L65" s="66" t="inlineStr"/>
+      <c r="L65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="53" t="inlineStr">
@@ -4314,7 +4340,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C66" s="76" t="inlineStr">
+      <c r="C66" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -4351,7 +4377,7 @@
         </is>
       </c>
       <c r="K66" s="23" t="n"/>
-      <c r="L66" s="66" t="inlineStr"/>
+      <c r="L66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="53" t="inlineStr">
@@ -4364,7 +4390,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C67" s="76" t="inlineStr">
+      <c r="C67" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4401,7 +4427,7 @@
         </is>
       </c>
       <c r="K67" s="23" t="n"/>
-      <c r="L67" s="66" t="inlineStr"/>
+      <c r="L67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="53" t="inlineStr">
@@ -4414,7 +4440,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C68" s="76" t="inlineStr">
+      <c r="C68" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4451,7 +4477,7 @@
         </is>
       </c>
       <c r="K68" s="23" t="n"/>
-      <c r="L68" s="66" t="inlineStr"/>
+      <c r="L68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="53" t="inlineStr">
@@ -4464,7 +4490,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C69" s="76" t="inlineStr">
+      <c r="C69" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -4501,7 +4527,7 @@
         </is>
       </c>
       <c r="K69" s="23" t="n"/>
-      <c r="L69" s="66" t="inlineStr"/>
+      <c r="L69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="53" t="inlineStr">
@@ -4514,7 +4540,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C70" s="76" t="inlineStr">
+      <c r="C70" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4551,7 +4577,7 @@
         </is>
       </c>
       <c r="K70" s="23" t="n"/>
-      <c r="L70" s="66" t="inlineStr"/>
+      <c r="L70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="53" t="inlineStr">
@@ -4564,7 +4590,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C71" s="75" t="inlineStr">
+      <c r="C71" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -4601,7 +4627,7 @@
         </is>
       </c>
       <c r="K71" s="23" t="n"/>
-      <c r="L71" s="66" t="inlineStr"/>
+      <c r="L71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="53" t="inlineStr">
@@ -4614,7 +4640,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C72" s="75" t="inlineStr">
+      <c r="C72" s="77" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -4651,7 +4677,7 @@
         </is>
       </c>
       <c r="K72" s="23" t="n"/>
-      <c r="L72" s="66" t="inlineStr"/>
+      <c r="L72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="53" t="inlineStr">
@@ -4664,7 +4690,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C73" s="76" t="inlineStr">
+      <c r="C73" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4701,7 +4727,7 @@
         </is>
       </c>
       <c r="K73" s="23" t="n"/>
-      <c r="L73" s="66" t="inlineStr"/>
+      <c r="L73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="53" t="inlineStr">
@@ -4714,7 +4740,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C74" s="74" t="inlineStr">
+      <c r="C74" s="76" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -4751,7 +4777,7 @@
         </is>
       </c>
       <c r="K74" s="23" t="n"/>
-      <c r="L74" s="66" t="inlineStr"/>
+      <c r="L74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="53" t="inlineStr">
@@ -4764,7 +4790,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C75" s="74" t="inlineStr">
+      <c r="C75" s="76" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -4801,7 +4827,7 @@
         </is>
       </c>
       <c r="K75" s="23" t="n"/>
-      <c r="L75" s="66" t="inlineStr"/>
+      <c r="L75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="53" t="inlineStr">
@@ -4814,7 +4840,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C76" s="76" t="inlineStr">
+      <c r="C76" s="78" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -4851,7 +4877,7 @@
         </is>
       </c>
       <c r="K76" s="23" t="n"/>
-      <c r="L76" s="66" t="inlineStr"/>
+      <c r="L76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="53" t="inlineStr">
@@ -4864,7 +4890,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C77" s="74" t="inlineStr">
+      <c r="C77" s="76" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -4901,7 +4927,7 @@
         </is>
       </c>
       <c r="K77" s="23" t="n"/>
-      <c r="L77" s="66" t="inlineStr"/>
+      <c r="L77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="53" t="inlineStr">
@@ -4914,7 +4940,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C78" s="76" t="inlineStr">
+      <c r="C78" s="78" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -4951,7 +4977,7 @@
         </is>
       </c>
       <c r="K78" s="23" t="n"/>
-      <c r="L78" s="66" t="inlineStr"/>
+      <c r="L78" s="67" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="53" t="inlineStr">
@@ -4964,7 +4990,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C79" s="76" t="inlineStr">
+      <c r="C79" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -5001,7 +5027,7 @@
         </is>
       </c>
       <c r="K79" s="23" t="n"/>
-      <c r="L79" s="66" t="inlineStr"/>
+      <c r="L79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="53" t="inlineStr">
@@ -5014,7 +5040,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C80" s="76" t="inlineStr">
+      <c r="C80" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5051,7 +5077,7 @@
         </is>
       </c>
       <c r="K80" s="23" t="n"/>
-      <c r="L80" s="66" t="inlineStr"/>
+      <c r="L80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="53" t="inlineStr">
@@ -5064,7 +5090,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C81" s="76" t="inlineStr">
+      <c r="C81" s="78" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -5101,7 +5127,7 @@
         </is>
       </c>
       <c r="K81" s="23" t="n"/>
-      <c r="L81" s="66" t="inlineStr"/>
+      <c r="L81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="53" t="inlineStr">
@@ -5114,7 +5140,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C82" s="76" t="inlineStr">
+      <c r="C82" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5151,7 +5177,7 @@
         </is>
       </c>
       <c r="K82" s="23" t="n"/>
-      <c r="L82" s="66" t="inlineStr"/>
+      <c r="L82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="53" t="inlineStr">
@@ -5164,7 +5190,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C83" s="76" t="inlineStr">
+      <c r="C83" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5197,7 +5223,7 @@
       <c r="I83" s="65" t="inlineStr"/>
       <c r="J83" s="23" t="inlineStr"/>
       <c r="K83" s="23" t="n"/>
-      <c r="L83" s="66" t="inlineStr"/>
+      <c r="L83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="53" t="inlineStr">
@@ -5210,7 +5236,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C84" s="76" t="inlineStr">
+      <c r="C84" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5247,7 +5273,7 @@
         </is>
       </c>
       <c r="K84" s="23" t="n"/>
-      <c r="L84" s="66" t="inlineStr"/>
+      <c r="L84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="53" t="inlineStr">
@@ -5260,7 +5286,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C85" s="76" t="inlineStr">
+      <c r="C85" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5297,7 +5323,7 @@
         </is>
       </c>
       <c r="K85" s="23" t="n"/>
-      <c r="L85" s="66" t="inlineStr"/>
+      <c r="L85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="53" t="inlineStr">
@@ -5310,7 +5336,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C86" s="74" t="inlineStr">
+      <c r="C86" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5349,7 +5375,7 @@
         </is>
       </c>
       <c r="K86" s="23" t="n"/>
-      <c r="L86" s="66" t="inlineStr"/>
+      <c r="L86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="53" t="inlineStr">
@@ -5358,7 +5384,7 @@
         </is>
       </c>
       <c r="B87" s="23" t="inlineStr"/>
-      <c r="C87" s="76" t="inlineStr">
+      <c r="C87" s="78" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -5377,7 +5403,7 @@
       <c r="I87" s="65" t="inlineStr"/>
       <c r="J87" s="23" t="inlineStr"/>
       <c r="K87" s="23" t="n"/>
-      <c r="L87" s="66" t="inlineStr"/>
+      <c r="L87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="53" t="inlineStr">
@@ -5386,7 +5412,7 @@
         </is>
       </c>
       <c r="B88" s="23" t="inlineStr"/>
-      <c r="C88" s="74" t="inlineStr">
+      <c r="C88" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5405,7 +5431,7 @@
       <c r="I88" s="65" t="inlineStr"/>
       <c r="J88" s="23" t="inlineStr"/>
       <c r="K88" s="23" t="n"/>
-      <c r="L88" s="66" t="inlineStr"/>
+      <c r="L88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="53" t="inlineStr">
@@ -5418,7 +5444,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C89" s="74" t="inlineStr">
+      <c r="C89" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5455,7 +5481,7 @@
         </is>
       </c>
       <c r="K89" s="23" t="n"/>
-      <c r="L89" s="66" t="inlineStr"/>
+      <c r="L89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="53" t="inlineStr">
@@ -5464,7 +5490,7 @@
         </is>
       </c>
       <c r="B90" s="23" t="inlineStr"/>
-      <c r="C90" s="76" t="inlineStr">
+      <c r="C90" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -5483,7 +5509,7 @@
       <c r="I90" s="65" t="inlineStr"/>
       <c r="J90" s="23" t="inlineStr"/>
       <c r="K90" s="23" t="n"/>
-      <c r="L90" s="66" t="inlineStr"/>
+      <c r="L90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="53" t="inlineStr">
@@ -5492,7 +5518,7 @@
         </is>
       </c>
       <c r="B91" s="23" t="inlineStr"/>
-      <c r="C91" s="76" t="inlineStr">
+      <c r="C91" s="78" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -5511,7 +5537,7 @@
       <c r="I91" s="65" t="inlineStr"/>
       <c r="J91" s="23" t="inlineStr"/>
       <c r="K91" s="23" t="n"/>
-      <c r="L91" s="66" t="inlineStr"/>
+      <c r="L91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="53" t="inlineStr">
@@ -5520,7 +5546,7 @@
         </is>
       </c>
       <c r="B92" s="23" t="inlineStr"/>
-      <c r="C92" s="75" t="inlineStr">
+      <c r="C92" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -5539,7 +5565,7 @@
       <c r="I92" s="65" t="inlineStr"/>
       <c r="J92" s="23" t="inlineStr"/>
       <c r="K92" s="23" t="n"/>
-      <c r="L92" s="66" t="inlineStr"/>
+      <c r="L92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="53" t="inlineStr">
@@ -5552,7 +5578,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C93" s="76" t="inlineStr">
+      <c r="C93" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5589,7 +5615,7 @@
         </is>
       </c>
       <c r="K93" s="23" t="n"/>
-      <c r="L93" s="66" t="inlineStr"/>
+      <c r="L93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="53" t="inlineStr">
@@ -5602,7 +5628,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C94" s="76" t="inlineStr">
+      <c r="C94" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5639,7 +5665,7 @@
         </is>
       </c>
       <c r="K94" s="23" t="n"/>
-      <c r="L94" s="66" t="inlineStr"/>
+      <c r="L94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="53" t="inlineStr">
@@ -5648,7 +5674,7 @@
         </is>
       </c>
       <c r="B95" s="23" t="inlineStr"/>
-      <c r="C95" s="75" t="inlineStr">
+      <c r="C95" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -5667,7 +5693,7 @@
       <c r="I95" s="65" t="inlineStr"/>
       <c r="J95" s="23" t="inlineStr"/>
       <c r="K95" s="23" t="n"/>
-      <c r="L95" s="66" t="inlineStr"/>
+      <c r="L95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="53" t="inlineStr">
@@ -5680,7 +5706,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C96" s="76" t="inlineStr">
+      <c r="C96" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5717,7 +5743,7 @@
         </is>
       </c>
       <c r="K96" s="23" t="n"/>
-      <c r="L96" s="66" t="inlineStr"/>
+      <c r="L96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="53" t="inlineStr">
@@ -5730,7 +5756,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C97" s="74" t="inlineStr">
+      <c r="C97" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5767,7 +5793,7 @@
         </is>
       </c>
       <c r="K97" s="23" t="n"/>
-      <c r="L97" s="66" t="inlineStr"/>
+      <c r="L97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="53" t="inlineStr">
@@ -5780,7 +5806,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C98" s="74" t="inlineStr">
+      <c r="C98" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5817,7 +5843,7 @@
         </is>
       </c>
       <c r="K98" s="23" t="n"/>
-      <c r="L98" s="66" t="inlineStr"/>
+      <c r="L98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="53" t="inlineStr">
@@ -5830,7 +5856,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C99" s="74" t="inlineStr">
+      <c r="C99" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5867,7 +5893,7 @@
         </is>
       </c>
       <c r="K99" s="23" t="n"/>
-      <c r="L99" s="66" t="inlineStr"/>
+      <c r="L99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="53" t="inlineStr">
@@ -5880,7 +5906,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C100" s="74" t="inlineStr">
+      <c r="C100" s="76" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -5917,7 +5943,7 @@
         </is>
       </c>
       <c r="K100" s="23" t="n"/>
-      <c r="L100" s="66" t="inlineStr"/>
+      <c r="L100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="53" t="inlineStr">
@@ -5930,7 +5956,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C101" s="74" t="inlineStr">
+      <c r="C101" s="76" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -5967,7 +5993,7 @@
         </is>
       </c>
       <c r="K101" s="23" t="n"/>
-      <c r="L101" s="66" t="inlineStr"/>
+      <c r="L101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="53" t="inlineStr">
@@ -5976,7 +6002,7 @@
         </is>
       </c>
       <c r="B102" s="23" t="inlineStr"/>
-      <c r="C102" s="74" t="inlineStr">
+      <c r="C102" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5995,7 +6021,7 @@
       <c r="I102" s="65" t="inlineStr"/>
       <c r="J102" s="23" t="inlineStr"/>
       <c r="K102" s="23" t="n"/>
-      <c r="L102" s="66" t="inlineStr"/>
+      <c r="L102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="53" t="inlineStr">
@@ -6004,7 +6030,7 @@
         </is>
       </c>
       <c r="B103" s="23" t="inlineStr"/>
-      <c r="C103" s="74" t="inlineStr">
+      <c r="C103" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6023,7 +6049,7 @@
       <c r="I103" s="65" t="inlineStr"/>
       <c r="J103" s="23" t="inlineStr"/>
       <c r="K103" s="23" t="n"/>
-      <c r="L103" s="66" t="inlineStr"/>
+      <c r="L103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="53" t="inlineStr">
@@ -6036,7 +6062,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C104" s="74" t="inlineStr">
+      <c r="C104" s="76" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6073,7 +6099,7 @@
         </is>
       </c>
       <c r="K104" s="23" t="n"/>
-      <c r="L104" s="66" t="inlineStr"/>
+      <c r="L104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="53" t="inlineStr">
@@ -6086,7 +6112,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C105" s="74" t="inlineStr">
+      <c r="C105" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6123,7 +6149,7 @@
         </is>
       </c>
       <c r="K105" s="23" t="n"/>
-      <c r="L105" s="66" t="inlineStr"/>
+      <c r="L105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="53" t="inlineStr">
@@ -6136,7 +6162,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C106" s="74" t="inlineStr">
+      <c r="C106" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6173,7 +6199,7 @@
         </is>
       </c>
       <c r="K106" s="23" t="n"/>
-      <c r="L106" s="66" t="inlineStr"/>
+      <c r="L106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="53" t="inlineStr">
@@ -6186,7 +6212,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C107" s="74" t="inlineStr">
+      <c r="C107" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6223,7 +6249,7 @@
         </is>
       </c>
       <c r="K107" s="23" t="n"/>
-      <c r="L107" s="66" t="inlineStr"/>
+      <c r="L107" s="67" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="53" t="inlineStr">
@@ -6236,7 +6262,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C108" s="74" t="inlineStr">
+      <c r="C108" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6273,7 +6299,7 @@
         </is>
       </c>
       <c r="K108" s="23" t="n"/>
-      <c r="L108" s="66" t="inlineStr"/>
+      <c r="L108" s="67" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="53" t="inlineStr">
@@ -6286,7 +6312,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C109" s="74" t="inlineStr">
+      <c r="C109" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6323,7 +6349,7 @@
         </is>
       </c>
       <c r="K109" s="23" t="n"/>
-      <c r="L109" s="66" t="inlineStr"/>
+      <c r="L109" s="67" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="53" t="inlineStr">
@@ -6336,7 +6362,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C110" s="74" t="inlineStr">
+      <c r="C110" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6373,7 +6399,7 @@
         </is>
       </c>
       <c r="K110" s="23" t="n"/>
-      <c r="L110" s="66" t="inlineStr"/>
+      <c r="L110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="53" t="inlineStr">
@@ -6382,7 +6408,7 @@
         </is>
       </c>
       <c r="B111" s="23" t="inlineStr"/>
-      <c r="C111" s="75" t="inlineStr">
+      <c r="C111" s="77" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -6401,7 +6427,7 @@
       <c r="I111" s="65" t="inlineStr"/>
       <c r="J111" s="23" t="inlineStr"/>
       <c r="K111" s="23" t="n"/>
-      <c r="L111" s="66" t="inlineStr"/>
+      <c r="L111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="53" t="inlineStr">
@@ -6414,7 +6440,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C112" s="74" t="inlineStr">
+      <c r="C112" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6451,7 +6477,7 @@
         </is>
       </c>
       <c r="K112" s="23" t="n"/>
-      <c r="L112" s="66" t="inlineStr"/>
+      <c r="L112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="53" t="inlineStr">
@@ -6464,7 +6490,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C113" s="74" t="inlineStr">
+      <c r="C113" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6501,7 +6527,7 @@
         </is>
       </c>
       <c r="K113" s="23" t="n"/>
-      <c r="L113" s="66" t="inlineStr"/>
+      <c r="L113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="53" t="inlineStr">
@@ -6514,7 +6540,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C114" s="74" t="inlineStr">
+      <c r="C114" s="76" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -6551,7 +6577,7 @@
         </is>
       </c>
       <c r="K114" s="23" t="n"/>
-      <c r="L114" s="66" t="inlineStr"/>
+      <c r="L114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="53" t="inlineStr">
@@ -6560,7 +6586,7 @@
         </is>
       </c>
       <c r="B115" s="23" t="inlineStr"/>
-      <c r="C115" s="74" t="inlineStr">
+      <c r="C115" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6579,7 +6605,7 @@
       <c r="I115" s="65" t="inlineStr"/>
       <c r="J115" s="23" t="inlineStr"/>
       <c r="K115" s="23" t="n"/>
-      <c r="L115" s="66" t="inlineStr"/>
+      <c r="L115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="53" t="inlineStr">
@@ -6592,7 +6618,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C116" s="74" t="inlineStr">
+      <c r="C116" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6629,7 +6655,7 @@
         </is>
       </c>
       <c r="K116" s="23" t="n"/>
-      <c r="L116" s="66" t="inlineStr"/>
+      <c r="L116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="53" t="inlineStr">
@@ -6642,7 +6668,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C117" s="74" t="inlineStr">
+      <c r="C117" s="76" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -6679,7 +6705,7 @@
         </is>
       </c>
       <c r="K117" s="23" t="n"/>
-      <c r="L117" s="66" t="inlineStr"/>
+      <c r="L117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="53" t="inlineStr">
@@ -6692,7 +6718,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C118" s="74" t="inlineStr">
+      <c r="C118" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6729,7 +6755,7 @@
         </is>
       </c>
       <c r="K118" s="23" t="n"/>
-      <c r="L118" s="66" t="inlineStr"/>
+      <c r="L118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="53" t="inlineStr">
@@ -6738,7 +6764,7 @@
         </is>
       </c>
       <c r="B119" s="23" t="inlineStr"/>
-      <c r="C119" s="74" t="inlineStr">
+      <c r="C119" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6757,7 +6783,7 @@
       <c r="I119" s="65" t="inlineStr"/>
       <c r="J119" s="23" t="inlineStr"/>
       <c r="K119" s="23" t="n"/>
-      <c r="L119" s="66" t="inlineStr"/>
+      <c r="L119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="53" t="inlineStr">
@@ -6766,7 +6792,7 @@
         </is>
       </c>
       <c r="B120" s="23" t="inlineStr"/>
-      <c r="C120" s="74" t="inlineStr">
+      <c r="C120" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6785,7 +6811,7 @@
       <c r="I120" s="65" t="inlineStr"/>
       <c r="J120" s="23" t="inlineStr"/>
       <c r="K120" s="23" t="n"/>
-      <c r="L120" s="66" t="inlineStr"/>
+      <c r="L120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="53" t="inlineStr">
@@ -6798,7 +6824,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C121" s="74" t="inlineStr">
+      <c r="C121" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6835,7 +6861,7 @@
         </is>
       </c>
       <c r="K121" s="23" t="n"/>
-      <c r="L121" s="66" t="inlineStr"/>
+      <c r="L121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="53" t="inlineStr">
@@ -6848,7 +6874,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C122" s="74" t="inlineStr">
+      <c r="C122" s="76" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -6885,7 +6911,7 @@
         </is>
       </c>
       <c r="K122" s="23" t="n"/>
-      <c r="L122" s="66" t="inlineStr"/>
+      <c r="L122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="53" t="inlineStr">
@@ -6894,7 +6920,7 @@
         </is>
       </c>
       <c r="B123" s="23" t="inlineStr"/>
-      <c r="C123" s="74" t="inlineStr">
+      <c r="C123" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6913,7 +6939,7 @@
       <c r="I123" s="65" t="inlineStr"/>
       <c r="J123" s="23" t="inlineStr"/>
       <c r="K123" s="23" t="n"/>
-      <c r="L123" s="66" t="inlineStr"/>
+      <c r="L123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="53" t="inlineStr">
@@ -6922,7 +6948,7 @@
         </is>
       </c>
       <c r="B124" s="23" t="inlineStr"/>
-      <c r="C124" s="74" t="inlineStr">
+      <c r="C124" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6941,7 +6967,7 @@
       <c r="I124" s="65" t="inlineStr"/>
       <c r="J124" s="23" t="inlineStr"/>
       <c r="K124" s="23" t="n"/>
-      <c r="L124" s="66" t="inlineStr"/>
+      <c r="L124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="53" t="inlineStr">
@@ -6954,7 +6980,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C125" s="74" t="inlineStr">
+      <c r="C125" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6991,7 +7017,7 @@
         </is>
       </c>
       <c r="K125" s="23" t="n"/>
-      <c r="L125" s="66" t="inlineStr"/>
+      <c r="L125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="53" t="inlineStr">
@@ -7004,7 +7030,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C126" s="74" t="inlineStr">
+      <c r="C126" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7041,7 +7067,7 @@
         </is>
       </c>
       <c r="K126" s="23" t="n"/>
-      <c r="L126" s="66" t="inlineStr"/>
+      <c r="L126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="53" t="inlineStr">
@@ -7050,7 +7076,7 @@
         </is>
       </c>
       <c r="B127" s="23" t="inlineStr"/>
-      <c r="C127" s="75" t="inlineStr">
+      <c r="C127" s="77" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -7069,7 +7095,7 @@
       <c r="I127" s="65" t="inlineStr"/>
       <c r="J127" s="23" t="inlineStr"/>
       <c r="K127" s="23" t="n"/>
-      <c r="L127" s="66" t="inlineStr"/>
+      <c r="L127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="53" t="inlineStr">
@@ -7082,7 +7108,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C128" s="75" t="inlineStr">
+      <c r="C128" s="77" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -7119,7 +7145,7 @@
         </is>
       </c>
       <c r="K128" s="23" t="n"/>
-      <c r="L128" s="66" t="inlineStr"/>
+      <c r="L128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="53" t="inlineStr">
@@ -7132,7 +7158,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C129" s="75" t="inlineStr">
+      <c r="C129" s="77" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -7169,7 +7195,7 @@
         </is>
       </c>
       <c r="K129" s="23" t="n"/>
-      <c r="L129" s="66" t="inlineStr"/>
+      <c r="L129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="53" t="inlineStr">
@@ -7182,7 +7208,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C130" s="75" t="inlineStr">
+      <c r="C130" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -7219,7 +7245,7 @@
         </is>
       </c>
       <c r="K130" s="23" t="n"/>
-      <c r="L130" s="66" t="inlineStr"/>
+      <c r="L130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="53" t="inlineStr">
@@ -7232,7 +7258,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C131" s="75" t="inlineStr">
+      <c r="C131" s="77" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7269,7 +7295,7 @@
         </is>
       </c>
       <c r="K131" s="23" t="n"/>
-      <c r="L131" s="66" t="inlineStr"/>
+      <c r="L131" s="67" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="53" t="inlineStr">
@@ -7282,7 +7308,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C132" s="75" t="inlineStr">
+      <c r="C132" s="77" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -7319,7 +7345,7 @@
         </is>
       </c>
       <c r="K132" s="23" t="n"/>
-      <c r="L132" s="66" t="inlineStr"/>
+      <c r="L132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="53" t="inlineStr">
@@ -7332,7 +7358,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C133" s="75" t="inlineStr">
+      <c r="C133" s="77" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -7369,7 +7395,7 @@
         </is>
       </c>
       <c r="K133" s="23" t="n"/>
-      <c r="L133" s="66" t="inlineStr"/>
+      <c r="L133" s="67" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="53" t="inlineStr">
@@ -7382,7 +7408,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C134" s="75" t="inlineStr">
+      <c r="C134" s="77" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7419,7 +7445,7 @@
         </is>
       </c>
       <c r="K134" s="23" t="n"/>
-      <c r="L134" s="66" t="inlineStr"/>
+      <c r="L134" s="67" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="53" t="inlineStr">
@@ -7432,7 +7458,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C135" s="75" t="inlineStr">
+      <c r="C135" s="77" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -7469,7 +7495,7 @@
         </is>
       </c>
       <c r="K135" s="23" t="n"/>
-      <c r="L135" s="66" t="inlineStr"/>
+      <c r="L135" s="67" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="53" t="inlineStr">
@@ -7482,7 +7508,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C136" s="76" t="inlineStr">
+      <c r="C136" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7519,7 +7545,7 @@
         </is>
       </c>
       <c r="K136" s="23" t="n"/>
-      <c r="L136" s="66" t="inlineStr"/>
+      <c r="L136" s="67" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="53" t="inlineStr">
@@ -7532,7 +7558,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C137" s="75" t="inlineStr">
+      <c r="C137" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7569,7 +7595,7 @@
         </is>
       </c>
       <c r="K137" s="23" t="n"/>
-      <c r="L137" s="66" t="inlineStr"/>
+      <c r="L137" s="67" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="53" t="inlineStr">
@@ -7582,7 +7608,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C138" s="76" t="inlineStr">
+      <c r="C138" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7619,7 +7645,7 @@
         </is>
       </c>
       <c r="K138" s="23" t="n"/>
-      <c r="L138" s="66" t="inlineStr"/>
+      <c r="L138" s="67" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="53" t="inlineStr">
@@ -7632,7 +7658,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C139" s="75" t="inlineStr">
+      <c r="C139" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7669,7 +7695,7 @@
         </is>
       </c>
       <c r="K139" s="23" t="n"/>
-      <c r="L139" s="66" t="inlineStr"/>
+      <c r="L139" s="67" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="53" t="inlineStr">
@@ -7682,7 +7708,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C140" s="76" t="inlineStr">
+      <c r="C140" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -7719,7 +7745,7 @@
         </is>
       </c>
       <c r="K140" s="23" t="n"/>
-      <c r="L140" s="66" t="inlineStr"/>
+      <c r="L140" s="67" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="53" t="inlineStr">
@@ -7732,7 +7758,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C141" s="74" t="inlineStr">
+      <c r="C141" s="76" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -7769,7 +7795,7 @@
         </is>
       </c>
       <c r="K141" s="23" t="n"/>
-      <c r="L141" s="66" t="inlineStr"/>
+      <c r="L141" s="67" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="53" t="inlineStr">
@@ -7782,7 +7808,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C142" s="75" t="inlineStr">
+      <c r="C142" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7819,7 +7845,7 @@
         </is>
       </c>
       <c r="K142" s="23" t="n"/>
-      <c r="L142" s="66" t="inlineStr"/>
+      <c r="L142" s="67" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="53" t="inlineStr">
@@ -7832,7 +7858,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C143" s="74" t="inlineStr">
+      <c r="C143" s="76" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7869,7 +7895,7 @@
         </is>
       </c>
       <c r="K143" s="23" t="n"/>
-      <c r="L143" s="66" t="inlineStr"/>
+      <c r="L143" s="67" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="53" t="inlineStr">
@@ -7882,7 +7908,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C144" s="75" t="inlineStr">
+      <c r="C144" s="77" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -7919,7 +7945,7 @@
         </is>
       </c>
       <c r="K144" s="23" t="n"/>
-      <c r="L144" s="66" t="inlineStr"/>
+      <c r="L144" s="67" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="53" t="inlineStr">
@@ -7932,7 +7958,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C145" s="75" t="inlineStr">
+      <c r="C145" s="77" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -7969,7 +7995,7 @@
         </is>
       </c>
       <c r="K145" s="23" t="n"/>
-      <c r="L145" s="66" t="inlineStr"/>
+      <c r="L145" s="67" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="53" t="inlineStr">
@@ -7982,7 +8008,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C146" s="75" t="inlineStr">
+      <c r="C146" s="77" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8019,7 +8045,7 @@
         </is>
       </c>
       <c r="K146" s="23" t="n"/>
-      <c r="L146" s="66" t="inlineStr"/>
+      <c r="L146" s="67" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="53" t="inlineStr">
@@ -8032,7 +8058,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C147" s="75" t="inlineStr">
+      <c r="C147" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8069,7 +8095,7 @@
         </is>
       </c>
       <c r="K147" s="23" t="n"/>
-      <c r="L147" s="66" t="inlineStr"/>
+      <c r="L147" s="67" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="53" t="inlineStr">
@@ -8082,7 +8108,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C148" s="75" t="inlineStr">
+      <c r="C148" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8119,7 +8145,7 @@
         </is>
       </c>
       <c r="K148" s="23" t="n"/>
-      <c r="L148" s="66" t="inlineStr"/>
+      <c r="L148" s="67" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="53" t="inlineStr">
@@ -8132,7 +8158,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C149" s="75" t="inlineStr">
+      <c r="C149" s="77" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -8169,7 +8195,7 @@
         </is>
       </c>
       <c r="K149" s="23" t="n"/>
-      <c r="L149" s="66" t="inlineStr"/>
+      <c r="L149" s="67" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="53" t="inlineStr">
@@ -8182,7 +8208,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C150" s="74" t="inlineStr">
+      <c r="C150" s="76" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8219,7 +8245,7 @@
         </is>
       </c>
       <c r="K150" s="23" t="n"/>
-      <c r="L150" s="66" t="inlineStr"/>
+      <c r="L150" s="67" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="53" t="inlineStr">
@@ -8232,7 +8258,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C151" s="74" t="inlineStr">
+      <c r="C151" s="76" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8269,7 +8295,7 @@
         </is>
       </c>
       <c r="K151" s="23" t="n"/>
-      <c r="L151" s="66" t="inlineStr"/>
+      <c r="L151" s="67" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="53" t="inlineStr">
@@ -8282,7 +8308,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C152" s="74" t="inlineStr">
+      <c r="C152" s="76" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8319,7 +8345,7 @@
         </is>
       </c>
       <c r="K152" s="23" t="n"/>
-      <c r="L152" s="66" t="inlineStr"/>
+      <c r="L152" s="67" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="53" t="inlineStr">
@@ -8332,7 +8358,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C153" s="75" t="inlineStr">
+      <c r="C153" s="77" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -8369,7 +8395,7 @@
         </is>
       </c>
       <c r="K153" s="23" t="n"/>
-      <c r="L153" s="66" t="inlineStr"/>
+      <c r="L153" s="67" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="53" t="inlineStr">
@@ -8382,7 +8408,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C154" s="75" t="inlineStr">
+      <c r="C154" s="77" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8419,7 +8445,7 @@
         </is>
       </c>
       <c r="K154" s="23" t="n"/>
-      <c r="L154" s="66" t="inlineStr"/>
+      <c r="L154" s="67" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="53" t="inlineStr">
@@ -8432,7 +8458,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C155" s="74" t="inlineStr">
+      <c r="C155" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8469,7 +8495,7 @@
         </is>
       </c>
       <c r="K155" s="23" t="n"/>
-      <c r="L155" s="66" t="inlineStr"/>
+      <c r="L155" s="67" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="53" t="inlineStr">
@@ -8482,7 +8508,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C156" s="76" t="inlineStr">
+      <c r="C156" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -8519,7 +8545,7 @@
         </is>
       </c>
       <c r="K156" s="23" t="n"/>
-      <c r="L156" s="66" t="inlineStr"/>
+      <c r="L156" s="67" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="53" t="inlineStr">
@@ -8532,7 +8558,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C157" s="75" t="inlineStr">
+      <c r="C157" s="77" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -8569,7 +8595,7 @@
         </is>
       </c>
       <c r="K157" s="23" t="n"/>
-      <c r="L157" s="66" t="inlineStr"/>
+      <c r="L157" s="67" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="53" t="inlineStr">
@@ -8582,7 +8608,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C158" s="76" t="inlineStr">
+      <c r="C158" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8615,11 +8641,11 @@
       </c>
       <c r="J158" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="K158" s="23" t="n"/>
-      <c r="L158" s="66" t="inlineStr"/>
+      <c r="L158" s="67" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="53" t="inlineStr">
@@ -8632,7 +8658,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C159" s="76" t="inlineStr">
+      <c r="C159" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8669,7 +8695,7 @@
         </is>
       </c>
       <c r="K159" s="23" t="n"/>
-      <c r="L159" s="66" t="inlineStr"/>
+      <c r="L159" s="67" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="53" t="inlineStr">
@@ -8682,7 +8708,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C160" s="76" t="inlineStr">
+      <c r="C160" s="78" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -8719,7 +8745,7 @@
         </is>
       </c>
       <c r="K160" s="23" t="n"/>
-      <c r="L160" s="66" t="inlineStr"/>
+      <c r="L160" s="67" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="53" t="inlineStr">
@@ -8732,7 +8758,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C161" s="76" t="inlineStr">
+      <c r="C161" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -8761,7 +8787,7 @@
       <c r="I161" s="65" t="inlineStr"/>
       <c r="J161" s="23" t="inlineStr"/>
       <c r="K161" s="23" t="n"/>
-      <c r="L161" s="66" t="inlineStr"/>
+      <c r="L161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="53" t="inlineStr">
@@ -8774,7 +8800,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C162" s="75" t="inlineStr">
+      <c r="C162" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8803,7 +8829,7 @@
       <c r="I162" s="65" t="inlineStr"/>
       <c r="J162" s="23" t="inlineStr"/>
       <c r="K162" s="23" t="n"/>
-      <c r="L162" s="66" t="inlineStr"/>
+      <c r="L162" s="67" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="53" t="inlineStr">
@@ -8816,7 +8842,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C163" s="75" t="inlineStr">
+      <c r="C163" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8845,7 +8871,7 @@
       <c r="I163" s="65" t="inlineStr"/>
       <c r="J163" s="23" t="inlineStr"/>
       <c r="K163" s="23" t="n"/>
-      <c r="L163" s="66" t="inlineStr"/>
+      <c r="L163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="53" t="inlineStr">
@@ -8858,7 +8884,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C164" s="75" t="inlineStr">
+      <c r="C164" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -8887,7 +8913,7 @@
       <c r="I164" s="65" t="inlineStr"/>
       <c r="J164" s="23" t="inlineStr"/>
       <c r="K164" s="23" t="n"/>
-      <c r="L164" s="66" t="inlineStr"/>
+      <c r="L164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="53" t="inlineStr">
@@ -8900,7 +8926,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C165" s="76" t="inlineStr">
+      <c r="C165" s="78" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -8937,7 +8963,7 @@
         </is>
       </c>
       <c r="K165" s="23" t="n"/>
-      <c r="L165" s="66" t="inlineStr"/>
+      <c r="L165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="53" t="inlineStr">
@@ -8950,7 +8976,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C166" s="75" t="inlineStr">
+      <c r="C166" s="77" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -8979,7 +9005,7 @@
       <c r="I166" s="65" t="inlineStr"/>
       <c r="J166" s="23" t="inlineStr"/>
       <c r="K166" s="23" t="n"/>
-      <c r="L166" s="66" t="inlineStr"/>
+      <c r="L166" s="67" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="53" t="inlineStr">
@@ -8992,7 +9018,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C167" s="75" t="inlineStr">
+      <c r="C167" s="77" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -9021,7 +9047,7 @@
       <c r="I167" s="65" t="inlineStr"/>
       <c r="J167" s="23" t="inlineStr"/>
       <c r="K167" s="23" t="n"/>
-      <c r="L167" s="66" t="inlineStr"/>
+      <c r="L167" s="67" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="53" t="inlineStr">
@@ -9034,7 +9060,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C168" s="76" t="inlineStr">
+      <c r="C168" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9071,7 +9097,7 @@
         </is>
       </c>
       <c r="K168" s="23" t="n"/>
-      <c r="L168" s="66" t="inlineStr"/>
+      <c r="L168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="53" t="inlineStr">
@@ -9084,7 +9110,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C169" s="76" t="inlineStr">
+      <c r="C169" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9121,7 +9147,7 @@
         </is>
       </c>
       <c r="K169" s="23" t="n"/>
-      <c r="L169" s="66" t="inlineStr"/>
+      <c r="L169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="53" t="inlineStr">
@@ -9134,7 +9160,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C170" s="76" t="inlineStr">
+      <c r="C170" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9171,7 +9197,7 @@
         </is>
       </c>
       <c r="K170" s="23" t="n"/>
-      <c r="L170" s="66" t="inlineStr"/>
+      <c r="L170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="53" t="inlineStr">
@@ -9184,7 +9210,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C171" s="76" t="inlineStr">
+      <c r="C171" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9221,7 +9247,7 @@
         </is>
       </c>
       <c r="K171" s="23" t="n"/>
-      <c r="L171" s="66" t="inlineStr"/>
+      <c r="L171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="53" t="inlineStr">
@@ -9234,7 +9260,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C172" s="76" t="inlineStr">
+      <c r="C172" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9271,7 +9297,7 @@
         </is>
       </c>
       <c r="K172" s="23" t="n"/>
-      <c r="L172" s="66" t="inlineStr"/>
+      <c r="L172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="53" t="inlineStr">
@@ -9284,7 +9310,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C173" s="76" t="inlineStr">
+      <c r="C173" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9321,7 +9347,7 @@
         </is>
       </c>
       <c r="K173" s="23" t="n"/>
-      <c r="L173" s="66" t="inlineStr"/>
+      <c r="L173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="53" t="inlineStr">
@@ -9334,7 +9360,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C174" s="76" t="inlineStr">
+      <c r="C174" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9371,7 +9397,7 @@
         </is>
       </c>
       <c r="K174" s="23" t="n"/>
-      <c r="L174" s="66" t="inlineStr"/>
+      <c r="L174" s="67" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="53" t="inlineStr">
@@ -9384,7 +9410,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C175" s="76" t="inlineStr">
+      <c r="C175" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9421,7 +9447,7 @@
         </is>
       </c>
       <c r="K175" s="23" t="n"/>
-      <c r="L175" s="66" t="inlineStr"/>
+      <c r="L175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="53" t="inlineStr">
@@ -9434,7 +9460,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C176" s="76" t="inlineStr">
+      <c r="C176" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9471,7 +9497,7 @@
         </is>
       </c>
       <c r="K176" s="23" t="n"/>
-      <c r="L176" s="66" t="inlineStr"/>
+      <c r="L176" s="67" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="53" t="inlineStr">
@@ -9484,7 +9510,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C177" s="76" t="inlineStr">
+      <c r="C177" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9521,7 +9547,7 @@
         </is>
       </c>
       <c r="K177" s="23" t="n"/>
-      <c r="L177" s="66" t="inlineStr"/>
+      <c r="L177" s="67" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="53" t="inlineStr">
@@ -9534,7 +9560,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C178" s="76" t="inlineStr">
+      <c r="C178" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9571,7 +9597,7 @@
         </is>
       </c>
       <c r="K178" s="23" t="n"/>
-      <c r="L178" s="66" t="inlineStr"/>
+      <c r="L178" s="67" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="53" t="inlineStr">
@@ -9584,7 +9610,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C179" s="76" t="inlineStr">
+      <c r="C179" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9621,7 +9647,7 @@
         </is>
       </c>
       <c r="K179" s="23" t="n"/>
-      <c r="L179" s="66" t="inlineStr"/>
+      <c r="L179" s="67" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="53" t="inlineStr">
@@ -9634,7 +9660,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C180" s="76" t="inlineStr">
+      <c r="C180" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9671,7 +9697,7 @@
         </is>
       </c>
       <c r="K180" s="23" t="n"/>
-      <c r="L180" s="66" t="inlineStr"/>
+      <c r="L180" s="67" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="53" t="inlineStr">
@@ -9684,7 +9710,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C181" s="76" t="inlineStr">
+      <c r="C181" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9721,7 +9747,7 @@
         </is>
       </c>
       <c r="K181" s="23" t="n"/>
-      <c r="L181" s="66" t="inlineStr"/>
+      <c r="L181" s="67" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="53" t="inlineStr">
@@ -9734,7 +9760,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C182" s="76" t="inlineStr">
+      <c r="C182" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9771,7 +9797,7 @@
         </is>
       </c>
       <c r="K182" s="23" t="n"/>
-      <c r="L182" s="66" t="inlineStr"/>
+      <c r="L182" s="67" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="53" t="inlineStr">
@@ -9784,7 +9810,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C183" s="76" t="inlineStr">
+      <c r="C183" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9821,7 +9847,7 @@
         </is>
       </c>
       <c r="K183" s="23" t="n"/>
-      <c r="L183" s="66" t="inlineStr"/>
+      <c r="L183" s="67" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="53" t="inlineStr">
@@ -9834,7 +9860,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C184" s="75" t="inlineStr">
+      <c r="C184" s="77" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9871,7 +9897,7 @@
         </is>
       </c>
       <c r="K184" s="23" t="n"/>
-      <c r="L184" s="66" t="inlineStr"/>
+      <c r="L184" s="67" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="53" t="inlineStr">
@@ -9884,7 +9910,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C185" s="76" t="inlineStr">
+      <c r="C185" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9921,7 +9947,7 @@
         </is>
       </c>
       <c r="K185" s="23" t="n"/>
-      <c r="L185" s="66" t="inlineStr"/>
+      <c r="L185" s="67" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="53" t="inlineStr">
@@ -9934,7 +9960,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C186" s="76" t="inlineStr">
+      <c r="C186" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9971,7 +9997,7 @@
         </is>
       </c>
       <c r="K186" s="23" t="n"/>
-      <c r="L186" s="66" t="inlineStr"/>
+      <c r="L186" s="67" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="53" t="inlineStr">
@@ -9984,7 +10010,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C187" s="76" t="inlineStr">
+      <c r="C187" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10021,7 +10047,7 @@
         </is>
       </c>
       <c r="K187" s="23" t="n"/>
-      <c r="L187" s="66" t="inlineStr"/>
+      <c r="L187" s="67" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="53" t="inlineStr">
@@ -10034,7 +10060,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C188" s="76" t="inlineStr">
+      <c r="C188" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10071,7 +10097,7 @@
         </is>
       </c>
       <c r="K188" s="23" t="n"/>
-      <c r="L188" s="66" t="inlineStr"/>
+      <c r="L188" s="67" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="53" t="inlineStr">
@@ -10084,7 +10110,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C189" s="76" t="inlineStr">
+      <c r="C189" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10121,7 +10147,7 @@
         </is>
       </c>
       <c r="K189" s="23" t="n"/>
-      <c r="L189" s="66" t="inlineStr"/>
+      <c r="L189" s="67" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="53" t="inlineStr">
@@ -10134,7 +10160,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C190" s="76" t="inlineStr">
+      <c r="C190" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10171,7 +10197,7 @@
         </is>
       </c>
       <c r="K190" s="23" t="n"/>
-      <c r="L190" s="66" t="inlineStr"/>
+      <c r="L190" s="67" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="53" t="inlineStr">
@@ -10184,7 +10210,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C191" s="76" t="inlineStr">
+      <c r="C191" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -10221,7 +10247,7 @@
         </is>
       </c>
       <c r="K191" s="23" t="n"/>
-      <c r="L191" s="66" t="inlineStr"/>
+      <c r="L191" s="67" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="53" t="inlineStr">
@@ -10234,7 +10260,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C192" s="76" t="inlineStr">
+      <c r="C192" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -10263,7 +10289,7 @@
       <c r="I192" s="65" t="inlineStr"/>
       <c r="J192" s="23" t="inlineStr"/>
       <c r="K192" s="23" t="n"/>
-      <c r="L192" s="66" t="inlineStr"/>
+      <c r="L192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="53" t="inlineStr">
@@ -10276,7 +10302,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C193" s="75" t="inlineStr">
+      <c r="C193" s="77" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -10305,7 +10331,7 @@
       <c r="I193" s="65" t="inlineStr"/>
       <c r="J193" s="23" t="inlineStr"/>
       <c r="K193" s="23" t="n"/>
-      <c r="L193" s="66" t="inlineStr"/>
+      <c r="L193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="53" t="inlineStr">
@@ -10318,7 +10344,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C194" s="76" t="inlineStr">
+      <c r="C194" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -10347,7 +10373,7 @@
       <c r="I194" s="65" t="inlineStr"/>
       <c r="J194" s="23" t="inlineStr"/>
       <c r="K194" s="23" t="n"/>
-      <c r="L194" s="66" t="inlineStr"/>
+      <c r="L194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="53" t="inlineStr">
@@ -10360,7 +10386,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C195" s="76" t="inlineStr">
+      <c r="C195" s="78" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -10389,7 +10415,7 @@
       <c r="I195" s="65" t="inlineStr"/>
       <c r="J195" s="23" t="inlineStr"/>
       <c r="K195" s="23" t="n"/>
-      <c r="L195" s="66" t="inlineStr"/>
+      <c r="L195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="53" t="inlineStr">
@@ -10402,7 +10428,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C196" s="75" t="inlineStr">
+      <c r="C196" s="77" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -10431,7 +10457,7 @@
       <c r="I196" s="65" t="inlineStr"/>
       <c r="J196" s="23" t="inlineStr"/>
       <c r="K196" s="23" t="n"/>
-      <c r="L196" s="66" t="inlineStr"/>
+      <c r="L196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="53" t="inlineStr">
@@ -10444,7 +10470,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C197" s="76" t="inlineStr">
+      <c r="C197" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10473,7 +10499,7 @@
       <c r="I197" s="65" t="inlineStr"/>
       <c r="J197" s="23" t="inlineStr"/>
       <c r="K197" s="23" t="n"/>
-      <c r="L197" s="66" t="inlineStr"/>
+      <c r="L197" s="67" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="53" t="inlineStr">
@@ -10486,7 +10512,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C198" s="76" t="inlineStr">
+      <c r="C198" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10515,7 +10541,7 @@
       <c r="I198" s="65" t="inlineStr"/>
       <c r="J198" s="23" t="inlineStr"/>
       <c r="K198" s="23" t="n"/>
-      <c r="L198" s="66" t="inlineStr"/>
+      <c r="L198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="53" t="inlineStr">
@@ -10528,7 +10554,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C199" s="75" t="inlineStr">
+      <c r="C199" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10557,7 +10583,7 @@
       <c r="I199" s="65" t="inlineStr"/>
       <c r="J199" s="23" t="inlineStr"/>
       <c r="K199" s="23" t="n"/>
-      <c r="L199" s="66" t="inlineStr"/>
+      <c r="L199" s="67" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="53" t="inlineStr">
@@ -10570,7 +10596,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C200" s="75" t="inlineStr">
+      <c r="C200" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10599,7 +10625,7 @@
       <c r="I200" s="65" t="inlineStr"/>
       <c r="J200" s="23" t="inlineStr"/>
       <c r="K200" s="23" t="n"/>
-      <c r="L200" s="66" t="inlineStr"/>
+      <c r="L200" s="67" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="53" t="inlineStr">
@@ -10612,7 +10638,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C201" s="75" t="inlineStr">
+      <c r="C201" s="77" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -10641,7 +10667,7 @@
       <c r="I201" s="65" t="inlineStr"/>
       <c r="J201" s="23" t="inlineStr"/>
       <c r="K201" s="23" t="n"/>
-      <c r="L201" s="66" t="inlineStr"/>
+      <c r="L201" s="67" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="53" t="inlineStr">
@@ -10654,7 +10680,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C202" s="76" t="inlineStr">
+      <c r="C202" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10691,7 +10717,7 @@
         </is>
       </c>
       <c r="K202" s="23" t="n"/>
-      <c r="L202" s="66" t="inlineStr"/>
+      <c r="L202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="53" t="inlineStr">
@@ -10704,7 +10730,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C203" s="76" t="inlineStr">
+      <c r="C203" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10741,7 +10767,7 @@
         </is>
       </c>
       <c r="K203" s="23" t="n"/>
-      <c r="L203" s="66" t="inlineStr"/>
+      <c r="L203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="53" t="inlineStr">
@@ -10754,7 +10780,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C204" s="76" t="inlineStr">
+      <c r="C204" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10791,7 +10817,7 @@
         </is>
       </c>
       <c r="K204" s="23" t="n"/>
-      <c r="L204" s="66" t="inlineStr"/>
+      <c r="L204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="53" t="inlineStr">
@@ -10804,7 +10830,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C205" s="76" t="inlineStr">
+      <c r="C205" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10841,7 +10867,7 @@
         </is>
       </c>
       <c r="K205" s="23" t="n"/>
-      <c r="L205" s="66" t="inlineStr"/>
+      <c r="L205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="53" t="inlineStr">
@@ -10854,7 +10880,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C206" s="76" t="inlineStr">
+      <c r="C206" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10891,7 +10917,7 @@
         </is>
       </c>
       <c r="K206" s="23" t="n"/>
-      <c r="L206" s="66" t="inlineStr"/>
+      <c r="L206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="53" t="inlineStr">
@@ -10904,7 +10930,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C207" s="76" t="inlineStr">
+      <c r="C207" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10941,7 +10967,7 @@
         </is>
       </c>
       <c r="K207" s="23" t="n"/>
-      <c r="L207" s="66" t="inlineStr"/>
+      <c r="L207" s="67" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="53" t="inlineStr">
@@ -10954,7 +10980,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C208" s="76" t="inlineStr">
+      <c r="C208" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -10991,7 +11017,7 @@
         </is>
       </c>
       <c r="K208" s="23" t="n"/>
-      <c r="L208" s="66" t="inlineStr"/>
+      <c r="L208" s="67" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="53" t="inlineStr">
@@ -11004,7 +11030,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C209" s="75" t="inlineStr">
+      <c r="C209" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -11041,7 +11067,7 @@
         </is>
       </c>
       <c r="K209" s="23" t="n"/>
-      <c r="L209" s="66" t="inlineStr"/>
+      <c r="L209" s="67" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="53" t="inlineStr">
@@ -11054,7 +11080,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C210" s="75" t="inlineStr">
+      <c r="C210" s="77" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11091,7 +11117,7 @@
         </is>
       </c>
       <c r="K210" s="23" t="n"/>
-      <c r="L210" s="66" t="inlineStr"/>
+      <c r="L210" s="67" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="53" t="inlineStr">
@@ -11104,7 +11130,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C211" s="76" t="inlineStr">
+      <c r="C211" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11141,7 +11167,7 @@
         </is>
       </c>
       <c r="K211" s="23" t="n"/>
-      <c r="L211" s="66" t="inlineStr"/>
+      <c r="L211" s="67" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="53" t="inlineStr">
@@ -11154,7 +11180,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C212" s="74" t="inlineStr">
+      <c r="C212" s="76" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -11191,7 +11217,7 @@
         </is>
       </c>
       <c r="K212" s="23" t="n"/>
-      <c r="L212" s="66" t="inlineStr"/>
+      <c r="L212" s="67" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="53" t="inlineStr">
@@ -11204,7 +11230,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C213" s="74" t="inlineStr">
+      <c r="C213" s="76" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -11241,7 +11267,7 @@
         </is>
       </c>
       <c r="K213" s="23" t="n"/>
-      <c r="L213" s="66" t="inlineStr"/>
+      <c r="L213" s="67" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="53" t="inlineStr">
@@ -11254,7 +11280,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C214" s="76" t="inlineStr">
+      <c r="C214" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11291,7 +11317,7 @@
         </is>
       </c>
       <c r="K214" s="23" t="n"/>
-      <c r="L214" s="66" t="inlineStr"/>
+      <c r="L214" s="67" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="53" t="inlineStr">
@@ -11304,7 +11330,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C215" s="76" t="inlineStr">
+      <c r="C215" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11341,7 +11367,7 @@
         </is>
       </c>
       <c r="K215" s="23" t="n"/>
-      <c r="L215" s="66" t="inlineStr"/>
+      <c r="L215" s="67" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="53" t="inlineStr">
@@ -11350,7 +11376,7 @@
         </is>
       </c>
       <c r="B216" s="23" t="inlineStr"/>
-      <c r="C216" s="74" t="inlineStr">
+      <c r="C216" s="76" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -11369,7 +11395,7 @@
       <c r="I216" s="65" t="inlineStr"/>
       <c r="J216" s="23" t="inlineStr"/>
       <c r="K216" s="23" t="n"/>
-      <c r="L216" s="66" t="inlineStr"/>
+      <c r="L216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="53" t="inlineStr">
@@ -11382,7 +11408,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C217" s="74" t="inlineStr">
+      <c r="C217" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11419,7 +11445,7 @@
         </is>
       </c>
       <c r="K217" s="23" t="n"/>
-      <c r="L217" s="66" t="inlineStr"/>
+      <c r="L217" s="67" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="53" t="inlineStr">
@@ -11432,7 +11458,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C218" s="74" t="inlineStr">
+      <c r="C218" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11469,7 +11495,7 @@
         </is>
       </c>
       <c r="K218" s="23" t="n"/>
-      <c r="L218" s="66" t="inlineStr"/>
+      <c r="L218" s="67" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="53" t="inlineStr">
@@ -11482,7 +11508,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C219" s="74" t="inlineStr">
+      <c r="C219" s="76" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -11519,7 +11545,7 @@
         </is>
       </c>
       <c r="K219" s="23" t="n"/>
-      <c r="L219" s="66" t="inlineStr"/>
+      <c r="L219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="53" t="inlineStr">
@@ -11532,7 +11558,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C220" s="74" t="inlineStr">
+      <c r="C220" s="76" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -11569,7 +11595,7 @@
         </is>
       </c>
       <c r="K220" s="23" t="n"/>
-      <c r="L220" s="66" t="inlineStr"/>
+      <c r="L220" s="67" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="53" t="inlineStr">
@@ -11582,7 +11608,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C221" s="75" t="inlineStr">
+      <c r="C221" s="77" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11619,7 +11645,7 @@
         </is>
       </c>
       <c r="K221" s="23" t="n"/>
-      <c r="L221" s="66" t="inlineStr"/>
+      <c r="L221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="53" t="inlineStr">
@@ -11632,7 +11658,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C222" s="76" t="inlineStr">
+      <c r="C222" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11669,7 +11695,7 @@
         </is>
       </c>
       <c r="K222" s="23" t="n"/>
-      <c r="L222" s="66" t="inlineStr"/>
+      <c r="L222" s="67" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="53" t="inlineStr">
@@ -11682,7 +11708,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C223" s="74" t="inlineStr">
+      <c r="C223" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11719,7 +11745,7 @@
         </is>
       </c>
       <c r="K223" s="23" t="n"/>
-      <c r="L223" s="66" t="inlineStr"/>
+      <c r="L223" s="67" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="53" t="inlineStr">
@@ -11732,7 +11758,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C224" s="74" t="inlineStr">
+      <c r="C224" s="76" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -11769,7 +11795,7 @@
         </is>
       </c>
       <c r="K224" s="23" t="n"/>
-      <c r="L224" s="66" t="inlineStr"/>
+      <c r="L224" s="67" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="53" t="inlineStr">
@@ -11782,7 +11808,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C225" s="74" t="inlineStr">
+      <c r="C225" s="76" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -11819,7 +11845,7 @@
         </is>
       </c>
       <c r="K225" s="23" t="n"/>
-      <c r="L225" s="66" t="inlineStr"/>
+      <c r="L225" s="67" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="53" t="inlineStr">
@@ -11832,7 +11858,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C226" s="74" t="inlineStr">
+      <c r="C226" s="76" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -11869,7 +11895,7 @@
         </is>
       </c>
       <c r="K226" s="23" t="n"/>
-      <c r="L226" s="66" t="inlineStr"/>
+      <c r="L226" s="67" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="53" t="inlineStr">
@@ -11882,7 +11908,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C227" s="74" t="inlineStr">
+      <c r="C227" s="76" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -11919,7 +11945,7 @@
         </is>
       </c>
       <c r="K227" s="23" t="n"/>
-      <c r="L227" s="66" t="inlineStr"/>
+      <c r="L227" s="67" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="53" t="inlineStr">
@@ -11932,7 +11958,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C228" s="74" t="inlineStr">
+      <c r="C228" s="76" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -11969,7 +11995,7 @@
         </is>
       </c>
       <c r="K228" s="23" t="n"/>
-      <c r="L228" s="66" t="inlineStr"/>
+      <c r="L228" s="67" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="53" t="inlineStr">
@@ -11982,7 +12008,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C229" s="74" t="inlineStr">
+      <c r="C229" s="76" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -12019,7 +12045,7 @@
         </is>
       </c>
       <c r="K229" s="23" t="n"/>
-      <c r="L229" s="66" t="inlineStr"/>
+      <c r="L229" s="67" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="53" t="inlineStr">
@@ -12028,7 +12054,7 @@
         </is>
       </c>
       <c r="B230" s="23" t="inlineStr"/>
-      <c r="C230" s="76" t="inlineStr">
+      <c r="C230" s="78" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -12047,7 +12073,7 @@
       <c r="I230" s="65" t="inlineStr"/>
       <c r="J230" s="23" t="inlineStr"/>
       <c r="K230" s="23" t="n"/>
-      <c r="L230" s="66" t="inlineStr"/>
+      <c r="L230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="53" t="inlineStr">
@@ -12056,7 +12082,7 @@
         </is>
       </c>
       <c r="B231" s="23" t="inlineStr"/>
-      <c r="C231" s="76" t="inlineStr">
+      <c r="C231" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -12075,7 +12101,7 @@
       <c r="I231" s="65" t="inlineStr"/>
       <c r="J231" s="23" t="inlineStr"/>
       <c r="K231" s="23" t="n"/>
-      <c r="L231" s="66" t="inlineStr"/>
+      <c r="L231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="53" t="inlineStr">
@@ -12088,7 +12114,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C232" s="74" t="inlineStr">
+      <c r="C232" s="76" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -12125,7 +12151,7 @@
         </is>
       </c>
       <c r="K232" s="23" t="n"/>
-      <c r="L232" s="66" t="inlineStr"/>
+      <c r="L232" s="67" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="53" t="inlineStr">
@@ -12138,7 +12164,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C233" s="74" t="inlineStr">
+      <c r="C233" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12175,7 +12201,7 @@
         </is>
       </c>
       <c r="K233" s="23" t="n"/>
-      <c r="L233" s="66" t="inlineStr"/>
+      <c r="L233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="53" t="inlineStr">
@@ -12188,7 +12214,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C234" s="74" t="inlineStr">
+      <c r="C234" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12225,7 +12251,7 @@
         </is>
       </c>
       <c r="K234" s="23" t="n"/>
-      <c r="L234" s="66" t="inlineStr"/>
+      <c r="L234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="53" t="inlineStr">
@@ -12238,7 +12264,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C235" s="74" t="inlineStr">
+      <c r="C235" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12275,7 +12301,7 @@
         </is>
       </c>
       <c r="K235" s="23" t="n"/>
-      <c r="L235" s="66" t="inlineStr"/>
+      <c r="L235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="53" t="inlineStr">
@@ -12288,7 +12314,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C236" s="74" t="inlineStr">
+      <c r="C236" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12325,7 +12351,7 @@
         </is>
       </c>
       <c r="K236" s="23" t="n"/>
-      <c r="L236" s="66" t="inlineStr"/>
+      <c r="L236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="53" t="inlineStr">
@@ -12338,7 +12364,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C237" s="74" t="inlineStr">
+      <c r="C237" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12375,7 +12401,7 @@
         </is>
       </c>
       <c r="K237" s="23" t="n"/>
-      <c r="L237" s="66" t="inlineStr"/>
+      <c r="L237" s="67" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="53" t="inlineStr">
@@ -12388,7 +12414,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C238" s="74" t="inlineStr">
+      <c r="C238" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12425,7 +12451,7 @@
         </is>
       </c>
       <c r="K238" s="23" t="n"/>
-      <c r="L238" s="66" t="inlineStr"/>
+      <c r="L238" s="67" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="53" t="inlineStr">
@@ -12438,7 +12464,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C239" s="74" t="inlineStr">
+      <c r="C239" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12475,7 +12501,7 @@
         </is>
       </c>
       <c r="K239" s="23" t="n"/>
-      <c r="L239" s="66" t="inlineStr"/>
+      <c r="L239" s="67" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="53" t="inlineStr">
@@ -12484,7 +12510,7 @@
         </is>
       </c>
       <c r="B240" s="23" t="inlineStr"/>
-      <c r="C240" s="76" t="inlineStr">
+      <c r="C240" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -12503,7 +12529,7 @@
       <c r="I240" s="65" t="inlineStr"/>
       <c r="J240" s="23" t="inlineStr"/>
       <c r="K240" s="23" t="n"/>
-      <c r="L240" s="66" t="inlineStr"/>
+      <c r="L240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="53" t="inlineStr">
@@ -12516,7 +12542,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C241" s="74" t="inlineStr">
+      <c r="C241" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12553,7 +12579,7 @@
         </is>
       </c>
       <c r="K241" s="23" t="n"/>
-      <c r="L241" s="66" t="inlineStr"/>
+      <c r="L241" s="67" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="53" t="inlineStr">
@@ -12566,7 +12592,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C242" s="74" t="inlineStr">
+      <c r="C242" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12603,7 +12629,7 @@
         </is>
       </c>
       <c r="K242" s="23" t="n"/>
-      <c r="L242" s="66" t="inlineStr"/>
+      <c r="L242" s="67" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="53" t="inlineStr">
@@ -12616,7 +12642,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C243" s="74" t="inlineStr">
+      <c r="C243" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12653,7 +12679,7 @@
         </is>
       </c>
       <c r="K243" s="23" t="n"/>
-      <c r="L243" s="66" t="inlineStr"/>
+      <c r="L243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="53" t="inlineStr">
@@ -12666,7 +12692,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C244" s="75" t="inlineStr">
+      <c r="C244" s="77" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -12703,7 +12729,7 @@
         </is>
       </c>
       <c r="K244" s="23" t="n"/>
-      <c r="L244" s="66" t="inlineStr"/>
+      <c r="L244" s="67" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="53" t="inlineStr">
@@ -12712,7 +12738,7 @@
         </is>
       </c>
       <c r="B245" s="23" t="inlineStr"/>
-      <c r="C245" s="74" t="inlineStr">
+      <c r="C245" s="76" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -12731,7 +12757,7 @@
       <c r="I245" s="65" t="inlineStr"/>
       <c r="J245" s="23" t="inlineStr"/>
       <c r="K245" s="23" t="n"/>
-      <c r="L245" s="66" t="inlineStr"/>
+      <c r="L245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="53" t="inlineStr">
@@ -12744,7 +12770,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C246" s="75" t="inlineStr">
+      <c r="C246" s="77" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -12781,7 +12807,7 @@
         </is>
       </c>
       <c r="K246" s="23" t="n"/>
-      <c r="L246" s="66" t="inlineStr"/>
+      <c r="L246" s="67" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="53" t="inlineStr">
@@ -12794,7 +12820,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C247" s="76" t="inlineStr">
+      <c r="C247" s="78" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -12823,7 +12849,7 @@
       <c r="I247" s="65" t="inlineStr"/>
       <c r="J247" s="23" t="inlineStr"/>
       <c r="K247" s="23" t="n"/>
-      <c r="L247" s="66" t="inlineStr"/>
+      <c r="L247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="53" t="inlineStr">
@@ -12836,7 +12862,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C248" s="75" t="inlineStr">
+      <c r="C248" s="77" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -12873,7 +12899,7 @@
         </is>
       </c>
       <c r="K248" s="23" t="n"/>
-      <c r="L248" s="66" t="inlineStr"/>
+      <c r="L248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="53" t="inlineStr">
@@ -12886,7 +12912,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C249" s="75" t="inlineStr">
+      <c r="C249" s="77" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -12923,7 +12949,7 @@
         </is>
       </c>
       <c r="K249" s="23" t="n"/>
-      <c r="L249" s="66" t="inlineStr"/>
+      <c r="L249" s="67" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="53" t="inlineStr">
@@ -12936,7 +12962,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C250" s="75" t="inlineStr">
+      <c r="C250" s="77" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -12973,7 +12999,7 @@
         </is>
       </c>
       <c r="K250" s="23" t="n"/>
-      <c r="L250" s="66" t="inlineStr"/>
+      <c r="L250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="53" t="inlineStr">
@@ -12986,7 +13012,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C251" s="75" t="inlineStr">
+      <c r="C251" s="77" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -13023,7 +13049,7 @@
         </is>
       </c>
       <c r="K251" s="23" t="n"/>
-      <c r="L251" s="66" t="inlineStr"/>
+      <c r="L251" s="67" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="53" t="inlineStr">
@@ -13036,7 +13062,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C252" s="76" t="inlineStr">
+      <c r="C252" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -13073,7 +13099,7 @@
         </is>
       </c>
       <c r="K252" s="23" t="n"/>
-      <c r="L252" s="66" t="inlineStr"/>
+      <c r="L252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="53" t="inlineStr">
@@ -13086,7 +13112,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C253" s="76" t="inlineStr">
+      <c r="C253" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -13123,7 +13149,7 @@
         </is>
       </c>
       <c r="K253" s="23" t="n"/>
-      <c r="L253" s="66" t="inlineStr"/>
+      <c r="L253" s="67" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="53" t="inlineStr">
@@ -13136,7 +13162,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C254" s="75" t="inlineStr">
+      <c r="C254" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13173,7 +13199,7 @@
         </is>
       </c>
       <c r="K254" s="23" t="n"/>
-      <c r="L254" s="66" t="inlineStr"/>
+      <c r="L254" s="67" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="53" t="inlineStr">
@@ -13186,7 +13212,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C255" s="75" t="inlineStr">
+      <c r="C255" s="77" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -13223,7 +13249,7 @@
         </is>
       </c>
       <c r="K255" s="23" t="n"/>
-      <c r="L255" s="66" t="inlineStr"/>
+      <c r="L255" s="67" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="53" t="inlineStr">
@@ -13236,7 +13262,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C256" s="76" t="inlineStr">
+      <c r="C256" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -13273,7 +13299,7 @@
         </is>
       </c>
       <c r="K256" s="23" t="n"/>
-      <c r="L256" s="66" t="inlineStr"/>
+      <c r="L256" s="67" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="53" t="inlineStr">
@@ -13286,7 +13312,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C257" s="75" t="inlineStr">
+      <c r="C257" s="77" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -13323,7 +13349,7 @@
         </is>
       </c>
       <c r="K257" s="23" t="n"/>
-      <c r="L257" s="66" t="inlineStr"/>
+      <c r="L257" s="67" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="53" t="inlineStr">
@@ -13336,7 +13362,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C258" s="74" t="inlineStr">
+      <c r="C258" s="76" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -13373,7 +13399,7 @@
         </is>
       </c>
       <c r="K258" s="23" t="n"/>
-      <c r="L258" s="66" t="inlineStr"/>
+      <c r="L258" s="67" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="53" t="inlineStr">
@@ -13386,7 +13412,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C259" s="75" t="inlineStr">
+      <c r="C259" s="77" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -13423,7 +13449,7 @@
         </is>
       </c>
       <c r="K259" s="23" t="n"/>
-      <c r="L259" s="66" t="inlineStr"/>
+      <c r="L259" s="67" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="53" t="inlineStr">
@@ -13436,7 +13462,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C260" s="75" t="inlineStr">
+      <c r="C260" s="77" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -13473,7 +13499,7 @@
         </is>
       </c>
       <c r="K260" s="23" t="n"/>
-      <c r="L260" s="66" t="inlineStr"/>
+      <c r="L260" s="67" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="53" t="inlineStr">
@@ -13486,7 +13512,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C261" s="75" t="inlineStr">
+      <c r="C261" s="77" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -13523,7 +13549,7 @@
         </is>
       </c>
       <c r="K261" s="23" t="n"/>
-      <c r="L261" s="66" t="inlineStr"/>
+      <c r="L261" s="67" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="53" t="inlineStr">
@@ -13536,7 +13562,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C262" s="74" t="inlineStr">
+      <c r="C262" s="76" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -13573,7 +13599,7 @@
         </is>
       </c>
       <c r="K262" s="23" t="n"/>
-      <c r="L262" s="66" t="inlineStr"/>
+      <c r="L262" s="67" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="53" t="inlineStr">
@@ -13586,7 +13612,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C263" s="74" t="inlineStr">
+      <c r="C263" s="76" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -13623,7 +13649,7 @@
         </is>
       </c>
       <c r="K263" s="23" t="n"/>
-      <c r="L263" s="66" t="inlineStr"/>
+      <c r="L263" s="67" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="53" t="inlineStr">
@@ -13636,7 +13662,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C264" s="74" t="inlineStr">
+      <c r="C264" s="76" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -13673,7 +13699,7 @@
         </is>
       </c>
       <c r="K264" s="23" t="n"/>
-      <c r="L264" s="66" t="inlineStr"/>
+      <c r="L264" s="67" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="53" t="inlineStr">
@@ -13686,7 +13712,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C265" s="74" t="inlineStr">
+      <c r="C265" s="76" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -13723,7 +13749,7 @@
         </is>
       </c>
       <c r="K265" s="23" t="n"/>
-      <c r="L265" s="66" t="inlineStr"/>
+      <c r="L265" s="67" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="53" t="inlineStr">
@@ -13736,7 +13762,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C266" s="74" t="inlineStr">
+      <c r="C266" s="76" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -13773,7 +13799,7 @@
         </is>
       </c>
       <c r="K266" s="23" t="n"/>
-      <c r="L266" s="66" t="inlineStr"/>
+      <c r="L266" s="67" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="53" t="inlineStr">
@@ -13786,7 +13812,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C267" s="74" t="inlineStr">
+      <c r="C267" s="76" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -13823,7 +13849,7 @@
         </is>
       </c>
       <c r="K267" s="23" t="n"/>
-      <c r="L267" s="66" t="inlineStr"/>
+      <c r="L267" s="67" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="53" t="inlineStr">
@@ -13836,7 +13862,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C268" s="74" t="inlineStr">
+      <c r="C268" s="76" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -13873,7 +13899,7 @@
         </is>
       </c>
       <c r="K268" s="23" t="n"/>
-      <c r="L268" s="66" t="inlineStr"/>
+      <c r="L268" s="67" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="53" t="inlineStr">
@@ -13886,7 +13912,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C269" s="74" t="inlineStr">
+      <c r="C269" s="76" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -13923,7 +13949,7 @@
         </is>
       </c>
       <c r="K269" s="23" t="n"/>
-      <c r="L269" s="66" t="inlineStr"/>
+      <c r="L269" s="67" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="53" t="inlineStr">
@@ -13936,7 +13962,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C270" s="74" t="inlineStr">
+      <c r="C270" s="76" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13973,7 +13999,7 @@
         </is>
       </c>
       <c r="K270" s="23" t="n"/>
-      <c r="L270" s="66" t="inlineStr"/>
+      <c r="L270" s="67" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="53" t="inlineStr">
@@ -13986,7 +14012,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C271" s="74" t="inlineStr">
+      <c r="C271" s="76" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -14023,7 +14049,7 @@
         </is>
       </c>
       <c r="K271" s="23" t="n"/>
-      <c r="L271" s="66" t="inlineStr"/>
+      <c r="L271" s="67" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="53" t="inlineStr">
@@ -14036,7 +14062,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C272" s="74" t="inlineStr">
+      <c r="C272" s="76" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -14073,7 +14099,7 @@
         </is>
       </c>
       <c r="K272" s="23" t="n"/>
-      <c r="L272" s="66" t="inlineStr"/>
+      <c r="L272" s="67" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="53" t="inlineStr">
@@ -14086,7 +14112,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C273" s="74" t="inlineStr">
+      <c r="C273" s="76" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -14123,7 +14149,7 @@
         </is>
       </c>
       <c r="K273" s="23" t="n"/>
-      <c r="L273" s="66" t="inlineStr"/>
+      <c r="L273" s="67" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="53" t="inlineStr">
@@ -14136,7 +14162,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C274" s="75" t="inlineStr">
+      <c r="C274" s="77" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -14173,7 +14199,7 @@
         </is>
       </c>
       <c r="K274" s="23" t="n"/>
-      <c r="L274" s="66" t="inlineStr"/>
+      <c r="L274" s="67" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="53" t="inlineStr">
@@ -14186,7 +14212,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C275" s="74" t="inlineStr">
+      <c r="C275" s="76" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -14223,7 +14249,7 @@
         </is>
       </c>
       <c r="K275" s="23" t="n"/>
-      <c r="L275" s="66" t="inlineStr"/>
+      <c r="L275" s="67" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="53" t="inlineStr">
@@ -14236,7 +14262,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C276" s="74" t="inlineStr">
+      <c r="C276" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14273,7 +14299,7 @@
         </is>
       </c>
       <c r="K276" s="23" t="n"/>
-      <c r="L276" s="66" t="inlineStr"/>
+      <c r="L276" s="67" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="53" t="inlineStr">
@@ -14286,7 +14312,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C277" s="75" t="inlineStr">
+      <c r="C277" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -14323,7 +14349,7 @@
         </is>
       </c>
       <c r="K277" s="23" t="n"/>
-      <c r="L277" s="66" t="inlineStr"/>
+      <c r="L277" s="67" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="53" t="inlineStr">
@@ -14336,7 +14362,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C278" s="74" t="inlineStr">
+      <c r="C278" s="76" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -14373,7 +14399,7 @@
         </is>
       </c>
       <c r="K278" s="23" t="n"/>
-      <c r="L278" s="66" t="inlineStr"/>
+      <c r="L278" s="67" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="53" t="inlineStr">
@@ -14386,7 +14412,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C279" s="74" t="inlineStr">
+      <c r="C279" s="76" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -14423,7 +14449,7 @@
         </is>
       </c>
       <c r="K279" s="23" t="n"/>
-      <c r="L279" s="66" t="inlineStr"/>
+      <c r="L279" s="67" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="53" t="inlineStr">
@@ -14436,7 +14462,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C280" s="74" t="inlineStr">
+      <c r="C280" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14473,7 +14499,7 @@
         </is>
       </c>
       <c r="K280" s="23" t="n"/>
-      <c r="L280" s="66" t="inlineStr"/>
+      <c r="L280" s="67" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="53" t="inlineStr">
@@ -14486,7 +14512,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C281" s="76" t="inlineStr">
+      <c r="C281" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14523,7 +14549,7 @@
         </is>
       </c>
       <c r="K281" s="23" t="n"/>
-      <c r="L281" s="66" t="inlineStr"/>
+      <c r="L281" s="67" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="53" t="inlineStr">
@@ -14536,7 +14562,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C282" s="74" t="inlineStr">
+      <c r="C282" s="76" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -14573,7 +14599,7 @@
         </is>
       </c>
       <c r="K282" s="23" t="n"/>
-      <c r="L282" s="66" t="inlineStr"/>
+      <c r="L282" s="67" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="53" t="inlineStr">
@@ -14586,7 +14612,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C283" s="74" t="inlineStr">
+      <c r="C283" s="76" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -14623,7 +14649,7 @@
         </is>
       </c>
       <c r="K283" s="23" t="n"/>
-      <c r="L283" s="66" t="inlineStr"/>
+      <c r="L283" s="67" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="53" t="inlineStr">
@@ -14636,7 +14662,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C284" s="76" t="inlineStr">
+      <c r="C284" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14673,7 +14699,7 @@
         </is>
       </c>
       <c r="K284" s="23" t="n"/>
-      <c r="L284" s="66" t="inlineStr"/>
+      <c r="L284" s="67" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="53" t="inlineStr">
@@ -14686,7 +14712,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C285" s="76" t="inlineStr">
+      <c r="C285" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14723,7 +14749,7 @@
         </is>
       </c>
       <c r="K285" s="23" t="n"/>
-      <c r="L285" s="66" t="inlineStr"/>
+      <c r="L285" s="67" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="53" t="inlineStr">
@@ -14736,7 +14762,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C286" s="76" t="inlineStr">
+      <c r="C286" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14773,7 +14799,7 @@
         </is>
       </c>
       <c r="K286" s="23" t="n"/>
-      <c r="L286" s="66" t="inlineStr"/>
+      <c r="L286" s="67" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="53" t="inlineStr">
@@ -14786,7 +14812,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C287" s="74" t="inlineStr">
+      <c r="C287" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14823,7 +14849,7 @@
         </is>
       </c>
       <c r="K287" s="23" t="n"/>
-      <c r="L287" s="66" t="inlineStr"/>
+      <c r="L287" s="67" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="53" t="inlineStr">
@@ -14836,7 +14862,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C288" s="74" t="inlineStr">
+      <c r="C288" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14873,7 +14899,7 @@
         </is>
       </c>
       <c r="K288" s="23" t="n"/>
-      <c r="L288" s="66" t="inlineStr"/>
+      <c r="L288" s="67" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="53" t="inlineStr">
@@ -14886,7 +14912,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C289" s="74" t="inlineStr">
+      <c r="C289" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14923,7 +14949,7 @@
         </is>
       </c>
       <c r="K289" s="23" t="n"/>
-      <c r="L289" s="66" t="inlineStr"/>
+      <c r="L289" s="67" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="53" t="inlineStr">
@@ -14936,7 +14962,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C290" s="74" t="inlineStr">
+      <c r="C290" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14973,7 +14999,7 @@
         </is>
       </c>
       <c r="K290" s="23" t="n"/>
-      <c r="L290" s="66" t="inlineStr"/>
+      <c r="L290" s="67" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="53" t="inlineStr">
@@ -14986,7 +15012,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C291" s="74" t="inlineStr">
+      <c r="C291" s="76" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -15023,7 +15049,7 @@
         </is>
       </c>
       <c r="K291" s="23" t="n"/>
-      <c r="L291" s="66" t="inlineStr"/>
+      <c r="L291" s="67" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="53" t="inlineStr">
@@ -15036,7 +15062,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C292" s="75" t="inlineStr">
+      <c r="C292" s="77" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -15073,7 +15099,7 @@
         </is>
       </c>
       <c r="K292" s="23" t="n"/>
-      <c r="L292" s="66" t="inlineStr"/>
+      <c r="L292" s="67" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L292"/>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -241,6 +241,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -309,12 +315,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -576,7 +576,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,13 +644,10 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -674,22 +671,25 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,13 +698,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1250,7 +1250,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -1304,7 +1304,7 @@
       <c r="L3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -1354,7 +1354,7 @@
       <c r="L4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="53" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -1404,7 +1404,7 @@
       <c r="L5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="53" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -1460,7 +1460,7 @@
       <c r="L6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="53" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -1512,7 +1512,7 @@
       <c r="L7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="53" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -1562,7 +1562,7 @@
       <c r="L8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="53" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -1612,7 +1612,7 @@
       <c r="L9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="53" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -1682,7 +1682,7 @@
       <c r="L10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -1732,7 +1732,7 @@
       <c r="L11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="53" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -1782,7 +1782,7 @@
       <c r="L12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -1834,7 +1834,7 @@
       <c r="L13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -1876,7 +1876,7 @@
       <c r="L14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="53" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -1926,7 +1926,7 @@
       <c r="L15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -1978,7 +1978,7 @@
       <c r="L16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -2030,7 +2030,7 @@
       <c r="L17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="68" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -2080,7 +2080,7 @@
       <c r="L18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="inlineStr">
+      <c r="A19" s="68" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -2130,7 +2130,7 @@
       <c r="L19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -2180,7 +2180,7 @@
       <c r="L20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="A21" s="68" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -2230,7 +2230,7 @@
       <c r="L21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="53" t="inlineStr">
+      <c r="A22" s="68" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -2280,7 +2280,7 @@
       <c r="L22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="inlineStr">
+      <c r="A23" s="68" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -2330,7 +2330,7 @@
       <c r="L23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="53" t="inlineStr">
+      <c r="A24" s="68" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -2384,7 +2384,7 @@
       <c r="L24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -2438,7 +2438,7 @@
       <c r="L25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -2490,7 +2490,7 @@
       <c r="L26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="inlineStr">
+      <c r="A27" s="68" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -2540,7 +2540,7 @@
       <c r="L27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="53" t="inlineStr">
+      <c r="A28" s="68" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -2590,7 +2590,7 @@
       <c r="L28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="inlineStr">
+      <c r="A29" s="68" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -2640,7 +2640,7 @@
       <c r="L29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="53" t="inlineStr">
+      <c r="A30" s="68" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -2690,7 +2690,7 @@
       <c r="L30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="53" t="inlineStr">
+      <c r="A31" s="68" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -2740,7 +2740,7 @@
       <c r="L31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="53" t="inlineStr">
+      <c r="A32" s="68" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -2782,7 +2782,7 @@
       <c r="L32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="inlineStr">
+      <c r="A33" s="68" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -2834,7 +2834,7 @@
       <c r="L33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="53" t="inlineStr">
+      <c r="A34" s="68" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -2884,7 +2884,7 @@
       <c r="L34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="53" t="inlineStr">
+      <c r="A35" s="68" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -2934,7 +2934,7 @@
       <c r="L35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="53" t="inlineStr">
+      <c r="A36" s="68" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -2976,7 +2976,7 @@
       <c r="L36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="53" t="inlineStr">
+      <c r="A37" s="68" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -3026,7 +3026,7 @@
       <c r="L37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="53" t="inlineStr">
+      <c r="A38" s="68" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -3078,7 +3078,7 @@
       <c r="L38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="53" t="inlineStr">
+      <c r="A39" s="68" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -3128,7 +3128,7 @@
       <c r="L39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="53" t="inlineStr">
+      <c r="A40" s="68" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -3178,7 +3178,7 @@
       <c r="L40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="53" t="inlineStr">
+      <c r="A41" s="68" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -3228,7 +3228,7 @@
       <c r="L41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="53" t="inlineStr">
+      <c r="A42" s="68" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -3270,7 +3270,7 @@
       <c r="L42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="53" t="inlineStr">
+      <c r="A43" s="68" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -3322,7 +3322,7 @@
       <c r="L43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="53" t="inlineStr">
+      <c r="A44" s="68" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -3372,7 +3372,7 @@
       <c r="L44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="53" t="inlineStr">
+      <c r="A45" s="68" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -3422,7 +3422,7 @@
       <c r="L45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="53" t="inlineStr">
+      <c r="A46" s="68" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -3464,7 +3464,7 @@
       <c r="L46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="53" t="inlineStr">
+      <c r="A47" s="68" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -3506,7 +3506,7 @@
       <c r="L47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="53" t="inlineStr">
+      <c r="A48" s="68" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -3548,7 +3548,7 @@
       <c r="L48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="53" t="inlineStr">
+      <c r="A49" s="68" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -3590,7 +3590,7 @@
       <c r="L49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="53" t="inlineStr">
+      <c r="A50" s="68" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="C51" s="80" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D51" s="66" t="inlineStr">
@@ -3690,7 +3690,7 @@
       <c r="L51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="inlineStr">
+      <c r="A52" s="68" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -3740,7 +3740,7 @@
       <c r="L52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="53" t="inlineStr">
+      <c r="A53" s="68" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -3790,7 +3790,7 @@
       <c r="L53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="53" t="inlineStr">
+      <c r="A54" s="68" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -3832,7 +3832,7 @@
       <c r="L54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="53" t="inlineStr">
+      <c r="A55" s="68" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -3874,7 +3874,7 @@
       <c r="L55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="53" t="inlineStr">
+      <c r="A56" s="68" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -3916,7 +3916,7 @@
       <c r="L56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="53" t="inlineStr">
+      <c r="A57" s="68" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -3958,7 +3958,7 @@
       <c r="L57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="53" t="inlineStr">
+      <c r="A58" s="68" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -4008,7 +4008,7 @@
       <c r="L58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="53" t="inlineStr">
+      <c r="A59" s="68" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -4050,7 +4050,7 @@
       <c r="L59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="53" t="inlineStr">
+      <c r="A60" s="68" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -4092,7 +4092,7 @@
       <c r="L60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="53" t="inlineStr">
+      <c r="A61" s="68" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -4142,7 +4142,7 @@
       <c r="L61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="53" t="inlineStr">
+      <c r="A62" s="68" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -4192,7 +4192,7 @@
       <c r="L62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="53" t="inlineStr">
+      <c r="A63" s="68" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -4238,7 +4238,7 @@
       <c r="L63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="53" t="inlineStr">
+      <c r="A64" s="68" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -4280,7 +4280,7 @@
       <c r="L64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="53" t="inlineStr">
+      <c r="A65" s="68" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -4330,7 +4330,7 @@
       <c r="L65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="53" t="inlineStr">
+      <c r="A66" s="68" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -4380,7 +4380,7 @@
       <c r="L66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="53" t="inlineStr">
+      <c r="A67" s="68" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -4430,7 +4430,7 @@
       <c r="L67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="53" t="inlineStr">
+      <c r="A68" s="68" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -4480,7 +4480,7 @@
       <c r="L68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="53" t="inlineStr">
+      <c r="A69" s="68" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -4530,7 +4530,7 @@
       <c r="L69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="53" t="inlineStr">
+      <c r="A70" s="68" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -4580,7 +4580,7 @@
       <c r="L70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="53" t="inlineStr">
+      <c r="A71" s="68" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -4630,7 +4630,7 @@
       <c r="L71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="53" t="inlineStr">
+      <c r="A72" s="68" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -4680,7 +4680,7 @@
       <c r="L72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="53" t="inlineStr">
+      <c r="A73" s="68" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -4730,7 +4730,7 @@
       <c r="L73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="53" t="inlineStr">
+      <c r="A74" s="68" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -4780,7 +4780,7 @@
       <c r="L74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="53" t="inlineStr">
+      <c r="A75" s="68" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -4830,7 +4830,7 @@
       <c r="L75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="53" t="inlineStr">
+      <c r="A76" s="68" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -4880,7 +4880,7 @@
       <c r="L76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="53" t="inlineStr">
+      <c r="A77" s="68" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -4930,7 +4930,7 @@
       <c r="L77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="53" t="inlineStr">
+      <c r="A78" s="68" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -4980,7 +4980,7 @@
       <c r="L78" s="67" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="53" t="inlineStr">
+      <c r="A79" s="68" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -5030,7 +5030,7 @@
       <c r="L79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="53" t="inlineStr">
+      <c r="A80" s="68" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -5080,7 +5080,7 @@
       <c r="L80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="53" t="inlineStr">
+      <c r="A81" s="68" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -5130,7 +5130,7 @@
       <c r="L81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="53" t="inlineStr">
+      <c r="A82" s="68" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -5180,7 +5180,7 @@
       <c r="L82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="53" t="inlineStr">
+      <c r="A83" s="68" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -5226,7 +5226,7 @@
       <c r="L83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="53" t="inlineStr">
+      <c r="A84" s="68" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -5276,7 +5276,7 @@
       <c r="L84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="53" t="inlineStr">
+      <c r="A85" s="68" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -5326,7 +5326,7 @@
       <c r="L85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="53" t="inlineStr">
+      <c r="A86" s="68" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -5378,7 +5378,7 @@
       <c r="L86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="53" t="inlineStr">
+      <c r="A87" s="68" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -5406,7 +5406,7 @@
       <c r="L87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="53" t="inlineStr">
+      <c r="A88" s="68" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -5434,7 +5434,7 @@
       <c r="L88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="53" t="inlineStr">
+      <c r="A89" s="68" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -5484,7 +5484,7 @@
       <c r="L89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="53" t="inlineStr">
+      <c r="A90" s="68" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -5512,7 +5512,7 @@
       <c r="L90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="53" t="inlineStr">
+      <c r="A91" s="68" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -5540,7 +5540,7 @@
       <c r="L91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="53" t="inlineStr">
+      <c r="A92" s="68" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -5568,7 +5568,7 @@
       <c r="L92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="53" t="inlineStr">
+      <c r="A93" s="68" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -5618,7 +5618,7 @@
       <c r="L93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="53" t="inlineStr">
+      <c r="A94" s="68" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -5668,7 +5668,7 @@
       <c r="L94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="53" t="inlineStr">
+      <c r="A95" s="68" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -5696,7 +5696,7 @@
       <c r="L95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="53" t="inlineStr">
+      <c r="A96" s="68" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -5746,7 +5746,7 @@
       <c r="L96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="53" t="inlineStr">
+      <c r="A97" s="68" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -5796,7 +5796,7 @@
       <c r="L97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="53" t="inlineStr">
+      <c r="A98" s="68" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -5846,7 +5846,7 @@
       <c r="L98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="53" t="inlineStr">
+      <c r="A99" s="68" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -5896,7 +5896,7 @@
       <c r="L99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="53" t="inlineStr">
+      <c r="A100" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -5946,7 +5946,7 @@
       <c r="L100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="53" t="inlineStr">
+      <c r="A101" s="68" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -5996,7 +5996,7 @@
       <c r="L101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="53" t="inlineStr">
+      <c r="A102" s="68" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -6024,7 +6024,7 @@
       <c r="L102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="53" t="inlineStr">
+      <c r="A103" s="68" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -6052,7 +6052,7 @@
       <c r="L103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="53" t="inlineStr">
+      <c r="A104" s="68" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -6102,7 +6102,7 @@
       <c r="L104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="53" t="inlineStr">
+      <c r="A105" s="68" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -6152,7 +6152,7 @@
       <c r="L105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="53" t="inlineStr">
+      <c r="A106" s="68" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -6202,7 +6202,7 @@
       <c r="L106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="53" t="inlineStr">
+      <c r="A107" s="68" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -6252,7 +6252,7 @@
       <c r="L107" s="67" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="53" t="inlineStr">
+      <c r="A108" s="68" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -6302,7 +6302,7 @@
       <c r="L108" s="67" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="53" t="inlineStr">
+      <c r="A109" s="68" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -6352,7 +6352,7 @@
       <c r="L109" s="67" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="53" t="inlineStr">
+      <c r="A110" s="68" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -6402,7 +6402,7 @@
       <c r="L110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="53" t="inlineStr">
+      <c r="A111" s="68" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -6430,7 +6430,7 @@
       <c r="L111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="53" t="inlineStr">
+      <c r="A112" s="68" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -6480,7 +6480,7 @@
       <c r="L112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="53" t="inlineStr">
+      <c r="A113" s="68" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -6530,7 +6530,7 @@
       <c r="L113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="53" t="inlineStr">
+      <c r="A114" s="68" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -6580,7 +6580,7 @@
       <c r="L114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="53" t="inlineStr">
+      <c r="A115" s="68" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -6608,7 +6608,7 @@
       <c r="L115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="53" t="inlineStr">
+      <c r="A116" s="68" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -6658,7 +6658,7 @@
       <c r="L116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="53" t="inlineStr">
+      <c r="A117" s="68" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -6708,7 +6708,7 @@
       <c r="L117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="53" t="inlineStr">
+      <c r="A118" s="68" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -6758,7 +6758,7 @@
       <c r="L118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="53" t="inlineStr">
+      <c r="A119" s="68" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -6786,7 +6786,7 @@
       <c r="L119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="53" t="inlineStr">
+      <c r="A120" s="68" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -6814,7 +6814,7 @@
       <c r="L120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="53" t="inlineStr">
+      <c r="A121" s="68" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -6864,7 +6864,7 @@
       <c r="L121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="53" t="inlineStr">
+      <c r="A122" s="68" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -6914,7 +6914,7 @@
       <c r="L122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="53" t="inlineStr">
+      <c r="A123" s="68" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -6942,7 +6942,7 @@
       <c r="L123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="53" t="inlineStr">
+      <c r="A124" s="68" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -6970,7 +6970,7 @@
       <c r="L124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="53" t="inlineStr">
+      <c r="A125" s="68" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -7020,7 +7020,7 @@
       <c r="L125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="53" t="inlineStr">
+      <c r="A126" s="68" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -7070,7 +7070,7 @@
       <c r="L126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="53" t="inlineStr">
+      <c r="A127" s="68" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -7098,7 +7098,7 @@
       <c r="L127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="53" t="inlineStr">
+      <c r="A128" s="68" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -7148,7 +7148,7 @@
       <c r="L128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="53" t="inlineStr">
+      <c r="A129" s="68" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -7198,7 +7198,7 @@
       <c r="L129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="53" t="inlineStr">
+      <c r="A130" s="68" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -7248,7 +7248,7 @@
       <c r="L130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="53" t="inlineStr">
+      <c r="A131" s="68" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -7298,7 +7298,7 @@
       <c r="L131" s="67" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="53" t="inlineStr">
+      <c r="A132" s="68" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -7348,7 +7348,7 @@
       <c r="L132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="53" t="inlineStr">
+      <c r="A133" s="68" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -7398,7 +7398,7 @@
       <c r="L133" s="67" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="53" t="inlineStr">
+      <c r="A134" s="68" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -7448,7 +7448,7 @@
       <c r="L134" s="67" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="53" t="inlineStr">
+      <c r="A135" s="68" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -7498,7 +7498,7 @@
       <c r="L135" s="67" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="53" t="inlineStr">
+      <c r="A136" s="68" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -7548,7 +7548,7 @@
       <c r="L136" s="67" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="53" t="inlineStr">
+      <c r="A137" s="68" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -7598,7 +7598,7 @@
       <c r="L137" s="67" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="53" t="inlineStr">
+      <c r="A138" s="68" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -7648,7 +7648,7 @@
       <c r="L138" s="67" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="53" t="inlineStr">
+      <c r="A139" s="68" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -7698,7 +7698,7 @@
       <c r="L139" s="67" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="53" t="inlineStr">
+      <c r="A140" s="68" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -7748,7 +7748,7 @@
       <c r="L140" s="67" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="53" t="inlineStr">
+      <c r="A141" s="68" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -7798,7 +7798,7 @@
       <c r="L141" s="67" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="53" t="inlineStr">
+      <c r="A142" s="68" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -7848,7 +7848,7 @@
       <c r="L142" s="67" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="53" t="inlineStr">
+      <c r="A143" s="68" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -7898,7 +7898,7 @@
       <c r="L143" s="67" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="53" t="inlineStr">
+      <c r="A144" s="68" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -7948,7 +7948,7 @@
       <c r="L144" s="67" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="53" t="inlineStr">
+      <c r="A145" s="68" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -7998,7 +7998,7 @@
       <c r="L145" s="67" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="53" t="inlineStr">
+      <c r="A146" s="68" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -8048,7 +8048,7 @@
       <c r="L146" s="67" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="53" t="inlineStr">
+      <c r="A147" s="68" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -8098,7 +8098,7 @@
       <c r="L147" s="67" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="53" t="inlineStr">
+      <c r="A148" s="68" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -8148,7 +8148,7 @@
       <c r="L148" s="67" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="53" t="inlineStr">
+      <c r="A149" s="68" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -8198,7 +8198,7 @@
       <c r="L149" s="67" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="53" t="inlineStr">
+      <c r="A150" s="68" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -8248,7 +8248,7 @@
       <c r="L150" s="67" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="53" t="inlineStr">
+      <c r="A151" s="68" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -8298,7 +8298,7 @@
       <c r="L151" s="67" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="53" t="inlineStr">
+      <c r="A152" s="68" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -8348,7 +8348,7 @@
       <c r="L152" s="67" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="53" t="inlineStr">
+      <c r="A153" s="68" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -8398,7 +8398,7 @@
       <c r="L153" s="67" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="53" t="inlineStr">
+      <c r="A154" s="68" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -8448,7 +8448,7 @@
       <c r="L154" s="67" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="53" t="inlineStr">
+      <c r="A155" s="68" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -8498,7 +8498,7 @@
       <c r="L155" s="67" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="53" t="inlineStr">
+      <c r="A156" s="68" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -8548,7 +8548,7 @@
       <c r="L156" s="67" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="53" t="inlineStr">
+      <c r="A157" s="68" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -8598,7 +8598,7 @@
       <c r="L157" s="67" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="53" t="inlineStr">
+      <c r="A158" s="68" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -8648,7 +8648,7 @@
       <c r="L158" s="67" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="53" t="inlineStr">
+      <c r="A159" s="68" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -8698,7 +8698,7 @@
       <c r="L159" s="67" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="53" t="inlineStr">
+      <c r="A160" s="68" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -8748,7 +8748,7 @@
       <c r="L160" s="67" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="53" t="inlineStr">
+      <c r="A161" s="68" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -8790,7 +8790,7 @@
       <c r="L161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="53" t="inlineStr">
+      <c r="A162" s="68" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -8832,7 +8832,7 @@
       <c r="L162" s="67" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="53" t="inlineStr">
+      <c r="A163" s="68" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -8874,7 +8874,7 @@
       <c r="L163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="53" t="inlineStr">
+      <c r="A164" s="68" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -8916,7 +8916,7 @@
       <c r="L164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="53" t="inlineStr">
+      <c r="A165" s="68" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -8966,7 +8966,7 @@
       <c r="L165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="53" t="inlineStr">
+      <c r="A166" s="68" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -9008,7 +9008,7 @@
       <c r="L166" s="67" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="53" t="inlineStr">
+      <c r="A167" s="68" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9050,7 +9050,7 @@
       <c r="L167" s="67" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="53" t="inlineStr">
+      <c r="A168" s="68" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -9100,7 +9100,7 @@
       <c r="L168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="53" t="inlineStr">
+      <c r="A169" s="68" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -9150,7 +9150,7 @@
       <c r="L169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="53" t="inlineStr">
+      <c r="A170" s="68" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -9200,7 +9200,7 @@
       <c r="L170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="53" t="inlineStr">
+      <c r="A171" s="68" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -9250,7 +9250,7 @@
       <c r="L171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="53" t="inlineStr">
+      <c r="A172" s="68" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -9300,7 +9300,7 @@
       <c r="L172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="53" t="inlineStr">
+      <c r="A173" s="68" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -9350,7 +9350,7 @@
       <c r="L173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="53" t="inlineStr">
+      <c r="A174" s="68" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -9400,7 +9400,7 @@
       <c r="L174" s="67" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="53" t="inlineStr">
+      <c r="A175" s="68" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -9450,7 +9450,7 @@
       <c r="L175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="53" t="inlineStr">
+      <c r="A176" s="68" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -9500,7 +9500,7 @@
       <c r="L176" s="67" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="53" t="inlineStr">
+      <c r="A177" s="68" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -9550,7 +9550,7 @@
       <c r="L177" s="67" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="53" t="inlineStr">
+      <c r="A178" s="68" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -9600,7 +9600,7 @@
       <c r="L178" s="67" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="53" t="inlineStr">
+      <c r="A179" s="68" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -9650,7 +9650,7 @@
       <c r="L179" s="67" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="53" t="inlineStr">
+      <c r="A180" s="68" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -9700,7 +9700,7 @@
       <c r="L180" s="67" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="53" t="inlineStr">
+      <c r="A181" s="68" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -9750,7 +9750,7 @@
       <c r="L181" s="67" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="53" t="inlineStr">
+      <c r="A182" s="68" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -9800,7 +9800,7 @@
       <c r="L182" s="67" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="53" t="inlineStr">
+      <c r="A183" s="68" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -9850,7 +9850,7 @@
       <c r="L183" s="67" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="53" t="inlineStr">
+      <c r="A184" s="68" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -9900,7 +9900,7 @@
       <c r="L184" s="67" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="53" t="inlineStr">
+      <c r="A185" s="68" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -9950,7 +9950,7 @@
       <c r="L185" s="67" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="53" t="inlineStr">
+      <c r="A186" s="68" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -10000,7 +10000,7 @@
       <c r="L186" s="67" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="53" t="inlineStr">
+      <c r="A187" s="68" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -10050,7 +10050,7 @@
       <c r="L187" s="67" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="53" t="inlineStr">
+      <c r="A188" s="68" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -10100,7 +10100,7 @@
       <c r="L188" s="67" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="53" t="inlineStr">
+      <c r="A189" s="68" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -10150,7 +10150,7 @@
       <c r="L189" s="67" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="53" t="inlineStr">
+      <c r="A190" s="68" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -10200,7 +10200,7 @@
       <c r="L190" s="67" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="53" t="inlineStr">
+      <c r="A191" s="68" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -10250,7 +10250,7 @@
       <c r="L191" s="67" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="53" t="inlineStr">
+      <c r="A192" s="68" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -10292,7 +10292,7 @@
       <c r="L192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="53" t="inlineStr">
+      <c r="A193" s="68" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -10334,7 +10334,7 @@
       <c r="L193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="53" t="inlineStr">
+      <c r="A194" s="68" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -10376,7 +10376,7 @@
       <c r="L194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="53" t="inlineStr">
+      <c r="A195" s="68" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -10418,7 +10418,7 @@
       <c r="L195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="53" t="inlineStr">
+      <c r="A196" s="68" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -10460,7 +10460,7 @@
       <c r="L196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="53" t="inlineStr">
+      <c r="A197" s="68" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -10502,7 +10502,7 @@
       <c r="L197" s="67" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="53" t="inlineStr">
+      <c r="A198" s="68" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -10544,7 +10544,7 @@
       <c r="L198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="53" t="inlineStr">
+      <c r="A199" s="68" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -10586,7 +10586,7 @@
       <c r="L199" s="67" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="53" t="inlineStr">
+      <c r="A200" s="68" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -10628,7 +10628,7 @@
       <c r="L200" s="67" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="53" t="inlineStr">
+      <c r="A201" s="68" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -10670,7 +10670,7 @@
       <c r="L201" s="67" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="53" t="inlineStr">
+      <c r="A202" s="68" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -10720,7 +10720,7 @@
       <c r="L202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="53" t="inlineStr">
+      <c r="A203" s="68" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -10770,7 +10770,7 @@
       <c r="L203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="53" t="inlineStr">
+      <c r="A204" s="68" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -10820,7 +10820,7 @@
       <c r="L204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="53" t="inlineStr">
+      <c r="A205" s="68" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -10870,7 +10870,7 @@
       <c r="L205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="53" t="inlineStr">
+      <c r="A206" s="68" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -10920,7 +10920,7 @@
       <c r="L206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="53" t="inlineStr">
+      <c r="A207" s="68" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -10970,7 +10970,7 @@
       <c r="L207" s="67" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="53" t="inlineStr">
+      <c r="A208" s="68" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -11020,7 +11020,7 @@
       <c r="L208" s="67" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="53" t="inlineStr">
+      <c r="A209" s="68" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -11070,7 +11070,7 @@
       <c r="L209" s="67" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="53" t="inlineStr">
+      <c r="A210" s="68" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -11120,7 +11120,7 @@
       <c r="L210" s="67" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="53" t="inlineStr">
+      <c r="A211" s="68" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -11170,7 +11170,7 @@
       <c r="L211" s="67" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="53" t="inlineStr">
+      <c r="A212" s="68" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -11220,7 +11220,7 @@
       <c r="L212" s="67" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="53" t="inlineStr">
+      <c r="A213" s="68" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -11270,7 +11270,7 @@
       <c r="L213" s="67" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="53" t="inlineStr">
+      <c r="A214" s="68" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -11320,7 +11320,7 @@
       <c r="L214" s="67" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="53" t="inlineStr">
+      <c r="A215" s="68" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -11370,7 +11370,7 @@
       <c r="L215" s="67" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="53" t="inlineStr">
+      <c r="A216" s="68" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -11398,7 +11398,7 @@
       <c r="L216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="53" t="inlineStr">
+      <c r="A217" s="68" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -11448,7 +11448,7 @@
       <c r="L217" s="67" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="53" t="inlineStr">
+      <c r="A218" s="68" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -11498,7 +11498,7 @@
       <c r="L218" s="67" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="53" t="inlineStr">
+      <c r="A219" s="68" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -11548,7 +11548,7 @@
       <c r="L219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="53" t="inlineStr">
+      <c r="A220" s="68" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -11598,7 +11598,7 @@
       <c r="L220" s="67" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="53" t="inlineStr">
+      <c r="A221" s="68" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -11648,7 +11648,7 @@
       <c r="L221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="53" t="inlineStr">
+      <c r="A222" s="68" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -11698,7 +11698,7 @@
       <c r="L222" s="67" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="53" t="inlineStr">
+      <c r="A223" s="68" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -11748,7 +11748,7 @@
       <c r="L223" s="67" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="53" t="inlineStr">
+      <c r="A224" s="68" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -11798,7 +11798,7 @@
       <c r="L224" s="67" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="53" t="inlineStr">
+      <c r="A225" s="68" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -11848,7 +11848,7 @@
       <c r="L225" s="67" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="53" t="inlineStr">
+      <c r="A226" s="68" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -11898,7 +11898,7 @@
       <c r="L226" s="67" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="53" t="inlineStr">
+      <c r="A227" s="68" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -11948,7 +11948,7 @@
       <c r="L227" s="67" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="53" t="inlineStr">
+      <c r="A228" s="68" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -11998,7 +11998,7 @@
       <c r="L228" s="67" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="53" t="inlineStr">
+      <c r="A229" s="68" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -12048,7 +12048,7 @@
       <c r="L229" s="67" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="53" t="inlineStr">
+      <c r="A230" s="68" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -12076,7 +12076,7 @@
       <c r="L230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="53" t="inlineStr">
+      <c r="A231" s="68" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -12104,7 +12104,7 @@
       <c r="L231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="53" t="inlineStr">
+      <c r="A232" s="68" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -12154,7 +12154,7 @@
       <c r="L232" s="67" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="53" t="inlineStr">
+      <c r="A233" s="68" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -12204,7 +12204,7 @@
       <c r="L233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="53" t="inlineStr">
+      <c r="A234" s="68" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -12254,7 +12254,7 @@
       <c r="L234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="53" t="inlineStr">
+      <c r="A235" s="68" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -12304,7 +12304,7 @@
       <c r="L235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="53" t="inlineStr">
+      <c r="A236" s="68" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -12354,7 +12354,7 @@
       <c r="L236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="53" t="inlineStr">
+      <c r="A237" s="68" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -12404,7 +12404,7 @@
       <c r="L237" s="67" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="53" t="inlineStr">
+      <c r="A238" s="68" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -12454,7 +12454,7 @@
       <c r="L238" s="67" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="53" t="inlineStr">
+      <c r="A239" s="68" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -12504,7 +12504,7 @@
       <c r="L239" s="67" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="53" t="inlineStr">
+      <c r="A240" s="68" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -12532,7 +12532,7 @@
       <c r="L240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="53" t="inlineStr">
+      <c r="A241" s="68" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -12582,7 +12582,7 @@
       <c r="L241" s="67" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="53" t="inlineStr">
+      <c r="A242" s="68" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -12632,7 +12632,7 @@
       <c r="L242" s="67" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="53" t="inlineStr">
+      <c r="A243" s="68" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -12682,7 +12682,7 @@
       <c r="L243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="53" t="inlineStr">
+      <c r="A244" s="68" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -12732,7 +12732,7 @@
       <c r="L244" s="67" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="53" t="inlineStr">
+      <c r="A245" s="68" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -12760,7 +12760,7 @@
       <c r="L245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="53" t="inlineStr">
+      <c r="A246" s="68" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -12810,7 +12810,7 @@
       <c r="L246" s="67" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="53" t="inlineStr">
+      <c r="A247" s="68" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -12852,7 +12852,7 @@
       <c r="L247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="53" t="inlineStr">
+      <c r="A248" s="68" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -12902,7 +12902,7 @@
       <c r="L248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="53" t="inlineStr">
+      <c r="A249" s="68" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -12952,7 +12952,7 @@
       <c r="L249" s="67" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="53" t="inlineStr">
+      <c r="A250" s="68" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -13002,7 +13002,7 @@
       <c r="L250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="53" t="inlineStr">
+      <c r="A251" s="68" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -13052,7 +13052,7 @@
       <c r="L251" s="67" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="53" t="inlineStr">
+      <c r="A252" s="68" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -13102,7 +13102,7 @@
       <c r="L252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="53" t="inlineStr">
+      <c r="A253" s="68" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -13152,7 +13152,7 @@
       <c r="L253" s="67" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="53" t="inlineStr">
+      <c r="A254" s="68" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -13202,7 +13202,7 @@
       <c r="L254" s="67" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="53" t="inlineStr">
+      <c r="A255" s="68" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -13252,7 +13252,7 @@
       <c r="L255" s="67" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="53" t="inlineStr">
+      <c r="A256" s="68" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -13302,7 +13302,7 @@
       <c r="L256" s="67" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="53" t="inlineStr">
+      <c r="A257" s="68" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -13352,7 +13352,7 @@
       <c r="L257" s="67" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="53" t="inlineStr">
+      <c r="A258" s="68" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -13402,7 +13402,7 @@
       <c r="L258" s="67" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="53" t="inlineStr">
+      <c r="A259" s="68" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -13452,7 +13452,7 @@
       <c r="L259" s="67" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="53" t="inlineStr">
+      <c r="A260" s="68" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -13502,7 +13502,7 @@
       <c r="L260" s="67" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="53" t="inlineStr">
+      <c r="A261" s="68" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -13552,7 +13552,7 @@
       <c r="L261" s="67" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="53" t="inlineStr">
+      <c r="A262" s="68" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -13602,7 +13602,7 @@
       <c r="L262" s="67" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="53" t="inlineStr">
+      <c r="A263" s="68" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -13652,7 +13652,7 @@
       <c r="L263" s="67" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="53" t="inlineStr">
+      <c r="A264" s="68" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -13702,7 +13702,7 @@
       <c r="L264" s="67" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="53" t="inlineStr">
+      <c r="A265" s="68" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -13752,7 +13752,7 @@
       <c r="L265" s="67" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="53" t="inlineStr">
+      <c r="A266" s="68" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -13802,7 +13802,7 @@
       <c r="L266" s="67" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="53" t="inlineStr">
+      <c r="A267" s="68" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -13852,7 +13852,7 @@
       <c r="L267" s="67" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="53" t="inlineStr">
+      <c r="A268" s="68" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -13902,7 +13902,7 @@
       <c r="L268" s="67" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="53" t="inlineStr">
+      <c r="A269" s="68" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -13952,7 +13952,7 @@
       <c r="L269" s="67" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="53" t="inlineStr">
+      <c r="A270" s="68" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -14002,7 +14002,7 @@
       <c r="L270" s="67" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="53" t="inlineStr">
+      <c r="A271" s="68" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -14052,7 +14052,7 @@
       <c r="L271" s="67" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="53" t="inlineStr">
+      <c r="A272" s="68" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -14102,7 +14102,7 @@
       <c r="L272" s="67" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="53" t="inlineStr">
+      <c r="A273" s="68" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -14152,7 +14152,7 @@
       <c r="L273" s="67" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="53" t="inlineStr">
+      <c r="A274" s="68" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -14202,7 +14202,7 @@
       <c r="L274" s="67" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="53" t="inlineStr">
+      <c r="A275" s="68" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -14252,7 +14252,7 @@
       <c r="L275" s="67" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="53" t="inlineStr">
+      <c r="A276" s="68" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -14302,7 +14302,7 @@
       <c r="L276" s="67" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="53" t="inlineStr">
+      <c r="A277" s="68" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -14352,7 +14352,7 @@
       <c r="L277" s="67" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="53" t="inlineStr">
+      <c r="A278" s="68" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -14402,7 +14402,7 @@
       <c r="L278" s="67" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="53" t="inlineStr">
+      <c r="A279" s="68" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -14452,7 +14452,7 @@
       <c r="L279" s="67" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="53" t="inlineStr">
+      <c r="A280" s="68" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -14502,7 +14502,7 @@
       <c r="L280" s="67" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="53" t="inlineStr">
+      <c r="A281" s="68" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -14552,7 +14552,7 @@
       <c r="L281" s="67" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="53" t="inlineStr">
+      <c r="A282" s="68" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -14602,7 +14602,7 @@
       <c r="L282" s="67" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="53" t="inlineStr">
+      <c r="A283" s="68" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -14652,7 +14652,7 @@
       <c r="L283" s="67" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="53" t="inlineStr">
+      <c r="A284" s="68" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -14702,7 +14702,7 @@
       <c r="L284" s="67" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="53" t="inlineStr">
+      <c r="A285" s="68" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -14752,7 +14752,7 @@
       <c r="L285" s="67" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="53" t="inlineStr">
+      <c r="A286" s="68" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -14802,7 +14802,7 @@
       <c r="L286" s="67" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="53" t="inlineStr">
+      <c r="A287" s="68" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -14852,7 +14852,7 @@
       <c r="L287" s="67" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="53" t="inlineStr">
+      <c r="A288" s="68" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -14902,7 +14902,7 @@
       <c r="L288" s="67" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="53" t="inlineStr">
+      <c r="A289" s="68" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -14952,7 +14952,7 @@
       <c r="L289" s="67" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="53" t="inlineStr">
+      <c r="A290" s="68" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -15002,7 +15002,7 @@
       <c r="L290" s="67" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="53" t="inlineStr">
+      <c r="A291" s="68" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -15052,7 +15052,7 @@
       <c r="L291" s="67" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="53" t="inlineStr">
+      <c r="A292" s="68" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -309,12 +309,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -518,6 +512,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,10 +524,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -542,19 +539,16 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -564,10 +558,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,21 +573,21 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -683,9 +677,6 @@
     <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -707,10 +698,10 @@
     <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,13 +713,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -737,7 +722,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -746,28 +731,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1175,17 +1160,17 @@
           <t>PS5 COMPLETION PLATFORM  |  BLOCKERS - sorted by blocking count</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="100" t="n"/>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="100" t="n"/>
-      <c r="J1" s="100" t="n"/>
-      <c r="K1" s="100" t="n"/>
-      <c r="L1" s="101" t="n"/>
+      <c r="B1" s="97" t="n"/>
+      <c r="C1" s="97" t="n"/>
+      <c r="D1" s="97" t="n"/>
+      <c r="E1" s="97" t="n"/>
+      <c r="F1" s="97" t="n"/>
+      <c r="G1" s="97" t="n"/>
+      <c r="H1" s="97" t="n"/>
+      <c r="I1" s="97" t="n"/>
+      <c r="J1" s="97" t="n"/>
+      <c r="K1" s="97" t="n"/>
+      <c r="L1" s="98" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1250,7 +1235,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -1260,7 +1245,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="76" t="inlineStr">
+      <c r="C3" s="75" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -1301,10 +1286,10 @@
         </is>
       </c>
       <c r="K3" s="23" t="n"/>
-      <c r="L3" s="67" t="inlineStr"/>
+      <c r="L3" s="66" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="68" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -1314,7 +1299,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C4" s="76" t="inlineStr">
+      <c r="C4" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1351,10 +1336,10 @@
         </is>
       </c>
       <c r="K4" s="23" t="n"/>
-      <c r="L4" s="67" t="inlineStr"/>
+      <c r="L4" s="66" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -1364,7 +1349,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C5" s="76" t="inlineStr">
+      <c r="C5" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1401,10 +1386,10 @@
         </is>
       </c>
       <c r="K5" s="23" t="n"/>
-      <c r="L5" s="67" t="inlineStr"/>
+      <c r="L5" s="66" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -1414,7 +1399,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C6" s="76" t="inlineStr">
+      <c r="C6" s="75" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -1457,10 +1442,10 @@
         </is>
       </c>
       <c r="K6" s="23" t="n"/>
-      <c r="L6" s="67" t="inlineStr"/>
+      <c r="L6" s="66" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -1470,7 +1455,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C7" s="77" t="inlineStr">
+      <c r="C7" s="76" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -1509,10 +1494,10 @@
         </is>
       </c>
       <c r="K7" s="23" t="n"/>
-      <c r="L7" s="67" t="inlineStr"/>
+      <c r="L7" s="66" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" s="67" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -1522,7 +1507,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="76" t="inlineStr">
+      <c r="C8" s="75" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -1550,7 +1535,7 @@
       <c r="H8" s="65" t="inlineStr"/>
       <c r="I8" s="65" t="inlineStr">
         <is>
-          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -1559,10 +1544,10 @@
         </is>
       </c>
       <c r="K8" s="23" t="n"/>
-      <c r="L8" s="67" t="inlineStr"/>
+      <c r="L8" s="66" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="67" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -1572,7 +1557,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C9" s="77" t="inlineStr">
+      <c r="C9" s="76" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -1609,10 +1594,10 @@
         </is>
       </c>
       <c r="K9" s="23" t="n"/>
-      <c r="L9" s="67" t="inlineStr"/>
+      <c r="L9" s="66" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -1622,7 +1607,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C10" s="77" t="inlineStr">
+      <c r="C10" s="76" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -1679,10 +1664,10 @@
         </is>
       </c>
       <c r="K10" s="23" t="n"/>
-      <c r="L10" s="67" t="inlineStr"/>
+      <c r="L10" s="66" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="67" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -1692,7 +1677,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C11" s="76" t="inlineStr">
+      <c r="C11" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1729,10 +1714,10 @@
         </is>
       </c>
       <c r="K11" s="23" t="n"/>
-      <c r="L11" s="67" t="inlineStr"/>
+      <c r="L11" s="66" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="68" t="inlineStr">
+      <c r="A12" s="67" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -1742,7 +1727,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C12" s="76" t="inlineStr">
+      <c r="C12" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1779,10 +1764,10 @@
         </is>
       </c>
       <c r="K12" s="23" t="n"/>
-      <c r="L12" s="67" t="inlineStr"/>
+      <c r="L12" s="66" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="inlineStr">
+      <c r="A13" s="67" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -1792,7 +1777,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C13" s="77" t="inlineStr">
+      <c r="C13" s="76" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -1831,10 +1816,10 @@
         </is>
       </c>
       <c r="K13" s="23" t="n"/>
-      <c r="L13" s="67" t="inlineStr"/>
+      <c r="L13" s="66" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -1844,7 +1829,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C14" s="76" t="inlineStr">
+      <c r="C14" s="75" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -1873,10 +1858,10 @@
       <c r="I14" s="65" t="inlineStr"/>
       <c r="J14" s="23" t="inlineStr"/>
       <c r="K14" s="23" t="n"/>
-      <c r="L14" s="67" t="inlineStr"/>
+      <c r="L14" s="66" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="68" t="inlineStr">
+      <c r="A15" s="67" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -1886,7 +1871,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C15" s="76" t="inlineStr">
+      <c r="C15" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1923,10 +1908,10 @@
         </is>
       </c>
       <c r="K15" s="23" t="n"/>
-      <c r="L15" s="67" t="inlineStr"/>
+      <c r="L15" s="66" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="68" t="inlineStr">
+      <c r="A16" s="67" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -1936,7 +1921,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C16" s="78" t="inlineStr">
+      <c r="C16" s="77" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -1975,10 +1960,10 @@
         </is>
       </c>
       <c r="K16" s="23" t="n"/>
-      <c r="L16" s="67" t="inlineStr"/>
+      <c r="L16" s="66" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="68" t="inlineStr">
+      <c r="A17" s="67" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -1988,7 +1973,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="77" t="inlineStr">
+      <c r="C17" s="76" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -2027,10 +2012,10 @@
         </is>
       </c>
       <c r="K17" s="23" t="n"/>
-      <c r="L17" s="67" t="inlineStr"/>
+      <c r="L17" s="66" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="68" t="inlineStr">
+      <c r="A18" s="67" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -2040,7 +2025,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C18" s="78" t="inlineStr">
+      <c r="C18" s="77" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -2077,10 +2062,10 @@
         </is>
       </c>
       <c r="K18" s="23" t="n"/>
-      <c r="L18" s="67" t="inlineStr"/>
+      <c r="L18" s="66" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="68" t="inlineStr">
+      <c r="A19" s="67" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -2090,7 +2075,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C19" s="76" t="inlineStr">
+      <c r="C19" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2127,10 +2112,10 @@
         </is>
       </c>
       <c r="K19" s="23" t="n"/>
-      <c r="L19" s="67" t="inlineStr"/>
+      <c r="L19" s="66" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="68" t="inlineStr">
+      <c r="A20" s="67" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -2140,7 +2125,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C20" s="76" t="inlineStr">
+      <c r="C20" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2177,10 +2162,10 @@
         </is>
       </c>
       <c r="K20" s="23" t="n"/>
-      <c r="L20" s="67" t="inlineStr"/>
+      <c r="L20" s="66" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="68" t="inlineStr">
+      <c r="A21" s="67" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -2190,7 +2175,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C21" s="76" t="inlineStr">
+      <c r="C21" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2227,10 +2212,10 @@
         </is>
       </c>
       <c r="K21" s="23" t="n"/>
-      <c r="L21" s="67" t="inlineStr"/>
+      <c r="L21" s="66" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="68" t="inlineStr">
+      <c r="A22" s="67" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -2240,7 +2225,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C22" s="78" t="inlineStr">
+      <c r="C22" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2277,10 +2262,10 @@
         </is>
       </c>
       <c r="K22" s="23" t="n"/>
-      <c r="L22" s="67" t="inlineStr"/>
+      <c r="L22" s="66" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="68" t="inlineStr">
+      <c r="A23" s="67" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -2290,7 +2275,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C23" s="78" t="inlineStr">
+      <c r="C23" s="77" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -2327,10 +2312,10 @@
         </is>
       </c>
       <c r="K23" s="23" t="n"/>
-      <c r="L23" s="67" t="inlineStr"/>
+      <c r="L23" s="66" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="68" t="inlineStr">
+      <c r="A24" s="67" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -2340,7 +2325,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C24" s="76" t="inlineStr">
+      <c r="C24" s="75" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -2365,11 +2350,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H24" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H24" s="65" t="inlineStr"/>
       <c r="I24" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-0007, PS5-71-TW-0003, PS5-71-TW-0004, PS5-71-TW-0006 not arrived</t>
@@ -2381,10 +2362,10 @@
         </is>
       </c>
       <c r="K24" s="23" t="n"/>
-      <c r="L24" s="67" t="inlineStr"/>
+      <c r="L24" s="66" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="68" t="inlineStr">
+      <c r="A25" s="67" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -2394,7 +2375,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C25" s="77" t="inlineStr">
+      <c r="C25" s="76" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -2435,10 +2416,10 @@
         </is>
       </c>
       <c r="K25" s="23" t="n"/>
-      <c r="L25" s="67" t="inlineStr"/>
+      <c r="L25" s="66" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="68" t="inlineStr">
+      <c r="A26" s="67" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -2448,7 +2429,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C26" s="78" t="inlineStr">
+      <c r="C26" s="77" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -2487,10 +2468,10 @@
         </is>
       </c>
       <c r="K26" s="23" t="n"/>
-      <c r="L26" s="67" t="inlineStr"/>
+      <c r="L26" s="66" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="68" t="inlineStr">
+      <c r="A27" s="67" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -2500,7 +2481,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C27" s="76" t="inlineStr">
+      <c r="C27" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2537,10 +2518,10 @@
         </is>
       </c>
       <c r="K27" s="23" t="n"/>
-      <c r="L27" s="67" t="inlineStr"/>
+      <c r="L27" s="66" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="67" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -2550,7 +2531,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C28" s="76" t="inlineStr">
+      <c r="C28" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2587,10 +2568,10 @@
         </is>
       </c>
       <c r="K28" s="23" t="n"/>
-      <c r="L28" s="67" t="inlineStr"/>
+      <c r="L28" s="66" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="68" t="inlineStr">
+      <c r="A29" s="67" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -2600,7 +2581,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C29" s="76" t="inlineStr">
+      <c r="C29" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2637,10 +2618,10 @@
         </is>
       </c>
       <c r="K29" s="23" t="n"/>
-      <c r="L29" s="67" t="inlineStr"/>
+      <c r="L29" s="66" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="68" t="inlineStr">
+      <c r="A30" s="67" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -2650,7 +2631,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C30" s="77" t="inlineStr">
+      <c r="C30" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -2687,10 +2668,10 @@
         </is>
       </c>
       <c r="K30" s="23" t="n"/>
-      <c r="L30" s="67" t="inlineStr"/>
+      <c r="L30" s="66" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="68" t="inlineStr">
+      <c r="A31" s="67" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -2700,7 +2681,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C31" s="77" t="inlineStr">
+      <c r="C31" s="76" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -2737,10 +2718,10 @@
         </is>
       </c>
       <c r="K31" s="23" t="n"/>
-      <c r="L31" s="67" t="inlineStr"/>
+      <c r="L31" s="66" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="68" t="inlineStr">
+      <c r="A32" s="67" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -2750,7 +2731,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C32" s="77" t="inlineStr">
+      <c r="C32" s="76" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -2779,10 +2760,10 @@
       <c r="I32" s="65" t="inlineStr"/>
       <c r="J32" s="23" t="inlineStr"/>
       <c r="K32" s="23" t="n"/>
-      <c r="L32" s="67" t="inlineStr"/>
+      <c r="L32" s="66" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="68" t="inlineStr">
+      <c r="A33" s="67" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -2792,7 +2773,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C33" s="78" t="inlineStr">
+      <c r="C33" s="77" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -2831,10 +2812,10 @@
         </is>
       </c>
       <c r="K33" s="23" t="n"/>
-      <c r="L33" s="67" t="inlineStr"/>
+      <c r="L33" s="66" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="68" t="inlineStr">
+      <c r="A34" s="67" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -2844,7 +2825,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C34" s="78" t="inlineStr">
+      <c r="C34" s="77" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -2881,10 +2862,10 @@
         </is>
       </c>
       <c r="K34" s="23" t="n"/>
-      <c r="L34" s="67" t="inlineStr"/>
+      <c r="L34" s="66" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="68" t="inlineStr">
+      <c r="A35" s="67" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -2894,7 +2875,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C35" s="77" t="inlineStr">
+      <c r="C35" s="76" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -2931,10 +2912,10 @@
         </is>
       </c>
       <c r="K35" s="23" t="n"/>
-      <c r="L35" s="67" t="inlineStr"/>
+      <c r="L35" s="66" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="68" t="inlineStr">
+      <c r="A36" s="67" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -2944,7 +2925,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C36" s="78" t="inlineStr">
+      <c r="C36" s="77" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -2973,10 +2954,10 @@
       <c r="I36" s="65" t="inlineStr"/>
       <c r="J36" s="23" t="inlineStr"/>
       <c r="K36" s="23" t="n"/>
-      <c r="L36" s="67" t="inlineStr"/>
+      <c r="L36" s="66" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="68" t="inlineStr">
+      <c r="A37" s="67" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -2986,7 +2967,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C37" s="78" t="inlineStr">
+      <c r="C37" s="77" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -3023,10 +3004,10 @@
         </is>
       </c>
       <c r="K37" s="23" t="n"/>
-      <c r="L37" s="67" t="inlineStr"/>
+      <c r="L37" s="66" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="68" t="inlineStr">
+      <c r="A38" s="67" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -3036,7 +3017,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C38" s="77" t="inlineStr">
+      <c r="C38" s="76" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -3075,10 +3056,10 @@
         </is>
       </c>
       <c r="K38" s="23" t="n"/>
-      <c r="L38" s="67" t="inlineStr"/>
+      <c r="L38" s="66" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="68" t="inlineStr">
+      <c r="A39" s="67" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -3088,7 +3069,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C39" s="77" t="inlineStr">
+      <c r="C39" s="76" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -3125,10 +3106,10 @@
         </is>
       </c>
       <c r="K39" s="23" t="n"/>
-      <c r="L39" s="67" t="inlineStr"/>
+      <c r="L39" s="66" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="68" t="inlineStr">
+      <c r="A40" s="67" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -3138,7 +3119,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C40" s="78" t="inlineStr">
+      <c r="C40" s="77" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -3166,7 +3147,7 @@
       <c r="H40" s="65" t="inlineStr"/>
       <c r="I40" s="65" t="inlineStr">
         <is>
-          <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
+          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -3175,10 +3156,10 @@
         </is>
       </c>
       <c r="K40" s="23" t="n"/>
-      <c r="L40" s="67" t="inlineStr"/>
+      <c r="L40" s="66" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="68" t="inlineStr">
+      <c r="A41" s="67" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -3188,7 +3169,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C41" s="78" t="inlineStr">
+      <c r="C41" s="77" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -3225,10 +3206,10 @@
         </is>
       </c>
       <c r="K41" s="23" t="n"/>
-      <c r="L41" s="67" t="inlineStr"/>
+      <c r="L41" s="66" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="68" t="inlineStr">
+      <c r="A42" s="67" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -3238,7 +3219,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C42" s="78" t="inlineStr">
+      <c r="C42" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3267,10 +3248,10 @@
       <c r="I42" s="65" t="inlineStr"/>
       <c r="J42" s="23" t="inlineStr"/>
       <c r="K42" s="23" t="n"/>
-      <c r="L42" s="67" t="inlineStr"/>
+      <c r="L42" s="66" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="68" t="inlineStr">
+      <c r="A43" s="67" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -3280,7 +3261,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C43" s="78" t="inlineStr">
+      <c r="C43" s="77" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -3319,10 +3300,10 @@
         </is>
       </c>
       <c r="K43" s="23" t="n"/>
-      <c r="L43" s="67" t="inlineStr"/>
+      <c r="L43" s="66" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="68" t="inlineStr">
+      <c r="A44" s="67" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -3332,7 +3313,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C44" s="78" t="inlineStr">
+      <c r="C44" s="77" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3369,10 +3350,10 @@
         </is>
       </c>
       <c r="K44" s="23" t="n"/>
-      <c r="L44" s="67" t="inlineStr"/>
+      <c r="L44" s="66" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="68" t="inlineStr">
+      <c r="A45" s="67" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -3382,7 +3363,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C45" s="78" t="inlineStr">
+      <c r="C45" s="77" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3419,10 +3400,10 @@
         </is>
       </c>
       <c r="K45" s="23" t="n"/>
-      <c r="L45" s="67" t="inlineStr"/>
+      <c r="L45" s="66" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="68" t="inlineStr">
+      <c r="A46" s="67" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -3432,7 +3413,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C46" s="78" t="inlineStr">
+      <c r="C46" s="77" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3461,10 +3442,10 @@
       <c r="I46" s="65" t="inlineStr"/>
       <c r="J46" s="23" t="inlineStr"/>
       <c r="K46" s="23" t="n"/>
-      <c r="L46" s="67" t="inlineStr"/>
+      <c r="L46" s="66" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="68" t="inlineStr">
+      <c r="A47" s="67" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -3474,7 +3455,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C47" s="78" t="inlineStr">
+      <c r="C47" s="77" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3503,10 +3484,10 @@
       <c r="I47" s="65" t="inlineStr"/>
       <c r="J47" s="23" t="inlineStr"/>
       <c r="K47" s="23" t="n"/>
-      <c r="L47" s="67" t="inlineStr"/>
+      <c r="L47" s="66" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="68" t="inlineStr">
+      <c r="A48" s="67" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -3516,7 +3497,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C48" s="78" t="inlineStr">
+      <c r="C48" s="77" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3545,10 +3526,10 @@
       <c r="I48" s="65" t="inlineStr"/>
       <c r="J48" s="23" t="inlineStr"/>
       <c r="K48" s="23" t="n"/>
-      <c r="L48" s="67" t="inlineStr"/>
+      <c r="L48" s="66" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="68" t="inlineStr">
+      <c r="A49" s="67" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -3558,7 +3539,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C49" s="78" t="inlineStr">
+      <c r="C49" s="77" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3587,10 +3568,10 @@
       <c r="I49" s="65" t="inlineStr"/>
       <c r="J49" s="23" t="inlineStr"/>
       <c r="K49" s="23" t="n"/>
-      <c r="L49" s="67" t="inlineStr"/>
+      <c r="L49" s="66" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="68" t="inlineStr">
+      <c r="A50" s="67" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -3600,7 +3581,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C50" s="77" t="inlineStr">
+      <c r="C50" s="76" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -3637,35 +3618,35 @@
         </is>
       </c>
       <c r="K50" s="23" t="n"/>
-      <c r="L50" s="67" t="inlineStr"/>
+      <c r="L50" s="66" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="79" t="inlineStr">
+      <c r="A51" s="67" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
       </c>
-      <c r="B51" s="66" t="inlineStr">
+      <c r="B51" s="23" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="C51" s="80" t="inlineStr">
+      <c r="C51" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D51" s="66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E51" s="66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F51" s="66" t="inlineStr">
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3681,16 +3662,16 @@
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="J51" s="66" t="inlineStr">
+      <c r="J51" s="23" t="inlineStr">
         <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="K51" s="66" t="n"/>
-      <c r="L51" s="67" t="inlineStr"/>
+      <c r="K51" s="23" t="n"/>
+      <c r="L51" s="66" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="68" t="inlineStr">
+      <c r="A52" s="67" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -3700,7 +3681,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C52" s="77" t="inlineStr">
+      <c r="C52" s="76" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -3737,10 +3718,10 @@
         </is>
       </c>
       <c r="K52" s="23" t="n"/>
-      <c r="L52" s="67" t="inlineStr"/>
+      <c r="L52" s="66" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="68" t="inlineStr">
+      <c r="A53" s="67" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -3750,7 +3731,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C53" s="78" t="inlineStr">
+      <c r="C53" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3787,10 +3768,10 @@
         </is>
       </c>
       <c r="K53" s="23" t="n"/>
-      <c r="L53" s="67" t="inlineStr"/>
+      <c r="L53" s="66" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="68" t="inlineStr">
+      <c r="A54" s="67" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -3800,7 +3781,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C54" s="78" t="inlineStr">
+      <c r="C54" s="77" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -3829,10 +3810,10 @@
       <c r="I54" s="65" t="inlineStr"/>
       <c r="J54" s="23" t="inlineStr"/>
       <c r="K54" s="23" t="n"/>
-      <c r="L54" s="67" t="inlineStr"/>
+      <c r="L54" s="66" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="68" t="inlineStr">
+      <c r="A55" s="67" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -3842,7 +3823,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C55" s="77" t="inlineStr">
+      <c r="C55" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -3871,10 +3852,10 @@
       <c r="I55" s="65" t="inlineStr"/>
       <c r="J55" s="23" t="inlineStr"/>
       <c r="K55" s="23" t="n"/>
-      <c r="L55" s="67" t="inlineStr"/>
+      <c r="L55" s="66" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="68" t="inlineStr">
+      <c r="A56" s="67" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -3884,7 +3865,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C56" s="78" t="inlineStr">
+      <c r="C56" s="77" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -3913,10 +3894,10 @@
       <c r="I56" s="65" t="inlineStr"/>
       <c r="J56" s="23" t="inlineStr"/>
       <c r="K56" s="23" t="n"/>
-      <c r="L56" s="67" t="inlineStr"/>
+      <c r="L56" s="66" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="68" t="inlineStr">
+      <c r="A57" s="67" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -3926,7 +3907,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C57" s="77" t="inlineStr">
+      <c r="C57" s="76" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -3955,10 +3936,10 @@
       <c r="I57" s="65" t="inlineStr"/>
       <c r="J57" s="23" t="inlineStr"/>
       <c r="K57" s="23" t="n"/>
-      <c r="L57" s="67" t="inlineStr"/>
+      <c r="L57" s="66" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="68" t="inlineStr">
+      <c r="A58" s="67" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -3968,7 +3949,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C58" s="78" t="inlineStr">
+      <c r="C58" s="77" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -4005,10 +3986,10 @@
         </is>
       </c>
       <c r="K58" s="23" t="n"/>
-      <c r="L58" s="67" t="inlineStr"/>
+      <c r="L58" s="66" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="68" t="inlineStr">
+      <c r="A59" s="67" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -4018,7 +3999,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C59" s="78" t="inlineStr">
+      <c r="C59" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4047,10 +4028,10 @@
       <c r="I59" s="65" t="inlineStr"/>
       <c r="J59" s="23" t="inlineStr"/>
       <c r="K59" s="23" t="n"/>
-      <c r="L59" s="67" t="inlineStr"/>
+      <c r="L59" s="66" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="68" t="inlineStr">
+      <c r="A60" s="67" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -4060,7 +4041,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C60" s="78" t="inlineStr">
+      <c r="C60" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4089,10 +4070,10 @@
       <c r="I60" s="65" t="inlineStr"/>
       <c r="J60" s="23" t="inlineStr"/>
       <c r="K60" s="23" t="n"/>
-      <c r="L60" s="67" t="inlineStr"/>
+      <c r="L60" s="66" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="68" t="inlineStr">
+      <c r="A61" s="67" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -4102,7 +4083,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C61" s="77" t="inlineStr">
+      <c r="C61" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -4139,10 +4120,10 @@
         </is>
       </c>
       <c r="K61" s="23" t="n"/>
-      <c r="L61" s="67" t="inlineStr"/>
+      <c r="L61" s="66" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="68" t="inlineStr">
+      <c r="A62" s="67" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -4152,7 +4133,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C62" s="77" t="inlineStr">
+      <c r="C62" s="76" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -4189,10 +4170,10 @@
         </is>
       </c>
       <c r="K62" s="23" t="n"/>
-      <c r="L62" s="67" t="inlineStr"/>
+      <c r="L62" s="66" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="68" t="inlineStr">
+      <c r="A63" s="67" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -4202,7 +4183,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C63" s="78" t="inlineStr">
+      <c r="C63" s="77" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4229,16 +4210,12 @@
       </c>
       <c r="H63" s="65" t="inlineStr"/>
       <c r="I63" s="65" t="inlineStr"/>
-      <c r="J63" s="23" t="inlineStr">
-        <is>
-          <t>OBSERVATION -CLEANING ON PROGRESS</t>
-        </is>
-      </c>
+      <c r="J63" s="23" t="inlineStr"/>
       <c r="K63" s="23" t="n"/>
-      <c r="L63" s="67" t="inlineStr"/>
+      <c r="L63" s="66" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="68" t="inlineStr">
+      <c r="A64" s="67" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -4248,7 +4225,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C64" s="78" t="inlineStr">
+      <c r="C64" s="77" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4277,10 +4254,10 @@
       <c r="I64" s="65" t="inlineStr"/>
       <c r="J64" s="23" t="inlineStr"/>
       <c r="K64" s="23" t="n"/>
-      <c r="L64" s="67" t="inlineStr"/>
+      <c r="L64" s="66" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="68" t="inlineStr">
+      <c r="A65" s="67" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -4290,7 +4267,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C65" s="78" t="inlineStr">
+      <c r="C65" s="77" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -4327,10 +4304,10 @@
         </is>
       </c>
       <c r="K65" s="23" t="n"/>
-      <c r="L65" s="67" t="inlineStr"/>
+      <c r="L65" s="66" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="68" t="inlineStr">
+      <c r="A66" s="67" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -4340,7 +4317,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C66" s="78" t="inlineStr">
+      <c r="C66" s="77" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -4377,10 +4354,10 @@
         </is>
       </c>
       <c r="K66" s="23" t="n"/>
-      <c r="L66" s="67" t="inlineStr"/>
+      <c r="L66" s="66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="68" t="inlineStr">
+      <c r="A67" s="67" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -4390,7 +4367,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C67" s="78" t="inlineStr">
+      <c r="C67" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4427,10 +4404,10 @@
         </is>
       </c>
       <c r="K67" s="23" t="n"/>
-      <c r="L67" s="67" t="inlineStr"/>
+      <c r="L67" s="66" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="68" t="inlineStr">
+      <c r="A68" s="67" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -4440,7 +4417,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C68" s="78" t="inlineStr">
+      <c r="C68" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4477,10 +4454,10 @@
         </is>
       </c>
       <c r="K68" s="23" t="n"/>
-      <c r="L68" s="67" t="inlineStr"/>
+      <c r="L68" s="66" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="68" t="inlineStr">
+      <c r="A69" s="67" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -4490,7 +4467,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C69" s="78" t="inlineStr">
+      <c r="C69" s="77" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -4527,10 +4504,10 @@
         </is>
       </c>
       <c r="K69" s="23" t="n"/>
-      <c r="L69" s="67" t="inlineStr"/>
+      <c r="L69" s="66" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="68" t="inlineStr">
+      <c r="A70" s="67" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -4540,7 +4517,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C70" s="78" t="inlineStr">
+      <c r="C70" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4577,10 +4554,10 @@
         </is>
       </c>
       <c r="K70" s="23" t="n"/>
-      <c r="L70" s="67" t="inlineStr"/>
+      <c r="L70" s="66" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="68" t="inlineStr">
+      <c r="A71" s="67" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -4590,7 +4567,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C71" s="77" t="inlineStr">
+      <c r="C71" s="76" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -4627,10 +4604,10 @@
         </is>
       </c>
       <c r="K71" s="23" t="n"/>
-      <c r="L71" s="67" t="inlineStr"/>
+      <c r="L71" s="66" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="68" t="inlineStr">
+      <c r="A72" s="67" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -4640,7 +4617,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C72" s="77" t="inlineStr">
+      <c r="C72" s="76" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -4677,10 +4654,10 @@
         </is>
       </c>
       <c r="K72" s="23" t="n"/>
-      <c r="L72" s="67" t="inlineStr"/>
+      <c r="L72" s="66" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="68" t="inlineStr">
+      <c r="A73" s="67" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -4690,7 +4667,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C73" s="78" t="inlineStr">
+      <c r="C73" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4727,10 +4704,10 @@
         </is>
       </c>
       <c r="K73" s="23" t="n"/>
-      <c r="L73" s="67" t="inlineStr"/>
+      <c r="L73" s="66" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="68" t="inlineStr">
+      <c r="A74" s="67" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -4740,7 +4717,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C74" s="76" t="inlineStr">
+      <c r="C74" s="75" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -4777,10 +4754,10 @@
         </is>
       </c>
       <c r="K74" s="23" t="n"/>
-      <c r="L74" s="67" t="inlineStr"/>
+      <c r="L74" s="66" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="68" t="inlineStr">
+      <c r="A75" s="67" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -4790,7 +4767,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C75" s="76" t="inlineStr">
+      <c r="C75" s="75" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -4827,10 +4804,10 @@
         </is>
       </c>
       <c r="K75" s="23" t="n"/>
-      <c r="L75" s="67" t="inlineStr"/>
+      <c r="L75" s="66" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="68" t="inlineStr">
+      <c r="A76" s="67" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -4840,7 +4817,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C76" s="78" t="inlineStr">
+      <c r="C76" s="77" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -4877,10 +4854,10 @@
         </is>
       </c>
       <c r="K76" s="23" t="n"/>
-      <c r="L76" s="67" t="inlineStr"/>
+      <c r="L76" s="66" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="68" t="inlineStr">
+      <c r="A77" s="67" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -4890,7 +4867,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C77" s="76" t="inlineStr">
+      <c r="C77" s="75" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -4927,10 +4904,10 @@
         </is>
       </c>
       <c r="K77" s="23" t="n"/>
-      <c r="L77" s="67" t="inlineStr"/>
+      <c r="L77" s="66" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="68" t="inlineStr">
+      <c r="A78" s="67" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -4940,7 +4917,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C78" s="78" t="inlineStr">
+      <c r="C78" s="77" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -4977,10 +4954,10 @@
         </is>
       </c>
       <c r="K78" s="23" t="n"/>
-      <c r="L78" s="67" t="inlineStr"/>
+      <c r="L78" s="66" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="68" t="inlineStr">
+      <c r="A79" s="67" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -4990,7 +4967,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C79" s="78" t="inlineStr">
+      <c r="C79" s="77" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -5027,10 +5004,10 @@
         </is>
       </c>
       <c r="K79" s="23" t="n"/>
-      <c r="L79" s="67" t="inlineStr"/>
+      <c r="L79" s="66" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="68" t="inlineStr">
+      <c r="A80" s="67" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -5040,7 +5017,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C80" s="78" t="inlineStr">
+      <c r="C80" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5077,10 +5054,10 @@
         </is>
       </c>
       <c r="K80" s="23" t="n"/>
-      <c r="L80" s="67" t="inlineStr"/>
+      <c r="L80" s="66" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="68" t="inlineStr">
+      <c r="A81" s="67" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -5090,7 +5067,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C81" s="78" t="inlineStr">
+      <c r="C81" s="77" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -5127,10 +5104,10 @@
         </is>
       </c>
       <c r="K81" s="23" t="n"/>
-      <c r="L81" s="67" t="inlineStr"/>
+      <c r="L81" s="66" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="68" t="inlineStr">
+      <c r="A82" s="67" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -5140,7 +5117,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C82" s="78" t="inlineStr">
+      <c r="C82" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5177,10 +5154,10 @@
         </is>
       </c>
       <c r="K82" s="23" t="n"/>
-      <c r="L82" s="67" t="inlineStr"/>
+      <c r="L82" s="66" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="68" t="inlineStr">
+      <c r="A83" s="67" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -5190,7 +5167,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C83" s="78" t="inlineStr">
+      <c r="C83" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5223,10 +5200,10 @@
       <c r="I83" s="65" t="inlineStr"/>
       <c r="J83" s="23" t="inlineStr"/>
       <c r="K83" s="23" t="n"/>
-      <c r="L83" s="67" t="inlineStr"/>
+      <c r="L83" s="66" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="68" t="inlineStr">
+      <c r="A84" s="67" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -5236,7 +5213,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C84" s="78" t="inlineStr">
+      <c r="C84" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5273,10 +5250,10 @@
         </is>
       </c>
       <c r="K84" s="23" t="n"/>
-      <c r="L84" s="67" t="inlineStr"/>
+      <c r="L84" s="66" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="68" t="inlineStr">
+      <c r="A85" s="67" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -5286,7 +5263,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C85" s="78" t="inlineStr">
+      <c r="C85" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5323,10 +5300,10 @@
         </is>
       </c>
       <c r="K85" s="23" t="n"/>
-      <c r="L85" s="67" t="inlineStr"/>
+      <c r="L85" s="66" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="68" t="inlineStr">
+      <c r="A86" s="67" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -5336,7 +5313,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C86" s="76" t="inlineStr">
+      <c r="C86" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5375,16 +5352,16 @@
         </is>
       </c>
       <c r="K86" s="23" t="n"/>
-      <c r="L86" s="67" t="inlineStr"/>
+      <c r="L86" s="66" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="68" t="inlineStr">
+      <c r="A87" s="67" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
       </c>
       <c r="B87" s="23" t="inlineStr"/>
-      <c r="C87" s="78" t="inlineStr">
+      <c r="C87" s="77" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -5403,16 +5380,16 @@
       <c r="I87" s="65" t="inlineStr"/>
       <c r="J87" s="23" t="inlineStr"/>
       <c r="K87" s="23" t="n"/>
-      <c r="L87" s="67" t="inlineStr"/>
+      <c r="L87" s="66" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="68" t="inlineStr">
+      <c r="A88" s="67" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
       </c>
       <c r="B88" s="23" t="inlineStr"/>
-      <c r="C88" s="76" t="inlineStr">
+      <c r="C88" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5431,10 +5408,10 @@
       <c r="I88" s="65" t="inlineStr"/>
       <c r="J88" s="23" t="inlineStr"/>
       <c r="K88" s="23" t="n"/>
-      <c r="L88" s="67" t="inlineStr"/>
+      <c r="L88" s="66" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="68" t="inlineStr">
+      <c r="A89" s="67" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -5444,7 +5421,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C89" s="76" t="inlineStr">
+      <c r="C89" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5481,16 +5458,16 @@
         </is>
       </c>
       <c r="K89" s="23" t="n"/>
-      <c r="L89" s="67" t="inlineStr"/>
+      <c r="L89" s="66" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="68" t="inlineStr">
+      <c r="A90" s="67" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
       </c>
       <c r="B90" s="23" t="inlineStr"/>
-      <c r="C90" s="78" t="inlineStr">
+      <c r="C90" s="77" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -5509,16 +5486,16 @@
       <c r="I90" s="65" t="inlineStr"/>
       <c r="J90" s="23" t="inlineStr"/>
       <c r="K90" s="23" t="n"/>
-      <c r="L90" s="67" t="inlineStr"/>
+      <c r="L90" s="66" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="68" t="inlineStr">
+      <c r="A91" s="67" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
       </c>
       <c r="B91" s="23" t="inlineStr"/>
-      <c r="C91" s="78" t="inlineStr">
+      <c r="C91" s="77" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -5537,16 +5514,16 @@
       <c r="I91" s="65" t="inlineStr"/>
       <c r="J91" s="23" t="inlineStr"/>
       <c r="K91" s="23" t="n"/>
-      <c r="L91" s="67" t="inlineStr"/>
+      <c r="L91" s="66" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="68" t="inlineStr">
+      <c r="A92" s="67" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
       </c>
       <c r="B92" s="23" t="inlineStr"/>
-      <c r="C92" s="77" t="inlineStr">
+      <c r="C92" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -5565,10 +5542,10 @@
       <c r="I92" s="65" t="inlineStr"/>
       <c r="J92" s="23" t="inlineStr"/>
       <c r="K92" s="23" t="n"/>
-      <c r="L92" s="67" t="inlineStr"/>
+      <c r="L92" s="66" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="68" t="inlineStr">
+      <c r="A93" s="67" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -5578,7 +5555,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C93" s="78" t="inlineStr">
+      <c r="C93" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5615,10 +5592,10 @@
         </is>
       </c>
       <c r="K93" s="23" t="n"/>
-      <c r="L93" s="67" t="inlineStr"/>
+      <c r="L93" s="66" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="68" t="inlineStr">
+      <c r="A94" s="67" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -5628,7 +5605,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C94" s="78" t="inlineStr">
+      <c r="C94" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5665,16 +5642,16 @@
         </is>
       </c>
       <c r="K94" s="23" t="n"/>
-      <c r="L94" s="67" t="inlineStr"/>
+      <c r="L94" s="66" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="68" t="inlineStr">
+      <c r="A95" s="67" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
       </c>
       <c r="B95" s="23" t="inlineStr"/>
-      <c r="C95" s="77" t="inlineStr">
+      <c r="C95" s="76" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -5693,10 +5670,10 @@
       <c r="I95" s="65" t="inlineStr"/>
       <c r="J95" s="23" t="inlineStr"/>
       <c r="K95" s="23" t="n"/>
-      <c r="L95" s="67" t="inlineStr"/>
+      <c r="L95" s="66" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="68" t="inlineStr">
+      <c r="A96" s="67" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -5706,7 +5683,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C96" s="78" t="inlineStr">
+      <c r="C96" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5743,10 +5720,10 @@
         </is>
       </c>
       <c r="K96" s="23" t="n"/>
-      <c r="L96" s="67" t="inlineStr"/>
+      <c r="L96" s="66" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="68" t="inlineStr">
+      <c r="A97" s="67" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -5756,7 +5733,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C97" s="76" t="inlineStr">
+      <c r="C97" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5793,10 +5770,10 @@
         </is>
       </c>
       <c r="K97" s="23" t="n"/>
-      <c r="L97" s="67" t="inlineStr"/>
+      <c r="L97" s="66" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="68" t="inlineStr">
+      <c r="A98" s="67" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -5806,7 +5783,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C98" s="76" t="inlineStr">
+      <c r="C98" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5843,10 +5820,10 @@
         </is>
       </c>
       <c r="K98" s="23" t="n"/>
-      <c r="L98" s="67" t="inlineStr"/>
+      <c r="L98" s="66" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="68" t="inlineStr">
+      <c r="A99" s="67" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -5856,7 +5833,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C99" s="76" t="inlineStr">
+      <c r="C99" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5893,10 +5870,10 @@
         </is>
       </c>
       <c r="K99" s="23" t="n"/>
-      <c r="L99" s="67" t="inlineStr"/>
+      <c r="L99" s="66" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="68" t="inlineStr">
+      <c r="A100" s="67" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -5906,7 +5883,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C100" s="76" t="inlineStr">
+      <c r="C100" s="75" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -5943,10 +5920,10 @@
         </is>
       </c>
       <c r="K100" s="23" t="n"/>
-      <c r="L100" s="67" t="inlineStr"/>
+      <c r="L100" s="66" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="68" t="inlineStr">
+      <c r="A101" s="67" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -5956,7 +5933,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C101" s="76" t="inlineStr">
+      <c r="C101" s="75" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -5993,16 +5970,16 @@
         </is>
       </c>
       <c r="K101" s="23" t="n"/>
-      <c r="L101" s="67" t="inlineStr"/>
+      <c r="L101" s="66" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="68" t="inlineStr">
+      <c r="A102" s="67" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
       </c>
       <c r="B102" s="23" t="inlineStr"/>
-      <c r="C102" s="76" t="inlineStr">
+      <c r="C102" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6021,16 +5998,16 @@
       <c r="I102" s="65" t="inlineStr"/>
       <c r="J102" s="23" t="inlineStr"/>
       <c r="K102" s="23" t="n"/>
-      <c r="L102" s="67" t="inlineStr"/>
+      <c r="L102" s="66" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="68" t="inlineStr">
+      <c r="A103" s="67" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
       </c>
       <c r="B103" s="23" t="inlineStr"/>
-      <c r="C103" s="76" t="inlineStr">
+      <c r="C103" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6049,10 +6026,10 @@
       <c r="I103" s="65" t="inlineStr"/>
       <c r="J103" s="23" t="inlineStr"/>
       <c r="K103" s="23" t="n"/>
-      <c r="L103" s="67" t="inlineStr"/>
+      <c r="L103" s="66" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="68" t="inlineStr">
+      <c r="A104" s="67" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -6062,7 +6039,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C104" s="76" t="inlineStr">
+      <c r="C104" s="75" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6099,10 +6076,10 @@
         </is>
       </c>
       <c r="K104" s="23" t="n"/>
-      <c r="L104" s="67" t="inlineStr"/>
+      <c r="L104" s="66" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="68" t="inlineStr">
+      <c r="A105" s="67" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -6112,7 +6089,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C105" s="76" t="inlineStr">
+      <c r="C105" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6149,10 +6126,10 @@
         </is>
       </c>
       <c r="K105" s="23" t="n"/>
-      <c r="L105" s="67" t="inlineStr"/>
+      <c r="L105" s="66" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="68" t="inlineStr">
+      <c r="A106" s="67" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -6162,7 +6139,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C106" s="76" t="inlineStr">
+      <c r="C106" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6199,10 +6176,10 @@
         </is>
       </c>
       <c r="K106" s="23" t="n"/>
-      <c r="L106" s="67" t="inlineStr"/>
+      <c r="L106" s="66" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="68" t="inlineStr">
+      <c r="A107" s="67" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -6212,7 +6189,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C107" s="76" t="inlineStr">
+      <c r="C107" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6249,10 +6226,10 @@
         </is>
       </c>
       <c r="K107" s="23" t="n"/>
-      <c r="L107" s="67" t="inlineStr"/>
+      <c r="L107" s="66" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="68" t="inlineStr">
+      <c r="A108" s="67" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -6262,7 +6239,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C108" s="76" t="inlineStr">
+      <c r="C108" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6299,10 +6276,10 @@
         </is>
       </c>
       <c r="K108" s="23" t="n"/>
-      <c r="L108" s="67" t="inlineStr"/>
+      <c r="L108" s="66" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="68" t="inlineStr">
+      <c r="A109" s="67" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -6312,7 +6289,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C109" s="76" t="inlineStr">
+      <c r="C109" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6349,10 +6326,10 @@
         </is>
       </c>
       <c r="K109" s="23" t="n"/>
-      <c r="L109" s="67" t="inlineStr"/>
+      <c r="L109" s="66" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="68" t="inlineStr">
+      <c r="A110" s="67" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -6362,7 +6339,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C110" s="76" t="inlineStr">
+      <c r="C110" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6399,16 +6376,16 @@
         </is>
       </c>
       <c r="K110" s="23" t="n"/>
-      <c r="L110" s="67" t="inlineStr"/>
+      <c r="L110" s="66" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="68" t="inlineStr">
+      <c r="A111" s="67" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
       </c>
       <c r="B111" s="23" t="inlineStr"/>
-      <c r="C111" s="77" t="inlineStr">
+      <c r="C111" s="76" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -6427,10 +6404,10 @@
       <c r="I111" s="65" t="inlineStr"/>
       <c r="J111" s="23" t="inlineStr"/>
       <c r="K111" s="23" t="n"/>
-      <c r="L111" s="67" t="inlineStr"/>
+      <c r="L111" s="66" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="68" t="inlineStr">
+      <c r="A112" s="67" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -6440,7 +6417,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C112" s="76" t="inlineStr">
+      <c r="C112" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6477,10 +6454,10 @@
         </is>
       </c>
       <c r="K112" s="23" t="n"/>
-      <c r="L112" s="67" t="inlineStr"/>
+      <c r="L112" s="66" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="68" t="inlineStr">
+      <c r="A113" s="67" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -6490,7 +6467,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C113" s="76" t="inlineStr">
+      <c r="C113" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6527,10 +6504,10 @@
         </is>
       </c>
       <c r="K113" s="23" t="n"/>
-      <c r="L113" s="67" t="inlineStr"/>
+      <c r="L113" s="66" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="68" t="inlineStr">
+      <c r="A114" s="67" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -6540,7 +6517,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C114" s="76" t="inlineStr">
+      <c r="C114" s="75" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -6577,16 +6554,16 @@
         </is>
       </c>
       <c r="K114" s="23" t="n"/>
-      <c r="L114" s="67" t="inlineStr"/>
+      <c r="L114" s="66" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="68" t="inlineStr">
+      <c r="A115" s="67" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
       </c>
       <c r="B115" s="23" t="inlineStr"/>
-      <c r="C115" s="76" t="inlineStr">
+      <c r="C115" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6605,10 +6582,10 @@
       <c r="I115" s="65" t="inlineStr"/>
       <c r="J115" s="23" t="inlineStr"/>
       <c r="K115" s="23" t="n"/>
-      <c r="L115" s="67" t="inlineStr"/>
+      <c r="L115" s="66" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="68" t="inlineStr">
+      <c r="A116" s="67" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -6618,7 +6595,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C116" s="76" t="inlineStr">
+      <c r="C116" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6655,10 +6632,10 @@
         </is>
       </c>
       <c r="K116" s="23" t="n"/>
-      <c r="L116" s="67" t="inlineStr"/>
+      <c r="L116" s="66" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="68" t="inlineStr">
+      <c r="A117" s="67" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -6668,7 +6645,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C117" s="76" t="inlineStr">
+      <c r="C117" s="75" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -6705,10 +6682,10 @@
         </is>
       </c>
       <c r="K117" s="23" t="n"/>
-      <c r="L117" s="67" t="inlineStr"/>
+      <c r="L117" s="66" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="68" t="inlineStr">
+      <c r="A118" s="67" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -6718,7 +6695,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C118" s="76" t="inlineStr">
+      <c r="C118" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6755,16 +6732,16 @@
         </is>
       </c>
       <c r="K118" s="23" t="n"/>
-      <c r="L118" s="67" t="inlineStr"/>
+      <c r="L118" s="66" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="68" t="inlineStr">
+      <c r="A119" s="67" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
       </c>
       <c r="B119" s="23" t="inlineStr"/>
-      <c r="C119" s="76" t="inlineStr">
+      <c r="C119" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6783,16 +6760,16 @@
       <c r="I119" s="65" t="inlineStr"/>
       <c r="J119" s="23" t="inlineStr"/>
       <c r="K119" s="23" t="n"/>
-      <c r="L119" s="67" t="inlineStr"/>
+      <c r="L119" s="66" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="68" t="inlineStr">
+      <c r="A120" s="67" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B120" s="23" t="inlineStr"/>
-      <c r="C120" s="76" t="inlineStr">
+      <c r="C120" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6811,10 +6788,10 @@
       <c r="I120" s="65" t="inlineStr"/>
       <c r="J120" s="23" t="inlineStr"/>
       <c r="K120" s="23" t="n"/>
-      <c r="L120" s="67" t="inlineStr"/>
+      <c r="L120" s="66" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="68" t="inlineStr">
+      <c r="A121" s="67" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -6824,7 +6801,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C121" s="76" t="inlineStr">
+      <c r="C121" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6861,10 +6838,10 @@
         </is>
       </c>
       <c r="K121" s="23" t="n"/>
-      <c r="L121" s="67" t="inlineStr"/>
+      <c r="L121" s="66" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="68" t="inlineStr">
+      <c r="A122" s="67" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -6874,7 +6851,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C122" s="76" t="inlineStr">
+      <c r="C122" s="75" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -6911,16 +6888,16 @@
         </is>
       </c>
       <c r="K122" s="23" t="n"/>
-      <c r="L122" s="67" t="inlineStr"/>
+      <c r="L122" s="66" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="68" t="inlineStr">
+      <c r="A123" s="67" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
       </c>
       <c r="B123" s="23" t="inlineStr"/>
-      <c r="C123" s="76" t="inlineStr">
+      <c r="C123" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6939,16 +6916,16 @@
       <c r="I123" s="65" t="inlineStr"/>
       <c r="J123" s="23" t="inlineStr"/>
       <c r="K123" s="23" t="n"/>
-      <c r="L123" s="67" t="inlineStr"/>
+      <c r="L123" s="66" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="68" t="inlineStr">
+      <c r="A124" s="67" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
       </c>
       <c r="B124" s="23" t="inlineStr"/>
-      <c r="C124" s="76" t="inlineStr">
+      <c r="C124" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6967,10 +6944,10 @@
       <c r="I124" s="65" t="inlineStr"/>
       <c r="J124" s="23" t="inlineStr"/>
       <c r="K124" s="23" t="n"/>
-      <c r="L124" s="67" t="inlineStr"/>
+      <c r="L124" s="66" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="68" t="inlineStr">
+      <c r="A125" s="67" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -6980,7 +6957,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C125" s="76" t="inlineStr">
+      <c r="C125" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7017,10 +6994,10 @@
         </is>
       </c>
       <c r="K125" s="23" t="n"/>
-      <c r="L125" s="67" t="inlineStr"/>
+      <c r="L125" s="66" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="68" t="inlineStr">
+      <c r="A126" s="67" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -7030,7 +7007,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C126" s="76" t="inlineStr">
+      <c r="C126" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7067,16 +7044,16 @@
         </is>
       </c>
       <c r="K126" s="23" t="n"/>
-      <c r="L126" s="67" t="inlineStr"/>
+      <c r="L126" s="66" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="68" t="inlineStr">
+      <c r="A127" s="67" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
       </c>
       <c r="B127" s="23" t="inlineStr"/>
-      <c r="C127" s="77" t="inlineStr">
+      <c r="C127" s="76" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -7095,10 +7072,10 @@
       <c r="I127" s="65" t="inlineStr"/>
       <c r="J127" s="23" t="inlineStr"/>
       <c r="K127" s="23" t="n"/>
-      <c r="L127" s="67" t="inlineStr"/>
+      <c r="L127" s="66" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="68" t="inlineStr">
+      <c r="A128" s="67" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -7108,7 +7085,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C128" s="77" t="inlineStr">
+      <c r="C128" s="76" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -7145,10 +7122,10 @@
         </is>
       </c>
       <c r="K128" s="23" t="n"/>
-      <c r="L128" s="67" t="inlineStr"/>
+      <c r="L128" s="66" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="68" t="inlineStr">
+      <c r="A129" s="67" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -7158,7 +7135,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C129" s="77" t="inlineStr">
+      <c r="C129" s="76" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -7195,10 +7172,10 @@
         </is>
       </c>
       <c r="K129" s="23" t="n"/>
-      <c r="L129" s="67" t="inlineStr"/>
+      <c r="L129" s="66" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="68" t="inlineStr">
+      <c r="A130" s="67" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -7208,7 +7185,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C130" s="77" t="inlineStr">
+      <c r="C130" s="76" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -7245,10 +7222,10 @@
         </is>
       </c>
       <c r="K130" s="23" t="n"/>
-      <c r="L130" s="67" t="inlineStr"/>
+      <c r="L130" s="66" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="68" t="inlineStr">
+      <c r="A131" s="67" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -7258,7 +7235,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C131" s="77" t="inlineStr">
+      <c r="C131" s="76" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7295,10 +7272,10 @@
         </is>
       </c>
       <c r="K131" s="23" t="n"/>
-      <c r="L131" s="67" t="inlineStr"/>
+      <c r="L131" s="66" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="68" t="inlineStr">
+      <c r="A132" s="67" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -7308,7 +7285,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C132" s="77" t="inlineStr">
+      <c r="C132" s="76" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -7345,10 +7322,10 @@
         </is>
       </c>
       <c r="K132" s="23" t="n"/>
-      <c r="L132" s="67" t="inlineStr"/>
+      <c r="L132" s="66" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="68" t="inlineStr">
+      <c r="A133" s="67" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -7358,7 +7335,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C133" s="77" t="inlineStr">
+      <c r="C133" s="76" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -7395,10 +7372,10 @@
         </is>
       </c>
       <c r="K133" s="23" t="n"/>
-      <c r="L133" s="67" t="inlineStr"/>
+      <c r="L133" s="66" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="68" t="inlineStr">
+      <c r="A134" s="67" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -7408,7 +7385,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C134" s="77" t="inlineStr">
+      <c r="C134" s="76" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7445,10 +7422,10 @@
         </is>
       </c>
       <c r="K134" s="23" t="n"/>
-      <c r="L134" s="67" t="inlineStr"/>
+      <c r="L134" s="66" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="68" t="inlineStr">
+      <c r="A135" s="67" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -7458,7 +7435,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C135" s="77" t="inlineStr">
+      <c r="C135" s="76" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -7495,10 +7472,10 @@
         </is>
       </c>
       <c r="K135" s="23" t="n"/>
-      <c r="L135" s="67" t="inlineStr"/>
+      <c r="L135" s="66" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="68" t="inlineStr">
+      <c r="A136" s="67" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -7508,7 +7485,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C136" s="78" t="inlineStr">
+      <c r="C136" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7545,10 +7522,10 @@
         </is>
       </c>
       <c r="K136" s="23" t="n"/>
-      <c r="L136" s="67" t="inlineStr"/>
+      <c r="L136" s="66" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="68" t="inlineStr">
+      <c r="A137" s="67" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -7558,7 +7535,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C137" s="77" t="inlineStr">
+      <c r="C137" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7595,10 +7572,10 @@
         </is>
       </c>
       <c r="K137" s="23" t="n"/>
-      <c r="L137" s="67" t="inlineStr"/>
+      <c r="L137" s="66" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="68" t="inlineStr">
+      <c r="A138" s="67" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -7608,7 +7585,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C138" s="78" t="inlineStr">
+      <c r="C138" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7645,10 +7622,10 @@
         </is>
       </c>
       <c r="K138" s="23" t="n"/>
-      <c r="L138" s="67" t="inlineStr"/>
+      <c r="L138" s="66" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="68" t="inlineStr">
+      <c r="A139" s="67" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -7658,7 +7635,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C139" s="77" t="inlineStr">
+      <c r="C139" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7695,10 +7672,10 @@
         </is>
       </c>
       <c r="K139" s="23" t="n"/>
-      <c r="L139" s="67" t="inlineStr"/>
+      <c r="L139" s="66" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="68" t="inlineStr">
+      <c r="A140" s="67" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -7708,7 +7685,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C140" s="78" t="inlineStr">
+      <c r="C140" s="77" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -7745,10 +7722,10 @@
         </is>
       </c>
       <c r="K140" s="23" t="n"/>
-      <c r="L140" s="67" t="inlineStr"/>
+      <c r="L140" s="66" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="68" t="inlineStr">
+      <c r="A141" s="67" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -7758,7 +7735,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C141" s="76" t="inlineStr">
+      <c r="C141" s="75" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -7795,10 +7772,10 @@
         </is>
       </c>
       <c r="K141" s="23" t="n"/>
-      <c r="L141" s="67" t="inlineStr"/>
+      <c r="L141" s="66" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="68" t="inlineStr">
+      <c r="A142" s="67" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -7808,7 +7785,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C142" s="77" t="inlineStr">
+      <c r="C142" s="76" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7845,10 +7822,10 @@
         </is>
       </c>
       <c r="K142" s="23" t="n"/>
-      <c r="L142" s="67" t="inlineStr"/>
+      <c r="L142" s="66" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="68" t="inlineStr">
+      <c r="A143" s="67" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -7858,7 +7835,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C143" s="76" t="inlineStr">
+      <c r="C143" s="75" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7895,10 +7872,10 @@
         </is>
       </c>
       <c r="K143" s="23" t="n"/>
-      <c r="L143" s="67" t="inlineStr"/>
+      <c r="L143" s="66" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="68" t="inlineStr">
+      <c r="A144" s="67" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -7908,7 +7885,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C144" s="77" t="inlineStr">
+      <c r="C144" s="76" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -7945,10 +7922,10 @@
         </is>
       </c>
       <c r="K144" s="23" t="n"/>
-      <c r="L144" s="67" t="inlineStr"/>
+      <c r="L144" s="66" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="68" t="inlineStr">
+      <c r="A145" s="67" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -7958,7 +7935,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C145" s="77" t="inlineStr">
+      <c r="C145" s="76" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -7995,10 +7972,10 @@
         </is>
       </c>
       <c r="K145" s="23" t="n"/>
-      <c r="L145" s="67" t="inlineStr"/>
+      <c r="L145" s="66" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="68" t="inlineStr">
+      <c r="A146" s="67" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -8008,7 +7985,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C146" s="77" t="inlineStr">
+      <c r="C146" s="76" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8045,10 +8022,10 @@
         </is>
       </c>
       <c r="K146" s="23" t="n"/>
-      <c r="L146" s="67" t="inlineStr"/>
+      <c r="L146" s="66" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="68" t="inlineStr">
+      <c r="A147" s="67" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -8058,7 +8035,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C147" s="77" t="inlineStr">
+      <c r="C147" s="76" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8095,10 +8072,10 @@
         </is>
       </c>
       <c r="K147" s="23" t="n"/>
-      <c r="L147" s="67" t="inlineStr"/>
+      <c r="L147" s="66" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="68" t="inlineStr">
+      <c r="A148" s="67" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -8108,7 +8085,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C148" s="77" t="inlineStr">
+      <c r="C148" s="76" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8145,10 +8122,10 @@
         </is>
       </c>
       <c r="K148" s="23" t="n"/>
-      <c r="L148" s="67" t="inlineStr"/>
+      <c r="L148" s="66" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="68" t="inlineStr">
+      <c r="A149" s="67" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -8158,7 +8135,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C149" s="77" t="inlineStr">
+      <c r="C149" s="76" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -8195,10 +8172,10 @@
         </is>
       </c>
       <c r="K149" s="23" t="n"/>
-      <c r="L149" s="67" t="inlineStr"/>
+      <c r="L149" s="66" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="68" t="inlineStr">
+      <c r="A150" s="67" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -8208,7 +8185,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C150" s="76" t="inlineStr">
+      <c r="C150" s="75" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8245,10 +8222,10 @@
         </is>
       </c>
       <c r="K150" s="23" t="n"/>
-      <c r="L150" s="67" t="inlineStr"/>
+      <c r="L150" s="66" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="68" t="inlineStr">
+      <c r="A151" s="67" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -8258,7 +8235,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C151" s="76" t="inlineStr">
+      <c r="C151" s="75" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8295,10 +8272,10 @@
         </is>
       </c>
       <c r="K151" s="23" t="n"/>
-      <c r="L151" s="67" t="inlineStr"/>
+      <c r="L151" s="66" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="68" t="inlineStr">
+      <c r="A152" s="67" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -8308,7 +8285,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C152" s="76" t="inlineStr">
+      <c r="C152" s="75" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8345,10 +8322,10 @@
         </is>
       </c>
       <c r="K152" s="23" t="n"/>
-      <c r="L152" s="67" t="inlineStr"/>
+      <c r="L152" s="66" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="68" t="inlineStr">
+      <c r="A153" s="67" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -8358,7 +8335,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C153" s="77" t="inlineStr">
+      <c r="C153" s="76" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -8395,10 +8372,10 @@
         </is>
       </c>
       <c r="K153" s="23" t="n"/>
-      <c r="L153" s="67" t="inlineStr"/>
+      <c r="L153" s="66" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="68" t="inlineStr">
+      <c r="A154" s="67" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -8408,7 +8385,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C154" s="77" t="inlineStr">
+      <c r="C154" s="76" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8445,10 +8422,10 @@
         </is>
       </c>
       <c r="K154" s="23" t="n"/>
-      <c r="L154" s="67" t="inlineStr"/>
+      <c r="L154" s="66" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="68" t="inlineStr">
+      <c r="A155" s="67" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -8458,7 +8435,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C155" s="76" t="inlineStr">
+      <c r="C155" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8495,10 +8472,10 @@
         </is>
       </c>
       <c r="K155" s="23" t="n"/>
-      <c r="L155" s="67" t="inlineStr"/>
+      <c r="L155" s="66" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="68" t="inlineStr">
+      <c r="A156" s="67" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -8508,7 +8485,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C156" s="78" t="inlineStr">
+      <c r="C156" s="77" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -8545,10 +8522,10 @@
         </is>
       </c>
       <c r="K156" s="23" t="n"/>
-      <c r="L156" s="67" t="inlineStr"/>
+      <c r="L156" s="66" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="68" t="inlineStr">
+      <c r="A157" s="67" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -8558,7 +8535,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C157" s="77" t="inlineStr">
+      <c r="C157" s="76" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -8595,10 +8572,10 @@
         </is>
       </c>
       <c r="K157" s="23" t="n"/>
-      <c r="L157" s="67" t="inlineStr"/>
+      <c r="L157" s="66" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="68" t="inlineStr">
+      <c r="A158" s="67" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -8608,7 +8585,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C158" s="78" t="inlineStr">
+      <c r="C158" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8641,14 +8618,14 @@
       </c>
       <c r="J158" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K158" s="23" t="n"/>
-      <c r="L158" s="67" t="inlineStr"/>
+      <c r="L158" s="66" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="68" t="inlineStr">
+      <c r="A159" s="67" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -8658,7 +8635,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C159" s="78" t="inlineStr">
+      <c r="C159" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8695,10 +8672,10 @@
         </is>
       </c>
       <c r="K159" s="23" t="n"/>
-      <c r="L159" s="67" t="inlineStr"/>
+      <c r="L159" s="66" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="68" t="inlineStr">
+      <c r="A160" s="67" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -8708,7 +8685,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C160" s="78" t="inlineStr">
+      <c r="C160" s="77" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -8745,10 +8722,10 @@
         </is>
       </c>
       <c r="K160" s="23" t="n"/>
-      <c r="L160" s="67" t="inlineStr"/>
+      <c r="L160" s="66" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="68" t="inlineStr">
+      <c r="A161" s="67" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -8758,7 +8735,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C161" s="78" t="inlineStr">
+      <c r="C161" s="77" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -8787,10 +8764,10 @@
       <c r="I161" s="65" t="inlineStr"/>
       <c r="J161" s="23" t="inlineStr"/>
       <c r="K161" s="23" t="n"/>
-      <c r="L161" s="67" t="inlineStr"/>
+      <c r="L161" s="66" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="68" t="inlineStr">
+      <c r="A162" s="67" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -8800,7 +8777,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C162" s="77" t="inlineStr">
+      <c r="C162" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8829,10 +8806,10 @@
       <c r="I162" s="65" t="inlineStr"/>
       <c r="J162" s="23" t="inlineStr"/>
       <c r="K162" s="23" t="n"/>
-      <c r="L162" s="67" t="inlineStr"/>
+      <c r="L162" s="66" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="68" t="inlineStr">
+      <c r="A163" s="67" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -8842,7 +8819,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C163" s="77" t="inlineStr">
+      <c r="C163" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8871,10 +8848,10 @@
       <c r="I163" s="65" t="inlineStr"/>
       <c r="J163" s="23" t="inlineStr"/>
       <c r="K163" s="23" t="n"/>
-      <c r="L163" s="67" t="inlineStr"/>
+      <c r="L163" s="66" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="68" t="inlineStr">
+      <c r="A164" s="67" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -8884,7 +8861,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C164" s="77" t="inlineStr">
+      <c r="C164" s="76" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -8913,10 +8890,10 @@
       <c r="I164" s="65" t="inlineStr"/>
       <c r="J164" s="23" t="inlineStr"/>
       <c r="K164" s="23" t="n"/>
-      <c r="L164" s="67" t="inlineStr"/>
+      <c r="L164" s="66" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="68" t="inlineStr">
+      <c r="A165" s="67" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -8926,7 +8903,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C165" s="78" t="inlineStr">
+      <c r="C165" s="77" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -8963,10 +8940,10 @@
         </is>
       </c>
       <c r="K165" s="23" t="n"/>
-      <c r="L165" s="67" t="inlineStr"/>
+      <c r="L165" s="66" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="68" t="inlineStr">
+      <c r="A166" s="67" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -8976,7 +8953,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C166" s="77" t="inlineStr">
+      <c r="C166" s="76" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -9005,10 +8982,10 @@
       <c r="I166" s="65" t="inlineStr"/>
       <c r="J166" s="23" t="inlineStr"/>
       <c r="K166" s="23" t="n"/>
-      <c r="L166" s="67" t="inlineStr"/>
+      <c r="L166" s="66" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="68" t="inlineStr">
+      <c r="A167" s="67" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9018,7 +8995,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C167" s="77" t="inlineStr">
+      <c r="C167" s="76" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -9047,10 +9024,10 @@
       <c r="I167" s="65" t="inlineStr"/>
       <c r="J167" s="23" t="inlineStr"/>
       <c r="K167" s="23" t="n"/>
-      <c r="L167" s="67" t="inlineStr"/>
+      <c r="L167" s="66" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="68" t="inlineStr">
+      <c r="A168" s="67" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -9060,7 +9037,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C168" s="78" t="inlineStr">
+      <c r="C168" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9097,10 +9074,10 @@
         </is>
       </c>
       <c r="K168" s="23" t="n"/>
-      <c r="L168" s="67" t="inlineStr"/>
+      <c r="L168" s="66" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="68" t="inlineStr">
+      <c r="A169" s="67" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -9110,7 +9087,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C169" s="78" t="inlineStr">
+      <c r="C169" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9147,10 +9124,10 @@
         </is>
       </c>
       <c r="K169" s="23" t="n"/>
-      <c r="L169" s="67" t="inlineStr"/>
+      <c r="L169" s="66" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="68" t="inlineStr">
+      <c r="A170" s="67" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -9160,7 +9137,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C170" s="78" t="inlineStr">
+      <c r="C170" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9197,10 +9174,10 @@
         </is>
       </c>
       <c r="K170" s="23" t="n"/>
-      <c r="L170" s="67" t="inlineStr"/>
+      <c r="L170" s="66" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="68" t="inlineStr">
+      <c r="A171" s="67" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -9210,7 +9187,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C171" s="78" t="inlineStr">
+      <c r="C171" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9247,10 +9224,10 @@
         </is>
       </c>
       <c r="K171" s="23" t="n"/>
-      <c r="L171" s="67" t="inlineStr"/>
+      <c r="L171" s="66" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="68" t="inlineStr">
+      <c r="A172" s="67" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -9260,7 +9237,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C172" s="78" t="inlineStr">
+      <c r="C172" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9297,10 +9274,10 @@
         </is>
       </c>
       <c r="K172" s="23" t="n"/>
-      <c r="L172" s="67" t="inlineStr"/>
+      <c r="L172" s="66" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="68" t="inlineStr">
+      <c r="A173" s="67" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -9310,7 +9287,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C173" s="78" t="inlineStr">
+      <c r="C173" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9347,10 +9324,10 @@
         </is>
       </c>
       <c r="K173" s="23" t="n"/>
-      <c r="L173" s="67" t="inlineStr"/>
+      <c r="L173" s="66" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="68" t="inlineStr">
+      <c r="A174" s="67" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -9360,7 +9337,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C174" s="78" t="inlineStr">
+      <c r="C174" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9397,10 +9374,10 @@
         </is>
       </c>
       <c r="K174" s="23" t="n"/>
-      <c r="L174" s="67" t="inlineStr"/>
+      <c r="L174" s="66" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="68" t="inlineStr">
+      <c r="A175" s="67" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -9410,7 +9387,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C175" s="78" t="inlineStr">
+      <c r="C175" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9447,10 +9424,10 @@
         </is>
       </c>
       <c r="K175" s="23" t="n"/>
-      <c r="L175" s="67" t="inlineStr"/>
+      <c r="L175" s="66" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="68" t="inlineStr">
+      <c r="A176" s="67" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -9460,7 +9437,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C176" s="78" t="inlineStr">
+      <c r="C176" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9497,10 +9474,10 @@
         </is>
       </c>
       <c r="K176" s="23" t="n"/>
-      <c r="L176" s="67" t="inlineStr"/>
+      <c r="L176" s="66" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="68" t="inlineStr">
+      <c r="A177" s="67" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -9510,7 +9487,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C177" s="78" t="inlineStr">
+      <c r="C177" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9547,10 +9524,10 @@
         </is>
       </c>
       <c r="K177" s="23" t="n"/>
-      <c r="L177" s="67" t="inlineStr"/>
+      <c r="L177" s="66" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="68" t="inlineStr">
+      <c r="A178" s="67" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -9560,7 +9537,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C178" s="78" t="inlineStr">
+      <c r="C178" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9597,10 +9574,10 @@
         </is>
       </c>
       <c r="K178" s="23" t="n"/>
-      <c r="L178" s="67" t="inlineStr"/>
+      <c r="L178" s="66" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="68" t="inlineStr">
+      <c r="A179" s="67" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -9610,7 +9587,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C179" s="78" t="inlineStr">
+      <c r="C179" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9647,10 +9624,10 @@
         </is>
       </c>
       <c r="K179" s="23" t="n"/>
-      <c r="L179" s="67" t="inlineStr"/>
+      <c r="L179" s="66" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="68" t="inlineStr">
+      <c r="A180" s="67" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -9660,7 +9637,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C180" s="78" t="inlineStr">
+      <c r="C180" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9697,10 +9674,10 @@
         </is>
       </c>
       <c r="K180" s="23" t="n"/>
-      <c r="L180" s="67" t="inlineStr"/>
+      <c r="L180" s="66" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="68" t="inlineStr">
+      <c r="A181" s="67" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -9710,7 +9687,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C181" s="78" t="inlineStr">
+      <c r="C181" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9747,10 +9724,10 @@
         </is>
       </c>
       <c r="K181" s="23" t="n"/>
-      <c r="L181" s="67" t="inlineStr"/>
+      <c r="L181" s="66" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="68" t="inlineStr">
+      <c r="A182" s="67" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -9760,7 +9737,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C182" s="78" t="inlineStr">
+      <c r="C182" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9797,10 +9774,10 @@
         </is>
       </c>
       <c r="K182" s="23" t="n"/>
-      <c r="L182" s="67" t="inlineStr"/>
+      <c r="L182" s="66" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="68" t="inlineStr">
+      <c r="A183" s="67" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -9810,7 +9787,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C183" s="78" t="inlineStr">
+      <c r="C183" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9847,10 +9824,10 @@
         </is>
       </c>
       <c r="K183" s="23" t="n"/>
-      <c r="L183" s="67" t="inlineStr"/>
+      <c r="L183" s="66" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="68" t="inlineStr">
+      <c r="A184" s="67" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -9860,7 +9837,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C184" s="77" t="inlineStr">
+      <c r="C184" s="76" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9897,10 +9874,10 @@
         </is>
       </c>
       <c r="K184" s="23" t="n"/>
-      <c r="L184" s="67" t="inlineStr"/>
+      <c r="L184" s="66" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="68" t="inlineStr">
+      <c r="A185" s="67" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -9910,7 +9887,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C185" s="78" t="inlineStr">
+      <c r="C185" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9947,10 +9924,10 @@
         </is>
       </c>
       <c r="K185" s="23" t="n"/>
-      <c r="L185" s="67" t="inlineStr"/>
+      <c r="L185" s="66" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="68" t="inlineStr">
+      <c r="A186" s="67" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -9960,7 +9937,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C186" s="78" t="inlineStr">
+      <c r="C186" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9997,10 +9974,10 @@
         </is>
       </c>
       <c r="K186" s="23" t="n"/>
-      <c r="L186" s="67" t="inlineStr"/>
+      <c r="L186" s="66" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="68" t="inlineStr">
+      <c r="A187" s="67" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -10010,7 +9987,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C187" s="78" t="inlineStr">
+      <c r="C187" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10047,10 +10024,10 @@
         </is>
       </c>
       <c r="K187" s="23" t="n"/>
-      <c r="L187" s="67" t="inlineStr"/>
+      <c r="L187" s="66" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="68" t="inlineStr">
+      <c r="A188" s="67" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -10060,7 +10037,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C188" s="78" t="inlineStr">
+      <c r="C188" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10097,10 +10074,10 @@
         </is>
       </c>
       <c r="K188" s="23" t="n"/>
-      <c r="L188" s="67" t="inlineStr"/>
+      <c r="L188" s="66" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="68" t="inlineStr">
+      <c r="A189" s="67" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -10110,7 +10087,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C189" s="78" t="inlineStr">
+      <c r="C189" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10147,10 +10124,10 @@
         </is>
       </c>
       <c r="K189" s="23" t="n"/>
-      <c r="L189" s="67" t="inlineStr"/>
+      <c r="L189" s="66" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="68" t="inlineStr">
+      <c r="A190" s="67" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -10160,7 +10137,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C190" s="78" t="inlineStr">
+      <c r="C190" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10197,10 +10174,10 @@
         </is>
       </c>
       <c r="K190" s="23" t="n"/>
-      <c r="L190" s="67" t="inlineStr"/>
+      <c r="L190" s="66" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="68" t="inlineStr">
+      <c r="A191" s="67" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -10210,7 +10187,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C191" s="78" t="inlineStr">
+      <c r="C191" s="77" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -10247,10 +10224,10 @@
         </is>
       </c>
       <c r="K191" s="23" t="n"/>
-      <c r="L191" s="67" t="inlineStr"/>
+      <c r="L191" s="66" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="68" t="inlineStr">
+      <c r="A192" s="67" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -10260,7 +10237,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C192" s="78" t="inlineStr">
+      <c r="C192" s="77" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -10289,10 +10266,10 @@
       <c r="I192" s="65" t="inlineStr"/>
       <c r="J192" s="23" t="inlineStr"/>
       <c r="K192" s="23" t="n"/>
-      <c r="L192" s="67" t="inlineStr"/>
+      <c r="L192" s="66" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="68" t="inlineStr">
+      <c r="A193" s="67" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -10302,7 +10279,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C193" s="77" t="inlineStr">
+      <c r="C193" s="76" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -10331,10 +10308,10 @@
       <c r="I193" s="65" t="inlineStr"/>
       <c r="J193" s="23" t="inlineStr"/>
       <c r="K193" s="23" t="n"/>
-      <c r="L193" s="67" t="inlineStr"/>
+      <c r="L193" s="66" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="68" t="inlineStr">
+      <c r="A194" s="67" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -10344,7 +10321,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C194" s="78" t="inlineStr">
+      <c r="C194" s="77" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -10373,10 +10350,10 @@
       <c r="I194" s="65" t="inlineStr"/>
       <c r="J194" s="23" t="inlineStr"/>
       <c r="K194" s="23" t="n"/>
-      <c r="L194" s="67" t="inlineStr"/>
+      <c r="L194" s="66" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="68" t="inlineStr">
+      <c r="A195" s="67" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -10386,7 +10363,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C195" s="78" t="inlineStr">
+      <c r="C195" s="77" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -10415,10 +10392,10 @@
       <c r="I195" s="65" t="inlineStr"/>
       <c r="J195" s="23" t="inlineStr"/>
       <c r="K195" s="23" t="n"/>
-      <c r="L195" s="67" t="inlineStr"/>
+      <c r="L195" s="66" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="68" t="inlineStr">
+      <c r="A196" s="67" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -10428,7 +10405,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C196" s="77" t="inlineStr">
+      <c r="C196" s="76" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -10457,10 +10434,10 @@
       <c r="I196" s="65" t="inlineStr"/>
       <c r="J196" s="23" t="inlineStr"/>
       <c r="K196" s="23" t="n"/>
-      <c r="L196" s="67" t="inlineStr"/>
+      <c r="L196" s="66" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="68" t="inlineStr">
+      <c r="A197" s="67" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -10470,7 +10447,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C197" s="78" t="inlineStr">
+      <c r="C197" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10499,10 +10476,10 @@
       <c r="I197" s="65" t="inlineStr"/>
       <c r="J197" s="23" t="inlineStr"/>
       <c r="K197" s="23" t="n"/>
-      <c r="L197" s="67" t="inlineStr"/>
+      <c r="L197" s="66" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="68" t="inlineStr">
+      <c r="A198" s="67" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -10512,7 +10489,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C198" s="78" t="inlineStr">
+      <c r="C198" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10541,10 +10518,10 @@
       <c r="I198" s="65" t="inlineStr"/>
       <c r="J198" s="23" t="inlineStr"/>
       <c r="K198" s="23" t="n"/>
-      <c r="L198" s="67" t="inlineStr"/>
+      <c r="L198" s="66" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="68" t="inlineStr">
+      <c r="A199" s="67" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -10554,7 +10531,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C199" s="77" t="inlineStr">
+      <c r="C199" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10583,10 +10560,10 @@
       <c r="I199" s="65" t="inlineStr"/>
       <c r="J199" s="23" t="inlineStr"/>
       <c r="K199" s="23" t="n"/>
-      <c r="L199" s="67" t="inlineStr"/>
+      <c r="L199" s="66" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="68" t="inlineStr">
+      <c r="A200" s="67" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -10596,7 +10573,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C200" s="77" t="inlineStr">
+      <c r="C200" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10625,10 +10602,10 @@
       <c r="I200" s="65" t="inlineStr"/>
       <c r="J200" s="23" t="inlineStr"/>
       <c r="K200" s="23" t="n"/>
-      <c r="L200" s="67" t="inlineStr"/>
+      <c r="L200" s="66" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="68" t="inlineStr">
+      <c r="A201" s="67" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -10638,7 +10615,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C201" s="77" t="inlineStr">
+      <c r="C201" s="76" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -10667,10 +10644,10 @@
       <c r="I201" s="65" t="inlineStr"/>
       <c r="J201" s="23" t="inlineStr"/>
       <c r="K201" s="23" t="n"/>
-      <c r="L201" s="67" t="inlineStr"/>
+      <c r="L201" s="66" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="68" t="inlineStr">
+      <c r="A202" s="67" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -10680,7 +10657,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C202" s="78" t="inlineStr">
+      <c r="C202" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10717,10 +10694,10 @@
         </is>
       </c>
       <c r="K202" s="23" t="n"/>
-      <c r="L202" s="67" t="inlineStr"/>
+      <c r="L202" s="66" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="68" t="inlineStr">
+      <c r="A203" s="67" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -10730,7 +10707,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C203" s="78" t="inlineStr">
+      <c r="C203" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10767,10 +10744,10 @@
         </is>
       </c>
       <c r="K203" s="23" t="n"/>
-      <c r="L203" s="67" t="inlineStr"/>
+      <c r="L203" s="66" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="68" t="inlineStr">
+      <c r="A204" s="67" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -10780,7 +10757,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C204" s="78" t="inlineStr">
+      <c r="C204" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10817,10 +10794,10 @@
         </is>
       </c>
       <c r="K204" s="23" t="n"/>
-      <c r="L204" s="67" t="inlineStr"/>
+      <c r="L204" s="66" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="68" t="inlineStr">
+      <c r="A205" s="67" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -10830,7 +10807,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C205" s="78" t="inlineStr">
+      <c r="C205" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10867,10 +10844,10 @@
         </is>
       </c>
       <c r="K205" s="23" t="n"/>
-      <c r="L205" s="67" t="inlineStr"/>
+      <c r="L205" s="66" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="68" t="inlineStr">
+      <c r="A206" s="67" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -10880,7 +10857,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C206" s="78" t="inlineStr">
+      <c r="C206" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10917,10 +10894,10 @@
         </is>
       </c>
       <c r="K206" s="23" t="n"/>
-      <c r="L206" s="67" t="inlineStr"/>
+      <c r="L206" s="66" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="68" t="inlineStr">
+      <c r="A207" s="67" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -10930,7 +10907,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C207" s="78" t="inlineStr">
+      <c r="C207" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10967,10 +10944,10 @@
         </is>
       </c>
       <c r="K207" s="23" t="n"/>
-      <c r="L207" s="67" t="inlineStr"/>
+      <c r="L207" s="66" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="68" t="inlineStr">
+      <c r="A208" s="67" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -10980,7 +10957,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C208" s="78" t="inlineStr">
+      <c r="C208" s="77" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -11017,10 +10994,10 @@
         </is>
       </c>
       <c r="K208" s="23" t="n"/>
-      <c r="L208" s="67" t="inlineStr"/>
+      <c r="L208" s="66" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="68" t="inlineStr">
+      <c r="A209" s="67" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -11030,7 +11007,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C209" s="77" t="inlineStr">
+      <c r="C209" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -11067,10 +11044,10 @@
         </is>
       </c>
       <c r="K209" s="23" t="n"/>
-      <c r="L209" s="67" t="inlineStr"/>
+      <c r="L209" s="66" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="68" t="inlineStr">
+      <c r="A210" s="67" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -11080,7 +11057,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C210" s="77" t="inlineStr">
+      <c r="C210" s="76" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11117,10 +11094,10 @@
         </is>
       </c>
       <c r="K210" s="23" t="n"/>
-      <c r="L210" s="67" t="inlineStr"/>
+      <c r="L210" s="66" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="68" t="inlineStr">
+      <c r="A211" s="67" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -11130,7 +11107,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C211" s="78" t="inlineStr">
+      <c r="C211" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11167,10 +11144,10 @@
         </is>
       </c>
       <c r="K211" s="23" t="n"/>
-      <c r="L211" s="67" t="inlineStr"/>
+      <c r="L211" s="66" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="68" t="inlineStr">
+      <c r="A212" s="67" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -11180,7 +11157,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C212" s="76" t="inlineStr">
+      <c r="C212" s="75" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -11217,10 +11194,10 @@
         </is>
       </c>
       <c r="K212" s="23" t="n"/>
-      <c r="L212" s="67" t="inlineStr"/>
+      <c r="L212" s="66" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="68" t="inlineStr">
+      <c r="A213" s="67" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -11230,7 +11207,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C213" s="76" t="inlineStr">
+      <c r="C213" s="75" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -11267,10 +11244,10 @@
         </is>
       </c>
       <c r="K213" s="23" t="n"/>
-      <c r="L213" s="67" t="inlineStr"/>
+      <c r="L213" s="66" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="68" t="inlineStr">
+      <c r="A214" s="67" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -11280,7 +11257,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C214" s="78" t="inlineStr">
+      <c r="C214" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11317,10 +11294,10 @@
         </is>
       </c>
       <c r="K214" s="23" t="n"/>
-      <c r="L214" s="67" t="inlineStr"/>
+      <c r="L214" s="66" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="68" t="inlineStr">
+      <c r="A215" s="67" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -11330,7 +11307,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C215" s="78" t="inlineStr">
+      <c r="C215" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11367,16 +11344,16 @@
         </is>
       </c>
       <c r="K215" s="23" t="n"/>
-      <c r="L215" s="67" t="inlineStr"/>
+      <c r="L215" s="66" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="68" t="inlineStr">
+      <c r="A216" s="67" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
       </c>
       <c r="B216" s="23" t="inlineStr"/>
-      <c r="C216" s="76" t="inlineStr">
+      <c r="C216" s="75" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -11395,10 +11372,10 @@
       <c r="I216" s="65" t="inlineStr"/>
       <c r="J216" s="23" t="inlineStr"/>
       <c r="K216" s="23" t="n"/>
-      <c r="L216" s="67" t="inlineStr"/>
+      <c r="L216" s="66" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="68" t="inlineStr">
+      <c r="A217" s="67" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -11408,7 +11385,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C217" s="76" t="inlineStr">
+      <c r="C217" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11445,10 +11422,10 @@
         </is>
       </c>
       <c r="K217" s="23" t="n"/>
-      <c r="L217" s="67" t="inlineStr"/>
+      <c r="L217" s="66" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="68" t="inlineStr">
+      <c r="A218" s="67" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -11458,7 +11435,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C218" s="76" t="inlineStr">
+      <c r="C218" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11495,10 +11472,10 @@
         </is>
       </c>
       <c r="K218" s="23" t="n"/>
-      <c r="L218" s="67" t="inlineStr"/>
+      <c r="L218" s="66" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="68" t="inlineStr">
+      <c r="A219" s="67" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -11508,7 +11485,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C219" s="76" t="inlineStr">
+      <c r="C219" s="75" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -11545,10 +11522,10 @@
         </is>
       </c>
       <c r="K219" s="23" t="n"/>
-      <c r="L219" s="67" t="inlineStr"/>
+      <c r="L219" s="66" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="68" t="inlineStr">
+      <c r="A220" s="67" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -11558,7 +11535,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C220" s="76" t="inlineStr">
+      <c r="C220" s="75" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -11595,10 +11572,10 @@
         </is>
       </c>
       <c r="K220" s="23" t="n"/>
-      <c r="L220" s="67" t="inlineStr"/>
+      <c r="L220" s="66" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="68" t="inlineStr">
+      <c r="A221" s="67" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -11608,7 +11585,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C221" s="77" t="inlineStr">
+      <c r="C221" s="76" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11645,10 +11622,10 @@
         </is>
       </c>
       <c r="K221" s="23" t="n"/>
-      <c r="L221" s="67" t="inlineStr"/>
+      <c r="L221" s="66" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="68" t="inlineStr">
+      <c r="A222" s="67" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -11658,7 +11635,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C222" s="78" t="inlineStr">
+      <c r="C222" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11695,10 +11672,10 @@
         </is>
       </c>
       <c r="K222" s="23" t="n"/>
-      <c r="L222" s="67" t="inlineStr"/>
+      <c r="L222" s="66" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="68" t="inlineStr">
+      <c r="A223" s="67" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -11708,7 +11685,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C223" s="76" t="inlineStr">
+      <c r="C223" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11745,10 +11722,10 @@
         </is>
       </c>
       <c r="K223" s="23" t="n"/>
-      <c r="L223" s="67" t="inlineStr"/>
+      <c r="L223" s="66" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="68" t="inlineStr">
+      <c r="A224" s="67" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -11758,7 +11735,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C224" s="76" t="inlineStr">
+      <c r="C224" s="75" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -11795,10 +11772,10 @@
         </is>
       </c>
       <c r="K224" s="23" t="n"/>
-      <c r="L224" s="67" t="inlineStr"/>
+      <c r="L224" s="66" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="68" t="inlineStr">
+      <c r="A225" s="67" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -11808,7 +11785,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C225" s="76" t="inlineStr">
+      <c r="C225" s="75" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -11845,10 +11822,10 @@
         </is>
       </c>
       <c r="K225" s="23" t="n"/>
-      <c r="L225" s="67" t="inlineStr"/>
+      <c r="L225" s="66" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="68" t="inlineStr">
+      <c r="A226" s="67" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -11858,7 +11835,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C226" s="76" t="inlineStr">
+      <c r="C226" s="75" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -11895,10 +11872,10 @@
         </is>
       </c>
       <c r="K226" s="23" t="n"/>
-      <c r="L226" s="67" t="inlineStr"/>
+      <c r="L226" s="66" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="68" t="inlineStr">
+      <c r="A227" s="67" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -11908,7 +11885,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C227" s="76" t="inlineStr">
+      <c r="C227" s="75" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -11945,10 +11922,10 @@
         </is>
       </c>
       <c r="K227" s="23" t="n"/>
-      <c r="L227" s="67" t="inlineStr"/>
+      <c r="L227" s="66" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="68" t="inlineStr">
+      <c r="A228" s="67" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -11958,7 +11935,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C228" s="76" t="inlineStr">
+      <c r="C228" s="75" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -11995,10 +11972,10 @@
         </is>
       </c>
       <c r="K228" s="23" t="n"/>
-      <c r="L228" s="67" t="inlineStr"/>
+      <c r="L228" s="66" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="68" t="inlineStr">
+      <c r="A229" s="67" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -12008,7 +11985,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C229" s="76" t="inlineStr">
+      <c r="C229" s="75" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -12045,16 +12022,16 @@
         </is>
       </c>
       <c r="K229" s="23" t="n"/>
-      <c r="L229" s="67" t="inlineStr"/>
+      <c r="L229" s="66" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="68" t="inlineStr">
+      <c r="A230" s="67" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
       </c>
       <c r="B230" s="23" t="inlineStr"/>
-      <c r="C230" s="78" t="inlineStr">
+      <c r="C230" s="77" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -12073,16 +12050,16 @@
       <c r="I230" s="65" t="inlineStr"/>
       <c r="J230" s="23" t="inlineStr"/>
       <c r="K230" s="23" t="n"/>
-      <c r="L230" s="67" t="inlineStr"/>
+      <c r="L230" s="66" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="68" t="inlineStr">
+      <c r="A231" s="67" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
       </c>
       <c r="B231" s="23" t="inlineStr"/>
-      <c r="C231" s="78" t="inlineStr">
+      <c r="C231" s="77" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -12101,10 +12078,10 @@
       <c r="I231" s="65" t="inlineStr"/>
       <c r="J231" s="23" t="inlineStr"/>
       <c r="K231" s="23" t="n"/>
-      <c r="L231" s="67" t="inlineStr"/>
+      <c r="L231" s="66" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="68" t="inlineStr">
+      <c r="A232" s="67" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -12114,7 +12091,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C232" s="76" t="inlineStr">
+      <c r="C232" s="75" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -12151,10 +12128,10 @@
         </is>
       </c>
       <c r="K232" s="23" t="n"/>
-      <c r="L232" s="67" t="inlineStr"/>
+      <c r="L232" s="66" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="68" t="inlineStr">
+      <c r="A233" s="67" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -12164,7 +12141,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C233" s="76" t="inlineStr">
+      <c r="C233" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12201,10 +12178,10 @@
         </is>
       </c>
       <c r="K233" s="23" t="n"/>
-      <c r="L233" s="67" t="inlineStr"/>
+      <c r="L233" s="66" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="68" t="inlineStr">
+      <c r="A234" s="67" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -12214,7 +12191,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C234" s="76" t="inlineStr">
+      <c r="C234" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12251,10 +12228,10 @@
         </is>
       </c>
       <c r="K234" s="23" t="n"/>
-      <c r="L234" s="67" t="inlineStr"/>
+      <c r="L234" s="66" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="68" t="inlineStr">
+      <c r="A235" s="67" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -12264,7 +12241,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C235" s="76" t="inlineStr">
+      <c r="C235" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12301,10 +12278,10 @@
         </is>
       </c>
       <c r="K235" s="23" t="n"/>
-      <c r="L235" s="67" t="inlineStr"/>
+      <c r="L235" s="66" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="68" t="inlineStr">
+      <c r="A236" s="67" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -12314,7 +12291,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C236" s="76" t="inlineStr">
+      <c r="C236" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12351,10 +12328,10 @@
         </is>
       </c>
       <c r="K236" s="23" t="n"/>
-      <c r="L236" s="67" t="inlineStr"/>
+      <c r="L236" s="66" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="68" t="inlineStr">
+      <c r="A237" s="67" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -12364,7 +12341,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C237" s="76" t="inlineStr">
+      <c r="C237" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12401,10 +12378,10 @@
         </is>
       </c>
       <c r="K237" s="23" t="n"/>
-      <c r="L237" s="67" t="inlineStr"/>
+      <c r="L237" s="66" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="68" t="inlineStr">
+      <c r="A238" s="67" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -12414,7 +12391,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C238" s="76" t="inlineStr">
+      <c r="C238" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12451,10 +12428,10 @@
         </is>
       </c>
       <c r="K238" s="23" t="n"/>
-      <c r="L238" s="67" t="inlineStr"/>
+      <c r="L238" s="66" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="68" t="inlineStr">
+      <c r="A239" s="67" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -12464,7 +12441,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C239" s="76" t="inlineStr">
+      <c r="C239" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12501,16 +12478,16 @@
         </is>
       </c>
       <c r="K239" s="23" t="n"/>
-      <c r="L239" s="67" t="inlineStr"/>
+      <c r="L239" s="66" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="68" t="inlineStr">
+      <c r="A240" s="67" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="B240" s="23" t="inlineStr"/>
-      <c r="C240" s="78" t="inlineStr">
+      <c r="C240" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -12529,10 +12506,10 @@
       <c r="I240" s="65" t="inlineStr"/>
       <c r="J240" s="23" t="inlineStr"/>
       <c r="K240" s="23" t="n"/>
-      <c r="L240" s="67" t="inlineStr"/>
+      <c r="L240" s="66" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="68" t="inlineStr">
+      <c r="A241" s="67" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -12542,7 +12519,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C241" s="76" t="inlineStr">
+      <c r="C241" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12579,10 +12556,10 @@
         </is>
       </c>
       <c r="K241" s="23" t="n"/>
-      <c r="L241" s="67" t="inlineStr"/>
+      <c r="L241" s="66" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="68" t="inlineStr">
+      <c r="A242" s="67" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -12592,7 +12569,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C242" s="76" t="inlineStr">
+      <c r="C242" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12629,10 +12606,10 @@
         </is>
       </c>
       <c r="K242" s="23" t="n"/>
-      <c r="L242" s="67" t="inlineStr"/>
+      <c r="L242" s="66" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="68" t="inlineStr">
+      <c r="A243" s="67" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -12642,7 +12619,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C243" s="76" t="inlineStr">
+      <c r="C243" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12679,10 +12656,10 @@
         </is>
       </c>
       <c r="K243" s="23" t="n"/>
-      <c r="L243" s="67" t="inlineStr"/>
+      <c r="L243" s="66" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="68" t="inlineStr">
+      <c r="A244" s="67" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -12692,7 +12669,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C244" s="77" t="inlineStr">
+      <c r="C244" s="76" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -12729,16 +12706,16 @@
         </is>
       </c>
       <c r="K244" s="23" t="n"/>
-      <c r="L244" s="67" t="inlineStr"/>
+      <c r="L244" s="66" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="68" t="inlineStr">
+      <c r="A245" s="67" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
       </c>
       <c r="B245" s="23" t="inlineStr"/>
-      <c r="C245" s="76" t="inlineStr">
+      <c r="C245" s="75" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -12757,10 +12734,10 @@
       <c r="I245" s="65" t="inlineStr"/>
       <c r="J245" s="23" t="inlineStr"/>
       <c r="K245" s="23" t="n"/>
-      <c r="L245" s="67" t="inlineStr"/>
+      <c r="L245" s="66" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="68" t="inlineStr">
+      <c r="A246" s="67" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -12770,7 +12747,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C246" s="77" t="inlineStr">
+      <c r="C246" s="76" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -12807,10 +12784,10 @@
         </is>
       </c>
       <c r="K246" s="23" t="n"/>
-      <c r="L246" s="67" t="inlineStr"/>
+      <c r="L246" s="66" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="68" t="inlineStr">
+      <c r="A247" s="67" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -12820,7 +12797,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C247" s="78" t="inlineStr">
+      <c r="C247" s="77" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -12849,10 +12826,10 @@
       <c r="I247" s="65" t="inlineStr"/>
       <c r="J247" s="23" t="inlineStr"/>
       <c r="K247" s="23" t="n"/>
-      <c r="L247" s="67" t="inlineStr"/>
+      <c r="L247" s="66" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="68" t="inlineStr">
+      <c r="A248" s="67" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -12862,7 +12839,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C248" s="77" t="inlineStr">
+      <c r="C248" s="76" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -12899,10 +12876,10 @@
         </is>
       </c>
       <c r="K248" s="23" t="n"/>
-      <c r="L248" s="67" t="inlineStr"/>
+      <c r="L248" s="66" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="68" t="inlineStr">
+      <c r="A249" s="67" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -12912,7 +12889,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C249" s="77" t="inlineStr">
+      <c r="C249" s="76" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -12949,10 +12926,10 @@
         </is>
       </c>
       <c r="K249" s="23" t="n"/>
-      <c r="L249" s="67" t="inlineStr"/>
+      <c r="L249" s="66" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="68" t="inlineStr">
+      <c r="A250" s="67" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -12962,7 +12939,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C250" s="77" t="inlineStr">
+      <c r="C250" s="76" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -12999,10 +12976,10 @@
         </is>
       </c>
       <c r="K250" s="23" t="n"/>
-      <c r="L250" s="67" t="inlineStr"/>
+      <c r="L250" s="66" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="68" t="inlineStr">
+      <c r="A251" s="67" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -13012,7 +12989,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C251" s="77" t="inlineStr">
+      <c r="C251" s="76" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -13049,10 +13026,10 @@
         </is>
       </c>
       <c r="K251" s="23" t="n"/>
-      <c r="L251" s="67" t="inlineStr"/>
+      <c r="L251" s="66" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="68" t="inlineStr">
+      <c r="A252" s="67" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -13062,7 +13039,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C252" s="78" t="inlineStr">
+      <c r="C252" s="77" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -13099,10 +13076,10 @@
         </is>
       </c>
       <c r="K252" s="23" t="n"/>
-      <c r="L252" s="67" t="inlineStr"/>
+      <c r="L252" s="66" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="68" t="inlineStr">
+      <c r="A253" s="67" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -13112,7 +13089,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C253" s="78" t="inlineStr">
+      <c r="C253" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -13149,10 +13126,10 @@
         </is>
       </c>
       <c r="K253" s="23" t="n"/>
-      <c r="L253" s="67" t="inlineStr"/>
+      <c r="L253" s="66" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="68" t="inlineStr">
+      <c r="A254" s="67" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -13162,7 +13139,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C254" s="77" t="inlineStr">
+      <c r="C254" s="76" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13199,10 +13176,10 @@
         </is>
       </c>
       <c r="K254" s="23" t="n"/>
-      <c r="L254" s="67" t="inlineStr"/>
+      <c r="L254" s="66" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="68" t="inlineStr">
+      <c r="A255" s="67" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -13212,7 +13189,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C255" s="77" t="inlineStr">
+      <c r="C255" s="76" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -13249,10 +13226,10 @@
         </is>
       </c>
       <c r="K255" s="23" t="n"/>
-      <c r="L255" s="67" t="inlineStr"/>
+      <c r="L255" s="66" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="68" t="inlineStr">
+      <c r="A256" s="67" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -13262,7 +13239,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C256" s="78" t="inlineStr">
+      <c r="C256" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -13299,10 +13276,10 @@
         </is>
       </c>
       <c r="K256" s="23" t="n"/>
-      <c r="L256" s="67" t="inlineStr"/>
+      <c r="L256" s="66" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="68" t="inlineStr">
+      <c r="A257" s="67" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -13312,7 +13289,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C257" s="77" t="inlineStr">
+      <c r="C257" s="76" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -13349,10 +13326,10 @@
         </is>
       </c>
       <c r="K257" s="23" t="n"/>
-      <c r="L257" s="67" t="inlineStr"/>
+      <c r="L257" s="66" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="68" t="inlineStr">
+      <c r="A258" s="67" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -13362,7 +13339,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C258" s="76" t="inlineStr">
+      <c r="C258" s="75" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -13399,10 +13376,10 @@
         </is>
       </c>
       <c r="K258" s="23" t="n"/>
-      <c r="L258" s="67" t="inlineStr"/>
+      <c r="L258" s="66" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="68" t="inlineStr">
+      <c r="A259" s="67" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -13412,7 +13389,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C259" s="77" t="inlineStr">
+      <c r="C259" s="76" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -13449,10 +13426,10 @@
         </is>
       </c>
       <c r="K259" s="23" t="n"/>
-      <c r="L259" s="67" t="inlineStr"/>
+      <c r="L259" s="66" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="68" t="inlineStr">
+      <c r="A260" s="67" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -13462,7 +13439,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C260" s="77" t="inlineStr">
+      <c r="C260" s="76" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -13499,10 +13476,10 @@
         </is>
       </c>
       <c r="K260" s="23" t="n"/>
-      <c r="L260" s="67" t="inlineStr"/>
+      <c r="L260" s="66" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="68" t="inlineStr">
+      <c r="A261" s="67" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -13512,7 +13489,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C261" s="77" t="inlineStr">
+      <c r="C261" s="76" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -13549,10 +13526,10 @@
         </is>
       </c>
       <c r="K261" s="23" t="n"/>
-      <c r="L261" s="67" t="inlineStr"/>
+      <c r="L261" s="66" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="68" t="inlineStr">
+      <c r="A262" s="67" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -13562,7 +13539,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C262" s="76" t="inlineStr">
+      <c r="C262" s="75" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -13599,10 +13576,10 @@
         </is>
       </c>
       <c r="K262" s="23" t="n"/>
-      <c r="L262" s="67" t="inlineStr"/>
+      <c r="L262" s="66" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="68" t="inlineStr">
+      <c r="A263" s="67" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -13612,7 +13589,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C263" s="76" t="inlineStr">
+      <c r="C263" s="75" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -13649,10 +13626,10 @@
         </is>
       </c>
       <c r="K263" s="23" t="n"/>
-      <c r="L263" s="67" t="inlineStr"/>
+      <c r="L263" s="66" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="68" t="inlineStr">
+      <c r="A264" s="67" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -13662,7 +13639,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C264" s="76" t="inlineStr">
+      <c r="C264" s="75" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -13699,10 +13676,10 @@
         </is>
       </c>
       <c r="K264" s="23" t="n"/>
-      <c r="L264" s="67" t="inlineStr"/>
+      <c r="L264" s="66" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="68" t="inlineStr">
+      <c r="A265" s="67" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -13712,7 +13689,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C265" s="76" t="inlineStr">
+      <c r="C265" s="75" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -13749,10 +13726,10 @@
         </is>
       </c>
       <c r="K265" s="23" t="n"/>
-      <c r="L265" s="67" t="inlineStr"/>
+      <c r="L265" s="66" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="68" t="inlineStr">
+      <c r="A266" s="67" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -13762,7 +13739,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C266" s="76" t="inlineStr">
+      <c r="C266" s="75" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -13799,10 +13776,10 @@
         </is>
       </c>
       <c r="K266" s="23" t="n"/>
-      <c r="L266" s="67" t="inlineStr"/>
+      <c r="L266" s="66" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="68" t="inlineStr">
+      <c r="A267" s="67" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -13812,7 +13789,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C267" s="76" t="inlineStr">
+      <c r="C267" s="75" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -13849,10 +13826,10 @@
         </is>
       </c>
       <c r="K267" s="23" t="n"/>
-      <c r="L267" s="67" t="inlineStr"/>
+      <c r="L267" s="66" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="68" t="inlineStr">
+      <c r="A268" s="67" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -13862,7 +13839,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C268" s="76" t="inlineStr">
+      <c r="C268" s="75" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -13899,10 +13876,10 @@
         </is>
       </c>
       <c r="K268" s="23" t="n"/>
-      <c r="L268" s="67" t="inlineStr"/>
+      <c r="L268" s="66" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="68" t="inlineStr">
+      <c r="A269" s="67" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -13912,7 +13889,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C269" s="76" t="inlineStr">
+      <c r="C269" s="75" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -13949,10 +13926,10 @@
         </is>
       </c>
       <c r="K269" s="23" t="n"/>
-      <c r="L269" s="67" t="inlineStr"/>
+      <c r="L269" s="66" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="68" t="inlineStr">
+      <c r="A270" s="67" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -13962,7 +13939,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C270" s="76" t="inlineStr">
+      <c r="C270" s="75" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13999,10 +13976,10 @@
         </is>
       </c>
       <c r="K270" s="23" t="n"/>
-      <c r="L270" s="67" t="inlineStr"/>
+      <c r="L270" s="66" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="68" t="inlineStr">
+      <c r="A271" s="67" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -14012,7 +13989,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C271" s="76" t="inlineStr">
+      <c r="C271" s="75" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -14049,10 +14026,10 @@
         </is>
       </c>
       <c r="K271" s="23" t="n"/>
-      <c r="L271" s="67" t="inlineStr"/>
+      <c r="L271" s="66" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="68" t="inlineStr">
+      <c r="A272" s="67" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -14062,7 +14039,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C272" s="76" t="inlineStr">
+      <c r="C272" s="75" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -14099,10 +14076,10 @@
         </is>
       </c>
       <c r="K272" s="23" t="n"/>
-      <c r="L272" s="67" t="inlineStr"/>
+      <c r="L272" s="66" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="68" t="inlineStr">
+      <c r="A273" s="67" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -14112,7 +14089,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C273" s="76" t="inlineStr">
+      <c r="C273" s="75" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -14149,10 +14126,10 @@
         </is>
       </c>
       <c r="K273" s="23" t="n"/>
-      <c r="L273" s="67" t="inlineStr"/>
+      <c r="L273" s="66" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="68" t="inlineStr">
+      <c r="A274" s="67" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -14162,7 +14139,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C274" s="77" t="inlineStr">
+      <c r="C274" s="76" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -14199,10 +14176,10 @@
         </is>
       </c>
       <c r="K274" s="23" t="n"/>
-      <c r="L274" s="67" t="inlineStr"/>
+      <c r="L274" s="66" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="68" t="inlineStr">
+      <c r="A275" s="67" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -14212,7 +14189,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C275" s="76" t="inlineStr">
+      <c r="C275" s="75" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -14249,10 +14226,10 @@
         </is>
       </c>
       <c r="K275" s="23" t="n"/>
-      <c r="L275" s="67" t="inlineStr"/>
+      <c r="L275" s="66" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="68" t="inlineStr">
+      <c r="A276" s="67" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -14262,7 +14239,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C276" s="76" t="inlineStr">
+      <c r="C276" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14299,10 +14276,10 @@
         </is>
       </c>
       <c r="K276" s="23" t="n"/>
-      <c r="L276" s="67" t="inlineStr"/>
+      <c r="L276" s="66" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="68" t="inlineStr">
+      <c r="A277" s="67" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -14312,7 +14289,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C277" s="77" t="inlineStr">
+      <c r="C277" s="76" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -14349,10 +14326,10 @@
         </is>
       </c>
       <c r="K277" s="23" t="n"/>
-      <c r="L277" s="67" t="inlineStr"/>
+      <c r="L277" s="66" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="68" t="inlineStr">
+      <c r="A278" s="67" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -14362,7 +14339,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C278" s="76" t="inlineStr">
+      <c r="C278" s="75" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -14399,10 +14376,10 @@
         </is>
       </c>
       <c r="K278" s="23" t="n"/>
-      <c r="L278" s="67" t="inlineStr"/>
+      <c r="L278" s="66" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="68" t="inlineStr">
+      <c r="A279" s="67" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -14412,7 +14389,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C279" s="76" t="inlineStr">
+      <c r="C279" s="75" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -14449,10 +14426,10 @@
         </is>
       </c>
       <c r="K279" s="23" t="n"/>
-      <c r="L279" s="67" t="inlineStr"/>
+      <c r="L279" s="66" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="68" t="inlineStr">
+      <c r="A280" s="67" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -14462,7 +14439,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C280" s="76" t="inlineStr">
+      <c r="C280" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14499,10 +14476,10 @@
         </is>
       </c>
       <c r="K280" s="23" t="n"/>
-      <c r="L280" s="67" t="inlineStr"/>
+      <c r="L280" s="66" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="68" t="inlineStr">
+      <c r="A281" s="67" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -14512,7 +14489,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C281" s="78" t="inlineStr">
+      <c r="C281" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14549,10 +14526,10 @@
         </is>
       </c>
       <c r="K281" s="23" t="n"/>
-      <c r="L281" s="67" t="inlineStr"/>
+      <c r="L281" s="66" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="68" t="inlineStr">
+      <c r="A282" s="67" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -14562,7 +14539,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C282" s="76" t="inlineStr">
+      <c r="C282" s="75" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -14599,10 +14576,10 @@
         </is>
       </c>
       <c r="K282" s="23" t="n"/>
-      <c r="L282" s="67" t="inlineStr"/>
+      <c r="L282" s="66" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="68" t="inlineStr">
+      <c r="A283" s="67" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -14612,7 +14589,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C283" s="76" t="inlineStr">
+      <c r="C283" s="75" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -14649,10 +14626,10 @@
         </is>
       </c>
       <c r="K283" s="23" t="n"/>
-      <c r="L283" s="67" t="inlineStr"/>
+      <c r="L283" s="66" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="68" t="inlineStr">
+      <c r="A284" s="67" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -14662,7 +14639,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C284" s="78" t="inlineStr">
+      <c r="C284" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14699,10 +14676,10 @@
         </is>
       </c>
       <c r="K284" s="23" t="n"/>
-      <c r="L284" s="67" t="inlineStr"/>
+      <c r="L284" s="66" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="68" t="inlineStr">
+      <c r="A285" s="67" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -14712,7 +14689,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C285" s="78" t="inlineStr">
+      <c r="C285" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14749,10 +14726,10 @@
         </is>
       </c>
       <c r="K285" s="23" t="n"/>
-      <c r="L285" s="67" t="inlineStr"/>
+      <c r="L285" s="66" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="68" t="inlineStr">
+      <c r="A286" s="67" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -14762,7 +14739,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C286" s="78" t="inlineStr">
+      <c r="C286" s="77" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14799,10 +14776,10 @@
         </is>
       </c>
       <c r="K286" s="23" t="n"/>
-      <c r="L286" s="67" t="inlineStr"/>
+      <c r="L286" s="66" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="68" t="inlineStr">
+      <c r="A287" s="67" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -14812,7 +14789,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C287" s="76" t="inlineStr">
+      <c r="C287" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14849,10 +14826,10 @@
         </is>
       </c>
       <c r="K287" s="23" t="n"/>
-      <c r="L287" s="67" t="inlineStr"/>
+      <c r="L287" s="66" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="68" t="inlineStr">
+      <c r="A288" s="67" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -14862,7 +14839,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C288" s="76" t="inlineStr">
+      <c r="C288" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14899,10 +14876,10 @@
         </is>
       </c>
       <c r="K288" s="23" t="n"/>
-      <c r="L288" s="67" t="inlineStr"/>
+      <c r="L288" s="66" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="68" t="inlineStr">
+      <c r="A289" s="67" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -14912,7 +14889,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C289" s="76" t="inlineStr">
+      <c r="C289" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14949,10 +14926,10 @@
         </is>
       </c>
       <c r="K289" s="23" t="n"/>
-      <c r="L289" s="67" t="inlineStr"/>
+      <c r="L289" s="66" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="68" t="inlineStr">
+      <c r="A290" s="67" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -14962,7 +14939,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C290" s="76" t="inlineStr">
+      <c r="C290" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14999,10 +14976,10 @@
         </is>
       </c>
       <c r="K290" s="23" t="n"/>
-      <c r="L290" s="67" t="inlineStr"/>
+      <c r="L290" s="66" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="68" t="inlineStr">
+      <c r="A291" s="67" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -15012,7 +14989,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C291" s="76" t="inlineStr">
+      <c r="C291" s="75" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -15049,10 +15026,10 @@
         </is>
       </c>
       <c r="K291" s="23" t="n"/>
-      <c r="L291" s="67" t="inlineStr"/>
+      <c r="L291" s="66" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="68" t="inlineStr">
+      <c r="A292" s="67" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -15062,7 +15039,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C292" s="77" t="inlineStr">
+      <c r="C292" s="76" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -15099,7 +15076,7 @@
         </is>
       </c>
       <c r="K292" s="23" t="n"/>
-      <c r="L292" s="67" t="inlineStr"/>
+      <c r="L292" s="66" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L292"/>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -309,6 +309,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -512,9 +518,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,10 +527,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,16 +542,19 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,10 +564,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -573,21 +579,21 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,6 +683,9 @@
     <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -698,10 +707,10 @@
     <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -713,7 +722,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,7 +737,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -731,28 +746,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1160,17 +1175,17 @@
           <t>PS5 COMPLETION PLATFORM  |  BLOCKERS - sorted by blocking count</t>
         </is>
       </c>
-      <c r="B1" s="97" t="n"/>
-      <c r="C1" s="97" t="n"/>
-      <c r="D1" s="97" t="n"/>
-      <c r="E1" s="97" t="n"/>
-      <c r="F1" s="97" t="n"/>
-      <c r="G1" s="97" t="n"/>
-      <c r="H1" s="97" t="n"/>
-      <c r="I1" s="97" t="n"/>
-      <c r="J1" s="97" t="n"/>
-      <c r="K1" s="97" t="n"/>
-      <c r="L1" s="98" t="n"/>
+      <c r="B1" s="100" t="n"/>
+      <c r="C1" s="100" t="n"/>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="100" t="n"/>
+      <c r="G1" s="100" t="n"/>
+      <c r="H1" s="100" t="n"/>
+      <c r="I1" s="100" t="n"/>
+      <c r="J1" s="100" t="n"/>
+      <c r="K1" s="100" t="n"/>
+      <c r="L1" s="101" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1235,7 +1250,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -1245,7 +1260,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="75" t="inlineStr">
+      <c r="C3" s="76" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -1286,10 +1301,10 @@
         </is>
       </c>
       <c r="K3" s="23" t="n"/>
-      <c r="L3" s="66" t="inlineStr"/>
+      <c r="L3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -1299,7 +1314,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C4" s="75" t="inlineStr">
+      <c r="C4" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1336,10 +1351,10 @@
         </is>
       </c>
       <c r="K4" s="23" t="n"/>
-      <c r="L4" s="66" t="inlineStr"/>
+      <c r="L4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -1349,7 +1364,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C5" s="75" t="inlineStr">
+      <c r="C5" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1386,10 +1401,10 @@
         </is>
       </c>
       <c r="K5" s="23" t="n"/>
-      <c r="L5" s="66" t="inlineStr"/>
+      <c r="L5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -1399,7 +1414,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C6" s="75" t="inlineStr">
+      <c r="C6" s="76" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -1442,10 +1457,10 @@
         </is>
       </c>
       <c r="K6" s="23" t="n"/>
-      <c r="L6" s="66" t="inlineStr"/>
+      <c r="L6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -1455,7 +1470,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C7" s="76" t="inlineStr">
+      <c r="C7" s="77" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -1494,10 +1509,10 @@
         </is>
       </c>
       <c r="K7" s="23" t="n"/>
-      <c r="L7" s="66" t="inlineStr"/>
+      <c r="L7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -1507,7 +1522,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="75" t="inlineStr">
+      <c r="C8" s="76" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -1535,7 +1550,7 @@
       <c r="H8" s="65" t="inlineStr"/>
       <c r="I8" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -1544,10 +1559,10 @@
         </is>
       </c>
       <c r="K8" s="23" t="n"/>
-      <c r="L8" s="66" t="inlineStr"/>
+      <c r="L8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -1557,7 +1572,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C9" s="76" t="inlineStr">
+      <c r="C9" s="77" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -1594,10 +1609,10 @@
         </is>
       </c>
       <c r="K9" s="23" t="n"/>
-      <c r="L9" s="66" t="inlineStr"/>
+      <c r="L9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -1607,7 +1622,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C10" s="76" t="inlineStr">
+      <c r="C10" s="77" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -1664,10 +1679,10 @@
         </is>
       </c>
       <c r="K10" s="23" t="n"/>
-      <c r="L10" s="66" t="inlineStr"/>
+      <c r="L10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -1677,7 +1692,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C11" s="75" t="inlineStr">
+      <c r="C11" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1714,10 +1729,10 @@
         </is>
       </c>
       <c r="K11" s="23" t="n"/>
-      <c r="L11" s="66" t="inlineStr"/>
+      <c r="L11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -1727,7 +1742,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C12" s="75" t="inlineStr">
+      <c r="C12" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1764,10 +1779,10 @@
         </is>
       </c>
       <c r="K12" s="23" t="n"/>
-      <c r="L12" s="66" t="inlineStr"/>
+      <c r="L12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -1777,7 +1792,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C13" s="76" t="inlineStr">
+      <c r="C13" s="77" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -1816,10 +1831,10 @@
         </is>
       </c>
       <c r="K13" s="23" t="n"/>
-      <c r="L13" s="66" t="inlineStr"/>
+      <c r="L13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -1829,7 +1844,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C14" s="75" t="inlineStr">
+      <c r="C14" s="76" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -1858,10 +1873,10 @@
       <c r="I14" s="65" t="inlineStr"/>
       <c r="J14" s="23" t="inlineStr"/>
       <c r="K14" s="23" t="n"/>
-      <c r="L14" s="66" t="inlineStr"/>
+      <c r="L14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -1871,7 +1886,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C15" s="75" t="inlineStr">
+      <c r="C15" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1908,10 +1923,10 @@
         </is>
       </c>
       <c r="K15" s="23" t="n"/>
-      <c r="L15" s="66" t="inlineStr"/>
+      <c r="L15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -1921,7 +1936,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C16" s="77" t="inlineStr">
+      <c r="C16" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -1960,10 +1975,10 @@
         </is>
       </c>
       <c r="K16" s="23" t="n"/>
-      <c r="L16" s="66" t="inlineStr"/>
+      <c r="L16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="67" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -1973,7 +1988,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="76" t="inlineStr">
+      <c r="C17" s="77" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -2012,10 +2027,10 @@
         </is>
       </c>
       <c r="K17" s="23" t="n"/>
-      <c r="L17" s="66" t="inlineStr"/>
+      <c r="L17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="67" t="inlineStr">
+      <c r="A18" s="68" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -2025,7 +2040,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C18" s="77" t="inlineStr">
+      <c r="C18" s="78" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -2062,10 +2077,10 @@
         </is>
       </c>
       <c r="K18" s="23" t="n"/>
-      <c r="L18" s="66" t="inlineStr"/>
+      <c r="L18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="67" t="inlineStr">
+      <c r="A19" s="68" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -2075,7 +2090,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C19" s="75" t="inlineStr">
+      <c r="C19" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2112,10 +2127,10 @@
         </is>
       </c>
       <c r="K19" s="23" t="n"/>
-      <c r="L19" s="66" t="inlineStr"/>
+      <c r="L19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="67" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -2125,7 +2140,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C20" s="75" t="inlineStr">
+      <c r="C20" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2162,10 +2177,10 @@
         </is>
       </c>
       <c r="K20" s="23" t="n"/>
-      <c r="L20" s="66" t="inlineStr"/>
+      <c r="L20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="67" t="inlineStr">
+      <c r="A21" s="68" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -2175,7 +2190,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C21" s="75" t="inlineStr">
+      <c r="C21" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2212,10 +2227,10 @@
         </is>
       </c>
       <c r="K21" s="23" t="n"/>
-      <c r="L21" s="66" t="inlineStr"/>
+      <c r="L21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="67" t="inlineStr">
+      <c r="A22" s="68" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -2225,7 +2240,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C22" s="77" t="inlineStr">
+      <c r="C22" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2262,10 +2277,10 @@
         </is>
       </c>
       <c r="K22" s="23" t="n"/>
-      <c r="L22" s="66" t="inlineStr"/>
+      <c r="L22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="67" t="inlineStr">
+      <c r="A23" s="68" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -2275,7 +2290,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C23" s="77" t="inlineStr">
+      <c r="C23" s="78" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -2312,10 +2327,10 @@
         </is>
       </c>
       <c r="K23" s="23" t="n"/>
-      <c r="L23" s="66" t="inlineStr"/>
+      <c r="L23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="67" t="inlineStr">
+      <c r="A24" s="68" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -2325,7 +2340,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C24" s="75" t="inlineStr">
+      <c r="C24" s="76" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -2350,7 +2365,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H24" s="65" t="inlineStr"/>
+      <c r="H24" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I24" s="65" t="inlineStr">
         <is>
           <t>PS5-71-TW-0007, PS5-71-TW-0003, PS5-71-TW-0004, PS5-71-TW-0006 not arrived</t>
@@ -2362,10 +2381,10 @@
         </is>
       </c>
       <c r="K24" s="23" t="n"/>
-      <c r="L24" s="66" t="inlineStr"/>
+      <c r="L24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="67" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -2375,7 +2394,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C25" s="76" t="inlineStr">
+      <c r="C25" s="77" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -2416,10 +2435,10 @@
         </is>
       </c>
       <c r="K25" s="23" t="n"/>
-      <c r="L25" s="66" t="inlineStr"/>
+      <c r="L25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="67" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -2429,7 +2448,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C26" s="77" t="inlineStr">
+      <c r="C26" s="78" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -2468,10 +2487,10 @@
         </is>
       </c>
       <c r="K26" s="23" t="n"/>
-      <c r="L26" s="66" t="inlineStr"/>
+      <c r="L26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="67" t="inlineStr">
+      <c r="A27" s="68" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -2481,7 +2500,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C27" s="75" t="inlineStr">
+      <c r="C27" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2518,10 +2537,10 @@
         </is>
       </c>
       <c r="K27" s="23" t="n"/>
-      <c r="L27" s="66" t="inlineStr"/>
+      <c r="L27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="67" t="inlineStr">
+      <c r="A28" s="68" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -2531,7 +2550,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C28" s="75" t="inlineStr">
+      <c r="C28" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2568,10 +2587,10 @@
         </is>
       </c>
       <c r="K28" s="23" t="n"/>
-      <c r="L28" s="66" t="inlineStr"/>
+      <c r="L28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="67" t="inlineStr">
+      <c r="A29" s="68" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -2581,7 +2600,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C29" s="75" t="inlineStr">
+      <c r="C29" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2618,10 +2637,10 @@
         </is>
       </c>
       <c r="K29" s="23" t="n"/>
-      <c r="L29" s="66" t="inlineStr"/>
+      <c r="L29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="67" t="inlineStr">
+      <c r="A30" s="68" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -2631,7 +2650,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C30" s="76" t="inlineStr">
+      <c r="C30" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -2668,10 +2687,10 @@
         </is>
       </c>
       <c r="K30" s="23" t="n"/>
-      <c r="L30" s="66" t="inlineStr"/>
+      <c r="L30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="67" t="inlineStr">
+      <c r="A31" s="68" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -2681,7 +2700,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C31" s="76" t="inlineStr">
+      <c r="C31" s="77" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -2718,10 +2737,10 @@
         </is>
       </c>
       <c r="K31" s="23" t="n"/>
-      <c r="L31" s="66" t="inlineStr"/>
+      <c r="L31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="67" t="inlineStr">
+      <c r="A32" s="68" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -2731,7 +2750,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C32" s="76" t="inlineStr">
+      <c r="C32" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -2760,10 +2779,10 @@
       <c r="I32" s="65" t="inlineStr"/>
       <c r="J32" s="23" t="inlineStr"/>
       <c r="K32" s="23" t="n"/>
-      <c r="L32" s="66" t="inlineStr"/>
+      <c r="L32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="67" t="inlineStr">
+      <c r="A33" s="68" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -2773,7 +2792,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C33" s="77" t="inlineStr">
+      <c r="C33" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -2812,10 +2831,10 @@
         </is>
       </c>
       <c r="K33" s="23" t="n"/>
-      <c r="L33" s="66" t="inlineStr"/>
+      <c r="L33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="67" t="inlineStr">
+      <c r="A34" s="68" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -2825,7 +2844,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C34" s="77" t="inlineStr">
+      <c r="C34" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -2862,10 +2881,10 @@
         </is>
       </c>
       <c r="K34" s="23" t="n"/>
-      <c r="L34" s="66" t="inlineStr"/>
+      <c r="L34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="67" t="inlineStr">
+      <c r="A35" s="68" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -2875,7 +2894,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C35" s="76" t="inlineStr">
+      <c r="C35" s="77" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -2912,10 +2931,10 @@
         </is>
       </c>
       <c r="K35" s="23" t="n"/>
-      <c r="L35" s="66" t="inlineStr"/>
+      <c r="L35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="67" t="inlineStr">
+      <c r="A36" s="68" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -2925,7 +2944,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C36" s="77" t="inlineStr">
+      <c r="C36" s="78" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -2954,10 +2973,10 @@
       <c r="I36" s="65" t="inlineStr"/>
       <c r="J36" s="23" t="inlineStr"/>
       <c r="K36" s="23" t="n"/>
-      <c r="L36" s="66" t="inlineStr"/>
+      <c r="L36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="67" t="inlineStr">
+      <c r="A37" s="68" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -2967,7 +2986,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C37" s="77" t="inlineStr">
+      <c r="C37" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -3004,10 +3023,10 @@
         </is>
       </c>
       <c r="K37" s="23" t="n"/>
-      <c r="L37" s="66" t="inlineStr"/>
+      <c r="L37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="A38" s="68" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -3017,7 +3036,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C38" s="76" t="inlineStr">
+      <c r="C38" s="77" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -3056,10 +3075,10 @@
         </is>
       </c>
       <c r="K38" s="23" t="n"/>
-      <c r="L38" s="66" t="inlineStr"/>
+      <c r="L38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="67" t="inlineStr">
+      <c r="A39" s="68" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -3069,7 +3088,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C39" s="76" t="inlineStr">
+      <c r="C39" s="77" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -3106,10 +3125,10 @@
         </is>
       </c>
       <c r="K39" s="23" t="n"/>
-      <c r="L39" s="66" t="inlineStr"/>
+      <c r="L39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="67" t="inlineStr">
+      <c r="A40" s="68" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -3119,7 +3138,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C40" s="77" t="inlineStr">
+      <c r="C40" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -3147,19 +3166,19 @@
       <c r="H40" s="65" t="inlineStr"/>
       <c r="I40" s="65" t="inlineStr">
         <is>
+          <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
-        </is>
-      </c>
       <c r="K40" s="23" t="n"/>
-      <c r="L40" s="66" t="inlineStr"/>
+      <c r="L40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="67" t="inlineStr">
+      <c r="A41" s="68" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -3169,7 +3188,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C41" s="77" t="inlineStr">
+      <c r="C41" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -3206,10 +3225,10 @@
         </is>
       </c>
       <c r="K41" s="23" t="n"/>
-      <c r="L41" s="66" t="inlineStr"/>
+      <c r="L41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="67" t="inlineStr">
+      <c r="A42" s="68" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -3219,7 +3238,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C42" s="77" t="inlineStr">
+      <c r="C42" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3248,10 +3267,10 @@
       <c r="I42" s="65" t="inlineStr"/>
       <c r="J42" s="23" t="inlineStr"/>
       <c r="K42" s="23" t="n"/>
-      <c r="L42" s="66" t="inlineStr"/>
+      <c r="L42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="67" t="inlineStr">
+      <c r="A43" s="68" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -3261,7 +3280,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C43" s="77" t="inlineStr">
+      <c r="C43" s="78" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -3300,10 +3319,10 @@
         </is>
       </c>
       <c r="K43" s="23" t="n"/>
-      <c r="L43" s="66" t="inlineStr"/>
+      <c r="L43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="67" t="inlineStr">
+      <c r="A44" s="68" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -3313,7 +3332,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C44" s="77" t="inlineStr">
+      <c r="C44" s="78" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3350,10 +3369,10 @@
         </is>
       </c>
       <c r="K44" s="23" t="n"/>
-      <c r="L44" s="66" t="inlineStr"/>
+      <c r="L44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="67" t="inlineStr">
+      <c r="A45" s="68" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -3363,7 +3382,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C45" s="77" t="inlineStr">
+      <c r="C45" s="78" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3400,10 +3419,10 @@
         </is>
       </c>
       <c r="K45" s="23" t="n"/>
-      <c r="L45" s="66" t="inlineStr"/>
+      <c r="L45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="67" t="inlineStr">
+      <c r="A46" s="68" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -3413,7 +3432,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C46" s="77" t="inlineStr">
+      <c r="C46" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3442,10 +3461,10 @@
       <c r="I46" s="65" t="inlineStr"/>
       <c r="J46" s="23" t="inlineStr"/>
       <c r="K46" s="23" t="n"/>
-      <c r="L46" s="66" t="inlineStr"/>
+      <c r="L46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="67" t="inlineStr">
+      <c r="A47" s="68" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -3455,7 +3474,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C47" s="77" t="inlineStr">
+      <c r="C47" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3484,10 +3503,10 @@
       <c r="I47" s="65" t="inlineStr"/>
       <c r="J47" s="23" t="inlineStr"/>
       <c r="K47" s="23" t="n"/>
-      <c r="L47" s="66" t="inlineStr"/>
+      <c r="L47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="67" t="inlineStr">
+      <c r="A48" s="68" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -3497,7 +3516,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C48" s="77" t="inlineStr">
+      <c r="C48" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3526,10 +3545,10 @@
       <c r="I48" s="65" t="inlineStr"/>
       <c r="J48" s="23" t="inlineStr"/>
       <c r="K48" s="23" t="n"/>
-      <c r="L48" s="66" t="inlineStr"/>
+      <c r="L48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="67" t="inlineStr">
+      <c r="A49" s="68" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -3539,7 +3558,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C49" s="77" t="inlineStr">
+      <c r="C49" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -3568,10 +3587,10 @@
       <c r="I49" s="65" t="inlineStr"/>
       <c r="J49" s="23" t="inlineStr"/>
       <c r="K49" s="23" t="n"/>
-      <c r="L49" s="66" t="inlineStr"/>
+      <c r="L49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="67" t="inlineStr">
+      <c r="A50" s="68" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -3581,7 +3600,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C50" s="76" t="inlineStr">
+      <c r="C50" s="77" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -3618,35 +3637,35 @@
         </is>
       </c>
       <c r="K50" s="23" t="n"/>
-      <c r="L50" s="66" t="inlineStr"/>
+      <c r="L50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="67" t="inlineStr">
+      <c r="A51" s="79" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="66" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="C51" s="77" t="inlineStr">
+      <c r="C51" s="80" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
+      <c r="D51" s="66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E51" s="66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" s="66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3662,16 +3681,16 @@
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="J51" s="23" t="inlineStr">
+      <c r="J51" s="66" t="inlineStr">
         <is>
           <t>Hydraulic tubing could not be connected in HPU due to Fittings/socket issues</t>
         </is>
       </c>
-      <c r="K51" s="23" t="n"/>
-      <c r="L51" s="66" t="inlineStr"/>
+      <c r="K51" s="66" t="n"/>
+      <c r="L51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="67" t="inlineStr">
+      <c r="A52" s="68" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -3681,7 +3700,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C52" s="76" t="inlineStr">
+      <c r="C52" s="77" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -3718,10 +3737,10 @@
         </is>
       </c>
       <c r="K52" s="23" t="n"/>
-      <c r="L52" s="66" t="inlineStr"/>
+      <c r="L52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="67" t="inlineStr">
+      <c r="A53" s="68" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -3731,7 +3750,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C53" s="77" t="inlineStr">
+      <c r="C53" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3768,10 +3787,10 @@
         </is>
       </c>
       <c r="K53" s="23" t="n"/>
-      <c r="L53" s="66" t="inlineStr"/>
+      <c r="L53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="67" t="inlineStr">
+      <c r="A54" s="68" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -3781,7 +3800,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C54" s="77" t="inlineStr">
+      <c r="C54" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -3810,10 +3829,10 @@
       <c r="I54" s="65" t="inlineStr"/>
       <c r="J54" s="23" t="inlineStr"/>
       <c r="K54" s="23" t="n"/>
-      <c r="L54" s="66" t="inlineStr"/>
+      <c r="L54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="67" t="inlineStr">
+      <c r="A55" s="68" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -3823,7 +3842,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C55" s="76" t="inlineStr">
+      <c r="C55" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -3852,10 +3871,10 @@
       <c r="I55" s="65" t="inlineStr"/>
       <c r="J55" s="23" t="inlineStr"/>
       <c r="K55" s="23" t="n"/>
-      <c r="L55" s="66" t="inlineStr"/>
+      <c r="L55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="67" t="inlineStr">
+      <c r="A56" s="68" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -3865,7 +3884,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C56" s="77" t="inlineStr">
+      <c r="C56" s="78" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -3894,10 +3913,10 @@
       <c r="I56" s="65" t="inlineStr"/>
       <c r="J56" s="23" t="inlineStr"/>
       <c r="K56" s="23" t="n"/>
-      <c r="L56" s="66" t="inlineStr"/>
+      <c r="L56" s="67" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="67" t="inlineStr">
+      <c r="A57" s="68" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -3907,7 +3926,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C57" s="76" t="inlineStr">
+      <c r="C57" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -3936,10 +3955,10 @@
       <c r="I57" s="65" t="inlineStr"/>
       <c r="J57" s="23" t="inlineStr"/>
       <c r="K57" s="23" t="n"/>
-      <c r="L57" s="66" t="inlineStr"/>
+      <c r="L57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="67" t="inlineStr">
+      <c r="A58" s="68" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -3949,7 +3968,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C58" s="77" t="inlineStr">
+      <c r="C58" s="78" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -3986,10 +4005,10 @@
         </is>
       </c>
       <c r="K58" s="23" t="n"/>
-      <c r="L58" s="66" t="inlineStr"/>
+      <c r="L58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="67" t="inlineStr">
+      <c r="A59" s="68" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -3999,7 +4018,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C59" s="77" t="inlineStr">
+      <c r="C59" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4028,10 +4047,10 @@
       <c r="I59" s="65" t="inlineStr"/>
       <c r="J59" s="23" t="inlineStr"/>
       <c r="K59" s="23" t="n"/>
-      <c r="L59" s="66" t="inlineStr"/>
+      <c r="L59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="67" t="inlineStr">
+      <c r="A60" s="68" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -4041,7 +4060,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C60" s="77" t="inlineStr">
+      <c r="C60" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4070,10 +4089,10 @@
       <c r="I60" s="65" t="inlineStr"/>
       <c r="J60" s="23" t="inlineStr"/>
       <c r="K60" s="23" t="n"/>
-      <c r="L60" s="66" t="inlineStr"/>
+      <c r="L60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="67" t="inlineStr">
+      <c r="A61" s="68" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -4083,7 +4102,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C61" s="76" t="inlineStr">
+      <c r="C61" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -4120,10 +4139,10 @@
         </is>
       </c>
       <c r="K61" s="23" t="n"/>
-      <c r="L61" s="66" t="inlineStr"/>
+      <c r="L61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="67" t="inlineStr">
+      <c r="A62" s="68" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -4133,7 +4152,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C62" s="76" t="inlineStr">
+      <c r="C62" s="77" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -4170,10 +4189,10 @@
         </is>
       </c>
       <c r="K62" s="23" t="n"/>
-      <c r="L62" s="66" t="inlineStr"/>
+      <c r="L62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="67" t="inlineStr">
+      <c r="A63" s="68" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -4183,7 +4202,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C63" s="77" t="inlineStr">
+      <c r="C63" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4210,12 +4229,16 @@
       </c>
       <c r="H63" s="65" t="inlineStr"/>
       <c r="I63" s="65" t="inlineStr"/>
-      <c r="J63" s="23" t="inlineStr"/>
+      <c r="J63" s="23" t="inlineStr">
+        <is>
+          <t>OBSERVATION -CLEANING ON PROGRESS</t>
+        </is>
+      </c>
       <c r="K63" s="23" t="n"/>
-      <c r="L63" s="66" t="inlineStr"/>
+      <c r="L63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="67" t="inlineStr">
+      <c r="A64" s="68" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -4225,7 +4248,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C64" s="77" t="inlineStr">
+      <c r="C64" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -4254,10 +4277,10 @@
       <c r="I64" s="65" t="inlineStr"/>
       <c r="J64" s="23" t="inlineStr"/>
       <c r="K64" s="23" t="n"/>
-      <c r="L64" s="66" t="inlineStr"/>
+      <c r="L64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="67" t="inlineStr">
+      <c r="A65" s="68" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -4267,7 +4290,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C65" s="77" t="inlineStr">
+      <c r="C65" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -4304,10 +4327,10 @@
         </is>
       </c>
       <c r="K65" s="23" t="n"/>
-      <c r="L65" s="66" t="inlineStr"/>
+      <c r="L65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="67" t="inlineStr">
+      <c r="A66" s="68" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -4317,7 +4340,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C66" s="77" t="inlineStr">
+      <c r="C66" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -4354,10 +4377,10 @@
         </is>
       </c>
       <c r="K66" s="23" t="n"/>
-      <c r="L66" s="66" t="inlineStr"/>
+      <c r="L66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="67" t="inlineStr">
+      <c r="A67" s="68" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -4367,7 +4390,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C67" s="77" t="inlineStr">
+      <c r="C67" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4404,10 +4427,10 @@
         </is>
       </c>
       <c r="K67" s="23" t="n"/>
-      <c r="L67" s="66" t="inlineStr"/>
+      <c r="L67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="67" t="inlineStr">
+      <c r="A68" s="68" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -4417,7 +4440,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C68" s="77" t="inlineStr">
+      <c r="C68" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4454,10 +4477,10 @@
         </is>
       </c>
       <c r="K68" s="23" t="n"/>
-      <c r="L68" s="66" t="inlineStr"/>
+      <c r="L68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="67" t="inlineStr">
+      <c r="A69" s="68" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -4467,7 +4490,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C69" s="77" t="inlineStr">
+      <c r="C69" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -4504,10 +4527,10 @@
         </is>
       </c>
       <c r="K69" s="23" t="n"/>
-      <c r="L69" s="66" t="inlineStr"/>
+      <c r="L69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="67" t="inlineStr">
+      <c r="A70" s="68" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -4517,7 +4540,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C70" s="77" t="inlineStr">
+      <c r="C70" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4554,10 +4577,10 @@
         </is>
       </c>
       <c r="K70" s="23" t="n"/>
-      <c r="L70" s="66" t="inlineStr"/>
+      <c r="L70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="67" t="inlineStr">
+      <c r="A71" s="68" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -4567,7 +4590,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C71" s="76" t="inlineStr">
+      <c r="C71" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -4604,10 +4627,10 @@
         </is>
       </c>
       <c r="K71" s="23" t="n"/>
-      <c r="L71" s="66" t="inlineStr"/>
+      <c r="L71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="67" t="inlineStr">
+      <c r="A72" s="68" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -4617,7 +4640,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C72" s="76" t="inlineStr">
+      <c r="C72" s="77" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -4654,10 +4677,10 @@
         </is>
       </c>
       <c r="K72" s="23" t="n"/>
-      <c r="L72" s="66" t="inlineStr"/>
+      <c r="L72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="67" t="inlineStr">
+      <c r="A73" s="68" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -4667,7 +4690,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C73" s="77" t="inlineStr">
+      <c r="C73" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4704,10 +4727,10 @@
         </is>
       </c>
       <c r="K73" s="23" t="n"/>
-      <c r="L73" s="66" t="inlineStr"/>
+      <c r="L73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="67" t="inlineStr">
+      <c r="A74" s="68" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -4717,7 +4740,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C74" s="75" t="inlineStr">
+      <c r="C74" s="76" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -4754,10 +4777,10 @@
         </is>
       </c>
       <c r="K74" s="23" t="n"/>
-      <c r="L74" s="66" t="inlineStr"/>
+      <c r="L74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="67" t="inlineStr">
+      <c r="A75" s="68" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -4767,7 +4790,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C75" s="75" t="inlineStr">
+      <c r="C75" s="76" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -4804,10 +4827,10 @@
         </is>
       </c>
       <c r="K75" s="23" t="n"/>
-      <c r="L75" s="66" t="inlineStr"/>
+      <c r="L75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="67" t="inlineStr">
+      <c r="A76" s="68" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -4817,7 +4840,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C76" s="77" t="inlineStr">
+      <c r="C76" s="78" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -4854,10 +4877,10 @@
         </is>
       </c>
       <c r="K76" s="23" t="n"/>
-      <c r="L76" s="66" t="inlineStr"/>
+      <c r="L76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="67" t="inlineStr">
+      <c r="A77" s="68" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -4867,7 +4890,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C77" s="75" t="inlineStr">
+      <c r="C77" s="76" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -4904,10 +4927,10 @@
         </is>
       </c>
       <c r="K77" s="23" t="n"/>
-      <c r="L77" s="66" t="inlineStr"/>
+      <c r="L77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="67" t="inlineStr">
+      <c r="A78" s="68" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -4917,7 +4940,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C78" s="77" t="inlineStr">
+      <c r="C78" s="78" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -4954,10 +4977,10 @@
         </is>
       </c>
       <c r="K78" s="23" t="n"/>
-      <c r="L78" s="66" t="inlineStr"/>
+      <c r="L78" s="67" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="67" t="inlineStr">
+      <c r="A79" s="68" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -4967,7 +4990,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C79" s="77" t="inlineStr">
+      <c r="C79" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -5004,10 +5027,10 @@
         </is>
       </c>
       <c r="K79" s="23" t="n"/>
-      <c r="L79" s="66" t="inlineStr"/>
+      <c r="L79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="67" t="inlineStr">
+      <c r="A80" s="68" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -5017,7 +5040,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C80" s="77" t="inlineStr">
+      <c r="C80" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5054,10 +5077,10 @@
         </is>
       </c>
       <c r="K80" s="23" t="n"/>
-      <c r="L80" s="66" t="inlineStr"/>
+      <c r="L80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="67" t="inlineStr">
+      <c r="A81" s="68" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -5067,7 +5090,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C81" s="77" t="inlineStr">
+      <c r="C81" s="78" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -5104,10 +5127,10 @@
         </is>
       </c>
       <c r="K81" s="23" t="n"/>
-      <c r="L81" s="66" t="inlineStr"/>
+      <c r="L81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="67" t="inlineStr">
+      <c r="A82" s="68" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -5117,7 +5140,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C82" s="77" t="inlineStr">
+      <c r="C82" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5154,10 +5177,10 @@
         </is>
       </c>
       <c r="K82" s="23" t="n"/>
-      <c r="L82" s="66" t="inlineStr"/>
+      <c r="L82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="67" t="inlineStr">
+      <c r="A83" s="68" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -5167,7 +5190,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C83" s="77" t="inlineStr">
+      <c r="C83" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5200,10 +5223,10 @@
       <c r="I83" s="65" t="inlineStr"/>
       <c r="J83" s="23" t="inlineStr"/>
       <c r="K83" s="23" t="n"/>
-      <c r="L83" s="66" t="inlineStr"/>
+      <c r="L83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="67" t="inlineStr">
+      <c r="A84" s="68" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -5213,7 +5236,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C84" s="77" t="inlineStr">
+      <c r="C84" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5250,10 +5273,10 @@
         </is>
       </c>
       <c r="K84" s="23" t="n"/>
-      <c r="L84" s="66" t="inlineStr"/>
+      <c r="L84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="67" t="inlineStr">
+      <c r="A85" s="68" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -5263,7 +5286,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C85" s="77" t="inlineStr">
+      <c r="C85" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5300,10 +5323,10 @@
         </is>
       </c>
       <c r="K85" s="23" t="n"/>
-      <c r="L85" s="66" t="inlineStr"/>
+      <c r="L85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="67" t="inlineStr">
+      <c r="A86" s="68" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -5313,7 +5336,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C86" s="75" t="inlineStr">
+      <c r="C86" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5352,16 +5375,16 @@
         </is>
       </c>
       <c r="K86" s="23" t="n"/>
-      <c r="L86" s="66" t="inlineStr"/>
+      <c r="L86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="67" t="inlineStr">
+      <c r="A87" s="68" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
       </c>
       <c r="B87" s="23" t="inlineStr"/>
-      <c r="C87" s="77" t="inlineStr">
+      <c r="C87" s="78" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -5380,16 +5403,16 @@
       <c r="I87" s="65" t="inlineStr"/>
       <c r="J87" s="23" t="inlineStr"/>
       <c r="K87" s="23" t="n"/>
-      <c r="L87" s="66" t="inlineStr"/>
+      <c r="L87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="67" t="inlineStr">
+      <c r="A88" s="68" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
       </c>
       <c r="B88" s="23" t="inlineStr"/>
-      <c r="C88" s="75" t="inlineStr">
+      <c r="C88" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5408,10 +5431,10 @@
       <c r="I88" s="65" t="inlineStr"/>
       <c r="J88" s="23" t="inlineStr"/>
       <c r="K88" s="23" t="n"/>
-      <c r="L88" s="66" t="inlineStr"/>
+      <c r="L88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="67" t="inlineStr">
+      <c r="A89" s="68" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -5421,7 +5444,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C89" s="75" t="inlineStr">
+      <c r="C89" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5458,16 +5481,16 @@
         </is>
       </c>
       <c r="K89" s="23" t="n"/>
-      <c r="L89" s="66" t="inlineStr"/>
+      <c r="L89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="67" t="inlineStr">
+      <c r="A90" s="68" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
       </c>
       <c r="B90" s="23" t="inlineStr"/>
-      <c r="C90" s="77" t="inlineStr">
+      <c r="C90" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -5486,16 +5509,16 @@
       <c r="I90" s="65" t="inlineStr"/>
       <c r="J90" s="23" t="inlineStr"/>
       <c r="K90" s="23" t="n"/>
-      <c r="L90" s="66" t="inlineStr"/>
+      <c r="L90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="67" t="inlineStr">
+      <c r="A91" s="68" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
       </c>
       <c r="B91" s="23" t="inlineStr"/>
-      <c r="C91" s="77" t="inlineStr">
+      <c r="C91" s="78" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -5514,16 +5537,16 @@
       <c r="I91" s="65" t="inlineStr"/>
       <c r="J91" s="23" t="inlineStr"/>
       <c r="K91" s="23" t="n"/>
-      <c r="L91" s="66" t="inlineStr"/>
+      <c r="L91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="67" t="inlineStr">
+      <c r="A92" s="68" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
       </c>
       <c r="B92" s="23" t="inlineStr"/>
-      <c r="C92" s="76" t="inlineStr">
+      <c r="C92" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -5542,10 +5565,10 @@
       <c r="I92" s="65" t="inlineStr"/>
       <c r="J92" s="23" t="inlineStr"/>
       <c r="K92" s="23" t="n"/>
-      <c r="L92" s="66" t="inlineStr"/>
+      <c r="L92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="67" t="inlineStr">
+      <c r="A93" s="68" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -5555,7 +5578,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C93" s="77" t="inlineStr">
+      <c r="C93" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5592,10 +5615,10 @@
         </is>
       </c>
       <c r="K93" s="23" t="n"/>
-      <c r="L93" s="66" t="inlineStr"/>
+      <c r="L93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="67" t="inlineStr">
+      <c r="A94" s="68" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -5605,7 +5628,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C94" s="77" t="inlineStr">
+      <c r="C94" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5642,16 +5665,16 @@
         </is>
       </c>
       <c r="K94" s="23" t="n"/>
-      <c r="L94" s="66" t="inlineStr"/>
+      <c r="L94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="67" t="inlineStr">
+      <c r="A95" s="68" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
       </c>
       <c r="B95" s="23" t="inlineStr"/>
-      <c r="C95" s="76" t="inlineStr">
+      <c r="C95" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -5670,10 +5693,10 @@
       <c r="I95" s="65" t="inlineStr"/>
       <c r="J95" s="23" t="inlineStr"/>
       <c r="K95" s="23" t="n"/>
-      <c r="L95" s="66" t="inlineStr"/>
+      <c r="L95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="67" t="inlineStr">
+      <c r="A96" s="68" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -5683,7 +5706,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C96" s="77" t="inlineStr">
+      <c r="C96" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5720,10 +5743,10 @@
         </is>
       </c>
       <c r="K96" s="23" t="n"/>
-      <c r="L96" s="66" t="inlineStr"/>
+      <c r="L96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="67" t="inlineStr">
+      <c r="A97" s="68" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -5733,7 +5756,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C97" s="75" t="inlineStr">
+      <c r="C97" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5770,10 +5793,10 @@
         </is>
       </c>
       <c r="K97" s="23" t="n"/>
-      <c r="L97" s="66" t="inlineStr"/>
+      <c r="L97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="67" t="inlineStr">
+      <c r="A98" s="68" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -5783,7 +5806,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C98" s="75" t="inlineStr">
+      <c r="C98" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5820,10 +5843,10 @@
         </is>
       </c>
       <c r="K98" s="23" t="n"/>
-      <c r="L98" s="66" t="inlineStr"/>
+      <c r="L98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="67" t="inlineStr">
+      <c r="A99" s="68" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -5833,7 +5856,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C99" s="75" t="inlineStr">
+      <c r="C99" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5870,10 +5893,10 @@
         </is>
       </c>
       <c r="K99" s="23" t="n"/>
-      <c r="L99" s="66" t="inlineStr"/>
+      <c r="L99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="67" t="inlineStr">
+      <c r="A100" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -5883,7 +5906,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C100" s="75" t="inlineStr">
+      <c r="C100" s="76" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -5920,10 +5943,10 @@
         </is>
       </c>
       <c r="K100" s="23" t="n"/>
-      <c r="L100" s="66" t="inlineStr"/>
+      <c r="L100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="67" t="inlineStr">
+      <c r="A101" s="68" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -5933,7 +5956,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C101" s="75" t="inlineStr">
+      <c r="C101" s="76" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -5970,16 +5993,16 @@
         </is>
       </c>
       <c r="K101" s="23" t="n"/>
-      <c r="L101" s="66" t="inlineStr"/>
+      <c r="L101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="67" t="inlineStr">
+      <c r="A102" s="68" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
       </c>
       <c r="B102" s="23" t="inlineStr"/>
-      <c r="C102" s="75" t="inlineStr">
+      <c r="C102" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5998,16 +6021,16 @@
       <c r="I102" s="65" t="inlineStr"/>
       <c r="J102" s="23" t="inlineStr"/>
       <c r="K102" s="23" t="n"/>
-      <c r="L102" s="66" t="inlineStr"/>
+      <c r="L102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="67" t="inlineStr">
+      <c r="A103" s="68" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
       </c>
       <c r="B103" s="23" t="inlineStr"/>
-      <c r="C103" s="75" t="inlineStr">
+      <c r="C103" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6026,10 +6049,10 @@
       <c r="I103" s="65" t="inlineStr"/>
       <c r="J103" s="23" t="inlineStr"/>
       <c r="K103" s="23" t="n"/>
-      <c r="L103" s="66" t="inlineStr"/>
+      <c r="L103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="67" t="inlineStr">
+      <c r="A104" s="68" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -6039,7 +6062,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C104" s="75" t="inlineStr">
+      <c r="C104" s="76" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6076,10 +6099,10 @@
         </is>
       </c>
       <c r="K104" s="23" t="n"/>
-      <c r="L104" s="66" t="inlineStr"/>
+      <c r="L104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="67" t="inlineStr">
+      <c r="A105" s="68" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -6089,7 +6112,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C105" s="75" t="inlineStr">
+      <c r="C105" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6126,10 +6149,10 @@
         </is>
       </c>
       <c r="K105" s="23" t="n"/>
-      <c r="L105" s="66" t="inlineStr"/>
+      <c r="L105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="67" t="inlineStr">
+      <c r="A106" s="68" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -6139,7 +6162,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C106" s="75" t="inlineStr">
+      <c r="C106" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6176,10 +6199,10 @@
         </is>
       </c>
       <c r="K106" s="23" t="n"/>
-      <c r="L106" s="66" t="inlineStr"/>
+      <c r="L106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="67" t="inlineStr">
+      <c r="A107" s="68" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -6189,7 +6212,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C107" s="75" t="inlineStr">
+      <c r="C107" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6226,10 +6249,10 @@
         </is>
       </c>
       <c r="K107" s="23" t="n"/>
-      <c r="L107" s="66" t="inlineStr"/>
+      <c r="L107" s="67" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="67" t="inlineStr">
+      <c r="A108" s="68" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -6239,7 +6262,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C108" s="75" t="inlineStr">
+      <c r="C108" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6276,10 +6299,10 @@
         </is>
       </c>
       <c r="K108" s="23" t="n"/>
-      <c r="L108" s="66" t="inlineStr"/>
+      <c r="L108" s="67" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="67" t="inlineStr">
+      <c r="A109" s="68" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -6289,7 +6312,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C109" s="75" t="inlineStr">
+      <c r="C109" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6326,10 +6349,10 @@
         </is>
       </c>
       <c r="K109" s="23" t="n"/>
-      <c r="L109" s="66" t="inlineStr"/>
+      <c r="L109" s="67" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="67" t="inlineStr">
+      <c r="A110" s="68" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -6339,7 +6362,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C110" s="75" t="inlineStr">
+      <c r="C110" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6376,16 +6399,16 @@
         </is>
       </c>
       <c r="K110" s="23" t="n"/>
-      <c r="L110" s="66" t="inlineStr"/>
+      <c r="L110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="67" t="inlineStr">
+      <c r="A111" s="68" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
       </c>
       <c r="B111" s="23" t="inlineStr"/>
-      <c r="C111" s="76" t="inlineStr">
+      <c r="C111" s="77" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -6404,10 +6427,10 @@
       <c r="I111" s="65" t="inlineStr"/>
       <c r="J111" s="23" t="inlineStr"/>
       <c r="K111" s="23" t="n"/>
-      <c r="L111" s="66" t="inlineStr"/>
+      <c r="L111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="67" t="inlineStr">
+      <c r="A112" s="68" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -6417,7 +6440,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C112" s="75" t="inlineStr">
+      <c r="C112" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6454,10 +6477,10 @@
         </is>
       </c>
       <c r="K112" s="23" t="n"/>
-      <c r="L112" s="66" t="inlineStr"/>
+      <c r="L112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="67" t="inlineStr">
+      <c r="A113" s="68" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -6467,7 +6490,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C113" s="75" t="inlineStr">
+      <c r="C113" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6504,10 +6527,10 @@
         </is>
       </c>
       <c r="K113" s="23" t="n"/>
-      <c r="L113" s="66" t="inlineStr"/>
+      <c r="L113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="67" t="inlineStr">
+      <c r="A114" s="68" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -6517,7 +6540,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C114" s="75" t="inlineStr">
+      <c r="C114" s="76" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -6554,16 +6577,16 @@
         </is>
       </c>
       <c r="K114" s="23" t="n"/>
-      <c r="L114" s="66" t="inlineStr"/>
+      <c r="L114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="67" t="inlineStr">
+      <c r="A115" s="68" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
       </c>
       <c r="B115" s="23" t="inlineStr"/>
-      <c r="C115" s="75" t="inlineStr">
+      <c r="C115" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6582,10 +6605,10 @@
       <c r="I115" s="65" t="inlineStr"/>
       <c r="J115" s="23" t="inlineStr"/>
       <c r="K115" s="23" t="n"/>
-      <c r="L115" s="66" t="inlineStr"/>
+      <c r="L115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="67" t="inlineStr">
+      <c r="A116" s="68" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -6595,7 +6618,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C116" s="75" t="inlineStr">
+      <c r="C116" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6632,10 +6655,10 @@
         </is>
       </c>
       <c r="K116" s="23" t="n"/>
-      <c r="L116" s="66" t="inlineStr"/>
+      <c r="L116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="67" t="inlineStr">
+      <c r="A117" s="68" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -6645,7 +6668,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C117" s="75" t="inlineStr">
+      <c r="C117" s="76" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -6682,10 +6705,10 @@
         </is>
       </c>
       <c r="K117" s="23" t="n"/>
-      <c r="L117" s="66" t="inlineStr"/>
+      <c r="L117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="67" t="inlineStr">
+      <c r="A118" s="68" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -6695,7 +6718,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C118" s="75" t="inlineStr">
+      <c r="C118" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6732,16 +6755,16 @@
         </is>
       </c>
       <c r="K118" s="23" t="n"/>
-      <c r="L118" s="66" t="inlineStr"/>
+      <c r="L118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="67" t="inlineStr">
+      <c r="A119" s="68" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
       </c>
       <c r="B119" s="23" t="inlineStr"/>
-      <c r="C119" s="75" t="inlineStr">
+      <c r="C119" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6760,16 +6783,16 @@
       <c r="I119" s="65" t="inlineStr"/>
       <c r="J119" s="23" t="inlineStr"/>
       <c r="K119" s="23" t="n"/>
-      <c r="L119" s="66" t="inlineStr"/>
+      <c r="L119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="67" t="inlineStr">
+      <c r="A120" s="68" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B120" s="23" t="inlineStr"/>
-      <c r="C120" s="75" t="inlineStr">
+      <c r="C120" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6788,10 +6811,10 @@
       <c r="I120" s="65" t="inlineStr"/>
       <c r="J120" s="23" t="inlineStr"/>
       <c r="K120" s="23" t="n"/>
-      <c r="L120" s="66" t="inlineStr"/>
+      <c r="L120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="67" t="inlineStr">
+      <c r="A121" s="68" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -6801,7 +6824,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C121" s="75" t="inlineStr">
+      <c r="C121" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6838,10 +6861,10 @@
         </is>
       </c>
       <c r="K121" s="23" t="n"/>
-      <c r="L121" s="66" t="inlineStr"/>
+      <c r="L121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="67" t="inlineStr">
+      <c r="A122" s="68" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -6851,7 +6874,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C122" s="75" t="inlineStr">
+      <c r="C122" s="76" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -6888,16 +6911,16 @@
         </is>
       </c>
       <c r="K122" s="23" t="n"/>
-      <c r="L122" s="66" t="inlineStr"/>
+      <c r="L122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="67" t="inlineStr">
+      <c r="A123" s="68" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
       </c>
       <c r="B123" s="23" t="inlineStr"/>
-      <c r="C123" s="75" t="inlineStr">
+      <c r="C123" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6916,16 +6939,16 @@
       <c r="I123" s="65" t="inlineStr"/>
       <c r="J123" s="23" t="inlineStr"/>
       <c r="K123" s="23" t="n"/>
-      <c r="L123" s="66" t="inlineStr"/>
+      <c r="L123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="67" t="inlineStr">
+      <c r="A124" s="68" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
       </c>
       <c r="B124" s="23" t="inlineStr"/>
-      <c r="C124" s="75" t="inlineStr">
+      <c r="C124" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6944,10 +6967,10 @@
       <c r="I124" s="65" t="inlineStr"/>
       <c r="J124" s="23" t="inlineStr"/>
       <c r="K124" s="23" t="n"/>
-      <c r="L124" s="66" t="inlineStr"/>
+      <c r="L124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="67" t="inlineStr">
+      <c r="A125" s="68" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -6957,7 +6980,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C125" s="75" t="inlineStr">
+      <c r="C125" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6994,10 +7017,10 @@
         </is>
       </c>
       <c r="K125" s="23" t="n"/>
-      <c r="L125" s="66" t="inlineStr"/>
+      <c r="L125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="67" t="inlineStr">
+      <c r="A126" s="68" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -7007,7 +7030,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C126" s="75" t="inlineStr">
+      <c r="C126" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7044,16 +7067,16 @@
         </is>
       </c>
       <c r="K126" s="23" t="n"/>
-      <c r="L126" s="66" t="inlineStr"/>
+      <c r="L126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="67" t="inlineStr">
+      <c r="A127" s="68" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
       </c>
       <c r="B127" s="23" t="inlineStr"/>
-      <c r="C127" s="76" t="inlineStr">
+      <c r="C127" s="77" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -7072,10 +7095,10 @@
       <c r="I127" s="65" t="inlineStr"/>
       <c r="J127" s="23" t="inlineStr"/>
       <c r="K127" s="23" t="n"/>
-      <c r="L127" s="66" t="inlineStr"/>
+      <c r="L127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="67" t="inlineStr">
+      <c r="A128" s="68" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -7085,7 +7108,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C128" s="76" t="inlineStr">
+      <c r="C128" s="77" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -7122,10 +7145,10 @@
         </is>
       </c>
       <c r="K128" s="23" t="n"/>
-      <c r="L128" s="66" t="inlineStr"/>
+      <c r="L128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="67" t="inlineStr">
+      <c r="A129" s="68" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -7135,7 +7158,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C129" s="76" t="inlineStr">
+      <c r="C129" s="77" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -7172,10 +7195,10 @@
         </is>
       </c>
       <c r="K129" s="23" t="n"/>
-      <c r="L129" s="66" t="inlineStr"/>
+      <c r="L129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="67" t="inlineStr">
+      <c r="A130" s="68" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -7185,7 +7208,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C130" s="76" t="inlineStr">
+      <c r="C130" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -7222,10 +7245,10 @@
         </is>
       </c>
       <c r="K130" s="23" t="n"/>
-      <c r="L130" s="66" t="inlineStr"/>
+      <c r="L130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="67" t="inlineStr">
+      <c r="A131" s="68" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -7235,7 +7258,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C131" s="76" t="inlineStr">
+      <c r="C131" s="77" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7272,10 +7295,10 @@
         </is>
       </c>
       <c r="K131" s="23" t="n"/>
-      <c r="L131" s="66" t="inlineStr"/>
+      <c r="L131" s="67" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="67" t="inlineStr">
+      <c r="A132" s="68" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -7285,7 +7308,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C132" s="76" t="inlineStr">
+      <c r="C132" s="77" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -7322,10 +7345,10 @@
         </is>
       </c>
       <c r="K132" s="23" t="n"/>
-      <c r="L132" s="66" t="inlineStr"/>
+      <c r="L132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="67" t="inlineStr">
+      <c r="A133" s="68" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -7335,7 +7358,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C133" s="76" t="inlineStr">
+      <c r="C133" s="77" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -7372,10 +7395,10 @@
         </is>
       </c>
       <c r="K133" s="23" t="n"/>
-      <c r="L133" s="66" t="inlineStr"/>
+      <c r="L133" s="67" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="67" t="inlineStr">
+      <c r="A134" s="68" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -7385,7 +7408,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C134" s="76" t="inlineStr">
+      <c r="C134" s="77" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7422,10 +7445,10 @@
         </is>
       </c>
       <c r="K134" s="23" t="n"/>
-      <c r="L134" s="66" t="inlineStr"/>
+      <c r="L134" s="67" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="67" t="inlineStr">
+      <c r="A135" s="68" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -7435,7 +7458,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C135" s="76" t="inlineStr">
+      <c r="C135" s="77" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -7472,10 +7495,10 @@
         </is>
       </c>
       <c r="K135" s="23" t="n"/>
-      <c r="L135" s="66" t="inlineStr"/>
+      <c r="L135" s="67" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="67" t="inlineStr">
+      <c r="A136" s="68" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -7485,7 +7508,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C136" s="77" t="inlineStr">
+      <c r="C136" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7522,10 +7545,10 @@
         </is>
       </c>
       <c r="K136" s="23" t="n"/>
-      <c r="L136" s="66" t="inlineStr"/>
+      <c r="L136" s="67" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="67" t="inlineStr">
+      <c r="A137" s="68" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -7535,7 +7558,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C137" s="76" t="inlineStr">
+      <c r="C137" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7572,10 +7595,10 @@
         </is>
       </c>
       <c r="K137" s="23" t="n"/>
-      <c r="L137" s="66" t="inlineStr"/>
+      <c r="L137" s="67" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="67" t="inlineStr">
+      <c r="A138" s="68" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -7585,7 +7608,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C138" s="77" t="inlineStr">
+      <c r="C138" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7622,10 +7645,10 @@
         </is>
       </c>
       <c r="K138" s="23" t="n"/>
-      <c r="L138" s="66" t="inlineStr"/>
+      <c r="L138" s="67" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="67" t="inlineStr">
+      <c r="A139" s="68" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -7635,7 +7658,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C139" s="76" t="inlineStr">
+      <c r="C139" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7672,10 +7695,10 @@
         </is>
       </c>
       <c r="K139" s="23" t="n"/>
-      <c r="L139" s="66" t="inlineStr"/>
+      <c r="L139" s="67" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="67" t="inlineStr">
+      <c r="A140" s="68" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -7685,7 +7708,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C140" s="77" t="inlineStr">
+      <c r="C140" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -7722,10 +7745,10 @@
         </is>
       </c>
       <c r="K140" s="23" t="n"/>
-      <c r="L140" s="66" t="inlineStr"/>
+      <c r="L140" s="67" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="67" t="inlineStr">
+      <c r="A141" s="68" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -7735,7 +7758,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C141" s="75" t="inlineStr">
+      <c r="C141" s="76" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -7772,10 +7795,10 @@
         </is>
       </c>
       <c r="K141" s="23" t="n"/>
-      <c r="L141" s="66" t="inlineStr"/>
+      <c r="L141" s="67" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="67" t="inlineStr">
+      <c r="A142" s="68" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -7785,7 +7808,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C142" s="76" t="inlineStr">
+      <c r="C142" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7822,10 +7845,10 @@
         </is>
       </c>
       <c r="K142" s="23" t="n"/>
-      <c r="L142" s="66" t="inlineStr"/>
+      <c r="L142" s="67" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="67" t="inlineStr">
+      <c r="A143" s="68" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -7835,7 +7858,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C143" s="75" t="inlineStr">
+      <c r="C143" s="76" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7872,10 +7895,10 @@
         </is>
       </c>
       <c r="K143" s="23" t="n"/>
-      <c r="L143" s="66" t="inlineStr"/>
+      <c r="L143" s="67" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="67" t="inlineStr">
+      <c r="A144" s="68" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -7885,7 +7908,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C144" s="76" t="inlineStr">
+      <c r="C144" s="77" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -7922,10 +7945,10 @@
         </is>
       </c>
       <c r="K144" s="23" t="n"/>
-      <c r="L144" s="66" t="inlineStr"/>
+      <c r="L144" s="67" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="67" t="inlineStr">
+      <c r="A145" s="68" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -7935,7 +7958,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C145" s="76" t="inlineStr">
+      <c r="C145" s="77" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -7972,10 +7995,10 @@
         </is>
       </c>
       <c r="K145" s="23" t="n"/>
-      <c r="L145" s="66" t="inlineStr"/>
+      <c r="L145" s="67" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="67" t="inlineStr">
+      <c r="A146" s="68" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -7985,7 +8008,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C146" s="76" t="inlineStr">
+      <c r="C146" s="77" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8022,10 +8045,10 @@
         </is>
       </c>
       <c r="K146" s="23" t="n"/>
-      <c r="L146" s="66" t="inlineStr"/>
+      <c r="L146" s="67" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="67" t="inlineStr">
+      <c r="A147" s="68" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -8035,7 +8058,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C147" s="76" t="inlineStr">
+      <c r="C147" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8072,10 +8095,10 @@
         </is>
       </c>
       <c r="K147" s="23" t="n"/>
-      <c r="L147" s="66" t="inlineStr"/>
+      <c r="L147" s="67" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="67" t="inlineStr">
+      <c r="A148" s="68" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -8085,7 +8108,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C148" s="76" t="inlineStr">
+      <c r="C148" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8122,10 +8145,10 @@
         </is>
       </c>
       <c r="K148" s="23" t="n"/>
-      <c r="L148" s="66" t="inlineStr"/>
+      <c r="L148" s="67" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="67" t="inlineStr">
+      <c r="A149" s="68" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -8135,7 +8158,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C149" s="76" t="inlineStr">
+      <c r="C149" s="77" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -8172,10 +8195,10 @@
         </is>
       </c>
       <c r="K149" s="23" t="n"/>
-      <c r="L149" s="66" t="inlineStr"/>
+      <c r="L149" s="67" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="67" t="inlineStr">
+      <c r="A150" s="68" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -8185,7 +8208,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C150" s="75" t="inlineStr">
+      <c r="C150" s="76" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8222,10 +8245,10 @@
         </is>
       </c>
       <c r="K150" s="23" t="n"/>
-      <c r="L150" s="66" t="inlineStr"/>
+      <c r="L150" s="67" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="67" t="inlineStr">
+      <c r="A151" s="68" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -8235,7 +8258,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C151" s="75" t="inlineStr">
+      <c r="C151" s="76" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8272,10 +8295,10 @@
         </is>
       </c>
       <c r="K151" s="23" t="n"/>
-      <c r="L151" s="66" t="inlineStr"/>
+      <c r="L151" s="67" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="67" t="inlineStr">
+      <c r="A152" s="68" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -8285,7 +8308,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C152" s="75" t="inlineStr">
+      <c r="C152" s="76" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8322,10 +8345,10 @@
         </is>
       </c>
       <c r="K152" s="23" t="n"/>
-      <c r="L152" s="66" t="inlineStr"/>
+      <c r="L152" s="67" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="67" t="inlineStr">
+      <c r="A153" s="68" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -8335,7 +8358,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C153" s="76" t="inlineStr">
+      <c r="C153" s="77" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -8372,10 +8395,10 @@
         </is>
       </c>
       <c r="K153" s="23" t="n"/>
-      <c r="L153" s="66" t="inlineStr"/>
+      <c r="L153" s="67" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="67" t="inlineStr">
+      <c r="A154" s="68" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -8385,7 +8408,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C154" s="76" t="inlineStr">
+      <c r="C154" s="77" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8422,10 +8445,10 @@
         </is>
       </c>
       <c r="K154" s="23" t="n"/>
-      <c r="L154" s="66" t="inlineStr"/>
+      <c r="L154" s="67" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="67" t="inlineStr">
+      <c r="A155" s="68" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -8435,7 +8458,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C155" s="75" t="inlineStr">
+      <c r="C155" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8472,10 +8495,10 @@
         </is>
       </c>
       <c r="K155" s="23" t="n"/>
-      <c r="L155" s="66" t="inlineStr"/>
+      <c r="L155" s="67" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="67" t="inlineStr">
+      <c r="A156" s="68" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -8485,7 +8508,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C156" s="77" t="inlineStr">
+      <c r="C156" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -8522,10 +8545,10 @@
         </is>
       </c>
       <c r="K156" s="23" t="n"/>
-      <c r="L156" s="66" t="inlineStr"/>
+      <c r="L156" s="67" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="67" t="inlineStr">
+      <c r="A157" s="68" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -8535,7 +8558,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C157" s="76" t="inlineStr">
+      <c r="C157" s="77" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -8572,10 +8595,10 @@
         </is>
       </c>
       <c r="K157" s="23" t="n"/>
-      <c r="L157" s="66" t="inlineStr"/>
+      <c r="L157" s="67" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="67" t="inlineStr">
+      <c r="A158" s="68" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -8585,7 +8608,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C158" s="77" t="inlineStr">
+      <c r="C158" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8618,14 +8641,14 @@
       </c>
       <c r="J158" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="K158" s="23" t="n"/>
-      <c r="L158" s="66" t="inlineStr"/>
+      <c r="L158" s="67" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="67" t="inlineStr">
+      <c r="A159" s="68" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -8635,7 +8658,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C159" s="77" t="inlineStr">
+      <c r="C159" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8672,10 +8695,10 @@
         </is>
       </c>
       <c r="K159" s="23" t="n"/>
-      <c r="L159" s="66" t="inlineStr"/>
+      <c r="L159" s="67" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="67" t="inlineStr">
+      <c r="A160" s="68" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -8685,7 +8708,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C160" s="77" t="inlineStr">
+      <c r="C160" s="78" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
@@ -8722,10 +8745,10 @@
         </is>
       </c>
       <c r="K160" s="23" t="n"/>
-      <c r="L160" s="66" t="inlineStr"/>
+      <c r="L160" s="67" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="67" t="inlineStr">
+      <c r="A161" s="68" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -8735,7 +8758,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C161" s="77" t="inlineStr">
+      <c r="C161" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -8764,10 +8787,10 @@
       <c r="I161" s="65" t="inlineStr"/>
       <c r="J161" s="23" t="inlineStr"/>
       <c r="K161" s="23" t="n"/>
-      <c r="L161" s="66" t="inlineStr"/>
+      <c r="L161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="67" t="inlineStr">
+      <c r="A162" s="68" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -8777,7 +8800,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C162" s="76" t="inlineStr">
+      <c r="C162" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8806,10 +8829,10 @@
       <c r="I162" s="65" t="inlineStr"/>
       <c r="J162" s="23" t="inlineStr"/>
       <c r="K162" s="23" t="n"/>
-      <c r="L162" s="66" t="inlineStr"/>
+      <c r="L162" s="67" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="67" t="inlineStr">
+      <c r="A163" s="68" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -8819,7 +8842,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C163" s="76" t="inlineStr">
+      <c r="C163" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -8848,10 +8871,10 @@
       <c r="I163" s="65" t="inlineStr"/>
       <c r="J163" s="23" t="inlineStr"/>
       <c r="K163" s="23" t="n"/>
-      <c r="L163" s="66" t="inlineStr"/>
+      <c r="L163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="67" t="inlineStr">
+      <c r="A164" s="68" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -8861,7 +8884,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C164" s="76" t="inlineStr">
+      <c r="C164" s="77" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -8890,10 +8913,10 @@
       <c r="I164" s="65" t="inlineStr"/>
       <c r="J164" s="23" t="inlineStr"/>
       <c r="K164" s="23" t="n"/>
-      <c r="L164" s="66" t="inlineStr"/>
+      <c r="L164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="67" t="inlineStr">
+      <c r="A165" s="68" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -8903,7 +8926,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C165" s="77" t="inlineStr">
+      <c r="C165" s="78" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -8940,10 +8963,10 @@
         </is>
       </c>
       <c r="K165" s="23" t="n"/>
-      <c r="L165" s="66" t="inlineStr"/>
+      <c r="L165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="67" t="inlineStr">
+      <c r="A166" s="68" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -8953,7 +8976,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C166" s="76" t="inlineStr">
+      <c r="C166" s="77" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -8982,10 +9005,10 @@
       <c r="I166" s="65" t="inlineStr"/>
       <c r="J166" s="23" t="inlineStr"/>
       <c r="K166" s="23" t="n"/>
-      <c r="L166" s="66" t="inlineStr"/>
+      <c r="L166" s="67" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="67" t="inlineStr">
+      <c r="A167" s="68" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -8995,7 +9018,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C167" s="76" t="inlineStr">
+      <c r="C167" s="77" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -9024,10 +9047,10 @@
       <c r="I167" s="65" t="inlineStr"/>
       <c r="J167" s="23" t="inlineStr"/>
       <c r="K167" s="23" t="n"/>
-      <c r="L167" s="66" t="inlineStr"/>
+      <c r="L167" s="67" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="67" t="inlineStr">
+      <c r="A168" s="68" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -9037,7 +9060,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C168" s="77" t="inlineStr">
+      <c r="C168" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9074,10 +9097,10 @@
         </is>
       </c>
       <c r="K168" s="23" t="n"/>
-      <c r="L168" s="66" t="inlineStr"/>
+      <c r="L168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="67" t="inlineStr">
+      <c r="A169" s="68" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -9087,7 +9110,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C169" s="77" t="inlineStr">
+      <c r="C169" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9124,10 +9147,10 @@
         </is>
       </c>
       <c r="K169" s="23" t="n"/>
-      <c r="L169" s="66" t="inlineStr"/>
+      <c r="L169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="67" t="inlineStr">
+      <c r="A170" s="68" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -9137,7 +9160,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C170" s="77" t="inlineStr">
+      <c r="C170" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9174,10 +9197,10 @@
         </is>
       </c>
       <c r="K170" s="23" t="n"/>
-      <c r="L170" s="66" t="inlineStr"/>
+      <c r="L170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="67" t="inlineStr">
+      <c r="A171" s="68" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -9187,7 +9210,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C171" s="77" t="inlineStr">
+      <c r="C171" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9224,10 +9247,10 @@
         </is>
       </c>
       <c r="K171" s="23" t="n"/>
-      <c r="L171" s="66" t="inlineStr"/>
+      <c r="L171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="67" t="inlineStr">
+      <c r="A172" s="68" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -9237,7 +9260,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C172" s="77" t="inlineStr">
+      <c r="C172" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9274,10 +9297,10 @@
         </is>
       </c>
       <c r="K172" s="23" t="n"/>
-      <c r="L172" s="66" t="inlineStr"/>
+      <c r="L172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="67" t="inlineStr">
+      <c r="A173" s="68" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -9287,7 +9310,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C173" s="77" t="inlineStr">
+      <c r="C173" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9324,10 +9347,10 @@
         </is>
       </c>
       <c r="K173" s="23" t="n"/>
-      <c r="L173" s="66" t="inlineStr"/>
+      <c r="L173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="67" t="inlineStr">
+      <c r="A174" s="68" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -9337,7 +9360,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C174" s="77" t="inlineStr">
+      <c r="C174" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9374,10 +9397,10 @@
         </is>
       </c>
       <c r="K174" s="23" t="n"/>
-      <c r="L174" s="66" t="inlineStr"/>
+      <c r="L174" s="67" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="67" t="inlineStr">
+      <c r="A175" s="68" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -9387,7 +9410,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C175" s="77" t="inlineStr">
+      <c r="C175" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9424,10 +9447,10 @@
         </is>
       </c>
       <c r="K175" s="23" t="n"/>
-      <c r="L175" s="66" t="inlineStr"/>
+      <c r="L175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="67" t="inlineStr">
+      <c r="A176" s="68" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -9437,7 +9460,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C176" s="77" t="inlineStr">
+      <c r="C176" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9474,10 +9497,10 @@
         </is>
       </c>
       <c r="K176" s="23" t="n"/>
-      <c r="L176" s="66" t="inlineStr"/>
+      <c r="L176" s="67" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="67" t="inlineStr">
+      <c r="A177" s="68" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -9487,7 +9510,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C177" s="77" t="inlineStr">
+      <c r="C177" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9524,10 +9547,10 @@
         </is>
       </c>
       <c r="K177" s="23" t="n"/>
-      <c r="L177" s="66" t="inlineStr"/>
+      <c r="L177" s="67" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="67" t="inlineStr">
+      <c r="A178" s="68" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -9537,7 +9560,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C178" s="77" t="inlineStr">
+      <c r="C178" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9574,10 +9597,10 @@
         </is>
       </c>
       <c r="K178" s="23" t="n"/>
-      <c r="L178" s="66" t="inlineStr"/>
+      <c r="L178" s="67" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="67" t="inlineStr">
+      <c r="A179" s="68" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -9587,7 +9610,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C179" s="77" t="inlineStr">
+      <c r="C179" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9624,10 +9647,10 @@
         </is>
       </c>
       <c r="K179" s="23" t="n"/>
-      <c r="L179" s="66" t="inlineStr"/>
+      <c r="L179" s="67" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="67" t="inlineStr">
+      <c r="A180" s="68" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -9637,7 +9660,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C180" s="77" t="inlineStr">
+      <c r="C180" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9674,10 +9697,10 @@
         </is>
       </c>
       <c r="K180" s="23" t="n"/>
-      <c r="L180" s="66" t="inlineStr"/>
+      <c r="L180" s="67" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="67" t="inlineStr">
+      <c r="A181" s="68" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -9687,7 +9710,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C181" s="77" t="inlineStr">
+      <c r="C181" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9724,10 +9747,10 @@
         </is>
       </c>
       <c r="K181" s="23" t="n"/>
-      <c r="L181" s="66" t="inlineStr"/>
+      <c r="L181" s="67" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="67" t="inlineStr">
+      <c r="A182" s="68" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -9737,7 +9760,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C182" s="77" t="inlineStr">
+      <c r="C182" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9774,10 +9797,10 @@
         </is>
       </c>
       <c r="K182" s="23" t="n"/>
-      <c r="L182" s="66" t="inlineStr"/>
+      <c r="L182" s="67" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="67" t="inlineStr">
+      <c r="A183" s="68" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -9787,7 +9810,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C183" s="77" t="inlineStr">
+      <c r="C183" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9824,10 +9847,10 @@
         </is>
       </c>
       <c r="K183" s="23" t="n"/>
-      <c r="L183" s="66" t="inlineStr"/>
+      <c r="L183" s="67" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="67" t="inlineStr">
+      <c r="A184" s="68" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -9837,7 +9860,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C184" s="76" t="inlineStr">
+      <c r="C184" s="77" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9874,10 +9897,10 @@
         </is>
       </c>
       <c r="K184" s="23" t="n"/>
-      <c r="L184" s="66" t="inlineStr"/>
+      <c r="L184" s="67" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="67" t="inlineStr">
+      <c r="A185" s="68" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -9887,7 +9910,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C185" s="77" t="inlineStr">
+      <c r="C185" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9924,10 +9947,10 @@
         </is>
       </c>
       <c r="K185" s="23" t="n"/>
-      <c r="L185" s="66" t="inlineStr"/>
+      <c r="L185" s="67" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="67" t="inlineStr">
+      <c r="A186" s="68" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -9937,7 +9960,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C186" s="77" t="inlineStr">
+      <c r="C186" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9974,10 +9997,10 @@
         </is>
       </c>
       <c r="K186" s="23" t="n"/>
-      <c r="L186" s="66" t="inlineStr"/>
+      <c r="L186" s="67" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="67" t="inlineStr">
+      <c r="A187" s="68" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -9987,7 +10010,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C187" s="77" t="inlineStr">
+      <c r="C187" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10024,10 +10047,10 @@
         </is>
       </c>
       <c r="K187" s="23" t="n"/>
-      <c r="L187" s="66" t="inlineStr"/>
+      <c r="L187" s="67" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="67" t="inlineStr">
+      <c r="A188" s="68" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -10037,7 +10060,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C188" s="77" t="inlineStr">
+      <c r="C188" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10074,10 +10097,10 @@
         </is>
       </c>
       <c r="K188" s="23" t="n"/>
-      <c r="L188" s="66" t="inlineStr"/>
+      <c r="L188" s="67" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="67" t="inlineStr">
+      <c r="A189" s="68" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -10087,7 +10110,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C189" s="77" t="inlineStr">
+      <c r="C189" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10124,10 +10147,10 @@
         </is>
       </c>
       <c r="K189" s="23" t="n"/>
-      <c r="L189" s="66" t="inlineStr"/>
+      <c r="L189" s="67" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="67" t="inlineStr">
+      <c r="A190" s="68" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -10137,7 +10160,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C190" s="77" t="inlineStr">
+      <c r="C190" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10174,10 +10197,10 @@
         </is>
       </c>
       <c r="K190" s="23" t="n"/>
-      <c r="L190" s="66" t="inlineStr"/>
+      <c r="L190" s="67" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="67" t="inlineStr">
+      <c r="A191" s="68" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -10187,7 +10210,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C191" s="77" t="inlineStr">
+      <c r="C191" s="78" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -10224,10 +10247,10 @@
         </is>
       </c>
       <c r="K191" s="23" t="n"/>
-      <c r="L191" s="66" t="inlineStr"/>
+      <c r="L191" s="67" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="67" t="inlineStr">
+      <c r="A192" s="68" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -10237,7 +10260,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C192" s="77" t="inlineStr">
+      <c r="C192" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -10266,10 +10289,10 @@
       <c r="I192" s="65" t="inlineStr"/>
       <c r="J192" s="23" t="inlineStr"/>
       <c r="K192" s="23" t="n"/>
-      <c r="L192" s="66" t="inlineStr"/>
+      <c r="L192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="67" t="inlineStr">
+      <c r="A193" s="68" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -10279,7 +10302,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C193" s="76" t="inlineStr">
+      <c r="C193" s="77" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -10308,10 +10331,10 @@
       <c r="I193" s="65" t="inlineStr"/>
       <c r="J193" s="23" t="inlineStr"/>
       <c r="K193" s="23" t="n"/>
-      <c r="L193" s="66" t="inlineStr"/>
+      <c r="L193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="67" t="inlineStr">
+      <c r="A194" s="68" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -10321,7 +10344,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C194" s="77" t="inlineStr">
+      <c r="C194" s="78" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -10350,10 +10373,10 @@
       <c r="I194" s="65" t="inlineStr"/>
       <c r="J194" s="23" t="inlineStr"/>
       <c r="K194" s="23" t="n"/>
-      <c r="L194" s="66" t="inlineStr"/>
+      <c r="L194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="67" t="inlineStr">
+      <c r="A195" s="68" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -10363,7 +10386,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C195" s="77" t="inlineStr">
+      <c r="C195" s="78" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -10392,10 +10415,10 @@
       <c r="I195" s="65" t="inlineStr"/>
       <c r="J195" s="23" t="inlineStr"/>
       <c r="K195" s="23" t="n"/>
-      <c r="L195" s="66" t="inlineStr"/>
+      <c r="L195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="67" t="inlineStr">
+      <c r="A196" s="68" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -10405,7 +10428,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C196" s="76" t="inlineStr">
+      <c r="C196" s="77" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -10434,10 +10457,10 @@
       <c r="I196" s="65" t="inlineStr"/>
       <c r="J196" s="23" t="inlineStr"/>
       <c r="K196" s="23" t="n"/>
-      <c r="L196" s="66" t="inlineStr"/>
+      <c r="L196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="67" t="inlineStr">
+      <c r="A197" s="68" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -10447,7 +10470,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C197" s="77" t="inlineStr">
+      <c r="C197" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10476,10 +10499,10 @@
       <c r="I197" s="65" t="inlineStr"/>
       <c r="J197" s="23" t="inlineStr"/>
       <c r="K197" s="23" t="n"/>
-      <c r="L197" s="66" t="inlineStr"/>
+      <c r="L197" s="67" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="67" t="inlineStr">
+      <c r="A198" s="68" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -10489,7 +10512,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C198" s="77" t="inlineStr">
+      <c r="C198" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10518,10 +10541,10 @@
       <c r="I198" s="65" t="inlineStr"/>
       <c r="J198" s="23" t="inlineStr"/>
       <c r="K198" s="23" t="n"/>
-      <c r="L198" s="66" t="inlineStr"/>
+      <c r="L198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="67" t="inlineStr">
+      <c r="A199" s="68" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -10531,7 +10554,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C199" s="76" t="inlineStr">
+      <c r="C199" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10560,10 +10583,10 @@
       <c r="I199" s="65" t="inlineStr"/>
       <c r="J199" s="23" t="inlineStr"/>
       <c r="K199" s="23" t="n"/>
-      <c r="L199" s="66" t="inlineStr"/>
+      <c r="L199" s="67" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="67" t="inlineStr">
+      <c r="A200" s="68" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -10573,7 +10596,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C200" s="76" t="inlineStr">
+      <c r="C200" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10602,10 +10625,10 @@
       <c r="I200" s="65" t="inlineStr"/>
       <c r="J200" s="23" t="inlineStr"/>
       <c r="K200" s="23" t="n"/>
-      <c r="L200" s="66" t="inlineStr"/>
+      <c r="L200" s="67" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="67" t="inlineStr">
+      <c r="A201" s="68" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -10615,7 +10638,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C201" s="76" t="inlineStr">
+      <c r="C201" s="77" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -10644,10 +10667,10 @@
       <c r="I201" s="65" t="inlineStr"/>
       <c r="J201" s="23" t="inlineStr"/>
       <c r="K201" s="23" t="n"/>
-      <c r="L201" s="66" t="inlineStr"/>
+      <c r="L201" s="67" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="67" t="inlineStr">
+      <c r="A202" s="68" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -10657,7 +10680,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C202" s="77" t="inlineStr">
+      <c r="C202" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10694,10 +10717,10 @@
         </is>
       </c>
       <c r="K202" s="23" t="n"/>
-      <c r="L202" s="66" t="inlineStr"/>
+      <c r="L202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="67" t="inlineStr">
+      <c r="A203" s="68" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -10707,7 +10730,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C203" s="77" t="inlineStr">
+      <c r="C203" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10744,10 +10767,10 @@
         </is>
       </c>
       <c r="K203" s="23" t="n"/>
-      <c r="L203" s="66" t="inlineStr"/>
+      <c r="L203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="67" t="inlineStr">
+      <c r="A204" s="68" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -10757,7 +10780,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C204" s="77" t="inlineStr">
+      <c r="C204" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10794,10 +10817,10 @@
         </is>
       </c>
       <c r="K204" s="23" t="n"/>
-      <c r="L204" s="66" t="inlineStr"/>
+      <c r="L204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="67" t="inlineStr">
+      <c r="A205" s="68" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -10807,7 +10830,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C205" s="77" t="inlineStr">
+      <c r="C205" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10844,10 +10867,10 @@
         </is>
       </c>
       <c r="K205" s="23" t="n"/>
-      <c r="L205" s="66" t="inlineStr"/>
+      <c r="L205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="67" t="inlineStr">
+      <c r="A206" s="68" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -10857,7 +10880,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C206" s="77" t="inlineStr">
+      <c r="C206" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10894,10 +10917,10 @@
         </is>
       </c>
       <c r="K206" s="23" t="n"/>
-      <c r="L206" s="66" t="inlineStr"/>
+      <c r="L206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="67" t="inlineStr">
+      <c r="A207" s="68" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -10907,7 +10930,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C207" s="77" t="inlineStr">
+      <c r="C207" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10944,10 +10967,10 @@
         </is>
       </c>
       <c r="K207" s="23" t="n"/>
-      <c r="L207" s="66" t="inlineStr"/>
+      <c r="L207" s="67" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="67" t="inlineStr">
+      <c r="A208" s="68" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -10957,7 +10980,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C208" s="77" t="inlineStr">
+      <c r="C208" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -10994,10 +11017,10 @@
         </is>
       </c>
       <c r="K208" s="23" t="n"/>
-      <c r="L208" s="66" t="inlineStr"/>
+      <c r="L208" s="67" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="67" t="inlineStr">
+      <c r="A209" s="68" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -11007,7 +11030,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C209" s="76" t="inlineStr">
+      <c r="C209" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -11044,10 +11067,10 @@
         </is>
       </c>
       <c r="K209" s="23" t="n"/>
-      <c r="L209" s="66" t="inlineStr"/>
+      <c r="L209" s="67" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="67" t="inlineStr">
+      <c r="A210" s="68" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -11057,7 +11080,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C210" s="76" t="inlineStr">
+      <c r="C210" s="77" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11094,10 +11117,10 @@
         </is>
       </c>
       <c r="K210" s="23" t="n"/>
-      <c r="L210" s="66" t="inlineStr"/>
+      <c r="L210" s="67" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="67" t="inlineStr">
+      <c r="A211" s="68" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -11107,7 +11130,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C211" s="77" t="inlineStr">
+      <c r="C211" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11144,10 +11167,10 @@
         </is>
       </c>
       <c r="K211" s="23" t="n"/>
-      <c r="L211" s="66" t="inlineStr"/>
+      <c r="L211" s="67" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="67" t="inlineStr">
+      <c r="A212" s="68" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -11157,7 +11180,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C212" s="75" t="inlineStr">
+      <c r="C212" s="76" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -11194,10 +11217,10 @@
         </is>
       </c>
       <c r="K212" s="23" t="n"/>
-      <c r="L212" s="66" t="inlineStr"/>
+      <c r="L212" s="67" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="67" t="inlineStr">
+      <c r="A213" s="68" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -11207,7 +11230,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C213" s="75" t="inlineStr">
+      <c r="C213" s="76" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -11244,10 +11267,10 @@
         </is>
       </c>
       <c r="K213" s="23" t="n"/>
-      <c r="L213" s="66" t="inlineStr"/>
+      <c r="L213" s="67" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="67" t="inlineStr">
+      <c r="A214" s="68" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -11257,7 +11280,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C214" s="77" t="inlineStr">
+      <c r="C214" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11294,10 +11317,10 @@
         </is>
       </c>
       <c r="K214" s="23" t="n"/>
-      <c r="L214" s="66" t="inlineStr"/>
+      <c r="L214" s="67" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="67" t="inlineStr">
+      <c r="A215" s="68" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -11307,7 +11330,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C215" s="77" t="inlineStr">
+      <c r="C215" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11344,16 +11367,16 @@
         </is>
       </c>
       <c r="K215" s="23" t="n"/>
-      <c r="L215" s="66" t="inlineStr"/>
+      <c r="L215" s="67" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="67" t="inlineStr">
+      <c r="A216" s="68" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
       </c>
       <c r="B216" s="23" t="inlineStr"/>
-      <c r="C216" s="75" t="inlineStr">
+      <c r="C216" s="76" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -11372,10 +11395,10 @@
       <c r="I216" s="65" t="inlineStr"/>
       <c r="J216" s="23" t="inlineStr"/>
       <c r="K216" s="23" t="n"/>
-      <c r="L216" s="66" t="inlineStr"/>
+      <c r="L216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="67" t="inlineStr">
+      <c r="A217" s="68" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -11385,7 +11408,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C217" s="75" t="inlineStr">
+      <c r="C217" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11422,10 +11445,10 @@
         </is>
       </c>
       <c r="K217" s="23" t="n"/>
-      <c r="L217" s="66" t="inlineStr"/>
+      <c r="L217" s="67" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="67" t="inlineStr">
+      <c r="A218" s="68" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -11435,7 +11458,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C218" s="75" t="inlineStr">
+      <c r="C218" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11472,10 +11495,10 @@
         </is>
       </c>
       <c r="K218" s="23" t="n"/>
-      <c r="L218" s="66" t="inlineStr"/>
+      <c r="L218" s="67" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="67" t="inlineStr">
+      <c r="A219" s="68" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -11485,7 +11508,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C219" s="75" t="inlineStr">
+      <c r="C219" s="76" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -11522,10 +11545,10 @@
         </is>
       </c>
       <c r="K219" s="23" t="n"/>
-      <c r="L219" s="66" t="inlineStr"/>
+      <c r="L219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="67" t="inlineStr">
+      <c r="A220" s="68" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -11535,7 +11558,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C220" s="75" t="inlineStr">
+      <c r="C220" s="76" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -11572,10 +11595,10 @@
         </is>
       </c>
       <c r="K220" s="23" t="n"/>
-      <c r="L220" s="66" t="inlineStr"/>
+      <c r="L220" s="67" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="67" t="inlineStr">
+      <c r="A221" s="68" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -11585,7 +11608,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C221" s="76" t="inlineStr">
+      <c r="C221" s="77" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11622,10 +11645,10 @@
         </is>
       </c>
       <c r="K221" s="23" t="n"/>
-      <c r="L221" s="66" t="inlineStr"/>
+      <c r="L221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="67" t="inlineStr">
+      <c r="A222" s="68" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -11635,7 +11658,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C222" s="77" t="inlineStr">
+      <c r="C222" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11672,10 +11695,10 @@
         </is>
       </c>
       <c r="K222" s="23" t="n"/>
-      <c r="L222" s="66" t="inlineStr"/>
+      <c r="L222" s="67" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="67" t="inlineStr">
+      <c r="A223" s="68" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -11685,7 +11708,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C223" s="75" t="inlineStr">
+      <c r="C223" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11722,10 +11745,10 @@
         </is>
       </c>
       <c r="K223" s="23" t="n"/>
-      <c r="L223" s="66" t="inlineStr"/>
+      <c r="L223" s="67" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="67" t="inlineStr">
+      <c r="A224" s="68" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -11735,7 +11758,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C224" s="75" t="inlineStr">
+      <c r="C224" s="76" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -11772,10 +11795,10 @@
         </is>
       </c>
       <c r="K224" s="23" t="n"/>
-      <c r="L224" s="66" t="inlineStr"/>
+      <c r="L224" s="67" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="67" t="inlineStr">
+      <c r="A225" s="68" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -11785,7 +11808,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C225" s="75" t="inlineStr">
+      <c r="C225" s="76" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -11822,10 +11845,10 @@
         </is>
       </c>
       <c r="K225" s="23" t="n"/>
-      <c r="L225" s="66" t="inlineStr"/>
+      <c r="L225" s="67" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="67" t="inlineStr">
+      <c r="A226" s="68" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -11835,7 +11858,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C226" s="75" t="inlineStr">
+      <c r="C226" s="76" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -11872,10 +11895,10 @@
         </is>
       </c>
       <c r="K226" s="23" t="n"/>
-      <c r="L226" s="66" t="inlineStr"/>
+      <c r="L226" s="67" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="67" t="inlineStr">
+      <c r="A227" s="68" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -11885,7 +11908,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C227" s="75" t="inlineStr">
+      <c r="C227" s="76" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -11922,10 +11945,10 @@
         </is>
       </c>
       <c r="K227" s="23" t="n"/>
-      <c r="L227" s="66" t="inlineStr"/>
+      <c r="L227" s="67" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="67" t="inlineStr">
+      <c r="A228" s="68" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -11935,7 +11958,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C228" s="75" t="inlineStr">
+      <c r="C228" s="76" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -11972,10 +11995,10 @@
         </is>
       </c>
       <c r="K228" s="23" t="n"/>
-      <c r="L228" s="66" t="inlineStr"/>
+      <c r="L228" s="67" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="67" t="inlineStr">
+      <c r="A229" s="68" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -11985,7 +12008,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C229" s="75" t="inlineStr">
+      <c r="C229" s="76" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -12022,16 +12045,16 @@
         </is>
       </c>
       <c r="K229" s="23" t="n"/>
-      <c r="L229" s="66" t="inlineStr"/>
+      <c r="L229" s="67" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="67" t="inlineStr">
+      <c r="A230" s="68" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
       </c>
       <c r="B230" s="23" t="inlineStr"/>
-      <c r="C230" s="77" t="inlineStr">
+      <c r="C230" s="78" t="inlineStr">
         <is>
           <t>96%</t>
         </is>
@@ -12050,16 +12073,16 @@
       <c r="I230" s="65" t="inlineStr"/>
       <c r="J230" s="23" t="inlineStr"/>
       <c r="K230" s="23" t="n"/>
-      <c r="L230" s="66" t="inlineStr"/>
+      <c r="L230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="67" t="inlineStr">
+      <c r="A231" s="68" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
       </c>
       <c r="B231" s="23" t="inlineStr"/>
-      <c r="C231" s="77" t="inlineStr">
+      <c r="C231" s="78" t="inlineStr">
         <is>
           <t>97%</t>
         </is>
@@ -12078,10 +12101,10 @@
       <c r="I231" s="65" t="inlineStr"/>
       <c r="J231" s="23" t="inlineStr"/>
       <c r="K231" s="23" t="n"/>
-      <c r="L231" s="66" t="inlineStr"/>
+      <c r="L231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="67" t="inlineStr">
+      <c r="A232" s="68" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -12091,7 +12114,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C232" s="75" t="inlineStr">
+      <c r="C232" s="76" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -12128,10 +12151,10 @@
         </is>
       </c>
       <c r="K232" s="23" t="n"/>
-      <c r="L232" s="66" t="inlineStr"/>
+      <c r="L232" s="67" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="67" t="inlineStr">
+      <c r="A233" s="68" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -12141,7 +12164,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C233" s="75" t="inlineStr">
+      <c r="C233" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12178,10 +12201,10 @@
         </is>
       </c>
       <c r="K233" s="23" t="n"/>
-      <c r="L233" s="66" t="inlineStr"/>
+      <c r="L233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="67" t="inlineStr">
+      <c r="A234" s="68" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -12191,7 +12214,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C234" s="75" t="inlineStr">
+      <c r="C234" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12228,10 +12251,10 @@
         </is>
       </c>
       <c r="K234" s="23" t="n"/>
-      <c r="L234" s="66" t="inlineStr"/>
+      <c r="L234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="67" t="inlineStr">
+      <c r="A235" s="68" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -12241,7 +12264,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C235" s="75" t="inlineStr">
+      <c r="C235" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12278,10 +12301,10 @@
         </is>
       </c>
       <c r="K235" s="23" t="n"/>
-      <c r="L235" s="66" t="inlineStr"/>
+      <c r="L235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="67" t="inlineStr">
+      <c r="A236" s="68" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -12291,7 +12314,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C236" s="75" t="inlineStr">
+      <c r="C236" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12328,10 +12351,10 @@
         </is>
       </c>
       <c r="K236" s="23" t="n"/>
-      <c r="L236" s="66" t="inlineStr"/>
+      <c r="L236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="67" t="inlineStr">
+      <c r="A237" s="68" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -12341,7 +12364,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C237" s="75" t="inlineStr">
+      <c r="C237" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12378,10 +12401,10 @@
         </is>
       </c>
       <c r="K237" s="23" t="n"/>
-      <c r="L237" s="66" t="inlineStr"/>
+      <c r="L237" s="67" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="67" t="inlineStr">
+      <c r="A238" s="68" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -12391,7 +12414,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C238" s="75" t="inlineStr">
+      <c r="C238" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12428,10 +12451,10 @@
         </is>
       </c>
       <c r="K238" s="23" t="n"/>
-      <c r="L238" s="66" t="inlineStr"/>
+      <c r="L238" s="67" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="67" t="inlineStr">
+      <c r="A239" s="68" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -12441,7 +12464,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C239" s="75" t="inlineStr">
+      <c r="C239" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12478,16 +12501,16 @@
         </is>
       </c>
       <c r="K239" s="23" t="n"/>
-      <c r="L239" s="66" t="inlineStr"/>
+      <c r="L239" s="67" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="67" t="inlineStr">
+      <c r="A240" s="68" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="B240" s="23" t="inlineStr"/>
-      <c r="C240" s="77" t="inlineStr">
+      <c r="C240" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -12506,10 +12529,10 @@
       <c r="I240" s="65" t="inlineStr"/>
       <c r="J240" s="23" t="inlineStr"/>
       <c r="K240" s="23" t="n"/>
-      <c r="L240" s="66" t="inlineStr"/>
+      <c r="L240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="67" t="inlineStr">
+      <c r="A241" s="68" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -12519,7 +12542,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C241" s="75" t="inlineStr">
+      <c r="C241" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12556,10 +12579,10 @@
         </is>
       </c>
       <c r="K241" s="23" t="n"/>
-      <c r="L241" s="66" t="inlineStr"/>
+      <c r="L241" s="67" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="67" t="inlineStr">
+      <c r="A242" s="68" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -12569,7 +12592,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C242" s="75" t="inlineStr">
+      <c r="C242" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12606,10 +12629,10 @@
         </is>
       </c>
       <c r="K242" s="23" t="n"/>
-      <c r="L242" s="66" t="inlineStr"/>
+      <c r="L242" s="67" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="67" t="inlineStr">
+      <c r="A243" s="68" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -12619,7 +12642,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C243" s="75" t="inlineStr">
+      <c r="C243" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12656,10 +12679,10 @@
         </is>
       </c>
       <c r="K243" s="23" t="n"/>
-      <c r="L243" s="66" t="inlineStr"/>
+      <c r="L243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="67" t="inlineStr">
+      <c r="A244" s="68" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -12669,7 +12692,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C244" s="76" t="inlineStr">
+      <c r="C244" s="77" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -12706,16 +12729,16 @@
         </is>
       </c>
       <c r="K244" s="23" t="n"/>
-      <c r="L244" s="66" t="inlineStr"/>
+      <c r="L244" s="67" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="67" t="inlineStr">
+      <c r="A245" s="68" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
       </c>
       <c r="B245" s="23" t="inlineStr"/>
-      <c r="C245" s="75" t="inlineStr">
+      <c r="C245" s="76" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -12734,10 +12757,10 @@
       <c r="I245" s="65" t="inlineStr"/>
       <c r="J245" s="23" t="inlineStr"/>
       <c r="K245" s="23" t="n"/>
-      <c r="L245" s="66" t="inlineStr"/>
+      <c r="L245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="67" t="inlineStr">
+      <c r="A246" s="68" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -12747,7 +12770,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C246" s="76" t="inlineStr">
+      <c r="C246" s="77" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -12784,10 +12807,10 @@
         </is>
       </c>
       <c r="K246" s="23" t="n"/>
-      <c r="L246" s="66" t="inlineStr"/>
+      <c r="L246" s="67" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="67" t="inlineStr">
+      <c r="A247" s="68" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -12797,7 +12820,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C247" s="77" t="inlineStr">
+      <c r="C247" s="78" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -12826,10 +12849,10 @@
       <c r="I247" s="65" t="inlineStr"/>
       <c r="J247" s="23" t="inlineStr"/>
       <c r="K247" s="23" t="n"/>
-      <c r="L247" s="66" t="inlineStr"/>
+      <c r="L247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="67" t="inlineStr">
+      <c r="A248" s="68" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -12839,7 +12862,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C248" s="76" t="inlineStr">
+      <c r="C248" s="77" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -12876,10 +12899,10 @@
         </is>
       </c>
       <c r="K248" s="23" t="n"/>
-      <c r="L248" s="66" t="inlineStr"/>
+      <c r="L248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="67" t="inlineStr">
+      <c r="A249" s="68" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -12889,7 +12912,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C249" s="76" t="inlineStr">
+      <c r="C249" s="77" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -12926,10 +12949,10 @@
         </is>
       </c>
       <c r="K249" s="23" t="n"/>
-      <c r="L249" s="66" t="inlineStr"/>
+      <c r="L249" s="67" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="67" t="inlineStr">
+      <c r="A250" s="68" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -12939,7 +12962,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C250" s="76" t="inlineStr">
+      <c r="C250" s="77" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -12976,10 +12999,10 @@
         </is>
       </c>
       <c r="K250" s="23" t="n"/>
-      <c r="L250" s="66" t="inlineStr"/>
+      <c r="L250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="67" t="inlineStr">
+      <c r="A251" s="68" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -12989,7 +13012,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C251" s="76" t="inlineStr">
+      <c r="C251" s="77" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -13026,10 +13049,10 @@
         </is>
       </c>
       <c r="K251" s="23" t="n"/>
-      <c r="L251" s="66" t="inlineStr"/>
+      <c r="L251" s="67" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="67" t="inlineStr">
+      <c r="A252" s="68" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -13039,7 +13062,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C252" s="77" t="inlineStr">
+      <c r="C252" s="78" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
@@ -13076,10 +13099,10 @@
         </is>
       </c>
       <c r="K252" s="23" t="n"/>
-      <c r="L252" s="66" t="inlineStr"/>
+      <c r="L252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="67" t="inlineStr">
+      <c r="A253" s="68" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -13089,7 +13112,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C253" s="77" t="inlineStr">
+      <c r="C253" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -13126,10 +13149,10 @@
         </is>
       </c>
       <c r="K253" s="23" t="n"/>
-      <c r="L253" s="66" t="inlineStr"/>
+      <c r="L253" s="67" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="67" t="inlineStr">
+      <c r="A254" s="68" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -13139,7 +13162,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C254" s="76" t="inlineStr">
+      <c r="C254" s="77" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13176,10 +13199,10 @@
         </is>
       </c>
       <c r="K254" s="23" t="n"/>
-      <c r="L254" s="66" t="inlineStr"/>
+      <c r="L254" s="67" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="67" t="inlineStr">
+      <c r="A255" s="68" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -13189,7 +13212,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C255" s="76" t="inlineStr">
+      <c r="C255" s="77" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -13226,10 +13249,10 @@
         </is>
       </c>
       <c r="K255" s="23" t="n"/>
-      <c r="L255" s="66" t="inlineStr"/>
+      <c r="L255" s="67" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="67" t="inlineStr">
+      <c r="A256" s="68" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -13239,7 +13262,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C256" s="77" t="inlineStr">
+      <c r="C256" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -13276,10 +13299,10 @@
         </is>
       </c>
       <c r="K256" s="23" t="n"/>
-      <c r="L256" s="66" t="inlineStr"/>
+      <c r="L256" s="67" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="67" t="inlineStr">
+      <c r="A257" s="68" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -13289,7 +13312,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C257" s="76" t="inlineStr">
+      <c r="C257" s="77" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -13326,10 +13349,10 @@
         </is>
       </c>
       <c r="K257" s="23" t="n"/>
-      <c r="L257" s="66" t="inlineStr"/>
+      <c r="L257" s="67" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="67" t="inlineStr">
+      <c r="A258" s="68" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -13339,7 +13362,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C258" s="75" t="inlineStr">
+      <c r="C258" s="76" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -13376,10 +13399,10 @@
         </is>
       </c>
       <c r="K258" s="23" t="n"/>
-      <c r="L258" s="66" t="inlineStr"/>
+      <c r="L258" s="67" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="67" t="inlineStr">
+      <c r="A259" s="68" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -13389,7 +13412,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C259" s="76" t="inlineStr">
+      <c r="C259" s="77" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -13426,10 +13449,10 @@
         </is>
       </c>
       <c r="K259" s="23" t="n"/>
-      <c r="L259" s="66" t="inlineStr"/>
+      <c r="L259" s="67" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="67" t="inlineStr">
+      <c r="A260" s="68" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -13439,7 +13462,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C260" s="76" t="inlineStr">
+      <c r="C260" s="77" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -13476,10 +13499,10 @@
         </is>
       </c>
       <c r="K260" s="23" t="n"/>
-      <c r="L260" s="66" t="inlineStr"/>
+      <c r="L260" s="67" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="67" t="inlineStr">
+      <c r="A261" s="68" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -13489,7 +13512,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C261" s="76" t="inlineStr">
+      <c r="C261" s="77" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -13526,10 +13549,10 @@
         </is>
       </c>
       <c r="K261" s="23" t="n"/>
-      <c r="L261" s="66" t="inlineStr"/>
+      <c r="L261" s="67" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="67" t="inlineStr">
+      <c r="A262" s="68" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -13539,7 +13562,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C262" s="75" t="inlineStr">
+      <c r="C262" s="76" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -13576,10 +13599,10 @@
         </is>
       </c>
       <c r="K262" s="23" t="n"/>
-      <c r="L262" s="66" t="inlineStr"/>
+      <c r="L262" s="67" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="67" t="inlineStr">
+      <c r="A263" s="68" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -13589,7 +13612,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C263" s="75" t="inlineStr">
+      <c r="C263" s="76" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -13626,10 +13649,10 @@
         </is>
       </c>
       <c r="K263" s="23" t="n"/>
-      <c r="L263" s="66" t="inlineStr"/>
+      <c r="L263" s="67" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="67" t="inlineStr">
+      <c r="A264" s="68" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -13639,7 +13662,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C264" s="75" t="inlineStr">
+      <c r="C264" s="76" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -13676,10 +13699,10 @@
         </is>
       </c>
       <c r="K264" s="23" t="n"/>
-      <c r="L264" s="66" t="inlineStr"/>
+      <c r="L264" s="67" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="67" t="inlineStr">
+      <c r="A265" s="68" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -13689,7 +13712,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C265" s="75" t="inlineStr">
+      <c r="C265" s="76" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -13726,10 +13749,10 @@
         </is>
       </c>
       <c r="K265" s="23" t="n"/>
-      <c r="L265" s="66" t="inlineStr"/>
+      <c r="L265" s="67" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="67" t="inlineStr">
+      <c r="A266" s="68" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -13739,7 +13762,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C266" s="75" t="inlineStr">
+      <c r="C266" s="76" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -13776,10 +13799,10 @@
         </is>
       </c>
       <c r="K266" s="23" t="n"/>
-      <c r="L266" s="66" t="inlineStr"/>
+      <c r="L266" s="67" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="67" t="inlineStr">
+      <c r="A267" s="68" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -13789,7 +13812,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C267" s="75" t="inlineStr">
+      <c r="C267" s="76" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -13826,10 +13849,10 @@
         </is>
       </c>
       <c r="K267" s="23" t="n"/>
-      <c r="L267" s="66" t="inlineStr"/>
+      <c r="L267" s="67" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="67" t="inlineStr">
+      <c r="A268" s="68" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -13839,7 +13862,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C268" s="75" t="inlineStr">
+      <c r="C268" s="76" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -13876,10 +13899,10 @@
         </is>
       </c>
       <c r="K268" s="23" t="n"/>
-      <c r="L268" s="66" t="inlineStr"/>
+      <c r="L268" s="67" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="67" t="inlineStr">
+      <c r="A269" s="68" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -13889,7 +13912,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C269" s="75" t="inlineStr">
+      <c r="C269" s="76" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -13926,10 +13949,10 @@
         </is>
       </c>
       <c r="K269" s="23" t="n"/>
-      <c r="L269" s="66" t="inlineStr"/>
+      <c r="L269" s="67" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="67" t="inlineStr">
+      <c r="A270" s="68" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -13939,7 +13962,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C270" s="75" t="inlineStr">
+      <c r="C270" s="76" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13976,10 +13999,10 @@
         </is>
       </c>
       <c r="K270" s="23" t="n"/>
-      <c r="L270" s="66" t="inlineStr"/>
+      <c r="L270" s="67" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="67" t="inlineStr">
+      <c r="A271" s="68" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -13989,7 +14012,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C271" s="75" t="inlineStr">
+      <c r="C271" s="76" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -14026,10 +14049,10 @@
         </is>
       </c>
       <c r="K271" s="23" t="n"/>
-      <c r="L271" s="66" t="inlineStr"/>
+      <c r="L271" s="67" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="67" t="inlineStr">
+      <c r="A272" s="68" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -14039,7 +14062,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C272" s="75" t="inlineStr">
+      <c r="C272" s="76" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -14076,10 +14099,10 @@
         </is>
       </c>
       <c r="K272" s="23" t="n"/>
-      <c r="L272" s="66" t="inlineStr"/>
+      <c r="L272" s="67" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="67" t="inlineStr">
+      <c r="A273" s="68" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -14089,7 +14112,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C273" s="75" t="inlineStr">
+      <c r="C273" s="76" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -14126,10 +14149,10 @@
         </is>
       </c>
       <c r="K273" s="23" t="n"/>
-      <c r="L273" s="66" t="inlineStr"/>
+      <c r="L273" s="67" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="67" t="inlineStr">
+      <c r="A274" s="68" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -14139,7 +14162,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C274" s="76" t="inlineStr">
+      <c r="C274" s="77" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -14176,10 +14199,10 @@
         </is>
       </c>
       <c r="K274" s="23" t="n"/>
-      <c r="L274" s="66" t="inlineStr"/>
+      <c r="L274" s="67" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="67" t="inlineStr">
+      <c r="A275" s="68" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -14189,7 +14212,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C275" s="75" t="inlineStr">
+      <c r="C275" s="76" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -14226,10 +14249,10 @@
         </is>
       </c>
       <c r="K275" s="23" t="n"/>
-      <c r="L275" s="66" t="inlineStr"/>
+      <c r="L275" s="67" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="67" t="inlineStr">
+      <c r="A276" s="68" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -14239,7 +14262,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C276" s="75" t="inlineStr">
+      <c r="C276" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14276,10 +14299,10 @@
         </is>
       </c>
       <c r="K276" s="23" t="n"/>
-      <c r="L276" s="66" t="inlineStr"/>
+      <c r="L276" s="67" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="67" t="inlineStr">
+      <c r="A277" s="68" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -14289,7 +14312,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C277" s="76" t="inlineStr">
+      <c r="C277" s="77" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -14326,10 +14349,10 @@
         </is>
       </c>
       <c r="K277" s="23" t="n"/>
-      <c r="L277" s="66" t="inlineStr"/>
+      <c r="L277" s="67" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="67" t="inlineStr">
+      <c r="A278" s="68" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -14339,7 +14362,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C278" s="75" t="inlineStr">
+      <c r="C278" s="76" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -14376,10 +14399,10 @@
         </is>
       </c>
       <c r="K278" s="23" t="n"/>
-      <c r="L278" s="66" t="inlineStr"/>
+      <c r="L278" s="67" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="67" t="inlineStr">
+      <c r="A279" s="68" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -14389,7 +14412,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C279" s="75" t="inlineStr">
+      <c r="C279" s="76" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -14426,10 +14449,10 @@
         </is>
       </c>
       <c r="K279" s="23" t="n"/>
-      <c r="L279" s="66" t="inlineStr"/>
+      <c r="L279" s="67" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="67" t="inlineStr">
+      <c r="A280" s="68" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -14439,7 +14462,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C280" s="75" t="inlineStr">
+      <c r="C280" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14476,10 +14499,10 @@
         </is>
       </c>
       <c r="K280" s="23" t="n"/>
-      <c r="L280" s="66" t="inlineStr"/>
+      <c r="L280" s="67" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="67" t="inlineStr">
+      <c r="A281" s="68" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -14489,7 +14512,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C281" s="77" t="inlineStr">
+      <c r="C281" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14526,10 +14549,10 @@
         </is>
       </c>
       <c r="K281" s="23" t="n"/>
-      <c r="L281" s="66" t="inlineStr"/>
+      <c r="L281" s="67" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="67" t="inlineStr">
+      <c r="A282" s="68" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -14539,7 +14562,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C282" s="75" t="inlineStr">
+      <c r="C282" s="76" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -14576,10 +14599,10 @@
         </is>
       </c>
       <c r="K282" s="23" t="n"/>
-      <c r="L282" s="66" t="inlineStr"/>
+      <c r="L282" s="67" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="67" t="inlineStr">
+      <c r="A283" s="68" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -14589,7 +14612,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C283" s="75" t="inlineStr">
+      <c r="C283" s="76" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -14626,10 +14649,10 @@
         </is>
       </c>
       <c r="K283" s="23" t="n"/>
-      <c r="L283" s="66" t="inlineStr"/>
+      <c r="L283" s="67" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="67" t="inlineStr">
+      <c r="A284" s="68" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -14639,7 +14662,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C284" s="77" t="inlineStr">
+      <c r="C284" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14676,10 +14699,10 @@
         </is>
       </c>
       <c r="K284" s="23" t="n"/>
-      <c r="L284" s="66" t="inlineStr"/>
+      <c r="L284" s="67" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="67" t="inlineStr">
+      <c r="A285" s="68" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -14689,7 +14712,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C285" s="77" t="inlineStr">
+      <c r="C285" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14726,10 +14749,10 @@
         </is>
       </c>
       <c r="K285" s="23" t="n"/>
-      <c r="L285" s="66" t="inlineStr"/>
+      <c r="L285" s="67" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="67" t="inlineStr">
+      <c r="A286" s="68" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -14739,7 +14762,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C286" s="77" t="inlineStr">
+      <c r="C286" s="78" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14776,10 +14799,10 @@
         </is>
       </c>
       <c r="K286" s="23" t="n"/>
-      <c r="L286" s="66" t="inlineStr"/>
+      <c r="L286" s="67" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="67" t="inlineStr">
+      <c r="A287" s="68" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -14789,7 +14812,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C287" s="75" t="inlineStr">
+      <c r="C287" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14826,10 +14849,10 @@
         </is>
       </c>
       <c r="K287" s="23" t="n"/>
-      <c r="L287" s="66" t="inlineStr"/>
+      <c r="L287" s="67" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="67" t="inlineStr">
+      <c r="A288" s="68" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -14839,7 +14862,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C288" s="75" t="inlineStr">
+      <c r="C288" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14876,10 +14899,10 @@
         </is>
       </c>
       <c r="K288" s="23" t="n"/>
-      <c r="L288" s="66" t="inlineStr"/>
+      <c r="L288" s="67" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="67" t="inlineStr">
+      <c r="A289" s="68" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -14889,7 +14912,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C289" s="75" t="inlineStr">
+      <c r="C289" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14926,10 +14949,10 @@
         </is>
       </c>
       <c r="K289" s="23" t="n"/>
-      <c r="L289" s="66" t="inlineStr"/>
+      <c r="L289" s="67" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="67" t="inlineStr">
+      <c r="A290" s="68" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -14939,7 +14962,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C290" s="75" t="inlineStr">
+      <c r="C290" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14976,10 +14999,10 @@
         </is>
       </c>
       <c r="K290" s="23" t="n"/>
-      <c r="L290" s="66" t="inlineStr"/>
+      <c r="L290" s="67" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="67" t="inlineStr">
+      <c r="A291" s="68" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -14989,7 +15012,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C291" s="75" t="inlineStr">
+      <c r="C291" s="76" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -15026,10 +15049,10 @@
         </is>
       </c>
       <c r="K291" s="23" t="n"/>
-      <c r="L291" s="66" t="inlineStr"/>
+      <c r="L291" s="67" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="67" t="inlineStr">
+      <c r="A292" s="68" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -15039,7 +15062,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C292" s="76" t="inlineStr">
+      <c r="C292" s="77" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -15076,7 +15099,7 @@
         </is>
       </c>
       <c r="K292" s="23" t="n"/>
-      <c r="L292" s="66" t="inlineStr"/>
+      <c r="L292" s="67" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L292"/>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3 · BLOCKING – REMARKS'!$A$2:$L$292</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3 · BLOCKING – REMARKS'!$A$2:$L$297</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,14 +570,14 @@
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L292"/>
+  <dimension ref="A1:L297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5898,7 +5898,7 @@
     <row r="100">
       <c r="A100" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-01 - PAGA</t>
+          <t>PS5-08-01</t>
         </is>
       </c>
       <c r="B100" s="23" t="inlineStr">
@@ -5948,63 +5948,41 @@
     <row r="101">
       <c r="A101" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
-        </is>
-      </c>
-      <c r="B101" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-01a - PAGA (Required for SU)</t>
+        </is>
+      </c>
+      <c r="B101" s="23" t="inlineStr"/>
       <c r="C101" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="D101" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E101" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F101" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G101" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="65" t="inlineStr"/>
       <c r="H101" s="65" t="inlineStr"/>
-      <c r="I101" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J101" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I101" s="65" t="inlineStr"/>
+      <c r="J101" s="23" t="inlineStr"/>
       <c r="K101" s="23" t="n"/>
       <c r="L101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-04 - Hotline</t>
+          <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
       </c>
       <c r="B102" s="23" t="inlineStr"/>
       <c r="C102" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="D102" s="23" t="n">
@@ -6026,135 +6004,113 @@
     <row r="103">
       <c r="A103" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
-        </is>
-      </c>
-      <c r="B103" s="23" t="inlineStr"/>
+          <t>PS5-08-03 - Telephone</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C103" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D103" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="65" t="inlineStr"/>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="D103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G103" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H103" s="65" t="inlineStr"/>
-      <c r="I103" s="65" t="inlineStr"/>
-      <c r="J103" s="23" t="inlineStr"/>
+      <c r="I103" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K103" s="23" t="n"/>
       <c r="L103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
-        </is>
-      </c>
-      <c r="B104" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>PS5-08-04 - Hotline</t>
+        </is>
+      </c>
+      <c r="B104" s="23" t="inlineStr"/>
       <c r="C104" s="76" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="D104" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E104" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F104" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G104" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D104" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="65" t="inlineStr"/>
       <c r="H104" s="65" t="inlineStr"/>
-      <c r="I104" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J104" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I104" s="65" t="inlineStr"/>
+      <c r="J104" s="23" t="inlineStr"/>
       <c r="K104" s="23" t="n"/>
       <c r="L104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
-        </is>
-      </c>
-      <c r="B105" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="inlineStr"/>
       <c r="C105" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D105" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E105" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F105" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="D105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="65" t="inlineStr"/>
       <c r="H105" s="65" t="inlineStr"/>
-      <c r="I105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J105" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I105" s="65" t="inlineStr"/>
+      <c r="J105" s="23" t="inlineStr"/>
       <c r="K105" s="23" t="n"/>
       <c r="L105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
+          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
       </c>
       <c r="B106" s="23" t="inlineStr">
@@ -6164,7 +6120,7 @@
       </c>
       <c r="C106" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="D106" s="23" t="inlineStr">
@@ -6204,12 +6160,12 @@
     <row r="107">
       <c r="A107" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B107" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C107" s="76" t="inlineStr">
@@ -6254,12 +6210,12 @@
     <row r="108">
       <c r="A108" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
+          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
       </c>
       <c r="B108" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C108" s="76" t="inlineStr">
@@ -6304,7 +6260,7 @@
     <row r="109">
       <c r="A109" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-23 - VHF Trunk Radio System</t>
+          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
       </c>
       <c r="B109" s="23" t="inlineStr">
@@ -6354,7 +6310,7 @@
     <row r="110">
       <c r="A110" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-34 - Satphone</t>
+          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
       </c>
       <c r="B110" s="23" t="inlineStr">
@@ -6404,40 +6360,62 @@
     <row r="111">
       <c r="A111" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-35 - Optical Transport Network</t>
-        </is>
-      </c>
-      <c r="B111" s="23" t="inlineStr"/>
-      <c r="C111" s="77" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="D111" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="65" t="inlineStr"/>
+          <t>PS5-08-23 - VHF Trunk Radio System</t>
+        </is>
+      </c>
+      <c r="B111" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C111" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D111" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E111" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F111" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G111" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H111" s="65" t="inlineStr"/>
-      <c r="I111" s="65" t="inlineStr"/>
-      <c r="J111" s="23" t="inlineStr"/>
+      <c r="I111" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J111" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K111" s="23" t="n"/>
       <c r="L111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
+          <t>PS5-08-34 - Satphone</t>
         </is>
       </c>
       <c r="B112" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C112" s="76" t="inlineStr">
@@ -6482,67 +6460,45 @@
     <row r="113">
       <c r="A113" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-51 - Entertainment</t>
-        </is>
-      </c>
-      <c r="B113" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C113" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G113" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-08-35 - Optical Transport Network</t>
+        </is>
+      </c>
+      <c r="B113" s="23" t="inlineStr"/>
+      <c r="C113" s="77" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="D113" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="65" t="inlineStr"/>
       <c r="H113" s="65" t="inlineStr"/>
-      <c r="I113" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I113" s="65" t="inlineStr"/>
+      <c r="J113" s="23" t="inlineStr"/>
       <c r="K113" s="23" t="n"/>
       <c r="L113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-52 - Process &amp; Security CCTV</t>
+          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
       </c>
       <c r="B114" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C114" s="76" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D114" s="23" t="inlineStr">
@@ -6582,246 +6538,246 @@
     <row r="115">
       <c r="A115" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-55 - Videoconference</t>
-        </is>
-      </c>
-      <c r="B115" s="23" t="inlineStr"/>
+          <t>PS5-08-51 - Entertainment</t>
+        </is>
+      </c>
+      <c r="B115" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C115" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D115" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="65" t="inlineStr"/>
+      <c r="D115" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E115" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F115" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G115" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H115" s="65" t="inlineStr"/>
-      <c r="I115" s="65" t="inlineStr"/>
-      <c r="J115" s="23" t="inlineStr"/>
+      <c r="I115" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J115" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K115" s="23" t="n"/>
       <c r="L115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-61 - Meteocean</t>
-        </is>
-      </c>
-      <c r="B116" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
+        </is>
+      </c>
+      <c r="B116" s="23" t="inlineStr"/>
       <c r="C116" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D116" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E116" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F116" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G116" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="D116" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="65" t="inlineStr"/>
       <c r="H116" s="65" t="inlineStr"/>
-      <c r="I116" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J116" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I116" s="65" t="inlineStr"/>
+      <c r="J116" s="23" t="inlineStr"/>
       <c r="K116" s="23" t="n"/>
       <c r="L116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
-        </is>
-      </c>
-      <c r="B117" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
+        </is>
+      </c>
+      <c r="B117" s="23" t="inlineStr"/>
       <c r="C117" s="76" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D117" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E117" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F117" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D117" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="65" t="inlineStr"/>
       <c r="H117" s="65" t="inlineStr"/>
-      <c r="I117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J117" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I117" s="65" t="inlineStr"/>
+      <c r="J117" s="23" t="inlineStr"/>
       <c r="K117" s="23" t="n"/>
       <c r="L117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-72 - Structured Cabling (FO)</t>
-        </is>
-      </c>
-      <c r="B118" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>PS5-08-55 - Videoconference</t>
+        </is>
+      </c>
+      <c r="B118" s="23" t="inlineStr"/>
       <c r="C118" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="D118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="65" t="inlineStr"/>
       <c r="H118" s="65" t="inlineStr"/>
-      <c r="I118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I118" s="65" t="inlineStr"/>
+      <c r="J118" s="23" t="inlineStr"/>
       <c r="K118" s="23" t="n"/>
       <c r="L118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-81 - Guard tour</t>
-        </is>
-      </c>
-      <c r="B119" s="23" t="inlineStr"/>
+          <t>PS5-08-61 - Meteocean</t>
+        </is>
+      </c>
+      <c r="B119" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C119" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D119" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="65" t="inlineStr"/>
+      <c r="D119" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E119" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F119" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G119" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H119" s="65" t="inlineStr"/>
-      <c r="I119" s="65" t="inlineStr"/>
-      <c r="J119" s="23" t="inlineStr"/>
+      <c r="I119" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J119" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K119" s="23" t="n"/>
       <c r="L119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-82 - Key Management</t>
-        </is>
-      </c>
-      <c r="B120" s="23" t="inlineStr"/>
+          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
+        </is>
+      </c>
+      <c r="B120" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C120" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D120" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="65" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D120" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E120" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F120" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G120" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H120" s="65" t="inlineStr"/>
-      <c r="I120" s="65" t="inlineStr"/>
-      <c r="J120" s="23" t="inlineStr"/>
+      <c r="I120" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J120" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K120" s="23" t="n"/>
       <c r="L120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+          <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
       </c>
       <c r="B121" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C121" s="76" t="inlineStr">
@@ -6866,57 +6822,35 @@
     <row r="122">
       <c r="A122" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
-        </is>
-      </c>
-      <c r="B122" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-81 - Guard tour</t>
+        </is>
+      </c>
+      <c r="B122" s="23" t="inlineStr"/>
       <c r="C122" s="76" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="D122" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E122" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F122" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D122" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="65" t="inlineStr"/>
       <c r="H122" s="65" t="inlineStr"/>
-      <c r="I122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J122" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I122" s="65" t="inlineStr"/>
+      <c r="J122" s="23" t="inlineStr"/>
       <c r="K122" s="23" t="n"/>
       <c r="L122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-86 - Integrated Security Management System</t>
+          <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B123" s="23" t="inlineStr"/>
@@ -6944,35 +6878,57 @@
     <row r="124">
       <c r="A124" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-92 - Telecom Mast</t>
-        </is>
-      </c>
-      <c r="B124" s="23" t="inlineStr"/>
+          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+        </is>
+      </c>
+      <c r="B124" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C124" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="65" t="inlineStr"/>
+      <c r="D124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G124" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H124" s="65" t="inlineStr"/>
-      <c r="I124" s="65" t="inlineStr"/>
-      <c r="J124" s="23" t="inlineStr"/>
+      <c r="I124" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K124" s="23" t="n"/>
       <c r="L124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-93 - Telecom Monitoring System</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
       <c r="B125" s="23" t="inlineStr">
@@ -6982,7 +6938,7 @@
       </c>
       <c r="C125" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="D125" s="23" t="inlineStr">
@@ -7022,63 +6978,41 @@
     <row r="126">
       <c r="A126" s="68" t="inlineStr">
         <is>
-          <t>PS5-09-02 - HVAC for Guard House</t>
-        </is>
-      </c>
-      <c r="B126" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
+        </is>
+      </c>
+      <c r="B126" s="23" t="inlineStr"/>
       <c r="C126" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D126" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E126" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F126" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G126" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="D126" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="65" t="inlineStr"/>
       <c r="H126" s="65" t="inlineStr"/>
-      <c r="I126" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J126" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I126" s="65" t="inlineStr"/>
+      <c r="J126" s="23" t="inlineStr"/>
       <c r="K126" s="23" t="n"/>
       <c r="L126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="68" t="inlineStr">
         <is>
-          <t>PS5-0H-01 - HIPPS</t>
+          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
       </c>
       <c r="B127" s="23" t="inlineStr"/>
-      <c r="C127" s="77" t="inlineStr">
-        <is>
-          <t>71%</t>
+      <c r="C127" s="76" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
       <c r="D127" s="23" t="n">
@@ -7100,117 +7034,73 @@
     <row r="128">
       <c r="A128" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
-        </is>
-      </c>
-      <c r="B128" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C128" s="77" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="D128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G128" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>PS5-08-86 - Integrated Security Management System</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="inlineStr"/>
+      <c r="C128" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="65" t="inlineStr"/>
       <c r="H128" s="65" t="inlineStr"/>
-      <c r="I128" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I128" s="65" t="inlineStr"/>
+      <c r="J128" s="23" t="inlineStr"/>
       <c r="K128" s="23" t="n"/>
       <c r="L128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
-        </is>
-      </c>
-      <c r="B129" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C129" s="77" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="D129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-08-92 - Telecom Mast</t>
+        </is>
+      </c>
+      <c r="B129" s="23" t="inlineStr"/>
+      <c r="C129" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="65" t="inlineStr"/>
       <c r="H129" s="65" t="inlineStr"/>
-      <c r="I129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I129" s="65" t="inlineStr"/>
+      <c r="J129" s="23" t="inlineStr"/>
       <c r="K129" s="23" t="n"/>
       <c r="L129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
       </c>
       <c r="B130" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C130" s="77" t="inlineStr">
-        <is>
-          <t>75%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C130" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D130" s="23" t="inlineStr">
@@ -7250,17 +7140,17 @@
     <row r="131">
       <c r="A131" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
       </c>
       <c r="B131" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C131" s="77" t="inlineStr">
-        <is>
-          <t>73%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C131" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" s="23" t="inlineStr">
@@ -7300,57 +7190,35 @@
     <row r="132">
       <c r="A132" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
-        </is>
-      </c>
-      <c r="B132" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>PS5-0H-01 - HIPPS</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="inlineStr"/>
       <c r="C132" s="77" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="D132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="D132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="65" t="inlineStr"/>
       <c r="H132" s="65" t="inlineStr"/>
-      <c r="I132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I132" s="65" t="inlineStr"/>
+      <c r="J132" s="23" t="inlineStr"/>
       <c r="K132" s="23" t="n"/>
       <c r="L132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
+          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
       </c>
       <c r="B133" s="23" t="inlineStr">
@@ -7360,7 +7228,7 @@
       </c>
       <c r="C133" s="77" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="D133" s="23" t="inlineStr">
@@ -7380,7 +7248,7 @@
       </c>
       <c r="G133" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H133" s="65" t="inlineStr"/>
@@ -7400,7 +7268,7 @@
     <row r="134">
       <c r="A134" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B134" s="23" t="inlineStr">
@@ -7410,7 +7278,7 @@
       </c>
       <c r="C134" s="77" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="D134" s="23" t="inlineStr">
@@ -7450,7 +7318,7 @@
     <row r="135">
       <c r="A135" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-01 - Closed Drain Header 1</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B135" s="23" t="inlineStr">
@@ -7460,7 +7328,7 @@
       </c>
       <c r="C135" s="77" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="D135" s="23" t="inlineStr">
@@ -7500,17 +7368,17 @@
     <row r="136">
       <c r="A136" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B136" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C136" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C136" s="77" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="D136" s="23" t="inlineStr">
@@ -7550,7 +7418,7 @@
     <row r="137">
       <c r="A137" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="B137" s="23" t="inlineStr">
@@ -7560,7 +7428,7 @@
       </c>
       <c r="C137" s="77" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="D137" s="23" t="inlineStr">
@@ -7600,17 +7468,17 @@
     <row r="138">
       <c r="A138" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
       </c>
       <c r="B138" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C138" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C138" s="77" t="inlineStr">
+        <is>
+          <t>57%</t>
         </is>
       </c>
       <c r="D138" s="23" t="inlineStr">
@@ -7650,17 +7518,17 @@
     <row r="139">
       <c r="A139" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
       </c>
       <c r="B139" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C139" s="77" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="D139" s="23" t="inlineStr">
@@ -7700,7 +7568,7 @@
     <row r="140">
       <c r="A140" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
+          <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
       </c>
       <c r="B140" s="23" t="inlineStr">
@@ -7708,9 +7576,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C140" s="78" t="inlineStr">
-        <is>
-          <t>94%</t>
+      <c r="C140" s="77" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
       <c r="D140" s="23" t="inlineStr">
@@ -7750,17 +7618,17 @@
     <row r="141">
       <c r="A141" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="B141" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C141" s="76" t="inlineStr">
-        <is>
-          <t>44%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C141" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D141" s="23" t="inlineStr">
@@ -7800,7 +7668,7 @@
     <row r="142">
       <c r="A142" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-09 - Observation Basin</t>
+          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
       </c>
       <c r="B142" s="23" t="inlineStr">
@@ -7810,7 +7678,7 @@
       </c>
       <c r="C142" s="77" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D142" s="23" t="inlineStr">
@@ -7850,17 +7718,17 @@
     <row r="143">
       <c r="A143" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-10 - Oil Skimmer Package</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="B143" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C143" s="76" t="inlineStr">
-        <is>
-          <t>9%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C143" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D143" s="23" t="inlineStr">
@@ -7900,17 +7768,17 @@
     <row r="144">
       <c r="A144" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
       </c>
       <c r="B144" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C144" s="77" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D144" s="23" t="inlineStr">
@@ -7950,7 +7818,7 @@
     <row r="145">
       <c r="A145" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
       <c r="B145" s="23" t="inlineStr">
@@ -7958,9 +7826,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C145" s="77" t="inlineStr">
-        <is>
-          <t>65%</t>
+      <c r="C145" s="78" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="D145" s="23" t="inlineStr">
@@ -8000,17 +7868,17 @@
     <row r="146">
       <c r="A146" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
       <c r="B146" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C146" s="77" t="inlineStr">
-        <is>
-          <t>78%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C146" s="76" t="inlineStr">
+        <is>
+          <t>44%</t>
         </is>
       </c>
       <c r="D146" s="23" t="inlineStr">
@@ -8050,7 +7918,7 @@
     <row r="147">
       <c r="A147" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+          <t>PS5-28-09 - Observation Basin</t>
         </is>
       </c>
       <c r="B147" s="23" t="inlineStr">
@@ -8060,7 +7928,7 @@
       </c>
       <c r="C147" s="77" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="D147" s="23" t="inlineStr">
@@ -8100,7 +7968,7 @@
     <row r="148">
       <c r="A148" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+          <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
       </c>
       <c r="B148" s="23" t="inlineStr">
@@ -8108,9 +7976,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C148" s="77" t="inlineStr">
-        <is>
-          <t>75%</t>
+      <c r="C148" s="76" t="inlineStr">
+        <is>
+          <t>9%</t>
         </is>
       </c>
       <c r="D148" s="23" t="inlineStr">
@@ -8150,17 +8018,17 @@
     <row r="149">
       <c r="A149" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="B149" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C149" s="77" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="D149" s="23" t="inlineStr">
@@ -8200,17 +8068,17 @@
     <row r="150">
       <c r="A150" s="68" t="inlineStr">
         <is>
-          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="B150" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C150" s="76" t="inlineStr">
-        <is>
-          <t>38%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C150" s="77" t="inlineStr">
+        <is>
+          <t>65%</t>
         </is>
       </c>
       <c r="D150" s="23" t="inlineStr">
@@ -8250,17 +8118,17 @@
     <row r="151">
       <c r="A151" s="68" t="inlineStr">
         <is>
-          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
       </c>
       <c r="B151" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C151" s="76" t="inlineStr">
-        <is>
-          <t>42%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C151" s="77" t="inlineStr">
+        <is>
+          <t>78%</t>
         </is>
       </c>
       <c r="D151" s="23" t="inlineStr">
@@ -8300,17 +8168,17 @@
     <row r="152">
       <c r="A152" s="68" t="inlineStr">
         <is>
-          <t>PS5-50-03 - Water Pre-Treatment Package</t>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
       </c>
       <c r="B152" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C152" s="76" t="inlineStr">
-        <is>
-          <t>38%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C152" s="77" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
       <c r="D152" s="23" t="inlineStr">
@@ -8330,7 +8198,7 @@
       </c>
       <c r="G152" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H152" s="65" t="inlineStr"/>
@@ -8350,17 +8218,17 @@
     <row r="153">
       <c r="A153" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
       </c>
       <c r="B153" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C153" s="77" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="D153" s="23" t="inlineStr">
@@ -8400,7 +8268,7 @@
     <row r="154">
       <c r="A154" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-03 - Water Softener Package</t>
+          <t>PS5-28-16 - LP Relief Header</t>
         </is>
       </c>
       <c r="B154" s="23" t="inlineStr">
@@ -8410,7 +8278,7 @@
       </c>
       <c r="C154" s="77" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="D154" s="23" t="inlineStr">
@@ -8430,7 +8298,7 @@
       </c>
       <c r="G154" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H154" s="65" t="inlineStr"/>
@@ -8450,17 +8318,17 @@
     <row r="155">
       <c r="A155" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-04 - Water Treatment Purification Package</t>
+          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
       </c>
       <c r="B155" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C155" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="D155" s="23" t="inlineStr">
@@ -8480,7 +8348,7 @@
       </c>
       <c r="G155" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H155" s="65" t="inlineStr"/>
@@ -8500,17 +8368,17 @@
     <row r="156">
       <c r="A156" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
       </c>
       <c r="B156" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C156" s="78" t="inlineStr">
-        <is>
-          <t>97%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C156" s="76" t="inlineStr">
+        <is>
+          <t>42%</t>
         </is>
       </c>
       <c r="D156" s="23" t="inlineStr">
@@ -8550,17 +8418,17 @@
     <row r="157">
       <c r="A157" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-06 - Water Distribution Consumers</t>
+          <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
       </c>
       <c r="B157" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C157" s="77" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C157" s="76" t="inlineStr">
+        <is>
+          <t>38%</t>
         </is>
       </c>
       <c r="D157" s="23" t="inlineStr">
@@ -8580,7 +8448,7 @@
       </c>
       <c r="G157" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H157" s="65" t="inlineStr"/>
@@ -8600,17 +8468,17 @@
     <row r="158">
       <c r="A158" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="B158" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C158" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C158" s="77" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
       <c r="D158" s="23" t="inlineStr">
@@ -8641,7 +8509,7 @@
       </c>
       <c r="J158" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K158" s="23" t="n"/>
@@ -8650,37 +8518,37 @@
     <row r="159">
       <c r="A159" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-53-03 - Water Softener Package</t>
         </is>
       </c>
       <c r="B159" s="23" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C159" s="77" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="D159" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E159" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F159" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G159" s="65" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C159" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D159" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E159" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F159" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G159" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H159" s="65" t="inlineStr"/>
@@ -8700,7 +8568,7 @@
     <row r="160">
       <c r="A160" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
       </c>
       <c r="B160" s="23" t="inlineStr">
@@ -8708,9 +8576,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C160" s="78" t="inlineStr">
-        <is>
-          <t>98%</t>
+      <c r="C160" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D160" s="23" t="inlineStr">
@@ -8730,7 +8598,7 @@
       </c>
       <c r="G160" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H160" s="65" t="inlineStr"/>
@@ -8750,7 +8618,7 @@
     <row r="161">
       <c r="A161" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="B161" s="23" t="inlineStr">
@@ -8760,7 +8628,7 @@
       </c>
       <c r="C161" s="78" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D161" s="23" t="inlineStr">
@@ -8784,25 +8652,33 @@
         </is>
       </c>
       <c r="H161" s="65" t="inlineStr"/>
-      <c r="I161" s="65" t="inlineStr"/>
-      <c r="J161" s="23" t="inlineStr"/>
+      <c r="I161" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J161" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K161" s="23" t="n"/>
       <c r="L161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
       </c>
       <c r="B162" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C162" s="77" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="D162" s="23" t="inlineStr">
@@ -8826,25 +8702,33 @@
         </is>
       </c>
       <c r="H162" s="65" t="inlineStr"/>
-      <c r="I162" s="65" t="inlineStr"/>
-      <c r="J162" s="23" t="inlineStr"/>
+      <c r="I162" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J162" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K162" s="23" t="n"/>
       <c r="L162" s="67" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="B163" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C163" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D163" s="23" t="inlineStr">
@@ -8868,25 +8752,33 @@
         </is>
       </c>
       <c r="H163" s="65" t="inlineStr"/>
-      <c r="I163" s="65" t="inlineStr"/>
-      <c r="J163" s="23" t="inlineStr"/>
+      <c r="I163" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J163" s="23" t="inlineStr">
+        <is>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+        </is>
+      </c>
       <c r="K163" s="23" t="n"/>
       <c r="L163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="B164" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C164" s="77" t="inlineStr">
-        <is>
-          <t>86%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D164" s="23" t="inlineStr">
@@ -8910,15 +8802,23 @@
         </is>
       </c>
       <c r="H164" s="65" t="inlineStr"/>
-      <c r="I164" s="65" t="inlineStr"/>
-      <c r="J164" s="23" t="inlineStr"/>
+      <c r="I164" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J164" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K164" s="23" t="n"/>
       <c r="L164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-19 - Power Generation Package G</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="B165" s="23" t="inlineStr">
@@ -8928,7 +8828,7 @@
       </c>
       <c r="C165" s="78" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="D165" s="23" t="inlineStr">
@@ -8968,7 +8868,7 @@
     <row r="166">
       <c r="A166" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="B166" s="23" t="inlineStr">
@@ -8976,9 +8876,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C166" s="77" t="inlineStr">
-        <is>
-          <t>60%</t>
+      <c r="C166" s="78" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D166" s="23" t="inlineStr">
@@ -9010,7 +8910,7 @@
     <row r="167">
       <c r="A167" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B167" s="23" t="inlineStr">
@@ -9020,7 +8920,7 @@
       </c>
       <c r="C167" s="77" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D167" s="23" t="inlineStr">
@@ -9052,17 +8952,17 @@
     <row r="168">
       <c r="A168" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="B168" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C168" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C168" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D168" s="23" t="inlineStr">
@@ -9086,33 +8986,25 @@
         </is>
       </c>
       <c r="H168" s="65" t="inlineStr"/>
-      <c r="I168" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J168" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I168" s="65" t="inlineStr"/>
+      <c r="J168" s="23" t="inlineStr"/>
       <c r="K168" s="23" t="n"/>
       <c r="L168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B169" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C169" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C169" s="77" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="D169" s="23" t="inlineStr">
@@ -9136,33 +9028,25 @@
         </is>
       </c>
       <c r="H169" s="65" t="inlineStr"/>
-      <c r="I169" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J169" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I169" s="65" t="inlineStr"/>
+      <c r="J169" s="23" t="inlineStr"/>
       <c r="K169" s="23" t="n"/>
       <c r="L169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-19 - Power Generation Package G</t>
         </is>
       </c>
       <c r="B170" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C170" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="D170" s="23" t="inlineStr">
@@ -9202,17 +9086,17 @@
     <row r="171">
       <c r="A171" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="B171" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C171" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C171" s="77" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="D171" s="23" t="inlineStr">
@@ -9236,33 +9120,25 @@
         </is>
       </c>
       <c r="H171" s="65" t="inlineStr"/>
-      <c r="I171" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J171" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I171" s="65" t="inlineStr"/>
+      <c r="J171" s="23" t="inlineStr"/>
       <c r="K171" s="23" t="n"/>
       <c r="L171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B172" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C172" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C172" s="77" t="inlineStr">
+        <is>
+          <t>83%</t>
         </is>
       </c>
       <c r="D172" s="23" t="inlineStr">
@@ -9286,28 +9162,20 @@
         </is>
       </c>
       <c r="H172" s="65" t="inlineStr"/>
-      <c r="I172" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J172" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I172" s="65" t="inlineStr"/>
+      <c r="J172" s="23" t="inlineStr"/>
       <c r="K172" s="23" t="n"/>
       <c r="L172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="B173" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C173" s="78" t="inlineStr">
@@ -9352,12 +9220,12 @@
     <row r="174">
       <c r="A174" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="B174" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C174" s="78" t="inlineStr">
@@ -9402,12 +9270,12 @@
     <row r="175">
       <c r="A175" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="B175" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C175" s="78" t="inlineStr">
@@ -9452,12 +9320,12 @@
     <row r="176">
       <c r="A176" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="B176" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C176" s="78" t="inlineStr">
@@ -9502,12 +9370,12 @@
     <row r="177">
       <c r="A177" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="B177" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C177" s="78" t="inlineStr">
@@ -9552,12 +9420,12 @@
     <row r="178">
       <c r="A178" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="B178" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C178" s="78" t="inlineStr">
@@ -9602,12 +9470,12 @@
     <row r="179">
       <c r="A179" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="B179" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C179" s="78" t="inlineStr">
@@ -9652,12 +9520,12 @@
     <row r="180">
       <c r="A180" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="B180" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C180" s="78" t="inlineStr">
@@ -9702,12 +9570,12 @@
     <row r="181">
       <c r="A181" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="B181" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C181" s="78" t="inlineStr">
@@ -9752,7 +9620,7 @@
     <row r="182">
       <c r="A182" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="B182" s="23" t="inlineStr">
@@ -9802,12 +9670,12 @@
     <row r="183">
       <c r="A183" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="B183" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C183" s="78" t="inlineStr">
@@ -9852,17 +9720,17 @@
     <row r="184">
       <c r="A184" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="B184" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C184" s="77" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D184" s="23" t="inlineStr">
@@ -9902,12 +9770,12 @@
     <row r="185">
       <c r="A185" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="B185" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C185" s="78" t="inlineStr">
@@ -9952,12 +9820,12 @@
     <row r="186">
       <c r="A186" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="B186" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C186" s="78" t="inlineStr">
@@ -10002,12 +9870,12 @@
     <row r="187">
       <c r="A187" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="B187" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C187" s="78" t="inlineStr">
@@ -10052,12 +9920,12 @@
     <row r="188">
       <c r="A188" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="B188" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C188" s="78" t="inlineStr">
@@ -10102,7 +9970,7 @@
     <row r="189">
       <c r="A189" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="B189" s="23" t="inlineStr">
@@ -10110,9 +9978,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C189" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C189" s="77" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="D189" s="23" t="inlineStr">
@@ -10152,12 +10020,12 @@
     <row r="190">
       <c r="A190" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="B190" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C190" s="78" t="inlineStr">
@@ -10202,17 +10070,17 @@
     <row r="191">
       <c r="A191" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="B191" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C191" s="78" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D191" s="23" t="inlineStr">
@@ -10252,7 +10120,7 @@
     <row r="192">
       <c r="A192" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="B192" s="23" t="inlineStr">
@@ -10262,7 +10130,7 @@
       </c>
       <c r="C192" s="78" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D192" s="23" t="inlineStr">
@@ -10286,15 +10154,23 @@
         </is>
       </c>
       <c r="H192" s="65" t="inlineStr"/>
-      <c r="I192" s="65" t="inlineStr"/>
-      <c r="J192" s="23" t="inlineStr"/>
+      <c r="I192" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J192" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K192" s="23" t="n"/>
       <c r="L192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="B193" s="23" t="inlineStr">
@@ -10302,9 +10178,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C193" s="77" t="inlineStr">
-        <is>
-          <t>89%</t>
+      <c r="C193" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D193" s="23" t="inlineStr">
@@ -10328,15 +10204,23 @@
         </is>
       </c>
       <c r="H193" s="65" t="inlineStr"/>
-      <c r="I193" s="65" t="inlineStr"/>
-      <c r="J193" s="23" t="inlineStr"/>
+      <c r="I193" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J193" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K193" s="23" t="n"/>
       <c r="L193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="B194" s="23" t="inlineStr">
@@ -10346,7 +10230,7 @@
       </c>
       <c r="C194" s="78" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D194" s="23" t="inlineStr">
@@ -10370,15 +10254,23 @@
         </is>
       </c>
       <c r="H194" s="65" t="inlineStr"/>
-      <c r="I194" s="65" t="inlineStr"/>
-      <c r="J194" s="23" t="inlineStr"/>
+      <c r="I194" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J194" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K194" s="23" t="n"/>
       <c r="L194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="B195" s="23" t="inlineStr">
@@ -10388,7 +10280,7 @@
       </c>
       <c r="C195" s="78" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D195" s="23" t="inlineStr">
@@ -10412,15 +10304,23 @@
         </is>
       </c>
       <c r="H195" s="65" t="inlineStr"/>
-      <c r="I195" s="65" t="inlineStr"/>
-      <c r="J195" s="23" t="inlineStr"/>
+      <c r="I195" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J195" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K195" s="23" t="n"/>
       <c r="L195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="B196" s="23" t="inlineStr">
@@ -10428,9 +10328,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C196" s="77" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="C196" s="78" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="D196" s="23" t="inlineStr">
@@ -10454,15 +10354,23 @@
         </is>
       </c>
       <c r="H196" s="65" t="inlineStr"/>
-      <c r="I196" s="65" t="inlineStr"/>
-      <c r="J196" s="23" t="inlineStr"/>
+      <c r="I196" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J196" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K196" s="23" t="n"/>
       <c r="L196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="B197" s="23" t="inlineStr">
@@ -10472,7 +10380,7 @@
       </c>
       <c r="C197" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D197" s="23" t="inlineStr">
@@ -10504,7 +10412,7 @@
     <row r="198">
       <c r="A198" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="B198" s="23" t="inlineStr">
@@ -10512,9 +10420,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C198" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C198" s="77" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="D198" s="23" t="inlineStr">
@@ -10546,7 +10454,7 @@
     <row r="199">
       <c r="A199" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="B199" s="23" t="inlineStr">
@@ -10554,9 +10462,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C199" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="C199" s="78" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="D199" s="23" t="inlineStr">
@@ -10588,7 +10496,7 @@
     <row r="200">
       <c r="A200" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="B200" s="23" t="inlineStr">
@@ -10596,9 +10504,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C200" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="C200" s="78" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="D200" s="23" t="inlineStr">
@@ -10630,7 +10538,7 @@
     <row r="201">
       <c r="A201" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="B201" s="23" t="inlineStr">
@@ -10640,7 +10548,7 @@
       </c>
       <c r="C201" s="77" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="D201" s="23" t="inlineStr">
@@ -10672,12 +10580,12 @@
     <row r="202">
       <c r="A202" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="B202" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C202" s="78" t="inlineStr">
@@ -10706,28 +10614,20 @@
         </is>
       </c>
       <c r="H202" s="65" t="inlineStr"/>
-      <c r="I202" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J202" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I202" s="65" t="inlineStr"/>
+      <c r="J202" s="23" t="inlineStr"/>
       <c r="K202" s="23" t="n"/>
       <c r="L202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="B203" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C203" s="78" t="inlineStr">
@@ -10756,33 +10656,25 @@
         </is>
       </c>
       <c r="H203" s="65" t="inlineStr"/>
-      <c r="I203" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J203" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I203" s="65" t="inlineStr"/>
+      <c r="J203" s="23" t="inlineStr"/>
       <c r="K203" s="23" t="n"/>
       <c r="L203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="B204" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C204" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C204" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D204" s="23" t="inlineStr">
@@ -10806,33 +10698,25 @@
         </is>
       </c>
       <c r="H204" s="65" t="inlineStr"/>
-      <c r="I204" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J204" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I204" s="65" t="inlineStr"/>
+      <c r="J204" s="23" t="inlineStr"/>
       <c r="K204" s="23" t="n"/>
       <c r="L204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="B205" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C205" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C205" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D205" s="23" t="inlineStr">
@@ -10856,23 +10740,15 @@
         </is>
       </c>
       <c r="H205" s="65" t="inlineStr"/>
-      <c r="I205" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J205" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I205" s="65" t="inlineStr"/>
+      <c r="J205" s="23" t="inlineStr"/>
       <c r="K205" s="23" t="n"/>
       <c r="L205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="B206" s="23" t="inlineStr">
@@ -10880,9 +10756,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C206" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C206" s="77" t="inlineStr">
+        <is>
+          <t>71%</t>
         </is>
       </c>
       <c r="D206" s="23" t="inlineStr">
@@ -10906,28 +10782,20 @@
         </is>
       </c>
       <c r="H206" s="65" t="inlineStr"/>
-      <c r="I206" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J206" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I206" s="65" t="inlineStr"/>
+      <c r="J206" s="23" t="inlineStr"/>
       <c r="K206" s="23" t="n"/>
       <c r="L206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="B207" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C207" s="78" t="inlineStr">
@@ -10972,17 +10840,17 @@
     <row r="208">
       <c r="A208" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="B208" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C208" s="78" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D208" s="23" t="inlineStr">
@@ -11022,17 +10890,17 @@
     <row r="209">
       <c r="A209" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="B209" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C209" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C209" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D209" s="23" t="inlineStr">
@@ -11072,17 +10940,17 @@
     <row r="210">
       <c r="A210" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="B210" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C210" s="77" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C210" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D210" s="23" t="inlineStr">
@@ -11122,12 +10990,12 @@
     <row r="211">
       <c r="A211" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="B211" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C211" s="78" t="inlineStr">
@@ -11172,7 +11040,7 @@
     <row r="212">
       <c r="A212" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-08 - Electrical Control System</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="B212" s="23" t="inlineStr">
@@ -11180,9 +11048,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C212" s="76" t="inlineStr">
-        <is>
-          <t>21%</t>
+      <c r="C212" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D212" s="23" t="inlineStr">
@@ -11222,7 +11090,7 @@
     <row r="213">
       <c r="A213" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="B213" s="23" t="inlineStr">
@@ -11230,9 +11098,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C213" s="76" t="inlineStr">
-        <is>
-          <t>5%</t>
+      <c r="C213" s="78" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D213" s="23" t="inlineStr">
@@ -11272,17 +11140,17 @@
     <row r="214">
       <c r="A214" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="B214" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C214" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C214" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D214" s="23" t="inlineStr">
@@ -11322,17 +11190,17 @@
     <row r="215">
       <c r="A215" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="B215" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C215" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C215" s="77" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="D215" s="23" t="inlineStr">
@@ -11372,45 +11240,67 @@
     <row r="216">
       <c r="A216" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
-        </is>
-      </c>
-      <c r="B216" s="23" t="inlineStr"/>
-      <c r="C216" s="76" t="inlineStr">
-        <is>
-          <t>32%</t>
-        </is>
-      </c>
-      <c r="D216" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E216" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F216" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" s="65" t="inlineStr"/>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+        </is>
+      </c>
+      <c r="B216" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C216" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D216" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E216" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F216" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G216" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H216" s="65" t="inlineStr"/>
-      <c r="I216" s="65" t="inlineStr"/>
-      <c r="J216" s="23" t="inlineStr"/>
+      <c r="I216" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J216" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K216" s="23" t="n"/>
       <c r="L216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
+          <t>PS5-61-08 - Electrical Control System</t>
         </is>
       </c>
       <c r="B217" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C217" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="D217" s="23" t="inlineStr">
@@ -11450,17 +11340,17 @@
     <row r="218">
       <c r="A218" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
+          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
       </c>
       <c r="B218" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C218" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="D218" s="23" t="inlineStr">
@@ -11500,7 +11390,7 @@
     <row r="219">
       <c r="A219" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="B219" s="23" t="inlineStr">
@@ -11508,9 +11398,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C219" s="76" t="inlineStr">
-        <is>
-          <t>6%</t>
+      <c r="C219" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D219" s="23" t="inlineStr">
@@ -11550,17 +11440,17 @@
     <row r="220">
       <c r="A220" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="B220" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C220" s="76" t="inlineStr">
-        <is>
-          <t>4%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C220" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D220" s="23" t="inlineStr">
@@ -11600,67 +11490,45 @@
     <row r="221">
       <c r="A221" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
-        </is>
-      </c>
-      <c r="B221" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C221" s="77" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="D221" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E221" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F221" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
+        </is>
+      </c>
+      <c r="B221" s="23" t="inlineStr"/>
+      <c r="C221" s="76" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="D221" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" s="65" t="inlineStr"/>
       <c r="H221" s="65" t="inlineStr"/>
-      <c r="I221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J221" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I221" s="65" t="inlineStr"/>
+      <c r="J221" s="23" t="inlineStr"/>
       <c r="K221" s="23" t="n"/>
       <c r="L221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
       </c>
       <c r="B222" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C222" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C222" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D222" s="23" t="inlineStr">
@@ -11700,7 +11568,7 @@
     <row r="223">
       <c r="A223" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
       </c>
       <c r="B223" s="23" t="inlineStr">
@@ -11750,17 +11618,17 @@
     <row r="224">
       <c r="A224" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
+          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
       </c>
       <c r="B224" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C224" s="76" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="D224" s="23" t="inlineStr">
@@ -11800,17 +11668,17 @@
     <row r="225">
       <c r="A225" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
       </c>
       <c r="B225" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C225" s="76" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D225" s="23" t="inlineStr">
@@ -11850,7 +11718,7 @@
     <row r="226">
       <c r="A226" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="B226" s="23" t="inlineStr">
@@ -11858,9 +11726,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C226" s="76" t="inlineStr">
-        <is>
-          <t>5%</t>
+      <c r="C226" s="77" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="D226" s="23" t="inlineStr">
@@ -11900,7 +11768,7 @@
     <row r="227">
       <c r="A227" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="B227" s="23" t="inlineStr">
@@ -11908,9 +11776,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C227" s="76" t="inlineStr">
-        <is>
-          <t>46%</t>
+      <c r="C227" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D227" s="23" t="inlineStr">
@@ -11950,17 +11818,17 @@
     <row r="228">
       <c r="A228" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B228" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C228" s="76" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D228" s="23" t="inlineStr">
@@ -12000,7 +11868,7 @@
     <row r="229">
       <c r="A229" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
       </c>
       <c r="B229" s="23" t="inlineStr">
@@ -12010,7 +11878,7 @@
       </c>
       <c r="C229" s="76" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="D229" s="23" t="inlineStr">
@@ -12050,73 +11918,117 @@
     <row r="230">
       <c r="A230" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
-        </is>
-      </c>
-      <c r="B230" s="23" t="inlineStr"/>
-      <c r="C230" s="78" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="D230" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E230" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F230" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" s="65" t="inlineStr"/>
+          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+        </is>
+      </c>
+      <c r="B230" s="23" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C230" s="76" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="D230" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E230" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F230" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G230" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H230" s="65" t="inlineStr"/>
-      <c r="I230" s="65" t="inlineStr"/>
-      <c r="J230" s="23" t="inlineStr"/>
+      <c r="I230" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J230" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K230" s="23" t="n"/>
       <c r="L230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
-        </is>
-      </c>
-      <c r="B231" s="23" t="inlineStr"/>
-      <c r="C231" s="78" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="D231" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E231" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F231" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" s="65" t="inlineStr"/>
+          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+        </is>
+      </c>
+      <c r="B231" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C231" s="76" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D231" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E231" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F231" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G231" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H231" s="65" t="inlineStr"/>
-      <c r="I231" s="65" t="inlineStr"/>
-      <c r="J231" s="23" t="inlineStr"/>
+      <c r="I231" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J231" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K231" s="23" t="n"/>
       <c r="L231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
       </c>
       <c r="B232" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C232" s="76" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="D232" s="23" t="inlineStr">
@@ -12156,17 +12068,17 @@
     <row r="233">
       <c r="A233" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
       </c>
       <c r="B233" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C233" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="D233" s="23" t="inlineStr">
@@ -12206,17 +12118,17 @@
     <row r="234">
       <c r="A234" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
       </c>
       <c r="B234" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C234" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="D234" s="23" t="inlineStr">
@@ -12256,107 +12168,63 @@
     <row r="235">
       <c r="A235" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
-        </is>
-      </c>
-      <c r="B235" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C235" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D235" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E235" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F235" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G235" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
+        </is>
+      </c>
+      <c r="B235" s="23" t="inlineStr"/>
+      <c r="C235" s="78" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="D235" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="65" t="inlineStr"/>
       <c r="H235" s="65" t="inlineStr"/>
-      <c r="I235" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J235" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I235" s="65" t="inlineStr"/>
+      <c r="J235" s="23" t="inlineStr"/>
       <c r="K235" s="23" t="n"/>
       <c r="L235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
-        </is>
-      </c>
-      <c r="B236" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C236" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D236" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E236" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F236" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
+        </is>
+      </c>
+      <c r="B236" s="23" t="inlineStr"/>
+      <c r="C236" s="78" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="D236" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="65" t="inlineStr"/>
       <c r="H236" s="65" t="inlineStr"/>
-      <c r="I236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J236" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I236" s="65" t="inlineStr"/>
+      <c r="J236" s="23" t="inlineStr"/>
       <c r="K236" s="23" t="n"/>
       <c r="L236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B237" s="23" t="inlineStr">
@@ -12366,7 +12234,7 @@
       </c>
       <c r="C237" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D237" s="23" t="inlineStr">
@@ -12406,7 +12274,7 @@
     <row r="238">
       <c r="A238" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B238" s="23" t="inlineStr">
@@ -12456,12 +12324,12 @@
     <row r="239">
       <c r="A239" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B239" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C239" s="76" t="inlineStr">
@@ -12506,40 +12374,62 @@
     <row r="240">
       <c r="A240" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
-        </is>
-      </c>
-      <c r="B240" s="23" t="inlineStr"/>
-      <c r="C240" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D240" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E240" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F240" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" s="65" t="inlineStr"/>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+        </is>
+      </c>
+      <c r="B240" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C240" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D240" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E240" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F240" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G240" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H240" s="65" t="inlineStr"/>
-      <c r="I240" s="65" t="inlineStr"/>
-      <c r="J240" s="23" t="inlineStr"/>
+      <c r="I240" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J240" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K240" s="23" t="n"/>
       <c r="L240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
+          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
       </c>
       <c r="B241" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C241" s="76" t="inlineStr">
@@ -12584,12 +12474,12 @@
     <row r="242">
       <c r="A242" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
+          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
       </c>
       <c r="B242" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C242" s="76" t="inlineStr">
@@ -12634,12 +12524,12 @@
     <row r="243">
       <c r="A243" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B243" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C243" s="76" t="inlineStr">
@@ -12684,17 +12574,17 @@
     <row r="244">
       <c r="A244" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
       </c>
       <c r="B244" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C244" s="77" t="inlineStr">
-        <is>
-          <t>71%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C244" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D244" s="23" t="inlineStr">
@@ -12734,13 +12624,13 @@
     <row r="245">
       <c r="A245" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="B245" s="23" t="inlineStr"/>
-      <c r="C245" s="76" t="inlineStr">
-        <is>
-          <t>47%</t>
+      <c r="C245" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D245" s="23" t="n">
@@ -12762,17 +12652,17 @@
     <row r="246">
       <c r="A246" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
+          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
       </c>
       <c r="B246" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C246" s="77" t="inlineStr">
-        <is>
-          <t>66%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C246" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D246" s="23" t="inlineStr">
@@ -12812,17 +12702,17 @@
     <row r="247">
       <c r="A247" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
       </c>
       <c r="B247" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C247" s="78" t="inlineStr">
-        <is>
-          <t>95%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C247" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D247" s="23" t="inlineStr">
@@ -12846,25 +12736,33 @@
         </is>
       </c>
       <c r="H247" s="65" t="inlineStr"/>
-      <c r="I247" s="65" t="inlineStr"/>
-      <c r="J247" s="23" t="inlineStr"/>
+      <c r="I247" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J247" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K247" s="23" t="n"/>
       <c r="L247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B248" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C248" s="77" t="inlineStr">
-        <is>
-          <t>66%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C248" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D248" s="23" t="inlineStr">
@@ -12904,7 +12802,7 @@
     <row r="249">
       <c r="A249" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="B249" s="23" t="inlineStr">
@@ -12914,7 +12812,7 @@
       </c>
       <c r="C249" s="77" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="D249" s="23" t="inlineStr">
@@ -12954,57 +12852,35 @@
     <row r="250">
       <c r="A250" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
-        </is>
-      </c>
-      <c r="B250" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C250" s="77" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="D250" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E250" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F250" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+        </is>
+      </c>
+      <c r="B250" s="23" t="inlineStr"/>
+      <c r="C250" s="76" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="D250" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="65" t="inlineStr"/>
       <c r="H250" s="65" t="inlineStr"/>
-      <c r="I250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J250" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I250" s="65" t="inlineStr"/>
+      <c r="J250" s="23" t="inlineStr"/>
       <c r="K250" s="23" t="n"/>
       <c r="L250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B251" s="23" t="inlineStr">
@@ -13014,7 +12890,7 @@
       </c>
       <c r="C251" s="77" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="D251" s="23" t="inlineStr">
@@ -13054,17 +12930,17 @@
     <row r="252">
       <c r="A252" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
       </c>
       <c r="B252" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C252" s="78" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="D252" s="23" t="inlineStr">
@@ -13088,33 +12964,25 @@
         </is>
       </c>
       <c r="H252" s="65" t="inlineStr"/>
-      <c r="I252" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J252" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I252" s="65" t="inlineStr"/>
+      <c r="J252" s="23" t="inlineStr"/>
       <c r="K252" s="23" t="n"/>
       <c r="L252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B253" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C253" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C253" s="77" t="inlineStr">
+        <is>
+          <t>66%</t>
         </is>
       </c>
       <c r="D253" s="23" t="inlineStr">
@@ -13154,7 +13022,7 @@
     <row r="254">
       <c r="A254" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="B254" s="23" t="inlineStr">
@@ -13164,7 +13032,7 @@
       </c>
       <c r="C254" s="77" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="D254" s="23" t="inlineStr">
@@ -13204,7 +13072,7 @@
     <row r="255">
       <c r="A255" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B255" s="23" t="inlineStr">
@@ -13214,7 +13082,7 @@
       </c>
       <c r="C255" s="77" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="D255" s="23" t="inlineStr">
@@ -13254,7 +13122,7 @@
     <row r="256">
       <c r="A256" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="B256" s="23" t="inlineStr">
@@ -13262,9 +13130,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C256" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C256" s="77" t="inlineStr">
+        <is>
+          <t>82%</t>
         </is>
       </c>
       <c r="D256" s="23" t="inlineStr">
@@ -13304,7 +13172,7 @@
     <row r="257">
       <c r="A257" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
       </c>
       <c r="B257" s="23" t="inlineStr">
@@ -13312,9 +13180,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C257" s="77" t="inlineStr">
-        <is>
-          <t>81%</t>
+      <c r="C257" s="78" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D257" s="23" t="inlineStr">
@@ -13354,17 +13222,17 @@
     <row r="258">
       <c r="A258" s="68" t="inlineStr">
         <is>
-          <t>PS5-75-01 - DRA Injection Package</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="B258" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C258" s="76" t="inlineStr">
-        <is>
-          <t>37%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C258" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D258" s="23" t="inlineStr">
@@ -13384,7 +13252,7 @@
       </c>
       <c r="G258" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H258" s="65" t="inlineStr"/>
@@ -13404,17 +13272,17 @@
     <row r="259">
       <c r="A259" s="68" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="B259" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C259" s="77" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D259" s="23" t="inlineStr">
@@ -13454,17 +13322,17 @@
     <row r="260">
       <c r="A260" s="68" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
       </c>
       <c r="B260" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C260" s="77" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="D260" s="23" t="inlineStr">
@@ -13504,17 +13372,17 @@
     <row r="261">
       <c r="A261" s="68" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="B261" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C261" s="77" t="inlineStr">
-        <is>
-          <t>73%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C261" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D261" s="23" t="inlineStr">
@@ -13554,17 +13422,17 @@
     <row r="262">
       <c r="A262" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="B262" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C262" s="76" t="inlineStr">
-        <is>
-          <t>10%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C262" s="77" t="inlineStr">
+        <is>
+          <t>81%</t>
         </is>
       </c>
       <c r="D262" s="23" t="inlineStr">
@@ -13604,7 +13472,7 @@
     <row r="263">
       <c r="A263" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
+          <t>PS5-75-01 - DRA Injection Package</t>
         </is>
       </c>
       <c r="B263" s="23" t="inlineStr">
@@ -13614,7 +13482,7 @@
       </c>
       <c r="C263" s="76" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="D263" s="23" t="inlineStr">
@@ -13634,7 +13502,7 @@
       </c>
       <c r="G263" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H263" s="65" t="inlineStr"/>
@@ -13654,7 +13522,7 @@
     <row r="264">
       <c r="A264" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="B264" s="23" t="inlineStr">
@@ -13662,9 +13530,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C264" s="76" t="inlineStr">
-        <is>
-          <t>10%</t>
+      <c r="C264" s="77" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
       <c r="D264" s="23" t="inlineStr">
@@ -13704,7 +13572,7 @@
     <row r="265">
       <c r="A265" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
       </c>
       <c r="B265" s="23" t="inlineStr">
@@ -13712,9 +13580,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C265" s="76" t="inlineStr">
-        <is>
-          <t>31%</t>
+      <c r="C265" s="77" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
       <c r="D265" s="23" t="inlineStr">
@@ -13754,7 +13622,7 @@
     <row r="266">
       <c r="A266" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
       <c r="B266" s="23" t="inlineStr">
@@ -13762,9 +13630,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C266" s="76" t="inlineStr">
-        <is>
-          <t>24%</t>
+      <c r="C266" s="77" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="D266" s="23" t="inlineStr">
@@ -13804,7 +13672,7 @@
     <row r="267">
       <c r="A267" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
+          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
       </c>
       <c r="B267" s="23" t="inlineStr">
@@ -13814,7 +13682,7 @@
       </c>
       <c r="C267" s="76" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D267" s="23" t="inlineStr">
@@ -13854,7 +13722,7 @@
     <row r="268">
       <c r="A268" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
+          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
       </c>
       <c r="B268" s="23" t="inlineStr">
@@ -13864,7 +13732,7 @@
       </c>
       <c r="C268" s="76" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="D268" s="23" t="inlineStr">
@@ -13904,7 +13772,7 @@
     <row r="269">
       <c r="A269" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
+          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
       </c>
       <c r="B269" s="23" t="inlineStr">
@@ -13914,7 +13782,7 @@
       </c>
       <c r="C269" s="76" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D269" s="23" t="inlineStr">
@@ -13954,7 +13822,7 @@
     <row r="270">
       <c r="A270" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
+          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
       </c>
       <c r="B270" s="23" t="inlineStr">
@@ -13964,7 +13832,7 @@
       </c>
       <c r="C270" s="76" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="D270" s="23" t="inlineStr">
@@ -14004,7 +13872,7 @@
     <row r="271">
       <c r="A271" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
+          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
       </c>
       <c r="B271" s="23" t="inlineStr">
@@ -14014,7 +13882,7 @@
       </c>
       <c r="C271" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="D271" s="23" t="inlineStr">
@@ -14054,7 +13922,7 @@
     <row r="272">
       <c r="A272" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
+          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
       </c>
       <c r="B272" s="23" t="inlineStr">
@@ -14064,7 +13932,7 @@
       </c>
       <c r="C272" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="D272" s="23" t="inlineStr">
@@ -14104,7 +13972,7 @@
     <row r="273">
       <c r="A273" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
+          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
       </c>
       <c r="B273" s="23" t="inlineStr">
@@ -14114,7 +13982,7 @@
       </c>
       <c r="C273" s="76" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="D273" s="23" t="inlineStr">
@@ -14154,17 +14022,17 @@
     <row r="274">
       <c r="A274" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
       </c>
       <c r="B274" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C274" s="77" t="inlineStr">
-        <is>
-          <t>60%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C274" s="76" t="inlineStr">
+        <is>
+          <t>8%</t>
         </is>
       </c>
       <c r="D274" s="23" t="inlineStr">
@@ -14204,12 +14072,12 @@
     <row r="275">
       <c r="A275" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
+          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
       </c>
       <c r="B275" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C275" s="76" t="inlineStr">
@@ -14254,17 +14122,17 @@
     <row r="276">
       <c r="A276" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
+          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
       </c>
       <c r="B276" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C276" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="D276" s="23" t="inlineStr">
@@ -14304,17 +14172,17 @@
     <row r="277">
       <c r="A277" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
+          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
       </c>
       <c r="B277" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C277" s="77" t="inlineStr">
-        <is>
-          <t>75%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C277" s="76" t="inlineStr">
+        <is>
+          <t>11%</t>
         </is>
       </c>
       <c r="D277" s="23" t="inlineStr">
@@ -14354,17 +14222,17 @@
     <row r="278">
       <c r="A278" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
       </c>
       <c r="B278" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C278" s="76" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="D278" s="23" t="inlineStr">
@@ -14404,17 +14272,17 @@
     <row r="279">
       <c r="A279" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="B279" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C279" s="76" t="inlineStr">
-        <is>
-          <t>8%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C279" s="77" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="D279" s="23" t="inlineStr">
@@ -14454,17 +14322,17 @@
     <row r="280">
       <c r="A280" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-07 - Guard Huts</t>
+          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
       </c>
       <c r="B280" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C280" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="D280" s="23" t="inlineStr">
@@ -14504,17 +14372,17 @@
     <row r="281">
       <c r="A281" s="68" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
       </c>
       <c r="B281" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C281" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C281" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D281" s="23" t="inlineStr">
@@ -14554,17 +14422,17 @@
     <row r="282">
       <c r="A282" s="68" t="inlineStr">
         <is>
-          <t>PS5-84-01 - Generator Building</t>
+          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
       </c>
       <c r="B282" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C282" s="76" t="inlineStr">
-        <is>
-          <t>45%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C282" s="77" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
       <c r="D282" s="23" t="inlineStr">
@@ -14604,7 +14472,7 @@
     <row r="283">
       <c r="A283" s="68" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B283" s="23" t="inlineStr">
@@ -14614,7 +14482,7 @@
       </c>
       <c r="C283" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="D283" s="23" t="inlineStr">
@@ -14654,17 +14522,17 @@
     <row r="284">
       <c r="A284" s="68" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B284" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C284" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C284" s="76" t="inlineStr">
+        <is>
+          <t>8%</t>
         </is>
       </c>
       <c r="D284" s="23" t="inlineStr">
@@ -14704,17 +14572,17 @@
     <row r="285">
       <c r="A285" s="68" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-82-07 - Guard Huts</t>
         </is>
       </c>
       <c r="B285" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C285" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C285" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D285" s="23" t="inlineStr">
@@ -14754,12 +14622,12 @@
     <row r="286">
       <c r="A286" s="68" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="B286" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C286" s="78" t="inlineStr">
@@ -14804,17 +14672,17 @@
     <row r="287">
       <c r="A287" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-01 - Area Completion for Building area</t>
+          <t>PS5-84-01 - Generator Building</t>
         </is>
       </c>
       <c r="B287" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C287" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="D287" s="23" t="inlineStr">
@@ -14854,17 +14722,17 @@
     <row r="288">
       <c r="A288" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-02 - Area Completion for Utility area</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B288" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C288" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="D288" s="23" t="inlineStr">
@@ -14904,17 +14772,17 @@
     <row r="289">
       <c r="A289" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="B289" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C289" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C289" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D289" s="23" t="inlineStr">
@@ -14954,17 +14822,17 @@
     <row r="290">
       <c r="A290" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-04 - Area Completion for Process area</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="B290" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C290" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C290" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D290" s="23" t="inlineStr">
@@ -15004,17 +14872,17 @@
     <row r="291">
       <c r="A291" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-05 - Area Completion for CFO area</t>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
       <c r="B291" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C291" s="76" t="inlineStr">
-        <is>
-          <t>33%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C291" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D291" s="23" t="inlineStr">
@@ -15054,17 +14922,17 @@
     <row r="292">
       <c r="A292" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-06 - Area Completion for Power Generation area</t>
+          <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
       </c>
       <c r="B292" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C292" s="77" t="inlineStr">
-        <is>
-          <t>67%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C292" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D292" s="23" t="inlineStr">
@@ -15101,8 +14969,258 @@
       <c r="K292" s="23" t="n"/>
       <c r="L292" s="67" t="inlineStr"/>
     </row>
+    <row r="293">
+      <c r="A293" s="68" t="inlineStr">
+        <is>
+          <t>PS5-99-02 - Area Completion for Utility area</t>
+        </is>
+      </c>
+      <c r="B293" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C293" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D293" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E293" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F293" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G293" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H293" s="65" t="inlineStr"/>
+      <c r="I293" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J293" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K293" s="23" t="n"/>
+      <c r="L293" s="67" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="68" t="inlineStr">
+        <is>
+          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+        </is>
+      </c>
+      <c r="B294" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C294" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D294" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E294" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F294" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G294" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H294" s="65" t="inlineStr"/>
+      <c r="I294" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J294" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K294" s="23" t="n"/>
+      <c r="L294" s="67" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="68" t="inlineStr">
+        <is>
+          <t>PS5-99-04 - Area Completion for Process area</t>
+        </is>
+      </c>
+      <c r="B295" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C295" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D295" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E295" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F295" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G295" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H295" s="65" t="inlineStr"/>
+      <c r="I295" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J295" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K295" s="23" t="n"/>
+      <c r="L295" s="67" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="68" t="inlineStr">
+        <is>
+          <t>PS5-99-05 - Area Completion for CFO area</t>
+        </is>
+      </c>
+      <c r="B296" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C296" s="76" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="D296" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E296" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F296" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G296" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H296" s="65" t="inlineStr"/>
+      <c r="I296" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J296" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K296" s="23" t="n"/>
+      <c r="L296" s="67" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="68" t="inlineStr">
+        <is>
+          <t>PS5-99-06 - Area Completion for Power Generation area</t>
+        </is>
+      </c>
+      <c r="B297" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C297" s="77" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="D297" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E297" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F297" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G297" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H297" s="65" t="inlineStr"/>
+      <c r="I297" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J297" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K297" s="23" t="n"/>
+      <c r="L297" s="67" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L292"/>
+  <autoFilter ref="A2:L297"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -15397,6 +15515,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A290" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A291" r:id="rId289"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A292" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A293" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A294" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A295" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId295"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15408,7 +15531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15990,7 +16113,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PS5-08-01 - PAGA</t>
+          <t>PS5-08-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -16002,2890 +16125,2950 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
+          <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PS5-08-03</t>
+          <t>PS5-08-01a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PS5-08-04 - Hotline</t>
+          <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PS5-08-04</t>
+          <t>PS5-08-01b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
+          <t>PS5-08-03 - Telephone</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PS5-08-07</t>
+          <t>PS5-08-03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
+          <t>PS5-08-04 - Hotline</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PS5-08-11</t>
+          <t>PS5-08-04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PS5-08-12</t>
+          <t>PS5-08-07</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
+          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PS5-08-13</t>
+          <t>PS5-08-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PS5-08-14</t>
+          <t>PS5-08-12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
+          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PS5-08-15</t>
+          <t>PS5-08-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PS5-08-23 - VHF Trunk Radio System</t>
+          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PS5-08-23</t>
+          <t>PS5-08-14</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PS5-08-34 - Satphone</t>
+          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PS5-08-34</t>
+          <t>PS5-08-15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PS5-08-35 - Optical Transport Network</t>
+          <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PS5-08-35</t>
+          <t>PS5-08-23</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
+          <t>PS5-08-34 - Satphone</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PS5-08-36</t>
+          <t>PS5-08-34</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PS5-08-51 - Entertainment</t>
+          <t>PS5-08-35 - Optical Transport Network</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PS5-08-51</t>
+          <t>PS5-08-35</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PS5-08-52 - Process &amp; Security CCTV</t>
+          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PS5-08-52</t>
+          <t>PS5-08-36</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PS5-08-55 - Videoconference</t>
+          <t>PS5-08-51 - Entertainment</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PS5-08-55</t>
+          <t>PS5-08-51</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PS5-08-61 - Meteocean</t>
+          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PS5-08-61</t>
+          <t>PS5-08-52a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
+          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PS5-08-71</t>
+          <t>PS5-08-52b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PS5-08-72 - Structured Cabling (FO)</t>
+          <t>PS5-08-55 - Videoconference</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PS5-08-72</t>
+          <t>PS5-08-55</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PS5-08-81 - Guard tour</t>
+          <t>PS5-08-61 - Meteocean</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PS5-08-81</t>
+          <t>PS5-08-61</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PS5-08-82 - Key Management</t>
+          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PS5-08-82</t>
+          <t>PS5-08-71</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+          <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PS5-08-83</t>
+          <t>PS5-08-72</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
+          <t>PS5-08-81 - Guard tour</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PS5-08-85</t>
+          <t>PS5-08-81</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PS5-08-86 - Integrated Security Management System</t>
+          <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PS5-08-86</t>
+          <t>PS5-08-82</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PS5-08-92 - Telecom Mast</t>
+          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PS5-08-92</t>
+          <t>PS5-08-83</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PS5-08-93 - Telecom Monitoring System</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PS5-08-93</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
+          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PS5-09-01</t>
+          <t>PS5-08-85a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PS5-09-02 - HVAC for Guard House</t>
+          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PS5-09-02</t>
+          <t>PS5-08-85b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PS5-09-03 - HVAC for Generator Building</t>
+          <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PS5-09-03</t>
+          <t>PS5-08-86</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
+          <t>PS5-08-92 - Telecom Mast</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PS5-09-04</t>
+          <t>PS5-08-92</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
+          <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PS5-09-05</t>
+          <t>PS5-08-93</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PS5-0H-01 - HIPPS</t>
+          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PS5-0H-01</t>
+          <t>PS5-09-01</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
+          <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PS5-25-01</t>
+          <t>PS5-09-02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+          <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PS5-25-02</t>
+          <t>PS5-09-03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PS5-25-03</t>
+          <t>PS5-09-04</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PS5-25-04</t>
+          <t>PS5-09-05</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+          <t>PS5-0H-01 - HIPPS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PS5-25-05</t>
+          <t>PS5-0H-01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
+          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PS5-25-06</t>
+          <t>PS5-25-01</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PS5-25-07</t>
+          <t>PS5-25-02</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PS5-28-01 - Closed Drain Header 1</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PS5-28-01</t>
+          <t>PS5-25-03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PS5-28-02</t>
+          <t>PS5-25-04</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PS5-28-03</t>
+          <t>PS5-25-05</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
+          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PS5-28-04</t>
+          <t>PS5-25-06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PS5-28-05</t>
+          <t>PS5-25-07</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PS5-28-06</t>
+          <t>PS5-28-01</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PS5-28-07</t>
+          <t>PS5-28-02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PS5-28-08</t>
+          <t>PS5-28-03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PS5-28-09 - Observation Basin</t>
+          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PS5-28-09</t>
+          <t>PS5-28-04</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PS5-28-10 - Oil Skimmer Package</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PS5-28-10</t>
+          <t>PS5-28-05</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PS5-28-11</t>
+          <t>PS5-28-06</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PS5-28-12</t>
+          <t>PS5-28-07</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PS5-28-13</t>
+          <t>PS5-28-08</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+          <t>PS5-28-09 - Observation Basin</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PS5-28-14</t>
+          <t>PS5-28-09</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+          <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PS5-28-15</t>
+          <t>PS5-28-10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PS5-28-16</t>
+          <t>PS5-28-11</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PS5-28-17 - Reinjection Pump</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PS5-28-17</t>
+          <t>PS5-28-12</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PS5-50-01</t>
+          <t>PS5-28-13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PS5-50-02</t>
+          <t>PS5-28-14</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PS5-50-03 - Water Pre-Treatment Package</t>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PS5-50-03</t>
+          <t>PS5-28-15</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PS5-53-01 - Utility Water / Storage Tank</t>
+          <t>PS5-28-16 - LP Relief Header</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PS5-53-01</t>
+          <t>PS5-28-16</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+          <t>PS5-28-17 - Reinjection Pump</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PS5-53-02</t>
+          <t>PS5-28-17</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PS5-53-03 - Water Softener Package</t>
+          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PS5-53-03</t>
+          <t>PS5-50-01</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PS5-53-04 - Water Treatment Purification Package</t>
+          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PS5-53-04</t>
+          <t>PS5-50-02</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PS5-53-05</t>
+          <t>PS5-50-03</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PS5-53-06 - Water Distribution Consumers</t>
+          <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PS5-53-06</t>
+          <t>PS5-53-01</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PS5-60-01</t>
+          <t>PS5-53-02</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-53-03 - Water Softener Package</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PS5-60-02</t>
+          <t>PS5-53-03</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PS5-60-03</t>
+          <t>PS5-53-04</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PS5-60-04</t>
+          <t>PS5-53-05</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+          <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PS5-60-05</t>
+          <t>PS5-53-06</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PS5-60-06</t>
+          <t>PS5-60-01</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PS5-60-07 - Power Generation Package C</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PS5-60-07</t>
+          <t>PS5-60-02</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PS5-60-08</t>
+          <t>PS5-60-03</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PS5-60-09</t>
+          <t>PS5-60-04</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PS5-60-10 - Power Generation Package D</t>
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PS5-60-10</t>
+          <t>PS5-60-05</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PS5-60-11</t>
+          <t>PS5-60-06</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-07 - Power Generation Package C</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PS5-60-12</t>
+          <t>PS5-60-07</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PS5-60-13</t>
+          <t>PS5-60-08</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PS5-60-14</t>
+          <t>PS5-60-09</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-10 - Power Generation Package D</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PS5-60-15</t>
+          <t>PS5-60-10</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PS5-60-16 - Power Generation Package F</t>
+          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PS5-60-16</t>
+          <t>PS5-60-11</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PS5-60-17</t>
+          <t>PS5-60-12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PS5-60-18</t>
+          <t>PS5-60-13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PS5-60-19 - Power Generation Package G</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PS5-60-19</t>
+          <t>PS5-60-14</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PS5-60-20</t>
+          <t>PS5-60-15</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-16 - Power Generation Package F</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PS5-60-21</t>
+          <t>PS5-60-16</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PS5-60-22 - Power Gen Master UCP</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PS5-60-22</t>
+          <t>PS5-60-17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PS5-60-23</t>
+          <t>PS5-60-18</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
+          <t>PS5-60-19 - Power Generation Package G</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PS5-60-24</t>
+          <t>PS5-60-19</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PS5-60-25</t>
+          <t>PS5-60-20</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PS5-60-26</t>
+          <t>PS5-60-21</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PS5-60-27</t>
+          <t>PS5-60-22</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PS5-60-28</t>
+          <t>PS5-60-23</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PS5-60-29</t>
+          <t>PS5-60-24</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PS5-60-30</t>
+          <t>PS5-60-25</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PS5-60-31</t>
+          <t>PS5-60-26</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PS5-60-32</t>
+          <t>PS5-60-27</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PS5-60-33</t>
+          <t>PS5-60-28</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PS5-60-34</t>
+          <t>PS5-60-29</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PS5-60-35</t>
+          <t>PS5-60-30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PS5-60-36</t>
+          <t>PS5-60-31</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PS5-60-37</t>
+          <t>PS5-60-32</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PS5-60-38</t>
+          <t>PS5-60-33</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PS5-60-39</t>
+          <t>PS5-60-34</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PS5-60-40</t>
+          <t>PS5-60-35</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PS5-60-41</t>
+          <t>PS5-60-36</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PS5-60-42</t>
+          <t>PS5-60-37</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PS5-60-43</t>
+          <t>PS5-60-38</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PS5-60-44</t>
+          <t>PS5-60-39</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PS5-60-45</t>
+          <t>PS5-60-40</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PS5-60-46</t>
+          <t>PS5-60-41</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PS5-60-47</t>
+          <t>PS5-60-42</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PS5-60-48</t>
+          <t>PS5-60-43</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PS5-60-49</t>
+          <t>PS5-60-44</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PS5-60-50</t>
+          <t>PS5-60-45</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PS5-60-51</t>
+          <t>PS5-60-46</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PS5-60-52</t>
+          <t>PS5-60-47</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PS5-60-53</t>
+          <t>PS5-60-48</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PS5-60-54</t>
+          <t>PS5-60-49</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PS5-60-55</t>
+          <t>PS5-60-50</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PS5-60-56</t>
+          <t>PS5-60-51</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PS5-60-57</t>
+          <t>PS5-60-52</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PS5-60-58</t>
+          <t>PS5-60-53</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PS5-60-59</t>
+          <t>PS5-60-54</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PS5-60-60</t>
+          <t>PS5-60-55</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PS5-60-61</t>
+          <t>PS5-60-56</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PS5-60-62</t>
+          <t>PS5-60-57</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PS5-60-63</t>
+          <t>PS5-60-58</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PS5-60-64</t>
+          <t>PS5-60-59</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PS5-60-65</t>
+          <t>PS5-60-60</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
+          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PS5-60-66</t>
+          <t>PS5-60-61</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PS5-60-67</t>
+          <t>PS5-60-62</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PS5-60-68</t>
+          <t>PS5-60-63</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PS5-60-69</t>
+          <t>PS5-60-64</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PS5-60-70</t>
+          <t>PS5-60-65</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PS5-60-71</t>
+          <t>PS5-60-66</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PS5-60-72</t>
+          <t>PS5-60-67</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PS5-60-73</t>
+          <t>PS5-60-68</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PS5-60-74</t>
+          <t>PS5-60-69</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PS5-60-75</t>
+          <t>PS5-60-70</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PS5-60-76</t>
+          <t>PS5-60-71</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PS5-61-01</t>
+          <t>PS5-60-72</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PS5-61-02</t>
+          <t>PS5-60-73</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PS5-61-03</t>
+          <t>PS5-60-74</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PS5-61-04</t>
+          <t>PS5-60-75</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PS5-61-05</t>
+          <t>PS5-60-76</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
+          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PS5-61-06</t>
+          <t>PS5-61-01</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PS5-61-07</t>
+          <t>PS5-61-02</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PS5-61-08 - Electrical Control System</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PS5-61-08</t>
+          <t>PS5-61-03</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
+          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PS5-61-09</t>
+          <t>PS5-61-04</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PS5-61-10</t>
+          <t>PS5-61-05</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PS5-61-11</t>
+          <t>PS5-61-06</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PS5-61-12</t>
+          <t>PS5-61-07</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
+          <t>PS5-61-08 - Electrical Control System</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PS5-61-13</t>
+          <t>PS5-61-08</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
+          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PS5-61-14</t>
+          <t>PS5-61-09</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PS5-62-01</t>
+          <t>PS5-61-10</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PS5-62-02</t>
+          <t>PS5-61-11</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PS5-62-03</t>
+          <t>PS5-61-12</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PS5-62-04</t>
+          <t>PS5-61-13</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PS5-62-05</t>
+          <t>PS5-61-14</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
+          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PS5-62-06</t>
+          <t>PS5-62-01</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PS5-62-07</t>
+          <t>PS5-62-02</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PS5-62-08</t>
+          <t>PS5-62-03</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PS5-62-09</t>
+          <t>PS5-62-04</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PS5-62-10</t>
+          <t>PS5-62-05</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PS5-62-11</t>
+          <t>PS5-62-06</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
+          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PS5-62-12</t>
+          <t>PS5-62-07</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
+          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PS5-62-13</t>
+          <t>PS5-62-08</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PS5-62-14</t>
+          <t>PS5-62-09</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PS5-62-15</t>
+          <t>PS5-62-10</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PS5-62-16</t>
+          <t>PS5-62-11</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PS5-62-17</t>
+          <t>PS5-62-12</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
+          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PS5-62-18</t>
+          <t>PS5-62-13</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PS5-62-19</t>
+          <t>PS5-62-14</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PS5-62-20</t>
+          <t>PS5-62-15</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PS5-63-01 - Electrical Earthing</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PS5-63-01</t>
+          <t>PS5-62-16</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PS5-63-02</t>
+          <t>PS5-62-17</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
+          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PS5-63-03</t>
+          <t>PS5-62-18</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PS5-63-04</t>
+          <t>PS5-62-19</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PS5-63-05</t>
+          <t>PS5-62-20</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
+          <t>PS5-63-01 - Electrical Earthing</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PS5-63-06</t>
+          <t>PS5-63-01</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
+          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PS5-63-07</t>
+          <t>PS5-63-02</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
+          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PS5-71-01</t>
+          <t>PS5-63-03</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PS5-71-02</t>
+          <t>PS5-63-04</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PS5-71-03</t>
+          <t>PS5-63-05</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PS5-71-04 - CFO Storage Tank</t>
+          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PS5-71-04</t>
+          <t>PS5-63-06</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
+          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PS5-71-05</t>
+          <t>PS5-63-07</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PS5-71-06 - Crude Fuel Separation Module</t>
+          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PS5-71-06</t>
+          <t>PS5-71-01</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PS5-71-07</t>
+          <t>PS5-71-02</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PS5-71-08</t>
+          <t>PS5-71-03</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PS5-71-09</t>
+          <t>PS5-71-04</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>PS5-71-12 - CFO Service Tank</t>
+          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PS5-71-12</t>
+          <t>PS5-71-05</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PS5-71-13</t>
+          <t>PS5-71-06</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PS5-71-14</t>
+          <t>PS5-71-07</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
+          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PS5-71-15</t>
+          <t>PS5-71-08</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PS5-71-16</t>
+          <t>PS5-71-09</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
+          <t>PS5-71-12 - CFO Service Tank</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PS5-71-17</t>
+          <t>PS5-71-12</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PS5-71-18 - Diesel Separator Module</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PS5-71-18</t>
+          <t>PS5-71-13</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PS5-71-19</t>
+          <t>PS5-71-14</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PS5-71-20</t>
+          <t>PS5-71-15</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PS5-71-21</t>
+          <t>PS5-71-16</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PS5-71-22</t>
+          <t>PS5-71-17</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
+          <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PS5-71-23</t>
+          <t>PS5-71-18</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PS5-74-01</t>
+          <t>PS5-71-19</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
+          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PS5-74-02</t>
+          <t>PS5-71-20</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PS5-74-03</t>
+          <t>PS5-71-21</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PS5-74-04</t>
+          <t>PS5-71-22</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PS5-75-01 - DRA Injection Package</t>
+          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PS5-75-01</t>
+          <t>PS5-71-23</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PS5-75-02</t>
+          <t>PS5-74-01</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PS5-75-03</t>
+          <t>PS5-74-02</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PS5-78-01</t>
+          <t>PS5-74-03</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PS5-79-01</t>
+          <t>PS5-74-04</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
+          <t>PS5-75-01 - DRA Injection Package</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PS5-79-02</t>
+          <t>PS5-75-01</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PS5-79-03</t>
+          <t>PS5-75-02</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PS5-79-04</t>
+          <t>PS5-75-03</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PS5-79-05</t>
+          <t>PS5-78-01</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
+          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PS5-79-06</t>
+          <t>PS5-79-01</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
+          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PS5-79-07</t>
+          <t>PS5-79-02</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
+          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PS5-79-08</t>
+          <t>PS5-79-03</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
+          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PS5-79-09</t>
+          <t>PS5-79-04</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
+          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PS5-79-10</t>
+          <t>PS5-79-05</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
+          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PS5-79-11</t>
+          <t>PS5-79-06</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
+          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PS5-79-12</t>
+          <t>PS5-79-07</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PS5-82-01</t>
+          <t>PS5-79-08</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
+          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PS5-82-02</t>
+          <t>PS5-79-09</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
+          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PS5-82-03</t>
+          <t>PS5-79-10</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
+          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PS5-82-04</t>
+          <t>PS5-79-11</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PS5-82-05</t>
+          <t>PS5-79-12</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PS5-82-06</t>
+          <t>PS5-82-01</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PS5-82-07 - Guard Huts</t>
+          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PS5-82-07</t>
+          <t>PS5-82-02</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PS5-83-01</t>
+          <t>PS5-82-03</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PS5-84-01 - Generator Building</t>
+          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PS5-84-01</t>
+          <t>PS5-82-04</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PS5-84-02</t>
+          <t>PS5-82-05</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PS5-84-03</t>
+          <t>PS5-82-06</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-82-07 - Guard Huts</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PS5-86-01</t>
+          <t>PS5-82-07</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PS5-91-01</t>
+          <t>PS5-83-01</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PS5-99-01 - Area Completion for Building area</t>
+          <t>PS5-84-01 - Generator Building</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PS5-99-01</t>
+          <t>PS5-84-01</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PS5-99-02 - Area Completion for Utility area</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PS5-99-02</t>
+          <t>PS5-84-02</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PS5-99-03</t>
+          <t>PS5-84-03</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>PS5-99-04 - Area Completion for Process area</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PS5-99-04</t>
+          <t>PS5-86-01</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PS5-99-05 - Area Completion for CFO area</t>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PS5-99-05</t>
+          <t>PS5-91-01</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
+          <t>PS5-99-01 - Area Completion for Building area</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>PS5-99-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>PS5-99-02 - Area Completion for Utility area</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>PS5-99-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>PS5-99-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>PS5-99-04 - Area Completion for Process area</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>PS5-99-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>PS5-99-05 - Area Completion for CFO area</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>PS5-99-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>PS5-99-06</t>
         </is>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 · BLOCKING – REMARKS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="3 · BLOCKING – REMARKS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3 · BLOCKING – REMARKS'!$A$2:$L$297</definedName>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3 · BLOCKING – REMARKS'!$A$2:$L$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3 · BLOCKING – REMARKS'!$A$2:$L$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -116,14 +116,14 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="FFb35900"/>
+      <color rgb="FF0a58ca"/>
       <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="FF0a58ca"/>
+      <color rgb="FFb35900"/>
       <sz val="10"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -728,22 +728,22 @@
     <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -761,13 +761,13 @@
     <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L297"/>
+  <dimension ref="A1:L295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5520,7 +5520,7 @@
       <c r="B91" s="23" t="inlineStr"/>
       <c r="C91" s="78" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="D91" s="23" t="n">
@@ -5546,9 +5546,9 @@
         </is>
       </c>
       <c r="B92" s="23" t="inlineStr"/>
-      <c r="C92" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="C92" s="78" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="D92" s="23" t="n">
@@ -5676,7 +5676,7 @@
       <c r="B95" s="23" t="inlineStr"/>
       <c r="C95" s="77" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="D95" s="23" t="n">
@@ -5898,63 +5898,41 @@
     <row r="100">
       <c r="A100" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-01</t>
-        </is>
-      </c>
-      <c r="B100" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>PS5-08-01a - PAGA (Required for SU)</t>
+        </is>
+      </c>
+      <c r="B100" s="23" t="inlineStr"/>
       <c r="C100" s="76" t="inlineStr">
         <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="D100" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E100" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F100" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G100" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="65" t="inlineStr"/>
       <c r="H100" s="65" t="inlineStr"/>
-      <c r="I100" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J100" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I100" s="65" t="inlineStr"/>
+      <c r="J100" s="23" t="inlineStr"/>
       <c r="K100" s="23" t="n"/>
       <c r="L100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-01a - PAGA (Required for SU)</t>
+          <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
       </c>
       <c r="B101" s="23" t="inlineStr"/>
       <c r="C101" s="76" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="D101" s="23" t="n">
@@ -5976,85 +5954,85 @@
     <row r="102">
       <c r="A102" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-01b - PAGA (Not required for SU)</t>
-        </is>
-      </c>
-      <c r="B102" s="23" t="inlineStr"/>
+          <t>PS5-08-03 - Telephone</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C102" s="76" t="inlineStr">
         <is>
-          <t>14%</t>
-        </is>
-      </c>
-      <c r="D102" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="65" t="inlineStr"/>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="D102" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E102" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F102" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G102" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H102" s="65" t="inlineStr"/>
-      <c r="I102" s="65" t="inlineStr"/>
-      <c r="J102" s="23" t="inlineStr"/>
+      <c r="I102" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J102" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K102" s="23" t="n"/>
       <c r="L102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
-        </is>
-      </c>
-      <c r="B103" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-04 - Hotline</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="inlineStr"/>
       <c r="C103" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="D103" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E103" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F103" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G103" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D103" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="65" t="inlineStr"/>
       <c r="H103" s="65" t="inlineStr"/>
-      <c r="I103" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J103" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I103" s="65" t="inlineStr"/>
+      <c r="J103" s="23" t="inlineStr"/>
       <c r="K103" s="23" t="n"/>
       <c r="L103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-04 - Hotline</t>
+          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
       </c>
       <c r="B104" s="23" t="inlineStr"/>
@@ -6082,35 +6060,57 @@
     <row r="105">
       <c r="A105" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
-        </is>
-      </c>
-      <c r="B105" s="23" t="inlineStr"/>
+          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C105" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D105" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="65" t="inlineStr"/>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D105" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G105" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H105" s="65" t="inlineStr"/>
-      <c r="I105" s="65" t="inlineStr"/>
-      <c r="J105" s="23" t="inlineStr"/>
+      <c r="I105" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J105" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K105" s="23" t="n"/>
       <c r="L105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B106" s="23" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C106" s="76" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D106" s="23" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="107">
       <c r="A107" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
       </c>
       <c r="B107" s="23" t="inlineStr">
@@ -6210,12 +6210,12 @@
     <row r="108">
       <c r="A108" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
+          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
       </c>
       <c r="B108" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C108" s="76" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="109">
       <c r="A109" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
+          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
       </c>
       <c r="B109" s="23" t="inlineStr">
@@ -6310,7 +6310,7 @@
     <row r="110">
       <c r="A110" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
+          <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
       </c>
       <c r="B110" s="23" t="inlineStr">
@@ -6360,7 +6360,7 @@
     <row r="111">
       <c r="A111" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-23 - VHF Trunk Radio System</t>
+          <t>PS5-08-34 - Satphone</t>
         </is>
       </c>
       <c r="B111" s="23" t="inlineStr">
@@ -6410,90 +6410,90 @@
     <row r="112">
       <c r="A112" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-34 - Satphone</t>
-        </is>
-      </c>
-      <c r="B112" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C112" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D112" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E112" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F112" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G112" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-08-35 - Optical Transport Network</t>
+        </is>
+      </c>
+      <c r="B112" s="23" t="inlineStr"/>
+      <c r="C112" s="77" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="D112" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="65" t="inlineStr"/>
       <c r="H112" s="65" t="inlineStr"/>
-      <c r="I112" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J112" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I112" s="65" t="inlineStr"/>
+      <c r="J112" s="23" t="inlineStr"/>
       <c r="K112" s="23" t="n"/>
       <c r="L112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-35 - Optical Transport Network</t>
-        </is>
-      </c>
-      <c r="B113" s="23" t="inlineStr"/>
-      <c r="C113" s="77" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="D113" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="65" t="inlineStr"/>
+          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
+        </is>
+      </c>
+      <c r="B113" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C113" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D113" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E113" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F113" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G113" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H113" s="65" t="inlineStr"/>
-      <c r="I113" s="65" t="inlineStr"/>
-      <c r="J113" s="23" t="inlineStr"/>
+      <c r="I113" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J113" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K113" s="23" t="n"/>
       <c r="L113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
+          <t>PS5-08-51 - Entertainment</t>
         </is>
       </c>
       <c r="B114" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C114" s="76" t="inlineStr">
@@ -6538,63 +6538,41 @@
     <row r="115">
       <c r="A115" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-51 - Entertainment</t>
-        </is>
-      </c>
-      <c r="B115" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
+        </is>
+      </c>
+      <c r="B115" s="23" t="inlineStr"/>
       <c r="C115" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D115" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E115" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F115" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G115" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="D115" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="65" t="inlineStr"/>
       <c r="H115" s="65" t="inlineStr"/>
-      <c r="I115" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J115" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I115" s="65" t="inlineStr"/>
+      <c r="J115" s="23" t="inlineStr"/>
       <c r="K115" s="23" t="n"/>
       <c r="L115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
+          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
       </c>
       <c r="B116" s="23" t="inlineStr"/>
       <c r="C116" s="76" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="D116" s="23" t="n">
@@ -6616,13 +6594,13 @@
     <row r="117">
       <c r="A117" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
+          <t>PS5-08-55 - Videoconference</t>
         </is>
       </c>
       <c r="B117" s="23" t="inlineStr"/>
       <c r="C117" s="76" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D117" s="23" t="n">
@@ -6644,35 +6622,57 @@
     <row r="118">
       <c r="A118" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-55 - Videoconference</t>
-        </is>
-      </c>
-      <c r="B118" s="23" t="inlineStr"/>
+          <t>PS5-08-61 - Meteocean</t>
+        </is>
+      </c>
+      <c r="B118" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C118" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D118" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="65" t="inlineStr"/>
+      <c r="D118" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E118" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F118" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G118" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H118" s="65" t="inlineStr"/>
-      <c r="I118" s="65" t="inlineStr"/>
-      <c r="J118" s="23" t="inlineStr"/>
+      <c r="I118" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J118" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K118" s="23" t="n"/>
       <c r="L118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-61 - Meteocean</t>
+          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
       </c>
       <c r="B119" s="23" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C119" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D119" s="23" t="inlineStr">
@@ -6722,17 +6722,17 @@
     <row r="120">
       <c r="A120" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
+          <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
       </c>
       <c r="B120" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C120" s="76" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D120" s="23" t="inlineStr">
@@ -6772,57 +6772,35 @@
     <row r="121">
       <c r="A121" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-72 - Structured Cabling (FO)</t>
-        </is>
-      </c>
-      <c r="B121" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>PS5-08-81 - Guard tour</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="inlineStr"/>
       <c r="C121" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D121" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E121" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F121" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G121" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="D121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="65" t="inlineStr"/>
       <c r="H121" s="65" t="inlineStr"/>
-      <c r="I121" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J121" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I121" s="65" t="inlineStr"/>
+      <c r="J121" s="23" t="inlineStr"/>
       <c r="K121" s="23" t="n"/>
       <c r="L121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-81 - Guard tour</t>
+          <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B122" s="23" t="inlineStr"/>
@@ -6850,141 +6828,119 @@
     <row r="123">
       <c r="A123" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-82 - Key Management</t>
-        </is>
-      </c>
-      <c r="B123" s="23" t="inlineStr"/>
+          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C123" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D123" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="65" t="inlineStr"/>
+      <c r="D123" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E123" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F123" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G123" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H123" s="65" t="inlineStr"/>
-      <c r="I123" s="65" t="inlineStr"/>
-      <c r="J123" s="23" t="inlineStr"/>
+      <c r="I123" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J123" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K123" s="23" t="n"/>
       <c r="L123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
-        </is>
-      </c>
-      <c r="B124" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
+        </is>
+      </c>
+      <c r="B124" s="23" t="inlineStr"/>
       <c r="C124" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D124" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E124" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F124" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G124" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="D124" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="65" t="inlineStr"/>
       <c r="H124" s="65" t="inlineStr"/>
-      <c r="I124" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J124" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I124" s="65" t="inlineStr"/>
+      <c r="J124" s="23" t="inlineStr"/>
       <c r="K124" s="23" t="n"/>
       <c r="L124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-85</t>
-        </is>
-      </c>
-      <c r="B125" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
+        </is>
+      </c>
+      <c r="B125" s="23" t="inlineStr"/>
       <c r="C125" s="76" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="D125" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E125" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F125" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G125" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="65" t="inlineStr"/>
       <c r="H125" s="65" t="inlineStr"/>
-      <c r="I125" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J125" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I125" s="65" t="inlineStr"/>
+      <c r="J125" s="23" t="inlineStr"/>
       <c r="K125" s="23" t="n"/>
       <c r="L125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
+          <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
       </c>
       <c r="B126" s="23" t="inlineStr"/>
       <c r="C126" s="76" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D126" s="23" t="n">
@@ -7006,13 +6962,13 @@
     <row r="127">
       <c r="A127" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
+          <t>PS5-08-92 - Telecom Mast</t>
         </is>
       </c>
       <c r="B127" s="23" t="inlineStr"/>
       <c r="C127" s="76" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D127" s="23" t="n">
@@ -7034,123 +6990,145 @@
     <row r="128">
       <c r="A128" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-86 - Integrated Security Management System</t>
-        </is>
-      </c>
-      <c r="B128" s="23" t="inlineStr"/>
+          <t>PS5-08-93 - Telecom Monitoring System</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C128" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D128" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="65" t="inlineStr"/>
+      <c r="D128" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E128" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F128" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G128" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H128" s="65" t="inlineStr"/>
-      <c r="I128" s="65" t="inlineStr"/>
-      <c r="J128" s="23" t="inlineStr"/>
+      <c r="I128" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J128" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K128" s="23" t="n"/>
       <c r="L128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-92 - Telecom Mast</t>
-        </is>
-      </c>
-      <c r="B129" s="23" t="inlineStr"/>
+          <t>PS5-09-02 - HVAC for Guard House</t>
+        </is>
+      </c>
+      <c r="B129" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="C129" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" s="65" t="inlineStr"/>
+      <c r="D129" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E129" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F129" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G129" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H129" s="65" t="inlineStr"/>
-      <c r="I129" s="65" t="inlineStr"/>
-      <c r="J129" s="23" t="inlineStr"/>
+      <c r="I129" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J129" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K129" s="23" t="n"/>
       <c r="L129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-93 - Telecom Monitoring System</t>
-        </is>
-      </c>
-      <c r="B130" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C130" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D130" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E130" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F130" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-0H-01 - HIPPS</t>
+        </is>
+      </c>
+      <c r="B130" s="23" t="inlineStr"/>
+      <c r="C130" s="77" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="D130" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="65" t="inlineStr"/>
       <c r="H130" s="65" t="inlineStr"/>
-      <c r="I130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J130" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I130" s="65" t="inlineStr"/>
+      <c r="J130" s="23" t="inlineStr"/>
       <c r="K130" s="23" t="n"/>
       <c r="L130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="68" t="inlineStr">
         <is>
-          <t>PS5-09-02 - HVAC for Guard House</t>
+          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
       </c>
       <c r="B131" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C131" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C131" s="77" t="inlineStr">
+        <is>
+          <t>76%</t>
         </is>
       </c>
       <c r="D131" s="23" t="inlineStr">
@@ -7170,7 +7148,7 @@
       </c>
       <c r="G131" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H131" s="65" t="inlineStr"/>
@@ -7190,35 +7168,57 @@
     <row r="132">
       <c r="A132" s="68" t="inlineStr">
         <is>
-          <t>PS5-0H-01 - HIPPS</t>
-        </is>
-      </c>
-      <c r="B132" s="23" t="inlineStr"/>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C132" s="77" t="inlineStr">
         <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="D132" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="65" t="inlineStr"/>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="D132" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E132" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F132" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G132" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H132" s="65" t="inlineStr"/>
-      <c r="I132" s="65" t="inlineStr"/>
-      <c r="J132" s="23" t="inlineStr"/>
+      <c r="I132" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J132" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K132" s="23" t="n"/>
       <c r="L132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B133" s="23" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="C133" s="77" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="D133" s="23" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="G133" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H133" s="65" t="inlineStr"/>
@@ -7268,7 +7268,7 @@
     <row r="134">
       <c r="A134" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B134" s="23" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="C134" s="77" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="D134" s="23" t="inlineStr">
@@ -7318,7 +7318,7 @@
     <row r="135">
       <c r="A135" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="B135" s="23" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C135" s="77" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="D135" s="23" t="inlineStr">
@@ -7368,7 +7368,7 @@
     <row r="136">
       <c r="A136" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
       </c>
       <c r="B136" s="23" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="C136" s="77" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="D136" s="23" t="inlineStr">
@@ -7418,7 +7418,7 @@
     <row r="137">
       <c r="A137" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
       </c>
       <c r="B137" s="23" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="C137" s="77" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="D137" s="23" t="inlineStr">
@@ -7468,7 +7468,7 @@
     <row r="138">
       <c r="A138" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
+          <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
       </c>
       <c r="B138" s="23" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C138" s="77" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="D138" s="23" t="inlineStr">
@@ -7518,17 +7518,17 @@
     <row r="139">
       <c r="A139" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="B139" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C139" s="77" t="inlineStr">
-        <is>
-          <t>84%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C139" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D139" s="23" t="inlineStr">
@@ -7568,7 +7568,7 @@
     <row r="140">
       <c r="A140" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-01 - Closed Drain Header 1</t>
+          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
       </c>
       <c r="B140" s="23" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="C140" s="77" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D140" s="23" t="inlineStr">
@@ -7618,12 +7618,12 @@
     <row r="141">
       <c r="A141" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="B141" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C141" s="78" t="inlineStr">
@@ -7668,12 +7668,12 @@
     <row r="142">
       <c r="A142" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
       </c>
       <c r="B142" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C142" s="77" t="inlineStr">
@@ -7718,17 +7718,17 @@
     <row r="143">
       <c r="A143" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
       <c r="B143" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C143" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D143" s="23" t="inlineStr">
@@ -7768,7 +7768,7 @@
     <row r="144">
       <c r="A144" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
       <c r="B144" s="23" t="inlineStr">
@@ -7776,9 +7776,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C144" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="C144" s="76" t="inlineStr">
+        <is>
+          <t>44%</t>
         </is>
       </c>
       <c r="D144" s="23" t="inlineStr">
@@ -7818,7 +7818,7 @@
     <row r="145">
       <c r="A145" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
+          <t>PS5-28-09 - Observation Basin</t>
         </is>
       </c>
       <c r="B145" s="23" t="inlineStr">
@@ -7826,9 +7826,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C145" s="78" t="inlineStr">
-        <is>
-          <t>94%</t>
+      <c r="C145" s="77" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="D145" s="23" t="inlineStr">
@@ -7868,17 +7868,17 @@
     <row r="146">
       <c r="A146" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+          <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
       </c>
       <c r="B146" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C146" s="76" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="D146" s="23" t="inlineStr">
@@ -7918,7 +7918,7 @@
     <row r="147">
       <c r="A147" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-09 - Observation Basin</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="B147" s="23" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C147" s="77" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="D147" s="23" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="148">
       <c r="A148" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-10 - Oil Skimmer Package</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="B148" s="23" t="inlineStr">
@@ -7976,9 +7976,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C148" s="76" t="inlineStr">
-        <is>
-          <t>9%</t>
+      <c r="C148" s="77" t="inlineStr">
+        <is>
+          <t>65%</t>
         </is>
       </c>
       <c r="D148" s="23" t="inlineStr">
@@ -8018,7 +8018,7 @@
     <row r="149">
       <c r="A149" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
       </c>
       <c r="B149" s="23" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C149" s="77" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="D149" s="23" t="inlineStr">
@@ -8068,7 +8068,7 @@
     <row r="150">
       <c r="A150" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
       </c>
       <c r="B150" s="23" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="C150" s="77" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="D150" s="23" t="inlineStr">
@@ -8118,7 +8118,7 @@
     <row r="151">
       <c r="A151" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
       </c>
       <c r="B151" s="23" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="C151" s="77" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="D151" s="23" t="inlineStr">
@@ -8168,17 +8168,17 @@
     <row r="152">
       <c r="A152" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+          <t>PS5-28-16 - LP Relief Header</t>
         </is>
       </c>
       <c r="B152" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C152" s="77" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="D152" s="23" t="inlineStr">
@@ -8218,17 +8218,17 @@
     <row r="153">
       <c r="A153" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
       </c>
       <c r="B153" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C153" s="77" t="inlineStr">
-        <is>
-          <t>75%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C153" s="76" t="inlineStr">
+        <is>
+          <t>38%</t>
         </is>
       </c>
       <c r="D153" s="23" t="inlineStr">
@@ -8268,17 +8268,17 @@
     <row r="154">
       <c r="A154" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
       </c>
       <c r="B154" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C154" s="77" t="inlineStr">
-        <is>
-          <t>82%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C154" s="76" t="inlineStr">
+        <is>
+          <t>42%</t>
         </is>
       </c>
       <c r="D154" s="23" t="inlineStr">
@@ -8318,12 +8318,12 @@
     <row r="155">
       <c r="A155" s="68" t="inlineStr">
         <is>
-          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
+          <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
       </c>
       <c r="B155" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C155" s="76" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="G155" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H155" s="65" t="inlineStr"/>
@@ -8368,17 +8368,17 @@
     <row r="156">
       <c r="A156" s="68" t="inlineStr">
         <is>
-          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="B156" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C156" s="76" t="inlineStr">
-        <is>
-          <t>42%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C156" s="77" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
       <c r="D156" s="23" t="inlineStr">
@@ -8418,7 +8418,7 @@
     <row r="157">
       <c r="A157" s="68" t="inlineStr">
         <is>
-          <t>PS5-50-03 - Water Pre-Treatment Package</t>
+          <t>PS5-53-03 - Water Softener Package</t>
         </is>
       </c>
       <c r="B157" s="23" t="inlineStr">
@@ -8426,9 +8426,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C157" s="76" t="inlineStr">
-        <is>
-          <t>38%</t>
+      <c r="C157" s="77" t="inlineStr">
+        <is>
+          <t>65%</t>
         </is>
       </c>
       <c r="D157" s="23" t="inlineStr">
@@ -8468,7 +8468,7 @@
     <row r="158">
       <c r="A158" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+          <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
       </c>
       <c r="B158" s="23" t="inlineStr">
@@ -8476,9 +8476,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C158" s="77" t="inlineStr">
-        <is>
-          <t>62%</t>
+      <c r="C158" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D158" s="23" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="G158" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H158" s="65" t="inlineStr"/>
@@ -8518,7 +8518,7 @@
     <row r="159">
       <c r="A159" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-03 - Water Softener Package</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="B159" s="23" t="inlineStr">
@@ -8526,9 +8526,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C159" s="77" t="inlineStr">
-        <is>
-          <t>65%</t>
+      <c r="C159" s="78" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="D159" s="23" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="G159" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H159" s="65" t="inlineStr"/>
@@ -8568,17 +8568,17 @@
     <row r="160">
       <c r="A160" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-04 - Water Treatment Purification Package</t>
+          <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
       </c>
       <c r="B160" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C160" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C160" s="77" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="D160" s="23" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="G160" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H160" s="65" t="inlineStr"/>
@@ -8618,17 +8618,17 @@
     <row r="161">
       <c r="A161" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="B161" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C161" s="78" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D161" s="23" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="J161" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="K161" s="23" t="n"/>
@@ -8668,17 +8668,17 @@
     <row r="162">
       <c r="A162" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-06 - Water Distribution Consumers</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="B162" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C162" s="77" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D162" s="23" t="inlineStr">
@@ -8718,17 +8718,17 @@
     <row r="163">
       <c r="A163" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="B163" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C163" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="D163" s="23" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="J163" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K163" s="23" t="n"/>
@@ -8768,17 +8768,17 @@
     <row r="164">
       <c r="A164" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="B164" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C164" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="D164" s="23" t="inlineStr">
@@ -8802,23 +8802,15 @@
         </is>
       </c>
       <c r="H164" s="65" t="inlineStr"/>
-      <c r="I164" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J164" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I164" s="65" t="inlineStr"/>
+      <c r="J164" s="23" t="inlineStr"/>
       <c r="K164" s="23" t="n"/>
       <c r="L164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B165" s="23" t="inlineStr">
@@ -8826,9 +8818,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C165" s="78" t="inlineStr">
-        <is>
-          <t>98%</t>
+      <c r="C165" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D165" s="23" t="inlineStr">
@@ -8852,23 +8844,15 @@
         </is>
       </c>
       <c r="H165" s="65" t="inlineStr"/>
-      <c r="I165" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J165" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I165" s="65" t="inlineStr"/>
+      <c r="J165" s="23" t="inlineStr"/>
       <c r="K165" s="23" t="n"/>
       <c r="L165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="B166" s="23" t="inlineStr">
@@ -8876,9 +8860,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C166" s="78" t="inlineStr">
-        <is>
-          <t>90%</t>
+      <c r="C166" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D166" s="23" t="inlineStr">
@@ -8910,7 +8894,7 @@
     <row r="167">
       <c r="A167" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B167" s="23" t="inlineStr">
@@ -8920,7 +8904,7 @@
       </c>
       <c r="C167" s="77" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="D167" s="23" t="inlineStr">
@@ -8952,7 +8936,7 @@
     <row r="168">
       <c r="A168" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-19 - Power Generation Package G</t>
         </is>
       </c>
       <c r="B168" s="23" t="inlineStr">
@@ -8960,9 +8944,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C168" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="C168" s="78" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="D168" s="23" t="inlineStr">
@@ -8986,15 +8970,23 @@
         </is>
       </c>
       <c r="H168" s="65" t="inlineStr"/>
-      <c r="I168" s="65" t="inlineStr"/>
-      <c r="J168" s="23" t="inlineStr"/>
+      <c r="I168" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J168" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K168" s="23" t="n"/>
       <c r="L168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="B169" s="23" t="inlineStr">
@@ -9004,7 +8996,7 @@
       </c>
       <c r="C169" s="77" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="D169" s="23" t="inlineStr">
@@ -9036,7 +9028,7 @@
     <row r="170">
       <c r="A170" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-19 - Power Generation Package G</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B170" s="23" t="inlineStr">
@@ -9044,9 +9036,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C170" s="78" t="inlineStr">
-        <is>
-          <t>96%</t>
+      <c r="C170" s="77" t="inlineStr">
+        <is>
+          <t>83%</t>
         </is>
       </c>
       <c r="D170" s="23" t="inlineStr">
@@ -9070,33 +9062,25 @@
         </is>
       </c>
       <c r="H170" s="65" t="inlineStr"/>
-      <c r="I170" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J170" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I170" s="65" t="inlineStr"/>
+      <c r="J170" s="23" t="inlineStr"/>
       <c r="K170" s="23" t="n"/>
       <c r="L170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="B171" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C171" s="77" t="inlineStr">
-        <is>
-          <t>60%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D171" s="23" t="inlineStr">
@@ -9120,25 +9104,33 @@
         </is>
       </c>
       <c r="H171" s="65" t="inlineStr"/>
-      <c r="I171" s="65" t="inlineStr"/>
-      <c r="J171" s="23" t="inlineStr"/>
+      <c r="I171" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J171" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K171" s="23" t="n"/>
       <c r="L171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="B172" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C172" s="77" t="inlineStr">
-        <is>
-          <t>83%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C172" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D172" s="23" t="inlineStr">
@@ -9162,15 +9154,23 @@
         </is>
       </c>
       <c r="H172" s="65" t="inlineStr"/>
-      <c r="I172" s="65" t="inlineStr"/>
-      <c r="J172" s="23" t="inlineStr"/>
+      <c r="I172" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J172" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K172" s="23" t="n"/>
       <c r="L172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="B173" s="23" t="inlineStr">
@@ -9220,7 +9220,7 @@
     <row r="174">
       <c r="A174" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="B174" s="23" t="inlineStr">
@@ -9270,7 +9270,7 @@
     <row r="175">
       <c r="A175" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="B175" s="23" t="inlineStr">
@@ -9320,12 +9320,12 @@
     <row r="176">
       <c r="A176" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="B176" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C176" s="78" t="inlineStr">
@@ -9370,12 +9370,12 @@
     <row r="177">
       <c r="A177" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="B177" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C177" s="78" t="inlineStr">
@@ -9420,12 +9420,12 @@
     <row r="178">
       <c r="A178" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="B178" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C178" s="78" t="inlineStr">
@@ -9470,12 +9470,12 @@
     <row r="179">
       <c r="A179" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="B179" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C179" s="78" t="inlineStr">
@@ -9520,7 +9520,7 @@
     <row r="180">
       <c r="A180" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="B180" s="23" t="inlineStr">
@@ -9570,12 +9570,12 @@
     <row r="181">
       <c r="A181" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="B181" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C181" s="78" t="inlineStr">
@@ -9620,12 +9620,12 @@
     <row r="182">
       <c r="A182" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="B182" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C182" s="78" t="inlineStr">
@@ -9670,12 +9670,12 @@
     <row r="183">
       <c r="A183" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="B183" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C183" s="78" t="inlineStr">
@@ -9720,12 +9720,12 @@
     <row r="184">
       <c r="A184" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="B184" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C184" s="78" t="inlineStr">
@@ -9770,12 +9770,12 @@
     <row r="185">
       <c r="A185" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="B185" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C185" s="78" t="inlineStr">
@@ -9820,12 +9820,12 @@
     <row r="186">
       <c r="A186" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="B186" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C186" s="78" t="inlineStr">
@@ -9870,7 +9870,7 @@
     <row r="187">
       <c r="A187" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="B187" s="23" t="inlineStr">
@@ -9878,9 +9878,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C187" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C187" s="77" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="D187" s="23" t="inlineStr">
@@ -9920,12 +9920,12 @@
     <row r="188">
       <c r="A188" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="B188" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C188" s="78" t="inlineStr">
@@ -9970,17 +9970,17 @@
     <row r="189">
       <c r="A189" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="B189" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C189" s="77" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D189" s="23" t="inlineStr">
@@ -10020,12 +10020,12 @@
     <row r="190">
       <c r="A190" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="B190" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C190" s="78" t="inlineStr">
@@ -10070,12 +10070,12 @@
     <row r="191">
       <c r="A191" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="B191" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C191" s="78" t="inlineStr">
@@ -10120,12 +10120,12 @@
     <row r="192">
       <c r="A192" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="B192" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C192" s="78" t="inlineStr">
@@ -10170,12 +10170,12 @@
     <row r="193">
       <c r="A193" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="B193" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C193" s="78" t="inlineStr">
@@ -10220,7 +10220,7 @@
     <row r="194">
       <c r="A194" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="B194" s="23" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="C194" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="D194" s="23" t="inlineStr">
@@ -10270,17 +10270,17 @@
     <row r="195">
       <c r="A195" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="B195" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C195" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D195" s="23" t="inlineStr">
@@ -10304,33 +10304,25 @@
         </is>
       </c>
       <c r="H195" s="65" t="inlineStr"/>
-      <c r="I195" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J195" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I195" s="65" t="inlineStr"/>
+      <c r="J195" s="23" t="inlineStr"/>
       <c r="K195" s="23" t="n"/>
       <c r="L195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="B196" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C196" s="78" t="inlineStr">
-        <is>
-          <t>93%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C196" s="77" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="D196" s="23" t="inlineStr">
@@ -10354,28 +10346,20 @@
         </is>
       </c>
       <c r="H196" s="65" t="inlineStr"/>
-      <c r="I196" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J196" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I196" s="65" t="inlineStr"/>
+      <c r="J196" s="23" t="inlineStr"/>
       <c r="K196" s="23" t="n"/>
       <c r="L196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="B197" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C197" s="78" t="inlineStr">
@@ -10412,17 +10396,17 @@
     <row r="198">
       <c r="A198" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="B198" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C198" s="77" t="inlineStr">
-        <is>
-          <t>89%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C198" s="78" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="D198" s="23" t="inlineStr">
@@ -10454,7 +10438,7 @@
     <row r="199">
       <c r="A199" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="B199" s="23" t="inlineStr">
@@ -10462,9 +10446,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C199" s="78" t="inlineStr">
-        <is>
-          <t>94%</t>
+      <c r="C199" s="77" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="D199" s="23" t="inlineStr">
@@ -10496,17 +10480,17 @@
     <row r="200">
       <c r="A200" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="B200" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C200" s="78" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D200" s="23" t="inlineStr">
@@ -10538,17 +10522,17 @@
     <row r="201">
       <c r="A201" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="B201" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C201" s="77" t="inlineStr">
-        <is>
-          <t>74%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C201" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D201" s="23" t="inlineStr">
@@ -10580,17 +10564,17 @@
     <row r="202">
       <c r="A202" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="B202" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C202" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C202" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D202" s="23" t="inlineStr">
@@ -10622,17 +10606,17 @@
     <row r="203">
       <c r="A203" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="B203" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C203" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C203" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D203" s="23" t="inlineStr">
@@ -10664,7 +10648,7 @@
     <row r="204">
       <c r="A204" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="B204" s="23" t="inlineStr">
@@ -10674,7 +10658,7 @@
       </c>
       <c r="C204" s="77" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="D204" s="23" t="inlineStr">
@@ -10706,17 +10690,17 @@
     <row r="205">
       <c r="A205" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="B205" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C205" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D205" s="23" t="inlineStr">
@@ -10740,25 +10724,33 @@
         </is>
       </c>
       <c r="H205" s="65" t="inlineStr"/>
-      <c r="I205" s="65" t="inlineStr"/>
-      <c r="J205" s="23" t="inlineStr"/>
+      <c r="I205" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J205" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K205" s="23" t="n"/>
       <c r="L205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="B206" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C206" s="77" t="inlineStr">
-        <is>
-          <t>71%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C206" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D206" s="23" t="inlineStr">
@@ -10782,20 +10774,28 @@
         </is>
       </c>
       <c r="H206" s="65" t="inlineStr"/>
-      <c r="I206" s="65" t="inlineStr"/>
-      <c r="J206" s="23" t="inlineStr"/>
+      <c r="I206" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J206" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K206" s="23" t="n"/>
       <c r="L206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="B207" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C207" s="78" t="inlineStr">
@@ -10840,12 +10840,12 @@
     <row r="208">
       <c r="A208" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="B208" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C208" s="78" t="inlineStr">
@@ -10890,12 +10890,12 @@
     <row r="209">
       <c r="A209" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="B209" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C209" s="78" t="inlineStr">
@@ -10940,12 +10940,12 @@
     <row r="210">
       <c r="A210" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="B210" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C210" s="78" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="211">
       <c r="A211" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="B211" s="23" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="C211" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="D211" s="23" t="inlineStr">
@@ -11040,17 +11040,17 @@
     <row r="212">
       <c r="A212" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="B212" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C212" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C212" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D212" s="23" t="inlineStr">
@@ -11090,17 +11090,17 @@
     <row r="213">
       <c r="A213" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="B213" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C213" s="78" t="inlineStr">
-        <is>
-          <t>90%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C213" s="77" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="D213" s="23" t="inlineStr">
@@ -11140,17 +11140,17 @@
     <row r="214">
       <c r="A214" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="B214" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C214" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C214" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D214" s="23" t="inlineStr">
@@ -11190,17 +11190,17 @@
     <row r="215">
       <c r="A215" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-61-08 - Electrical Control System</t>
         </is>
       </c>
       <c r="B215" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C215" s="77" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C215" s="76" t="inlineStr">
+        <is>
+          <t>21%</t>
         </is>
       </c>
       <c r="D215" s="23" t="inlineStr">
@@ -11240,17 +11240,17 @@
     <row r="216">
       <c r="A216" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
       </c>
       <c r="B216" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C216" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C216" s="76" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
       <c r="D216" s="23" t="inlineStr">
@@ -11290,7 +11290,7 @@
     <row r="217">
       <c r="A217" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-08 - Electrical Control System</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="B217" s="23" t="inlineStr">
@@ -11298,9 +11298,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C217" s="76" t="inlineStr">
-        <is>
-          <t>21%</t>
+      <c r="C217" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D217" s="23" t="inlineStr">
@@ -11340,17 +11340,17 @@
     <row r="218">
       <c r="A218" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="B218" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C218" s="76" t="inlineStr">
-        <is>
-          <t>5%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C218" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D218" s="23" t="inlineStr">
@@ -11390,67 +11390,45 @@
     <row r="219">
       <c r="A219" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
-        </is>
-      </c>
-      <c r="B219" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C219" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D219" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E219" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F219" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G219" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
+        </is>
+      </c>
+      <c r="B219" s="23" t="inlineStr"/>
+      <c r="C219" s="76" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="D219" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" s="65" t="inlineStr"/>
       <c r="H219" s="65" t="inlineStr"/>
-      <c r="I219" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J219" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I219" s="65" t="inlineStr"/>
+      <c r="J219" s="23" t="inlineStr"/>
       <c r="K219" s="23" t="n"/>
       <c r="L219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
       </c>
       <c r="B220" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C220" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C220" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D220" s="23" t="inlineStr">
@@ -11490,45 +11468,67 @@
     <row r="221">
       <c r="A221" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
-        </is>
-      </c>
-      <c r="B221" s="23" t="inlineStr"/>
+          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
+        </is>
+      </c>
+      <c r="B221" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C221" s="76" t="inlineStr">
         <is>
-          <t>32%</t>
-        </is>
-      </c>
-      <c r="D221" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E221" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F221" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" s="65" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D221" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E221" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F221" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G221" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H221" s="65" t="inlineStr"/>
-      <c r="I221" s="65" t="inlineStr"/>
-      <c r="J221" s="23" t="inlineStr"/>
+      <c r="I221" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J221" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K221" s="23" t="n"/>
       <c r="L221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
+          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
       </c>
       <c r="B222" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C222" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="D222" s="23" t="inlineStr">
@@ -11568,17 +11568,17 @@
     <row r="223">
       <c r="A223" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
+          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
       </c>
       <c r="B223" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C223" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D223" s="23" t="inlineStr">
@@ -11618,7 +11618,7 @@
     <row r="224">
       <c r="A224" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="B224" s="23" t="inlineStr">
@@ -11626,9 +11626,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C224" s="76" t="inlineStr">
-        <is>
-          <t>6%</t>
+      <c r="C224" s="77" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="D224" s="23" t="inlineStr">
@@ -11668,7 +11668,7 @@
     <row r="225">
       <c r="A225" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="B225" s="23" t="inlineStr">
@@ -11676,9 +11676,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C225" s="76" t="inlineStr">
-        <is>
-          <t>4%</t>
+      <c r="C225" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D225" s="23" t="inlineStr">
@@ -11718,17 +11718,17 @@
     <row r="226">
       <c r="A226" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B226" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C226" s="77" t="inlineStr">
-        <is>
-          <t>50%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C226" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D226" s="23" t="inlineStr">
@@ -11768,17 +11768,17 @@
     <row r="227">
       <c r="A227" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
       </c>
       <c r="B227" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C227" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C227" s="76" t="inlineStr">
+        <is>
+          <t>26%</t>
         </is>
       </c>
       <c r="D227" s="23" t="inlineStr">
@@ -11818,17 +11818,17 @@
     <row r="228">
       <c r="A228" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
       </c>
       <c r="B228" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C228" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="D228" s="23" t="inlineStr">
@@ -11868,17 +11868,17 @@
     <row r="229">
       <c r="A229" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
+          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
       </c>
       <c r="B229" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C229" s="76" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="D229" s="23" t="inlineStr">
@@ -11918,17 +11918,17 @@
     <row r="230">
       <c r="A230" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
       </c>
       <c r="B230" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C230" s="76" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="D230" s="23" t="inlineStr">
@@ -11968,17 +11968,17 @@
     <row r="231">
       <c r="A231" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
       </c>
       <c r="B231" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C231" s="76" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="D231" s="23" t="inlineStr">
@@ -12018,17 +12018,17 @@
     <row r="232">
       <c r="A232" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
       </c>
       <c r="B232" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C232" s="76" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="D232" s="23" t="inlineStr">
@@ -12068,163 +12068,163 @@
     <row r="233">
       <c r="A233" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
-        </is>
-      </c>
-      <c r="B233" s="23" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C233" s="76" t="inlineStr">
-        <is>
-          <t>23%</t>
-        </is>
-      </c>
-      <c r="D233" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E233" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F233" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G233" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
+        </is>
+      </c>
+      <c r="B233" s="23" t="inlineStr"/>
+      <c r="C233" s="78" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="D233" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="65" t="inlineStr"/>
       <c r="H233" s="65" t="inlineStr"/>
-      <c r="I233" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J233" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I233" s="65" t="inlineStr"/>
+      <c r="J233" s="23" t="inlineStr"/>
       <c r="K233" s="23" t="n"/>
       <c r="L233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
-        </is>
-      </c>
-      <c r="B234" s="23" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C234" s="76" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="D234" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E234" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F234" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
+        </is>
+      </c>
+      <c r="B234" s="23" t="inlineStr"/>
+      <c r="C234" s="78" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="D234" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" s="65" t="inlineStr"/>
       <c r="H234" s="65" t="inlineStr"/>
-      <c r="I234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J234" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I234" s="65" t="inlineStr"/>
+      <c r="J234" s="23" t="inlineStr"/>
       <c r="K234" s="23" t="n"/>
       <c r="L234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
-        </is>
-      </c>
-      <c r="B235" s="23" t="inlineStr"/>
-      <c r="C235" s="78" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="D235" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E235" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F235" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" s="65" t="inlineStr"/>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+        </is>
+      </c>
+      <c r="B235" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C235" s="76" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D235" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E235" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F235" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G235" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H235" s="65" t="inlineStr"/>
-      <c r="I235" s="65" t="inlineStr"/>
-      <c r="J235" s="23" t="inlineStr"/>
+      <c r="I235" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J235" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K235" s="23" t="n"/>
       <c r="L235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
-        </is>
-      </c>
-      <c r="B236" s="23" t="inlineStr"/>
-      <c r="C236" s="78" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="D236" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E236" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F236" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" s="65" t="inlineStr"/>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+        </is>
+      </c>
+      <c r="B236" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C236" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D236" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E236" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F236" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G236" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H236" s="65" t="inlineStr"/>
-      <c r="I236" s="65" t="inlineStr"/>
-      <c r="J236" s="23" t="inlineStr"/>
+      <c r="I236" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J236" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K236" s="23" t="n"/>
       <c r="L236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B237" s="23" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="C237" s="76" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D237" s="23" t="inlineStr">
@@ -12274,7 +12274,7 @@
     <row r="238">
       <c r="A238" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B238" s="23" t="inlineStr">
@@ -12324,7 +12324,7 @@
     <row r="239">
       <c r="A239" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
       </c>
       <c r="B239" s="23" t="inlineStr">
@@ -12374,7 +12374,7 @@
     <row r="240">
       <c r="A240" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
       </c>
       <c r="B240" s="23" t="inlineStr">
@@ -12424,7 +12424,7 @@
     <row r="241">
       <c r="A241" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B241" s="23" t="inlineStr">
@@ -12474,12 +12474,12 @@
     <row r="242">
       <c r="A242" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
+          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
       </c>
       <c r="B242" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C242" s="76" t="inlineStr">
@@ -12524,57 +12524,35 @@
     <row r="243">
       <c r="A243" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
-        </is>
-      </c>
-      <c r="B243" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C243" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D243" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E243" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F243" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G243" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+        </is>
+      </c>
+      <c r="B243" s="23" t="inlineStr"/>
+      <c r="C243" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D243" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="65" t="inlineStr"/>
       <c r="H243" s="65" t="inlineStr"/>
-      <c r="I243" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J243" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I243" s="65" t="inlineStr"/>
+      <c r="J243" s="23" t="inlineStr"/>
       <c r="K243" s="23" t="n"/>
       <c r="L243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
+          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
       </c>
       <c r="B244" s="23" t="inlineStr">
@@ -12624,35 +12602,57 @@
     <row r="245">
       <c r="A245" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
-        </is>
-      </c>
-      <c r="B245" s="23" t="inlineStr"/>
-      <c r="C245" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D245" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E245" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F245" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" s="65" t="inlineStr"/>
+          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
+        </is>
+      </c>
+      <c r="B245" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C245" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D245" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E245" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F245" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G245" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H245" s="65" t="inlineStr"/>
-      <c r="I245" s="65" t="inlineStr"/>
-      <c r="J245" s="23" t="inlineStr"/>
+      <c r="I245" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J245" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K245" s="23" t="n"/>
       <c r="L245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
+          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B246" s="23" t="inlineStr">
@@ -12702,17 +12702,17 @@
     <row r="247">
       <c r="A247" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="B247" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C247" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C247" s="77" t="inlineStr">
+        <is>
+          <t>71%</t>
         </is>
       </c>
       <c r="D247" s="23" t="inlineStr">
@@ -12752,57 +12752,35 @@
     <row r="248">
       <c r="A248" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
-        </is>
-      </c>
-      <c r="B248" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C248" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D248" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E248" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F248" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G248" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+        </is>
+      </c>
+      <c r="B248" s="23" t="inlineStr"/>
+      <c r="C248" s="77" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="D248" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="65" t="inlineStr"/>
       <c r="H248" s="65" t="inlineStr"/>
-      <c r="I248" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J248" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I248" s="65" t="inlineStr"/>
+      <c r="J248" s="23" t="inlineStr"/>
       <c r="K248" s="23" t="n"/>
       <c r="L248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B249" s="23" t="inlineStr">
@@ -12812,7 +12790,7 @@
       </c>
       <c r="C249" s="77" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="D249" s="23" t="inlineStr">
@@ -12852,25 +12830,39 @@
     <row r="250">
       <c r="A250" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
-        </is>
-      </c>
-      <c r="B250" s="23" t="inlineStr"/>
-      <c r="C250" s="76" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="D250" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E250" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F250" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" s="65" t="inlineStr"/>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+        </is>
+      </c>
+      <c r="B250" s="23" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C250" s="78" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="D250" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E250" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F250" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G250" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H250" s="65" t="inlineStr"/>
       <c r="I250" s="65" t="inlineStr"/>
       <c r="J250" s="23" t="inlineStr"/>
@@ -12880,7 +12872,7 @@
     <row r="251">
       <c r="A251" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B251" s="23" t="inlineStr">
@@ -12930,17 +12922,17 @@
     <row r="252">
       <c r="A252" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="B252" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C252" s="78" t="inlineStr">
-        <is>
-          <t>95%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C252" s="77" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
       <c r="D252" s="23" t="inlineStr">
@@ -12964,15 +12956,23 @@
         </is>
       </c>
       <c r="H252" s="65" t="inlineStr"/>
-      <c r="I252" s="65" t="inlineStr"/>
-      <c r="J252" s="23" t="inlineStr"/>
+      <c r="I252" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J252" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K252" s="23" t="n"/>
       <c r="L252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B253" s="23" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="C253" s="77" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="D253" s="23" t="inlineStr">
@@ -13022,7 +13022,7 @@
     <row r="254">
       <c r="A254" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="B254" s="23" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="C254" s="77" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="D254" s="23" t="inlineStr">
@@ -13072,7 +13072,7 @@
     <row r="255">
       <c r="A255" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
+          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
       </c>
       <c r="B255" s="23" t="inlineStr">
@@ -13080,9 +13080,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C255" s="77" t="inlineStr">
-        <is>
-          <t>73%</t>
+      <c r="C255" s="78" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D255" s="23" t="inlineStr">
@@ -13122,17 +13122,17 @@
     <row r="256">
       <c r="A256" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="B256" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C256" s="77" t="inlineStr">
-        <is>
-          <t>82%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C256" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D256" s="23" t="inlineStr">
@@ -13172,7 +13172,7 @@
     <row r="257">
       <c r="A257" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="B257" s="23" t="inlineStr">
@@ -13180,9 +13180,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C257" s="78" t="inlineStr">
-        <is>
-          <t>90%</t>
+      <c r="C257" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D257" s="23" t="inlineStr">
@@ -13222,17 +13222,17 @@
     <row r="258">
       <c r="A258" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
       </c>
       <c r="B258" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C258" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C258" s="77" t="inlineStr">
+        <is>
+          <t>78%</t>
         </is>
       </c>
       <c r="D258" s="23" t="inlineStr">
@@ -13272,7 +13272,7 @@
     <row r="259">
       <c r="A259" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="B259" s="23" t="inlineStr">
@@ -13280,9 +13280,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C259" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="C259" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D259" s="23" t="inlineStr">
@@ -13322,7 +13322,7 @@
     <row r="260">
       <c r="A260" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="B260" s="23" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="C260" s="77" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="D260" s="23" t="inlineStr">
@@ -13372,17 +13372,17 @@
     <row r="261">
       <c r="A261" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-75-01 - DRA Injection Package</t>
         </is>
       </c>
       <c r="B261" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C261" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C261" s="76" t="inlineStr">
+        <is>
+          <t>37%</t>
         </is>
       </c>
       <c r="D261" s="23" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="G261" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H261" s="65" t="inlineStr"/>
@@ -13422,17 +13422,17 @@
     <row r="262">
       <c r="A262" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="B262" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C262" s="77" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="D262" s="23" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="263">
       <c r="A263" s="68" t="inlineStr">
         <is>
-          <t>PS5-75-01 - DRA Injection Package</t>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
       </c>
       <c r="B263" s="23" t="inlineStr">
@@ -13480,9 +13480,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C263" s="76" t="inlineStr">
-        <is>
-          <t>37%</t>
+      <c r="C263" s="77" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
       <c r="D263" s="23" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="G263" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H263" s="65" t="inlineStr"/>
@@ -13522,7 +13522,7 @@
     <row r="264">
       <c r="A264" s="68" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
       <c r="B264" s="23" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="C264" s="77" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="D264" s="23" t="inlineStr">
@@ -13572,7 +13572,7 @@
     <row r="265">
       <c r="A265" s="68" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
       </c>
       <c r="B265" s="23" t="inlineStr">
@@ -13580,9 +13580,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C265" s="77" t="inlineStr">
-        <is>
-          <t>64%</t>
+      <c r="C265" s="76" t="inlineStr">
+        <is>
+          <t>10%</t>
         </is>
       </c>
       <c r="D265" s="23" t="inlineStr">
@@ -13622,7 +13622,7 @@
     <row r="266">
       <c r="A266" s="68" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
       </c>
       <c r="B266" s="23" t="inlineStr">
@@ -13630,9 +13630,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C266" s="77" t="inlineStr">
-        <is>
-          <t>73%</t>
+      <c r="C266" s="76" t="inlineStr">
+        <is>
+          <t>7%</t>
         </is>
       </c>
       <c r="D266" s="23" t="inlineStr">
@@ -13672,7 +13672,7 @@
     <row r="267">
       <c r="A267" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
+          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
       </c>
       <c r="B267" s="23" t="inlineStr">
@@ -13722,7 +13722,7 @@
     <row r="268">
       <c r="A268" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
+          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
       </c>
       <c r="B268" s="23" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="C268" s="76" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="D268" s="23" t="inlineStr">
@@ -13772,7 +13772,7 @@
     <row r="269">
       <c r="A269" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
+          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
       </c>
       <c r="B269" s="23" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="C269" s="76" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="D269" s="23" t="inlineStr">
@@ -13822,7 +13822,7 @@
     <row r="270">
       <c r="A270" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
+          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
       </c>
       <c r="B270" s="23" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C270" s="76" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="D270" s="23" t="inlineStr">
@@ -13872,7 +13872,7 @@
     <row r="271">
       <c r="A271" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
+          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
       </c>
       <c r="B271" s="23" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="C271" s="76" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="D271" s="23" t="inlineStr">
@@ -13922,7 +13922,7 @@
     <row r="272">
       <c r="A272" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
+          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
       </c>
       <c r="B272" s="23" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C272" s="76" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="D272" s="23" t="inlineStr">
@@ -13972,7 +13972,7 @@
     <row r="273">
       <c r="A273" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
+          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
       </c>
       <c r="B273" s="23" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="C273" s="76" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="D273" s="23" t="inlineStr">
@@ -14022,7 +14022,7 @@
     <row r="274">
       <c r="A274" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
+          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
       </c>
       <c r="B274" s="23" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C274" s="76" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="D274" s="23" t="inlineStr">
@@ -14072,7 +14072,7 @@
     <row r="275">
       <c r="A275" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
+          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
       </c>
       <c r="B275" s="23" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="C275" s="76" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="D275" s="23" t="inlineStr">
@@ -14122,7 +14122,7 @@
     <row r="276">
       <c r="A276" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
+          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
       </c>
       <c r="B276" s="23" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="C276" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="D276" s="23" t="inlineStr">
@@ -14172,17 +14172,17 @@
     <row r="277">
       <c r="A277" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="B277" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C277" s="76" t="inlineStr">
-        <is>
-          <t>11%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C277" s="77" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="D277" s="23" t="inlineStr">
@@ -14222,17 +14222,17 @@
     <row r="278">
       <c r="A278" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
+          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
       </c>
       <c r="B278" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C278" s="76" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="D278" s="23" t="inlineStr">
@@ -14272,7 +14272,7 @@
     <row r="279">
       <c r="A279" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
       </c>
       <c r="B279" s="23" t="inlineStr">
@@ -14280,9 +14280,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C279" s="77" t="inlineStr">
-        <is>
-          <t>60%</t>
+      <c r="C279" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D279" s="23" t="inlineStr">
@@ -14322,7 +14322,7 @@
     <row r="280">
       <c r="A280" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
+          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
       </c>
       <c r="B280" s="23" t="inlineStr">
@@ -14330,9 +14330,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C280" s="76" t="inlineStr">
-        <is>
-          <t>17%</t>
+      <c r="C280" s="77" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
       <c r="D280" s="23" t="inlineStr">
@@ -14372,17 +14372,17 @@
     <row r="281">
       <c r="A281" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B281" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C281" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="D281" s="23" t="inlineStr">
@@ -14422,17 +14422,17 @@
     <row r="282">
       <c r="A282" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B282" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C282" s="77" t="inlineStr">
-        <is>
-          <t>75%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C282" s="76" t="inlineStr">
+        <is>
+          <t>8%</t>
         </is>
       </c>
       <c r="D282" s="23" t="inlineStr">
@@ -14472,7 +14472,7 @@
     <row r="283">
       <c r="A283" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-82-07 - Guard Huts</t>
         </is>
       </c>
       <c r="B283" s="23" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="C283" s="76" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D283" s="23" t="inlineStr">
@@ -14522,17 +14522,17 @@
     <row r="284">
       <c r="A284" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="B284" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C284" s="76" t="inlineStr">
-        <is>
-          <t>8%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C284" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D284" s="23" t="inlineStr">
@@ -14572,17 +14572,17 @@
     <row r="285">
       <c r="A285" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-07 - Guard Huts</t>
+          <t>PS5-84-01 - Generator Building</t>
         </is>
       </c>
       <c r="B285" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C285" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="D285" s="23" t="inlineStr">
@@ -14622,17 +14622,17 @@
     <row r="286">
       <c r="A286" s="68" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B286" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C286" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C286" s="76" t="inlineStr">
+        <is>
+          <t>11%</t>
         </is>
       </c>
       <c r="D286" s="23" t="inlineStr">
@@ -14672,17 +14672,17 @@
     <row r="287">
       <c r="A287" s="68" t="inlineStr">
         <is>
-          <t>PS5-84-01 - Generator Building</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="B287" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C287" s="76" t="inlineStr">
-        <is>
-          <t>45%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C287" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D287" s="23" t="inlineStr">
@@ -14722,17 +14722,17 @@
     <row r="288">
       <c r="A288" s="68" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="B288" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C288" s="76" t="inlineStr">
-        <is>
-          <t>11%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C288" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D288" s="23" t="inlineStr">
@@ -14772,12 +14772,12 @@
     <row r="289">
       <c r="A289" s="68" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
       <c r="B289" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C289" s="78" t="inlineStr">
@@ -14822,7 +14822,7 @@
     <row r="290">
       <c r="A290" s="68" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
       </c>
       <c r="B290" s="23" t="inlineStr">
@@ -14830,9 +14830,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C290" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C290" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D290" s="23" t="inlineStr">
@@ -14872,17 +14872,17 @@
     <row r="291">
       <c r="A291" s="68" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
       </c>
       <c r="B291" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C291" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C291" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D291" s="23" t="inlineStr">
@@ -14922,12 +14922,12 @@
     <row r="292">
       <c r="A292" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-01 - Area Completion for Building area</t>
+          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
       </c>
       <c r="B292" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C292" s="76" t="inlineStr">
@@ -14972,12 +14972,12 @@
     <row r="293">
       <c r="A293" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-02 - Area Completion for Utility area</t>
+          <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
       </c>
       <c r="B293" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C293" s="76" t="inlineStr">
@@ -15022,7 +15022,7 @@
     <row r="294">
       <c r="A294" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+          <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
       </c>
       <c r="B294" s="23" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="C294" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="D294" s="23" t="inlineStr">
@@ -15072,7 +15072,7 @@
     <row r="295">
       <c r="A295" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-04 - Area Completion for Process area</t>
+          <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
       </c>
       <c r="B295" s="23" t="inlineStr">
@@ -15080,9 +15080,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C295" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C295" s="77" t="inlineStr">
+        <is>
+          <t>67%</t>
         </is>
       </c>
       <c r="D295" s="23" t="inlineStr">
@@ -15119,108 +15119,8 @@
       <c r="K295" s="23" t="n"/>
       <c r="L295" s="67" t="inlineStr"/>
     </row>
-    <row r="296">
-      <c r="A296" s="68" t="inlineStr">
-        <is>
-          <t>PS5-99-05 - Area Completion for CFO area</t>
-        </is>
-      </c>
-      <c r="B296" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C296" s="76" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="D296" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E296" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F296" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G296" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H296" s="65" t="inlineStr"/>
-      <c r="I296" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J296" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K296" s="23" t="n"/>
-      <c r="L296" s="67" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="68" t="inlineStr">
-        <is>
-          <t>PS5-99-06 - Area Completion for Power Generation area</t>
-        </is>
-      </c>
-      <c r="B297" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C297" s="77" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="D297" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E297" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F297" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G297" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H297" s="65" t="inlineStr"/>
-      <c r="I297" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J297" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K297" s="23" t="n"/>
-      <c r="L297" s="67" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:L297"/>
+  <autoFilter ref="A2:L295"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -15518,8 +15418,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A293" r:id="rId291"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A294" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A295" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId295"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15531,7 +15429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16113,2962 +16011,2938 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PS5-08-01</t>
+          <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PS5-08-01</t>
+          <t>PS5-08-01a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PS5-08-01a - PAGA (Required for SU)</t>
+          <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PS5-08-01a</t>
+          <t>PS5-08-01b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PS5-08-01b - PAGA (Not required for SU)</t>
+          <t>PS5-08-03 - Telephone</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PS5-08-01b</t>
+          <t>PS5-08-03</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
+          <t>PS5-08-04 - Hotline</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PS5-08-03</t>
+          <t>PS5-08-04</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PS5-08-04 - Hotline</t>
+          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PS5-08-04</t>
+          <t>PS5-08-07</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
+          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PS5-08-07</t>
+          <t>PS5-08-11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PS5-08-11</t>
+          <t>PS5-08-12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PS5-08-12</t>
+          <t>PS5-08-13</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
+          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PS5-08-13</t>
+          <t>PS5-08-14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
+          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PS5-08-14</t>
+          <t>PS5-08-15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
+          <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PS5-08-15</t>
+          <t>PS5-08-23</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PS5-08-23 - VHF Trunk Radio System</t>
+          <t>PS5-08-34 - Satphone</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PS5-08-23</t>
+          <t>PS5-08-34</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PS5-08-34 - Satphone</t>
+          <t>PS5-08-35 - Optical Transport Network</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PS5-08-34</t>
+          <t>PS5-08-35</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PS5-08-35 - Optical Transport Network</t>
+          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PS5-08-35</t>
+          <t>PS5-08-36</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
+          <t>PS5-08-51 - Entertainment</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PS5-08-36</t>
+          <t>PS5-08-51</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PS5-08-51 - Entertainment</t>
+          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PS5-08-51</t>
+          <t>PS5-08-52a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
+          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PS5-08-52a</t>
+          <t>PS5-08-52b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
+          <t>PS5-08-55 - Videoconference</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PS5-08-52b</t>
+          <t>PS5-08-55</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PS5-08-55 - Videoconference</t>
+          <t>PS5-08-61 - Meteocean</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PS5-08-55</t>
+          <t>PS5-08-61</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PS5-08-61 - Meteocean</t>
+          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PS5-08-61</t>
+          <t>PS5-08-71</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
+          <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PS5-08-71</t>
+          <t>PS5-08-72</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PS5-08-72 - Structured Cabling (FO)</t>
+          <t>PS5-08-81 - Guard tour</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PS5-08-72</t>
+          <t>PS5-08-81</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PS5-08-81 - Guard tour</t>
+          <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PS5-08-81</t>
+          <t>PS5-08-82</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PS5-08-82 - Key Management</t>
+          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PS5-08-82</t>
+          <t>PS5-08-83</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PS5-08-83</t>
+          <t>PS5-08-85a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PS5-08-85</t>
+          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PS5-08-85</t>
+          <t>PS5-08-85b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
+          <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PS5-08-85a</t>
+          <t>PS5-08-86</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
+          <t>PS5-08-92 - Telecom Mast</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PS5-08-85b</t>
+          <t>PS5-08-92</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PS5-08-86 - Integrated Security Management System</t>
+          <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PS5-08-86</t>
+          <t>PS5-08-93</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PS5-08-92 - Telecom Mast</t>
+          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PS5-08-92</t>
+          <t>PS5-09-01</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PS5-08-93 - Telecom Monitoring System</t>
+          <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PS5-08-93</t>
+          <t>PS5-09-02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
+          <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PS5-09-01</t>
+          <t>PS5-09-03</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PS5-09-02 - HVAC for Guard House</t>
+          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PS5-09-02</t>
+          <t>PS5-09-04</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PS5-09-03 - HVAC for Generator Building</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PS5-09-03</t>
+          <t>PS5-09-05</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
+          <t>PS5-0H-01 - HIPPS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PS5-09-04</t>
+          <t>PS5-0H-01</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
+          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PS5-09-05</t>
+          <t>PS5-25-01</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PS5-0H-01 - HIPPS</t>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PS5-0H-01</t>
+          <t>PS5-25-02</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PS5-25-01</t>
+          <t>PS5-25-03</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PS5-25-02</t>
+          <t>PS5-25-04</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PS5-25-03</t>
+          <t>PS5-25-05</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PS5-25-04</t>
+          <t>PS5-25-06</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PS5-25-05</t>
+          <t>PS5-25-07</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
+          <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PS5-25-06</t>
+          <t>PS5-28-01</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PS5-25-07</t>
+          <t>PS5-28-02</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PS5-28-01 - Closed Drain Header 1</t>
+          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PS5-28-01</t>
+          <t>PS5-28-03</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PS5-28-02</t>
+          <t>PS5-28-04</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PS5-28-03</t>
+          <t>PS5-28-05</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PS5-28-04</t>
+          <t>PS5-28-06</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PS5-28-05</t>
+          <t>PS5-28-07</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PS5-28-06</t>
+          <t>PS5-28-08</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
+          <t>PS5-28-09 - Observation Basin</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PS5-28-07</t>
+          <t>PS5-28-09</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+          <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PS5-28-08</t>
+          <t>PS5-28-10</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PS5-28-09 - Observation Basin</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PS5-28-09</t>
+          <t>PS5-28-11</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PS5-28-10 - Oil Skimmer Package</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PS5-28-10</t>
+          <t>PS5-28-12</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PS5-28-11</t>
+          <t>PS5-28-13</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PS5-28-12</t>
+          <t>PS5-28-14</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PS5-28-13</t>
+          <t>PS5-28-15</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+          <t>PS5-28-16 - LP Relief Header</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PS5-28-14</t>
+          <t>PS5-28-16</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+          <t>PS5-28-17 - Reinjection Pump</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PS5-28-15</t>
+          <t>PS5-28-17</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PS5-28-16</t>
+          <t>PS5-50-01</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PS5-28-17 - Reinjection Pump</t>
+          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PS5-28-17</t>
+          <t>PS5-50-02</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
+          <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PS5-50-01</t>
+          <t>PS5-50-03</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
+          <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PS5-50-02</t>
+          <t>PS5-53-01</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PS5-50-03 - Water Pre-Treatment Package</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PS5-50-03</t>
+          <t>PS5-53-02</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PS5-53-01 - Utility Water / Storage Tank</t>
+          <t>PS5-53-03 - Water Softener Package</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PS5-53-01</t>
+          <t>PS5-53-03</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+          <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PS5-53-02</t>
+          <t>PS5-53-04</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PS5-53-03 - Water Softener Package</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PS5-53-03</t>
+          <t>PS5-53-05</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PS5-53-04 - Water Treatment Purification Package</t>
+          <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PS5-53-04</t>
+          <t>PS5-53-06</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PS5-53-05</t>
+          <t>PS5-60-01</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PS5-53-06 - Water Distribution Consumers</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PS5-53-06</t>
+          <t>PS5-60-02</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PS5-60-01</t>
+          <t>PS5-60-03</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PS5-60-02</t>
+          <t>PS5-60-04</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PS5-60-03</t>
+          <t>PS5-60-05</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PS5-60-04</t>
+          <t>PS5-60-06</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+          <t>PS5-60-07 - Power Generation Package C</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PS5-60-05</t>
+          <t>PS5-60-07</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PS5-60-06</t>
+          <t>PS5-60-08</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PS5-60-07 - Power Generation Package C</t>
+          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PS5-60-07</t>
+          <t>PS5-60-09</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
+          <t>PS5-60-10 - Power Generation Package D</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PS5-60-08</t>
+          <t>PS5-60-10</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PS5-60-09</t>
+          <t>PS5-60-11</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PS5-60-10 - Power Generation Package D</t>
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PS5-60-10</t>
+          <t>PS5-60-12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PS5-60-11</t>
+          <t>PS5-60-13</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PS5-60-12</t>
+          <t>PS5-60-14</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PS5-60-13</t>
+          <t>PS5-60-15</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-60-16 - Power Generation Package F</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PS5-60-14</t>
+          <t>PS5-60-16</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PS5-60-15</t>
+          <t>PS5-60-17</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PS5-60-16 - Power Generation Package F</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PS5-60-16</t>
+          <t>PS5-60-18</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-19 - Power Generation Package G</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PS5-60-17</t>
+          <t>PS5-60-19</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PS5-60-18</t>
+          <t>PS5-60-20</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PS5-60-19 - Power Generation Package G</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PS5-60-19</t>
+          <t>PS5-60-21</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PS5-60-20</t>
+          <t>PS5-60-22</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PS5-60-21</t>
+          <t>PS5-60-23</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PS5-60-22 - Power Gen Master UCP</t>
+          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PS5-60-22</t>
+          <t>PS5-60-24</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PS5-60-23</t>
+          <t>PS5-60-25</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PS5-60-24</t>
+          <t>PS5-60-26</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PS5-60-25</t>
+          <t>PS5-60-27</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PS5-60-26</t>
+          <t>PS5-60-28</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PS5-60-27</t>
+          <t>PS5-60-29</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PS5-60-28</t>
+          <t>PS5-60-30</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PS5-60-29</t>
+          <t>PS5-60-31</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PS5-60-30</t>
+          <t>PS5-60-32</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PS5-60-31</t>
+          <t>PS5-60-33</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PS5-60-32</t>
+          <t>PS5-60-34</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PS5-60-33</t>
+          <t>PS5-60-35</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PS5-60-34</t>
+          <t>PS5-60-36</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PS5-60-35</t>
+          <t>PS5-60-37</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PS5-60-36</t>
+          <t>PS5-60-38</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PS5-60-37</t>
+          <t>PS5-60-39</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PS5-60-38</t>
+          <t>PS5-60-40</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PS5-60-39</t>
+          <t>PS5-60-41</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PS5-60-40</t>
+          <t>PS5-60-42</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PS5-60-41</t>
+          <t>PS5-60-43</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PS5-60-42</t>
+          <t>PS5-60-44</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PS5-60-43</t>
+          <t>PS5-60-45</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PS5-60-44</t>
+          <t>PS5-60-46</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PS5-60-45</t>
+          <t>PS5-60-47</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PS5-60-46</t>
+          <t>PS5-60-48</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PS5-60-47</t>
+          <t>PS5-60-49</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PS5-60-48</t>
+          <t>PS5-60-50</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PS5-60-49</t>
+          <t>PS5-60-51</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PS5-60-50</t>
+          <t>PS5-60-52</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PS5-60-51</t>
+          <t>PS5-60-53</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PS5-60-52</t>
+          <t>PS5-60-54</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PS5-60-53</t>
+          <t>PS5-60-55</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PS5-60-54</t>
+          <t>PS5-60-56</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PS5-60-55</t>
+          <t>PS5-60-57</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PS5-60-56</t>
+          <t>PS5-60-58</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PS5-60-57</t>
+          <t>PS5-60-59</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PS5-60-58</t>
+          <t>PS5-60-60</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PS5-60-59</t>
+          <t>PS5-60-61</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PS5-60-60</t>
+          <t>PS5-60-62</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
+          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PS5-60-61</t>
+          <t>PS5-60-63</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PS5-60-62</t>
+          <t>PS5-60-64</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PS5-60-63</t>
+          <t>PS5-60-65</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
+          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PS5-60-64</t>
+          <t>PS5-60-66</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PS5-60-65</t>
+          <t>PS5-60-67</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PS5-60-66</t>
+          <t>PS5-60-68</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PS5-60-67</t>
+          <t>PS5-60-69</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PS5-60-68</t>
+          <t>PS5-60-70</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PS5-60-69</t>
+          <t>PS5-60-71</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PS5-60-70</t>
+          <t>PS5-60-72</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PS5-60-71</t>
+          <t>PS5-60-73</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PS5-60-72</t>
+          <t>PS5-60-74</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PS5-60-73</t>
+          <t>PS5-60-75</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PS5-60-74</t>
+          <t>PS5-60-76</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PS5-60-75</t>
+          <t>PS5-61-01</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PS5-60-76</t>
+          <t>PS5-61-02</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PS5-61-01</t>
+          <t>PS5-61-03</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PS5-61-02</t>
+          <t>PS5-61-04</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PS5-61-03</t>
+          <t>PS5-61-05</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
+          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PS5-61-04</t>
+          <t>PS5-61-06</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PS5-61-05</t>
+          <t>PS5-61-07</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
+          <t>PS5-61-08 - Electrical Control System</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PS5-61-06</t>
+          <t>PS5-61-08</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PS5-61-07</t>
+          <t>PS5-61-09</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PS5-61-08 - Electrical Control System</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PS5-61-08</t>
+          <t>PS5-61-10</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PS5-61-09</t>
+          <t>PS5-61-11</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PS5-61-10</t>
+          <t>PS5-61-12</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PS5-61-11</t>
+          <t>PS5-61-13</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
+          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PS5-61-12</t>
+          <t>PS5-61-14</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
+          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PS5-61-13</t>
+          <t>PS5-62-01</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
+          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PS5-61-14</t>
+          <t>PS5-62-02</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PS5-62-01</t>
+          <t>PS5-62-03</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PS5-62-02</t>
+          <t>PS5-62-04</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PS5-62-03</t>
+          <t>PS5-62-05</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PS5-62-04</t>
+          <t>PS5-62-06</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PS5-62-05</t>
+          <t>PS5-62-07</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
+          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PS5-62-06</t>
+          <t>PS5-62-08</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PS5-62-07</t>
+          <t>PS5-62-09</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PS5-62-08</t>
+          <t>PS5-62-10</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PS5-62-09</t>
+          <t>PS5-62-11</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
+          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PS5-62-10</t>
+          <t>PS5-62-12</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PS5-62-11</t>
+          <t>PS5-62-13</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PS5-62-12</t>
+          <t>PS5-62-14</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PS5-62-13</t>
+          <t>PS5-62-15</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PS5-62-14</t>
+          <t>PS5-62-16</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PS5-62-15</t>
+          <t>PS5-62-17</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PS5-62-16</t>
+          <t>PS5-62-18</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PS5-62-17</t>
+          <t>PS5-62-19</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PS5-62-18</t>
+          <t>PS5-62-20</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
+          <t>PS5-63-01 - Electrical Earthing</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PS5-62-19</t>
+          <t>PS5-63-01</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PS5-62-20</t>
+          <t>PS5-63-02</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PS5-63-01 - Electrical Earthing</t>
+          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PS5-63-01</t>
+          <t>PS5-63-03</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PS5-63-02</t>
+          <t>PS5-63-04</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
+          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PS5-63-03</t>
+          <t>PS5-63-05</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PS5-63-04</t>
+          <t>PS5-63-06</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
+          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PS5-63-05</t>
+          <t>PS5-63-07</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
+          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PS5-63-06</t>
+          <t>PS5-71-01</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PS5-63-07</t>
+          <t>PS5-71-02</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PS5-71-01</t>
+          <t>PS5-71-03</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PS5-71-02</t>
+          <t>PS5-71-04</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PS5-71-03</t>
+          <t>PS5-71-05</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PS5-71-04 - CFO Storage Tank</t>
+          <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PS5-71-04</t>
+          <t>PS5-71-06</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
+          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PS5-71-05</t>
+          <t>PS5-71-07</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PS5-71-06 - Crude Fuel Separation Module</t>
+          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PS5-71-06</t>
+          <t>PS5-71-08</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PS5-71-07</t>
+          <t>PS5-71-09</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
+          <t>PS5-71-12 - CFO Service Tank</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PS5-71-08</t>
+          <t>PS5-71-12</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PS5-71-09</t>
+          <t>PS5-71-13</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PS5-71-12 - CFO Service Tank</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PS5-71-12</t>
+          <t>PS5-71-14</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PS5-71-13</t>
+          <t>PS5-71-15</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PS5-71-14</t>
+          <t>PS5-71-16</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
+          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PS5-71-15</t>
+          <t>PS5-71-17</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PS5-71-16</t>
+          <t>PS5-71-18</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
+          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PS5-71-17</t>
+          <t>PS5-71-19</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PS5-71-18 - Diesel Separator Module</t>
+          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PS5-71-18</t>
+          <t>PS5-71-20</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
+          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PS5-71-19</t>
+          <t>PS5-71-21</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PS5-71-20</t>
+          <t>PS5-71-22</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
+          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PS5-71-21</t>
+          <t>PS5-71-23</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PS5-71-22</t>
+          <t>PS5-74-01</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
+          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PS5-71-23</t>
+          <t>PS5-74-02</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PS5-74-01</t>
+          <t>PS5-74-03</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PS5-74-02</t>
+          <t>PS5-74-04</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-75-01 - DRA Injection Package</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PS5-74-03</t>
+          <t>PS5-75-01</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PS5-74-04</t>
+          <t>PS5-75-02</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PS5-75-01 - DRA Injection Package</t>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PS5-75-01</t>
+          <t>PS5-75-03</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PS5-75-02</t>
+          <t>PS5-78-01</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PS5-75-03</t>
+          <t>PS5-79-01</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PS5-78-01</t>
+          <t>PS5-79-02</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
+          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PS5-79-01</t>
+          <t>PS5-79-03</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
+          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PS5-79-02</t>
+          <t>PS5-79-04</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
+          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PS5-79-03</t>
+          <t>PS5-79-05</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
+          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PS5-79-04</t>
+          <t>PS5-79-06</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
+          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PS5-79-05</t>
+          <t>PS5-79-07</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
+          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PS5-79-06</t>
+          <t>PS5-79-08</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
+          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PS5-79-07</t>
+          <t>PS5-79-09</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
+          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PS5-79-08</t>
+          <t>PS5-79-10</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
+          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PS5-79-09</t>
+          <t>PS5-79-11</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
+          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PS5-79-10</t>
+          <t>PS5-79-12</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PS5-79-11</t>
+          <t>PS5-82-01</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
+          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PS5-79-12</t>
+          <t>PS5-82-02</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PS5-82-01</t>
+          <t>PS5-82-03</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
+          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PS5-82-02</t>
+          <t>PS5-82-04</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PS5-82-03</t>
+          <t>PS5-82-05</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PS5-82-04</t>
+          <t>PS5-82-06</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-82-07 - Guard Huts</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PS5-82-05</t>
+          <t>PS5-82-07</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PS5-82-06</t>
+          <t>PS5-83-01</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>PS5-82-07 - Guard Huts</t>
+          <t>PS5-84-01 - Generator Building</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PS5-82-07</t>
+          <t>PS5-84-01</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PS5-83-01</t>
+          <t>PS5-84-02</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PS5-84-01 - Generator Building</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PS5-84-01</t>
+          <t>PS5-84-03</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PS5-84-02</t>
+          <t>PS5-86-01</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PS5-84-03</t>
+          <t>PS5-91-01</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PS5-86-01</t>
+          <t>PS5-99-01</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PS5-91-01</t>
+          <t>PS5-99-02</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PS5-99-01 - Area Completion for Building area</t>
+          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PS5-99-01</t>
+          <t>PS5-99-03</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PS5-99-02 - Area Completion for Utility area</t>
+          <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PS5-99-02</t>
+          <t>PS5-99-04</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+          <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PS5-99-03</t>
+          <t>PS5-99-05</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PS5-99-04 - Area Completion for Process area</t>
+          <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
-        <is>
-          <t>PS5-99-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>PS5-99-05 - Area Completion for CFO area</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>PS5-99-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>PS5-99-06 - Area Completion for Power Generation area</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
         <is>
           <t>PS5-99-06</t>
         </is>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -5674,9 +5674,9 @@
         </is>
       </c>
       <c r="B95" s="23" t="inlineStr"/>
-      <c r="C95" s="77" t="inlineStr">
-        <is>
-          <t>78%</t>
+      <c r="C95" s="78" t="inlineStr">
+        <is>
+          <t>99%</t>
         </is>
       </c>
       <c r="D95" s="23" t="n">
@@ -6416,7 +6416,7 @@
       <c r="B112" s="23" t="inlineStr"/>
       <c r="C112" s="77" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="D112" s="23" t="n">
@@ -11394,9 +11394,9 @@
         </is>
       </c>
       <c r="B219" s="23" t="inlineStr"/>
-      <c r="C219" s="76" t="inlineStr">
-        <is>
-          <t>32%</t>
+      <c r="C219" s="78" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="D219" s="23" t="n">
@@ -12758,7 +12758,7 @@
       <c r="B248" s="23" t="inlineStr"/>
       <c r="C248" s="77" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="D248" s="23" t="n">

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3 · BLOCKING – REMARKS'!$A$2:$L$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3 · BLOCKING – REMARKS'!$A$2:$L$297</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -116,14 +116,14 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FFb35900"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF0a58ca"/>
       <sz val="10"/>
       <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FFb35900"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -570,14 +570,14 @@
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -728,22 +728,22 @@
     <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -761,13 +761,13 @@
     <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1152,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L295"/>
+  <dimension ref="A1:L297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5492,7 +5492,7 @@
       <c r="B90" s="23" t="inlineStr"/>
       <c r="C90" s="78" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D90" s="23" t="n">
@@ -5898,41 +5898,63 @@
     <row r="100">
       <c r="A100" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-01a - PAGA (Required for SU)</t>
-        </is>
-      </c>
-      <c r="B100" s="23" t="inlineStr"/>
+          <t>PS5-08-01</t>
+        </is>
+      </c>
+      <c r="B100" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C100" s="76" t="inlineStr">
         <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D100" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="65" t="inlineStr"/>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="D100" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E100" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F100" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G100" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H100" s="65" t="inlineStr"/>
-      <c r="I100" s="65" t="inlineStr"/>
-      <c r="J100" s="23" t="inlineStr"/>
+      <c r="I100" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J100" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K100" s="23" t="n"/>
       <c r="L100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-01b - PAGA (Not required for SU)</t>
+          <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
       </c>
       <c r="B101" s="23" t="inlineStr"/>
       <c r="C101" s="76" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="D101" s="23" t="n">
@@ -5954,85 +5976,85 @@
     <row r="102">
       <c r="A102" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
-        </is>
-      </c>
-      <c r="B102" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-01b - PAGA (Not required for SU)</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="inlineStr"/>
       <c r="C102" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="D102" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E102" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F102" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G102" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="D102" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="65" t="inlineStr"/>
       <c r="H102" s="65" t="inlineStr"/>
-      <c r="I102" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J102" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I102" s="65" t="inlineStr"/>
+      <c r="J102" s="23" t="inlineStr"/>
       <c r="K102" s="23" t="n"/>
       <c r="L102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-04 - Hotline</t>
-        </is>
-      </c>
-      <c r="B103" s="23" t="inlineStr"/>
+          <t>PS5-08-03 - Telephone</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C103" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D103" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="65" t="inlineStr"/>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="D103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G103" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H103" s="65" t="inlineStr"/>
-      <c r="I103" s="65" t="inlineStr"/>
-      <c r="J103" s="23" t="inlineStr"/>
+      <c r="I103" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J103" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K103" s="23" t="n"/>
       <c r="L103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
+          <t>PS5-08-04 - Hotline</t>
         </is>
       </c>
       <c r="B104" s="23" t="inlineStr"/>
@@ -6060,57 +6082,35 @@
     <row r="105">
       <c r="A105" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
-        </is>
-      </c>
-      <c r="B105" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="inlineStr"/>
       <c r="C105" s="76" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="D105" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E105" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F105" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="65" t="inlineStr"/>
       <c r="H105" s="65" t="inlineStr"/>
-      <c r="I105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J105" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I105" s="65" t="inlineStr"/>
+      <c r="J105" s="23" t="inlineStr"/>
       <c r="K105" s="23" t="n"/>
       <c r="L105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
       </c>
       <c r="B106" s="23" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C106" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="D106" s="23" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="107">
       <c r="A107" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B107" s="23" t="inlineStr">
@@ -6210,12 +6210,12 @@
     <row r="108">
       <c r="A108" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
+          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
       </c>
       <c r="B108" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C108" s="76" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="109">
       <c r="A109" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
+          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
       </c>
       <c r="B109" s="23" t="inlineStr">
@@ -6310,7 +6310,7 @@
     <row r="110">
       <c r="A110" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-23 - VHF Trunk Radio System</t>
+          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
       </c>
       <c r="B110" s="23" t="inlineStr">
@@ -6360,7 +6360,7 @@
     <row r="111">
       <c r="A111" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-34 - Satphone</t>
+          <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
       </c>
       <c r="B111" s="23" t="inlineStr">
@@ -6410,90 +6410,90 @@
     <row r="112">
       <c r="A112" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-35 - Optical Transport Network</t>
-        </is>
-      </c>
-      <c r="B112" s="23" t="inlineStr"/>
-      <c r="C112" s="77" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="D112" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="65" t="inlineStr"/>
+          <t>PS5-08-34 - Satphone</t>
+        </is>
+      </c>
+      <c r="B112" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C112" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D112" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E112" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F112" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G112" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H112" s="65" t="inlineStr"/>
-      <c r="I112" s="65" t="inlineStr"/>
-      <c r="J112" s="23" t="inlineStr"/>
+      <c r="I112" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J112" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K112" s="23" t="n"/>
       <c r="L112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
-        </is>
-      </c>
-      <c r="B113" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C113" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G113" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-08-35 - Optical Transport Network</t>
+        </is>
+      </c>
+      <c r="B113" s="23" t="inlineStr"/>
+      <c r="C113" s="77" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="D113" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="65" t="inlineStr"/>
       <c r="H113" s="65" t="inlineStr"/>
-      <c r="I113" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I113" s="65" t="inlineStr"/>
+      <c r="J113" s="23" t="inlineStr"/>
       <c r="K113" s="23" t="n"/>
       <c r="L113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-51 - Entertainment</t>
+          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
       </c>
       <c r="B114" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C114" s="76" t="inlineStr">
@@ -6538,41 +6538,63 @@
     <row r="115">
       <c r="A115" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
-        </is>
-      </c>
-      <c r="B115" s="23" t="inlineStr"/>
+          <t>PS5-08-51 - Entertainment</t>
+        </is>
+      </c>
+      <c r="B115" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C115" s="76" t="inlineStr">
         <is>
-          <t>17%</t>
-        </is>
-      </c>
-      <c r="D115" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="65" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D115" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E115" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F115" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G115" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H115" s="65" t="inlineStr"/>
-      <c r="I115" s="65" t="inlineStr"/>
-      <c r="J115" s="23" t="inlineStr"/>
+      <c r="I115" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J115" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K115" s="23" t="n"/>
       <c r="L115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
+          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
       </c>
       <c r="B116" s="23" t="inlineStr"/>
       <c r="C116" s="76" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="D116" s="23" t="n">
@@ -6594,13 +6616,13 @@
     <row r="117">
       <c r="A117" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-55 - Videoconference</t>
+          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
       </c>
       <c r="B117" s="23" t="inlineStr"/>
       <c r="C117" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="D117" s="23" t="n">
@@ -6622,57 +6644,35 @@
     <row r="118">
       <c r="A118" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-61 - Meteocean</t>
-        </is>
-      </c>
-      <c r="B118" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-55 - Videoconference</t>
+        </is>
+      </c>
+      <c r="B118" s="23" t="inlineStr"/>
       <c r="C118" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="D118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="65" t="inlineStr"/>
       <c r="H118" s="65" t="inlineStr"/>
-      <c r="I118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I118" s="65" t="inlineStr"/>
+      <c r="J118" s="23" t="inlineStr"/>
       <c r="K118" s="23" t="n"/>
       <c r="L118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
+          <t>PS5-08-61 - Meteocean</t>
         </is>
       </c>
       <c r="B119" s="23" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C119" s="76" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D119" s="23" t="inlineStr">
@@ -6722,17 +6722,17 @@
     <row r="120">
       <c r="A120" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-72 - Structured Cabling (FO)</t>
+          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
       </c>
       <c r="B120" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C120" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D120" s="23" t="inlineStr">
@@ -6772,35 +6772,57 @@
     <row r="121">
       <c r="A121" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-81 - Guard tour</t>
-        </is>
-      </c>
-      <c r="B121" s="23" t="inlineStr"/>
+          <t>PS5-08-72 - Structured Cabling (FO)</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C121" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D121" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="65" t="inlineStr"/>
+      <c r="D121" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E121" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F121" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G121" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H121" s="65" t="inlineStr"/>
-      <c r="I121" s="65" t="inlineStr"/>
-      <c r="J121" s="23" t="inlineStr"/>
+      <c r="I121" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J121" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K121" s="23" t="n"/>
       <c r="L121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-82 - Key Management</t>
+          <t>PS5-08-81 - Guard tour</t>
         </is>
       </c>
       <c r="B122" s="23" t="inlineStr"/>
@@ -6828,119 +6850,141 @@
     <row r="123">
       <c r="A123" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
-        </is>
-      </c>
-      <c r="B123" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-82 - Key Management</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="inlineStr"/>
       <c r="C123" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D123" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E123" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F123" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G123" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="D123" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="65" t="inlineStr"/>
       <c r="H123" s="65" t="inlineStr"/>
-      <c r="I123" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J123" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I123" s="65" t="inlineStr"/>
+      <c r="J123" s="23" t="inlineStr"/>
       <c r="K123" s="23" t="n"/>
       <c r="L123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
-        </is>
-      </c>
-      <c r="B124" s="23" t="inlineStr"/>
+          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+        </is>
+      </c>
+      <c r="B124" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C124" s="76" t="inlineStr">
         <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="D124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="65" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G124" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H124" s="65" t="inlineStr"/>
-      <c r="I124" s="65" t="inlineStr"/>
-      <c r="J124" s="23" t="inlineStr"/>
+      <c r="I124" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J124" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K124" s="23" t="n"/>
       <c r="L124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
-        </is>
-      </c>
-      <c r="B125" s="23" t="inlineStr"/>
+          <t>PS5-08-85</t>
+        </is>
+      </c>
+      <c r="B125" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C125" s="76" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="D125" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="65" t="inlineStr"/>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="D125" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E125" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F125" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G125" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H125" s="65" t="inlineStr"/>
-      <c r="I125" s="65" t="inlineStr"/>
-      <c r="J125" s="23" t="inlineStr"/>
+      <c r="I125" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J125" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K125" s="23" t="n"/>
       <c r="L125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-86 - Integrated Security Management System</t>
+          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
       </c>
       <c r="B126" s="23" t="inlineStr"/>
       <c r="C126" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="D126" s="23" t="n">
@@ -6962,13 +7006,13 @@
     <row r="127">
       <c r="A127" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-92 - Telecom Mast</t>
+          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
       </c>
       <c r="B127" s="23" t="inlineStr"/>
       <c r="C127" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="D127" s="23" t="n">
@@ -6990,145 +7034,123 @@
     <row r="128">
       <c r="A128" s="68" t="inlineStr">
         <is>
-          <t>PS5-08-93 - Telecom Monitoring System</t>
-        </is>
-      </c>
-      <c r="B128" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>PS5-08-86 - Integrated Security Management System</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="inlineStr"/>
       <c r="C128" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G128" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="D128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="65" t="inlineStr"/>
       <c r="H128" s="65" t="inlineStr"/>
-      <c r="I128" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J128" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I128" s="65" t="inlineStr"/>
+      <c r="J128" s="23" t="inlineStr"/>
       <c r="K128" s="23" t="n"/>
       <c r="L128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="68" t="inlineStr">
         <is>
-          <t>PS5-09-02 - HVAC for Guard House</t>
-        </is>
-      </c>
-      <c r="B129" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>PS5-08-92 - Telecom Mast</t>
+        </is>
+      </c>
+      <c r="B129" s="23" t="inlineStr"/>
       <c r="C129" s="76" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="D129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="65" t="inlineStr"/>
       <c r="H129" s="65" t="inlineStr"/>
-      <c r="I129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I129" s="65" t="inlineStr"/>
+      <c r="J129" s="23" t="inlineStr"/>
       <c r="K129" s="23" t="n"/>
       <c r="L129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="68" t="inlineStr">
         <is>
-          <t>PS5-0H-01 - HIPPS</t>
-        </is>
-      </c>
-      <c r="B130" s="23" t="inlineStr"/>
-      <c r="C130" s="77" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="D130" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="65" t="inlineStr"/>
+          <t>PS5-08-93 - Telecom Monitoring System</t>
+        </is>
+      </c>
+      <c r="B130" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C130" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D130" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E130" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F130" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G130" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H130" s="65" t="inlineStr"/>
-      <c r="I130" s="65" t="inlineStr"/>
-      <c r="J130" s="23" t="inlineStr"/>
+      <c r="I130" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J130" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K130" s="23" t="n"/>
       <c r="L130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
+          <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
       </c>
       <c r="B131" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C131" s="77" t="inlineStr">
-        <is>
-          <t>76%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C131" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" s="23" t="inlineStr">
@@ -7148,7 +7170,7 @@
       </c>
       <c r="G131" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H131" s="65" t="inlineStr"/>
@@ -7168,57 +7190,35 @@
     <row r="132">
       <c r="A132" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
-        </is>
-      </c>
-      <c r="B132" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>PS5-0H-01 - HIPPS</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="inlineStr"/>
       <c r="C132" s="77" t="inlineStr">
         <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="D132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="D132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="65" t="inlineStr"/>
       <c r="H132" s="65" t="inlineStr"/>
-      <c r="I132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I132" s="65" t="inlineStr"/>
+      <c r="J132" s="23" t="inlineStr"/>
       <c r="K132" s="23" t="n"/>
       <c r="L132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
       </c>
       <c r="B133" s="23" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="C133" s="77" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="D133" s="23" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="G133" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H133" s="65" t="inlineStr"/>
@@ -7268,7 +7268,7 @@
     <row r="134">
       <c r="A134" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B134" s="23" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="C134" s="77" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="D134" s="23" t="inlineStr">
@@ -7318,7 +7318,7 @@
     <row r="135">
       <c r="A135" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B135" s="23" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C135" s="77" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="D135" s="23" t="inlineStr">
@@ -7368,7 +7368,7 @@
     <row r="136">
       <c r="A136" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B136" s="23" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="C136" s="77" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="D136" s="23" t="inlineStr">
@@ -7418,7 +7418,7 @@
     <row r="137">
       <c r="A137" s="68" t="inlineStr">
         <is>
-          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="B137" s="23" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="C137" s="77" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="D137" s="23" t="inlineStr">
@@ -7468,7 +7468,7 @@
     <row r="138">
       <c r="A138" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-01 - Closed Drain Header 1</t>
+          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
       </c>
       <c r="B138" s="23" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C138" s="77" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="D138" s="23" t="inlineStr">
@@ -7518,17 +7518,17 @@
     <row r="139">
       <c r="A139" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
       </c>
       <c r="B139" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C139" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C139" s="77" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
       <c r="D139" s="23" t="inlineStr">
@@ -7568,7 +7568,7 @@
     <row r="140">
       <c r="A140" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
+          <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
       </c>
       <c r="B140" s="23" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="C140" s="77" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="D140" s="23" t="inlineStr">
@@ -7618,12 +7618,12 @@
     <row r="141">
       <c r="A141" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="B141" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C141" s="78" t="inlineStr">
@@ -7668,12 +7668,12 @@
     <row r="142">
       <c r="A142" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
       </c>
       <c r="B142" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C142" s="77" t="inlineStr">
@@ -7718,17 +7718,17 @@
     <row r="143">
       <c r="A143" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="B143" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C143" s="78" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D143" s="23" t="inlineStr">
@@ -7768,7 +7768,7 @@
     <row r="144">
       <c r="A144" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
       </c>
       <c r="B144" s="23" t="inlineStr">
@@ -7776,9 +7776,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C144" s="76" t="inlineStr">
-        <is>
-          <t>44%</t>
+      <c r="C144" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D144" s="23" t="inlineStr">
@@ -7818,7 +7818,7 @@
     <row r="145">
       <c r="A145" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-09 - Observation Basin</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
       <c r="B145" s="23" t="inlineStr">
@@ -7826,9 +7826,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C145" s="77" t="inlineStr">
-        <is>
-          <t>86%</t>
+      <c r="C145" s="78" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="D145" s="23" t="inlineStr">
@@ -7868,17 +7868,17 @@
     <row r="146">
       <c r="A146" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-10 - Oil Skimmer Package</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
       <c r="B146" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C146" s="76" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="D146" s="23" t="inlineStr">
@@ -7918,7 +7918,7 @@
     <row r="147">
       <c r="A147" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
+          <t>PS5-28-09 - Observation Basin</t>
         </is>
       </c>
       <c r="B147" s="23" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C147" s="77" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="D147" s="23" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="148">
       <c r="A148" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
       </c>
       <c r="B148" s="23" t="inlineStr">
@@ -7976,9 +7976,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C148" s="77" t="inlineStr">
-        <is>
-          <t>65%</t>
+      <c r="C148" s="76" t="inlineStr">
+        <is>
+          <t>9%</t>
         </is>
       </c>
       <c r="D148" s="23" t="inlineStr">
@@ -8018,7 +8018,7 @@
     <row r="149">
       <c r="A149" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="B149" s="23" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C149" s="77" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="D149" s="23" t="inlineStr">
@@ -8068,7 +8068,7 @@
     <row r="150">
       <c r="A150" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="B150" s="23" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="C150" s="77" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="D150" s="23" t="inlineStr">
@@ -8118,7 +8118,7 @@
     <row r="151">
       <c r="A151" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
       </c>
       <c r="B151" s="23" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="C151" s="77" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="D151" s="23" t="inlineStr">
@@ -8168,17 +8168,17 @@
     <row r="152">
       <c r="A152" s="68" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
       </c>
       <c r="B152" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C152" s="77" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="D152" s="23" t="inlineStr">
@@ -8218,17 +8218,17 @@
     <row r="153">
       <c r="A153" s="68" t="inlineStr">
         <is>
-          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
       </c>
       <c r="B153" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C153" s="76" t="inlineStr">
-        <is>
-          <t>38%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C153" s="77" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
       <c r="D153" s="23" t="inlineStr">
@@ -8268,17 +8268,17 @@
     <row r="154">
       <c r="A154" s="68" t="inlineStr">
         <is>
-          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
+          <t>PS5-28-16 - LP Relief Header</t>
         </is>
       </c>
       <c r="B154" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C154" s="76" t="inlineStr">
-        <is>
-          <t>42%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C154" s="77" t="inlineStr">
+        <is>
+          <t>82%</t>
         </is>
       </c>
       <c r="D154" s="23" t="inlineStr">
@@ -8318,12 +8318,12 @@
     <row r="155">
       <c r="A155" s="68" t="inlineStr">
         <is>
-          <t>PS5-50-03 - Water Pre-Treatment Package</t>
+          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
       </c>
       <c r="B155" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C155" s="76" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="G155" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H155" s="65" t="inlineStr"/>
@@ -8368,17 +8368,17 @@
     <row r="156">
       <c r="A156" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
       </c>
       <c r="B156" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C156" s="77" t="inlineStr">
-        <is>
-          <t>62%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C156" s="76" t="inlineStr">
+        <is>
+          <t>42%</t>
         </is>
       </c>
       <c r="D156" s="23" t="inlineStr">
@@ -8418,7 +8418,7 @@
     <row r="157">
       <c r="A157" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-03 - Water Softener Package</t>
+          <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
       </c>
       <c r="B157" s="23" t="inlineStr">
@@ -8426,9 +8426,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C157" s="77" t="inlineStr">
-        <is>
-          <t>65%</t>
+      <c r="C157" s="76" t="inlineStr">
+        <is>
+          <t>38%</t>
         </is>
       </c>
       <c r="D157" s="23" t="inlineStr">
@@ -8468,7 +8468,7 @@
     <row r="158">
       <c r="A158" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-04 - Water Treatment Purification Package</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="B158" s="23" t="inlineStr">
@@ -8476,9 +8476,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C158" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C158" s="77" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
       <c r="D158" s="23" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="G158" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H158" s="65" t="inlineStr"/>
@@ -8518,7 +8518,7 @@
     <row r="159">
       <c r="A159" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-53-03 - Water Softener Package</t>
         </is>
       </c>
       <c r="B159" s="23" t="inlineStr">
@@ -8526,9 +8526,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C159" s="78" t="inlineStr">
-        <is>
-          <t>97%</t>
+      <c r="C159" s="77" t="inlineStr">
+        <is>
+          <t>65%</t>
         </is>
       </c>
       <c r="D159" s="23" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="G159" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H159" s="65" t="inlineStr"/>
@@ -8568,17 +8568,17 @@
     <row r="160">
       <c r="A160" s="68" t="inlineStr">
         <is>
-          <t>PS5-53-06 - Water Distribution Consumers</t>
+          <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
       </c>
       <c r="B160" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C160" s="77" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C160" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D160" s="23" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="G160" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H160" s="65" t="inlineStr"/>
@@ -8618,17 +8618,17 @@
     <row r="161">
       <c r="A161" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="B161" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C161" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D161" s="23" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="J161" s="23" t="inlineStr">
         <is>
-          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K161" s="23" t="n"/>
@@ -8668,17 +8668,17 @@
     <row r="162">
       <c r="A162" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
       </c>
       <c r="B162" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C162" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C162" s="77" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="D162" s="23" t="inlineStr">
@@ -8718,17 +8718,17 @@
     <row r="163">
       <c r="A163" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="B163" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C163" s="78" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D163" s="23" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="J163" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
         </is>
       </c>
       <c r="K163" s="23" t="n"/>
@@ -8768,17 +8768,17 @@
     <row r="164">
       <c r="A164" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="B164" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C164" s="78" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D164" s="23" t="inlineStr">
@@ -8802,15 +8802,23 @@
         </is>
       </c>
       <c r="H164" s="65" t="inlineStr"/>
-      <c r="I164" s="65" t="inlineStr"/>
-      <c r="J164" s="23" t="inlineStr"/>
+      <c r="I164" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J164" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K164" s="23" t="n"/>
       <c r="L164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="B165" s="23" t="inlineStr">
@@ -8818,9 +8826,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C165" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="C165" s="78" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="D165" s="23" t="inlineStr">
@@ -8844,15 +8852,23 @@
         </is>
       </c>
       <c r="H165" s="65" t="inlineStr"/>
-      <c r="I165" s="65" t="inlineStr"/>
-      <c r="J165" s="23" t="inlineStr"/>
+      <c r="I165" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J165" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K165" s="23" t="n"/>
       <c r="L165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="B166" s="23" t="inlineStr">
@@ -8860,9 +8876,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C166" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="C166" s="78" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D166" s="23" t="inlineStr">
@@ -8894,7 +8910,7 @@
     <row r="167">
       <c r="A167" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B167" s="23" t="inlineStr">
@@ -8904,7 +8920,7 @@
       </c>
       <c r="C167" s="77" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D167" s="23" t="inlineStr">
@@ -8936,7 +8952,7 @@
     <row r="168">
       <c r="A168" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-19 - Power Generation Package G</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="B168" s="23" t="inlineStr">
@@ -8944,9 +8960,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C168" s="78" t="inlineStr">
-        <is>
-          <t>96%</t>
+      <c r="C168" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D168" s="23" t="inlineStr">
@@ -8970,23 +8986,15 @@
         </is>
       </c>
       <c r="H168" s="65" t="inlineStr"/>
-      <c r="I168" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J168" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I168" s="65" t="inlineStr"/>
+      <c r="J168" s="23" t="inlineStr"/>
       <c r="K168" s="23" t="n"/>
       <c r="L168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B169" s="23" t="inlineStr">
@@ -8996,7 +9004,7 @@
       </c>
       <c r="C169" s="77" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="D169" s="23" t="inlineStr">
@@ -9028,7 +9036,7 @@
     <row r="170">
       <c r="A170" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-19 - Power Generation Package G</t>
         </is>
       </c>
       <c r="B170" s="23" t="inlineStr">
@@ -9036,9 +9044,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C170" s="77" t="inlineStr">
-        <is>
-          <t>83%</t>
+      <c r="C170" s="78" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="D170" s="23" t="inlineStr">
@@ -9062,25 +9070,33 @@
         </is>
       </c>
       <c r="H170" s="65" t="inlineStr"/>
-      <c r="I170" s="65" t="inlineStr"/>
-      <c r="J170" s="23" t="inlineStr"/>
+      <c r="I170" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J170" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K170" s="23" t="n"/>
       <c r="L170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="B171" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C171" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C171" s="77" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="D171" s="23" t="inlineStr">
@@ -9104,33 +9120,25 @@
         </is>
       </c>
       <c r="H171" s="65" t="inlineStr"/>
-      <c r="I171" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J171" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I171" s="65" t="inlineStr"/>
+      <c r="J171" s="23" t="inlineStr"/>
       <c r="K171" s="23" t="n"/>
       <c r="L171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B172" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C172" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C172" s="77" t="inlineStr">
+        <is>
+          <t>83%</t>
         </is>
       </c>
       <c r="D172" s="23" t="inlineStr">
@@ -9154,23 +9162,15 @@
         </is>
       </c>
       <c r="H172" s="65" t="inlineStr"/>
-      <c r="I172" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J172" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I172" s="65" t="inlineStr"/>
+      <c r="J172" s="23" t="inlineStr"/>
       <c r="K172" s="23" t="n"/>
       <c r="L172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="B173" s="23" t="inlineStr">
@@ -9220,7 +9220,7 @@
     <row r="174">
       <c r="A174" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="B174" s="23" t="inlineStr">
@@ -9270,7 +9270,7 @@
     <row r="175">
       <c r="A175" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="B175" s="23" t="inlineStr">
@@ -9320,12 +9320,12 @@
     <row r="176">
       <c r="A176" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="B176" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C176" s="78" t="inlineStr">
@@ -9370,12 +9370,12 @@
     <row r="177">
       <c r="A177" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="B177" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C177" s="78" t="inlineStr">
@@ -9420,12 +9420,12 @@
     <row r="178">
       <c r="A178" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="B178" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C178" s="78" t="inlineStr">
@@ -9470,12 +9470,12 @@
     <row r="179">
       <c r="A179" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="B179" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C179" s="78" t="inlineStr">
@@ -9520,7 +9520,7 @@
     <row r="180">
       <c r="A180" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="B180" s="23" t="inlineStr">
@@ -9570,12 +9570,12 @@
     <row r="181">
       <c r="A181" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="B181" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C181" s="78" t="inlineStr">
@@ -9620,12 +9620,12 @@
     <row r="182">
       <c r="A182" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="B182" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C182" s="78" t="inlineStr">
@@ -9670,12 +9670,12 @@
     <row r="183">
       <c r="A183" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="B183" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C183" s="78" t="inlineStr">
@@ -9720,12 +9720,12 @@
     <row r="184">
       <c r="A184" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="B184" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C184" s="78" t="inlineStr">
@@ -9770,12 +9770,12 @@
     <row r="185">
       <c r="A185" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="B185" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C185" s="78" t="inlineStr">
@@ -9820,12 +9820,12 @@
     <row r="186">
       <c r="A186" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="B186" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C186" s="78" t="inlineStr">
@@ -9870,7 +9870,7 @@
     <row r="187">
       <c r="A187" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="B187" s="23" t="inlineStr">
@@ -9878,9 +9878,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C187" s="77" t="inlineStr">
-        <is>
-          <t>85%</t>
+      <c r="C187" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D187" s="23" t="inlineStr">
@@ -9920,12 +9920,12 @@
     <row r="188">
       <c r="A188" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="B188" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C188" s="78" t="inlineStr">
@@ -9970,17 +9970,17 @@
     <row r="189">
       <c r="A189" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="B189" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C189" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C189" s="77" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="D189" s="23" t="inlineStr">
@@ -10020,12 +10020,12 @@
     <row r="190">
       <c r="A190" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="B190" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C190" s="78" t="inlineStr">
@@ -10070,12 +10070,12 @@
     <row r="191">
       <c r="A191" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="B191" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C191" s="78" t="inlineStr">
@@ -10120,12 +10120,12 @@
     <row r="192">
       <c r="A192" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="B192" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C192" s="78" t="inlineStr">
@@ -10170,12 +10170,12 @@
     <row r="193">
       <c r="A193" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="B193" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C193" s="78" t="inlineStr">
@@ -10220,7 +10220,7 @@
     <row r="194">
       <c r="A194" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="B194" s="23" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="C194" s="78" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D194" s="23" t="inlineStr">
@@ -10270,17 +10270,17 @@
     <row r="195">
       <c r="A195" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="B195" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C195" s="78" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D195" s="23" t="inlineStr">
@@ -10304,25 +10304,33 @@
         </is>
       </c>
       <c r="H195" s="65" t="inlineStr"/>
-      <c r="I195" s="65" t="inlineStr"/>
-      <c r="J195" s="23" t="inlineStr"/>
+      <c r="I195" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J195" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K195" s="23" t="n"/>
       <c r="L195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="B196" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C196" s="77" t="inlineStr">
-        <is>
-          <t>89%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C196" s="78" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="D196" s="23" t="inlineStr">
@@ -10346,20 +10354,28 @@
         </is>
       </c>
       <c r="H196" s="65" t="inlineStr"/>
-      <c r="I196" s="65" t="inlineStr"/>
-      <c r="J196" s="23" t="inlineStr"/>
+      <c r="I196" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J196" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K196" s="23" t="n"/>
       <c r="L196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="B197" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C197" s="78" t="inlineStr">
@@ -10396,17 +10412,17 @@
     <row r="198">
       <c r="A198" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="B198" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C198" s="78" t="inlineStr">
-        <is>
-          <t>91%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C198" s="77" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="D198" s="23" t="inlineStr">
@@ -10438,7 +10454,7 @@
     <row r="199">
       <c r="A199" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="B199" s="23" t="inlineStr">
@@ -10446,9 +10462,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C199" s="77" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="C199" s="78" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="D199" s="23" t="inlineStr">
@@ -10480,17 +10496,17 @@
     <row r="200">
       <c r="A200" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="B200" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C200" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="D200" s="23" t="inlineStr">
@@ -10522,17 +10538,17 @@
     <row r="201">
       <c r="A201" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="B201" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C201" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C201" s="77" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="D201" s="23" t="inlineStr">
@@ -10564,17 +10580,17 @@
     <row r="202">
       <c r="A202" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="B202" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C202" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C202" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D202" s="23" t="inlineStr">
@@ -10606,17 +10622,17 @@
     <row r="203">
       <c r="A203" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="B203" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C203" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C203" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D203" s="23" t="inlineStr">
@@ -10648,7 +10664,7 @@
     <row r="204">
       <c r="A204" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="B204" s="23" t="inlineStr">
@@ -10658,7 +10674,7 @@
       </c>
       <c r="C204" s="77" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D204" s="23" t="inlineStr">
@@ -10690,17 +10706,17 @@
     <row r="205">
       <c r="A205" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="B205" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C205" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C205" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D205" s="23" t="inlineStr">
@@ -10724,33 +10740,25 @@
         </is>
       </c>
       <c r="H205" s="65" t="inlineStr"/>
-      <c r="I205" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J205" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I205" s="65" t="inlineStr"/>
+      <c r="J205" s="23" t="inlineStr"/>
       <c r="K205" s="23" t="n"/>
       <c r="L205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="B206" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C206" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C206" s="77" t="inlineStr">
+        <is>
+          <t>71%</t>
         </is>
       </c>
       <c r="D206" s="23" t="inlineStr">
@@ -10774,28 +10782,20 @@
         </is>
       </c>
       <c r="H206" s="65" t="inlineStr"/>
-      <c r="I206" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J206" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I206" s="65" t="inlineStr"/>
+      <c r="J206" s="23" t="inlineStr"/>
       <c r="K206" s="23" t="n"/>
       <c r="L206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="B207" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C207" s="78" t="inlineStr">
@@ -10840,12 +10840,12 @@
     <row r="208">
       <c r="A208" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="B208" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C208" s="78" t="inlineStr">
@@ -10890,12 +10890,12 @@
     <row r="209">
       <c r="A209" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="B209" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C209" s="78" t="inlineStr">
@@ -10940,12 +10940,12 @@
     <row r="210">
       <c r="A210" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="B210" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C210" s="78" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="211">
       <c r="A211" s="68" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="B211" s="23" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="C211" s="78" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D211" s="23" t="inlineStr">
@@ -11040,17 +11040,17 @@
     <row r="212">
       <c r="A212" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="B212" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C212" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C212" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D212" s="23" t="inlineStr">
@@ -11090,17 +11090,17 @@
     <row r="213">
       <c r="A213" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="B213" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C213" s="77" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C213" s="78" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D213" s="23" t="inlineStr">
@@ -11140,17 +11140,17 @@
     <row r="214">
       <c r="A214" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="B214" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C214" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C214" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D214" s="23" t="inlineStr">
@@ -11190,17 +11190,17 @@
     <row r="215">
       <c r="A215" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-08 - Electrical Control System</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="B215" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C215" s="76" t="inlineStr">
-        <is>
-          <t>21%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C215" s="77" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="D215" s="23" t="inlineStr">
@@ -11240,17 +11240,17 @@
     <row r="216">
       <c r="A216" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="B216" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C216" s="76" t="inlineStr">
-        <is>
-          <t>5%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C216" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D216" s="23" t="inlineStr">
@@ -11290,7 +11290,7 @@
     <row r="217">
       <c r="A217" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-08 - Electrical Control System</t>
         </is>
       </c>
       <c r="B217" s="23" t="inlineStr">
@@ -11298,9 +11298,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C217" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C217" s="76" t="inlineStr">
+        <is>
+          <t>21%</t>
         </is>
       </c>
       <c r="D217" s="23" t="inlineStr">
@@ -11340,17 +11340,17 @@
     <row r="218">
       <c r="A218" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
       </c>
       <c r="B218" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C218" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C218" s="76" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
       <c r="D218" s="23" t="inlineStr">
@@ -11390,45 +11390,67 @@
     <row r="219">
       <c r="A219" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
-        </is>
-      </c>
-      <c r="B219" s="23" t="inlineStr"/>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+        </is>
+      </c>
+      <c r="B219" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C219" s="78" t="inlineStr">
         <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="D219" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E219" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F219" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" s="65" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D219" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E219" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F219" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G219" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H219" s="65" t="inlineStr"/>
-      <c r="I219" s="65" t="inlineStr"/>
-      <c r="J219" s="23" t="inlineStr"/>
+      <c r="I219" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J219" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K219" s="23" t="n"/>
       <c r="L219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="B220" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C220" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C220" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D220" s="23" t="inlineStr">
@@ -11468,67 +11490,45 @@
     <row r="221">
       <c r="A221" s="68" t="inlineStr">
         <is>
-          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
-        </is>
-      </c>
-      <c r="B221" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C221" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D221" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E221" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F221" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
+        </is>
+      </c>
+      <c r="B221" s="23" t="inlineStr"/>
+      <c r="C221" s="78" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="D221" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" s="65" t="inlineStr"/>
       <c r="H221" s="65" t="inlineStr"/>
-      <c r="I221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J221" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I221" s="65" t="inlineStr"/>
+      <c r="J221" s="23" t="inlineStr"/>
       <c r="K221" s="23" t="n"/>
       <c r="L221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
+          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
       </c>
       <c r="B222" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C222" s="76" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D222" s="23" t="inlineStr">
@@ -11568,17 +11568,17 @@
     <row r="223">
       <c r="A223" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
+          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
       </c>
       <c r="B223" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C223" s="76" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D223" s="23" t="inlineStr">
@@ -11618,7 +11618,7 @@
     <row r="224">
       <c r="A224" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
       </c>
       <c r="B224" s="23" t="inlineStr">
@@ -11626,9 +11626,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C224" s="77" t="inlineStr">
-        <is>
-          <t>50%</t>
+      <c r="C224" s="76" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
       <c r="D224" s="23" t="inlineStr">
@@ -11668,7 +11668,7 @@
     <row r="225">
       <c r="A225" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
       </c>
       <c r="B225" s="23" t="inlineStr">
@@ -11676,9 +11676,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C225" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C225" s="76" t="inlineStr">
+        <is>
+          <t>4%</t>
         </is>
       </c>
       <c r="D225" s="23" t="inlineStr">
@@ -11718,17 +11718,17 @@
     <row r="226">
       <c r="A226" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="B226" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C226" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C226" s="77" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="D226" s="23" t="inlineStr">
@@ -11768,17 +11768,17 @@
     <row r="227">
       <c r="A227" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="B227" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C227" s="76" t="inlineStr">
-        <is>
-          <t>26%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C227" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D227" s="23" t="inlineStr">
@@ -11818,17 +11818,17 @@
     <row r="228">
       <c r="A228" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B228" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C228" s="76" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D228" s="23" t="inlineStr">
@@ -11868,17 +11868,17 @@
     <row r="229">
       <c r="A229" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
       </c>
       <c r="B229" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C229" s="76" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="D229" s="23" t="inlineStr">
@@ -11918,17 +11918,17 @@
     <row r="230">
       <c r="A230" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
+          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
       </c>
       <c r="B230" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C230" s="76" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="D230" s="23" t="inlineStr">
@@ -11968,17 +11968,17 @@
     <row r="231">
       <c r="A231" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
+          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
       </c>
       <c r="B231" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C231" s="76" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="D231" s="23" t="inlineStr">
@@ -12018,17 +12018,17 @@
     <row r="232">
       <c r="A232" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
       </c>
       <c r="B232" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C232" s="76" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="D232" s="23" t="inlineStr">
@@ -12068,163 +12068,163 @@
     <row r="233">
       <c r="A233" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
-        </is>
-      </c>
-      <c r="B233" s="23" t="inlineStr"/>
-      <c r="C233" s="78" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="D233" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E233" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F233" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" s="65" t="inlineStr"/>
+          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
+        </is>
+      </c>
+      <c r="B233" s="23" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C233" s="76" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D233" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E233" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F233" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G233" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H233" s="65" t="inlineStr"/>
-      <c r="I233" s="65" t="inlineStr"/>
-      <c r="J233" s="23" t="inlineStr"/>
+      <c r="I233" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J233" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K233" s="23" t="n"/>
       <c r="L233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
-        </is>
-      </c>
-      <c r="B234" s="23" t="inlineStr"/>
-      <c r="C234" s="78" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="D234" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E234" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F234" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" s="65" t="inlineStr"/>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+        </is>
+      </c>
+      <c r="B234" s="23" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C234" s="76" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="D234" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E234" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F234" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G234" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H234" s="65" t="inlineStr"/>
-      <c r="I234" s="65" t="inlineStr"/>
-      <c r="J234" s="23" t="inlineStr"/>
+      <c r="I234" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J234" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K234" s="23" t="n"/>
       <c r="L234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
-        </is>
-      </c>
-      <c r="B235" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C235" s="76" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="D235" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E235" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F235" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G235" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
+        </is>
+      </c>
+      <c r="B235" s="23" t="inlineStr"/>
+      <c r="C235" s="78" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="D235" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="65" t="inlineStr"/>
       <c r="H235" s="65" t="inlineStr"/>
-      <c r="I235" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J235" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I235" s="65" t="inlineStr"/>
+      <c r="J235" s="23" t="inlineStr"/>
       <c r="K235" s="23" t="n"/>
       <c r="L235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
-        </is>
-      </c>
-      <c r="B236" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C236" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D236" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E236" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F236" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
+        </is>
+      </c>
+      <c r="B236" s="23" t="inlineStr"/>
+      <c r="C236" s="78" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="D236" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="65" t="inlineStr"/>
       <c r="H236" s="65" t="inlineStr"/>
-      <c r="I236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J236" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I236" s="65" t="inlineStr"/>
+      <c r="J236" s="23" t="inlineStr"/>
       <c r="K236" s="23" t="n"/>
       <c r="L236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B237" s="23" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="C237" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D237" s="23" t="inlineStr">
@@ -12274,7 +12274,7 @@
     <row r="238">
       <c r="A238" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B238" s="23" t="inlineStr">
@@ -12324,7 +12324,7 @@
     <row r="239">
       <c r="A239" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B239" s="23" t="inlineStr">
@@ -12374,7 +12374,7 @@
     <row r="240">
       <c r="A240" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B240" s="23" t="inlineStr">
@@ -12424,7 +12424,7 @@
     <row r="241">
       <c r="A241" s="68" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
       </c>
       <c r="B241" s="23" t="inlineStr">
@@ -12474,12 +12474,12 @@
     <row r="242">
       <c r="A242" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
+          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
       </c>
       <c r="B242" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C242" s="76" t="inlineStr">
@@ -12524,35 +12524,57 @@
     <row r="243">
       <c r="A243" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
-        </is>
-      </c>
-      <c r="B243" s="23" t="inlineStr"/>
-      <c r="C243" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D243" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E243" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F243" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" s="65" t="inlineStr"/>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+        </is>
+      </c>
+      <c r="B243" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C243" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D243" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E243" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F243" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G243" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H243" s="65" t="inlineStr"/>
-      <c r="I243" s="65" t="inlineStr"/>
-      <c r="J243" s="23" t="inlineStr"/>
+      <c r="I243" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J243" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K243" s="23" t="n"/>
       <c r="L243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
+          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
       </c>
       <c r="B244" s="23" t="inlineStr">
@@ -12602,57 +12624,35 @@
     <row r="245">
       <c r="A245" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
-        </is>
-      </c>
-      <c r="B245" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C245" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D245" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E245" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F245" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G245" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+        </is>
+      </c>
+      <c r="B245" s="23" t="inlineStr"/>
+      <c r="C245" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D245" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="65" t="inlineStr"/>
       <c r="H245" s="65" t="inlineStr"/>
-      <c r="I245" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J245" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I245" s="65" t="inlineStr"/>
+      <c r="J245" s="23" t="inlineStr"/>
       <c r="K245" s="23" t="n"/>
       <c r="L245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="68" t="inlineStr">
         <is>
-          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
+          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
       </c>
       <c r="B246" s="23" t="inlineStr">
@@ -12702,17 +12702,17 @@
     <row r="247">
       <c r="A247" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
       </c>
       <c r="B247" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C247" s="77" t="inlineStr">
-        <is>
-          <t>71%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C247" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D247" s="23" t="inlineStr">
@@ -12752,35 +12752,57 @@
     <row r="248">
       <c r="A248" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
-        </is>
-      </c>
-      <c r="B248" s="23" t="inlineStr"/>
-      <c r="C248" s="77" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="D248" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E248" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F248" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="65" t="inlineStr"/>
+          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
+        </is>
+      </c>
+      <c r="B248" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C248" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D248" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E248" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F248" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G248" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H248" s="65" t="inlineStr"/>
-      <c r="I248" s="65" t="inlineStr"/>
-      <c r="J248" s="23" t="inlineStr"/>
+      <c r="I248" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J248" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K248" s="23" t="n"/>
       <c r="L248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="B249" s="23" t="inlineStr">
@@ -12790,7 +12812,7 @@
       </c>
       <c r="C249" s="77" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="D249" s="23" t="inlineStr">
@@ -12830,39 +12852,25 @@
     <row r="250">
       <c r="A250" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
-        </is>
-      </c>
-      <c r="B250" s="23" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C250" s="78" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="D250" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E250" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F250" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+        </is>
+      </c>
+      <c r="B250" s="23" t="inlineStr"/>
+      <c r="C250" s="77" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="D250" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="65" t="inlineStr"/>
       <c r="H250" s="65" t="inlineStr"/>
       <c r="I250" s="65" t="inlineStr"/>
       <c r="J250" s="23" t="inlineStr"/>
@@ -12872,7 +12880,7 @@
     <row r="251">
       <c r="A251" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B251" s="23" t="inlineStr">
@@ -12922,17 +12930,17 @@
     <row r="252">
       <c r="A252" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
       </c>
       <c r="B252" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C252" s="77" t="inlineStr">
-        <is>
-          <t>84%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C252" s="78" t="inlineStr">
+        <is>
+          <t>95%</t>
         </is>
       </c>
       <c r="D252" s="23" t="inlineStr">
@@ -12956,23 +12964,15 @@
         </is>
       </c>
       <c r="H252" s="65" t="inlineStr"/>
-      <c r="I252" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J252" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I252" s="65" t="inlineStr"/>
+      <c r="J252" s="23" t="inlineStr"/>
       <c r="K252" s="23" t="n"/>
       <c r="L252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B253" s="23" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="C253" s="77" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="D253" s="23" t="inlineStr">
@@ -13022,7 +13022,7 @@
     <row r="254">
       <c r="A254" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="B254" s="23" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="C254" s="77" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="D254" s="23" t="inlineStr">
@@ -13072,7 +13072,7 @@
     <row r="255">
       <c r="A255" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B255" s="23" t="inlineStr">
@@ -13080,9 +13080,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C255" s="78" t="inlineStr">
-        <is>
-          <t>90%</t>
+      <c r="C255" s="77" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="D255" s="23" t="inlineStr">
@@ -13122,17 +13122,17 @@
     <row r="256">
       <c r="A256" s="68" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="B256" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C256" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C256" s="77" t="inlineStr">
+        <is>
+          <t>82%</t>
         </is>
       </c>
       <c r="D256" s="23" t="inlineStr">
@@ -13172,7 +13172,7 @@
     <row r="257">
       <c r="A257" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
       </c>
       <c r="B257" s="23" t="inlineStr">
@@ -13180,9 +13180,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C257" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="C257" s="78" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D257" s="23" t="inlineStr">
@@ -13222,17 +13222,17 @@
     <row r="258">
       <c r="A258" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="B258" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C258" s="77" t="inlineStr">
-        <is>
-          <t>78%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C258" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D258" s="23" t="inlineStr">
@@ -13272,7 +13272,7 @@
     <row r="259">
       <c r="A259" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="B259" s="23" t="inlineStr">
@@ -13280,9 +13280,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C259" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C259" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D259" s="23" t="inlineStr">
@@ -13322,7 +13322,7 @@
     <row r="260">
       <c r="A260" s="68" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
       </c>
       <c r="B260" s="23" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="C260" s="77" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="D260" s="23" t="inlineStr">
@@ -13372,17 +13372,17 @@
     <row r="261">
       <c r="A261" s="68" t="inlineStr">
         <is>
-          <t>PS5-75-01 - DRA Injection Package</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="B261" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C261" s="76" t="inlineStr">
-        <is>
-          <t>37%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C261" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D261" s="23" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="G261" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H261" s="65" t="inlineStr"/>
@@ -13422,17 +13422,17 @@
     <row r="262">
       <c r="A262" s="68" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="B262" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C262" s="77" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="D262" s="23" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="263">
       <c r="A263" s="68" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-75-01 - DRA Injection Package</t>
         </is>
       </c>
       <c r="B263" s="23" t="inlineStr">
@@ -13480,9 +13480,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C263" s="77" t="inlineStr">
-        <is>
-          <t>64%</t>
+      <c r="C263" s="76" t="inlineStr">
+        <is>
+          <t>37%</t>
         </is>
       </c>
       <c r="D263" s="23" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="G263" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H263" s="65" t="inlineStr"/>
@@ -13522,7 +13522,7 @@
     <row r="264">
       <c r="A264" s="68" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="B264" s="23" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="C264" s="77" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="D264" s="23" t="inlineStr">
@@ -13572,7 +13572,7 @@
     <row r="265">
       <c r="A265" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
       </c>
       <c r="B265" s="23" t="inlineStr">
@@ -13580,9 +13580,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C265" s="76" t="inlineStr">
-        <is>
-          <t>10%</t>
+      <c r="C265" s="77" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
       <c r="D265" s="23" t="inlineStr">
@@ -13622,7 +13622,7 @@
     <row r="266">
       <c r="A266" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
       <c r="B266" s="23" t="inlineStr">
@@ -13630,9 +13630,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C266" s="76" t="inlineStr">
-        <is>
-          <t>7%</t>
+      <c r="C266" s="77" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="D266" s="23" t="inlineStr">
@@ -13672,7 +13672,7 @@
     <row r="267">
       <c r="A267" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
+          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
       </c>
       <c r="B267" s="23" t="inlineStr">
@@ -13722,7 +13722,7 @@
     <row r="268">
       <c r="A268" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
+          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
       </c>
       <c r="B268" s="23" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="C268" s="76" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="D268" s="23" t="inlineStr">
@@ -13772,7 +13772,7 @@
     <row r="269">
       <c r="A269" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
+          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
       </c>
       <c r="B269" s="23" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="C269" s="76" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D269" s="23" t="inlineStr">
@@ -13822,7 +13822,7 @@
     <row r="270">
       <c r="A270" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
+          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
       </c>
       <c r="B270" s="23" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C270" s="76" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="D270" s="23" t="inlineStr">
@@ -13872,7 +13872,7 @@
     <row r="271">
       <c r="A271" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
+          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
       </c>
       <c r="B271" s="23" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="C271" s="76" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="D271" s="23" t="inlineStr">
@@ -13922,7 +13922,7 @@
     <row r="272">
       <c r="A272" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
+          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
       </c>
       <c r="B272" s="23" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C272" s="76" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="D272" s="23" t="inlineStr">
@@ -13972,7 +13972,7 @@
     <row r="273">
       <c r="A273" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
+          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
       </c>
       <c r="B273" s="23" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="C273" s="76" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="D273" s="23" t="inlineStr">
@@ -14022,7 +14022,7 @@
     <row r="274">
       <c r="A274" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
+          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
       </c>
       <c r="B274" s="23" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C274" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="D274" s="23" t="inlineStr">
@@ -14072,7 +14072,7 @@
     <row r="275">
       <c r="A275" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
+          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
       </c>
       <c r="B275" s="23" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="C275" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="D275" s="23" t="inlineStr">
@@ -14122,7 +14122,7 @@
     <row r="276">
       <c r="A276" s="68" t="inlineStr">
         <is>
-          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
+          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
       </c>
       <c r="B276" s="23" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="C276" s="76" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="D276" s="23" t="inlineStr">
@@ -14172,17 +14172,17 @@
     <row r="277">
       <c r="A277" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
       </c>
       <c r="B277" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C277" s="77" t="inlineStr">
-        <is>
-          <t>60%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C277" s="76" t="inlineStr">
+        <is>
+          <t>11%</t>
         </is>
       </c>
       <c r="D277" s="23" t="inlineStr">
@@ -14222,17 +14222,17 @@
     <row r="278">
       <c r="A278" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
+          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
       </c>
       <c r="B278" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C278" s="76" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="D278" s="23" t="inlineStr">
@@ -14272,7 +14272,7 @@
     <row r="279">
       <c r="A279" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="B279" s="23" t="inlineStr">
@@ -14280,9 +14280,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C279" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C279" s="77" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="D279" s="23" t="inlineStr">
@@ -14322,7 +14322,7 @@
     <row r="280">
       <c r="A280" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
+          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
       </c>
       <c r="B280" s="23" t="inlineStr">
@@ -14330,9 +14330,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C280" s="77" t="inlineStr">
-        <is>
-          <t>75%</t>
+      <c r="C280" s="76" t="inlineStr">
+        <is>
+          <t>17%</t>
         </is>
       </c>
       <c r="D280" s="23" t="inlineStr">
@@ -14372,17 +14372,17 @@
     <row r="281">
       <c r="A281" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
       </c>
       <c r="B281" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C281" s="76" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D281" s="23" t="inlineStr">
@@ -14422,17 +14422,17 @@
     <row r="282">
       <c r="A282" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
       </c>
       <c r="B282" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C282" s="76" t="inlineStr">
-        <is>
-          <t>8%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C282" s="77" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
       <c r="D282" s="23" t="inlineStr">
@@ -14472,7 +14472,7 @@
     <row r="283">
       <c r="A283" s="68" t="inlineStr">
         <is>
-          <t>PS5-82-07 - Guard Huts</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B283" s="23" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="C283" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="D283" s="23" t="inlineStr">
@@ -14522,17 +14522,17 @@
     <row r="284">
       <c r="A284" s="68" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B284" s="23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C284" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C284" s="76" t="inlineStr">
+        <is>
+          <t>8%</t>
         </is>
       </c>
       <c r="D284" s="23" t="inlineStr">
@@ -14572,17 +14572,17 @@
     <row r="285">
       <c r="A285" s="68" t="inlineStr">
         <is>
-          <t>PS5-84-01 - Generator Building</t>
+          <t>PS5-82-07 - Guard Huts</t>
         </is>
       </c>
       <c r="B285" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C285" s="76" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D285" s="23" t="inlineStr">
@@ -14622,17 +14622,17 @@
     <row r="286">
       <c r="A286" s="68" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="B286" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C286" s="76" t="inlineStr">
-        <is>
-          <t>11%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C286" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D286" s="23" t="inlineStr">
@@ -14672,17 +14672,17 @@
     <row r="287">
       <c r="A287" s="68" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-84-01 - Generator Building</t>
         </is>
       </c>
       <c r="B287" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C287" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C287" s="76" t="inlineStr">
+        <is>
+          <t>45%</t>
         </is>
       </c>
       <c r="D287" s="23" t="inlineStr">
@@ -14722,17 +14722,17 @@
     <row r="288">
       <c r="A288" s="68" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B288" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C288" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C288" s="76" t="inlineStr">
+        <is>
+          <t>11%</t>
         </is>
       </c>
       <c r="D288" s="23" t="inlineStr">
@@ -14772,12 +14772,12 @@
     <row r="289">
       <c r="A289" s="68" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="B289" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C289" s="78" t="inlineStr">
@@ -14822,7 +14822,7 @@
     <row r="290">
       <c r="A290" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-01 - Area Completion for Building area</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="B290" s="23" t="inlineStr">
@@ -14830,9 +14830,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C290" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C290" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D290" s="23" t="inlineStr">
@@ -14872,17 +14872,17 @@
     <row r="291">
       <c r="A291" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-02 - Area Completion for Utility area</t>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
       <c r="B291" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C291" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C291" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D291" s="23" t="inlineStr">
@@ -14922,12 +14922,12 @@
     <row r="292">
       <c r="A292" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+          <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
       </c>
       <c r="B292" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C292" s="76" t="inlineStr">
@@ -14972,12 +14972,12 @@
     <row r="293">
       <c r="A293" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-04 - Area Completion for Process area</t>
+          <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
       </c>
       <c r="B293" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C293" s="76" t="inlineStr">
@@ -15022,7 +15022,7 @@
     <row r="294">
       <c r="A294" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-05 - Area Completion for CFO area</t>
+          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
       </c>
       <c r="B294" s="23" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="C294" s="76" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D294" s="23" t="inlineStr">
@@ -15072,7 +15072,7 @@
     <row r="295">
       <c r="A295" s="68" t="inlineStr">
         <is>
-          <t>PS5-99-06 - Area Completion for Power Generation area</t>
+          <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
       </c>
       <c r="B295" s="23" t="inlineStr">
@@ -15080,9 +15080,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C295" s="77" t="inlineStr">
-        <is>
-          <t>67%</t>
+      <c r="C295" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D295" s="23" t="inlineStr">
@@ -15119,8 +15119,108 @@
       <c r="K295" s="23" t="n"/>
       <c r="L295" s="67" t="inlineStr"/>
     </row>
+    <row r="296">
+      <c r="A296" s="68" t="inlineStr">
+        <is>
+          <t>PS5-99-05 - Area Completion for CFO area</t>
+        </is>
+      </c>
+      <c r="B296" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C296" s="76" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="D296" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E296" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F296" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G296" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H296" s="65" t="inlineStr"/>
+      <c r="I296" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J296" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K296" s="23" t="n"/>
+      <c r="L296" s="67" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="68" t="inlineStr">
+        <is>
+          <t>PS5-99-06 - Area Completion for Power Generation area</t>
+        </is>
+      </c>
+      <c r="B297" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C297" s="77" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="D297" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E297" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F297" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G297" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H297" s="65" t="inlineStr"/>
+      <c r="I297" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J297" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K297" s="23" t="n"/>
+      <c r="L297" s="67" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L295"/>
+  <autoFilter ref="A2:L297"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -15418,6 +15518,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A293" r:id="rId291"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A294" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A295" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId295"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15429,7 +15531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16011,2938 +16113,2962 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PS5-08-01a - PAGA (Required for SU)</t>
+          <t>PS5-08-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PS5-08-01a</t>
+          <t>PS5-08-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PS5-08-01b - PAGA (Not required for SU)</t>
+          <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PS5-08-01b</t>
+          <t>PS5-08-01a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
+          <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PS5-08-03</t>
+          <t>PS5-08-01b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PS5-08-04 - Hotline</t>
+          <t>PS5-08-03 - Telephone</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PS5-08-04</t>
+          <t>PS5-08-03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
+          <t>PS5-08-04 - Hotline</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PS5-08-07</t>
+          <t>PS5-08-04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
+          <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PS5-08-11</t>
+          <t>PS5-08-07</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+          <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PS5-08-12</t>
+          <t>PS5-08-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PS5-08-13</t>
+          <t>PS5-08-12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
+          <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PS5-08-14</t>
+          <t>PS5-08-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
+          <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PS5-08-15</t>
+          <t>PS5-08-14</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PS5-08-23 - VHF Trunk Radio System</t>
+          <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PS5-08-23</t>
+          <t>PS5-08-15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PS5-08-34 - Satphone</t>
+          <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PS5-08-34</t>
+          <t>PS5-08-23</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PS5-08-35 - Optical Transport Network</t>
+          <t>PS5-08-34 - Satphone</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PS5-08-35</t>
+          <t>PS5-08-34</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
+          <t>PS5-08-35 - Optical Transport Network</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PS5-08-36</t>
+          <t>PS5-08-35</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PS5-08-51 - Entertainment</t>
+          <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PS5-08-51</t>
+          <t>PS5-08-36</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
+          <t>PS5-08-51 - Entertainment</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PS5-08-52a</t>
+          <t>PS5-08-51</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
+          <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PS5-08-52b</t>
+          <t>PS5-08-52a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PS5-08-55 - Videoconference</t>
+          <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PS5-08-55</t>
+          <t>PS5-08-52b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PS5-08-61 - Meteocean</t>
+          <t>PS5-08-55 - Videoconference</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PS5-08-61</t>
+          <t>PS5-08-55</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
+          <t>PS5-08-61 - Meteocean</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PS5-08-71</t>
+          <t>PS5-08-61</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PS5-08-72 - Structured Cabling (FO)</t>
+          <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PS5-08-72</t>
+          <t>PS5-08-71</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PS5-08-81 - Guard tour</t>
+          <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PS5-08-81</t>
+          <t>PS5-08-72</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PS5-08-82 - Key Management</t>
+          <t>PS5-08-81 - Guard tour</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PS5-08-82</t>
+          <t>PS5-08-81</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
+          <t>PS5-08-82 - Key Management</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PS5-08-83</t>
+          <t>PS5-08-82</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
+          <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PS5-08-85a</t>
+          <t>PS5-08-83</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PS5-08-85b</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PS5-08-86 - Integrated Security Management System</t>
+          <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PS5-08-86</t>
+          <t>PS5-08-85a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PS5-08-92 - Telecom Mast</t>
+          <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PS5-08-92</t>
+          <t>PS5-08-85b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PS5-08-93 - Telecom Monitoring System</t>
+          <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PS5-08-93</t>
+          <t>PS5-08-86</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
+          <t>PS5-08-92 - Telecom Mast</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PS5-09-01</t>
+          <t>PS5-08-92</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PS5-09-02 - HVAC for Guard House</t>
+          <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PS5-09-02</t>
+          <t>PS5-08-93</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PS5-09-03 - HVAC for Generator Building</t>
+          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PS5-09-03</t>
+          <t>PS5-09-01</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
+          <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PS5-09-04</t>
+          <t>PS5-09-02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
+          <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PS5-09-05</t>
+          <t>PS5-09-03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PS5-0H-01 - HIPPS</t>
+          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PS5-0H-01</t>
+          <t>PS5-09-04</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PS5-25-01</t>
+          <t>PS5-09-05</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+          <t>PS5-0H-01 - HIPPS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PS5-25-02</t>
+          <t>PS5-0H-01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PS5-25-03</t>
+          <t>PS5-25-01</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PS5-25-04</t>
+          <t>PS5-25-02</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PS5-25-05</t>
+          <t>PS5-25-03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PS5-25-06</t>
+          <t>PS5-25-04</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
+          <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PS5-25-07</t>
+          <t>PS5-25-05</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PS5-28-01 - Closed Drain Header 1</t>
+          <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PS5-28-01</t>
+          <t>PS5-25-06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PS5-28-02 - Closed Drain Header 2</t>
+          <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PS5-28-02</t>
+          <t>PS5-25-07</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
+          <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PS5-28-03</t>
+          <t>PS5-28-01</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
+          <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PS5-28-04</t>
+          <t>PS5-28-02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PS5-28-05 - HP Relief Header</t>
+          <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PS5-28-05</t>
+          <t>PS5-28-03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PS5-28-06 - Relief Drum and Pump</t>
+          <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PS5-28-06</t>
+          <t>PS5-28-04</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PS5-28-07 - Open Drains (OD2)</t>
+          <t>PS5-28-05 - HP Relief Header</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PS5-28-07</t>
+          <t>PS5-28-05</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
+          <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PS5-28-08</t>
+          <t>PS5-28-06</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PS5-28-09 - Observation Basin</t>
+          <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PS5-28-09</t>
+          <t>PS5-28-07</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PS5-28-10 - Oil Skimmer Package</t>
+          <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PS5-28-10</t>
+          <t>PS5-28-08</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PS5-28-11 - Open Drain Interceptor</t>
+          <t>PS5-28-09 - Observation Basin</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PS5-28-11</t>
+          <t>PS5-28-09</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PS5-28-12 - Open Drains (OD3)</t>
+          <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PS5-28-12</t>
+          <t>PS5-28-10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
+          <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PS5-28-13</t>
+          <t>PS5-28-11</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
+          <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PS5-28-14</t>
+          <t>PS5-28-12</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
+          <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PS5-28-15</t>
+          <t>PS5-28-13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PS5-28-16 - LP Relief Header</t>
+          <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PS5-28-16</t>
+          <t>PS5-28-14</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PS5-28-17 - Reinjection Pump</t>
+          <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PS5-28-17</t>
+          <t>PS5-28-15</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
+          <t>PS5-28-16 - LP Relief Header</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PS5-50-01</t>
+          <t>PS5-28-16</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
+          <t>PS5-28-17 - Reinjection Pump</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PS5-50-02</t>
+          <t>PS5-28-17</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PS5-50-03 - Water Pre-Treatment Package</t>
+          <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PS5-50-03</t>
+          <t>PS5-50-01</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PS5-53-01 - Utility Water / Storage Tank</t>
+          <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PS5-53-01</t>
+          <t>PS5-50-02</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PS5-53-02 - Water Distribution Pump A/B</t>
+          <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PS5-53-02</t>
+          <t>PS5-50-03</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PS5-53-03 - Water Softener Package</t>
+          <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PS5-53-03</t>
+          <t>PS5-53-01</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PS5-53-04 - Water Treatment Purification Package</t>
+          <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PS5-53-04</t>
+          <t>PS5-53-02</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PS5-53-05 - Water Distribution Header</t>
+          <t>PS5-53-03 - Water Softener Package</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PS5-53-05</t>
+          <t>PS5-53-03</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PS5-53-06 - Water Distribution Consumers</t>
+          <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PS5-53-06</t>
+          <t>PS5-53-04</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
+          <t>PS5-53-05 - Water Distribution Header</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PS5-60-01</t>
+          <t>PS5-53-05</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
+          <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PS5-60-02</t>
+          <t>PS5-53-06</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PS5-60-03</t>
+          <t>PS5-60-01</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PS5-60-04</t>
+          <t>PS5-60-02</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PS5-60-05</t>
+          <t>PS5-60-03</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PS5-60-06</t>
+          <t>PS5-60-04</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PS5-60-07 - Power Generation Package C</t>
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PS5-60-07</t>
+          <t>PS5-60-05</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PS5-60-08</t>
+          <t>PS5-60-06</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-07 - Power Generation Package C</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PS5-60-09</t>
+          <t>PS5-60-07</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PS5-60-10 - Power Generation Package D</t>
+          <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PS5-60-10</t>
+          <t>PS5-60-08</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
+          <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PS5-60-11</t>
+          <t>PS5-60-09</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-10 - Power Generation Package D</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PS5-60-12</t>
+          <t>PS5-60-10</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PS5-60-13 - Power Generation Package E</t>
+          <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PS5-60-13</t>
+          <t>PS5-60-11</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PS5-60-14</t>
+          <t>PS5-60-12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-13 - Power Generation Package E</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PS5-60-15</t>
+          <t>PS5-60-13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PS5-60-16 - Power Generation Package F</t>
+          <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PS5-60-16</t>
+          <t>PS5-60-14</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
+          <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PS5-60-17</t>
+          <t>PS5-60-15</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-16 - Power Generation Package F</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PS5-60-18</t>
+          <t>PS5-60-16</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PS5-60-19 - Power Generation Package G</t>
+          <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PS5-60-19</t>
+          <t>PS5-60-17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
+          <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PS5-60-20</t>
+          <t>PS5-60-18</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-19 - Power Generation Package G</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PS5-60-21</t>
+          <t>PS5-60-19</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PS5-60-22 - Power Gen Master UCP</t>
+          <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PS5-60-22</t>
+          <t>PS5-60-20</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PS5-60-23 - Instrument Air Distribution lines</t>
+          <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PS5-60-23</t>
+          <t>PS5-60-21</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
+          <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PS5-60-24</t>
+          <t>PS5-60-22</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
+          <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PS5-60-25</t>
+          <t>PS5-60-23</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PS5-60-26</t>
+          <t>PS5-60-24</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PS5-60-27</t>
+          <t>PS5-60-25</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PS5-60-28</t>
+          <t>PS5-60-26</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PS5-60-29</t>
+          <t>PS5-60-27</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PS5-60-30</t>
+          <t>PS5-60-28</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PS5-60-31</t>
+          <t>PS5-60-29</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
+          <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PS5-60-32</t>
+          <t>PS5-60-30</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
+          <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PS5-60-33</t>
+          <t>PS5-60-31</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
+          <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PS5-60-34</t>
+          <t>PS5-60-32</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PS5-60-35</t>
+          <t>PS5-60-33</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PS5-60-36</t>
+          <t>PS5-60-34</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PS5-60-37</t>
+          <t>PS5-60-35</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PS5-60-38</t>
+          <t>PS5-60-36</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
+          <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PS5-60-39</t>
+          <t>PS5-60-37</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
+          <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PS5-60-40</t>
+          <t>PS5-60-38</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
+          <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PS5-60-41</t>
+          <t>PS5-60-39</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
+          <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PS5-60-42</t>
+          <t>PS5-60-40</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
+          <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PS5-60-43</t>
+          <t>PS5-60-41</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
+          <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PS5-60-44</t>
+          <t>PS5-60-42</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
+          <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PS5-60-45</t>
+          <t>PS5-60-43</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
+          <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PS5-60-46</t>
+          <t>PS5-60-44</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
+          <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PS5-60-47</t>
+          <t>PS5-60-45</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
+          <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PS5-60-48</t>
+          <t>PS5-60-46</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
+          <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PS5-60-49</t>
+          <t>PS5-60-47</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
+          <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PS5-60-50</t>
+          <t>PS5-60-48</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PS5-60-51</t>
+          <t>PS5-60-49</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PS5-60-52</t>
+          <t>PS5-60-50</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
+          <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PS5-60-53</t>
+          <t>PS5-60-51</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
+          <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PS5-60-54</t>
+          <t>PS5-60-52</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
+          <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PS5-60-55</t>
+          <t>PS5-60-53</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
+          <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PS5-60-56</t>
+          <t>PS5-60-54</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+          <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PS5-60-57</t>
+          <t>PS5-60-55</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PS5-60-58</t>
+          <t>PS5-60-56</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PS5-60-59</t>
+          <t>PS5-60-57</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PS5-60-60</t>
+          <t>PS5-60-58</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PS5-60-61</t>
+          <t>PS5-60-59</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
+          <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PS5-60-62</t>
+          <t>PS5-60-60</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
+          <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PS5-60-63</t>
+          <t>PS5-60-61</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
+          <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PS5-60-64</t>
+          <t>PS5-60-62</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
+          <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PS5-60-65</t>
+          <t>PS5-60-63</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
+          <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PS5-60-66</t>
+          <t>PS5-60-64</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
+          <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PS5-60-67</t>
+          <t>PS5-60-65</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+          <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PS5-60-68</t>
+          <t>PS5-60-66</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
+          <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PS5-60-69</t>
+          <t>PS5-60-67</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PS5-60-70</t>
+          <t>PS5-60-68</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PS5-60-71</t>
+          <t>PS5-60-69</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PS5-60-72 - Engine C Cooling system</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PS5-60-72</t>
+          <t>PS5-60-70</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PS5-60-73 - Engine D Cooling system</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PS5-60-73</t>
+          <t>PS5-60-71</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PS5-60-74 - Engine E Cooling system</t>
+          <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PS5-60-74</t>
+          <t>PS5-60-72</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PS5-60-75 - Engine F Cooling system</t>
+          <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PS5-60-75</t>
+          <t>PS5-60-73</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PS5-60-76 - Engine G Cooling system</t>
+          <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PS5-60-76</t>
+          <t>PS5-60-74</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
+          <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PS5-61-01</t>
+          <t>PS5-60-75</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
+          <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PS5-61-02</t>
+          <t>PS5-60-76</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
+          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PS5-61-03</t>
+          <t>PS5-61-01</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
+          <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PS5-61-04</t>
+          <t>PS5-61-02</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PS5-61-05</t>
+          <t>PS5-61-03</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
+          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PS5-61-06</t>
+          <t>PS5-61-04</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PS5-61-07</t>
+          <t>PS5-61-05</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PS5-61-08 - Electrical Control System</t>
+          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PS5-61-08</t>
+          <t>PS5-61-06</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
+          <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PS5-61-09</t>
+          <t>PS5-61-07</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
+          <t>PS5-61-08 - Electrical Control System</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PS5-61-10</t>
+          <t>PS5-61-08</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
+          <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PS5-61-11</t>
+          <t>PS5-61-09</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
+          <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PS5-61-12</t>
+          <t>PS5-61-10</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
+          <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PS5-61-13</t>
+          <t>PS5-61-11</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
+          <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PS5-61-14</t>
+          <t>PS5-61-12</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
+          <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PS5-62-01</t>
+          <t>PS5-61-13</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
+          <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PS5-62-02</t>
+          <t>PS5-61-14</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
+          <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PS5-62-03</t>
+          <t>PS5-62-01</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
+          <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PS5-62-04</t>
+          <t>PS5-62-02</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PS5-62-05</t>
+          <t>PS5-62-03</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
+          <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PS5-62-06</t>
+          <t>PS5-62-04</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PS5-62-07</t>
+          <t>PS5-62-05</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
+          <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PS5-62-08</t>
+          <t>PS5-62-06</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
+          <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PS5-62-09</t>
+          <t>PS5-62-07</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
+          <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PS5-62-10</t>
+          <t>PS5-62-08</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+          <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PS5-62-11</t>
+          <t>PS5-62-09</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
+          <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PS5-62-12</t>
+          <t>PS5-62-10</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PS5-62-13</t>
+          <t>PS5-62-11</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+          <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PS5-62-14</t>
+          <t>PS5-62-12</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+          <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PS5-62-15</t>
+          <t>PS5-62-13</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PS5-62-16</t>
+          <t>PS5-62-14</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PS5-62-17</t>
+          <t>PS5-62-15</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PS5-62-18</t>
+          <t>PS5-62-16</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PS5-62-19</t>
+          <t>PS5-62-17</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+          <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PS5-62-20</t>
+          <t>PS5-62-18</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PS5-63-01 - Electrical Earthing</t>
+          <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PS5-63-01</t>
+          <t>PS5-62-19</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PS5-63-02</t>
+          <t>PS5-62-20</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
+          <t>PS5-63-01 - Electrical Earthing</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PS5-63-03</t>
+          <t>PS5-63-01</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PS5-63-04</t>
+          <t>PS5-63-02</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
+          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PS5-63-05</t>
+          <t>PS5-63-03</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PS5-63-06</t>
+          <t>PS5-63-04</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
+          <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PS5-63-07</t>
+          <t>PS5-63-05</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
+          <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PS5-71-01</t>
+          <t>PS5-63-06</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PS5-71-02 - CFO Allocation Metering Package</t>
+          <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PS5-71-02</t>
+          <t>PS5-63-07</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PS5-71-03</t>
+          <t>PS5-71-01</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PS5-71-04 - CFO Storage Tank</t>
+          <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PS5-71-04</t>
+          <t>PS5-71-02</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PS5-71-05</t>
+          <t>PS5-71-03</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PS5-71-06 - Crude Fuel Separation Module</t>
+          <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PS5-71-06</t>
+          <t>PS5-71-04</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
+          <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PS5-71-07</t>
+          <t>PS5-71-05</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
+          <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PS5-71-08</t>
+          <t>PS5-71-06</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PS5-71-09</t>
+          <t>PS5-71-07</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PS5-71-12 - CFO Service Tank</t>
+          <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PS5-71-12</t>
+          <t>PS5-71-08</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PS5-71-13</t>
+          <t>PS5-71-09</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
+          <t>PS5-71-12 - CFO Service Tank</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PS5-71-14</t>
+          <t>PS5-71-12</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PS5-71-15</t>
+          <t>PS5-71-13</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
+          <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PS5-71-16</t>
+          <t>PS5-71-14</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PS5-71-17</t>
+          <t>PS5-71-15</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PS5-71-18 - Diesel Separator Module</t>
+          <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PS5-71-18</t>
+          <t>PS5-71-16</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
+          <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PS5-71-19</t>
+          <t>PS5-71-17</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
+          <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PS5-71-20</t>
+          <t>PS5-71-18</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
+          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PS5-71-21</t>
+          <t>PS5-71-19</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
+          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PS5-71-22</t>
+          <t>PS5-71-20</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
+          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PS5-71-23</t>
+          <t>PS5-71-21</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PS5-74-01 - N2 Generation Skid</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PS5-74-01</t>
+          <t>PS5-71-22</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
+          <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PS5-74-02</t>
+          <t>PS5-71-23</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PS5-74-03 - Nitrogen Receiver</t>
+          <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PS5-74-03</t>
+          <t>PS5-74-01</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PS5-74-04 - Nitrogen Distribution Header</t>
+          <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PS5-74-04</t>
+          <t>PS5-74-02</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PS5-75-01 - DRA Injection Package</t>
+          <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PS5-75-01</t>
+          <t>PS5-74-03</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PS5-75-02 - Biocide Injection Package</t>
+          <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PS5-75-02</t>
+          <t>PS5-74-04</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
+          <t>PS5-75-01 - DRA Injection Package</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PS5-75-03</t>
+          <t>PS5-75-01</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PS5-78-01</t>
+          <t>PS5-75-02</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
+          <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PS5-79-01</t>
+          <t>PS5-75-03</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PS5-79-02</t>
+          <t>PS5-78-01</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
+          <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PS5-79-03</t>
+          <t>PS5-79-01</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
+          <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PS5-79-04</t>
+          <t>PS5-79-02</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
+          <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PS5-79-05</t>
+          <t>PS5-79-03</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
+          <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PS5-79-06</t>
+          <t>PS5-79-04</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
+          <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PS5-79-07</t>
+          <t>PS5-79-05</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
+          <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PS5-79-08</t>
+          <t>PS5-79-06</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
+          <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PS5-79-09</t>
+          <t>PS5-79-07</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
+          <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PS5-79-10</t>
+          <t>PS5-79-08</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
+          <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PS5-79-11</t>
+          <t>PS5-79-09</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
+          <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PS5-79-12</t>
+          <t>PS5-79-10</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PS5-82-01 - Sanitary Sewage Collection</t>
+          <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PS5-82-01</t>
+          <t>PS5-79-11</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
+          <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PS5-82-02</t>
+          <t>PS5-79-12</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
+          <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PS5-82-03</t>
+          <t>PS5-82-01</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
+          <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PS5-82-04</t>
+          <t>PS5-82-02</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PS5-82-05</t>
+          <t>PS5-82-03</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PS5-82-06</t>
+          <t>PS5-82-04</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PS5-82-07 - Guard Huts</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PS5-82-07</t>
+          <t>PS5-82-05</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PS5-83-01 - EITS Building</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PS5-83-01</t>
+          <t>PS5-82-06</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>PS5-84-01 - Generator Building</t>
+          <t>PS5-82-07 - Guard Huts</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PS5-84-01</t>
+          <t>PS5-82-07</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-83-01 - EITS Building</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PS5-84-02</t>
+          <t>PS5-83-01</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PS5-84-03 - Shelters</t>
+          <t>PS5-84-01 - Generator Building</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PS5-84-03</t>
+          <t>PS5-84-01</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PS5-86-01 - Shelters</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PS5-86-01</t>
+          <t>PS5-84-02</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PS5-91-01 - Multicore cables &amp; JB</t>
+          <t>PS5-84-03 - Shelters</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PS5-91-01</t>
+          <t>PS5-84-03</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>PS5-99-01 - Area Completion for Building area</t>
+          <t>PS5-86-01 - Shelters</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PS5-99-01</t>
+          <t>PS5-86-01</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PS5-99-02 - Area Completion for Utility area</t>
+          <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PS5-99-02</t>
+          <t>PS5-91-01</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
+          <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PS5-99-03</t>
+          <t>PS5-99-01</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PS5-99-04 - Area Completion for Process area</t>
+          <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PS5-99-04</t>
+          <t>PS5-99-02</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PS5-99-05 - Area Completion for CFO area</t>
+          <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PS5-99-05</t>
+          <t>PS5-99-03</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
+          <t>PS5-99-04 - Area Completion for Process area</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>PS5-99-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>PS5-99-05 - Area Completion for CFO area</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>PS5-99-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>PS5-99-06</t>
         </is>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -241,6 +241,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -309,12 +315,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -570,7 +570,7 @@
     <xf numFmtId="0" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,13 +644,10 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -674,22 +671,25 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,10 +698,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,7 +710,7 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1250,7 +1250,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C3" s="76" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -1285,38 +1285,34 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H3" s="65" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="H3" s="65" t="inlineStr"/>
       <c r="I3" s="65" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>706</t>
         </is>
       </c>
       <c r="J3" s="23" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>706</t>
         </is>
       </c>
       <c r="K3" s="23" t="n"/>
       <c r="L3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
-        <is>
-          <t>PS5-08-85</t>
+      <c r="A4" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
       </c>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" s="76" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -1339,20 +1335,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H4" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H4" s="65" t="inlineStr"/>
       <c r="I4" s="65" t="inlineStr"/>
       <c r="J4" s="23" t="inlineStr"/>
       <c r="K4" s="23" t="n"/>
       <c r="L4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-24 - FZ - Office and Facilities Building</t>
+      <c r="A5" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B5" s="23" t="inlineStr">
@@ -1385,20 +1377,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H5" s="65" t="inlineStr"/>
       <c r="I5" s="65" t="inlineStr"/>
       <c r="J5" s="23" t="inlineStr"/>
       <c r="K5" s="23" t="n"/>
       <c r="L5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
+      <c r="A6" s="68" t="inlineStr">
+        <is>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
@@ -1431,30 +1419,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H6" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H6" s="65" t="inlineStr"/>
       <c r="I6" s="65" t="inlineStr"/>
       <c r="J6" s="23" t="inlineStr"/>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="53" t="inlineStr">
-        <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+      <c r="A7" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C7" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C7" s="77" t="inlineStr">
+        <is>
+          <t>63%</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -1469,7 +1453,7 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G7" s="65" t="inlineStr">
@@ -1477,30 +1461,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H7" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H7" s="65" t="inlineStr"/>
       <c r="I7" s="65" t="inlineStr"/>
       <c r="J7" s="23" t="inlineStr"/>
       <c r="K7" s="23" t="n"/>
       <c r="L7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
+      <c r="A8" s="68" t="inlineStr">
+        <is>
+          <t>PS5-63-01 - Electrical Earthing</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="77" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -1510,12 +1490,12 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" s="65" t="inlineStr">
@@ -1523,20 +1503,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H8" s="65" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I8" s="65" t="inlineStr"/>
-      <c r="J8" s="23" t="inlineStr"/>
+      <c r="H8" s="65" t="inlineStr"/>
+      <c r="I8" s="65" t="inlineStr">
+        <is>
+          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="53" t="inlineStr">
-        <is>
-          <t>PS5-63-01 - Electrical Earthing</t>
+      <c r="A9" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
@@ -1546,7 +1530,7 @@
       </c>
       <c r="C9" s="77" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -1556,12 +1540,12 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G9" s="65" t="inlineStr">
@@ -1569,38 +1553,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H9" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I9" s="65" t="inlineStr">
-        <is>
-          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="65" t="inlineStr"/>
+      <c r="J9" s="23" t="inlineStr"/>
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
+      <c r="A10" s="68" t="inlineStr">
+        <is>
+          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="77" t="inlineStr">
-        <is>
-          <t>51%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C10" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1615,7 +1587,7 @@
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="65" t="inlineStr">
@@ -1623,30 +1595,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H10" s="65" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+      <c r="H10" s="65" t="inlineStr"/>
       <c r="I10" s="65" t="inlineStr"/>
       <c r="J10" s="23" t="inlineStr"/>
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="53" t="inlineStr">
-        <is>
-          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
+      <c r="A11" s="68" t="inlineStr">
+        <is>
+          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C11" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="77" t="inlineStr">
+        <is>
+          <t>69%</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -1661,7 +1629,7 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G11" s="65" t="inlineStr">
@@ -1669,30 +1637,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H11" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H11" s="65" t="inlineStr"/>
       <c r="I11" s="65" t="inlineStr"/>
       <c r="J11" s="23" t="inlineStr"/>
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="53" t="inlineStr">
-        <is>
-          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
+      <c r="A12" s="68" t="inlineStr">
+        <is>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" s="77" t="inlineStr">
-        <is>
-          <t>69%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C12" s="76" t="inlineStr">
+        <is>
+          <t>3%</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -1707,7 +1671,7 @@
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" s="65" t="inlineStr">
@@ -1715,30 +1679,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H12" s="65" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="H12" s="65" t="inlineStr"/>
       <c r="I12" s="65" t="inlineStr"/>
       <c r="J12" s="23" t="inlineStr"/>
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr">
-        <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+      <c r="A13" s="68" t="inlineStr">
+        <is>
+          <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C13" s="76" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -1761,30 +1721,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H13" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" s="65" t="inlineStr"/>
-      <c r="J13" s="23" t="inlineStr"/>
+      <c r="H13" s="65" t="inlineStr"/>
+      <c r="I13" s="65" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="inlineStr">
-        <is>
-          <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
+      <c r="A14" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C14" s="76" t="inlineStr">
-        <is>
-          <t>1%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C14" s="77" t="inlineStr">
+        <is>
+          <t>58%</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -1799,7 +1763,7 @@
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G14" s="65" t="inlineStr">
@@ -1807,38 +1771,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H14" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I14" s="65" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J14" s="23" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+      <c r="H14" s="65" t="inlineStr"/>
+      <c r="I14" s="65" t="inlineStr"/>
+      <c r="J14" s="23" t="inlineStr"/>
       <c r="K14" s="23" t="n"/>
       <c r="L14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-06 - Crude Fuel Separation Module</t>
+      <c r="A15" s="68" t="inlineStr">
+        <is>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C15" s="77" t="inlineStr">
-        <is>
-          <t>58%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -1853,7 +1805,7 @@
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" s="65" t="inlineStr">
@@ -1861,20 +1813,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H15" s="65" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I15" s="65" t="inlineStr"/>
-      <c r="J15" s="23" t="inlineStr"/>
+      <c r="H15" s="65" t="inlineStr"/>
+      <c r="I15" s="65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="K15" s="23" t="n"/>
       <c r="L15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="inlineStr">
-        <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+      <c r="A16" s="68" t="inlineStr">
+        <is>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
@@ -1882,9 +1838,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C16" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C16" s="77" t="inlineStr">
+        <is>
+          <t>87%</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -1907,38 +1863,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H16" s="65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="H16" s="65" t="inlineStr"/>
       <c r="I16" s="65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K16" s="23" t="n"/>
       <c r="L16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
-        <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+      <c r="A17" s="68" t="inlineStr">
+        <is>
+          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C17" s="77" t="inlineStr">
-        <is>
-          <t>87%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C17" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -1961,25 +1913,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H17" s="65" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="H17" s="65" t="inlineStr"/>
       <c r="I17" s="65" t="inlineStr"/>
       <c r="J17" s="23" t="inlineStr"/>
       <c r="K17" s="23" t="n"/>
       <c r="L17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
-        <is>
-          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
+      <c r="A18" s="68" t="inlineStr">
+        <is>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" s="76" t="inlineStr">
@@ -2007,25 +1955,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H18" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I18" s="65" t="inlineStr"/>
-      <c r="J18" s="23" t="inlineStr"/>
+      <c r="H18" s="65" t="inlineStr"/>
+      <c r="I18" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="inlineStr">
-        <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+      <c r="A19" s="68" t="inlineStr">
+        <is>
+          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" s="76" t="inlineStr">
@@ -2040,7 +1992,7 @@
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -2053,38 +2005,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H19" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H19" s="65" t="inlineStr"/>
       <c r="I19" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K19" s="23" t="n"/>
       <c r="L19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
-        <is>
-          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
+      <c r="A20" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C20" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -2094,7 +2042,7 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -2107,38 +2055,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H20" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" s="65" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J20" s="23" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="H20" s="65" t="inlineStr"/>
+      <c r="I20" s="65" t="inlineStr"/>
+      <c r="J20" s="23" t="inlineStr"/>
       <c r="K20" s="23" t="n"/>
       <c r="L20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-03 - FZ-03 - Buildings Area</t>
+      <c r="A21" s="68" t="inlineStr">
+        <is>
+          <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C21" s="76" t="inlineStr">
-        <is>
-          <t>6%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C21" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -2153,7 +2089,7 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G21" s="65" t="inlineStr">
@@ -2161,20 +2097,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H21" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="H21" s="65" t="inlineStr"/>
       <c r="I21" s="65" t="inlineStr"/>
       <c r="J21" s="23" t="inlineStr"/>
       <c r="K21" s="23" t="n"/>
       <c r="L21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="53" t="inlineStr">
-        <is>
-          <t>PS5-01-11 - Inergen for Power Gen Building</t>
+      <c r="A22" s="68" t="inlineStr">
+        <is>
+          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
       </c>
       <c r="B22" s="23" t="inlineStr">
@@ -2182,9 +2114,9 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="C22" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C22" s="76" t="inlineStr">
+        <is>
+          <t>26%</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -2199,7 +2131,7 @@
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" s="65" t="inlineStr">
@@ -2207,30 +2139,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H22" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H22" s="65" t="inlineStr"/>
       <c r="I22" s="65" t="inlineStr"/>
       <c r="J22" s="23" t="inlineStr"/>
       <c r="K22" s="23" t="n"/>
       <c r="L22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="inlineStr">
-        <is>
-          <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
+      <c r="A23" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C23" s="76" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -2253,20 +2181,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H23" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="H23" s="65" t="inlineStr"/>
       <c r="I23" s="65" t="inlineStr"/>
       <c r="J23" s="23" t="inlineStr"/>
       <c r="K23" s="23" t="n"/>
       <c r="L23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-22 - FZ-G1 - Guard House</t>
+      <c r="A24" s="68" t="inlineStr">
+        <is>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B24" s="23" t="inlineStr">
@@ -2276,7 +2200,7 @@
       </c>
       <c r="C24" s="76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -2299,20 +2223,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H24" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H24" s="65" t="inlineStr"/>
       <c r="I24" s="65" t="inlineStr"/>
       <c r="J24" s="23" t="inlineStr"/>
       <c r="K24" s="23" t="n"/>
       <c r="L24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="inlineStr">
-        <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+      <c r="A25" s="68" t="inlineStr">
+        <is>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B25" s="23" t="inlineStr">
@@ -2345,20 +2265,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H25" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H25" s="65" t="inlineStr"/>
       <c r="I25" s="65" t="inlineStr"/>
       <c r="J25" s="23" t="inlineStr"/>
       <c r="K25" s="23" t="n"/>
       <c r="L25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
-        <is>
-          <t>PS5-82-06 - Guard House Building</t>
+      <c r="A26" s="68" t="inlineStr">
+        <is>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B26" s="23" t="inlineStr">
@@ -2368,7 +2284,7 @@
       </c>
       <c r="C26" s="76" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -2391,30 +2307,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H26" s="65" t="inlineStr"/>
       <c r="I26" s="65" t="inlineStr"/>
       <c r="J26" s="23" t="inlineStr"/>
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="inlineStr">
-        <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+      <c r="A27" s="68" t="inlineStr">
+        <is>
+          <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C27" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C27" s="77" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -2437,30 +2349,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H27" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I27" s="65" t="inlineStr"/>
-      <c r="J27" s="23" t="inlineStr"/>
+      <c r="H27" s="65" t="inlineStr"/>
+      <c r="I27" s="65" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="53" t="inlineStr">
-        <is>
-          <t>PS5-02-01 - Miscellaneous Safety equipment</t>
+      <c r="A28" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C28" s="77" t="inlineStr">
-        <is>
-          <t>59%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -2475,7 +2391,7 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G28" s="65" t="inlineStr">
@@ -2483,33 +2399,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H28" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I28" s="65" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="H28" s="65" t="inlineStr"/>
+      <c r="I28" s="65" t="inlineStr"/>
+      <c r="J28" s="23" t="inlineStr"/>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
+      <c r="A29" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C29" s="76" t="inlineStr">
@@ -2537,25 +2441,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H29" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H29" s="65" t="inlineStr"/>
       <c r="I29" s="65" t="inlineStr"/>
       <c r="J29" s="23" t="inlineStr"/>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
+      <c r="A30" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C30" s="76" t="inlineStr">
@@ -2575,7 +2475,7 @@
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G30" s="65" t="inlineStr">
@@ -2583,20 +2483,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H30" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H30" s="65" t="inlineStr"/>
       <c r="I30" s="65" t="inlineStr"/>
       <c r="J30" s="23" t="inlineStr"/>
       <c r="K30" s="23" t="n"/>
       <c r="L30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
+      <c r="A31" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
       </c>
       <c r="B31" s="23" t="inlineStr">
@@ -2629,25 +2525,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H31" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H31" s="65" t="inlineStr"/>
       <c r="I31" s="65" t="inlineStr"/>
       <c r="J31" s="23" t="inlineStr"/>
       <c r="K31" s="23" t="n"/>
       <c r="L31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
+      <c r="A32" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C32" s="76" t="inlineStr">
@@ -2667,7 +2559,7 @@
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G32" s="65" t="inlineStr">
@@ -2675,25 +2567,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H32" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H32" s="65" t="inlineStr"/>
       <c r="I32" s="65" t="inlineStr"/>
       <c r="J32" s="23" t="inlineStr"/>
       <c r="K32" s="23" t="n"/>
       <c r="L32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
+      <c r="A33" s="68" t="inlineStr">
+        <is>
+          <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C33" s="76" t="inlineStr">
@@ -2713,7 +2601,7 @@
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G33" s="65" t="inlineStr">
@@ -2721,25 +2609,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H33" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H33" s="65" t="inlineStr"/>
       <c r="I33" s="65" t="inlineStr"/>
       <c r="J33" s="23" t="inlineStr"/>
       <c r="K33" s="23" t="n"/>
       <c r="L33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="53" t="inlineStr">
-        <is>
-          <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
+      <c r="A34" s="68" t="inlineStr">
+        <is>
+          <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" s="76" t="inlineStr">
@@ -2767,30 +2651,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H34" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H34" s="65" t="inlineStr"/>
       <c r="I34" s="65" t="inlineStr"/>
       <c r="J34" s="23" t="inlineStr"/>
       <c r="K34" s="23" t="n"/>
       <c r="L34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="53" t="inlineStr">
-        <is>
-          <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
+      <c r="A35" s="68" t="inlineStr">
+        <is>
+          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C35" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="78" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -2805,7 +2685,7 @@
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" s="65" t="inlineStr">
@@ -2813,20 +2693,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H35" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H35" s="65" t="inlineStr"/>
       <c r="I35" s="65" t="inlineStr"/>
       <c r="J35" s="23" t="inlineStr"/>
       <c r="K35" s="23" t="n"/>
       <c r="L35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="53" t="inlineStr">
-        <is>
-          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
+      <c r="A36" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
       </c>
       <c r="B36" s="23" t="inlineStr">
@@ -2834,9 +2710,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C36" s="78" t="inlineStr">
-        <is>
-          <t>90%</t>
+      <c r="C36" s="77" t="inlineStr">
+        <is>
+          <t>78%</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
@@ -2851,7 +2727,7 @@
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G36" s="65" t="inlineStr">
@@ -2859,30 +2735,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H36" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H36" s="65" t="inlineStr"/>
       <c r="I36" s="65" t="inlineStr"/>
       <c r="J36" s="23" t="inlineStr"/>
       <c r="K36" s="23" t="n"/>
       <c r="L36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
+      <c r="A37" s="68" t="inlineStr">
+        <is>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C37" s="77" t="inlineStr">
-        <is>
-          <t>78%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C37" s="76" t="inlineStr">
+        <is>
+          <t>11%</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
@@ -2897,7 +2769,7 @@
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" s="65" t="inlineStr">
@@ -2905,30 +2777,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H37" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I37" s="65" t="inlineStr"/>
-      <c r="J37" s="23" t="inlineStr"/>
+      <c r="H37" s="65" t="inlineStr"/>
+      <c r="I37" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K37" s="23" t="n"/>
       <c r="L37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="53" t="inlineStr">
-        <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+      <c r="A38" s="68" t="inlineStr">
+        <is>
+          <t>PS5-08-03 - Telephone</t>
         </is>
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C38" s="76" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -2951,38 +2827,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H38" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H38" s="65" t="inlineStr"/>
       <c r="I38" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K38" s="23" t="n"/>
       <c r="L38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="53" t="inlineStr">
-        <is>
-          <t>PS5-08-03 - Telephone</t>
+      <c r="A39" s="68" t="inlineStr">
+        <is>
+          <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C39" s="76" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
@@ -3005,28 +2877,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H39" s="65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="H39" s="65" t="inlineStr"/>
       <c r="I39" s="65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K39" s="23" t="n"/>
       <c r="L39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="53" t="inlineStr">
-        <is>
-          <t>PS5-04-02 - Office Building SIS/FGS System</t>
+      <c r="A40" s="68" t="inlineStr">
+        <is>
+          <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
@@ -3059,38 +2927,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H40" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I40" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H40" s="65" t="inlineStr"/>
+      <c r="I40" s="65" t="inlineStr"/>
+      <c r="J40" s="23" t="inlineStr"/>
       <c r="K40" s="23" t="n"/>
       <c r="L40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="53" t="inlineStr">
-        <is>
-          <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
+      <c r="A41" s="68" t="inlineStr">
+        <is>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C41" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C41" s="78" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -3113,20 +2969,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H41" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I41" s="65" t="inlineStr"/>
-      <c r="J41" s="23" t="inlineStr"/>
+      <c r="H41" s="65" t="inlineStr"/>
+      <c r="I41" s="65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K41" s="23" t="n"/>
       <c r="L41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="53" t="inlineStr">
-        <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+      <c r="A42" s="68" t="inlineStr">
+        <is>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B42" s="23" t="inlineStr">
@@ -3159,45 +3019,49 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H42" s="65" t="inlineStr">
+      <c r="H42" s="65" t="inlineStr"/>
+      <c r="I42" s="65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I42" s="65" t="inlineStr"/>
-      <c r="J42" s="23" t="inlineStr"/>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K42" s="23" t="n"/>
       <c r="L42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="53" t="inlineStr">
-        <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+      <c r="A43" s="68" t="inlineStr">
+        <is>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C43" s="78" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G43" s="65" t="inlineStr">
@@ -3205,20 +3069,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H43" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H43" s="65" t="inlineStr"/>
       <c r="I43" s="65" t="inlineStr"/>
       <c r="J43" s="23" t="inlineStr"/>
       <c r="K43" s="23" t="n"/>
       <c r="L43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="53" t="inlineStr">
-        <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+      <c r="A44" s="68" t="inlineStr">
+        <is>
+          <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
       </c>
       <c r="B44" s="23" t="inlineStr">
@@ -3226,9 +3086,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C44" s="78" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C44" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
@@ -3238,12 +3098,12 @@
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G44" s="65" t="inlineStr">
@@ -3256,25 +3116,33 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I44" s="65" t="inlineStr"/>
-      <c r="J44" s="23" t="inlineStr"/>
+      <c r="I44" s="65" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K44" s="23" t="n"/>
       <c r="L44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="53" t="inlineStr">
-        <is>
-          <t>PS5-60-22 - Power Gen Master UCP</t>
+      <c r="A45" s="68" t="inlineStr">
+        <is>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C45" s="77" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C45" s="76" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
@@ -3289,7 +3157,7 @@
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G45" s="65" t="inlineStr">
@@ -3297,28 +3165,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H45" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I45" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="H45" s="65" t="inlineStr"/>
+      <c r="I45" s="65" t="inlineStr"/>
+      <c r="J45" s="23" t="inlineStr"/>
       <c r="K45" s="23" t="n"/>
       <c r="L45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="53" t="inlineStr">
-        <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+      <c r="A46" s="68" t="inlineStr">
+        <is>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B46" s="23" t="inlineStr">
@@ -3351,30 +3207,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H46" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H46" s="65" t="inlineStr"/>
       <c r="I46" s="65" t="inlineStr"/>
       <c r="J46" s="23" t="inlineStr"/>
       <c r="K46" s="23" t="n"/>
       <c r="L46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="53" t="inlineStr">
-        <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+      <c r="A47" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C47" s="76" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C47" s="78" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -3402,15 +3254,23 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I47" s="65" t="inlineStr"/>
-      <c r="J47" s="23" t="inlineStr"/>
+      <c r="I47" s="65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="K47" s="23" t="n"/>
       <c r="L47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
+      <c r="A48" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
       </c>
       <c r="B48" s="23" t="inlineStr">
@@ -3418,9 +3278,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C48" s="78" t="inlineStr">
-        <is>
-          <t>93%</t>
+      <c r="C48" s="77" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
@@ -3443,28 +3303,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H48" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H48" s="65" t="inlineStr"/>
       <c r="I48" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K48" s="23" t="n"/>
       <c r="L48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-04 - CFO Storage Tank</t>
+      <c r="A49" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-12 - CFO Service Tank</t>
         </is>
       </c>
       <c r="B49" s="23" t="inlineStr">
@@ -3497,38 +3353,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H49" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="H49" s="65" t="inlineStr"/>
       <c r="I49" s="65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K49" s="23" t="n"/>
       <c r="L49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-12 - CFO Service Tank</t>
+      <c r="A50" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C50" s="77" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
@@ -3543,7 +3395,7 @@
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G50" s="65" t="inlineStr">
@@ -3551,28 +3403,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H50" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I50" s="65" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J50" s="23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="H50" s="65" t="inlineStr"/>
+      <c r="I50" s="65" t="inlineStr"/>
+      <c r="J50" s="23" t="inlineStr"/>
       <c r="K50" s="23" t="n"/>
       <c r="L50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
+      <c r="A51" s="68" t="inlineStr">
+        <is>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
@@ -3580,9 +3420,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C51" s="77" t="inlineStr">
-        <is>
-          <t>89%</t>
+      <c r="C51" s="78" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
@@ -3592,12 +3432,12 @@
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G51" s="65" t="inlineStr">
@@ -3605,30 +3445,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H51" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H51" s="65" t="inlineStr"/>
       <c r="I51" s="65" t="inlineStr"/>
       <c r="J51" s="23" t="inlineStr"/>
       <c r="K51" s="23" t="n"/>
       <c r="L51" s="67" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="inlineStr">
-        <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+      <c r="A52" s="68" t="inlineStr">
+        <is>
+          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C52" s="78" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
@@ -3638,12 +3474,12 @@
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" s="65" t="inlineStr">
@@ -3651,20 +3487,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H52" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H52" s="65" t="inlineStr"/>
       <c r="I52" s="65" t="inlineStr"/>
       <c r="J52" s="23" t="inlineStr"/>
       <c r="K52" s="23" t="n"/>
       <c r="L52" s="67" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="53" t="inlineStr">
-        <is>
-          <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
+      <c r="A53" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B53" s="23" t="inlineStr">
@@ -3672,9 +3504,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C53" s="78" t="inlineStr">
-        <is>
-          <t>93%</t>
+      <c r="C53" s="77" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
@@ -3697,20 +3529,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H53" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="H53" s="65" t="inlineStr"/>
       <c r="I53" s="65" t="inlineStr"/>
       <c r="J53" s="23" t="inlineStr"/>
       <c r="K53" s="23" t="n"/>
       <c r="L53" s="67" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+      <c r="A54" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
       </c>
       <c r="B54" s="23" t="inlineStr">
@@ -3720,7 +3548,7 @@
       </c>
       <c r="C54" s="77" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
@@ -3745,43 +3573,51 @@
       </c>
       <c r="H54" s="65" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I54" s="65" t="inlineStr"/>
-      <c r="J54" s="23" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I54" s="65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K54" s="23" t="n"/>
       <c r="L54" s="67" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
+      <c r="A55" s="68" t="inlineStr">
+        <is>
+          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="78" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C55" s="77" t="inlineStr">
-        <is>
-          <t>82%</t>
-        </is>
-      </c>
-      <c r="D55" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E55" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G55" s="65" t="inlineStr">
@@ -3789,53 +3625,41 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H55" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I55" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="H55" s="65" t="inlineStr"/>
+      <c r="I55" s="65" t="inlineStr"/>
+      <c r="J55" s="23" t="inlineStr"/>
       <c r="K55" s="23" t="n"/>
       <c r="L55" s="67" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="53" t="inlineStr">
-        <is>
-          <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
-        </is>
-      </c>
-      <c r="B56" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C56" s="78" t="inlineStr">
-        <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="D56" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E56" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="A56" s="79" t="inlineStr">
+        <is>
+          <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
+        </is>
+      </c>
+      <c r="B56" s="66" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C56" s="80" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D56" s="66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E56" s="66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" s="66" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="G56" s="65" t="inlineStr">
@@ -3843,43 +3667,39 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H56" s="65" t="inlineStr">
+      <c r="H56" s="65" t="inlineStr"/>
+      <c r="I56" s="65" t="inlineStr"/>
+      <c r="J56" s="66" t="inlineStr"/>
+      <c r="K56" s="66" t="n"/>
+      <c r="L56" s="67" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="68" t="inlineStr">
+        <is>
+          <t>PS5-08-85</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I56" s="65" t="inlineStr"/>
-      <c r="J56" s="23" t="inlineStr"/>
-      <c r="K56" s="23" t="n"/>
-      <c r="L56" s="67" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="79" t="inlineStr">
-        <is>
-          <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
-        </is>
-      </c>
-      <c r="B57" s="66" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C57" s="80" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="D57" s="66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E57" s="66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F57" s="66" t="inlineStr">
+      <c r="C57" s="76" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3889,18 +3709,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H57" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H57" s="65" t="inlineStr"/>
       <c r="I57" s="65" t="inlineStr"/>
-      <c r="J57" s="66" t="inlineStr"/>
-      <c r="K57" s="66" t="n"/>
+      <c r="J57" s="23" t="inlineStr"/>
+      <c r="K57" s="23" t="n"/>
       <c r="L57" s="67" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="53" t="inlineStr">
+      <c r="A58" s="68" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -3935,18 +3751,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H58" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H58" s="65" t="inlineStr"/>
       <c r="I58" s="65" t="inlineStr"/>
       <c r="J58" s="23" t="inlineStr"/>
       <c r="K58" s="23" t="n"/>
       <c r="L58" s="67" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="53" t="inlineStr">
+      <c r="A59" s="68" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -3981,11 +3793,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H59" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H59" s="65" t="inlineStr"/>
       <c r="I59" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -4000,7 +3808,7 @@
       <c r="L59" s="67" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="53" t="inlineStr">
+      <c r="A60" s="68" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -4035,18 +3843,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H60" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H60" s="65" t="inlineStr"/>
       <c r="I60" s="65" t="inlineStr"/>
       <c r="J60" s="23" t="inlineStr"/>
       <c r="K60" s="23" t="n"/>
       <c r="L60" s="67" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="53" t="inlineStr">
+      <c r="A61" s="68" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -4081,18 +3885,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H61" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H61" s="65" t="inlineStr"/>
       <c r="I61" s="65" t="inlineStr"/>
       <c r="J61" s="23" t="inlineStr"/>
       <c r="K61" s="23" t="n"/>
       <c r="L61" s="67" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="53" t="inlineStr">
+      <c r="A62" s="68" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -4127,18 +3927,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H62" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H62" s="65" t="inlineStr"/>
       <c r="I62" s="65" t="inlineStr"/>
       <c r="J62" s="23" t="inlineStr"/>
       <c r="K62" s="23" t="n"/>
       <c r="L62" s="67" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="53" t="inlineStr">
+      <c r="A63" s="68" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -4173,18 +3969,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H63" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H63" s="65" t="inlineStr"/>
       <c r="I63" s="65" t="inlineStr"/>
       <c r="J63" s="23" t="inlineStr"/>
       <c r="K63" s="23" t="n"/>
       <c r="L63" s="67" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="53" t="inlineStr">
+      <c r="A64" s="68" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -4219,18 +4011,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H64" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H64" s="65" t="inlineStr"/>
       <c r="I64" s="65" t="inlineStr"/>
       <c r="J64" s="23" t="inlineStr"/>
       <c r="K64" s="23" t="n"/>
       <c r="L64" s="67" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="53" t="inlineStr">
+      <c r="A65" s="68" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -4265,18 +4053,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H65" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H65" s="65" t="inlineStr"/>
       <c r="I65" s="65" t="inlineStr"/>
       <c r="J65" s="23" t="inlineStr"/>
       <c r="K65" s="23" t="n"/>
       <c r="L65" s="67" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="53" t="inlineStr">
+      <c r="A66" s="68" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -4311,11 +4095,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H66" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H66" s="65" t="inlineStr"/>
       <c r="I66" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -4330,7 +4110,7 @@
       <c r="L66" s="67" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="53" t="inlineStr">
+      <c r="A67" s="68" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -4365,18 +4145,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H67" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H67" s="65" t="inlineStr"/>
       <c r="I67" s="65" t="inlineStr"/>
       <c r="J67" s="23" t="inlineStr"/>
       <c r="K67" s="23" t="n"/>
       <c r="L67" s="67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="53" t="inlineStr">
+      <c r="A68" s="68" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -4411,18 +4187,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H68" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H68" s="65" t="inlineStr"/>
       <c r="I68" s="65" t="inlineStr"/>
       <c r="J68" s="23" t="inlineStr"/>
       <c r="K68" s="23" t="n"/>
       <c r="L68" s="67" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="53" t="inlineStr">
+      <c r="A69" s="68" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -4457,11 +4229,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H69" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H69" s="65" t="inlineStr"/>
       <c r="I69" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -4476,7 +4244,7 @@
       <c r="L69" s="67" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="53" t="inlineStr">
+      <c r="A70" s="68" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -4511,18 +4279,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H70" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H70" s="65" t="inlineStr"/>
       <c r="I70" s="65" t="inlineStr"/>
       <c r="J70" s="23" t="inlineStr"/>
       <c r="K70" s="23" t="n"/>
       <c r="L70" s="67" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="53" t="inlineStr">
+      <c r="A71" s="68" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -4557,11 +4321,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H71" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H71" s="65" t="inlineStr"/>
       <c r="I71" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -4576,7 +4336,7 @@
       <c r="L71" s="67" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="53" t="inlineStr">
+      <c r="A72" s="68" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -4611,18 +4371,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H72" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H72" s="65" t="inlineStr"/>
       <c r="I72" s="65" t="inlineStr"/>
       <c r="J72" s="23" t="inlineStr"/>
       <c r="K72" s="23" t="n"/>
       <c r="L72" s="67" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="53" t="inlineStr">
+      <c r="A73" s="68" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -4657,18 +4413,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H73" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H73" s="65" t="inlineStr"/>
       <c r="I73" s="65" t="inlineStr"/>
       <c r="J73" s="23" t="inlineStr"/>
       <c r="K73" s="23" t="n"/>
       <c r="L73" s="67" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="53" t="inlineStr">
+      <c r="A74" s="68" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -4703,18 +4455,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H74" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H74" s="65" t="inlineStr"/>
       <c r="I74" s="65" t="inlineStr"/>
       <c r="J74" s="23" t="inlineStr"/>
       <c r="K74" s="23" t="n"/>
       <c r="L74" s="67" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="53" t="inlineStr">
+      <c r="A75" s="68" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -4749,18 +4497,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H75" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H75" s="65" t="inlineStr"/>
       <c r="I75" s="65" t="inlineStr"/>
       <c r="J75" s="23" t="inlineStr"/>
       <c r="K75" s="23" t="n"/>
       <c r="L75" s="67" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="53" t="inlineStr">
+      <c r="A76" s="68" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -4795,18 +4539,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H76" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H76" s="65" t="inlineStr"/>
       <c r="I76" s="65" t="inlineStr"/>
       <c r="J76" s="23" t="inlineStr"/>
       <c r="K76" s="23" t="n"/>
       <c r="L76" s="67" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="53" t="inlineStr">
+      <c r="A77" s="68" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -4841,18 +4581,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H77" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H77" s="65" t="inlineStr"/>
       <c r="I77" s="65" t="inlineStr"/>
       <c r="J77" s="23" t="inlineStr"/>
       <c r="K77" s="23" t="n"/>
       <c r="L77" s="67" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="53" t="inlineStr">
+      <c r="A78" s="68" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -4887,11 +4623,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H78" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H78" s="65" t="inlineStr"/>
       <c r="I78" s="65" t="inlineStr">
         <is>
           <t>3</t>
@@ -4906,7 +4638,7 @@
       <c r="L78" s="67" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="53" t="inlineStr">
+      <c r="A79" s="68" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -4941,11 +4673,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H79" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H79" s="65" t="inlineStr"/>
       <c r="I79" s="65" t="inlineStr">
         <is>
           <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
@@ -4960,7 +4688,7 @@
       <c r="L79" s="67" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="53" t="inlineStr">
+      <c r="A80" s="68" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -4995,11 +4723,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H80" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H80" s="65" t="inlineStr"/>
       <c r="I80" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -5014,7 +4738,7 @@
       <c r="L80" s="67" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="53" t="inlineStr">
+      <c r="A81" s="68" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -5049,18 +4773,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H81" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H81" s="65" t="inlineStr"/>
       <c r="I81" s="65" t="inlineStr"/>
       <c r="J81" s="23" t="inlineStr"/>
       <c r="K81" s="23" t="n"/>
       <c r="L81" s="67" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="53" t="inlineStr">
+      <c r="A82" s="68" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -5095,18 +4815,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H82" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H82" s="65" t="inlineStr"/>
       <c r="I82" s="65" t="inlineStr"/>
       <c r="J82" s="23" t="inlineStr"/>
       <c r="K82" s="23" t="n"/>
       <c r="L82" s="67" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="53" t="inlineStr">
+      <c r="A83" s="68" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -5141,18 +4857,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H83" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H83" s="65" t="inlineStr"/>
       <c r="I83" s="65" t="inlineStr"/>
       <c r="J83" s="23" t="inlineStr"/>
       <c r="K83" s="23" t="n"/>
       <c r="L83" s="67" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="53" t="inlineStr">
+      <c r="A84" s="68" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -5187,11 +4899,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H84" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H84" s="65" t="inlineStr"/>
       <c r="I84" s="65" t="inlineStr">
         <is>
           <t>5</t>
@@ -5206,7 +4914,7 @@
       <c r="L84" s="67" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="53" t="inlineStr">
+      <c r="A85" s="68" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -5241,18 +4949,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H85" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H85" s="65" t="inlineStr"/>
       <c r="I85" s="65" t="inlineStr"/>
       <c r="J85" s="23" t="inlineStr"/>
       <c r="K85" s="23" t="n"/>
       <c r="L85" s="67" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="53" t="inlineStr">
+      <c r="A86" s="68" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -5287,18 +4991,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H86" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H86" s="65" t="inlineStr"/>
       <c r="I86" s="65" t="inlineStr"/>
       <c r="J86" s="23" t="inlineStr"/>
       <c r="K86" s="23" t="n"/>
       <c r="L86" s="67" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="53" t="inlineStr">
+      <c r="A87" s="68" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -5333,18 +5033,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H87" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H87" s="65" t="inlineStr"/>
       <c r="I87" s="65" t="inlineStr"/>
       <c r="J87" s="23" t="inlineStr"/>
       <c r="K87" s="23" t="n"/>
       <c r="L87" s="67" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="53" t="inlineStr">
+      <c r="A88" s="68" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -5379,18 +5075,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H88" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H88" s="65" t="inlineStr"/>
       <c r="I88" s="65" t="inlineStr"/>
       <c r="J88" s="23" t="inlineStr"/>
       <c r="K88" s="23" t="n"/>
       <c r="L88" s="67" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="53" t="inlineStr">
+      <c r="A89" s="68" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -5425,18 +5117,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H89" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H89" s="65" t="inlineStr"/>
       <c r="I89" s="65" t="inlineStr"/>
       <c r="J89" s="23" t="inlineStr"/>
       <c r="K89" s="23" t="n"/>
       <c r="L89" s="67" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="53" t="inlineStr">
+      <c r="A90" s="68" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -5471,18 +5159,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H90" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H90" s="65" t="inlineStr"/>
       <c r="I90" s="65" t="inlineStr"/>
       <c r="J90" s="23" t="inlineStr"/>
       <c r="K90" s="23" t="n"/>
       <c r="L90" s="67" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="53" t="inlineStr">
+      <c r="A91" s="68" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -5517,18 +5201,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H91" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H91" s="65" t="inlineStr"/>
       <c r="I91" s="65" t="inlineStr"/>
       <c r="J91" s="23" t="inlineStr"/>
       <c r="K91" s="23" t="n"/>
       <c r="L91" s="67" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="53" t="inlineStr">
+      <c r="A92" s="68" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -5563,18 +5243,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H92" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H92" s="65" t="inlineStr"/>
       <c r="I92" s="65" t="inlineStr"/>
       <c r="J92" s="23" t="inlineStr"/>
       <c r="K92" s="23" t="n"/>
       <c r="L92" s="67" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="53" t="inlineStr">
+      <c r="A93" s="68" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -5609,18 +5285,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H93" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H93" s="65" t="inlineStr"/>
       <c r="I93" s="65" t="inlineStr"/>
       <c r="J93" s="23" t="inlineStr"/>
       <c r="K93" s="23" t="n"/>
       <c r="L93" s="67" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="53" t="inlineStr">
+      <c r="A94" s="68" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -5655,18 +5327,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H94" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H94" s="65" t="inlineStr"/>
       <c r="I94" s="65" t="inlineStr"/>
       <c r="J94" s="23" t="inlineStr"/>
       <c r="K94" s="23" t="n"/>
       <c r="L94" s="67" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="53" t="inlineStr">
+      <c r="A95" s="68" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -5701,18 +5369,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H95" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H95" s="65" t="inlineStr"/>
       <c r="I95" s="65" t="inlineStr"/>
       <c r="J95" s="23" t="inlineStr"/>
       <c r="K95" s="23" t="n"/>
       <c r="L95" s="67" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="53" t="inlineStr">
+      <c r="A96" s="68" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -5747,18 +5411,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H96" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H96" s="65" t="inlineStr"/>
       <c r="I96" s="65" t="inlineStr"/>
       <c r="J96" s="23" t="inlineStr"/>
       <c r="K96" s="23" t="n"/>
       <c r="L96" s="67" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="53" t="inlineStr">
+      <c r="A97" s="68" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -5793,11 +5453,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H97" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H97" s="65" t="inlineStr"/>
       <c r="I97" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -5812,7 +5468,7 @@
       <c r="L97" s="67" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="53" t="inlineStr">
+      <c r="A98" s="68" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -5847,18 +5503,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H98" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H98" s="65" t="inlineStr"/>
       <c r="I98" s="65" t="inlineStr"/>
       <c r="J98" s="23" t="inlineStr"/>
       <c r="K98" s="23" t="n"/>
       <c r="L98" s="67" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="53" t="inlineStr">
+      <c r="A99" s="68" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -5893,18 +5545,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H99" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H99" s="65" t="inlineStr"/>
       <c r="I99" s="65" t="inlineStr"/>
       <c r="J99" s="23" t="inlineStr"/>
       <c r="K99" s="23" t="n"/>
       <c r="L99" s="67" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="53" t="inlineStr">
+      <c r="A100" s="68" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -5939,11 +5587,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H100" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H100" s="65" t="inlineStr"/>
       <c r="I100" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -5958,7 +5602,7 @@
       <c r="L100" s="67" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="53" t="inlineStr">
+      <c r="A101" s="68" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -5993,11 +5637,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H101" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H101" s="65" t="inlineStr"/>
       <c r="I101" s="65" t="inlineStr">
         <is>
           <t>15</t>
@@ -6012,7 +5652,7 @@
       <c r="L101" s="67" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="53" t="inlineStr">
+      <c r="A102" s="68" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -6047,11 +5687,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H102" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H102" s="65" t="inlineStr"/>
       <c r="I102" s="65" t="inlineStr">
         <is>
           <t>19</t>
@@ -6066,7 +5702,7 @@
       <c r="L102" s="67" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="53" t="inlineStr">
+      <c r="A103" s="68" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -6101,11 +5737,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H103" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H103" s="65" t="inlineStr"/>
       <c r="I103" s="65" t="inlineStr">
         <is>
           <t>37</t>
@@ -6120,7 +5752,7 @@
       <c r="L103" s="67" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="53" t="inlineStr">
+      <c r="A104" s="68" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -6155,11 +5787,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H104" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H104" s="65" t="inlineStr"/>
       <c r="I104" s="65" t="inlineStr">
         <is>
           <t>36</t>
@@ -6174,7 +5802,7 @@
       <c r="L104" s="67" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="53" t="inlineStr">
+      <c r="A105" s="68" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -6209,11 +5837,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H105" s="65" t="inlineStr"/>
       <c r="I105" s="65" t="inlineStr">
         <is>
           <t>43</t>
@@ -6228,7 +5852,7 @@
       <c r="L105" s="67" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="53" t="inlineStr">
+      <c r="A106" s="68" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -6263,11 +5887,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H106" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H106" s="65" t="inlineStr"/>
       <c r="I106" s="65" t="inlineStr">
         <is>
           <t>60</t>
@@ -6282,7 +5902,7 @@
       <c r="L106" s="67" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="53" t="inlineStr">
+      <c r="A107" s="68" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -6317,11 +5937,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H107" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H107" s="65" t="inlineStr"/>
       <c r="I107" s="65" t="inlineStr">
         <is>
           <t>23</t>
@@ -6336,7 +5952,7 @@
       <c r="L107" s="67" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="53" t="inlineStr">
+      <c r="A108" s="68" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -6371,11 +5987,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H108" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H108" s="65" t="inlineStr"/>
       <c r="I108" s="65" t="inlineStr">
         <is>
           <t>28</t>
@@ -6390,7 +6002,7 @@
       <c r="L108" s="67" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="53" t="inlineStr">
+      <c r="A109" s="68" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -6425,11 +6037,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H109" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H109" s="65" t="inlineStr"/>
       <c r="I109" s="65" t="inlineStr">
         <is>
           <t>43</t>
@@ -6444,7 +6052,7 @@
       <c r="L109" s="67" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="53" t="inlineStr">
+      <c r="A110" s="68" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -6479,11 +6087,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H110" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H110" s="65" t="inlineStr"/>
       <c r="I110" s="65" t="inlineStr">
         <is>
           <t>32</t>
@@ -6498,7 +6102,7 @@
       <c r="L110" s="67" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="53" t="inlineStr">
+      <c r="A111" s="68" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -6533,11 +6137,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H111" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H111" s="65" t="inlineStr"/>
       <c r="I111" s="65" t="inlineStr">
         <is>
           <t>44</t>
@@ -6552,7 +6152,7 @@
       <c r="L111" s="67" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="53" t="inlineStr">
+      <c r="A112" s="68" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -6587,11 +6187,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H112" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H112" s="65" t="inlineStr"/>
       <c r="I112" s="65" t="inlineStr">
         <is>
           <t>46</t>
@@ -6606,7 +6202,7 @@
       <c r="L112" s="67" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="53" t="inlineStr">
+      <c r="A113" s="68" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -6641,26 +6237,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H113" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H113" s="65" t="inlineStr"/>
       <c r="I113" s="65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J113" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K113" s="23" t="n"/>
       <c r="L113" s="67" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="53" t="inlineStr">
+      <c r="A114" s="68" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -6695,11 +6287,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H114" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H114" s="65" t="inlineStr"/>
       <c r="I114" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -6714,7 +6302,7 @@
       <c r="L114" s="67" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="53" t="inlineStr">
+      <c r="A115" s="68" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -6749,18 +6337,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H115" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H115" s="65" t="inlineStr"/>
       <c r="I115" s="65" t="inlineStr"/>
       <c r="J115" s="23" t="inlineStr"/>
       <c r="K115" s="23" t="n"/>
       <c r="L115" s="67" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="53" t="inlineStr">
+      <c r="A116" s="68" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -6795,18 +6379,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H116" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I116" s="65" t="inlineStr"/>
-      <c r="J116" s="23" t="inlineStr"/>
+      <c r="H116" s="65" t="inlineStr"/>
+      <c r="I116" s="65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J116" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K116" s="23" t="n"/>
       <c r="L116" s="67" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="53" t="inlineStr">
+      <c r="A117" s="68" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -6841,11 +6429,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H117" s="65" t="inlineStr"/>
       <c r="I117" s="65" t="inlineStr"/>
       <c r="J117" s="23" t="inlineStr">
         <is>
@@ -6856,7 +6440,7 @@
       <c r="L117" s="67" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="53" t="inlineStr">
+      <c r="A118" s="68" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -6891,18 +6475,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H118" s="65" t="inlineStr"/>
       <c r="I118" s="65" t="inlineStr"/>
       <c r="J118" s="23" t="inlineStr"/>
       <c r="K118" s="23" t="n"/>
       <c r="L118" s="67" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="53" t="inlineStr">
+      <c r="A119" s="68" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -6937,11 +6517,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H119" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H119" s="65" t="inlineStr"/>
       <c r="I119" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -6956,7 +6532,7 @@
       <c r="L119" s="67" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="53" t="inlineStr">
+      <c r="A120" s="68" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -6991,11 +6567,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H120" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H120" s="65" t="inlineStr"/>
       <c r="I120" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -7010,7 +6582,7 @@
       <c r="L120" s="67" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="53" t="inlineStr">
+      <c r="A121" s="68" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -7045,18 +6617,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H121" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H121" s="65" t="inlineStr"/>
       <c r="I121" s="65" t="inlineStr"/>
       <c r="J121" s="23" t="inlineStr"/>
       <c r="K121" s="23" t="n"/>
       <c r="L121" s="67" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="53" t="inlineStr">
+      <c r="A122" s="68" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -7091,18 +6659,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H122" s="65" t="inlineStr"/>
       <c r="I122" s="65" t="inlineStr"/>
       <c r="J122" s="23" t="inlineStr"/>
       <c r="K122" s="23" t="n"/>
       <c r="L122" s="67" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="53" t="inlineStr">
+      <c r="A123" s="68" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -7137,18 +6701,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H123" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H123" s="65" t="inlineStr"/>
       <c r="I123" s="65" t="inlineStr"/>
       <c r="J123" s="23" t="inlineStr"/>
       <c r="K123" s="23" t="n"/>
       <c r="L123" s="67" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="53" t="inlineStr">
+      <c r="A124" s="68" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -7183,18 +6743,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H124" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H124" s="65" t="inlineStr"/>
       <c r="I124" s="65" t="inlineStr"/>
       <c r="J124" s="23" t="inlineStr"/>
       <c r="K124" s="23" t="n"/>
       <c r="L124" s="67" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="53" t="inlineStr">
+      <c r="A125" s="68" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -7229,18 +6785,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H125" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H125" s="65" t="inlineStr"/>
       <c r="I125" s="65" t="inlineStr"/>
       <c r="J125" s="23" t="inlineStr"/>
       <c r="K125" s="23" t="n"/>
       <c r="L125" s="67" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="53" t="inlineStr">
+      <c r="A126" s="68" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -7275,18 +6827,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H126" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H126" s="65" t="inlineStr"/>
       <c r="I126" s="65" t="inlineStr"/>
       <c r="J126" s="23" t="inlineStr"/>
       <c r="K126" s="23" t="n"/>
       <c r="L126" s="67" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="53" t="inlineStr">
+      <c r="A127" s="68" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -7321,18 +6869,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H127" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H127" s="65" t="inlineStr"/>
       <c r="I127" s="65" t="inlineStr"/>
       <c r="J127" s="23" t="inlineStr"/>
       <c r="K127" s="23" t="n"/>
       <c r="L127" s="67" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="53" t="inlineStr">
+      <c r="A128" s="68" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -7367,11 +6911,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H128" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H128" s="65" t="inlineStr"/>
       <c r="I128" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -7386,7 +6926,7 @@
       <c r="L128" s="67" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="53" t="inlineStr">
+      <c r="A129" s="68" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -7421,18 +6961,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H129" s="65" t="inlineStr"/>
       <c r="I129" s="65" t="inlineStr"/>
       <c r="J129" s="23" t="inlineStr"/>
       <c r="K129" s="23" t="n"/>
       <c r="L129" s="67" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="53" t="inlineStr">
+      <c r="A130" s="68" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -7467,18 +7003,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H130" s="65" t="inlineStr"/>
       <c r="I130" s="65" t="inlineStr"/>
       <c r="J130" s="23" t="inlineStr"/>
       <c r="K130" s="23" t="n"/>
       <c r="L130" s="67" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="53" t="inlineStr">
+      <c r="A131" s="68" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -7513,11 +7045,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H131" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H131" s="65" t="inlineStr"/>
       <c r="I131" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -7532,7 +7060,7 @@
       <c r="L131" s="67" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="53" t="inlineStr">
+      <c r="A132" s="68" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -7567,18 +7095,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H132" s="65" t="inlineStr"/>
       <c r="I132" s="65" t="inlineStr"/>
       <c r="J132" s="23" t="inlineStr"/>
       <c r="K132" s="23" t="n"/>
       <c r="L132" s="67" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="53" t="inlineStr">
+      <c r="A133" s="68" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -7613,18 +7137,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H133" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H133" s="65" t="inlineStr"/>
       <c r="I133" s="65" t="inlineStr"/>
       <c r="J133" s="23" t="inlineStr"/>
       <c r="K133" s="23" t="n"/>
       <c r="L133" s="67" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="53" t="inlineStr">
+      <c r="A134" s="68" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -7659,18 +7179,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H134" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H134" s="65" t="inlineStr"/>
       <c r="I134" s="65" t="inlineStr"/>
       <c r="J134" s="23" t="inlineStr"/>
       <c r="K134" s="23" t="n"/>
       <c r="L134" s="67" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="53" t="inlineStr">
+      <c r="A135" s="68" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -7705,18 +7221,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H135" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H135" s="65" t="inlineStr"/>
       <c r="I135" s="65" t="inlineStr"/>
       <c r="J135" s="23" t="inlineStr"/>
       <c r="K135" s="23" t="n"/>
       <c r="L135" s="67" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="53" t="inlineStr">
+      <c r="A136" s="68" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -7751,18 +7263,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H136" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H136" s="65" t="inlineStr"/>
       <c r="I136" s="65" t="inlineStr"/>
       <c r="J136" s="23" t="inlineStr"/>
       <c r="K136" s="23" t="n"/>
       <c r="L136" s="67" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="53" t="inlineStr">
+      <c r="A137" s="68" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -7797,18 +7305,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H137" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H137" s="65" t="inlineStr"/>
       <c r="I137" s="65" t="inlineStr"/>
       <c r="J137" s="23" t="inlineStr"/>
       <c r="K137" s="23" t="n"/>
       <c r="L137" s="67" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="53" t="inlineStr">
+      <c r="A138" s="68" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -7836,7 +7340,7 @@
       <c r="L138" s="67" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="53" t="inlineStr">
+      <c r="A139" s="68" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -7864,7 +7368,7 @@
       <c r="L139" s="67" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="53" t="inlineStr">
+      <c r="A140" s="68" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -7872,7 +7376,7 @@
       <c r="B140" s="23" t="inlineStr"/>
       <c r="C140" s="78" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="D140" s="23" t="n">
@@ -7892,7 +7396,7 @@
       <c r="L140" s="67" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="53" t="inlineStr">
+      <c r="A141" s="68" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -7920,7 +7424,7 @@
       <c r="L141" s="67" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="53" t="inlineStr">
+      <c r="A142" s="68" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -7948,7 +7452,7 @@
       <c r="L142" s="67" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="53" t="inlineStr">
+      <c r="A143" s="68" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -7983,18 +7487,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H143" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H143" s="65" t="inlineStr"/>
       <c r="I143" s="65" t="inlineStr"/>
       <c r="J143" s="23" t="inlineStr"/>
       <c r="K143" s="23" t="n"/>
       <c r="L143" s="67" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="53" t="inlineStr">
+      <c r="A144" s="68" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -8029,18 +7529,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H144" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H144" s="65" t="inlineStr"/>
       <c r="I144" s="65" t="inlineStr"/>
       <c r="J144" s="23" t="inlineStr"/>
       <c r="K144" s="23" t="n"/>
       <c r="L144" s="67" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="53" t="inlineStr">
+      <c r="A145" s="68" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -8068,7 +7564,7 @@
       <c r="L145" s="67" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="53" t="inlineStr">
+      <c r="A146" s="68" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -8103,18 +7599,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H146" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H146" s="65" t="inlineStr"/>
       <c r="I146" s="65" t="inlineStr"/>
       <c r="J146" s="23" t="inlineStr"/>
       <c r="K146" s="23" t="n"/>
       <c r="L146" s="67" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="53" t="inlineStr">
+      <c r="A147" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01</t>
         </is>
@@ -8149,11 +7641,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H147" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H147" s="65" t="inlineStr"/>
       <c r="I147" s="65" t="inlineStr">
         <is>
           <t>148</t>
@@ -8168,7 +7656,7 @@
       <c r="L147" s="67" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="53" t="inlineStr">
+      <c r="A148" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
@@ -8196,7 +7684,7 @@
       <c r="L148" s="67" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="53" t="inlineStr">
+      <c r="A149" s="68" t="inlineStr">
         <is>
           <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
@@ -8224,7 +7712,7 @@
       <c r="L149" s="67" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="53" t="inlineStr">
+      <c r="A150" s="68" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -8252,7 +7740,7 @@
       <c r="L150" s="67" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="53" t="inlineStr">
+      <c r="A151" s="68" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -8280,7 +7768,7 @@
       <c r="L151" s="67" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="53" t="inlineStr">
+      <c r="A152" s="68" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -8315,11 +7803,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H152" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H152" s="65" t="inlineStr"/>
       <c r="I152" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -8334,7 +7818,7 @@
       <c r="L152" s="67" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="53" t="inlineStr">
+      <c r="A153" s="68" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -8369,11 +7853,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H153" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H153" s="65" t="inlineStr"/>
       <c r="I153" s="65" t="inlineStr">
         <is>
           <t>13</t>
@@ -8388,7 +7868,7 @@
       <c r="L153" s="67" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="53" t="inlineStr">
+      <c r="A154" s="68" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -8423,11 +7903,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H154" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H154" s="65" t="inlineStr"/>
       <c r="I154" s="65" t="inlineStr">
         <is>
           <t>12</t>
@@ -8442,7 +7918,7 @@
       <c r="L154" s="67" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="53" t="inlineStr">
+      <c r="A155" s="68" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -8477,11 +7953,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H155" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H155" s="65" t="inlineStr"/>
       <c r="I155" s="65" t="inlineStr">
         <is>
           <t>9</t>
@@ -8496,7 +7968,7 @@
       <c r="L155" s="67" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="53" t="inlineStr">
+      <c r="A156" s="68" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -8531,11 +8003,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H156" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H156" s="65" t="inlineStr"/>
       <c r="I156" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -8550,7 +8018,7 @@
       <c r="L156" s="67" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="53" t="inlineStr">
+      <c r="A157" s="68" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -8585,11 +8053,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H157" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H157" s="65" t="inlineStr"/>
       <c r="I157" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -8604,7 +8068,7 @@
       <c r="L157" s="67" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="53" t="inlineStr">
+      <c r="A158" s="68" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -8632,7 +8096,7 @@
       <c r="L158" s="67" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="53" t="inlineStr">
+      <c r="A159" s="68" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -8667,11 +8131,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H159" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H159" s="65" t="inlineStr"/>
       <c r="I159" s="65" t="inlineStr">
         <is>
           <t>18</t>
@@ -8686,7 +8146,7 @@
       <c r="L159" s="67" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="53" t="inlineStr">
+      <c r="A160" s="68" t="inlineStr">
         <is>
           <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
@@ -8714,7 +8174,7 @@
       <c r="L160" s="67" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="53" t="inlineStr">
+      <c r="A161" s="68" t="inlineStr">
         <is>
           <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
@@ -8742,7 +8202,7 @@
       <c r="L161" s="67" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="53" t="inlineStr">
+      <c r="A162" s="68" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -8770,7 +8230,7 @@
       <c r="L162" s="67" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="53" t="inlineStr">
+      <c r="A163" s="68" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -8805,11 +8265,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H163" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H163" s="65" t="inlineStr"/>
       <c r="I163" s="65" t="inlineStr">
         <is>
           <t>10</t>
@@ -8824,7 +8280,7 @@
       <c r="L163" s="67" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="53" t="inlineStr">
+      <c r="A164" s="68" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -8859,11 +8315,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H164" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H164" s="65" t="inlineStr"/>
       <c r="I164" s="65" t="inlineStr">
         <is>
           <t>240</t>
@@ -8878,7 +8330,7 @@
       <c r="L164" s="67" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="53" t="inlineStr">
+      <c r="A165" s="68" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -8913,11 +8365,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H165" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H165" s="65" t="inlineStr"/>
       <c r="I165" s="65" t="inlineStr">
         <is>
           <t>6</t>
@@ -8932,7 +8380,7 @@
       <c r="L165" s="67" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="53" t="inlineStr">
+      <c r="A166" s="68" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -8960,7 +8408,7 @@
       <c r="L166" s="67" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="53" t="inlineStr">
+      <c r="A167" s="68" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -8988,7 +8436,7 @@
       <c r="L167" s="67" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="53" t="inlineStr">
+      <c r="A168" s="68" t="inlineStr">
         <is>
           <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
@@ -9016,7 +8464,7 @@
       <c r="L168" s="67" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="53" t="inlineStr">
+      <c r="A169" s="68" t="inlineStr">
         <is>
           <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
@@ -9044,7 +8492,7 @@
       <c r="L169" s="67" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="53" t="inlineStr">
+      <c r="A170" s="68" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -9072,7 +8520,7 @@
       <c r="L170" s="67" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="53" t="inlineStr">
+      <c r="A171" s="68" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -9100,7 +8548,7 @@
       <c r="L171" s="67" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="53" t="inlineStr">
+      <c r="A172" s="68" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -9135,11 +8583,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H172" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H172" s="65" t="inlineStr"/>
       <c r="I172" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -9154,7 +8598,7 @@
       <c r="L172" s="67" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="53" t="inlineStr">
+      <c r="A173" s="68" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -9162,7 +8606,7 @@
       <c r="B173" s="23" t="inlineStr"/>
       <c r="C173" s="77" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="D173" s="23" t="n">
@@ -9182,7 +8626,7 @@
       <c r="L173" s="67" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="53" t="inlineStr">
+      <c r="A174" s="68" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -9217,18 +8661,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H174" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H174" s="65" t="inlineStr"/>
       <c r="I174" s="65" t="inlineStr"/>
       <c r="J174" s="23" t="inlineStr"/>
       <c r="K174" s="23" t="n"/>
       <c r="L174" s="67" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="53" t="inlineStr">
+      <c r="A175" s="68" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -9263,18 +8703,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H175" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H175" s="65" t="inlineStr"/>
       <c r="I175" s="65" t="inlineStr"/>
       <c r="J175" s="23" t="inlineStr"/>
       <c r="K175" s="23" t="n"/>
       <c r="L175" s="67" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="53" t="inlineStr">
+      <c r="A176" s="68" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -9309,11 +8745,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H176" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H176" s="65" t="inlineStr"/>
       <c r="I176" s="65" t="inlineStr">
         <is>
           <t>0</t>
@@ -9328,7 +8760,7 @@
       <c r="L176" s="67" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="53" t="inlineStr">
+      <c r="A177" s="68" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -9363,18 +8795,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H177" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H177" s="65" t="inlineStr"/>
       <c r="I177" s="65" t="inlineStr"/>
       <c r="J177" s="23" t="inlineStr"/>
       <c r="K177" s="23" t="n"/>
       <c r="L177" s="67" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="53" t="inlineStr">
+      <c r="A178" s="68" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -9409,18 +8837,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H178" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H178" s="65" t="inlineStr"/>
       <c r="I178" s="65" t="inlineStr"/>
       <c r="J178" s="23" t="inlineStr"/>
       <c r="K178" s="23" t="n"/>
       <c r="L178" s="67" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="53" t="inlineStr">
+      <c r="A179" s="68" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -9455,18 +8879,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H179" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H179" s="65" t="inlineStr"/>
       <c r="I179" s="65" t="inlineStr"/>
       <c r="J179" s="23" t="inlineStr"/>
       <c r="K179" s="23" t="n"/>
       <c r="L179" s="67" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="53" t="inlineStr">
+      <c r="A180" s="68" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -9501,11 +8921,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H180" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H180" s="65" t="inlineStr"/>
       <c r="I180" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -9520,7 +8936,7 @@
       <c r="L180" s="67" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="53" t="inlineStr">
+      <c r="A181" s="68" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -9555,11 +8971,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H181" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H181" s="65" t="inlineStr"/>
       <c r="I181" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -9574,7 +8986,7 @@
       <c r="L181" s="67" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="53" t="inlineStr">
+      <c r="A182" s="68" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -9609,11 +9021,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H182" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H182" s="65" t="inlineStr"/>
       <c r="I182" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -9628,7 +9036,7 @@
       <c r="L182" s="67" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="53" t="inlineStr">
+      <c r="A183" s="68" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -9663,11 +9071,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H183" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H183" s="65" t="inlineStr"/>
       <c r="I183" s="65" t="inlineStr">
         <is>
           <t>7</t>
@@ -9682,7 +9086,7 @@
       <c r="L183" s="67" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="53" t="inlineStr">
+      <c r="A184" s="68" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -9717,18 +9121,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H184" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H184" s="65" t="inlineStr"/>
       <c r="I184" s="65" t="inlineStr"/>
       <c r="J184" s="23" t="inlineStr"/>
       <c r="K184" s="23" t="n"/>
       <c r="L184" s="67" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="53" t="inlineStr">
+      <c r="A185" s="68" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -9763,18 +9163,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H185" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H185" s="65" t="inlineStr"/>
       <c r="I185" s="65" t="inlineStr"/>
       <c r="J185" s="23" t="inlineStr"/>
       <c r="K185" s="23" t="n"/>
       <c r="L185" s="67" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="53" t="inlineStr">
+      <c r="A186" s="68" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -9809,18 +9205,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H186" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H186" s="65" t="inlineStr"/>
       <c r="I186" s="65" t="inlineStr"/>
       <c r="J186" s="23" t="inlineStr"/>
       <c r="K186" s="23" t="n"/>
       <c r="L186" s="67" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="53" t="inlineStr">
+      <c r="A187" s="68" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -9855,18 +9247,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H187" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H187" s="65" t="inlineStr"/>
       <c r="I187" s="65" t="inlineStr"/>
       <c r="J187" s="23" t="inlineStr"/>
       <c r="K187" s="23" t="n"/>
       <c r="L187" s="67" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="53" t="inlineStr">
+      <c r="A188" s="68" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -9901,18 +9289,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H188" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H188" s="65" t="inlineStr"/>
       <c r="I188" s="65" t="inlineStr"/>
       <c r="J188" s="23" t="inlineStr"/>
       <c r="K188" s="23" t="n"/>
       <c r="L188" s="67" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="53" t="inlineStr">
+      <c r="A189" s="68" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -9947,18 +9331,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H189" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H189" s="65" t="inlineStr"/>
       <c r="I189" s="65" t="inlineStr"/>
       <c r="J189" s="23" t="inlineStr"/>
       <c r="K189" s="23" t="n"/>
       <c r="L189" s="67" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="53" t="inlineStr">
+      <c r="A190" s="68" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -9993,11 +9373,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H190" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H190" s="65" t="inlineStr"/>
       <c r="I190" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -10012,7 +9388,7 @@
       <c r="L190" s="67" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="53" t="inlineStr">
+      <c r="A191" s="68" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -10047,11 +9423,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H191" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H191" s="65" t="inlineStr"/>
       <c r="I191" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -10066,7 +9438,7 @@
       <c r="L191" s="67" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="53" t="inlineStr">
+      <c r="A192" s="68" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -10101,11 +9473,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H192" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H192" s="65" t="inlineStr"/>
       <c r="I192" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -10120,7 +9488,7 @@
       <c r="L192" s="67" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="53" t="inlineStr">
+      <c r="A193" s="68" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -10155,18 +9523,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H193" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H193" s="65" t="inlineStr"/>
       <c r="I193" s="65" t="inlineStr"/>
       <c r="J193" s="23" t="inlineStr"/>
       <c r="K193" s="23" t="n"/>
       <c r="L193" s="67" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="53" t="inlineStr">
+      <c r="A194" s="68" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -10201,11 +9565,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H194" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H194" s="65" t="inlineStr"/>
       <c r="I194" s="65" t="inlineStr">
         <is>
           <t>3</t>
@@ -10220,7 +9580,7 @@
       <c r="L194" s="67" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="53" t="inlineStr">
+      <c r="A195" s="68" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -10255,11 +9615,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H195" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H195" s="65" t="inlineStr"/>
       <c r="I195" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -10274,7 +9630,7 @@
       <c r="L195" s="67" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="53" t="inlineStr">
+      <c r="A196" s="68" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -10309,18 +9665,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H196" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H196" s="65" t="inlineStr"/>
       <c r="I196" s="65" t="inlineStr"/>
       <c r="J196" s="23" t="inlineStr"/>
       <c r="K196" s="23" t="n"/>
       <c r="L196" s="67" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="53" t="inlineStr">
+      <c r="A197" s="68" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -10355,18 +9707,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H197" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H197" s="65" t="inlineStr"/>
       <c r="I197" s="65" t="inlineStr"/>
       <c r="J197" s="23" t="inlineStr"/>
       <c r="K197" s="23" t="n"/>
       <c r="L197" s="67" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="53" t="inlineStr">
+      <c r="A198" s="68" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -10401,11 +9749,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H198" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H198" s="65" t="inlineStr"/>
       <c r="I198" s="65" t="inlineStr"/>
       <c r="J198" s="23" t="inlineStr">
         <is>
@@ -10416,7 +9760,7 @@
       <c r="L198" s="67" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="53" t="inlineStr">
+      <c r="A199" s="68" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -10451,18 +9795,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H199" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H199" s="65" t="inlineStr"/>
       <c r="I199" s="65" t="inlineStr"/>
       <c r="J199" s="23" t="inlineStr"/>
       <c r="K199" s="23" t="n"/>
       <c r="L199" s="67" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="53" t="inlineStr">
+      <c r="A200" s="68" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -10497,18 +9837,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H200" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H200" s="65" t="inlineStr"/>
       <c r="I200" s="65" t="inlineStr"/>
       <c r="J200" s="23" t="inlineStr"/>
       <c r="K200" s="23" t="n"/>
       <c r="L200" s="67" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="53" t="inlineStr">
+      <c r="A201" s="68" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -10543,18 +9879,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H201" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H201" s="65" t="inlineStr"/>
       <c r="I201" s="65" t="inlineStr"/>
       <c r="J201" s="23" t="inlineStr"/>
       <c r="K201" s="23" t="n"/>
       <c r="L201" s="67" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="53" t="inlineStr">
+      <c r="A202" s="68" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10589,18 +9921,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H202" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H202" s="65" t="inlineStr"/>
       <c r="I202" s="65" t="inlineStr"/>
       <c r="J202" s="23" t="inlineStr"/>
       <c r="K202" s="23" t="n"/>
       <c r="L202" s="67" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="53" t="inlineStr">
+      <c r="A203" s="68" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -10635,18 +9963,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H203" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H203" s="65" t="inlineStr"/>
       <c r="I203" s="65" t="inlineStr"/>
       <c r="J203" s="23" t="inlineStr"/>
       <c r="K203" s="23" t="n"/>
       <c r="L203" s="67" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="53" t="inlineStr">
+      <c r="A204" s="68" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10681,18 +10005,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H204" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H204" s="65" t="inlineStr"/>
       <c r="I204" s="65" t="inlineStr"/>
       <c r="J204" s="23" t="inlineStr"/>
       <c r="K204" s="23" t="n"/>
       <c r="L204" s="67" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="53" t="inlineStr">
+      <c r="A205" s="68" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -10727,18 +10047,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H205" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H205" s="65" t="inlineStr"/>
       <c r="I205" s="65" t="inlineStr"/>
       <c r="J205" s="23" t="inlineStr"/>
       <c r="K205" s="23" t="n"/>
       <c r="L205" s="67" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="53" t="inlineStr">
+      <c r="A206" s="68" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10773,18 +10089,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H206" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H206" s="65" t="inlineStr"/>
       <c r="I206" s="65" t="inlineStr"/>
       <c r="J206" s="23" t="inlineStr"/>
       <c r="K206" s="23" t="n"/>
       <c r="L206" s="67" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="53" t="inlineStr">
+      <c r="A207" s="68" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -10819,18 +10131,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H207" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H207" s="65" t="inlineStr"/>
       <c r="I207" s="65" t="inlineStr"/>
       <c r="J207" s="23" t="inlineStr"/>
       <c r="K207" s="23" t="n"/>
       <c r="L207" s="67" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="53" t="inlineStr">
+      <c r="A208" s="68" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -10865,18 +10173,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H208" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H208" s="65" t="inlineStr"/>
       <c r="I208" s="65" t="inlineStr"/>
       <c r="J208" s="23" t="inlineStr"/>
       <c r="K208" s="23" t="n"/>
       <c r="L208" s="67" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="53" t="inlineStr">
+      <c r="A209" s="68" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -10911,18 +10215,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H209" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H209" s="65" t="inlineStr"/>
       <c r="I209" s="65" t="inlineStr"/>
       <c r="J209" s="23" t="inlineStr"/>
       <c r="K209" s="23" t="n"/>
       <c r="L209" s="67" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="53" t="inlineStr">
+      <c r="A210" s="68" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -10957,18 +10257,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H210" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H210" s="65" t="inlineStr"/>
       <c r="I210" s="65" t="inlineStr"/>
       <c r="J210" s="23" t="inlineStr"/>
       <c r="K210" s="23" t="n"/>
       <c r="L210" s="67" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="53" t="inlineStr">
+      <c r="A211" s="68" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -11003,18 +10299,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H211" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H211" s="65" t="inlineStr"/>
       <c r="I211" s="65" t="inlineStr"/>
       <c r="J211" s="23" t="inlineStr"/>
       <c r="K211" s="23" t="n"/>
       <c r="L211" s="67" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="53" t="inlineStr">
+      <c r="A212" s="68" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -11049,18 +10341,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H212" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H212" s="65" t="inlineStr"/>
       <c r="I212" s="65" t="inlineStr"/>
       <c r="J212" s="23" t="inlineStr"/>
       <c r="K212" s="23" t="n"/>
       <c r="L212" s="67" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="53" t="inlineStr">
+      <c r="A213" s="68" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -11095,18 +10383,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H213" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H213" s="65" t="inlineStr"/>
       <c r="I213" s="65" t="inlineStr"/>
       <c r="J213" s="23" t="inlineStr"/>
       <c r="K213" s="23" t="n"/>
       <c r="L213" s="67" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="53" t="inlineStr">
+      <c r="A214" s="68" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -11141,18 +10425,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H214" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H214" s="65" t="inlineStr"/>
       <c r="I214" s="65" t="inlineStr"/>
       <c r="J214" s="23" t="inlineStr"/>
       <c r="K214" s="23" t="n"/>
       <c r="L214" s="67" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="53" t="inlineStr">
+      <c r="A215" s="68" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -11187,18 +10467,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H215" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H215" s="65" t="inlineStr"/>
       <c r="I215" s="65" t="inlineStr"/>
       <c r="J215" s="23" t="inlineStr"/>
       <c r="K215" s="23" t="n"/>
       <c r="L215" s="67" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="53" t="inlineStr">
+      <c r="A216" s="68" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -11233,18 +10509,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H216" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H216" s="65" t="inlineStr"/>
       <c r="I216" s="65" t="inlineStr"/>
       <c r="J216" s="23" t="inlineStr"/>
       <c r="K216" s="23" t="n"/>
       <c r="L216" s="67" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="53" t="inlineStr">
+      <c r="A217" s="68" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -11279,18 +10551,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H217" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H217" s="65" t="inlineStr"/>
       <c r="I217" s="65" t="inlineStr"/>
       <c r="J217" s="23" t="inlineStr"/>
       <c r="K217" s="23" t="n"/>
       <c r="L217" s="67" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="53" t="inlineStr">
+      <c r="A218" s="68" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -11325,18 +10593,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H218" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H218" s="65" t="inlineStr"/>
       <c r="I218" s="65" t="inlineStr"/>
       <c r="J218" s="23" t="inlineStr"/>
       <c r="K218" s="23" t="n"/>
       <c r="L218" s="67" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="53" t="inlineStr">
+      <c r="A219" s="68" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -11371,18 +10635,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H219" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H219" s="65" t="inlineStr"/>
       <c r="I219" s="65" t="inlineStr"/>
       <c r="J219" s="23" t="inlineStr"/>
       <c r="K219" s="23" t="n"/>
       <c r="L219" s="67" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="53" t="inlineStr">
+      <c r="A220" s="68" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -11417,18 +10677,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H220" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H220" s="65" t="inlineStr"/>
       <c r="I220" s="65" t="inlineStr"/>
       <c r="J220" s="23" t="inlineStr"/>
       <c r="K220" s="23" t="n"/>
       <c r="L220" s="67" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="53" t="inlineStr">
+      <c r="A221" s="68" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -11463,18 +10719,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H221" s="65" t="inlineStr"/>
       <c r="I221" s="65" t="inlineStr"/>
       <c r="J221" s="23" t="inlineStr"/>
       <c r="K221" s="23" t="n"/>
       <c r="L221" s="67" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="53" t="inlineStr">
+      <c r="A222" s="68" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -11509,18 +10761,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H222" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H222" s="65" t="inlineStr"/>
       <c r="I222" s="65" t="inlineStr"/>
       <c r="J222" s="23" t="inlineStr"/>
       <c r="K222" s="23" t="n"/>
       <c r="L222" s="67" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="53" t="inlineStr">
+      <c r="A223" s="68" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -11555,18 +10803,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H223" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H223" s="65" t="inlineStr"/>
       <c r="I223" s="65" t="inlineStr"/>
       <c r="J223" s="23" t="inlineStr"/>
       <c r="K223" s="23" t="n"/>
       <c r="L223" s="67" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="53" t="inlineStr">
+      <c r="A224" s="68" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -11601,18 +10845,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H224" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H224" s="65" t="inlineStr"/>
       <c r="I224" s="65" t="inlineStr"/>
       <c r="J224" s="23" t="inlineStr"/>
       <c r="K224" s="23" t="n"/>
       <c r="L224" s="67" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="53" t="inlineStr">
+      <c r="A225" s="68" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -11647,18 +10887,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H225" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H225" s="65" t="inlineStr"/>
       <c r="I225" s="65" t="inlineStr"/>
       <c r="J225" s="23" t="inlineStr"/>
       <c r="K225" s="23" t="n"/>
       <c r="L225" s="67" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="53" t="inlineStr">
+      <c r="A226" s="68" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -11693,18 +10929,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H226" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H226" s="65" t="inlineStr"/>
       <c r="I226" s="65" t="inlineStr"/>
       <c r="J226" s="23" t="inlineStr"/>
       <c r="K226" s="23" t="n"/>
       <c r="L226" s="67" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="53" t="inlineStr">
+      <c r="A227" s="68" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -11739,18 +10971,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H227" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H227" s="65" t="inlineStr"/>
       <c r="I227" s="65" t="inlineStr"/>
       <c r="J227" s="23" t="inlineStr"/>
       <c r="K227" s="23" t="n"/>
       <c r="L227" s="67" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="53" t="inlineStr">
+      <c r="A228" s="68" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -11785,18 +11013,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H228" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H228" s="65" t="inlineStr"/>
       <c r="I228" s="65" t="inlineStr"/>
       <c r="J228" s="23" t="inlineStr"/>
       <c r="K228" s="23" t="n"/>
       <c r="L228" s="67" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="53" t="inlineStr">
+      <c r="A229" s="68" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -11831,18 +11055,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H229" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H229" s="65" t="inlineStr"/>
       <c r="I229" s="65" t="inlineStr"/>
       <c r="J229" s="23" t="inlineStr"/>
       <c r="K229" s="23" t="n"/>
       <c r="L229" s="67" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="53" t="inlineStr">
+      <c r="A230" s="68" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -11877,18 +11097,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H230" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H230" s="65" t="inlineStr"/>
       <c r="I230" s="65" t="inlineStr"/>
       <c r="J230" s="23" t="inlineStr"/>
       <c r="K230" s="23" t="n"/>
       <c r="L230" s="67" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="53" t="inlineStr">
+      <c r="A231" s="68" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -11923,18 +11139,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H231" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H231" s="65" t="inlineStr"/>
       <c r="I231" s="65" t="inlineStr"/>
       <c r="J231" s="23" t="inlineStr"/>
       <c r="K231" s="23" t="n"/>
       <c r="L231" s="67" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="53" t="inlineStr">
+      <c r="A232" s="68" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -11969,18 +11181,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H232" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H232" s="65" t="inlineStr"/>
       <c r="I232" s="65" t="inlineStr"/>
       <c r="J232" s="23" t="inlineStr"/>
       <c r="K232" s="23" t="n"/>
       <c r="L232" s="67" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="53" t="inlineStr">
+      <c r="A233" s="68" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -12015,18 +11223,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H233" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H233" s="65" t="inlineStr"/>
       <c r="I233" s="65" t="inlineStr"/>
       <c r="J233" s="23" t="inlineStr"/>
       <c r="K233" s="23" t="n"/>
       <c r="L233" s="67" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="53" t="inlineStr">
+      <c r="A234" s="68" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -12061,18 +11265,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H234" s="65" t="inlineStr"/>
       <c r="I234" s="65" t="inlineStr"/>
       <c r="J234" s="23" t="inlineStr"/>
       <c r="K234" s="23" t="n"/>
       <c r="L234" s="67" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="53" t="inlineStr">
+      <c r="A235" s="68" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -12107,18 +11307,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H235" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H235" s="65" t="inlineStr"/>
       <c r="I235" s="65" t="inlineStr"/>
       <c r="J235" s="23" t="inlineStr"/>
       <c r="K235" s="23" t="n"/>
       <c r="L235" s="67" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="53" t="inlineStr">
+      <c r="A236" s="68" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -12153,18 +11349,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H236" s="65" t="inlineStr"/>
       <c r="I236" s="65" t="inlineStr"/>
       <c r="J236" s="23" t="inlineStr"/>
       <c r="K236" s="23" t="n"/>
       <c r="L236" s="67" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="53" t="inlineStr">
+      <c r="A237" s="68" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -12199,18 +11391,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H237" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H237" s="65" t="inlineStr"/>
       <c r="I237" s="65" t="inlineStr"/>
       <c r="J237" s="23" t="inlineStr"/>
       <c r="K237" s="23" t="n"/>
       <c r="L237" s="67" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="53" t="inlineStr">
+      <c r="A238" s="68" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -12245,18 +11433,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H238" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H238" s="65" t="inlineStr"/>
       <c r="I238" s="65" t="inlineStr"/>
       <c r="J238" s="23" t="inlineStr"/>
       <c r="K238" s="23" t="n"/>
       <c r="L238" s="67" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="53" t="inlineStr">
+      <c r="A239" s="68" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -12291,18 +11475,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H239" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H239" s="65" t="inlineStr"/>
       <c r="I239" s="65" t="inlineStr"/>
       <c r="J239" s="23" t="inlineStr"/>
       <c r="K239" s="23" t="n"/>
       <c r="L239" s="67" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="53" t="inlineStr">
+      <c r="A240" s="68" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -12337,18 +11517,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H240" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H240" s="65" t="inlineStr"/>
       <c r="I240" s="65" t="inlineStr"/>
       <c r="J240" s="23" t="inlineStr"/>
       <c r="K240" s="23" t="n"/>
       <c r="L240" s="67" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="53" t="inlineStr">
+      <c r="A241" s="68" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -12383,18 +11559,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H241" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H241" s="65" t="inlineStr"/>
       <c r="I241" s="65" t="inlineStr"/>
       <c r="J241" s="23" t="inlineStr"/>
       <c r="K241" s="23" t="n"/>
       <c r="L241" s="67" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="53" t="inlineStr">
+      <c r="A242" s="68" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -12429,18 +11601,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H242" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H242" s="65" t="inlineStr"/>
       <c r="I242" s="65" t="inlineStr"/>
       <c r="J242" s="23" t="inlineStr"/>
       <c r="K242" s="23" t="n"/>
       <c r="L242" s="67" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="53" t="inlineStr">
+      <c r="A243" s="68" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -12475,18 +11643,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H243" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H243" s="65" t="inlineStr"/>
       <c r="I243" s="65" t="inlineStr"/>
       <c r="J243" s="23" t="inlineStr"/>
       <c r="K243" s="23" t="n"/>
       <c r="L243" s="67" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="53" t="inlineStr">
+      <c r="A244" s="68" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -12521,18 +11685,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H244" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H244" s="65" t="inlineStr"/>
       <c r="I244" s="65" t="inlineStr"/>
       <c r="J244" s="23" t="inlineStr"/>
       <c r="K244" s="23" t="n"/>
       <c r="L244" s="67" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="53" t="inlineStr">
+      <c r="A245" s="68" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -12567,18 +11727,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H245" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H245" s="65" t="inlineStr"/>
       <c r="I245" s="65" t="inlineStr"/>
       <c r="J245" s="23" t="inlineStr"/>
       <c r="K245" s="23" t="n"/>
       <c r="L245" s="67" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="53" t="inlineStr">
+      <c r="A246" s="68" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -12613,18 +11769,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H246" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H246" s="65" t="inlineStr"/>
       <c r="I246" s="65" t="inlineStr"/>
       <c r="J246" s="23" t="inlineStr"/>
       <c r="K246" s="23" t="n"/>
       <c r="L246" s="67" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="53" t="inlineStr">
+      <c r="A247" s="68" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -12659,18 +11811,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H247" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H247" s="65" t="inlineStr"/>
       <c r="I247" s="65" t="inlineStr"/>
       <c r="J247" s="23" t="inlineStr"/>
       <c r="K247" s="23" t="n"/>
       <c r="L247" s="67" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="53" t="inlineStr">
+      <c r="A248" s="68" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -12705,18 +11853,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H248" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H248" s="65" t="inlineStr"/>
       <c r="I248" s="65" t="inlineStr"/>
       <c r="J248" s="23" t="inlineStr"/>
       <c r="K248" s="23" t="n"/>
       <c r="L248" s="67" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="53" t="inlineStr">
+      <c r="A249" s="68" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -12751,18 +11895,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H249" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H249" s="65" t="inlineStr"/>
       <c r="I249" s="65" t="inlineStr"/>
       <c r="J249" s="23" t="inlineStr"/>
       <c r="K249" s="23" t="n"/>
       <c r="L249" s="67" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="53" t="inlineStr">
+      <c r="A250" s="68" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -12797,18 +11937,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H250" s="65" t="inlineStr"/>
       <c r="I250" s="65" t="inlineStr"/>
       <c r="J250" s="23" t="inlineStr"/>
       <c r="K250" s="23" t="n"/>
       <c r="L250" s="67" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="53" t="inlineStr">
+      <c r="A251" s="68" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -12843,18 +11979,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H251" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H251" s="65" t="inlineStr"/>
       <c r="I251" s="65" t="inlineStr"/>
       <c r="J251" s="23" t="inlineStr"/>
       <c r="K251" s="23" t="n"/>
       <c r="L251" s="67" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="53" t="inlineStr">
+      <c r="A252" s="68" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -12889,11 +12021,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H252" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H252" s="65" t="inlineStr"/>
       <c r="I252" s="65" t="inlineStr">
         <is>
           <t>1</t>
@@ -12908,7 +12036,7 @@
       <c r="L252" s="67" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="53" t="inlineStr">
+      <c r="A253" s="68" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -12943,11 +12071,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H253" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H253" s="65" t="inlineStr"/>
       <c r="I253" s="65" t="inlineStr">
         <is>
           <t>17</t>
@@ -12962,7 +12086,7 @@
       <c r="L253" s="67" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="53" t="inlineStr">
+      <c r="A254" s="68" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -12997,18 +12121,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H254" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H254" s="65" t="inlineStr"/>
       <c r="I254" s="65" t="inlineStr"/>
       <c r="J254" s="23" t="inlineStr"/>
       <c r="K254" s="23" t="n"/>
       <c r="L254" s="67" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="53" t="inlineStr">
+      <c r="A255" s="68" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -13043,18 +12163,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H255" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H255" s="65" t="inlineStr"/>
       <c r="I255" s="65" t="inlineStr"/>
       <c r="J255" s="23" t="inlineStr"/>
       <c r="K255" s="23" t="n"/>
       <c r="L255" s="67" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="53" t="inlineStr">
+      <c r="A256" s="68" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -13082,7 +12198,7 @@
       <c r="L256" s="67" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="53" t="inlineStr">
+      <c r="A257" s="68" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -13117,11 +12233,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H257" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H257" s="65" t="inlineStr"/>
       <c r="I257" s="65" t="inlineStr">
         <is>
           <t>34</t>
@@ -13136,7 +12248,7 @@
       <c r="L257" s="67" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="53" t="inlineStr">
+      <c r="A258" s="68" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -13171,11 +12283,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H258" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H258" s="65" t="inlineStr"/>
       <c r="I258" s="65" t="inlineStr">
         <is>
           <t>32</t>
@@ -13190,7 +12298,7 @@
       <c r="L258" s="67" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="53" t="inlineStr">
+      <c r="A259" s="68" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -13225,18 +12333,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H259" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H259" s="65" t="inlineStr"/>
       <c r="I259" s="65" t="inlineStr"/>
       <c r="J259" s="23" t="inlineStr"/>
       <c r="K259" s="23" t="n"/>
       <c r="L259" s="67" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="53" t="inlineStr">
+      <c r="A260" s="68" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -13271,18 +12375,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H260" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H260" s="65" t="inlineStr"/>
       <c r="I260" s="65" t="inlineStr"/>
       <c r="J260" s="23" t="inlineStr"/>
       <c r="K260" s="23" t="n"/>
       <c r="L260" s="67" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="53" t="inlineStr">
+      <c r="A261" s="68" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -13317,11 +12417,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H261" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H261" s="65" t="inlineStr"/>
       <c r="I261" s="65" t="inlineStr">
         <is>
           <t>14</t>
@@ -13336,7 +12432,7 @@
       <c r="L261" s="67" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="53" t="inlineStr">
+      <c r="A262" s="68" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -13371,11 +12467,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H262" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H262" s="65" t="inlineStr"/>
       <c r="I262" s="65" t="inlineStr">
         <is>
           <t>11</t>
@@ -13390,7 +12482,7 @@
       <c r="L262" s="67" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="53" t="inlineStr">
+      <c r="A263" s="68" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -13402,7 +12494,7 @@
       </c>
       <c r="C263" s="76" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="D263" s="23" t="inlineStr">
@@ -13425,26 +12517,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H263" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H263" s="65" t="inlineStr"/>
       <c r="I263" s="65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J263" s="23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K263" s="23" t="n"/>
       <c r="L263" s="67" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="53" t="inlineStr">
+      <c r="A264" s="68" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -13479,11 +12567,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H264" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H264" s="65" t="inlineStr"/>
       <c r="I264" s="65" t="inlineStr">
         <is>
           <t>12</t>
@@ -13498,7 +12582,7 @@
       <c r="L264" s="67" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="53" t="inlineStr">
+      <c r="A265" s="68" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -13533,18 +12617,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H265" s="65" t="inlineStr">
+      <c r="H265" s="65" t="inlineStr"/>
+      <c r="I265" s="65" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I265" s="65" t="inlineStr"/>
-      <c r="J265" s="23" t="inlineStr"/>
+      <c r="J265" s="23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="K265" s="23" t="n"/>
       <c r="L265" s="67" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="53" t="inlineStr">
+      <c r="A266" s="68" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -13572,7 +12660,7 @@
       <c r="L266" s="67" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="53" t="inlineStr">
+      <c r="A267" s="68" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -13600,7 +12688,7 @@
       <c r="L267" s="67" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="53" t="inlineStr">
+      <c r="A268" s="68" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -13635,11 +12723,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H268" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H268" s="65" t="inlineStr"/>
       <c r="I268" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -13654,7 +12738,7 @@
       <c r="L268" s="67" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="53" t="inlineStr">
+      <c r="A269" s="68" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -13682,7 +12766,7 @@
       <c r="L269" s="67" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="53" t="inlineStr">
+      <c r="A270" s="68" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -13717,11 +12801,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H270" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H270" s="65" t="inlineStr"/>
       <c r="I270" s="65" t="inlineStr">
         <is>
           <t>8</t>
@@ -13736,7 +12816,7 @@
       <c r="L270" s="67" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="53" t="inlineStr">
+      <c r="A271" s="68" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -13771,11 +12851,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H271" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H271" s="65" t="inlineStr"/>
       <c r="I271" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -13790,7 +12866,7 @@
       <c r="L271" s="67" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="53" t="inlineStr">
+      <c r="A272" s="68" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -13825,11 +12901,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H272" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H272" s="65" t="inlineStr"/>
       <c r="I272" s="65" t="inlineStr">
         <is>
           <t>4</t>
@@ -13844,7 +12916,7 @@
       <c r="L272" s="67" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="53" t="inlineStr">
+      <c r="A273" s="68" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -13879,18 +12951,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H273" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H273" s="65" t="inlineStr"/>
       <c r="I273" s="65" t="inlineStr"/>
       <c r="J273" s="23" t="inlineStr"/>
       <c r="K273" s="23" t="n"/>
       <c r="L273" s="67" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="53" t="inlineStr">
+      <c r="A274" s="68" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -13918,7 +12986,7 @@
       <c r="L274" s="67" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="53" t="inlineStr">
+      <c r="A275" s="68" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -13953,18 +13021,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H275" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H275" s="65" t="inlineStr"/>
       <c r="I275" s="65" t="inlineStr"/>
       <c r="J275" s="23" t="inlineStr"/>
       <c r="K275" s="23" t="n"/>
       <c r="L275" s="67" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="53" t="inlineStr">
+      <c r="A276" s="68" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -13999,18 +13063,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H276" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H276" s="65" t="inlineStr"/>
       <c r="I276" s="65" t="inlineStr"/>
       <c r="J276" s="23" t="inlineStr"/>
       <c r="K276" s="23" t="n"/>
       <c r="L276" s="67" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="53" t="inlineStr">
+      <c r="A277" s="68" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -14045,18 +13105,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H277" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H277" s="65" t="inlineStr"/>
       <c r="I277" s="65" t="inlineStr"/>
       <c r="J277" s="23" t="inlineStr"/>
       <c r="K277" s="23" t="n"/>
       <c r="L277" s="67" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="53" t="inlineStr">
+      <c r="A278" s="68" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -14091,18 +13147,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H278" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H278" s="65" t="inlineStr"/>
       <c r="I278" s="65" t="inlineStr"/>
       <c r="J278" s="23" t="inlineStr"/>
       <c r="K278" s="23" t="n"/>
       <c r="L278" s="67" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="53" t="inlineStr">
+      <c r="A279" s="68" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -14148,7 +13200,7 @@
       <c r="L279" s="67" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="53" t="inlineStr">
+      <c r="A280" s="68" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -14183,18 +13235,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H280" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H280" s="65" t="inlineStr"/>
       <c r="I280" s="65" t="inlineStr"/>
       <c r="J280" s="23" t="inlineStr"/>
       <c r="K280" s="23" t="n"/>
       <c r="L280" s="67" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="53" t="inlineStr">
+      <c r="A281" s="68" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -14229,26 +13277,22 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H281" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H281" s="65" t="inlineStr"/>
       <c r="I281" s="65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J281" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K281" s="23" t="n"/>
       <c r="L281" s="67" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="53" t="inlineStr">
+      <c r="A282" s="68" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -14283,18 +13327,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H282" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H282" s="65" t="inlineStr"/>
       <c r="I282" s="65" t="inlineStr"/>
       <c r="J282" s="23" t="inlineStr"/>
       <c r="K282" s="23" t="n"/>
       <c r="L282" s="67" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="53" t="inlineStr">
+      <c r="A283" s="68" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -14329,18 +13369,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H283" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H283" s="65" t="inlineStr"/>
       <c r="I283" s="65" t="inlineStr"/>
       <c r="J283" s="23" t="inlineStr"/>
       <c r="K283" s="23" t="n"/>
       <c r="L283" s="67" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="53" t="inlineStr">
+      <c r="A284" s="68" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -14375,11 +13411,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H284" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H284" s="65" t="inlineStr"/>
       <c r="I284" s="65" t="inlineStr">
         <is>
           <t>5</t>
@@ -14394,7 +13426,7 @@
       <c r="L284" s="67" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="53" t="inlineStr">
+      <c r="A285" s="68" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -14429,18 +13461,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H285" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H285" s="65" t="inlineStr"/>
       <c r="I285" s="65" t="inlineStr"/>
       <c r="J285" s="23" t="inlineStr"/>
       <c r="K285" s="23" t="n"/>
       <c r="L285" s="67" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="53" t="inlineStr">
+      <c r="A286" s="68" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -14475,11 +13503,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H286" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H286" s="65" t="inlineStr"/>
       <c r="I286" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -14494,7 +13518,7 @@
       <c r="L286" s="67" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="53" t="inlineStr">
+      <c r="A287" s="68" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -14529,11 +13553,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H287" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H287" s="65" t="inlineStr"/>
       <c r="I287" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -14548,7 +13568,7 @@
       <c r="L287" s="67" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="53" t="inlineStr">
+      <c r="A288" s="68" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -14583,18 +13603,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H288" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H288" s="65" t="inlineStr"/>
       <c r="I288" s="65" t="inlineStr"/>
       <c r="J288" s="23" t="inlineStr"/>
       <c r="K288" s="23" t="n"/>
       <c r="L288" s="67" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="53" t="inlineStr">
+      <c r="A289" s="68" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -14629,18 +13645,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H289" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H289" s="65" t="inlineStr"/>
       <c r="I289" s="65" t="inlineStr"/>
       <c r="J289" s="23" t="inlineStr"/>
       <c r="K289" s="23" t="n"/>
       <c r="L289" s="67" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="53" t="inlineStr">
+      <c r="A290" s="68" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -14675,18 +13687,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H290" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H290" s="65" t="inlineStr"/>
       <c r="I290" s="65" t="inlineStr"/>
       <c r="J290" s="23" t="inlineStr"/>
       <c r="K290" s="23" t="n"/>
       <c r="L290" s="67" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="53" t="inlineStr">
+      <c r="A291" s="68" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -14721,18 +13729,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H291" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H291" s="65" t="inlineStr"/>
       <c r="I291" s="65" t="inlineStr"/>
       <c r="J291" s="23" t="inlineStr"/>
       <c r="K291" s="23" t="n"/>
       <c r="L291" s="67" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="53" t="inlineStr">
+      <c r="A292" s="68" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -14767,11 +13771,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H292" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H292" s="65" t="inlineStr"/>
       <c r="I292" s="65" t="inlineStr">
         <is>
           <t>6</t>
@@ -14786,7 +13786,7 @@
       <c r="L292" s="67" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="53" t="inlineStr">
+      <c r="A293" s="68" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -14821,11 +13821,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H293" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H293" s="65" t="inlineStr"/>
       <c r="I293" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -14840,7 +13836,7 @@
       <c r="L293" s="67" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="53" t="inlineStr">
+      <c r="A294" s="68" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -14875,11 +13871,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H294" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H294" s="65" t="inlineStr"/>
       <c r="I294" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -14894,7 +13886,7 @@
       <c r="L294" s="67" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="53" t="inlineStr">
+      <c r="A295" s="68" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -14929,11 +13921,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H295" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H295" s="65" t="inlineStr"/>
       <c r="I295" s="65" t="inlineStr">
         <is>
           <t>9</t>
@@ -14948,7 +13936,7 @@
       <c r="L295" s="67" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="53" t="inlineStr">
+      <c r="A296" s="68" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -14983,11 +13971,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H296" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H296" s="65" t="inlineStr"/>
       <c r="I296" s="65" t="inlineStr">
         <is>
           <t>2</t>
@@ -15002,7 +13986,7 @@
       <c r="L296" s="67" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="53" t="inlineStr">
+      <c r="A297" s="68" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -15037,11 +14021,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H297" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H297" s="65" t="inlineStr"/>
       <c r="I297" s="65" t="inlineStr">
         <is>
           <t>1</t>

--- a/EXCEL/3 - BLOCKING-REMARKS.xlsx
+++ b/EXCEL/3 - BLOCKING-REMARKS.xlsx
@@ -1302,38 +1302,26 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H3" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I3" s="65" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="J3" s="23" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
+      <c r="H3" s="65" t="inlineStr"/>
+      <c r="I3" s="65" t="inlineStr"/>
+      <c r="J3" s="23" t="inlineStr"/>
       <c r="K3" s="23" t="n"/>
       <c r="L3" s="67" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="53" t="inlineStr">
         <is>
-          <t>PS5-08-85</t>
+          <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
       </c>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C4" s="79" t="inlineStr">
-        <is>
-          <t>50%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C4" s="78" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -1356,28 +1344,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H4" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="65" t="inlineStr">
-        <is>
-          <t>-208</t>
-        </is>
-      </c>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t>-208</t>
-        </is>
-      </c>
+      <c r="H4" s="65" t="inlineStr"/>
+      <c r="I4" s="65" t="inlineStr"/>
+      <c r="J4" s="23" t="inlineStr"/>
       <c r="K4" s="23" t="n"/>
       <c r="L4" s="67" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-24 - FZ - Office and Facilities Building</t>
+          <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B5" s="23" t="inlineStr">
@@ -1410,28 +1386,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H5" s="65" t="inlineStr"/>
+      <c r="I5" s="65" t="inlineStr"/>
+      <c r="J5" s="23" t="inlineStr"/>
       <c r="K5" s="23" t="n"/>
       <c r="L5" s="67" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
+          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
@@ -1464,38 +1428,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H6" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I6" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H6" s="65" t="inlineStr"/>
+      <c r="I6" s="65" t="inlineStr"/>
+      <c r="J6" s="23" t="inlineStr"/>
       <c r="K6" s="23" t="n"/>
       <c r="L6" s="67" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="53" t="inlineStr">
         <is>
-          <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
+          <t>PS5-63-01 - Electrical Earthing</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C7" s="78" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="79" t="inlineStr">
+        <is>
+          <t>54%</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -1505,7 +1457,7 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -1518,28 +1470,20 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H7" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H7" s="65" t="inlineStr"/>
       <c r="I7" s="65" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr"/>
       <c r="K7" s="23" t="n"/>
       <c r="L7" s="67" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="53" t="inlineStr">
         <is>
-          <t>PS5-63-01 - Electrical Earthing</t>
+          <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
@@ -1549,7 +1493,7 @@
       </c>
       <c r="C8" s="79" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -1559,12 +1503,12 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G8" s="65" t="inlineStr">
@@ -1572,38 +1516,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H8" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="65" t="inlineStr">
-        <is>
-          <t>18 ITRs for lightning, 22 ITRs for grounding cannot be closed due to material issues.</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+      <c r="H8" s="65" t="inlineStr"/>
+      <c r="I8" s="65" t="inlineStr"/>
+      <c r="J8" s="23" t="inlineStr"/>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="67" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
+          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C9" s="79" t="inlineStr">
-        <is>
-          <t>51%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" s="78" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -1618,7 +1550,7 @@
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" s="65" t="inlineStr">
@@ -1626,38 +1558,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H9" s="65" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I9" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H9" s="65" t="inlineStr"/>
+      <c r="I9" s="65" t="inlineStr"/>
+      <c r="J9" s="23" t="inlineStr"/>
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="67" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="53" t="inlineStr">
         <is>
-          <t>PS5-09-01 - HVAC for Office and Facilities building</t>
+          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C10" s="78" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="79" t="inlineStr">
+        <is>
+          <t>69%</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1672,7 +1592,7 @@
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G10" s="65" t="inlineStr">
@@ -1680,38 +1600,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H10" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H10" s="65" t="inlineStr"/>
+      <c r="I10" s="65" t="inlineStr"/>
+      <c r="J10" s="23" t="inlineStr"/>
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="67" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="53" t="inlineStr">
         <is>
-          <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
+          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="79" t="inlineStr">
-        <is>
-          <t>69%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C11" s="78" t="inlineStr">
+        <is>
+          <t>3%</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -1726,7 +1634,7 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="65" t="inlineStr">
@@ -1734,38 +1642,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H11" s="65" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I11" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H11" s="65" t="inlineStr"/>
+      <c r="I11" s="65" t="inlineStr"/>
+      <c r="J11" s="23" t="inlineStr"/>
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="67" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="53" t="inlineStr">
         <is>
-          <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
+          <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" s="78" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -1788,38 +1684,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H12" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I12" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H12" s="65" t="inlineStr"/>
+      <c r="I12" s="65" t="inlineStr"/>
+      <c r="J12" s="23" t="inlineStr"/>
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="67" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="53" t="inlineStr">
         <is>
-          <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
+          <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C13" s="78" t="inlineStr">
-        <is>
-          <t>1%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C13" s="79" t="inlineStr">
+        <is>
+          <t>58%</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -1834,7 +1718,7 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G13" s="65" t="inlineStr">
@@ -1842,38 +1726,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H13" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" s="65" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+      <c r="H13" s="65" t="inlineStr"/>
+      <c r="I13" s="65" t="inlineStr"/>
+      <c r="J13" s="23" t="inlineStr"/>
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="67" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="53" t="inlineStr">
         <is>
-          <t>PS5-71-06 - Crude Fuel Separation Module</t>
+          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C14" s="79" t="inlineStr">
-        <is>
-          <t>58%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" s="78" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -1888,7 +1760,7 @@
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" s="65" t="inlineStr">
@@ -1896,28 +1768,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H14" s="65" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I14" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H14" s="65" t="inlineStr"/>
+      <c r="I14" s="65" t="inlineStr"/>
+      <c r="J14" s="23" t="inlineStr"/>
       <c r="K14" s="23" t="n"/>
       <c r="L14" s="67" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="53" t="inlineStr">
         <is>
-          <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
+          <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
@@ -1925,9 +1785,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C15" s="78" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="C15" s="79" t="inlineStr">
+        <is>
+          <t>87%</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -1950,38 +1810,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H15" s="65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I15" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J15" s="23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H15" s="65" t="inlineStr"/>
+      <c r="I15" s="65" t="inlineStr"/>
+      <c r="J15" s="23" t="inlineStr"/>
       <c r="K15" s="23" t="n"/>
       <c r="L15" s="67" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="53" t="inlineStr">
         <is>
-          <t>PS5-25-02 - Crude Oil Export Pump A</t>
+          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C16" s="79" t="inlineStr">
-        <is>
-          <t>87%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C16" s="78" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -2004,33 +1852,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H16" s="65" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I16" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H16" s="65" t="inlineStr"/>
+      <c r="I16" s="65" t="inlineStr"/>
+      <c r="J16" s="23" t="inlineStr"/>
       <c r="K16" s="23" t="n"/>
       <c r="L16" s="67" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="53" t="inlineStr">
         <is>
-          <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
+          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C17" s="78" t="inlineStr">
@@ -2058,33 +1894,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H17" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I17" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H17" s="65" t="inlineStr"/>
+      <c r="I17" s="65" t="inlineStr"/>
+      <c r="J17" s="23" t="inlineStr"/>
       <c r="K17" s="23" t="n"/>
       <c r="L17" s="67" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="53" t="inlineStr">
         <is>
-          <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
+          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" s="78" t="inlineStr">
@@ -2099,7 +1923,7 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -2112,38 +1936,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H18" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I18" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J18" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H18" s="65" t="inlineStr"/>
+      <c r="I18" s="65" t="inlineStr"/>
+      <c r="J18" s="23" t="inlineStr"/>
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="67" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
+          <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C19" s="78" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C19" s="80" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -2153,12 +1965,12 @@
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G19" s="65" t="inlineStr">
@@ -2166,38 +1978,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H19" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="65" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J19" s="23" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="H19" s="65" t="inlineStr"/>
+      <c r="I19" s="65" t="inlineStr"/>
+      <c r="J19" s="23" t="inlineStr"/>
       <c r="K19" s="23" t="n"/>
       <c r="L19" s="67" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="53" t="inlineStr">
         <is>
-          <t>PS5-01-11 - Inergen for Power Gen Building</t>
+          <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C20" s="80" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C20" s="78" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -2212,7 +2012,7 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" s="65" t="inlineStr">
@@ -2220,28 +2020,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H20" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H20" s="65" t="inlineStr"/>
+      <c r="I20" s="65" t="inlineStr"/>
+      <c r="J20" s="23" t="inlineStr"/>
       <c r="K20" s="23" t="n"/>
       <c r="L20" s="67" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-22 - FZ-G1 - Guard House</t>
+          <t>PS5-82-05 - Office and Facilities building</t>
         </is>
       </c>
       <c r="B21" s="23" t="inlineStr">
@@ -2251,7 +2039,7 @@
       </c>
       <c r="C21" s="78" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -2274,28 +2062,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H21" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I21" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J21" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H21" s="65" t="inlineStr"/>
+      <c r="I21" s="65" t="inlineStr"/>
+      <c r="J21" s="23" t="inlineStr"/>
       <c r="K21" s="23" t="n"/>
       <c r="L21" s="67" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="53" t="inlineStr">
         <is>
-          <t>PS5-82-05 - Office and Facilities building</t>
+          <t>PS5-82-06 - Guard House Building</t>
         </is>
       </c>
       <c r="B22" s="23" t="inlineStr">
@@ -2328,28 +2104,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H22" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I22" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H22" s="65" t="inlineStr"/>
+      <c r="I22" s="65" t="inlineStr"/>
+      <c r="J22" s="23" t="inlineStr"/>
       <c r="K22" s="23" t="n"/>
       <c r="L22" s="67" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>PS5-82-06 - Guard House Building</t>
+          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
       </c>
       <c r="B23" s="23" t="inlineStr">
@@ -2359,7 +2123,7 @@
       </c>
       <c r="C23" s="78" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -2382,38 +2146,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H23" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I23" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J23" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H23" s="65" t="inlineStr"/>
+      <c r="I23" s="65" t="inlineStr"/>
+      <c r="J23" s="23" t="inlineStr"/>
       <c r="K23" s="23" t="n"/>
       <c r="L23" s="67" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
         <is>
-          <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
+          <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C24" s="78" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C24" s="79" t="inlineStr">
+        <is>
+          <t>61%</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -2436,38 +2188,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H24" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I24" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J24" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H24" s="65" t="inlineStr"/>
+      <c r="I24" s="65" t="inlineStr"/>
+      <c r="J24" s="23" t="inlineStr"/>
       <c r="K24" s="23" t="n"/>
       <c r="L24" s="67" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>PS5-02-01 - Miscellaneous Safety equipment</t>
+          <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C25" s="79" t="inlineStr">
-        <is>
-          <t>61%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="78" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -2482,7 +2222,7 @@
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G25" s="65" t="inlineStr">
@@ -2490,33 +2230,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H25" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I25" s="65" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J25" s="23" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="H25" s="65" t="inlineStr"/>
+      <c r="I25" s="65" t="inlineStr"/>
+      <c r="J25" s="23" t="inlineStr"/>
       <c r="K25" s="23" t="n"/>
       <c r="L25" s="67" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
+          <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C26" s="78" t="inlineStr">
@@ -2544,33 +2272,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H26" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I26" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H26" s="65" t="inlineStr"/>
+      <c r="I26" s="65" t="inlineStr"/>
+      <c r="J26" s="23" t="inlineStr"/>
       <c r="K26" s="23" t="n"/>
       <c r="L26" s="67" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
+          <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" s="78" t="inlineStr">
@@ -2590,7 +2306,7 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G27" s="65" t="inlineStr">
@@ -2598,28 +2314,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H27" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I27" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H27" s="65" t="inlineStr"/>
+      <c r="I27" s="65" t="inlineStr"/>
+      <c r="J27" s="23" t="inlineStr"/>
       <c r="K27" s="23" t="n"/>
       <c r="L27" s="67" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
+          <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
       </c>
       <c r="B28" s="23" t="inlineStr">
@@ -2652,33 +2356,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H28" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I28" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H28" s="65" t="inlineStr"/>
+      <c r="I28" s="65" t="inlineStr"/>
+      <c r="J28" s="23" t="inlineStr"/>
       <c r="K28" s="23" t="n"/>
       <c r="L28" s="67" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
+          <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C29" s="78" t="inlineStr">
@@ -2698,7 +2390,7 @@
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G29" s="65" t="inlineStr">
@@ -2706,33 +2398,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H29" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I29" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H29" s="65" t="inlineStr"/>
+      <c r="I29" s="65" t="inlineStr"/>
+      <c r="J29" s="23" t="inlineStr"/>
       <c r="K29" s="23" t="n"/>
       <c r="L29" s="67" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
+          <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" s="78" t="inlineStr">
@@ -2752,7 +2432,7 @@
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G30" s="65" t="inlineStr">
@@ -2760,33 +2440,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H30" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I30" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H30" s="65" t="inlineStr"/>
+      <c r="I30" s="65" t="inlineStr"/>
+      <c r="J30" s="23" t="inlineStr"/>
       <c r="K30" s="23" t="n"/>
       <c r="L30" s="67" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
+          <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C31" s="78" t="inlineStr">
@@ -2814,38 +2482,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H31" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I31" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H31" s="65" t="inlineStr"/>
+      <c r="I31" s="65" t="inlineStr"/>
+      <c r="J31" s="23" t="inlineStr"/>
       <c r="K31" s="23" t="n"/>
       <c r="L31" s="67" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="53" t="inlineStr">
         <is>
-          <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
+          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C32" s="78" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="80" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -2860,7 +2516,7 @@
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" s="65" t="inlineStr">
@@ -2868,28 +2524,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H32" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I32" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H32" s="65" t="inlineStr"/>
+      <c r="I32" s="65" t="inlineStr"/>
+      <c r="J32" s="23" t="inlineStr"/>
       <c r="K32" s="23" t="n"/>
       <c r="L32" s="67" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
+          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
       </c>
       <c r="B33" s="23" t="inlineStr">
@@ -2897,9 +2541,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C33" s="80" t="inlineStr">
-        <is>
-          <t>90%</t>
+      <c r="C33" s="79" t="inlineStr">
+        <is>
+          <t>78%</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -2914,7 +2558,7 @@
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G33" s="65" t="inlineStr">
@@ -2922,38 +2566,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H33" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I33" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H33" s="65" t="inlineStr"/>
+      <c r="I33" s="65" t="inlineStr"/>
+      <c r="J33" s="23" t="inlineStr"/>
       <c r="K33" s="23" t="n"/>
       <c r="L33" s="67" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="53" t="inlineStr">
         <is>
-          <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
+          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C34" s="79" t="inlineStr">
-        <is>
-          <t>78%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C34" s="78" t="inlineStr">
+        <is>
+          <t>11%</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -2968,7 +2600,7 @@
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G34" s="65" t="inlineStr">
@@ -2976,38 +2608,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H34" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I34" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="H34" s="65" t="inlineStr"/>
+      <c r="I34" s="65" t="inlineStr"/>
+      <c r="J34" s="23" t="inlineStr"/>
       <c r="K34" s="23" t="n"/>
       <c r="L34" s="67" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>PS5-84-02 - Workshop &amp; Warehouse</t>
+          <t>PS5-08-03 - Telephone</t>
         </is>
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C35" s="78" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -3030,38 +2650,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H35" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I35" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H35" s="65" t="inlineStr"/>
+      <c r="I35" s="65" t="inlineStr"/>
+      <c r="J35" s="23" t="inlineStr"/>
       <c r="K35" s="23" t="n"/>
       <c r="L35" s="67" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="53" t="inlineStr">
         <is>
-          <t>PS5-08-03 - Telephone</t>
+          <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C36" s="78" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
@@ -3084,28 +2692,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H36" s="65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I36" s="65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="H36" s="65" t="inlineStr"/>
+      <c r="I36" s="65" t="inlineStr"/>
+      <c r="J36" s="23" t="inlineStr"/>
       <c r="K36" s="23" t="n"/>
       <c r="L36" s="67" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>PS5-04-02 - Office Building SIS/FGS System</t>
+          <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
       </c>
       <c r="B37" s="23" t="inlineStr">
@@ -3138,38 +2734,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H37" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I37" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H37" s="65" t="inlineStr"/>
+      <c r="I37" s="65" t="inlineStr"/>
+      <c r="J37" s="23" t="inlineStr"/>
       <c r="K37" s="23" t="n"/>
       <c r="L37" s="67" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="53" t="inlineStr">
         <is>
-          <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
+          <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C38" s="78" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C38" s="80" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -3192,28 +2776,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H38" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I38" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H38" s="65" t="inlineStr"/>
+      <c r="I38" s="65" t="inlineStr"/>
+      <c r="J38" s="23" t="inlineStr"/>
       <c r="K38" s="23" t="n"/>
       <c r="L38" s="67" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>PS5-25-03 - Crude Oil Export Pump B</t>
+          <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
       </c>
       <c r="B39" s="23" t="inlineStr">
@@ -3246,53 +2818,41 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H39" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I39" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H39" s="65" t="inlineStr"/>
+      <c r="I39" s="65" t="inlineStr"/>
+      <c r="J39" s="23" t="inlineStr"/>
       <c r="K39" s="23" t="n"/>
       <c r="L39" s="67" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="53" t="inlineStr">
         <is>
-          <t>PS5-25-04 - Crude Oil Export Pump C</t>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="80" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C40" s="80" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G40" s="65" t="inlineStr">
@@ -3300,28 +2860,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H40" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I40" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H40" s="65" t="inlineStr"/>
+      <c r="I40" s="65" t="inlineStr"/>
+      <c r="J40" s="23" t="inlineStr"/>
       <c r="K40" s="23" t="n"/>
       <c r="L40" s="67" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
       </c>
       <c r="B41" s="23" t="inlineStr">
@@ -3329,9 +2877,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C41" s="80" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="C41" s="79" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -3341,12 +2889,12 @@
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G41" s="65" t="inlineStr">
@@ -3359,33 +2907,25 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I41" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I41" s="65" t="inlineStr"/>
+      <c r="J41" s="23" t="inlineStr"/>
       <c r="K41" s="23" t="n"/>
       <c r="L41" s="67" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="53" t="inlineStr">
         <is>
-          <t>PS5-60-22 - Power Gen Master UCP</t>
+          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C42" s="79" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C42" s="78" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
@@ -3400,7 +2940,7 @@
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G42" s="65" t="inlineStr">
@@ -3408,28 +2948,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H42" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I42" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="H42" s="65" t="inlineStr"/>
+      <c r="I42" s="65" t="inlineStr"/>
+      <c r="J42" s="23" t="inlineStr"/>
       <c r="K42" s="23" t="n"/>
       <c r="L42" s="67" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
+          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
       </c>
       <c r="B43" s="23" t="inlineStr">
@@ -3462,38 +2990,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H43" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I43" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H43" s="65" t="inlineStr"/>
+      <c r="I43" s="65" t="inlineStr"/>
+      <c r="J43" s="23" t="inlineStr"/>
       <c r="K43" s="23" t="n"/>
       <c r="L43" s="67" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="53" t="inlineStr">
         <is>
-          <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
+          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C44" s="78" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C44" s="80" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
@@ -3521,23 +3037,15 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I44" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I44" s="65" t="inlineStr"/>
+      <c r="J44" s="23" t="inlineStr"/>
       <c r="K44" s="23" t="n"/>
       <c r="L44" s="67" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
+          <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
       </c>
       <c r="B45" s="23" t="inlineStr">
@@ -3545,9 +3053,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C45" s="80" t="inlineStr">
-        <is>
-          <t>93%</t>
+      <c r="C45" s="79" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
@@ -3570,38 +3078,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H45" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I45" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H45" s="65" t="inlineStr"/>
+      <c r="I45" s="65" t="inlineStr"/>
+      <c r="J45" s="23" t="inlineStr"/>
       <c r="K45" s="23" t="n"/>
       <c r="L45" s="67" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="53" t="inlineStr">
         <is>
-          <t>PS5-71-04 - CFO Storage Tank</t>
+          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C46" s="79" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
@@ -3616,7 +3112,7 @@
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G46" s="65" t="inlineStr">
@@ -3624,38 +3120,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H46" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I46" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J46" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="H46" s="65" t="inlineStr"/>
+      <c r="I46" s="65" t="inlineStr"/>
+      <c r="J46" s="23" t="inlineStr"/>
       <c r="K46" s="23" t="n"/>
       <c r="L46" s="67" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
+          <t>PS5-71-12 - CFO Service Tank</t>
         </is>
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C47" s="79" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -3670,7 +3154,7 @@
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G47" s="65" t="inlineStr">
@@ -3678,38 +3162,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H47" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I47" s="65" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J47" s="23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="H47" s="65" t="inlineStr"/>
+      <c r="I47" s="65" t="inlineStr"/>
+      <c r="J47" s="23" t="inlineStr"/>
       <c r="K47" s="23" t="n"/>
       <c r="L47" s="67" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="53" t="inlineStr">
         <is>
-          <t>PS5-71-12 - CFO Service Tank</t>
+          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C48" s="79" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
@@ -3724,7 +3196,7 @@
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G48" s="65" t="inlineStr">
@@ -3732,28 +3204,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H48" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I48" s="65" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="H48" s="65" t="inlineStr"/>
+      <c r="I48" s="65" t="inlineStr"/>
+      <c r="J48" s="23" t="inlineStr"/>
       <c r="K48" s="23" t="n"/>
       <c r="L48" s="67" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>PS5-71-20 - Diesel Fuel Day Tank</t>
+          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="B49" s="23" t="inlineStr">
@@ -3761,9 +3221,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C49" s="79" t="inlineStr">
-        <is>
-          <t>89%</t>
+      <c r="C49" s="80" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
@@ -3773,12 +3233,12 @@
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G49" s="65" t="inlineStr">
@@ -3786,38 +3246,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H49" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I49" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H49" s="65" t="inlineStr"/>
+      <c r="I49" s="65" t="inlineStr"/>
+      <c r="J49" s="23" t="inlineStr"/>
       <c r="K49" s="23" t="n"/>
       <c r="L49" s="67" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="53" t="inlineStr">
         <is>
-          <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C50" s="80" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C50" s="79" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
@@ -3827,12 +3275,12 @@
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G50" s="65" t="inlineStr">
@@ -3840,38 +3288,26 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H50" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I50" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J50" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H50" s="65" t="inlineStr"/>
+      <c r="I50" s="65" t="inlineStr"/>
+      <c r="J50" s="23" t="inlineStr"/>
       <c r="K50" s="23" t="n"/>
       <c r="L50" s="67" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>PS5-71-13 - CFO Service Pump A/B</t>
+          <t>PS5-08-85</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C51" s="79" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
@@ -3894,21 +3330,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H51" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I51" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H51" s="65" t="inlineStr"/>
+      <c r="I51" s="65" t="inlineStr"/>
+      <c r="J51" s="23" t="inlineStr"/>
       <c r="K51" s="23" t="n"/>
       <c r="L51" s="67" t="inlineStr"/>
     </row>
@@ -3948,21 +3372,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H52" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I52" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J52" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H52" s="65" t="inlineStr"/>
+      <c r="I52" s="65" t="inlineStr"/>
+      <c r="J52" s="23" t="inlineStr"/>
       <c r="K52" s="23" t="n"/>
       <c r="L52" s="67" t="inlineStr"/>
     </row>
@@ -4002,21 +3414,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H53" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I53" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J53" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H53" s="65" t="inlineStr"/>
+      <c r="I53" s="65" t="inlineStr"/>
+      <c r="J53" s="23" t="inlineStr"/>
       <c r="K53" s="23" t="n"/>
       <c r="L53" s="67" t="inlineStr"/>
     </row>
@@ -4056,21 +3456,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H54" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I54" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J54" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H54" s="65" t="inlineStr"/>
+      <c r="I54" s="65" t="inlineStr"/>
+      <c r="J54" s="23" t="inlineStr"/>
       <c r="K54" s="23" t="n"/>
       <c r="L54" s="67" t="inlineStr"/>
     </row>
@@ -4110,21 +3498,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H55" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I55" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J55" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H55" s="65" t="inlineStr"/>
+      <c r="I55" s="65" t="inlineStr"/>
+      <c r="J55" s="23" t="inlineStr"/>
       <c r="K55" s="23" t="n"/>
       <c r="L55" s="67" t="inlineStr"/>
     </row>
@@ -4164,21 +3540,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H56" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I56" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J56" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H56" s="65" t="inlineStr"/>
+      <c r="I56" s="65" t="inlineStr"/>
+      <c r="J56" s="23" t="inlineStr"/>
       <c r="K56" s="23" t="n"/>
       <c r="L56" s="67" t="inlineStr"/>
     </row>
@@ -4218,21 +3582,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H57" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I57" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J57" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H57" s="65" t="inlineStr"/>
+      <c r="I57" s="65" t="inlineStr"/>
+      <c r="J57" s="23" t="inlineStr"/>
       <c r="K57" s="23" t="n"/>
       <c r="L57" s="67" t="inlineStr"/>
     </row>
@@ -4272,21 +3624,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H58" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I58" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J58" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H58" s="65" t="inlineStr"/>
+      <c r="I58" s="65" t="inlineStr"/>
+      <c r="J58" s="23" t="inlineStr"/>
       <c r="K58" s="23" t="n"/>
       <c r="L58" s="67" t="inlineStr"/>
     </row>
@@ -4326,21 +3666,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H59" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I59" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J59" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H59" s="65" t="inlineStr"/>
+      <c r="I59" s="65" t="inlineStr"/>
+      <c r="J59" s="23" t="inlineStr"/>
       <c r="K59" s="23" t="n"/>
       <c r="L59" s="67" t="inlineStr"/>
     </row>
@@ -4380,21 +3708,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H60" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I60" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J60" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H60" s="65" t="inlineStr"/>
+      <c r="I60" s="65" t="inlineStr"/>
+      <c r="J60" s="23" t="inlineStr"/>
       <c r="K60" s="23" t="n"/>
       <c r="L60" s="67" t="inlineStr"/>
     </row>
@@ -4434,21 +3750,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H61" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I61" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J61" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H61" s="65" t="inlineStr"/>
+      <c r="I61" s="65" t="inlineStr"/>
+      <c r="J61" s="23" t="inlineStr"/>
       <c r="K61" s="23" t="n"/>
       <c r="L61" s="67" t="inlineStr"/>
     </row>
@@ -4488,21 +3792,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H62" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I62" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J62" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H62" s="65" t="inlineStr"/>
+      <c r="I62" s="65" t="inlineStr"/>
+      <c r="J62" s="23" t="inlineStr"/>
       <c r="K62" s="23" t="n"/>
       <c r="L62" s="67" t="inlineStr"/>
     </row>
@@ -4542,21 +3834,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H63" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I63" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J63" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H63" s="65" t="inlineStr"/>
+      <c r="I63" s="65" t="inlineStr"/>
+      <c r="J63" s="23" t="inlineStr"/>
       <c r="K63" s="23" t="n"/>
       <c r="L63" s="67" t="inlineStr"/>
     </row>
@@ -4596,21 +3876,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H64" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I64" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H64" s="65" t="inlineStr"/>
+      <c r="I64" s="65" t="inlineStr"/>
+      <c r="J64" s="23" t="inlineStr"/>
       <c r="K64" s="23" t="n"/>
       <c r="L64" s="67" t="inlineStr"/>
     </row>
@@ -4650,21 +3918,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H65" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I65" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H65" s="65" t="inlineStr"/>
+      <c r="I65" s="65" t="inlineStr"/>
+      <c r="J65" s="23" t="inlineStr"/>
       <c r="K65" s="23" t="n"/>
       <c r="L65" s="67" t="inlineStr"/>
     </row>
@@ -4704,21 +3960,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H66" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I66" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J66" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H66" s="65" t="inlineStr"/>
+      <c r="I66" s="65" t="inlineStr"/>
+      <c r="J66" s="23" t="inlineStr"/>
       <c r="K66" s="23" t="n"/>
       <c r="L66" s="67" t="inlineStr"/>
     </row>
@@ -4758,21 +4002,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H67" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I67" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H67" s="65" t="inlineStr"/>
+      <c r="I67" s="65" t="inlineStr"/>
+      <c r="J67" s="23" t="inlineStr"/>
       <c r="K67" s="23" t="n"/>
       <c r="L67" s="67" t="inlineStr"/>
     </row>
@@ -4812,21 +4044,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H68" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I68" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J68" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H68" s="65" t="inlineStr"/>
+      <c r="I68" s="65" t="inlineStr"/>
+      <c r="J68" s="23" t="inlineStr"/>
       <c r="K68" s="23" t="n"/>
       <c r="L68" s="67" t="inlineStr"/>
     </row>
@@ -4866,21 +4086,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H69" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I69" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J69" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H69" s="65" t="inlineStr"/>
+      <c r="I69" s="65" t="inlineStr"/>
+      <c r="J69" s="23" t="inlineStr"/>
       <c r="K69" s="23" t="n"/>
       <c r="L69" s="67" t="inlineStr"/>
     </row>
@@ -4920,21 +4128,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H70" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I70" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J70" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H70" s="65" t="inlineStr"/>
+      <c r="I70" s="65" t="inlineStr"/>
+      <c r="J70" s="23" t="inlineStr"/>
       <c r="K70" s="23" t="n"/>
       <c r="L70" s="67" t="inlineStr"/>
     </row>
@@ -4974,21 +4170,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H71" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I71" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J71" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H71" s="65" t="inlineStr"/>
+      <c r="I71" s="65" t="inlineStr"/>
+      <c r="J71" s="23" t="inlineStr"/>
       <c r="K71" s="23" t="n"/>
       <c r="L71" s="67" t="inlineStr"/>
     </row>
@@ -5028,21 +4212,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H72" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I72" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J72" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H72" s="65" t="inlineStr"/>
+      <c r="I72" s="65" t="inlineStr"/>
+      <c r="J72" s="23" t="inlineStr"/>
       <c r="K72" s="23" t="n"/>
       <c r="L72" s="67" t="inlineStr"/>
     </row>
@@ -5082,21 +4254,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H73" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I73" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J73" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H73" s="65" t="inlineStr"/>
+      <c r="I73" s="65" t="inlineStr"/>
+      <c r="J73" s="23" t="inlineStr"/>
       <c r="K73" s="23" t="n"/>
       <c r="L73" s="67" t="inlineStr"/>
     </row>
@@ -5136,21 +4296,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H74" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I74" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J74" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H74" s="65" t="inlineStr"/>
+      <c r="I74" s="65" t="inlineStr"/>
+      <c r="J74" s="23" t="inlineStr"/>
       <c r="K74" s="23" t="n"/>
       <c r="L74" s="67" t="inlineStr"/>
     </row>
@@ -5190,21 +4338,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H75" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I75" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J75" s="66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H75" s="65" t="inlineStr"/>
+      <c r="I75" s="65" t="inlineStr"/>
+      <c r="J75" s="66" t="inlineStr"/>
       <c r="K75" s="66" t="n"/>
       <c r="L75" s="67" t="inlineStr"/>
     </row>
@@ -5244,21 +4380,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H76" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I76" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J76" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H76" s="65" t="inlineStr"/>
+      <c r="I76" s="65" t="inlineStr"/>
+      <c r="J76" s="23" t="inlineStr"/>
       <c r="K76" s="23" t="n"/>
       <c r="L76" s="67" t="inlineStr"/>
     </row>
@@ -5298,21 +4422,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H77" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I77" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J77" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H77" s="65" t="inlineStr"/>
+      <c r="I77" s="65" t="inlineStr"/>
+      <c r="J77" s="23" t="inlineStr"/>
       <c r="K77" s="23" t="n"/>
       <c r="L77" s="67" t="inlineStr"/>
     </row>
@@ -5352,21 +4464,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H78" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I78" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J78" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H78" s="65" t="inlineStr"/>
+      <c r="I78" s="65" t="inlineStr"/>
+      <c r="J78" s="23" t="inlineStr"/>
       <c r="K78" s="23" t="n"/>
       <c r="L78" s="67" t="inlineStr"/>
     </row>
@@ -5406,21 +4506,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H79" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I79" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J79" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H79" s="65" t="inlineStr"/>
+      <c r="I79" s="65" t="inlineStr"/>
+      <c r="J79" s="23" t="inlineStr"/>
       <c r="K79" s="23" t="n"/>
       <c r="L79" s="67" t="inlineStr"/>
     </row>
@@ -5460,21 +4548,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H80" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I80" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J80" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H80" s="65" t="inlineStr"/>
+      <c r="I80" s="65" t="inlineStr"/>
+      <c r="J80" s="23" t="inlineStr"/>
       <c r="K80" s="23" t="n"/>
       <c r="L80" s="67" t="inlineStr"/>
     </row>
@@ -5514,21 +4590,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H81" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I81" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J81" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H81" s="65" t="inlineStr"/>
+      <c r="I81" s="65" t="inlineStr"/>
+      <c r="J81" s="23" t="inlineStr"/>
       <c r="K81" s="23" t="n"/>
       <c r="L81" s="67" t="inlineStr"/>
     </row>
@@ -5568,21 +4632,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H82" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I82" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J82" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H82" s="65" t="inlineStr"/>
+      <c r="I82" s="65" t="inlineStr"/>
+      <c r="J82" s="23" t="inlineStr"/>
       <c r="K82" s="23" t="n"/>
       <c r="L82" s="67" t="inlineStr"/>
     </row>
@@ -5622,21 +4674,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H83" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I83" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J83" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H83" s="65" t="inlineStr"/>
+      <c r="I83" s="65" t="inlineStr"/>
+      <c r="J83" s="23" t="inlineStr"/>
       <c r="K83" s="23" t="n"/>
       <c r="L83" s="67" t="inlineStr"/>
     </row>
@@ -5676,21 +4716,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H84" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I84" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J84" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H84" s="65" t="inlineStr"/>
+      <c r="I84" s="65" t="inlineStr"/>
+      <c r="J84" s="23" t="inlineStr"/>
       <c r="K84" s="23" t="n"/>
       <c r="L84" s="67" t="inlineStr"/>
     </row>
@@ -5730,21 +4758,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H85" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I85" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J85" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H85" s="65" t="inlineStr"/>
+      <c r="I85" s="65" t="inlineStr"/>
+      <c r="J85" s="23" t="inlineStr"/>
       <c r="K85" s="23" t="n"/>
       <c r="L85" s="67" t="inlineStr"/>
     </row>
@@ -5784,21 +4800,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H86" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I86" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J86" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H86" s="65" t="inlineStr"/>
+      <c r="I86" s="65" t="inlineStr"/>
+      <c r="J86" s="23" t="inlineStr"/>
       <c r="K86" s="23" t="n"/>
       <c r="L86" s="67" t="inlineStr"/>
     </row>
@@ -5838,21 +4842,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H87" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I87" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J87" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H87" s="65" t="inlineStr"/>
+      <c r="I87" s="65" t="inlineStr"/>
+      <c r="J87" s="23" t="inlineStr"/>
       <c r="K87" s="23" t="n"/>
       <c r="L87" s="67" t="inlineStr"/>
     </row>
@@ -5892,21 +4884,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H88" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I88" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J88" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H88" s="65" t="inlineStr"/>
+      <c r="I88" s="65" t="inlineStr"/>
+      <c r="J88" s="23" t="inlineStr"/>
       <c r="K88" s="23" t="n"/>
       <c r="L88" s="67" t="inlineStr"/>
     </row>
@@ -5946,21 +4926,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H89" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I89" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J89" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H89" s="65" t="inlineStr"/>
+      <c r="I89" s="65" t="inlineStr"/>
+      <c r="J89" s="23" t="inlineStr"/>
       <c r="K89" s="23" t="n"/>
       <c r="L89" s="67" t="inlineStr"/>
     </row>
@@ -6005,16 +4973,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I90" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J90" s="23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I90" s="65" t="inlineStr"/>
+      <c r="J90" s="23" t="inlineStr"/>
       <c r="K90" s="23" t="n"/>
       <c r="L90" s="67" t="inlineStr"/>
     </row>
@@ -6054,21 +5014,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H91" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I91" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J91" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H91" s="65" t="inlineStr"/>
+      <c r="I91" s="65" t="inlineStr"/>
+      <c r="J91" s="23" t="inlineStr"/>
       <c r="K91" s="23" t="n"/>
       <c r="L91" s="67" t="inlineStr"/>
     </row>
@@ -6108,21 +5056,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H92" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I92" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J92" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H92" s="65" t="inlineStr"/>
+      <c r="I92" s="65" t="inlineStr"/>
+      <c r="J92" s="23" t="inlineStr"/>
       <c r="K92" s="23" t="n"/>
       <c r="L92" s="67" t="inlineStr"/>
     </row>
@@ -6162,21 +5098,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H93" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I93" s="65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J93" s="23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="H93" s="65" t="inlineStr"/>
+      <c r="I93" s="65" t="inlineStr"/>
+      <c r="J93" s="23" t="inlineStr"/>
       <c r="K93" s="23" t="n"/>
       <c r="L93" s="67" t="inlineStr"/>
     </row>
@@ -6216,21 +5140,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H94" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I94" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J94" s="23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="H94" s="65" t="inlineStr"/>
+      <c r="I94" s="65" t="inlineStr"/>
+      <c r="J94" s="23" t="inlineStr"/>
       <c r="K94" s="23" t="n"/>
       <c r="L94" s="67" t="inlineStr"/>
     </row>
@@ -6270,21 +5182,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H95" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I95" s="65" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J95" s="23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="H95" s="65" t="inlineStr"/>
+      <c r="I95" s="65" t="inlineStr"/>
+      <c r="J95" s="23" t="inlineStr"/>
       <c r="K95" s="23" t="n"/>
       <c r="L95" s="67" t="inlineStr"/>
     </row>
@@ -6324,21 +5224,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H96" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I96" s="65" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J96" s="23" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+      <c r="H96" s="65" t="inlineStr"/>
+      <c r="I96" s="65" t="inlineStr"/>
+      <c r="J96" s="23" t="inlineStr"/>
       <c r="K96" s="23" t="n"/>
       <c r="L96" s="67" t="inlineStr"/>
     </row>
@@ -6378,21 +5266,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H97" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I97" s="65" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J97" s="23" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+      <c r="H97" s="65" t="inlineStr"/>
+      <c r="I97" s="65" t="inlineStr"/>
+      <c r="J97" s="23" t="inlineStr"/>
       <c r="K97" s="23" t="n"/>
       <c r="L97" s="67" t="inlineStr"/>
     </row>
@@ -6432,21 +5308,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H98" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I98" s="65" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J98" s="23" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+      <c r="H98" s="65" t="inlineStr"/>
+      <c r="I98" s="65" t="inlineStr"/>
+      <c r="J98" s="23" t="inlineStr"/>
       <c r="K98" s="23" t="n"/>
       <c r="L98" s="67" t="inlineStr"/>
     </row>
@@ -6486,21 +5350,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H99" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I99" s="65" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J99" s="23" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="H99" s="65" t="inlineStr"/>
+      <c r="I99" s="65" t="inlineStr"/>
+      <c r="J99" s="23" t="inlineStr"/>
       <c r="K99" s="23" t="n"/>
       <c r="L99" s="67" t="inlineStr"/>
     </row>
@@ -6540,21 +5392,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H100" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I100" s="65" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J100" s="23" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="H100" s="65" t="inlineStr"/>
+      <c r="I100" s="65" t="inlineStr"/>
+      <c r="J100" s="23" t="inlineStr"/>
       <c r="K100" s="23" t="n"/>
       <c r="L100" s="67" t="inlineStr"/>
     </row>
@@ -6594,21 +5434,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H101" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I101" s="65" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J101" s="23" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="H101" s="65" t="inlineStr"/>
+      <c r="I101" s="65" t="inlineStr"/>
+      <c r="J101" s="23" t="inlineStr"/>
       <c r="K101" s="23" t="n"/>
       <c r="L101" s="67" t="inlineStr"/>
     </row>
@@ -6648,21 +5476,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H102" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I102" s="65" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J102" s="23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="H102" s="65" t="inlineStr"/>
+      <c r="I102" s="65" t="inlineStr"/>
+      <c r="J102" s="23" t="inlineStr"/>
       <c r="K102" s="23" t="n"/>
       <c r="L102" s="67" t="inlineStr"/>
     </row>
@@ -6702,21 +5518,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H103" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I103" s="65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J103" s="23" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="H103" s="65" t="inlineStr"/>
+      <c r="I103" s="65" t="inlineStr"/>
+      <c r="J103" s="23" t="inlineStr"/>
       <c r="K103" s="23" t="n"/>
       <c r="L103" s="67" t="inlineStr"/>
     </row>
@@ -6756,21 +5560,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H104" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I104" s="65" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J104" s="23" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+      <c r="H104" s="65" t="inlineStr"/>
+      <c r="I104" s="65" t="inlineStr"/>
+      <c r="J104" s="23" t="inlineStr"/>
       <c r="K104" s="23" t="n"/>
       <c r="L104" s="67" t="inlineStr"/>
     </row>
@@ -6810,21 +5602,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H105" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I105" s="65" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J105" s="23" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+      <c r="H105" s="65" t="inlineStr"/>
+      <c r="I105" s="65" t="inlineStr"/>
+      <c r="J105" s="23" t="inlineStr"/>
       <c r="K105" s="23" t="n"/>
       <c r="L105" s="67" t="inlineStr"/>
     </row>
@@ -6864,21 +5644,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H106" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H106" s="65" t="inlineStr"/>
       <c r="I106" s="65" t="inlineStr">
         <is>
           <t>EACOP(MR.BENHER TBC)-EXPECTED 19-08-2026</t>
         </is>
       </c>
-      <c r="J106" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="J106" s="23" t="inlineStr"/>
       <c r="K106" s="23" t="n"/>
       <c r="L106" s="67" t="inlineStr"/>
     </row>
@@ -6918,21 +5690,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H107" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I107" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J107" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H107" s="65" t="inlineStr"/>
+      <c r="I107" s="65" t="inlineStr"/>
+      <c r="J107" s="23" t="inlineStr"/>
       <c r="K107" s="23" t="n"/>
       <c r="L107" s="67" t="inlineStr"/>
     </row>
@@ -6972,21 +5732,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H108" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I108" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J108" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H108" s="65" t="inlineStr"/>
+      <c r="I108" s="65" t="inlineStr"/>
+      <c r="J108" s="23" t="inlineStr"/>
       <c r="K108" s="23" t="n"/>
       <c r="L108" s="67" t="inlineStr"/>
     </row>
@@ -7026,21 +5774,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H109" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I109" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J109" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H109" s="65" t="inlineStr"/>
+      <c r="I109" s="65" t="inlineStr"/>
+      <c r="J109" s="23" t="inlineStr"/>
       <c r="K109" s="23" t="n"/>
       <c r="L109" s="67" t="inlineStr"/>
     </row>
@@ -7080,21 +5816,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H110" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I110" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J110" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H110" s="65" t="inlineStr"/>
+      <c r="I110" s="65" t="inlineStr"/>
+      <c r="J110" s="23" t="inlineStr"/>
       <c r="K110" s="23" t="n"/>
       <c r="L110" s="67" t="inlineStr"/>
     </row>
@@ -7134,16 +5858,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H111" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I111" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H111" s="65" t="inlineStr"/>
+      <c r="I111" s="65" t="inlineStr"/>
       <c r="J111" s="23" t="inlineStr">
         <is>
           <t>OBSERVATION -CLEANING ON PROGRESS</t>
@@ -7188,21 +5904,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H112" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I112" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J112" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H112" s="65" t="inlineStr"/>
+      <c r="I112" s="65" t="inlineStr"/>
+      <c r="J112" s="23" t="inlineStr"/>
       <c r="K112" s="23" t="n"/>
       <c r="L112" s="67" t="inlineStr"/>
     </row>
@@ -7242,21 +5946,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H113" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I113" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J113" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H113" s="65" t="inlineStr"/>
+      <c r="I113" s="65" t="inlineStr"/>
+      <c r="J113" s="23" t="inlineStr"/>
       <c r="K113" s="23" t="n"/>
       <c r="L113" s="67" t="inlineStr"/>
     </row>
@@ -7296,21 +5988,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H114" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I114" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J114" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H114" s="65" t="inlineStr"/>
+      <c r="I114" s="65" t="inlineStr"/>
+      <c r="J114" s="23" t="inlineStr"/>
       <c r="K114" s="23" t="n"/>
       <c r="L114" s="67" t="inlineStr"/>
     </row>
@@ -7350,21 +6030,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H115" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I115" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J115" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H115" s="65" t="inlineStr"/>
+      <c r="I115" s="65" t="inlineStr"/>
+      <c r="J115" s="23" t="inlineStr"/>
       <c r="K115" s="23" t="n"/>
       <c r="L115" s="67" t="inlineStr"/>
     </row>
@@ -7404,21 +6072,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H116" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I116" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J116" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H116" s="65" t="inlineStr"/>
+      <c r="I116" s="65" t="inlineStr"/>
+      <c r="J116" s="23" t="inlineStr"/>
       <c r="K116" s="23" t="n"/>
       <c r="L116" s="67" t="inlineStr"/>
     </row>
@@ -7458,21 +6114,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I117" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J117" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H117" s="65" t="inlineStr"/>
+      <c r="I117" s="65" t="inlineStr"/>
+      <c r="J117" s="23" t="inlineStr"/>
       <c r="K117" s="23" t="n"/>
       <c r="L117" s="67" t="inlineStr"/>
     </row>
@@ -7512,21 +6156,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I118" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J118" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H118" s="65" t="inlineStr"/>
+      <c r="I118" s="65" t="inlineStr"/>
+      <c r="J118" s="23" t="inlineStr"/>
       <c r="K118" s="23" t="n"/>
       <c r="L118" s="67" t="inlineStr"/>
     </row>
@@ -7566,21 +6198,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H119" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I119" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J119" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H119" s="65" t="inlineStr"/>
+      <c r="I119" s="65" t="inlineStr"/>
+      <c r="J119" s="23" t="inlineStr"/>
       <c r="K119" s="23" t="n"/>
       <c r="L119" s="67" t="inlineStr"/>
     </row>
@@ -7620,21 +6240,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H120" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I120" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J120" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H120" s="65" t="inlineStr"/>
+      <c r="I120" s="65" t="inlineStr"/>
+      <c r="J120" s="23" t="inlineStr"/>
       <c r="K120" s="23" t="n"/>
       <c r="L120" s="67" t="inlineStr"/>
     </row>
@@ -7674,21 +6282,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H121" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I121" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J121" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H121" s="65" t="inlineStr"/>
+      <c r="I121" s="65" t="inlineStr"/>
+      <c r="J121" s="23" t="inlineStr"/>
       <c r="K121" s="23" t="n"/>
       <c r="L121" s="67" t="inlineStr"/>
     </row>
@@ -7728,21 +6324,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I122" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J122" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H122" s="65" t="inlineStr"/>
+      <c r="I122" s="65" t="inlineStr"/>
+      <c r="J122" s="23" t="inlineStr"/>
       <c r="K122" s="23" t="n"/>
       <c r="L122" s="67" t="inlineStr"/>
     </row>
@@ -7782,21 +6366,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H123" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I123" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J123" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H123" s="65" t="inlineStr"/>
+      <c r="I123" s="65" t="inlineStr"/>
+      <c r="J123" s="23" t="inlineStr"/>
       <c r="K123" s="23" t="n"/>
       <c r="L123" s="67" t="inlineStr"/>
     </row>
@@ -7836,21 +6408,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H124" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I124" s="65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J124" s="23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="H124" s="65" t="inlineStr"/>
+      <c r="I124" s="65" t="inlineStr"/>
+      <c r="J124" s="23" t="inlineStr"/>
       <c r="K124" s="23" t="n"/>
       <c r="L124" s="67" t="inlineStr"/>
     </row>
@@ -7890,21 +6450,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H125" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I125" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J125" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H125" s="65" t="inlineStr"/>
+      <c r="I125" s="65" t="inlineStr"/>
+      <c r="J125" s="23" t="inlineStr"/>
       <c r="K125" s="23" t="n"/>
       <c r="L125" s="67" t="inlineStr"/>
     </row>
@@ -7944,21 +6492,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H126" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I126" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J126" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H126" s="65" t="inlineStr"/>
+      <c r="I126" s="65" t="inlineStr"/>
+      <c r="J126" s="23" t="inlineStr"/>
       <c r="K126" s="23" t="n"/>
       <c r="L126" s="67" t="inlineStr"/>
     </row>
@@ -7998,21 +6534,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H127" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I127" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J127" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H127" s="65" t="inlineStr"/>
+      <c r="I127" s="65" t="inlineStr"/>
+      <c r="J127" s="23" t="inlineStr"/>
       <c r="K127" s="23" t="n"/>
       <c r="L127" s="67" t="inlineStr"/>
     </row>
@@ -8052,21 +6576,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H128" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I128" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H128" s="65" t="inlineStr"/>
+      <c r="I128" s="65" t="inlineStr"/>
+      <c r="J128" s="23" t="inlineStr"/>
       <c r="K128" s="23" t="n"/>
       <c r="L128" s="67" t="inlineStr"/>
     </row>
@@ -8106,21 +6618,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I129" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J129" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H129" s="65" t="inlineStr"/>
+      <c r="I129" s="65" t="inlineStr"/>
+      <c r="J129" s="23" t="inlineStr"/>
       <c r="K129" s="23" t="n"/>
       <c r="L129" s="67" t="inlineStr"/>
     </row>
@@ -8160,21 +6660,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I130" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J130" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H130" s="65" t="inlineStr"/>
+      <c r="I130" s="65" t="inlineStr"/>
+      <c r="J130" s="23" t="inlineStr"/>
       <c r="K130" s="23" t="n"/>
       <c r="L130" s="67" t="inlineStr"/>
     </row>
@@ -8214,21 +6702,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H131" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I131" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J131" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H131" s="65" t="inlineStr"/>
+      <c r="I131" s="65" t="inlineStr"/>
+      <c r="J131" s="23" t="inlineStr"/>
       <c r="K131" s="23" t="n"/>
       <c r="L131" s="67" t="inlineStr"/>
     </row>
@@ -8268,21 +6744,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I132" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J132" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H132" s="65" t="inlineStr"/>
+      <c r="I132" s="65" t="inlineStr"/>
+      <c r="J132" s="23" t="inlineStr"/>
       <c r="K132" s="23" t="n"/>
       <c r="L132" s="67" t="inlineStr"/>
     </row>
@@ -8322,21 +6786,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H133" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I133" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J133" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H133" s="65" t="inlineStr"/>
+      <c r="I133" s="65" t="inlineStr"/>
+      <c r="J133" s="23" t="inlineStr"/>
       <c r="K133" s="23" t="n"/>
       <c r="L133" s="67" t="inlineStr"/>
     </row>
@@ -8376,21 +6828,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H134" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I134" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J134" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H134" s="65" t="inlineStr"/>
+      <c r="I134" s="65" t="inlineStr"/>
+      <c r="J134" s="23" t="inlineStr"/>
       <c r="K134" s="23" t="n"/>
       <c r="L134" s="67" t="inlineStr"/>
     </row>
@@ -8570,21 +7010,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H140" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I140" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J140" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H140" s="65" t="inlineStr"/>
+      <c r="I140" s="65" t="inlineStr"/>
+      <c r="J140" s="23" t="inlineStr"/>
       <c r="K140" s="23" t="n"/>
       <c r="L140" s="67" t="inlineStr"/>
     </row>
@@ -8624,21 +7052,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H141" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I141" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J141" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H141" s="65" t="inlineStr"/>
+      <c r="I141" s="65" t="inlineStr"/>
+      <c r="J141" s="23" t="inlineStr"/>
       <c r="K141" s="23" t="n"/>
       <c r="L141" s="67" t="inlineStr"/>
     </row>
@@ -8706,21 +7122,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H143" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I143" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J143" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H143" s="65" t="inlineStr"/>
+      <c r="I143" s="65" t="inlineStr"/>
+      <c r="J143" s="23" t="inlineStr"/>
       <c r="K143" s="23" t="n"/>
       <c r="L143" s="67" t="inlineStr"/>
     </row>
@@ -8760,21 +7164,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H144" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I144" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J144" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H144" s="65" t="inlineStr"/>
+      <c r="I144" s="65" t="inlineStr"/>
+      <c r="J144" s="23" t="inlineStr"/>
       <c r="K144" s="23" t="n"/>
       <c r="L144" s="67" t="inlineStr"/>
     </row>
@@ -8785,9 +7177,9 @@
         </is>
       </c>
       <c r="B145" s="23" t="inlineStr"/>
-      <c r="C145" s="79" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="C145" s="78" t="inlineStr">
+        <is>
+          <t>9%</t>
         </is>
       </c>
       <c r="D145" s="23" t="n">
@@ -8815,7 +7207,7 @@
       <c r="B146" s="23" t="inlineStr"/>
       <c r="C146" s="78" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="D146" s="23" t="n">
@@ -8926,21 +7318,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H149" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I149" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J149" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H149" s="65" t="inlineStr"/>
+      <c r="I149" s="65" t="inlineStr"/>
+      <c r="J149" s="23" t="inlineStr"/>
       <c r="K149" s="23" t="n"/>
       <c r="L149" s="67" t="inlineStr"/>
     </row>
@@ -8980,21 +7360,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H150" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I150" s="65" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J150" s="23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="H150" s="65" t="inlineStr"/>
+      <c r="I150" s="65" t="inlineStr"/>
+      <c r="J150" s="23" t="inlineStr"/>
       <c r="K150" s="23" t="n"/>
       <c r="L150" s="67" t="inlineStr"/>
     </row>
@@ -9034,21 +7402,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H151" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I151" s="65" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J151" s="23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="H151" s="65" t="inlineStr"/>
+      <c r="I151" s="65" t="inlineStr"/>
+      <c r="J151" s="23" t="inlineStr"/>
       <c r="K151" s="23" t="n"/>
       <c r="L151" s="67" t="inlineStr"/>
     </row>
@@ -9088,21 +7444,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H152" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I152" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J152" s="23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H152" s="65" t="inlineStr"/>
+      <c r="I152" s="65" t="inlineStr"/>
+      <c r="J152" s="23" t="inlineStr"/>
       <c r="K152" s="23" t="n"/>
       <c r="L152" s="67" t="inlineStr"/>
     </row>
@@ -9142,21 +7486,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H153" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I153" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J153" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="H153" s="65" t="inlineStr"/>
+      <c r="I153" s="65" t="inlineStr"/>
+      <c r="J153" s="23" t="inlineStr"/>
       <c r="K153" s="23" t="n"/>
       <c r="L153" s="67" t="inlineStr"/>
     </row>
@@ -9196,21 +7528,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H154" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I154" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J154" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H154" s="65" t="inlineStr"/>
+      <c r="I154" s="65" t="inlineStr"/>
+      <c r="J154" s="23" t="inlineStr"/>
       <c r="K154" s="23" t="n"/>
       <c r="L154" s="67" t="inlineStr"/>
     </row>
@@ -9278,21 +7598,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H156" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I156" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J156" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H156" s="65" t="inlineStr"/>
+      <c r="I156" s="65" t="inlineStr"/>
+      <c r="J156" s="23" t="inlineStr"/>
       <c r="K156" s="23" t="n"/>
       <c r="L156" s="67" t="inlineStr"/>
     </row>
@@ -9332,21 +7640,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H157" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I157" s="65" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J157" s="23" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="H157" s="65" t="inlineStr"/>
+      <c r="I157" s="65" t="inlineStr"/>
+      <c r="J157" s="23" t="inlineStr"/>
       <c r="K157" s="23" t="n"/>
       <c r="L157" s="67" t="inlineStr"/>
     </row>
@@ -9359,7 +7655,7 @@
       <c r="B158" s="23" t="inlineStr"/>
       <c r="C158" s="78" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D158" s="23" t="n">
@@ -9387,7 +7683,7 @@
       <c r="B159" s="23" t="inlineStr"/>
       <c r="C159" s="78" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D159" s="23" t="n">
@@ -9470,21 +7766,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H161" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I161" s="65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J161" s="23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="H161" s="65" t="inlineStr"/>
+      <c r="I161" s="65" t="inlineStr"/>
+      <c r="J161" s="23" t="inlineStr"/>
       <c r="K161" s="23" t="n"/>
       <c r="L161" s="67" t="inlineStr"/>
     </row>
@@ -9524,21 +7808,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H162" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I162" s="65" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="J162" s="23" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
+      <c r="H162" s="65" t="inlineStr"/>
+      <c r="I162" s="65" t="inlineStr"/>
+      <c r="J162" s="23" t="inlineStr"/>
       <c r="K162" s="23" t="n"/>
       <c r="L162" s="67" t="inlineStr"/>
     </row>
@@ -9578,21 +7850,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H163" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I163" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J163" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H163" s="65" t="inlineStr"/>
+      <c r="I163" s="65" t="inlineStr"/>
+      <c r="J163" s="23" t="inlineStr"/>
       <c r="K163" s="23" t="n"/>
       <c r="L163" s="67" t="inlineStr"/>
     </row>
@@ -9661,7 +7921,7 @@
       <c r="B166" s="23" t="inlineStr"/>
       <c r="C166" s="78" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="D166" s="23" t="n">
@@ -9689,7 +7949,7 @@
       <c r="B167" s="23" t="inlineStr"/>
       <c r="C167" s="78" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="D167" s="23" t="n">
@@ -9800,21 +8060,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H170" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I170" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J170" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H170" s="65" t="inlineStr"/>
+      <c r="I170" s="65" t="inlineStr"/>
+      <c r="J170" s="23" t="inlineStr"/>
       <c r="K170" s="23" t="n"/>
       <c r="L170" s="67" t="inlineStr"/>
     </row>
@@ -9882,21 +8130,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H172" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I172" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J172" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H172" s="65" t="inlineStr"/>
+      <c r="I172" s="65" t="inlineStr"/>
+      <c r="J172" s="23" t="inlineStr"/>
       <c r="K172" s="23" t="n"/>
       <c r="L172" s="67" t="inlineStr"/>
     </row>
@@ -9936,21 +8172,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H173" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I173" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J173" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H173" s="65" t="inlineStr"/>
+      <c r="I173" s="65" t="inlineStr"/>
+      <c r="J173" s="23" t="inlineStr"/>
       <c r="K173" s="23" t="n"/>
       <c r="L173" s="67" t="inlineStr"/>
     </row>
@@ -9990,21 +8214,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H174" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I174" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J174" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="H174" s="65" t="inlineStr"/>
+      <c r="I174" s="65" t="inlineStr"/>
+      <c r="J174" s="23" t="inlineStr"/>
       <c r="K174" s="23" t="n"/>
       <c r="L174" s="67" t="inlineStr"/>
     </row>
@@ -10044,21 +8256,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H175" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I175" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J175" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H175" s="65" t="inlineStr"/>
+      <c r="I175" s="65" t="inlineStr"/>
+      <c r="J175" s="23" t="inlineStr"/>
       <c r="K175" s="23" t="n"/>
       <c r="L175" s="67" t="inlineStr"/>
     </row>
@@ -10098,21 +8298,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H176" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I176" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J176" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H176" s="65" t="inlineStr"/>
+      <c r="I176" s="65" t="inlineStr"/>
+      <c r="J176" s="23" t="inlineStr"/>
       <c r="K176" s="23" t="n"/>
       <c r="L176" s="67" t="inlineStr"/>
     </row>
@@ -10152,21 +8340,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H177" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I177" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J177" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H177" s="65" t="inlineStr"/>
+      <c r="I177" s="65" t="inlineStr"/>
+      <c r="J177" s="23" t="inlineStr"/>
       <c r="K177" s="23" t="n"/>
       <c r="L177" s="67" t="inlineStr"/>
     </row>
@@ -10206,21 +8382,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H178" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I178" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J178" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H178" s="65" t="inlineStr"/>
+      <c r="I178" s="65" t="inlineStr"/>
+      <c r="J178" s="23" t="inlineStr"/>
       <c r="K178" s="23" t="n"/>
       <c r="L178" s="67" t="inlineStr"/>
     </row>
@@ -10260,21 +8424,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H179" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I179" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J179" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H179" s="65" t="inlineStr"/>
+      <c r="I179" s="65" t="inlineStr"/>
+      <c r="J179" s="23" t="inlineStr"/>
       <c r="K179" s="23" t="n"/>
       <c r="L179" s="67" t="inlineStr"/>
     </row>
@@ -10314,21 +8466,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H180" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I180" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J180" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H180" s="65" t="inlineStr"/>
+      <c r="I180" s="65" t="inlineStr"/>
+      <c r="J180" s="23" t="inlineStr"/>
       <c r="K180" s="23" t="n"/>
       <c r="L180" s="67" t="inlineStr"/>
     </row>
@@ -10368,21 +8508,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H181" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I181" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J181" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H181" s="65" t="inlineStr"/>
+      <c r="I181" s="65" t="inlineStr"/>
+      <c r="J181" s="23" t="inlineStr"/>
       <c r="K181" s="23" t="n"/>
       <c r="L181" s="67" t="inlineStr"/>
     </row>
@@ -10422,21 +8550,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H182" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I182" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J182" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H182" s="65" t="inlineStr"/>
+      <c r="I182" s="65" t="inlineStr"/>
+      <c r="J182" s="23" t="inlineStr"/>
       <c r="K182" s="23" t="n"/>
       <c r="L182" s="67" t="inlineStr"/>
     </row>
@@ -10476,21 +8592,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H183" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I183" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J183" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H183" s="65" t="inlineStr"/>
+      <c r="I183" s="65" t="inlineStr"/>
+      <c r="J183" s="23" t="inlineStr"/>
       <c r="K183" s="23" t="n"/>
       <c r="L183" s="67" t="inlineStr"/>
     </row>
@@ -10530,21 +8634,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H184" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I184" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J184" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H184" s="65" t="inlineStr"/>
+      <c r="I184" s="65" t="inlineStr"/>
+      <c r="J184" s="23" t="inlineStr"/>
       <c r="K184" s="23" t="n"/>
       <c r="L184" s="67" t="inlineStr"/>
     </row>
@@ -10584,21 +8676,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H185" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I185" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J185" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H185" s="65" t="inlineStr"/>
+      <c r="I185" s="65" t="inlineStr"/>
+      <c r="J185" s="23" t="inlineStr"/>
       <c r="K185" s="23" t="n"/>
       <c r="L185" s="67" t="inlineStr"/>
     </row>
@@ -10638,21 +8718,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H186" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I186" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J186" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H186" s="65" t="inlineStr"/>
+      <c r="I186" s="65" t="inlineStr"/>
+      <c r="J186" s="23" t="inlineStr"/>
       <c r="K186" s="23" t="n"/>
       <c r="L186" s="67" t="inlineStr"/>
     </row>
@@ -10692,21 +8760,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H187" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I187" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J187" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H187" s="65" t="inlineStr"/>
+      <c r="I187" s="65" t="inlineStr"/>
+      <c r="J187" s="23" t="inlineStr"/>
       <c r="K187" s="23" t="n"/>
       <c r="L187" s="67" t="inlineStr"/>
     </row>
@@ -10746,21 +8802,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H188" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I188" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J188" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H188" s="65" t="inlineStr"/>
+      <c r="I188" s="65" t="inlineStr"/>
+      <c r="J188" s="23" t="inlineStr"/>
       <c r="K188" s="23" t="n"/>
       <c r="L188" s="67" t="inlineStr"/>
     </row>
@@ -10800,21 +8844,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H189" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I189" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J189" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="H189" s="65" t="inlineStr"/>
+      <c r="I189" s="65" t="inlineStr"/>
+      <c r="J189" s="23" t="inlineStr"/>
       <c r="K189" s="23" t="n"/>
       <c r="L189" s="67" t="inlineStr"/>
     </row>
@@ -10854,21 +8886,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H190" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I190" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J190" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="H190" s="65" t="inlineStr"/>
+      <c r="I190" s="65" t="inlineStr"/>
+      <c r="J190" s="23" t="inlineStr"/>
       <c r="K190" s="23" t="n"/>
       <c r="L190" s="67" t="inlineStr"/>
     </row>
@@ -10908,21 +8928,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H191" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I191" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J191" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H191" s="65" t="inlineStr"/>
+      <c r="I191" s="65" t="inlineStr"/>
+      <c r="J191" s="23" t="inlineStr"/>
       <c r="K191" s="23" t="n"/>
       <c r="L191" s="67" t="inlineStr"/>
     </row>
@@ -10962,21 +8970,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H192" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I192" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J192" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H192" s="65" t="inlineStr"/>
+      <c r="I192" s="65" t="inlineStr"/>
+      <c r="J192" s="23" t="inlineStr"/>
       <c r="K192" s="23" t="n"/>
       <c r="L192" s="67" t="inlineStr"/>
     </row>
@@ -11016,21 +9012,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H193" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I193" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J193" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H193" s="65" t="inlineStr"/>
+      <c r="I193" s="65" t="inlineStr"/>
+      <c r="J193" s="23" t="inlineStr"/>
       <c r="K193" s="23" t="n"/>
       <c r="L193" s="67" t="inlineStr"/>
     </row>
@@ -11070,21 +9054,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H194" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I194" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J194" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H194" s="65" t="inlineStr"/>
+      <c r="I194" s="65" t="inlineStr"/>
+      <c r="J194" s="23" t="inlineStr"/>
       <c r="K194" s="23" t="n"/>
       <c r="L194" s="67" t="inlineStr"/>
     </row>
@@ -11124,21 +9096,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H195" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I195" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J195" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H195" s="65" t="inlineStr"/>
+      <c r="I195" s="65" t="inlineStr"/>
+      <c r="J195" s="23" t="inlineStr"/>
       <c r="K195" s="23" t="n"/>
       <c r="L195" s="67" t="inlineStr"/>
     </row>
@@ -11178,21 +9138,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H196" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I196" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J196" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H196" s="65" t="inlineStr"/>
+      <c r="I196" s="65" t="inlineStr"/>
+      <c r="J196" s="23" t="inlineStr"/>
       <c r="K196" s="23" t="n"/>
       <c r="L196" s="67" t="inlineStr"/>
     </row>
@@ -11232,16 +9180,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H197" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I197" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H197" s="65" t="inlineStr"/>
+      <c r="I197" s="65" t="inlineStr"/>
       <c r="J197" s="23" t="inlineStr">
         <is>
           <t>WALKDOWN COMPLETE-20-08-26--ATTENDENCE SHEET TO BE SUBMITTED</t>
@@ -11286,21 +9226,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H198" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I198" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J198" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H198" s="65" t="inlineStr"/>
+      <c r="I198" s="65" t="inlineStr"/>
+      <c r="J198" s="23" t="inlineStr"/>
       <c r="K198" s="23" t="n"/>
       <c r="L198" s="67" t="inlineStr"/>
     </row>
@@ -11340,21 +9268,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H199" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I199" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J199" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H199" s="65" t="inlineStr"/>
+      <c r="I199" s="65" t="inlineStr"/>
+      <c r="J199" s="23" t="inlineStr"/>
       <c r="K199" s="23" t="n"/>
       <c r="L199" s="67" t="inlineStr"/>
     </row>
@@ -11394,21 +9310,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H200" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I200" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J200" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H200" s="65" t="inlineStr"/>
+      <c r="I200" s="65" t="inlineStr"/>
+      <c r="J200" s="23" t="inlineStr"/>
       <c r="K200" s="23" t="n"/>
       <c r="L200" s="67" t="inlineStr"/>
     </row>
@@ -11448,21 +9352,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H201" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I201" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J201" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H201" s="65" t="inlineStr"/>
+      <c r="I201" s="65" t="inlineStr"/>
+      <c r="J201" s="23" t="inlineStr"/>
       <c r="K201" s="23" t="n"/>
       <c r="L201" s="67" t="inlineStr"/>
     </row>
@@ -11502,21 +9394,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H202" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I202" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J202" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H202" s="65" t="inlineStr"/>
+      <c r="I202" s="65" t="inlineStr"/>
+      <c r="J202" s="23" t="inlineStr"/>
       <c r="K202" s="23" t="n"/>
       <c r="L202" s="67" t="inlineStr"/>
     </row>
@@ -11556,21 +9436,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H203" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I203" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J203" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H203" s="65" t="inlineStr"/>
+      <c r="I203" s="65" t="inlineStr"/>
+      <c r="J203" s="23" t="inlineStr"/>
       <c r="K203" s="23" t="n"/>
       <c r="L203" s="67" t="inlineStr"/>
     </row>
@@ -11610,21 +9478,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H204" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I204" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J204" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H204" s="65" t="inlineStr"/>
+      <c r="I204" s="65" t="inlineStr"/>
+      <c r="J204" s="23" t="inlineStr"/>
       <c r="K204" s="23" t="n"/>
       <c r="L204" s="67" t="inlineStr"/>
     </row>
@@ -11664,21 +9520,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H205" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I205" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J205" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H205" s="65" t="inlineStr"/>
+      <c r="I205" s="65" t="inlineStr"/>
+      <c r="J205" s="23" t="inlineStr"/>
       <c r="K205" s="23" t="n"/>
       <c r="L205" s="67" t="inlineStr"/>
     </row>
@@ -11718,21 +9562,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H206" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I206" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J206" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H206" s="65" t="inlineStr"/>
+      <c r="I206" s="65" t="inlineStr"/>
+      <c r="J206" s="23" t="inlineStr"/>
       <c r="K206" s="23" t="n"/>
       <c r="L206" s="67" t="inlineStr"/>
     </row>
@@ -11772,21 +9604,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H207" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I207" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J207" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H207" s="65" t="inlineStr"/>
+      <c r="I207" s="65" t="inlineStr"/>
+      <c r="J207" s="23" t="inlineStr"/>
       <c r="K207" s="23" t="n"/>
       <c r="L207" s="67" t="inlineStr"/>
     </row>
@@ -11826,21 +9646,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H208" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I208" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J208" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H208" s="65" t="inlineStr"/>
+      <c r="I208" s="65" t="inlineStr"/>
+      <c r="J208" s="23" t="inlineStr"/>
       <c r="K208" s="23" t="n"/>
       <c r="L208" s="67" t="inlineStr"/>
     </row>
@@ -11880,21 +9688,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H209" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I209" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J209" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H209" s="65" t="inlineStr"/>
+      <c r="I209" s="65" t="inlineStr"/>
+      <c r="J209" s="23" t="inlineStr"/>
       <c r="K209" s="23" t="n"/>
       <c r="L209" s="67" t="inlineStr"/>
     </row>
@@ -11934,21 +9730,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H210" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I210" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J210" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H210" s="65" t="inlineStr"/>
+      <c r="I210" s="65" t="inlineStr"/>
+      <c r="J210" s="23" t="inlineStr"/>
       <c r="K210" s="23" t="n"/>
       <c r="L210" s="67" t="inlineStr"/>
     </row>
@@ -11988,21 +9772,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H211" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I211" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J211" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H211" s="65" t="inlineStr"/>
+      <c r="I211" s="65" t="inlineStr"/>
+      <c r="J211" s="23" t="inlineStr"/>
       <c r="K211" s="23" t="n"/>
       <c r="L211" s="67" t="inlineStr"/>
     </row>
@@ -12042,21 +9814,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H212" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I212" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J212" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H212" s="65" t="inlineStr"/>
+      <c r="I212" s="65" t="inlineStr"/>
+      <c r="J212" s="23" t="inlineStr"/>
       <c r="K212" s="23" t="n"/>
       <c r="L212" s="67" t="inlineStr"/>
     </row>
@@ -12096,21 +9856,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H213" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I213" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J213" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H213" s="65" t="inlineStr"/>
+      <c r="I213" s="65" t="inlineStr"/>
+      <c r="J213" s="23" t="inlineStr"/>
       <c r="K213" s="23" t="n"/>
       <c r="L213" s="67" t="inlineStr"/>
     </row>
@@ -12150,21 +9898,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H214" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I214" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J214" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H214" s="65" t="inlineStr"/>
+      <c r="I214" s="65" t="inlineStr"/>
+      <c r="J214" s="23" t="inlineStr"/>
       <c r="K214" s="23" t="n"/>
       <c r="L214" s="67" t="inlineStr"/>
     </row>
@@ -12204,21 +9940,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H215" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I215" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J215" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H215" s="65" t="inlineStr"/>
+      <c r="I215" s="65" t="inlineStr"/>
+      <c r="J215" s="23" t="inlineStr"/>
       <c r="K215" s="23" t="n"/>
       <c r="L215" s="67" t="inlineStr"/>
     </row>
@@ -12258,21 +9982,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H216" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I216" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J216" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H216" s="65" t="inlineStr"/>
+      <c r="I216" s="65" t="inlineStr"/>
+      <c r="J216" s="23" t="inlineStr"/>
       <c r="K216" s="23" t="n"/>
       <c r="L216" s="67" t="inlineStr"/>
     </row>
@@ -12312,21 +10024,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H217" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I217" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J217" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H217" s="65" t="inlineStr"/>
+      <c r="I217" s="65" t="inlineStr"/>
+      <c r="J217" s="23" t="inlineStr"/>
       <c r="K217" s="23" t="n"/>
       <c r="L217" s="67" t="inlineStr"/>
     </row>
@@ -12366,21 +10066,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H218" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I218" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J218" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H218" s="65" t="inlineStr"/>
+      <c r="I218" s="65" t="inlineStr"/>
+      <c r="J218" s="23" t="inlineStr"/>
       <c r="K218" s="23" t="n"/>
       <c r="L218" s="67" t="inlineStr"/>
     </row>
@@ -12420,21 +10108,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H219" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I219" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J219" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H219" s="65" t="inlineStr"/>
+      <c r="I219" s="65" t="inlineStr"/>
+      <c r="J219" s="23" t="inlineStr"/>
       <c r="K219" s="23" t="n"/>
       <c r="L219" s="67" t="inlineStr"/>
     </row>
@@ -12474,21 +10150,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H220" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I220" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J220" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H220" s="65" t="inlineStr"/>
+      <c r="I220" s="65" t="inlineStr"/>
+      <c r="J220" s="23" t="inlineStr"/>
       <c r="K220" s="23" t="n"/>
       <c r="L220" s="67" t="inlineStr"/>
     </row>
@@ -12528,21 +10192,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I221" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J221" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H221" s="65" t="inlineStr"/>
+      <c r="I221" s="65" t="inlineStr"/>
+      <c r="J221" s="23" t="inlineStr"/>
       <c r="K221" s="23" t="n"/>
       <c r="L221" s="67" t="inlineStr"/>
     </row>
@@ -12582,21 +10234,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H222" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I222" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J222" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H222" s="65" t="inlineStr"/>
+      <c r="I222" s="65" t="inlineStr"/>
+      <c r="J222" s="23" t="inlineStr"/>
       <c r="K222" s="23" t="n"/>
       <c r="L222" s="67" t="inlineStr"/>
     </row>
@@ -12636,21 +10276,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H223" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I223" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J223" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H223" s="65" t="inlineStr"/>
+      <c r="I223" s="65" t="inlineStr"/>
+      <c r="J223" s="23" t="inlineStr"/>
       <c r="K223" s="23" t="n"/>
       <c r="L223" s="67" t="inlineStr"/>
     </row>
@@ -12690,21 +10318,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H224" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I224" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J224" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H224" s="65" t="inlineStr"/>
+      <c r="I224" s="65" t="inlineStr"/>
+      <c r="J224" s="23" t="inlineStr"/>
       <c r="K224" s="23" t="n"/>
       <c r="L224" s="67" t="inlineStr"/>
     </row>
@@ -12744,21 +10360,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H225" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I225" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J225" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H225" s="65" t="inlineStr"/>
+      <c r="I225" s="65" t="inlineStr"/>
+      <c r="J225" s="23" t="inlineStr"/>
       <c r="K225" s="23" t="n"/>
       <c r="L225" s="67" t="inlineStr"/>
     </row>
@@ -12798,21 +10402,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H226" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I226" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J226" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H226" s="65" t="inlineStr"/>
+      <c r="I226" s="65" t="inlineStr"/>
+      <c r="J226" s="23" t="inlineStr"/>
       <c r="K226" s="23" t="n"/>
       <c r="L226" s="67" t="inlineStr"/>
     </row>
@@ -12852,21 +10444,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H227" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I227" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J227" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H227" s="65" t="inlineStr"/>
+      <c r="I227" s="65" t="inlineStr"/>
+      <c r="J227" s="23" t="inlineStr"/>
       <c r="K227" s="23" t="n"/>
       <c r="L227" s="67" t="inlineStr"/>
     </row>
@@ -12906,21 +10486,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H228" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I228" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J228" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H228" s="65" t="inlineStr"/>
+      <c r="I228" s="65" t="inlineStr"/>
+      <c r="J228" s="23" t="inlineStr"/>
       <c r="K228" s="23" t="n"/>
       <c r="L228" s="67" t="inlineStr"/>
     </row>
@@ -12960,21 +10528,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H229" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I229" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J229" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H229" s="65" t="inlineStr"/>
+      <c r="I229" s="65" t="inlineStr"/>
+      <c r="J229" s="23" t="inlineStr"/>
       <c r="K229" s="23" t="n"/>
       <c r="L229" s="67" t="inlineStr"/>
     </row>
@@ -13014,21 +10570,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H230" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I230" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J230" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H230" s="65" t="inlineStr"/>
+      <c r="I230" s="65" t="inlineStr"/>
+      <c r="J230" s="23" t="inlineStr"/>
       <c r="K230" s="23" t="n"/>
       <c r="L230" s="67" t="inlineStr"/>
     </row>
@@ -13068,21 +10612,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H231" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I231" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J231" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H231" s="65" t="inlineStr"/>
+      <c r="I231" s="65" t="inlineStr"/>
+      <c r="J231" s="23" t="inlineStr"/>
       <c r="K231" s="23" t="n"/>
       <c r="L231" s="67" t="inlineStr"/>
     </row>
@@ -13122,21 +10654,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H232" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I232" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J232" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H232" s="65" t="inlineStr"/>
+      <c r="I232" s="65" t="inlineStr"/>
+      <c r="J232" s="23" t="inlineStr"/>
       <c r="K232" s="23" t="n"/>
       <c r="L232" s="67" t="inlineStr"/>
     </row>
@@ -13176,21 +10696,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H233" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I233" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J233" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H233" s="65" t="inlineStr"/>
+      <c r="I233" s="65" t="inlineStr"/>
+      <c r="J233" s="23" t="inlineStr"/>
       <c r="K233" s="23" t="n"/>
       <c r="L233" s="67" t="inlineStr"/>
     </row>
@@ -13230,21 +10738,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I234" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J234" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H234" s="65" t="inlineStr"/>
+      <c r="I234" s="65" t="inlineStr"/>
+      <c r="J234" s="23" t="inlineStr"/>
       <c r="K234" s="23" t="n"/>
       <c r="L234" s="67" t="inlineStr"/>
     </row>
@@ -13284,21 +10780,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H235" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I235" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J235" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H235" s="65" t="inlineStr"/>
+      <c r="I235" s="65" t="inlineStr"/>
+      <c r="J235" s="23" t="inlineStr"/>
       <c r="K235" s="23" t="n"/>
       <c r="L235" s="67" t="inlineStr"/>
     </row>
@@ -13338,21 +10822,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I236" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J236" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H236" s="65" t="inlineStr"/>
+      <c r="I236" s="65" t="inlineStr"/>
+      <c r="J236" s="23" t="inlineStr"/>
       <c r="K236" s="23" t="n"/>
       <c r="L236" s="67" t="inlineStr"/>
     </row>
@@ -13392,21 +10864,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H237" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I237" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J237" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H237" s="65" t="inlineStr"/>
+      <c r="I237" s="65" t="inlineStr"/>
+      <c r="J237" s="23" t="inlineStr"/>
       <c r="K237" s="23" t="n"/>
       <c r="L237" s="67" t="inlineStr"/>
     </row>
@@ -13446,21 +10906,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H238" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I238" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J238" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H238" s="65" t="inlineStr"/>
+      <c r="I238" s="65" t="inlineStr"/>
+      <c r="J238" s="23" t="inlineStr"/>
       <c r="K238" s="23" t="n"/>
       <c r="L238" s="67" t="inlineStr"/>
     </row>
@@ -13500,21 +10948,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H239" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I239" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J239" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H239" s="65" t="inlineStr"/>
+      <c r="I239" s="65" t="inlineStr"/>
+      <c r="J239" s="23" t="inlineStr"/>
       <c r="K239" s="23" t="n"/>
       <c r="L239" s="67" t="inlineStr"/>
     </row>
@@ -13554,21 +10990,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H240" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I240" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J240" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H240" s="65" t="inlineStr"/>
+      <c r="I240" s="65" t="inlineStr"/>
+      <c r="J240" s="23" t="inlineStr"/>
       <c r="K240" s="23" t="n"/>
       <c r="L240" s="67" t="inlineStr"/>
     </row>
@@ -13608,21 +11032,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H241" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I241" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J241" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H241" s="65" t="inlineStr"/>
+      <c r="I241" s="65" t="inlineStr"/>
+      <c r="J241" s="23" t="inlineStr"/>
       <c r="K241" s="23" t="n"/>
       <c r="L241" s="67" t="inlineStr"/>
     </row>
@@ -13662,21 +11074,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H242" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I242" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J242" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H242" s="65" t="inlineStr"/>
+      <c r="I242" s="65" t="inlineStr"/>
+      <c r="J242" s="23" t="inlineStr"/>
       <c r="K242" s="23" t="n"/>
       <c r="L242" s="67" t="inlineStr"/>
     </row>
@@ -13716,21 +11116,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H243" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I243" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J243" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H243" s="65" t="inlineStr"/>
+      <c r="I243" s="65" t="inlineStr"/>
+      <c r="J243" s="23" t="inlineStr"/>
       <c r="K243" s="23" t="n"/>
       <c r="L243" s="67" t="inlineStr"/>
     </row>
@@ -13770,21 +11158,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H244" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I244" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J244" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H244" s="65" t="inlineStr"/>
+      <c r="I244" s="65" t="inlineStr"/>
+      <c r="J244" s="23" t="inlineStr"/>
       <c r="K244" s="23" t="n"/>
       <c r="L244" s="67" t="inlineStr"/>
     </row>
@@ -13824,21 +11200,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H245" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I245" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J245" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H245" s="65" t="inlineStr"/>
+      <c r="I245" s="65" t="inlineStr"/>
+      <c r="J245" s="23" t="inlineStr"/>
       <c r="K245" s="23" t="n"/>
       <c r="L245" s="67" t="inlineStr"/>
     </row>
@@ -13878,21 +11242,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H246" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I246" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J246" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H246" s="65" t="inlineStr"/>
+      <c r="I246" s="65" t="inlineStr"/>
+      <c r="J246" s="23" t="inlineStr"/>
       <c r="K246" s="23" t="n"/>
       <c r="L246" s="67" t="inlineStr"/>
     </row>
@@ -13932,21 +11284,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H247" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I247" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J247" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H247" s="65" t="inlineStr"/>
+      <c r="I247" s="65" t="inlineStr"/>
+      <c r="J247" s="23" t="inlineStr"/>
       <c r="K247" s="23" t="n"/>
       <c r="L247" s="67" t="inlineStr"/>
     </row>
@@ -13986,21 +11326,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H248" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I248" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J248" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H248" s="65" t="inlineStr"/>
+      <c r="I248" s="65" t="inlineStr"/>
+      <c r="J248" s="23" t="inlineStr"/>
       <c r="K248" s="23" t="n"/>
       <c r="L248" s="67" t="inlineStr"/>
     </row>
@@ -14040,21 +11368,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H249" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I249" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J249" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H249" s="65" t="inlineStr"/>
+      <c r="I249" s="65" t="inlineStr"/>
+      <c r="J249" s="23" t="inlineStr"/>
       <c r="K249" s="23" t="n"/>
       <c r="L249" s="67" t="inlineStr"/>
     </row>
@@ -14094,21 +11410,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I250" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J250" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H250" s="65" t="inlineStr"/>
+      <c r="I250" s="65" t="inlineStr"/>
+      <c r="J250" s="23" t="inlineStr"/>
       <c r="K250" s="23" t="n"/>
       <c r="L250" s="67" t="inlineStr"/>
     </row>
@@ -14148,21 +11452,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H251" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I251" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J251" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H251" s="65" t="inlineStr"/>
+      <c r="I251" s="65" t="inlineStr"/>
+      <c r="J251" s="23" t="inlineStr"/>
       <c r="K251" s="23" t="n"/>
       <c r="L251" s="67" t="inlineStr"/>
     </row>
@@ -14202,21 +11494,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H252" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I252" s="65" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J252" s="23" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="H252" s="65" t="inlineStr"/>
+      <c r="I252" s="65" t="inlineStr"/>
+      <c r="J252" s="23" t="inlineStr"/>
       <c r="K252" s="23" t="n"/>
       <c r="L252" s="67" t="inlineStr"/>
     </row>
@@ -14256,21 +11536,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H253" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I253" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J253" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H253" s="65" t="inlineStr"/>
+      <c r="I253" s="65" t="inlineStr"/>
+      <c r="J253" s="23" t="inlineStr"/>
       <c r="K253" s="23" t="n"/>
       <c r="L253" s="67" t="inlineStr"/>
     </row>
@@ -14310,21 +11578,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H254" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I254" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J254" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H254" s="65" t="inlineStr"/>
+      <c r="I254" s="65" t="inlineStr"/>
+      <c r="J254" s="23" t="inlineStr"/>
       <c r="K254" s="23" t="n"/>
       <c r="L254" s="67" t="inlineStr"/>
     </row>
@@ -14392,21 +11648,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H256" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I256" s="65" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J256" s="23" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="H256" s="65" t="inlineStr"/>
+      <c r="I256" s="65" t="inlineStr"/>
+      <c r="J256" s="23" t="inlineStr"/>
       <c r="K256" s="23" t="n"/>
       <c r="L256" s="67" t="inlineStr"/>
     </row>
@@ -14446,21 +11690,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H257" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I257" s="65" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J257" s="23" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="H257" s="65" t="inlineStr"/>
+      <c r="I257" s="65" t="inlineStr"/>
+      <c r="J257" s="23" t="inlineStr"/>
       <c r="K257" s="23" t="n"/>
       <c r="L257" s="67" t="inlineStr"/>
     </row>
@@ -14500,21 +11732,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H258" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I258" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J258" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H258" s="65" t="inlineStr"/>
+      <c r="I258" s="65" t="inlineStr"/>
+      <c r="J258" s="23" t="inlineStr"/>
       <c r="K258" s="23" t="n"/>
       <c r="L258" s="67" t="inlineStr"/>
     </row>
@@ -14554,21 +11774,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H259" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I259" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J259" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H259" s="65" t="inlineStr"/>
+      <c r="I259" s="65" t="inlineStr"/>
+      <c r="J259" s="23" t="inlineStr"/>
       <c r="K259" s="23" t="n"/>
       <c r="L259" s="67" t="inlineStr"/>
     </row>
@@ -14608,21 +11816,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H260" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I260" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J260" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="H260" s="65" t="inlineStr"/>
+      <c r="I260" s="65" t="inlineStr"/>
+      <c r="J260" s="23" t="inlineStr"/>
       <c r="K260" s="23" t="n"/>
       <c r="L260" s="67" t="inlineStr"/>
     </row>
@@ -14662,21 +11858,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H261" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I261" s="65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J261" s="23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="H261" s="65" t="inlineStr"/>
+      <c r="I261" s="65" t="inlineStr"/>
+      <c r="J261" s="23" t="inlineStr"/>
       <c r="K261" s="23" t="n"/>
       <c r="L261" s="67" t="inlineStr"/>
     </row>
@@ -14716,21 +11900,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H262" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I262" s="65" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J262" s="23" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="H262" s="65" t="inlineStr"/>
+      <c r="I262" s="65" t="inlineStr"/>
+      <c r="J262" s="23" t="inlineStr"/>
       <c r="K262" s="23" t="n"/>
       <c r="L262" s="67" t="inlineStr"/>
     </row>
@@ -14770,21 +11942,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H263" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I263" s="65" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J263" s="23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="H263" s="65" t="inlineStr"/>
+      <c r="I263" s="65" t="inlineStr"/>
+      <c r="J263" s="23" t="inlineStr"/>
       <c r="K263" s="23" t="n"/>
       <c r="L263" s="67" t="inlineStr"/>
     </row>
@@ -14824,21 +11984,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H264" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I264" s="65" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J264" s="23" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="H264" s="65" t="inlineStr"/>
+      <c r="I264" s="65" t="inlineStr"/>
+      <c r="J264" s="23" t="inlineStr"/>
       <c r="K264" s="23" t="n"/>
       <c r="L264" s="67" t="inlineStr"/>
     </row>
@@ -14878,21 +12026,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H265" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I265" s="65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J265" s="23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="H265" s="65" t="inlineStr"/>
+      <c r="I265" s="65" t="inlineStr"/>
+      <c r="J265" s="23" t="inlineStr"/>
       <c r="K265" s="23" t="n"/>
       <c r="L265" s="67" t="inlineStr"/>
     </row>
@@ -14988,21 +12124,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H268" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I268" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J268" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H268" s="65" t="inlineStr"/>
+      <c r="I268" s="65" t="inlineStr"/>
+      <c r="J268" s="23" t="inlineStr"/>
       <c r="K268" s="23" t="n"/>
       <c r="L268" s="67" t="inlineStr"/>
     </row>
@@ -15070,21 +12194,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H270" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I270" s="65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J270" s="23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="H270" s="65" t="inlineStr"/>
+      <c r="I270" s="65" t="inlineStr"/>
+      <c r="J270" s="23" t="inlineStr"/>
       <c r="K270" s="23" t="n"/>
       <c r="L270" s="67" t="inlineStr"/>
     </row>
@@ -15124,21 +12236,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H271" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I271" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J271" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H271" s="65" t="inlineStr"/>
+      <c r="I271" s="65" t="inlineStr"/>
+      <c r="J271" s="23" t="inlineStr"/>
       <c r="K271" s="23" t="n"/>
       <c r="L271" s="67" t="inlineStr"/>
     </row>
@@ -15178,21 +12278,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H272" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I272" s="65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J272" s="23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="H272" s="65" t="inlineStr"/>
+      <c r="I272" s="65" t="inlineStr"/>
+      <c r="J272" s="23" t="inlineStr"/>
       <c r="K272" s="23" t="n"/>
       <c r="L272" s="67" t="inlineStr"/>
     </row>
@@ -15232,21 +12320,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H273" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I273" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J273" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H273" s="65" t="inlineStr"/>
+      <c r="I273" s="65" t="inlineStr"/>
+      <c r="J273" s="23" t="inlineStr"/>
       <c r="K273" s="23" t="n"/>
       <c r="L273" s="67" t="inlineStr"/>
     </row>
@@ -15314,21 +12390,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H275" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I275" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J275" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H275" s="65" t="inlineStr"/>
+      <c r="I275" s="65" t="inlineStr"/>
+      <c r="J275" s="23" t="inlineStr"/>
       <c r="K275" s="23" t="n"/>
       <c r="L275" s="67" t="inlineStr"/>
     </row>
@@ -15368,21 +12432,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H276" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I276" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J276" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H276" s="65" t="inlineStr"/>
+      <c r="I276" s="65" t="inlineStr"/>
+      <c r="J276" s="23" t="inlineStr"/>
       <c r="K276" s="23" t="n"/>
       <c r="L276" s="67" t="inlineStr"/>
     </row>
@@ -15422,21 +12474,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H277" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I277" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J277" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H277" s="65" t="inlineStr"/>
+      <c r="I277" s="65" t="inlineStr"/>
+      <c r="J277" s="23" t="inlineStr"/>
       <c r="K277" s="23" t="n"/>
       <c r="L277" s="67" t="inlineStr"/>
     </row>
@@ -15476,21 +12516,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H278" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I278" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J278" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H278" s="65" t="inlineStr"/>
+      <c r="I278" s="65" t="inlineStr"/>
+      <c r="J278" s="23" t="inlineStr"/>
       <c r="K278" s="23" t="n"/>
       <c r="L278" s="67" t="inlineStr"/>
     </row>
@@ -15535,16 +12563,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="I279" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J279" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I279" s="65" t="inlineStr"/>
+      <c r="J279" s="23" t="inlineStr"/>
       <c r="K279" s="23" t="n"/>
       <c r="L279" s="67" t="inlineStr"/>
     </row>
@@ -15584,21 +12604,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H280" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I280" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J280" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H280" s="65" t="inlineStr"/>
+      <c r="I280" s="65" t="inlineStr"/>
+      <c r="J280" s="23" t="inlineStr"/>
       <c r="K280" s="23" t="n"/>
       <c r="L280" s="67" t="inlineStr"/>
     </row>
@@ -15638,21 +12646,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H281" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I281" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J281" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H281" s="65" t="inlineStr"/>
+      <c r="I281" s="65" t="inlineStr"/>
+      <c r="J281" s="23" t="inlineStr"/>
       <c r="K281" s="23" t="n"/>
       <c r="L281" s="67" t="inlineStr"/>
     </row>
@@ -15692,21 +12688,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H282" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I282" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J282" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H282" s="65" t="inlineStr"/>
+      <c r="I282" s="65" t="inlineStr"/>
+      <c r="J282" s="23" t="inlineStr"/>
       <c r="K282" s="23" t="n"/>
       <c r="L282" s="67" t="inlineStr"/>
     </row>
@@ -15746,21 +12730,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H283" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I283" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J283" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H283" s="65" t="inlineStr"/>
+      <c r="I283" s="65" t="inlineStr"/>
+      <c r="J283" s="23" t="inlineStr"/>
       <c r="K283" s="23" t="n"/>
       <c r="L283" s="67" t="inlineStr"/>
     </row>
@@ -15800,21 +12772,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H284" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I284" s="65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J284" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="H284" s="65" t="inlineStr"/>
+      <c r="I284" s="65" t="inlineStr"/>
+      <c r="J284" s="23" t="inlineStr"/>
       <c r="K284" s="23" t="n"/>
       <c r="L284" s="67" t="inlineStr"/>
     </row>
@@ -15854,21 +12814,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H285" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I285" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J285" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H285" s="65" t="inlineStr"/>
+      <c r="I285" s="65" t="inlineStr"/>
+      <c r="J285" s="23" t="inlineStr"/>
       <c r="K285" s="23" t="n"/>
       <c r="L285" s="67" t="inlineStr"/>
     </row>
@@ -15908,21 +12856,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H286" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I286" s="65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J286" s="23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="H286" s="65" t="inlineStr"/>
+      <c r="I286" s="65" t="inlineStr"/>
+      <c r="J286" s="23" t="inlineStr"/>
       <c r="K286" s="23" t="n"/>
       <c r="L286" s="67" t="inlineStr"/>
     </row>
@@ -15962,21 +12898,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H287" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I287" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J287" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H287" s="65" t="inlineStr"/>
+      <c r="I287" s="65" t="inlineStr"/>
+      <c r="J287" s="23" t="inlineStr"/>
       <c r="K287" s="23" t="n"/>
       <c r="L287" s="67" t="inlineStr"/>
     </row>
@@ -16016,21 +12940,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H288" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I288" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J288" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H288" s="65" t="inlineStr"/>
+      <c r="I288" s="65" t="inlineStr"/>
+      <c r="J288" s="23" t="inlineStr"/>
       <c r="K288" s="23" t="n"/>
       <c r="L288" s="67" t="inlineStr"/>
     </row>
@@ -16070,21 +12982,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H289" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I289" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J289" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H289" s="65" t="inlineStr"/>
+      <c r="I289" s="65" t="inlineStr"/>
+      <c r="J289" s="23" t="inlineStr"/>
       <c r="K289" s="23" t="n"/>
       <c r="L289" s="67" t="inlineStr"/>
     </row>
@@ -16124,21 +13024,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H290" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I290" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J290" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H290" s="65" t="inlineStr"/>
+      <c r="I290" s="65" t="inlineStr"/>
+      <c r="J290" s="23" t="inlineStr"/>
       <c r="K290" s="23" t="n"/>
       <c r="L290" s="67" t="inlineStr"/>
     </row>
@@ -16178,21 +13066,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H291" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I291" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J291" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H291" s="65" t="inlineStr"/>
+      <c r="I291" s="65" t="inlineStr"/>
+      <c r="J291" s="23" t="inlineStr"/>
       <c r="K291" s="23" t="n"/>
       <c r="L291" s="67" t="inlineStr"/>
     </row>
@@ -16232,21 +13108,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H292" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I292" s="65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J292" s="23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="H292" s="65" t="inlineStr"/>
+      <c r="I292" s="65" t="inlineStr"/>
+      <c r="J292" s="23" t="inlineStr"/>
       <c r="K292" s="23" t="n"/>
       <c r="L292" s="67" t="inlineStr"/>
     </row>
@@ -16286,21 +13150,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H293" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I293" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J293" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H293" s="65" t="inlineStr"/>
+      <c r="I293" s="65" t="inlineStr"/>
+      <c r="J293" s="23" t="inlineStr"/>
       <c r="K293" s="23" t="n"/>
       <c r="L293" s="67" t="inlineStr"/>
     </row>
@@ -16340,21 +13192,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H294" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I294" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J294" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H294" s="65" t="inlineStr"/>
+      <c r="I294" s="65" t="inlineStr"/>
+      <c r="J294" s="23" t="inlineStr"/>
       <c r="K294" s="23" t="n"/>
       <c r="L294" s="67" t="inlineStr"/>
     </row>
@@ -16394,21 +13234,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H295" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I295" s="65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J295" s="23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="H295" s="65" t="inlineStr"/>
+      <c r="I295" s="65" t="inlineStr"/>
+      <c r="J295" s="23" t="inlineStr"/>
       <c r="K295" s="23" t="n"/>
       <c r="L295" s="67" t="inlineStr"/>
     </row>
@@ -16448,21 +13276,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H296" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I296" s="65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J296" s="23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="H296" s="65" t="inlineStr"/>
+      <c r="I296" s="65" t="inlineStr"/>
+      <c r="J296" s="23" t="inlineStr"/>
       <c r="K296" s="23" t="n"/>
       <c r="L296" s="67" t="inlineStr"/>
     </row>
@@ -16502,21 +13318,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H297" s="65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I297" s="65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J297" s="23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H297" s="65" t="inlineStr"/>
+      <c r="I297" s="65" t="inlineStr"/>
+      <c r="J297" s="23" t="inlineStr"/>
       <c r="K297" s="23" t="n"/>
       <c r="L297" s="67" t="inlineStr"/>
     </row>
